--- a/app/mevduat-kredi-faizleri/data/hoca-ile-borsa-faiz-takip-sablonu-guncel.xlsx
+++ b/app/mevduat-kredi-faizleri/data/hoca-ile-borsa-faiz-takip-sablonu-guncel.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projeler\hoca-ile-borsa\public\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projeler\hoca-ile-borsa\app\mevduat-kredi-faizleri\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{339FE24B-4581-4146-B23E-B98F473021A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA4D32E2-90F0-4ED1-8B1F-E35952CF845A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9060" yWindow="1680" windowWidth="29250" windowHeight="18705" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5085" yWindow="2175" windowWidth="29250" windowHeight="18705" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Mevduat" sheetId="1" r:id="rId1"/>
@@ -374,6 +374,9 @@
                 <c:pt idx="10">
                   <c:v>46139</c:v>
                 </c:pt>
+                <c:pt idx="11">
+                  <c:v>46140</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -417,7 +420,7 @@
                   <c:v>43.432916666666664</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0</c:v>
+                  <c:v>43.482083333333343</c:v>
                 </c:pt>
                 <c:pt idx="12">
                   <c:v>0</c:v>
@@ -1733,6 +1736,9 @@
                 <c:pt idx="10">
                   <c:v>46139</c:v>
                 </c:pt>
+                <c:pt idx="11">
+                  <c:v>46140</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1776,7 +1782,7 @@
                   <c:v>3.5499999999999994</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0</c:v>
+                  <c:v>3.5499999999999994</c:v>
                 </c:pt>
                 <c:pt idx="12">
                   <c:v>0</c:v>
@@ -3092,6 +3098,9 @@
                 <c:pt idx="10">
                   <c:v>46139</c:v>
                 </c:pt>
+                <c:pt idx="11">
+                  <c:v>46140</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3135,7 +3144,7 @@
                   <c:v>2.8077777777777779</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0</c:v>
+                  <c:v>2.8077777777777779</c:v>
                 </c:pt>
                 <c:pt idx="12">
                   <c:v>0</c:v>
@@ -4451,6 +4460,9 @@
                 <c:pt idx="10">
                   <c:v>46139</c:v>
                 </c:pt>
+                <c:pt idx="11">
+                  <c:v>46140</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -4494,7 +4506,7 @@
                   <c:v>3.31</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0</c:v>
+                  <c:v>3.31</c:v>
                 </c:pt>
                 <c:pt idx="12">
                   <c:v>0</c:v>
@@ -7188,34 +7200,84 @@
       </c>
     </row>
     <row r="16" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A16" s="2"/>
-      <c r="B16" s="3"/>
-      <c r="C16" s="3"/>
-      <c r="D16" s="3"/>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3"/>
-      <c r="G16" s="3"/>
-      <c r="H16" s="3"/>
-      <c r="I16" s="3"/>
-      <c r="J16" s="3"/>
-      <c r="K16" s="3"/>
-      <c r="L16" s="3"/>
-      <c r="M16" s="3"/>
-      <c r="N16" s="3"/>
-      <c r="O16" s="3"/>
-      <c r="P16" s="3"/>
-      <c r="Q16" s="3"/>
-      <c r="R16" s="3"/>
-      <c r="S16" s="3"/>
-      <c r="T16" s="3"/>
-      <c r="U16" s="3"/>
-      <c r="V16" s="3"/>
-      <c r="W16" s="3"/>
-      <c r="X16" s="3"/>
-      <c r="Y16" s="3"/>
-      <c r="Z16" s="4" t="str">
+      <c r="A16" s="2">
+        <v>46140</v>
+      </c>
+      <c r="B16" s="3">
+        <v>42</v>
+      </c>
+      <c r="C16" s="3">
+        <v>46</v>
+      </c>
+      <c r="D16" s="3">
+        <v>45</v>
+      </c>
+      <c r="E16" s="3">
+        <v>45</v>
+      </c>
+      <c r="F16" s="3">
+        <v>44.25</v>
+      </c>
+      <c r="G16" s="3">
+        <v>41.5</v>
+      </c>
+      <c r="H16" s="3">
+        <v>46</v>
+      </c>
+      <c r="I16" s="3">
+        <v>41.5</v>
+      </c>
+      <c r="J16" s="3">
+        <v>43</v>
+      </c>
+      <c r="K16" s="3">
+        <v>41</v>
+      </c>
+      <c r="L16" s="3">
+        <v>36</v>
+      </c>
+      <c r="M16" s="3">
+        <v>44</v>
+      </c>
+      <c r="N16" s="3">
+        <v>45</v>
+      </c>
+      <c r="O16" s="3">
+        <v>42.57</v>
+      </c>
+      <c r="P16" s="3">
+        <v>40</v>
+      </c>
+      <c r="Q16" s="3">
+        <v>45</v>
+      </c>
+      <c r="R16" s="3">
+        <v>45</v>
+      </c>
+      <c r="S16" s="3">
+        <v>45</v>
+      </c>
+      <c r="T16" s="3">
+        <v>45</v>
+      </c>
+      <c r="U16" s="3">
+        <v>43</v>
+      </c>
+      <c r="V16" s="3">
+        <v>43.5</v>
+      </c>
+      <c r="W16" s="3">
+        <v>42</v>
+      </c>
+      <c r="X16" s="3">
+        <v>47</v>
+      </c>
+      <c r="Y16" s="3">
+        <v>45.25</v>
+      </c>
+      <c r="Z16" s="4">
         <f t="shared" si="0"/>
-        <v/>
+        <v>43.482083333333343</v>
       </c>
     </row>
     <row r="17" spans="1:26" x14ac:dyDescent="0.25">
@@ -19679,29 +19741,69 @@
       </c>
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A16" s="2"/>
-      <c r="B16" s="3"/>
-      <c r="C16" s="3"/>
-      <c r="D16" s="3"/>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3"/>
-      <c r="G16" s="3"/>
-      <c r="H16" s="3"/>
-      <c r="I16" s="3"/>
-      <c r="J16" s="3"/>
-      <c r="K16" s="3"/>
-      <c r="L16" s="3"/>
-      <c r="M16" s="3"/>
-      <c r="N16" s="3"/>
-      <c r="O16" s="3"/>
-      <c r="P16" s="3"/>
-      <c r="Q16" s="3"/>
-      <c r="R16" s="3"/>
-      <c r="S16" s="3"/>
-      <c r="T16" s="3"/>
-      <c r="U16" s="4" t="str">
+      <c r="A16" s="2">
+        <v>46140</v>
+      </c>
+      <c r="B16" s="3">
+        <v>4.29</v>
+      </c>
+      <c r="C16" s="3">
+        <v>3.95</v>
+      </c>
+      <c r="D16" s="3">
+        <v>2.4900000000000002</v>
+      </c>
+      <c r="E16" s="3">
+        <v>3.8</v>
+      </c>
+      <c r="F16" s="3">
+        <v>4.3099999999999996</v>
+      </c>
+      <c r="G16" s="3">
+        <v>3.99</v>
+      </c>
+      <c r="H16" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="I16" s="3">
+        <v>3.39</v>
+      </c>
+      <c r="J16" s="3">
+        <v>3.09</v>
+      </c>
+      <c r="K16" s="3">
+        <v>3.99</v>
+      </c>
+      <c r="L16" s="3">
+        <v>2.39</v>
+      </c>
+      <c r="M16" s="3">
+        <v>3.79</v>
+      </c>
+      <c r="N16" s="3">
+        <v>3.79</v>
+      </c>
+      <c r="O16" s="3">
+        <v>3.8</v>
+      </c>
+      <c r="P16" s="3">
+        <v>3.89</v>
+      </c>
+      <c r="Q16" s="3">
+        <v>4.03</v>
+      </c>
+      <c r="R16" s="3">
+        <v>3.79</v>
+      </c>
+      <c r="S16" s="3">
+        <v>3.69</v>
+      </c>
+      <c r="T16" s="3">
+        <v>1.99</v>
+      </c>
+      <c r="U16" s="4">
         <f t="shared" si="0"/>
-        <v/>
+        <v>3.5499999999999994</v>
       </c>
     </row>
     <row r="17" spans="1:21" x14ac:dyDescent="0.25">
@@ -29915,19 +30017,39 @@
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A16" s="2"/>
-      <c r="B16" s="3"/>
-      <c r="C16" s="3"/>
-      <c r="D16" s="3"/>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3"/>
-      <c r="G16" s="3"/>
-      <c r="H16" s="3"/>
-      <c r="I16" s="3"/>
-      <c r="J16" s="3"/>
-      <c r="K16" s="4" t="str">
+      <c r="A16" s="2">
+        <v>46140</v>
+      </c>
+      <c r="B16" s="3">
+        <v>2.85</v>
+      </c>
+      <c r="C16" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="D16" s="3">
+        <v>2.67</v>
+      </c>
+      <c r="E16" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="F16" s="3">
+        <v>2.8</v>
+      </c>
+      <c r="G16" s="3">
+        <v>2.96</v>
+      </c>
+      <c r="H16" s="3">
+        <v>2.63</v>
+      </c>
+      <c r="I16" s="3">
+        <v>2.79</v>
+      </c>
+      <c r="J16" s="3">
+        <v>2.59</v>
+      </c>
+      <c r="K16" s="4">
         <f t="shared" si="0"/>
-        <v/>
+        <v>2.8077777777777779</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.25">
@@ -36439,20 +36561,42 @@
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A16" s="2"/>
-      <c r="B16" s="3"/>
-      <c r="C16" s="3"/>
-      <c r="D16" s="3"/>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3"/>
-      <c r="G16" s="3"/>
-      <c r="H16" s="3"/>
-      <c r="I16" s="3"/>
-      <c r="J16" s="3"/>
-      <c r="K16" s="3"/>
-      <c r="L16" s="4" t="str">
+      <c r="A16" s="2">
+        <v>46140</v>
+      </c>
+      <c r="B16" s="3">
+        <v>3.55</v>
+      </c>
+      <c r="C16" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="D16" s="3">
+        <v>3.15</v>
+      </c>
+      <c r="E16" s="3">
+        <v>3.35</v>
+      </c>
+      <c r="F16" s="3">
+        <v>3.43</v>
+      </c>
+      <c r="G16" s="3">
+        <v>3.69</v>
+      </c>
+      <c r="H16" s="3">
+        <v>3.11</v>
+      </c>
+      <c r="I16" s="3">
+        <v>3.29</v>
+      </c>
+      <c r="J16" s="3">
+        <v>3.55</v>
+      </c>
+      <c r="K16" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="L16" s="4">
         <f t="shared" si="0"/>
-        <v/>
+        <v>3.31</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">

--- a/app/mevduat-kredi-faizleri/data/hoca-ile-borsa-faiz-takip-sablonu-guncel.xlsx
+++ b/app/mevduat-kredi-faizleri/data/hoca-ile-borsa-faiz-takip-sablonu-guncel.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projeler\hoca-ile-borsa\app\mevduat-kredi-faizleri\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA4D32E2-90F0-4ED1-8B1F-E35952CF845A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D41AB2A-B838-48C7-B0D5-2E0245BBCDEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5085" yWindow="2175" windowWidth="29250" windowHeight="18705" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="18915" yWindow="5565" windowWidth="19665" windowHeight="15345" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Mevduat" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="39">
   <si>
     <t>Mevduat Günlük Oran Takip Şablonu</t>
   </si>
@@ -97,9 +97,6 @@
   </si>
   <si>
     <t>TEB - Türk Ekonomi Bankası</t>
-  </si>
-  <si>
-    <t>Şekerbank</t>
   </si>
   <si>
     <t>Yapı Kredi</t>
@@ -318,7 +315,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Mevduat!$Z$4</c:f>
+              <c:f>Mevduat!$Y$4</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -377,53 +374,56 @@
                 <c:pt idx="11">
                   <c:v>46140</c:v>
                 </c:pt>
+                <c:pt idx="12">
+                  <c:v>46141</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Mevduat!$Z$5:$Z$390</c:f>
+              <c:f>Mevduat!$Y$5:$Y$390</c:f>
               <c:numCache>
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="386"/>
                 <c:pt idx="0">
-                  <c:v>42.825416666666662</c:v>
+                  <c:v>43.078695652173913</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>42.825416666666662</c:v>
+                  <c:v>43.078695652173913</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>42.825416666666662</c:v>
+                  <c:v>43.078695652173913</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>43.248333333333335</c:v>
+                  <c:v>43.52</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>43.085416666666667</c:v>
+                  <c:v>43.35</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>43.127083333333331</c:v>
+                  <c:v>43.393478260869564</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>43.085416666666667</c:v>
+                  <c:v>43.35</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>43.078749999999992</c:v>
+                  <c:v>43.343043478260867</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>43.109999999999992</c:v>
+                  <c:v>43.375652173913046</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>43.443333333333328</c:v>
+                  <c:v>43.375652173913046</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>43.432916666666664</c:v>
+                  <c:v>43.364782608695648</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>43.482083333333343</c:v>
+                  <c:v>43.416086956521738</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0</c:v>
+                  <c:v>43.383478260869566</c:v>
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>0</c:v>
@@ -1739,6 +1739,9 @@
                 <c:pt idx="11">
                   <c:v>46140</c:v>
                 </c:pt>
+                <c:pt idx="12">
+                  <c:v>46141</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1785,7 +1788,7 @@
                   <c:v>3.5499999999999994</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0</c:v>
+                  <c:v>3.5657894736842097</c:v>
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>0</c:v>
@@ -3101,6 +3104,9 @@
                 <c:pt idx="11">
                   <c:v>46140</c:v>
                 </c:pt>
+                <c:pt idx="12">
+                  <c:v>46141</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3147,7 +3153,7 @@
                   <c:v>2.8077777777777779</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0</c:v>
+                  <c:v>2.8077777777777779</c:v>
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>0</c:v>
@@ -4463,6 +4469,9 @@
                 <c:pt idx="11">
                   <c:v>46140</c:v>
                 </c:pt>
+                <c:pt idx="12">
+                  <c:v>46141</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -4509,7 +4518,7 @@
                   <c:v>3.31</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0</c:v>
+                  <c:v>3.34</c:v>
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>0</c:v>
@@ -6160,15 +6169,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Z392"/>
+  <dimension ref="A1:Y392"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
-    <col min="2" max="25" width="18" customWidth="1"/>
-    <col min="26" max="26" width="16" customWidth="1"/>
+    <col min="2" max="24" width="18" customWidth="1"/>
+    <col min="25" max="25" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:25" ht="24" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
@@ -6196,9 +6205,8 @@
       <c r="W1" s="7"/>
       <c r="X1" s="7"/>
       <c r="Y1" s="7"/>
-      <c r="Z1" s="7"/>
-    </row>
-    <row r="2" spans="1:26" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:25" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
         <v>1</v>
       </c>
@@ -6226,9 +6234,8 @@
       <c r="W2" s="7"/>
       <c r="X2" s="7"/>
       <c r="Y2" s="7"/>
-      <c r="Z2" s="7"/>
-    </row>
-    <row r="4" spans="1:26" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4" spans="1:25" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
@@ -6304,11 +6311,8 @@
       <c r="Y4" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="Z4" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.25">
+    </row>
+    <row r="5" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>46123</v>
       </c>
@@ -6367,29 +6371,26 @@
         <v>37</v>
       </c>
       <c r="T5" s="3">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="U5" s="3">
-        <v>43</v>
+        <v>44.5</v>
       </c>
       <c r="V5" s="3">
-        <v>44.5</v>
+        <v>42</v>
       </c>
       <c r="W5" s="3">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="X5" s="3">
-        <v>46</v>
-      </c>
-      <c r="Y5" s="3">
         <v>45.25</v>
       </c>
-      <c r="Z5" s="4">
-        <f t="shared" ref="Z5:Z68" si="0">IF(COUNTA(B5:Y5)=0,"",AVERAGE(B5:Y5))</f>
-        <v>42.825416666666662</v>
-      </c>
-    </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y5" s="4">
+        <f>IF(COUNTA(B5:X5)=0,"",AVERAGE(B5:X5))</f>
+        <v>43.078695652173913</v>
+      </c>
+    </row>
+    <row r="6" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>46125</v>
       </c>
@@ -6448,29 +6449,26 @@
         <v>37</v>
       </c>
       <c r="T6" s="3">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="U6" s="3">
-        <v>43</v>
+        <v>44.5</v>
       </c>
       <c r="V6" s="3">
-        <v>44.5</v>
+        <v>42</v>
       </c>
       <c r="W6" s="3">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="X6" s="3">
-        <v>46</v>
-      </c>
-      <c r="Y6" s="3">
         <v>45.25</v>
       </c>
-      <c r="Z6" s="4">
-        <f t="shared" ref="Z6" si="1">IF(COUNTA(B6:Y6)=0,"",AVERAGE(B6:Y6))</f>
-        <v>42.825416666666662</v>
-      </c>
-    </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y6" s="4">
+        <f>IF(COUNTA(B6:X6)=0,"",AVERAGE(B6:X6))</f>
+        <v>43.078695652173913</v>
+      </c>
+    </row>
+    <row r="7" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>46126</v>
       </c>
@@ -6529,29 +6527,26 @@
         <v>37</v>
       </c>
       <c r="T7" s="3">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="U7" s="3">
-        <v>43</v>
+        <v>44.5</v>
       </c>
       <c r="V7" s="3">
-        <v>44.5</v>
+        <v>42</v>
       </c>
       <c r="W7" s="3">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="X7" s="3">
-        <v>46</v>
-      </c>
-      <c r="Y7" s="3">
         <v>45.25</v>
       </c>
-      <c r="Z7" s="4">
-        <f t="shared" si="0"/>
-        <v>42.825416666666662</v>
-      </c>
-    </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y7" s="4">
+        <f>IF(COUNTA(B7:X7)=0,"",AVERAGE(B7:X7))</f>
+        <v>43.078695652173913</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>46127</v>
       </c>
@@ -6610,29 +6605,26 @@
         <v>45</v>
       </c>
       <c r="T8" s="3">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="U8" s="3">
-        <v>43</v>
+        <v>44.5</v>
       </c>
       <c r="V8" s="3">
-        <v>44.5</v>
+        <v>42</v>
       </c>
       <c r="W8" s="3">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="X8" s="3">
-        <v>46</v>
-      </c>
-      <c r="Y8" s="3">
         <v>45.25</v>
       </c>
-      <c r="Z8" s="4">
-        <f t="shared" si="0"/>
-        <v>43.248333333333335</v>
-      </c>
-    </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y8" s="4">
+        <f>IF(COUNTA(B8:X8)=0,"",AVERAGE(B8:X8))</f>
+        <v>43.52</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>46128</v>
       </c>
@@ -6691,29 +6683,26 @@
         <v>45</v>
       </c>
       <c r="T9" s="3">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="U9" s="3">
-        <v>43</v>
+        <v>44.5</v>
       </c>
       <c r="V9" s="3">
-        <v>44.5</v>
+        <v>42</v>
       </c>
       <c r="W9" s="3">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="X9" s="3">
-        <v>46</v>
-      </c>
-      <c r="Y9" s="3">
         <v>45.25</v>
       </c>
-      <c r="Z9" s="4">
-        <f t="shared" si="0"/>
-        <v>43.085416666666667</v>
-      </c>
-    </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y9" s="4">
+        <f>IF(COUNTA(B9:X9)=0,"",AVERAGE(B9:X9))</f>
+        <v>43.35</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>46129</v>
       </c>
@@ -6772,29 +6761,26 @@
         <v>45</v>
       </c>
       <c r="T10" s="3">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="U10" s="3">
-        <v>43</v>
+        <v>44.5</v>
       </c>
       <c r="V10" s="3">
-        <v>44.5</v>
+        <v>42</v>
       </c>
       <c r="W10" s="3">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="X10" s="3">
-        <v>46</v>
-      </c>
-      <c r="Y10" s="3">
         <v>45.25</v>
       </c>
-      <c r="Z10" s="4">
-        <f t="shared" si="0"/>
-        <v>43.127083333333331</v>
-      </c>
-    </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y10" s="4">
+        <f>IF(COUNTA(B10:X10)=0,"",AVERAGE(B10:X10))</f>
+        <v>43.393478260869564</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <v>46132</v>
       </c>
@@ -6853,29 +6839,26 @@
         <v>45</v>
       </c>
       <c r="T11" s="3">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="U11" s="3">
-        <v>43</v>
+        <v>44.5</v>
       </c>
       <c r="V11" s="3">
-        <v>44.5</v>
+        <v>42</v>
       </c>
       <c r="W11" s="3">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="X11" s="3">
-        <v>46</v>
-      </c>
-      <c r="Y11" s="3">
         <v>45.25</v>
       </c>
-      <c r="Z11" s="4">
-        <f t="shared" si="0"/>
-        <v>43.085416666666667</v>
-      </c>
-    </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y11" s="4">
+        <f>IF(COUNTA(B11:X11)=0,"",AVERAGE(B11:X11))</f>
+        <v>43.35</v>
+      </c>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <v>46133</v>
       </c>
@@ -6934,29 +6917,26 @@
         <v>45</v>
       </c>
       <c r="T12" s="3">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="U12" s="3">
-        <v>43</v>
+        <v>44.25</v>
       </c>
       <c r="V12" s="3">
-        <v>44.25</v>
+        <v>42</v>
       </c>
       <c r="W12" s="3">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="X12" s="3">
-        <v>46</v>
-      </c>
-      <c r="Y12" s="3">
         <v>45.25</v>
       </c>
-      <c r="Z12" s="4">
-        <f t="shared" si="0"/>
-        <v>43.078749999999992</v>
-      </c>
-    </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y12" s="4">
+        <f>IF(COUNTA(B12:X12)=0,"",AVERAGE(B12:X12))</f>
+        <v>43.343043478260867</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
         <v>46134</v>
       </c>
@@ -7015,29 +6995,26 @@
         <v>45</v>
       </c>
       <c r="T13" s="3">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="U13" s="3">
-        <v>43</v>
+        <v>43.75</v>
       </c>
       <c r="V13" s="3">
-        <v>43.75</v>
+        <v>42</v>
       </c>
       <c r="W13" s="3">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="X13" s="3">
-        <v>46</v>
-      </c>
-      <c r="Y13" s="3">
         <v>45.25</v>
       </c>
-      <c r="Z13" s="4">
-        <f t="shared" si="0"/>
-        <v>43.109999999999992</v>
-      </c>
-    </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y13" s="4">
+        <f>IF(COUNTA(B13:X13)=0,"",AVERAGE(B13:X13))</f>
+        <v>43.375652173913046</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
         <v>46136</v>
       </c>
@@ -7096,29 +7073,26 @@
         <v>45</v>
       </c>
       <c r="T14" s="3">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="U14" s="3">
-        <v>43</v>
+        <v>43.75</v>
       </c>
       <c r="V14" s="3">
-        <v>43.75</v>
+        <v>42</v>
       </c>
       <c r="W14" s="3">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="X14" s="3">
-        <v>46</v>
-      </c>
-      <c r="Y14" s="3">
         <v>45.25</v>
       </c>
-      <c r="Z14" s="4">
-        <f t="shared" si="0"/>
-        <v>43.443333333333328</v>
-      </c>
-    </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y14" s="4">
+        <f>IF(COUNTA(B14:X14)=0,"",AVERAGE(B14:X14))</f>
+        <v>43.375652173913046</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
         <v>46139</v>
       </c>
@@ -7177,29 +7151,26 @@
         <v>45</v>
       </c>
       <c r="T15" s="3">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="U15" s="3">
-        <v>43</v>
+        <v>43.5</v>
       </c>
       <c r="V15" s="3">
-        <v>43.5</v>
+        <v>42</v>
       </c>
       <c r="W15" s="3">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="X15" s="3">
-        <v>46</v>
-      </c>
-      <c r="Y15" s="3">
         <v>45.25</v>
       </c>
-      <c r="Z15" s="4">
-        <f t="shared" si="0"/>
-        <v>43.432916666666664</v>
-      </c>
-    </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y15" s="4">
+        <f>IF(COUNTA(B15:X15)=0,"",AVERAGE(B15:X15))</f>
+        <v>43.364782608695648</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
         <v>46140</v>
       </c>
@@ -7258,60 +7229,104 @@
         <v>45</v>
       </c>
       <c r="T16" s="3">
+        <v>43</v>
+      </c>
+      <c r="U16" s="3">
+        <v>43.5</v>
+      </c>
+      <c r="V16" s="3">
+        <v>42</v>
+      </c>
+      <c r="W16" s="3">
+        <v>47</v>
+      </c>
+      <c r="X16" s="3">
+        <v>45.25</v>
+      </c>
+      <c r="Y16" s="4">
+        <f>IF(COUNTA(B16:X16)=0,"",AVERAGE(B16:X16))</f>
+        <v>43.416086956521738</v>
+      </c>
+    </row>
+    <row r="17" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A17" s="2">
+        <v>46141</v>
+      </c>
+      <c r="B17" s="3">
+        <v>42</v>
+      </c>
+      <c r="C17" s="3">
+        <v>46</v>
+      </c>
+      <c r="D17" s="3">
         <v>45</v>
       </c>
-      <c r="U16" s="3">
+      <c r="E17" s="3">
+        <v>45</v>
+      </c>
+      <c r="F17" s="3">
+        <v>43.5</v>
+      </c>
+      <c r="G17" s="3">
+        <v>41.5</v>
+      </c>
+      <c r="H17" s="3">
+        <v>46</v>
+      </c>
+      <c r="I17" s="3">
+        <v>41.5</v>
+      </c>
+      <c r="J17" s="3">
         <v>43</v>
       </c>
-      <c r="V16" s="3">
+      <c r="K17" s="3">
+        <v>41</v>
+      </c>
+      <c r="L17" s="3">
+        <v>36</v>
+      </c>
+      <c r="M17" s="3">
+        <v>44</v>
+      </c>
+      <c r="N17" s="3">
+        <v>45</v>
+      </c>
+      <c r="O17" s="3">
+        <v>42.57</v>
+      </c>
+      <c r="P17" s="3">
+        <v>40</v>
+      </c>
+      <c r="Q17" s="3">
+        <v>45</v>
+      </c>
+      <c r="R17" s="3">
+        <v>45</v>
+      </c>
+      <c r="S17" s="3">
+        <v>45</v>
+      </c>
+      <c r="T17" s="3">
+        <v>43</v>
+      </c>
+      <c r="U17" s="3">
         <v>43.5</v>
       </c>
-      <c r="W16" s="3">
+      <c r="V17" s="3">
         <v>42</v>
       </c>
-      <c r="X16" s="3">
+      <c r="W17" s="3">
         <v>47</v>
       </c>
-      <c r="Y16" s="3">
+      <c r="X17" s="3">
         <v>45.25</v>
       </c>
-      <c r="Z16" s="4">
-        <f t="shared" si="0"/>
-        <v>43.482083333333343</v>
-      </c>
-    </row>
-    <row r="17" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A17" s="2"/>
-      <c r="B17" s="3"/>
-      <c r="C17" s="3"/>
-      <c r="D17" s="3"/>
-      <c r="E17" s="3"/>
-      <c r="F17" s="3"/>
-      <c r="G17" s="3"/>
-      <c r="H17" s="3"/>
-      <c r="I17" s="3"/>
-      <c r="J17" s="3"/>
-      <c r="K17" s="3"/>
-      <c r="L17" s="3"/>
-      <c r="M17" s="3"/>
-      <c r="N17" s="3"/>
-      <c r="O17" s="3"/>
-      <c r="P17" s="3"/>
-      <c r="Q17" s="3"/>
-      <c r="R17" s="3"/>
-      <c r="S17" s="3"/>
-      <c r="T17" s="3"/>
-      <c r="U17" s="3"/>
-      <c r="V17" s="3"/>
-      <c r="W17" s="3"/>
-      <c r="X17" s="3"/>
-      <c r="Y17" s="3"/>
-      <c r="Z17" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="18" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y17" s="4">
+        <f>IF(COUNTA(B17:X17)=0,"",AVERAGE(B17:X17))</f>
+        <v>43.383478260869566</v>
+      </c>
+    </row>
+    <row r="18" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A18" s="2"/>
       <c r="B18" s="3"/>
       <c r="C18" s="3"/>
@@ -7336,13 +7351,12 @@
       <c r="V18" s="3"/>
       <c r="W18" s="3"/>
       <c r="X18" s="3"/>
-      <c r="Y18" s="3"/>
-      <c r="Z18" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="19" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y18" s="4" t="str">
+        <f>IF(COUNTA(B18:X18)=0,"",AVERAGE(B18:X18))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A19" s="2"/>
       <c r="B19" s="3"/>
       <c r="C19" s="3"/>
@@ -7367,13 +7381,12 @@
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
-      <c r="Y19" s="3"/>
-      <c r="Z19" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="20" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y19" s="4" t="str">
+        <f>IF(COUNTA(B19:X19)=0,"",AVERAGE(B19:X19))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A20" s="2"/>
       <c r="B20" s="3"/>
       <c r="C20" s="3"/>
@@ -7398,13 +7411,12 @@
       <c r="V20" s="3"/>
       <c r="W20" s="3"/>
       <c r="X20" s="3"/>
-      <c r="Y20" s="3"/>
-      <c r="Z20" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="21" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y20" s="4" t="str">
+        <f>IF(COUNTA(B20:X20)=0,"",AVERAGE(B20:X20))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A21" s="2"/>
       <c r="B21" s="3"/>
       <c r="C21" s="3"/>
@@ -7429,13 +7441,12 @@
       <c r="V21" s="3"/>
       <c r="W21" s="3"/>
       <c r="X21" s="3"/>
-      <c r="Y21" s="3"/>
-      <c r="Z21" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="22" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y21" s="4" t="str">
+        <f>IF(COUNTA(B21:X21)=0,"",AVERAGE(B21:X21))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A22" s="2"/>
       <c r="B22" s="3"/>
       <c r="C22" s="3"/>
@@ -7460,13 +7471,12 @@
       <c r="V22" s="3"/>
       <c r="W22" s="3"/>
       <c r="X22" s="3"/>
-      <c r="Y22" s="3"/>
-      <c r="Z22" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="23" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y22" s="4" t="str">
+        <f>IF(COUNTA(B22:X22)=0,"",AVERAGE(B22:X22))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A23" s="2"/>
       <c r="B23" s="3"/>
       <c r="C23" s="3"/>
@@ -7491,13 +7501,12 @@
       <c r="V23" s="3"/>
       <c r="W23" s="3"/>
       <c r="X23" s="3"/>
-      <c r="Y23" s="3"/>
-      <c r="Z23" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="24" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y23" s="4" t="str">
+        <f>IF(COUNTA(B23:X23)=0,"",AVERAGE(B23:X23))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A24" s="2"/>
       <c r="B24" s="3"/>
       <c r="C24" s="3"/>
@@ -7522,13 +7531,12 @@
       <c r="V24" s="3"/>
       <c r="W24" s="3"/>
       <c r="X24" s="3"/>
-      <c r="Y24" s="3"/>
-      <c r="Z24" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="25" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y24" s="4" t="str">
+        <f>IF(COUNTA(B24:X24)=0,"",AVERAGE(B24:X24))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A25" s="2"/>
       <c r="B25" s="3"/>
       <c r="C25" s="3"/>
@@ -7553,13 +7561,12 @@
       <c r="V25" s="3"/>
       <c r="W25" s="3"/>
       <c r="X25" s="3"/>
-      <c r="Y25" s="3"/>
-      <c r="Z25" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="26" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y25" s="4" t="str">
+        <f>IF(COUNTA(B25:X25)=0,"",AVERAGE(B25:X25))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A26" s="2"/>
       <c r="B26" s="3"/>
       <c r="C26" s="3"/>
@@ -7584,13 +7591,12 @@
       <c r="V26" s="3"/>
       <c r="W26" s="3"/>
       <c r="X26" s="3"/>
-      <c r="Y26" s="3"/>
-      <c r="Z26" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="27" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y26" s="4" t="str">
+        <f>IF(COUNTA(B26:X26)=0,"",AVERAGE(B26:X26))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A27" s="2"/>
       <c r="B27" s="3"/>
       <c r="C27" s="3"/>
@@ -7615,13 +7621,12 @@
       <c r="V27" s="3"/>
       <c r="W27" s="3"/>
       <c r="X27" s="3"/>
-      <c r="Y27" s="3"/>
-      <c r="Z27" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="28" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y27" s="4" t="str">
+        <f>IF(COUNTA(B27:X27)=0,"",AVERAGE(B27:X27))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A28" s="2"/>
       <c r="B28" s="3"/>
       <c r="C28" s="3"/>
@@ -7646,13 +7651,12 @@
       <c r="V28" s="3"/>
       <c r="W28" s="3"/>
       <c r="X28" s="3"/>
-      <c r="Y28" s="3"/>
-      <c r="Z28" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="29" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y28" s="4" t="str">
+        <f>IF(COUNTA(B28:X28)=0,"",AVERAGE(B28:X28))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A29" s="2"/>
       <c r="B29" s="3"/>
       <c r="C29" s="3"/>
@@ -7677,13 +7681,12 @@
       <c r="V29" s="3"/>
       <c r="W29" s="3"/>
       <c r="X29" s="3"/>
-      <c r="Y29" s="3"/>
-      <c r="Z29" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="30" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y29" s="4" t="str">
+        <f>IF(COUNTA(B29:X29)=0,"",AVERAGE(B29:X29))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A30" s="2"/>
       <c r="B30" s="3"/>
       <c r="C30" s="3"/>
@@ -7708,13 +7711,12 @@
       <c r="V30" s="3"/>
       <c r="W30" s="3"/>
       <c r="X30" s="3"/>
-      <c r="Y30" s="3"/>
-      <c r="Z30" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="31" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y30" s="4" t="str">
+        <f>IF(COUNTA(B30:X30)=0,"",AVERAGE(B30:X30))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A31" s="2"/>
       <c r="B31" s="3"/>
       <c r="C31" s="3"/>
@@ -7739,13 +7741,12 @@
       <c r="V31" s="3"/>
       <c r="W31" s="3"/>
       <c r="X31" s="3"/>
-      <c r="Y31" s="3"/>
-      <c r="Z31" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="32" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y31" s="4" t="str">
+        <f>IF(COUNTA(B31:X31)=0,"",AVERAGE(B31:X31))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A32" s="2"/>
       <c r="B32" s="3"/>
       <c r="C32" s="3"/>
@@ -7770,13 +7771,12 @@
       <c r="V32" s="3"/>
       <c r="W32" s="3"/>
       <c r="X32" s="3"/>
-      <c r="Y32" s="3"/>
-      <c r="Z32" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="33" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y32" s="4" t="str">
+        <f>IF(COUNTA(B32:X32)=0,"",AVERAGE(B32:X32))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A33" s="2"/>
       <c r="B33" s="3"/>
       <c r="C33" s="3"/>
@@ -7801,13 +7801,12 @@
       <c r="V33" s="3"/>
       <c r="W33" s="3"/>
       <c r="X33" s="3"/>
-      <c r="Y33" s="3"/>
-      <c r="Z33" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="34" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y33" s="4" t="str">
+        <f>IF(COUNTA(B33:X33)=0,"",AVERAGE(B33:X33))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A34" s="2"/>
       <c r="B34" s="3"/>
       <c r="C34" s="3"/>
@@ -7832,13 +7831,12 @@
       <c r="V34" s="3"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
-      <c r="Y34" s="3"/>
-      <c r="Z34" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="35" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y34" s="4" t="str">
+        <f>IF(COUNTA(B34:X34)=0,"",AVERAGE(B34:X34))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A35" s="2"/>
       <c r="B35" s="3"/>
       <c r="C35" s="3"/>
@@ -7863,13 +7861,12 @@
       <c r="V35" s="3"/>
       <c r="W35" s="3"/>
       <c r="X35" s="3"/>
-      <c r="Y35" s="3"/>
-      <c r="Z35" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="36" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y35" s="4" t="str">
+        <f>IF(COUNTA(B35:X35)=0,"",AVERAGE(B35:X35))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A36" s="2"/>
       <c r="B36" s="3"/>
       <c r="C36" s="3"/>
@@ -7894,13 +7891,12 @@
       <c r="V36" s="3"/>
       <c r="W36" s="3"/>
       <c r="X36" s="3"/>
-      <c r="Y36" s="3"/>
-      <c r="Z36" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="37" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y36" s="4" t="str">
+        <f>IF(COUNTA(B36:X36)=0,"",AVERAGE(B36:X36))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A37" s="2"/>
       <c r="B37" s="3"/>
       <c r="C37" s="3"/>
@@ -7925,13 +7921,12 @@
       <c r="V37" s="3"/>
       <c r="W37" s="3"/>
       <c r="X37" s="3"/>
-      <c r="Y37" s="3"/>
-      <c r="Z37" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="38" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y37" s="4" t="str">
+        <f>IF(COUNTA(B37:X37)=0,"",AVERAGE(B37:X37))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A38" s="2"/>
       <c r="B38" s="3"/>
       <c r="C38" s="3"/>
@@ -7956,13 +7951,12 @@
       <c r="V38" s="3"/>
       <c r="W38" s="3"/>
       <c r="X38" s="3"/>
-      <c r="Y38" s="3"/>
-      <c r="Z38" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="39" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y38" s="4" t="str">
+        <f>IF(COUNTA(B38:X38)=0,"",AVERAGE(B38:X38))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A39" s="2"/>
       <c r="B39" s="3"/>
       <c r="C39" s="3"/>
@@ -7987,13 +7981,12 @@
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
-      <c r="Y39" s="3"/>
-      <c r="Z39" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="40" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y39" s="4" t="str">
+        <f>IF(COUNTA(B39:X39)=0,"",AVERAGE(B39:X39))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A40" s="2"/>
       <c r="B40" s="3"/>
       <c r="C40" s="3"/>
@@ -8018,13 +8011,12 @@
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
-      <c r="Y40" s="3"/>
-      <c r="Z40" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="41" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y40" s="4" t="str">
+        <f>IF(COUNTA(B40:X40)=0,"",AVERAGE(B40:X40))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A41" s="2"/>
       <c r="B41" s="3"/>
       <c r="C41" s="3"/>
@@ -8049,13 +8041,12 @@
       <c r="V41" s="3"/>
       <c r="W41" s="3"/>
       <c r="X41" s="3"/>
-      <c r="Y41" s="3"/>
-      <c r="Z41" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="42" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y41" s="4" t="str">
+        <f>IF(COUNTA(B41:X41)=0,"",AVERAGE(B41:X41))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A42" s="2"/>
       <c r="B42" s="3"/>
       <c r="C42" s="3"/>
@@ -8080,13 +8071,12 @@
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
-      <c r="Y42" s="3"/>
-      <c r="Z42" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="43" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y42" s="4" t="str">
+        <f>IF(COUNTA(B42:X42)=0,"",AVERAGE(B42:X42))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A43" s="2"/>
       <c r="B43" s="3"/>
       <c r="C43" s="3"/>
@@ -8111,13 +8101,12 @@
       <c r="V43" s="3"/>
       <c r="W43" s="3"/>
       <c r="X43" s="3"/>
-      <c r="Y43" s="3"/>
-      <c r="Z43" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="44" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y43" s="4" t="str">
+        <f>IF(COUNTA(B43:X43)=0,"",AVERAGE(B43:X43))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A44" s="2"/>
       <c r="B44" s="3"/>
       <c r="C44" s="3"/>
@@ -8142,13 +8131,12 @@
       <c r="V44" s="3"/>
       <c r="W44" s="3"/>
       <c r="X44" s="3"/>
-      <c r="Y44" s="3"/>
-      <c r="Z44" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="45" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y44" s="4" t="str">
+        <f>IF(COUNTA(B44:X44)=0,"",AVERAGE(B44:X44))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A45" s="2"/>
       <c r="B45" s="3"/>
       <c r="C45" s="3"/>
@@ -8173,13 +8161,12 @@
       <c r="V45" s="3"/>
       <c r="W45" s="3"/>
       <c r="X45" s="3"/>
-      <c r="Y45" s="3"/>
-      <c r="Z45" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="46" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y45" s="4" t="str">
+        <f>IF(COUNTA(B45:X45)=0,"",AVERAGE(B45:X45))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A46" s="2"/>
       <c r="B46" s="3"/>
       <c r="C46" s="3"/>
@@ -8204,13 +8191,12 @@
       <c r="V46" s="3"/>
       <c r="W46" s="3"/>
       <c r="X46" s="3"/>
-      <c r="Y46" s="3"/>
-      <c r="Z46" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="47" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y46" s="4" t="str">
+        <f>IF(COUNTA(B46:X46)=0,"",AVERAGE(B46:X46))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A47" s="2"/>
       <c r="B47" s="3"/>
       <c r="C47" s="3"/>
@@ -8235,13 +8221,12 @@
       <c r="V47" s="3"/>
       <c r="W47" s="3"/>
       <c r="X47" s="3"/>
-      <c r="Y47" s="3"/>
-      <c r="Z47" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="48" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y47" s="4" t="str">
+        <f>IF(COUNTA(B47:X47)=0,"",AVERAGE(B47:X47))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A48" s="2"/>
       <c r="B48" s="3"/>
       <c r="C48" s="3"/>
@@ -8266,13 +8251,12 @@
       <c r="V48" s="3"/>
       <c r="W48" s="3"/>
       <c r="X48" s="3"/>
-      <c r="Y48" s="3"/>
-      <c r="Z48" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="49" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y48" s="4" t="str">
+        <f>IF(COUNTA(B48:X48)=0,"",AVERAGE(B48:X48))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A49" s="2"/>
       <c r="B49" s="3"/>
       <c r="C49" s="3"/>
@@ -8297,13 +8281,12 @@
       <c r="V49" s="3"/>
       <c r="W49" s="3"/>
       <c r="X49" s="3"/>
-      <c r="Y49" s="3"/>
-      <c r="Z49" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="50" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y49" s="4" t="str">
+        <f>IF(COUNTA(B49:X49)=0,"",AVERAGE(B49:X49))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A50" s="2"/>
       <c r="B50" s="3"/>
       <c r="C50" s="3"/>
@@ -8328,13 +8311,12 @@
       <c r="V50" s="3"/>
       <c r="W50" s="3"/>
       <c r="X50" s="3"/>
-      <c r="Y50" s="3"/>
-      <c r="Z50" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="51" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y50" s="4" t="str">
+        <f>IF(COUNTA(B50:X50)=0,"",AVERAGE(B50:X50))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A51" s="2"/>
       <c r="B51" s="3"/>
       <c r="C51" s="3"/>
@@ -8359,13 +8341,12 @@
       <c r="V51" s="3"/>
       <c r="W51" s="3"/>
       <c r="X51" s="3"/>
-      <c r="Y51" s="3"/>
-      <c r="Z51" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="52" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y51" s="4" t="str">
+        <f>IF(COUNTA(B51:X51)=0,"",AVERAGE(B51:X51))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A52" s="2"/>
       <c r="B52" s="3"/>
       <c r="C52" s="3"/>
@@ -8390,13 +8371,12 @@
       <c r="V52" s="3"/>
       <c r="W52" s="3"/>
       <c r="X52" s="3"/>
-      <c r="Y52" s="3"/>
-      <c r="Z52" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="53" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y52" s="4" t="str">
+        <f>IF(COUNTA(B52:X52)=0,"",AVERAGE(B52:X52))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A53" s="2"/>
       <c r="B53" s="3"/>
       <c r="C53" s="3"/>
@@ -8421,13 +8401,12 @@
       <c r="V53" s="3"/>
       <c r="W53" s="3"/>
       <c r="X53" s="3"/>
-      <c r="Y53" s="3"/>
-      <c r="Z53" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="54" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y53" s="4" t="str">
+        <f>IF(COUNTA(B53:X53)=0,"",AVERAGE(B53:X53))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A54" s="2"/>
       <c r="B54" s="3"/>
       <c r="C54" s="3"/>
@@ -8452,13 +8431,12 @@
       <c r="V54" s="3"/>
       <c r="W54" s="3"/>
       <c r="X54" s="3"/>
-      <c r="Y54" s="3"/>
-      <c r="Z54" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="55" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y54" s="4" t="str">
+        <f>IF(COUNTA(B54:X54)=0,"",AVERAGE(B54:X54))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A55" s="2"/>
       <c r="B55" s="3"/>
       <c r="C55" s="3"/>
@@ -8483,13 +8461,12 @@
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
-      <c r="Y55" s="3"/>
-      <c r="Z55" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="56" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y55" s="4" t="str">
+        <f>IF(COUNTA(B55:X55)=0,"",AVERAGE(B55:X55))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A56" s="2"/>
       <c r="B56" s="3"/>
       <c r="C56" s="3"/>
@@ -8514,13 +8491,12 @@
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
-      <c r="Y56" s="3"/>
-      <c r="Z56" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="57" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y56" s="4" t="str">
+        <f>IF(COUNTA(B56:X56)=0,"",AVERAGE(B56:X56))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A57" s="2"/>
       <c r="B57" s="3"/>
       <c r="C57" s="3"/>
@@ -8545,13 +8521,12 @@
       <c r="V57" s="3"/>
       <c r="W57" s="3"/>
       <c r="X57" s="3"/>
-      <c r="Y57" s="3"/>
-      <c r="Z57" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="58" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y57" s="4" t="str">
+        <f>IF(COUNTA(B57:X57)=0,"",AVERAGE(B57:X57))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A58" s="2"/>
       <c r="B58" s="3"/>
       <c r="C58" s="3"/>
@@ -8576,13 +8551,12 @@
       <c r="V58" s="3"/>
       <c r="W58" s="3"/>
       <c r="X58" s="3"/>
-      <c r="Y58" s="3"/>
-      <c r="Z58" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="59" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y58" s="4" t="str">
+        <f>IF(COUNTA(B58:X58)=0,"",AVERAGE(B58:X58))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A59" s="2"/>
       <c r="B59" s="3"/>
       <c r="C59" s="3"/>
@@ -8607,13 +8581,12 @@
       <c r="V59" s="3"/>
       <c r="W59" s="3"/>
       <c r="X59" s="3"/>
-      <c r="Y59" s="3"/>
-      <c r="Z59" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="60" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y59" s="4" t="str">
+        <f>IF(COUNTA(B59:X59)=0,"",AVERAGE(B59:X59))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A60" s="2"/>
       <c r="B60" s="3"/>
       <c r="C60" s="3"/>
@@ -8638,13 +8611,12 @@
       <c r="V60" s="3"/>
       <c r="W60" s="3"/>
       <c r="X60" s="3"/>
-      <c r="Y60" s="3"/>
-      <c r="Z60" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="61" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y60" s="4" t="str">
+        <f>IF(COUNTA(B60:X60)=0,"",AVERAGE(B60:X60))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="61" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A61" s="2"/>
       <c r="B61" s="3"/>
       <c r="C61" s="3"/>
@@ -8669,13 +8641,12 @@
       <c r="V61" s="3"/>
       <c r="W61" s="3"/>
       <c r="X61" s="3"/>
-      <c r="Y61" s="3"/>
-      <c r="Z61" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="62" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y61" s="4" t="str">
+        <f>IF(COUNTA(B61:X61)=0,"",AVERAGE(B61:X61))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="62" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A62" s="2"/>
       <c r="B62" s="3"/>
       <c r="C62" s="3"/>
@@ -8700,13 +8671,12 @@
       <c r="V62" s="3"/>
       <c r="W62" s="3"/>
       <c r="X62" s="3"/>
-      <c r="Y62" s="3"/>
-      <c r="Z62" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="63" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y62" s="4" t="str">
+        <f>IF(COUNTA(B62:X62)=0,"",AVERAGE(B62:X62))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="63" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A63" s="2"/>
       <c r="B63" s="3"/>
       <c r="C63" s="3"/>
@@ -8731,13 +8701,12 @@
       <c r="V63" s="3"/>
       <c r="W63" s="3"/>
       <c r="X63" s="3"/>
-      <c r="Y63" s="3"/>
-      <c r="Z63" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="64" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y63" s="4" t="str">
+        <f>IF(COUNTA(B63:X63)=0,"",AVERAGE(B63:X63))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="64" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A64" s="2"/>
       <c r="B64" s="3"/>
       <c r="C64" s="3"/>
@@ -8762,13 +8731,12 @@
       <c r="V64" s="3"/>
       <c r="W64" s="3"/>
       <c r="X64" s="3"/>
-      <c r="Y64" s="3"/>
-      <c r="Z64" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="65" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y64" s="4" t="str">
+        <f>IF(COUNTA(B64:X64)=0,"",AVERAGE(B64:X64))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="65" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A65" s="2"/>
       <c r="B65" s="3"/>
       <c r="C65" s="3"/>
@@ -8793,13 +8761,12 @@
       <c r="V65" s="3"/>
       <c r="W65" s="3"/>
       <c r="X65" s="3"/>
-      <c r="Y65" s="3"/>
-      <c r="Z65" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="66" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y65" s="4" t="str">
+        <f>IF(COUNTA(B65:X65)=0,"",AVERAGE(B65:X65))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="66" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A66" s="2"/>
       <c r="B66" s="3"/>
       <c r="C66" s="3"/>
@@ -8824,13 +8791,12 @@
       <c r="V66" s="3"/>
       <c r="W66" s="3"/>
       <c r="X66" s="3"/>
-      <c r="Y66" s="3"/>
-      <c r="Z66" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="67" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y66" s="4" t="str">
+        <f>IF(COUNTA(B66:X66)=0,"",AVERAGE(B66:X66))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="67" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A67" s="2"/>
       <c r="B67" s="3"/>
       <c r="C67" s="3"/>
@@ -8855,13 +8821,12 @@
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
-      <c r="Y67" s="3"/>
-      <c r="Z67" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="68" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y67" s="4" t="str">
+        <f>IF(COUNTA(B67:X67)=0,"",AVERAGE(B67:X67))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="68" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A68" s="2"/>
       <c r="B68" s="3"/>
       <c r="C68" s="3"/>
@@ -8886,13 +8851,12 @@
       <c r="V68" s="3"/>
       <c r="W68" s="3"/>
       <c r="X68" s="3"/>
-      <c r="Y68" s="3"/>
-      <c r="Z68" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="69" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y68" s="4" t="str">
+        <f>IF(COUNTA(B68:X68)=0,"",AVERAGE(B68:X68))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="69" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A69" s="2"/>
       <c r="B69" s="3"/>
       <c r="C69" s="3"/>
@@ -8917,13 +8881,12 @@
       <c r="V69" s="3"/>
       <c r="W69" s="3"/>
       <c r="X69" s="3"/>
-      <c r="Y69" s="3"/>
-      <c r="Z69" s="4" t="str">
-        <f t="shared" ref="Z69:Z132" si="2">IF(COUNTA(B69:Y69)=0,"",AVERAGE(B69:Y69))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="70" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y69" s="4" t="str">
+        <f>IF(COUNTA(B69:X69)=0,"",AVERAGE(B69:X69))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="70" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A70" s="2"/>
       <c r="B70" s="3"/>
       <c r="C70" s="3"/>
@@ -8948,13 +8911,12 @@
       <c r="V70" s="3"/>
       <c r="W70" s="3"/>
       <c r="X70" s="3"/>
-      <c r="Y70" s="3"/>
-      <c r="Z70" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="71" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y70" s="4" t="str">
+        <f>IF(COUNTA(B70:X70)=0,"",AVERAGE(B70:X70))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="71" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A71" s="2"/>
       <c r="B71" s="3"/>
       <c r="C71" s="3"/>
@@ -8979,13 +8941,12 @@
       <c r="V71" s="3"/>
       <c r="W71" s="3"/>
       <c r="X71" s="3"/>
-      <c r="Y71" s="3"/>
-      <c r="Z71" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="72" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y71" s="4" t="str">
+        <f>IF(COUNTA(B71:X71)=0,"",AVERAGE(B71:X71))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="72" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A72" s="2"/>
       <c r="B72" s="3"/>
       <c r="C72" s="3"/>
@@ -9010,13 +8971,12 @@
       <c r="V72" s="3"/>
       <c r="W72" s="3"/>
       <c r="X72" s="3"/>
-      <c r="Y72" s="3"/>
-      <c r="Z72" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="73" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y72" s="4" t="str">
+        <f>IF(COUNTA(B72:X72)=0,"",AVERAGE(B72:X72))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="73" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A73" s="2"/>
       <c r="B73" s="3"/>
       <c r="C73" s="3"/>
@@ -9041,13 +9001,12 @@
       <c r="V73" s="3"/>
       <c r="W73" s="3"/>
       <c r="X73" s="3"/>
-      <c r="Y73" s="3"/>
-      <c r="Z73" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="74" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y73" s="4" t="str">
+        <f>IF(COUNTA(B73:X73)=0,"",AVERAGE(B73:X73))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="74" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A74" s="2"/>
       <c r="B74" s="3"/>
       <c r="C74" s="3"/>
@@ -9072,13 +9031,12 @@
       <c r="V74" s="3"/>
       <c r="W74" s="3"/>
       <c r="X74" s="3"/>
-      <c r="Y74" s="3"/>
-      <c r="Z74" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="75" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y74" s="4" t="str">
+        <f>IF(COUNTA(B74:X74)=0,"",AVERAGE(B74:X74))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="75" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A75" s="2"/>
       <c r="B75" s="3"/>
       <c r="C75" s="3"/>
@@ -9103,13 +9061,12 @@
       <c r="V75" s="3"/>
       <c r="W75" s="3"/>
       <c r="X75" s="3"/>
-      <c r="Y75" s="3"/>
-      <c r="Z75" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="76" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y75" s="4" t="str">
+        <f>IF(COUNTA(B75:X75)=0,"",AVERAGE(B75:X75))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="76" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A76" s="2"/>
       <c r="B76" s="3"/>
       <c r="C76" s="3"/>
@@ -9134,13 +9091,12 @@
       <c r="V76" s="3"/>
       <c r="W76" s="3"/>
       <c r="X76" s="3"/>
-      <c r="Y76" s="3"/>
-      <c r="Z76" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="77" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y76" s="4" t="str">
+        <f>IF(COUNTA(B76:X76)=0,"",AVERAGE(B76:X76))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="77" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A77" s="2"/>
       <c r="B77" s="3"/>
       <c r="C77" s="3"/>
@@ -9165,13 +9121,12 @@
       <c r="V77" s="3"/>
       <c r="W77" s="3"/>
       <c r="X77" s="3"/>
-      <c r="Y77" s="3"/>
-      <c r="Z77" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="78" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y77" s="4" t="str">
+        <f>IF(COUNTA(B77:X77)=0,"",AVERAGE(B77:X77))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="78" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A78" s="2"/>
       <c r="B78" s="3"/>
       <c r="C78" s="3"/>
@@ -9196,13 +9151,12 @@
       <c r="V78" s="3"/>
       <c r="W78" s="3"/>
       <c r="X78" s="3"/>
-      <c r="Y78" s="3"/>
-      <c r="Z78" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="79" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y78" s="4" t="str">
+        <f>IF(COUNTA(B78:X78)=0,"",AVERAGE(B78:X78))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="79" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A79" s="2"/>
       <c r="B79" s="3"/>
       <c r="C79" s="3"/>
@@ -9227,13 +9181,12 @@
       <c r="V79" s="3"/>
       <c r="W79" s="3"/>
       <c r="X79" s="3"/>
-      <c r="Y79" s="3"/>
-      <c r="Z79" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="80" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y79" s="4" t="str">
+        <f>IF(COUNTA(B79:X79)=0,"",AVERAGE(B79:X79))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="80" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A80" s="2"/>
       <c r="B80" s="3"/>
       <c r="C80" s="3"/>
@@ -9258,13 +9211,12 @@
       <c r="V80" s="3"/>
       <c r="W80" s="3"/>
       <c r="X80" s="3"/>
-      <c r="Y80" s="3"/>
-      <c r="Z80" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="81" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y80" s="4" t="str">
+        <f>IF(COUNTA(B80:X80)=0,"",AVERAGE(B80:X80))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="81" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A81" s="2"/>
       <c r="B81" s="3"/>
       <c r="C81" s="3"/>
@@ -9289,13 +9241,12 @@
       <c r="V81" s="3"/>
       <c r="W81" s="3"/>
       <c r="X81" s="3"/>
-      <c r="Y81" s="3"/>
-      <c r="Z81" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="82" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y81" s="4" t="str">
+        <f>IF(COUNTA(B81:X81)=0,"",AVERAGE(B81:X81))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="82" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A82" s="2"/>
       <c r="B82" s="3"/>
       <c r="C82" s="3"/>
@@ -9320,13 +9271,12 @@
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
-      <c r="Y82" s="3"/>
-      <c r="Z82" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="83" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y82" s="4" t="str">
+        <f>IF(COUNTA(B82:X82)=0,"",AVERAGE(B82:X82))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="83" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A83" s="2"/>
       <c r="B83" s="3"/>
       <c r="C83" s="3"/>
@@ -9351,13 +9301,12 @@
       <c r="V83" s="3"/>
       <c r="W83" s="3"/>
       <c r="X83" s="3"/>
-      <c r="Y83" s="3"/>
-      <c r="Z83" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="84" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y83" s="4" t="str">
+        <f>IF(COUNTA(B83:X83)=0,"",AVERAGE(B83:X83))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="84" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A84" s="2"/>
       <c r="B84" s="3"/>
       <c r="C84" s="3"/>
@@ -9382,13 +9331,12 @@
       <c r="V84" s="3"/>
       <c r="W84" s="3"/>
       <c r="X84" s="3"/>
-      <c r="Y84" s="3"/>
-      <c r="Z84" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="85" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y84" s="4" t="str">
+        <f>IF(COUNTA(B84:X84)=0,"",AVERAGE(B84:X84))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="85" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A85" s="2"/>
       <c r="B85" s="3"/>
       <c r="C85" s="3"/>
@@ -9413,13 +9361,12 @@
       <c r="V85" s="3"/>
       <c r="W85" s="3"/>
       <c r="X85" s="3"/>
-      <c r="Y85" s="3"/>
-      <c r="Z85" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="86" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y85" s="4" t="str">
+        <f>IF(COUNTA(B85:X85)=0,"",AVERAGE(B85:X85))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="86" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A86" s="2"/>
       <c r="B86" s="3"/>
       <c r="C86" s="3"/>
@@ -9444,13 +9391,12 @@
       <c r="V86" s="3"/>
       <c r="W86" s="3"/>
       <c r="X86" s="3"/>
-      <c r="Y86" s="3"/>
-      <c r="Z86" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="87" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y86" s="4" t="str">
+        <f>IF(COUNTA(B86:X86)=0,"",AVERAGE(B86:X86))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="87" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A87" s="2"/>
       <c r="B87" s="3"/>
       <c r="C87" s="3"/>
@@ -9475,13 +9421,12 @@
       <c r="V87" s="3"/>
       <c r="W87" s="3"/>
       <c r="X87" s="3"/>
-      <c r="Y87" s="3"/>
-      <c r="Z87" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="88" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y87" s="4" t="str">
+        <f>IF(COUNTA(B87:X87)=0,"",AVERAGE(B87:X87))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="88" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A88" s="2"/>
       <c r="B88" s="3"/>
       <c r="C88" s="3"/>
@@ -9506,13 +9451,12 @@
       <c r="V88" s="3"/>
       <c r="W88" s="3"/>
       <c r="X88" s="3"/>
-      <c r="Y88" s="3"/>
-      <c r="Z88" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="89" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y88" s="4" t="str">
+        <f>IF(COUNTA(B88:X88)=0,"",AVERAGE(B88:X88))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="89" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A89" s="2"/>
       <c r="B89" s="3"/>
       <c r="C89" s="3"/>
@@ -9537,13 +9481,12 @@
       <c r="V89" s="3"/>
       <c r="W89" s="3"/>
       <c r="X89" s="3"/>
-      <c r="Y89" s="3"/>
-      <c r="Z89" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="90" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y89" s="4" t="str">
+        <f>IF(COUNTA(B89:X89)=0,"",AVERAGE(B89:X89))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="90" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A90" s="2"/>
       <c r="B90" s="3"/>
       <c r="C90" s="3"/>
@@ -9568,13 +9511,12 @@
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
-      <c r="Y90" s="3"/>
-      <c r="Z90" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="91" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y90" s="4" t="str">
+        <f>IF(COUNTA(B90:X90)=0,"",AVERAGE(B90:X90))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="91" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A91" s="2"/>
       <c r="B91" s="3"/>
       <c r="C91" s="3"/>
@@ -9599,13 +9541,12 @@
       <c r="V91" s="3"/>
       <c r="W91" s="3"/>
       <c r="X91" s="3"/>
-      <c r="Y91" s="3"/>
-      <c r="Z91" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="92" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y91" s="4" t="str">
+        <f>IF(COUNTA(B91:X91)=0,"",AVERAGE(B91:X91))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="92" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A92" s="2"/>
       <c r="B92" s="3"/>
       <c r="C92" s="3"/>
@@ -9630,13 +9571,12 @@
       <c r="V92" s="3"/>
       <c r="W92" s="3"/>
       <c r="X92" s="3"/>
-      <c r="Y92" s="3"/>
-      <c r="Z92" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="93" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y92" s="4" t="str">
+        <f>IF(COUNTA(B92:X92)=0,"",AVERAGE(B92:X92))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="93" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A93" s="2"/>
       <c r="B93" s="3"/>
       <c r="C93" s="3"/>
@@ -9661,13 +9601,12 @@
       <c r="V93" s="3"/>
       <c r="W93" s="3"/>
       <c r="X93" s="3"/>
-      <c r="Y93" s="3"/>
-      <c r="Z93" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="94" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y93" s="4" t="str">
+        <f>IF(COUNTA(B93:X93)=0,"",AVERAGE(B93:X93))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="94" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A94" s="2"/>
       <c r="B94" s="3"/>
       <c r="C94" s="3"/>
@@ -9692,13 +9631,12 @@
       <c r="V94" s="3"/>
       <c r="W94" s="3"/>
       <c r="X94" s="3"/>
-      <c r="Y94" s="3"/>
-      <c r="Z94" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="95" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y94" s="4" t="str">
+        <f>IF(COUNTA(B94:X94)=0,"",AVERAGE(B94:X94))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="95" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A95" s="2"/>
       <c r="B95" s="3"/>
       <c r="C95" s="3"/>
@@ -9723,13 +9661,12 @@
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
-      <c r="Y95" s="3"/>
-      <c r="Z95" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="96" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y95" s="4" t="str">
+        <f>IF(COUNTA(B95:X95)=0,"",AVERAGE(B95:X95))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="96" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A96" s="2"/>
       <c r="B96" s="3"/>
       <c r="C96" s="3"/>
@@ -9754,13 +9691,12 @@
       <c r="V96" s="3"/>
       <c r="W96" s="3"/>
       <c r="X96" s="3"/>
-      <c r="Y96" s="3"/>
-      <c r="Z96" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="97" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y96" s="4" t="str">
+        <f>IF(COUNTA(B96:X96)=0,"",AVERAGE(B96:X96))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="97" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A97" s="2"/>
       <c r="B97" s="3"/>
       <c r="C97" s="3"/>
@@ -9785,13 +9721,12 @@
       <c r="V97" s="3"/>
       <c r="W97" s="3"/>
       <c r="X97" s="3"/>
-      <c r="Y97" s="3"/>
-      <c r="Z97" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="98" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y97" s="4" t="str">
+        <f>IF(COUNTA(B97:X97)=0,"",AVERAGE(B97:X97))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="98" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A98" s="2"/>
       <c r="B98" s="3"/>
       <c r="C98" s="3"/>
@@ -9816,13 +9751,12 @@
       <c r="V98" s="3"/>
       <c r="W98" s="3"/>
       <c r="X98" s="3"/>
-      <c r="Y98" s="3"/>
-      <c r="Z98" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="99" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y98" s="4" t="str">
+        <f>IF(COUNTA(B98:X98)=0,"",AVERAGE(B98:X98))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="99" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A99" s="2"/>
       <c r="B99" s="3"/>
       <c r="C99" s="3"/>
@@ -9847,13 +9781,12 @@
       <c r="V99" s="3"/>
       <c r="W99" s="3"/>
       <c r="X99" s="3"/>
-      <c r="Y99" s="3"/>
-      <c r="Z99" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="100" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y99" s="4" t="str">
+        <f>IF(COUNTA(B99:X99)=0,"",AVERAGE(B99:X99))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="100" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A100" s="2"/>
       <c r="B100" s="3"/>
       <c r="C100" s="3"/>
@@ -9878,13 +9811,12 @@
       <c r="V100" s="3"/>
       <c r="W100" s="3"/>
       <c r="X100" s="3"/>
-      <c r="Y100" s="3"/>
-      <c r="Z100" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="101" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y100" s="4" t="str">
+        <f>IF(COUNTA(B100:X100)=0,"",AVERAGE(B100:X100))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="101" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A101" s="2"/>
       <c r="B101" s="3"/>
       <c r="C101" s="3"/>
@@ -9909,13 +9841,12 @@
       <c r="V101" s="3"/>
       <c r="W101" s="3"/>
       <c r="X101" s="3"/>
-      <c r="Y101" s="3"/>
-      <c r="Z101" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="102" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y101" s="4" t="str">
+        <f>IF(COUNTA(B101:X101)=0,"",AVERAGE(B101:X101))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="102" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A102" s="2"/>
       <c r="B102" s="3"/>
       <c r="C102" s="3"/>
@@ -9940,13 +9871,12 @@
       <c r="V102" s="3"/>
       <c r="W102" s="3"/>
       <c r="X102" s="3"/>
-      <c r="Y102" s="3"/>
-      <c r="Z102" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="103" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y102" s="4" t="str">
+        <f>IF(COUNTA(B102:X102)=0,"",AVERAGE(B102:X102))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="103" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A103" s="2"/>
       <c r="B103" s="3"/>
       <c r="C103" s="3"/>
@@ -9971,13 +9901,12 @@
       <c r="V103" s="3"/>
       <c r="W103" s="3"/>
       <c r="X103" s="3"/>
-      <c r="Y103" s="3"/>
-      <c r="Z103" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="104" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y103" s="4" t="str">
+        <f>IF(COUNTA(B103:X103)=0,"",AVERAGE(B103:X103))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="104" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A104" s="2"/>
       <c r="B104" s="3"/>
       <c r="C104" s="3"/>
@@ -10002,13 +9931,12 @@
       <c r="V104" s="3"/>
       <c r="W104" s="3"/>
       <c r="X104" s="3"/>
-      <c r="Y104" s="3"/>
-      <c r="Z104" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="105" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y104" s="4" t="str">
+        <f>IF(COUNTA(B104:X104)=0,"",AVERAGE(B104:X104))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="105" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A105" s="2"/>
       <c r="B105" s="3"/>
       <c r="C105" s="3"/>
@@ -10033,13 +9961,12 @@
       <c r="V105" s="3"/>
       <c r="W105" s="3"/>
       <c r="X105" s="3"/>
-      <c r="Y105" s="3"/>
-      <c r="Z105" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="106" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y105" s="4" t="str">
+        <f>IF(COUNTA(B105:X105)=0,"",AVERAGE(B105:X105))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="106" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A106" s="2"/>
       <c r="B106" s="3"/>
       <c r="C106" s="3"/>
@@ -10064,13 +9991,12 @@
       <c r="V106" s="3"/>
       <c r="W106" s="3"/>
       <c r="X106" s="3"/>
-      <c r="Y106" s="3"/>
-      <c r="Z106" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="107" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y106" s="4" t="str">
+        <f>IF(COUNTA(B106:X106)=0,"",AVERAGE(B106:X106))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="107" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A107" s="2"/>
       <c r="B107" s="3"/>
       <c r="C107" s="3"/>
@@ -10095,13 +10021,12 @@
       <c r="V107" s="3"/>
       <c r="W107" s="3"/>
       <c r="X107" s="3"/>
-      <c r="Y107" s="3"/>
-      <c r="Z107" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="108" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y107" s="4" t="str">
+        <f>IF(COUNTA(B107:X107)=0,"",AVERAGE(B107:X107))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="108" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A108" s="2"/>
       <c r="B108" s="3"/>
       <c r="C108" s="3"/>
@@ -10126,13 +10051,12 @@
       <c r="V108" s="3"/>
       <c r="W108" s="3"/>
       <c r="X108" s="3"/>
-      <c r="Y108" s="3"/>
-      <c r="Z108" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="109" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y108" s="4" t="str">
+        <f>IF(COUNTA(B108:X108)=0,"",AVERAGE(B108:X108))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="109" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A109" s="2"/>
       <c r="B109" s="3"/>
       <c r="C109" s="3"/>
@@ -10157,13 +10081,12 @@
       <c r="V109" s="3"/>
       <c r="W109" s="3"/>
       <c r="X109" s="3"/>
-      <c r="Y109" s="3"/>
-      <c r="Z109" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="110" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y109" s="4" t="str">
+        <f>IF(COUNTA(B109:X109)=0,"",AVERAGE(B109:X109))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="110" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A110" s="2"/>
       <c r="B110" s="3"/>
       <c r="C110" s="3"/>
@@ -10188,13 +10111,12 @@
       <c r="V110" s="3"/>
       <c r="W110" s="3"/>
       <c r="X110" s="3"/>
-      <c r="Y110" s="3"/>
-      <c r="Z110" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="111" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y110" s="4" t="str">
+        <f>IF(COUNTA(B110:X110)=0,"",AVERAGE(B110:X110))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="111" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A111" s="2"/>
       <c r="B111" s="3"/>
       <c r="C111" s="3"/>
@@ -10219,13 +10141,12 @@
       <c r="V111" s="3"/>
       <c r="W111" s="3"/>
       <c r="X111" s="3"/>
-      <c r="Y111" s="3"/>
-      <c r="Z111" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="112" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y111" s="4" t="str">
+        <f>IF(COUNTA(B111:X111)=0,"",AVERAGE(B111:X111))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="112" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A112" s="2"/>
       <c r="B112" s="3"/>
       <c r="C112" s="3"/>
@@ -10250,13 +10171,12 @@
       <c r="V112" s="3"/>
       <c r="W112" s="3"/>
       <c r="X112" s="3"/>
-      <c r="Y112" s="3"/>
-      <c r="Z112" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="113" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y112" s="4" t="str">
+        <f>IF(COUNTA(B112:X112)=0,"",AVERAGE(B112:X112))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="113" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A113" s="2"/>
       <c r="B113" s="3"/>
       <c r="C113" s="3"/>
@@ -10281,13 +10201,12 @@
       <c r="V113" s="3"/>
       <c r="W113" s="3"/>
       <c r="X113" s="3"/>
-      <c r="Y113" s="3"/>
-      <c r="Z113" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="114" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y113" s="4" t="str">
+        <f>IF(COUNTA(B113:X113)=0,"",AVERAGE(B113:X113))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="114" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A114" s="2"/>
       <c r="B114" s="3"/>
       <c r="C114" s="3"/>
@@ -10312,13 +10231,12 @@
       <c r="V114" s="3"/>
       <c r="W114" s="3"/>
       <c r="X114" s="3"/>
-      <c r="Y114" s="3"/>
-      <c r="Z114" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="115" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y114" s="4" t="str">
+        <f>IF(COUNTA(B114:X114)=0,"",AVERAGE(B114:X114))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="115" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A115" s="2"/>
       <c r="B115" s="3"/>
       <c r="C115" s="3"/>
@@ -10343,13 +10261,12 @@
       <c r="V115" s="3"/>
       <c r="W115" s="3"/>
       <c r="X115" s="3"/>
-      <c r="Y115" s="3"/>
-      <c r="Z115" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="116" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y115" s="4" t="str">
+        <f>IF(COUNTA(B115:X115)=0,"",AVERAGE(B115:X115))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="116" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A116" s="2"/>
       <c r="B116" s="3"/>
       <c r="C116" s="3"/>
@@ -10374,13 +10291,12 @@
       <c r="V116" s="3"/>
       <c r="W116" s="3"/>
       <c r="X116" s="3"/>
-      <c r="Y116" s="3"/>
-      <c r="Z116" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="117" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y116" s="4" t="str">
+        <f>IF(COUNTA(B116:X116)=0,"",AVERAGE(B116:X116))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="117" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A117" s="2"/>
       <c r="B117" s="3"/>
       <c r="C117" s="3"/>
@@ -10405,13 +10321,12 @@
       <c r="V117" s="3"/>
       <c r="W117" s="3"/>
       <c r="X117" s="3"/>
-      <c r="Y117" s="3"/>
-      <c r="Z117" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="118" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y117" s="4" t="str">
+        <f>IF(COUNTA(B117:X117)=0,"",AVERAGE(B117:X117))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="118" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A118" s="2"/>
       <c r="B118" s="3"/>
       <c r="C118" s="3"/>
@@ -10436,13 +10351,12 @@
       <c r="V118" s="3"/>
       <c r="W118" s="3"/>
       <c r="X118" s="3"/>
-      <c r="Y118" s="3"/>
-      <c r="Z118" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="119" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y118" s="4" t="str">
+        <f>IF(COUNTA(B118:X118)=0,"",AVERAGE(B118:X118))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="119" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A119" s="2"/>
       <c r="B119" s="3"/>
       <c r="C119" s="3"/>
@@ -10467,13 +10381,12 @@
       <c r="V119" s="3"/>
       <c r="W119" s="3"/>
       <c r="X119" s="3"/>
-      <c r="Y119" s="3"/>
-      <c r="Z119" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="120" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y119" s="4" t="str">
+        <f>IF(COUNTA(B119:X119)=0,"",AVERAGE(B119:X119))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="120" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A120" s="2"/>
       <c r="B120" s="3"/>
       <c r="C120" s="3"/>
@@ -10498,13 +10411,12 @@
       <c r="V120" s="3"/>
       <c r="W120" s="3"/>
       <c r="X120" s="3"/>
-      <c r="Y120" s="3"/>
-      <c r="Z120" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="121" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y120" s="4" t="str">
+        <f>IF(COUNTA(B120:X120)=0,"",AVERAGE(B120:X120))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="121" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A121" s="2"/>
       <c r="B121" s="3"/>
       <c r="C121" s="3"/>
@@ -10529,13 +10441,12 @@
       <c r="V121" s="3"/>
       <c r="W121" s="3"/>
       <c r="X121" s="3"/>
-      <c r="Y121" s="3"/>
-      <c r="Z121" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="122" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y121" s="4" t="str">
+        <f>IF(COUNTA(B121:X121)=0,"",AVERAGE(B121:X121))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="122" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A122" s="2"/>
       <c r="B122" s="3"/>
       <c r="C122" s="3"/>
@@ -10560,13 +10471,12 @@
       <c r="V122" s="3"/>
       <c r="W122" s="3"/>
       <c r="X122" s="3"/>
-      <c r="Y122" s="3"/>
-      <c r="Z122" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="123" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y122" s="4" t="str">
+        <f>IF(COUNTA(B122:X122)=0,"",AVERAGE(B122:X122))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="123" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A123" s="2"/>
       <c r="B123" s="3"/>
       <c r="C123" s="3"/>
@@ -10591,13 +10501,12 @@
       <c r="V123" s="3"/>
       <c r="W123" s="3"/>
       <c r="X123" s="3"/>
-      <c r="Y123" s="3"/>
-      <c r="Z123" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="124" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y123" s="4" t="str">
+        <f>IF(COUNTA(B123:X123)=0,"",AVERAGE(B123:X123))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="124" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A124" s="2"/>
       <c r="B124" s="3"/>
       <c r="C124" s="3"/>
@@ -10622,13 +10531,12 @@
       <c r="V124" s="3"/>
       <c r="W124" s="3"/>
       <c r="X124" s="3"/>
-      <c r="Y124" s="3"/>
-      <c r="Z124" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="125" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y124" s="4" t="str">
+        <f>IF(COUNTA(B124:X124)=0,"",AVERAGE(B124:X124))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="125" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A125" s="2"/>
       <c r="B125" s="3"/>
       <c r="C125" s="3"/>
@@ -10653,13 +10561,12 @@
       <c r="V125" s="3"/>
       <c r="W125" s="3"/>
       <c r="X125" s="3"/>
-      <c r="Y125" s="3"/>
-      <c r="Z125" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="126" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y125" s="4" t="str">
+        <f>IF(COUNTA(B125:X125)=0,"",AVERAGE(B125:X125))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="126" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A126" s="2"/>
       <c r="B126" s="3"/>
       <c r="C126" s="3"/>
@@ -10684,13 +10591,12 @@
       <c r="V126" s="3"/>
       <c r="W126" s="3"/>
       <c r="X126" s="3"/>
-      <c r="Y126" s="3"/>
-      <c r="Z126" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="127" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y126" s="4" t="str">
+        <f>IF(COUNTA(B126:X126)=0,"",AVERAGE(B126:X126))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="127" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A127" s="2"/>
       <c r="B127" s="3"/>
       <c r="C127" s="3"/>
@@ -10715,13 +10621,12 @@
       <c r="V127" s="3"/>
       <c r="W127" s="3"/>
       <c r="X127" s="3"/>
-      <c r="Y127" s="3"/>
-      <c r="Z127" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="128" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y127" s="4" t="str">
+        <f>IF(COUNTA(B127:X127)=0,"",AVERAGE(B127:X127))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="128" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A128" s="2"/>
       <c r="B128" s="3"/>
       <c r="C128" s="3"/>
@@ -10746,13 +10651,12 @@
       <c r="V128" s="3"/>
       <c r="W128" s="3"/>
       <c r="X128" s="3"/>
-      <c r="Y128" s="3"/>
-      <c r="Z128" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="129" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y128" s="4" t="str">
+        <f>IF(COUNTA(B128:X128)=0,"",AVERAGE(B128:X128))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="129" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A129" s="2"/>
       <c r="B129" s="3"/>
       <c r="C129" s="3"/>
@@ -10777,13 +10681,12 @@
       <c r="V129" s="3"/>
       <c r="W129" s="3"/>
       <c r="X129" s="3"/>
-      <c r="Y129" s="3"/>
-      <c r="Z129" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="130" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y129" s="4" t="str">
+        <f>IF(COUNTA(B129:X129)=0,"",AVERAGE(B129:X129))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="130" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A130" s="2"/>
       <c r="B130" s="3"/>
       <c r="C130" s="3"/>
@@ -10808,13 +10711,12 @@
       <c r="V130" s="3"/>
       <c r="W130" s="3"/>
       <c r="X130" s="3"/>
-      <c r="Y130" s="3"/>
-      <c r="Z130" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="131" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y130" s="4" t="str">
+        <f>IF(COUNTA(B130:X130)=0,"",AVERAGE(B130:X130))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="131" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A131" s="2"/>
       <c r="B131" s="3"/>
       <c r="C131" s="3"/>
@@ -10839,13 +10741,12 @@
       <c r="V131" s="3"/>
       <c r="W131" s="3"/>
       <c r="X131" s="3"/>
-      <c r="Y131" s="3"/>
-      <c r="Z131" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="132" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y131" s="4" t="str">
+        <f>IF(COUNTA(B131:X131)=0,"",AVERAGE(B131:X131))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="132" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A132" s="2"/>
       <c r="B132" s="3"/>
       <c r="C132" s="3"/>
@@ -10870,13 +10771,12 @@
       <c r="V132" s="3"/>
       <c r="W132" s="3"/>
       <c r="X132" s="3"/>
-      <c r="Y132" s="3"/>
-      <c r="Z132" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="133" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y132" s="4" t="str">
+        <f>IF(COUNTA(B132:X132)=0,"",AVERAGE(B132:X132))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="133" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A133" s="2"/>
       <c r="B133" s="3"/>
       <c r="C133" s="3"/>
@@ -10901,13 +10801,12 @@
       <c r="V133" s="3"/>
       <c r="W133" s="3"/>
       <c r="X133" s="3"/>
-      <c r="Y133" s="3"/>
-      <c r="Z133" s="4" t="str">
-        <f t="shared" ref="Z133:Z196" si="3">IF(COUNTA(B133:Y133)=0,"",AVERAGE(B133:Y133))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="134" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y133" s="4" t="str">
+        <f>IF(COUNTA(B133:X133)=0,"",AVERAGE(B133:X133))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="134" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A134" s="2"/>
       <c r="B134" s="3"/>
       <c r="C134" s="3"/>
@@ -10932,13 +10831,12 @@
       <c r="V134" s="3"/>
       <c r="W134" s="3"/>
       <c r="X134" s="3"/>
-      <c r="Y134" s="3"/>
-      <c r="Z134" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="135" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y134" s="4" t="str">
+        <f>IF(COUNTA(B134:X134)=0,"",AVERAGE(B134:X134))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="135" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A135" s="2"/>
       <c r="B135" s="3"/>
       <c r="C135" s="3"/>
@@ -10963,13 +10861,12 @@
       <c r="V135" s="3"/>
       <c r="W135" s="3"/>
       <c r="X135" s="3"/>
-      <c r="Y135" s="3"/>
-      <c r="Z135" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="136" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y135" s="4" t="str">
+        <f>IF(COUNTA(B135:X135)=0,"",AVERAGE(B135:X135))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="136" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A136" s="2"/>
       <c r="B136" s="3"/>
       <c r="C136" s="3"/>
@@ -10994,13 +10891,12 @@
       <c r="V136" s="3"/>
       <c r="W136" s="3"/>
       <c r="X136" s="3"/>
-      <c r="Y136" s="3"/>
-      <c r="Z136" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="137" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y136" s="4" t="str">
+        <f>IF(COUNTA(B136:X136)=0,"",AVERAGE(B136:X136))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="137" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A137" s="2"/>
       <c r="B137" s="3"/>
       <c r="C137" s="3"/>
@@ -11025,13 +10921,12 @@
       <c r="V137" s="3"/>
       <c r="W137" s="3"/>
       <c r="X137" s="3"/>
-      <c r="Y137" s="3"/>
-      <c r="Z137" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="138" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y137" s="4" t="str">
+        <f>IF(COUNTA(B137:X137)=0,"",AVERAGE(B137:X137))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="138" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A138" s="2"/>
       <c r="B138" s="3"/>
       <c r="C138" s="3"/>
@@ -11056,13 +10951,12 @@
       <c r="V138" s="3"/>
       <c r="W138" s="3"/>
       <c r="X138" s="3"/>
-      <c r="Y138" s="3"/>
-      <c r="Z138" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="139" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y138" s="4" t="str">
+        <f>IF(COUNTA(B138:X138)=0,"",AVERAGE(B138:X138))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="139" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A139" s="2"/>
       <c r="B139" s="3"/>
       <c r="C139" s="3"/>
@@ -11087,13 +10981,12 @@
       <c r="V139" s="3"/>
       <c r="W139" s="3"/>
       <c r="X139" s="3"/>
-      <c r="Y139" s="3"/>
-      <c r="Z139" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="140" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y139" s="4" t="str">
+        <f>IF(COUNTA(B139:X139)=0,"",AVERAGE(B139:X139))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="140" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A140" s="2"/>
       <c r="B140" s="3"/>
       <c r="C140" s="3"/>
@@ -11118,13 +11011,12 @@
       <c r="V140" s="3"/>
       <c r="W140" s="3"/>
       <c r="X140" s="3"/>
-      <c r="Y140" s="3"/>
-      <c r="Z140" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="141" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y140" s="4" t="str">
+        <f>IF(COUNTA(B140:X140)=0,"",AVERAGE(B140:X140))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="141" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A141" s="2"/>
       <c r="B141" s="3"/>
       <c r="C141" s="3"/>
@@ -11149,13 +11041,12 @@
       <c r="V141" s="3"/>
       <c r="W141" s="3"/>
       <c r="X141" s="3"/>
-      <c r="Y141" s="3"/>
-      <c r="Z141" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="142" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y141" s="4" t="str">
+        <f>IF(COUNTA(B141:X141)=0,"",AVERAGE(B141:X141))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="142" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A142" s="2"/>
       <c r="B142" s="3"/>
       <c r="C142" s="3"/>
@@ -11180,13 +11071,12 @@
       <c r="V142" s="3"/>
       <c r="W142" s="3"/>
       <c r="X142" s="3"/>
-      <c r="Y142" s="3"/>
-      <c r="Z142" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="143" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y142" s="4" t="str">
+        <f>IF(COUNTA(B142:X142)=0,"",AVERAGE(B142:X142))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="143" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A143" s="2"/>
       <c r="B143" s="3"/>
       <c r="C143" s="3"/>
@@ -11211,13 +11101,12 @@
       <c r="V143" s="3"/>
       <c r="W143" s="3"/>
       <c r="X143" s="3"/>
-      <c r="Y143" s="3"/>
-      <c r="Z143" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="144" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y143" s="4" t="str">
+        <f>IF(COUNTA(B143:X143)=0,"",AVERAGE(B143:X143))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="144" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A144" s="2"/>
       <c r="B144" s="3"/>
       <c r="C144" s="3"/>
@@ -11242,13 +11131,12 @@
       <c r="V144" s="3"/>
       <c r="W144" s="3"/>
       <c r="X144" s="3"/>
-      <c r="Y144" s="3"/>
-      <c r="Z144" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="145" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y144" s="4" t="str">
+        <f>IF(COUNTA(B144:X144)=0,"",AVERAGE(B144:X144))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="145" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A145" s="2"/>
       <c r="B145" s="3"/>
       <c r="C145" s="3"/>
@@ -11273,13 +11161,12 @@
       <c r="V145" s="3"/>
       <c r="W145" s="3"/>
       <c r="X145" s="3"/>
-      <c r="Y145" s="3"/>
-      <c r="Z145" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="146" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y145" s="4" t="str">
+        <f>IF(COUNTA(B145:X145)=0,"",AVERAGE(B145:X145))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="146" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A146" s="2"/>
       <c r="B146" s="3"/>
       <c r="C146" s="3"/>
@@ -11304,13 +11191,12 @@
       <c r="V146" s="3"/>
       <c r="W146" s="3"/>
       <c r="X146" s="3"/>
-      <c r="Y146" s="3"/>
-      <c r="Z146" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="147" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y146" s="4" t="str">
+        <f>IF(COUNTA(B146:X146)=0,"",AVERAGE(B146:X146))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="147" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A147" s="2"/>
       <c r="B147" s="3"/>
       <c r="C147" s="3"/>
@@ -11335,13 +11221,12 @@
       <c r="V147" s="3"/>
       <c r="W147" s="3"/>
       <c r="X147" s="3"/>
-      <c r="Y147" s="3"/>
-      <c r="Z147" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="148" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y147" s="4" t="str">
+        <f>IF(COUNTA(B147:X147)=0,"",AVERAGE(B147:X147))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="148" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A148" s="2"/>
       <c r="B148" s="3"/>
       <c r="C148" s="3"/>
@@ -11366,13 +11251,12 @@
       <c r="V148" s="3"/>
       <c r="W148" s="3"/>
       <c r="X148" s="3"/>
-      <c r="Y148" s="3"/>
-      <c r="Z148" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="149" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y148" s="4" t="str">
+        <f>IF(COUNTA(B148:X148)=0,"",AVERAGE(B148:X148))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="149" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A149" s="2"/>
       <c r="B149" s="3"/>
       <c r="C149" s="3"/>
@@ -11397,13 +11281,12 @@
       <c r="V149" s="3"/>
       <c r="W149" s="3"/>
       <c r="X149" s="3"/>
-      <c r="Y149" s="3"/>
-      <c r="Z149" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="150" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y149" s="4" t="str">
+        <f>IF(COUNTA(B149:X149)=0,"",AVERAGE(B149:X149))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="150" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A150" s="2"/>
       <c r="B150" s="3"/>
       <c r="C150" s="3"/>
@@ -11428,13 +11311,12 @@
       <c r="V150" s="3"/>
       <c r="W150" s="3"/>
       <c r="X150" s="3"/>
-      <c r="Y150" s="3"/>
-      <c r="Z150" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="151" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y150" s="4" t="str">
+        <f>IF(COUNTA(B150:X150)=0,"",AVERAGE(B150:X150))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="151" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A151" s="2"/>
       <c r="B151" s="3"/>
       <c r="C151" s="3"/>
@@ -11459,13 +11341,12 @@
       <c r="V151" s="3"/>
       <c r="W151" s="3"/>
       <c r="X151" s="3"/>
-      <c r="Y151" s="3"/>
-      <c r="Z151" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="152" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y151" s="4" t="str">
+        <f>IF(COUNTA(B151:X151)=0,"",AVERAGE(B151:X151))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="152" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A152" s="2"/>
       <c r="B152" s="3"/>
       <c r="C152" s="3"/>
@@ -11490,13 +11371,12 @@
       <c r="V152" s="3"/>
       <c r="W152" s="3"/>
       <c r="X152" s="3"/>
-      <c r="Y152" s="3"/>
-      <c r="Z152" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="153" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y152" s="4" t="str">
+        <f>IF(COUNTA(B152:X152)=0,"",AVERAGE(B152:X152))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="153" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A153" s="2"/>
       <c r="B153" s="3"/>
       <c r="C153" s="3"/>
@@ -11521,13 +11401,12 @@
       <c r="V153" s="3"/>
       <c r="W153" s="3"/>
       <c r="X153" s="3"/>
-      <c r="Y153" s="3"/>
-      <c r="Z153" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="154" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y153" s="4" t="str">
+        <f>IF(COUNTA(B153:X153)=0,"",AVERAGE(B153:X153))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="154" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A154" s="2"/>
       <c r="B154" s="3"/>
       <c r="C154" s="3"/>
@@ -11552,13 +11431,12 @@
       <c r="V154" s="3"/>
       <c r="W154" s="3"/>
       <c r="X154" s="3"/>
-      <c r="Y154" s="3"/>
-      <c r="Z154" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="155" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y154" s="4" t="str">
+        <f>IF(COUNTA(B154:X154)=0,"",AVERAGE(B154:X154))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="155" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A155" s="2"/>
       <c r="B155" s="3"/>
       <c r="C155" s="3"/>
@@ -11583,13 +11461,12 @@
       <c r="V155" s="3"/>
       <c r="W155" s="3"/>
       <c r="X155" s="3"/>
-      <c r="Y155" s="3"/>
-      <c r="Z155" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="156" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y155" s="4" t="str">
+        <f>IF(COUNTA(B155:X155)=0,"",AVERAGE(B155:X155))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="156" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A156" s="2"/>
       <c r="B156" s="3"/>
       <c r="C156" s="3"/>
@@ -11614,13 +11491,12 @@
       <c r="V156" s="3"/>
       <c r="W156" s="3"/>
       <c r="X156" s="3"/>
-      <c r="Y156" s="3"/>
-      <c r="Z156" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="157" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y156" s="4" t="str">
+        <f>IF(COUNTA(B156:X156)=0,"",AVERAGE(B156:X156))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="157" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A157" s="2"/>
       <c r="B157" s="3"/>
       <c r="C157" s="3"/>
@@ -11645,13 +11521,12 @@
       <c r="V157" s="3"/>
       <c r="W157" s="3"/>
       <c r="X157" s="3"/>
-      <c r="Y157" s="3"/>
-      <c r="Z157" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="158" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y157" s="4" t="str">
+        <f>IF(COUNTA(B157:X157)=0,"",AVERAGE(B157:X157))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="158" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A158" s="2"/>
       <c r="B158" s="3"/>
       <c r="C158" s="3"/>
@@ -11676,13 +11551,12 @@
       <c r="V158" s="3"/>
       <c r="W158" s="3"/>
       <c r="X158" s="3"/>
-      <c r="Y158" s="3"/>
-      <c r="Z158" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="159" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y158" s="4" t="str">
+        <f>IF(COUNTA(B158:X158)=0,"",AVERAGE(B158:X158))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="159" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A159" s="2"/>
       <c r="B159" s="3"/>
       <c r="C159" s="3"/>
@@ -11707,13 +11581,12 @@
       <c r="V159" s="3"/>
       <c r="W159" s="3"/>
       <c r="X159" s="3"/>
-      <c r="Y159" s="3"/>
-      <c r="Z159" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="160" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y159" s="4" t="str">
+        <f>IF(COUNTA(B159:X159)=0,"",AVERAGE(B159:X159))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="160" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A160" s="2"/>
       <c r="B160" s="3"/>
       <c r="C160" s="3"/>
@@ -11738,13 +11611,12 @@
       <c r="V160" s="3"/>
       <c r="W160" s="3"/>
       <c r="X160" s="3"/>
-      <c r="Y160" s="3"/>
-      <c r="Z160" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="161" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y160" s="4" t="str">
+        <f>IF(COUNTA(B160:X160)=0,"",AVERAGE(B160:X160))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="161" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A161" s="2"/>
       <c r="B161" s="3"/>
       <c r="C161" s="3"/>
@@ -11769,13 +11641,12 @@
       <c r="V161" s="3"/>
       <c r="W161" s="3"/>
       <c r="X161" s="3"/>
-      <c r="Y161" s="3"/>
-      <c r="Z161" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="162" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y161" s="4" t="str">
+        <f>IF(COUNTA(B161:X161)=0,"",AVERAGE(B161:X161))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="162" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A162" s="2"/>
       <c r="B162" s="3"/>
       <c r="C162" s="3"/>
@@ -11800,13 +11671,12 @@
       <c r="V162" s="3"/>
       <c r="W162" s="3"/>
       <c r="X162" s="3"/>
-      <c r="Y162" s="3"/>
-      <c r="Z162" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="163" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y162" s="4" t="str">
+        <f>IF(COUNTA(B162:X162)=0,"",AVERAGE(B162:X162))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="163" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A163" s="2"/>
       <c r="B163" s="3"/>
       <c r="C163" s="3"/>
@@ -11831,13 +11701,12 @@
       <c r="V163" s="3"/>
       <c r="W163" s="3"/>
       <c r="X163" s="3"/>
-      <c r="Y163" s="3"/>
-      <c r="Z163" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="164" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y163" s="4" t="str">
+        <f>IF(COUNTA(B163:X163)=0,"",AVERAGE(B163:X163))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="164" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A164" s="2"/>
       <c r="B164" s="3"/>
       <c r="C164" s="3"/>
@@ -11862,13 +11731,12 @@
       <c r="V164" s="3"/>
       <c r="W164" s="3"/>
       <c r="X164" s="3"/>
-      <c r="Y164" s="3"/>
-      <c r="Z164" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="165" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y164" s="4" t="str">
+        <f>IF(COUNTA(B164:X164)=0,"",AVERAGE(B164:X164))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="165" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A165" s="2"/>
       <c r="B165" s="3"/>
       <c r="C165" s="3"/>
@@ -11893,13 +11761,12 @@
       <c r="V165" s="3"/>
       <c r="W165" s="3"/>
       <c r="X165" s="3"/>
-      <c r="Y165" s="3"/>
-      <c r="Z165" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="166" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y165" s="4" t="str">
+        <f>IF(COUNTA(B165:X165)=0,"",AVERAGE(B165:X165))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="166" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A166" s="2"/>
       <c r="B166" s="3"/>
       <c r="C166" s="3"/>
@@ -11924,13 +11791,12 @@
       <c r="V166" s="3"/>
       <c r="W166" s="3"/>
       <c r="X166" s="3"/>
-      <c r="Y166" s="3"/>
-      <c r="Z166" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="167" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y166" s="4" t="str">
+        <f>IF(COUNTA(B166:X166)=0,"",AVERAGE(B166:X166))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="167" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A167" s="2"/>
       <c r="B167" s="3"/>
       <c r="C167" s="3"/>
@@ -11955,13 +11821,12 @@
       <c r="V167" s="3"/>
       <c r="W167" s="3"/>
       <c r="X167" s="3"/>
-      <c r="Y167" s="3"/>
-      <c r="Z167" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="168" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y167" s="4" t="str">
+        <f>IF(COUNTA(B167:X167)=0,"",AVERAGE(B167:X167))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="168" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A168" s="2"/>
       <c r="B168" s="3"/>
       <c r="C168" s="3"/>
@@ -11986,13 +11851,12 @@
       <c r="V168" s="3"/>
       <c r="W168" s="3"/>
       <c r="X168" s="3"/>
-      <c r="Y168" s="3"/>
-      <c r="Z168" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="169" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y168" s="4" t="str">
+        <f>IF(COUNTA(B168:X168)=0,"",AVERAGE(B168:X168))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="169" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A169" s="2"/>
       <c r="B169" s="3"/>
       <c r="C169" s="3"/>
@@ -12017,13 +11881,12 @@
       <c r="V169" s="3"/>
       <c r="W169" s="3"/>
       <c r="X169" s="3"/>
-      <c r="Y169" s="3"/>
-      <c r="Z169" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="170" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y169" s="4" t="str">
+        <f>IF(COUNTA(B169:X169)=0,"",AVERAGE(B169:X169))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="170" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A170" s="2"/>
       <c r="B170" s="3"/>
       <c r="C170" s="3"/>
@@ -12048,13 +11911,12 @@
       <c r="V170" s="3"/>
       <c r="W170" s="3"/>
       <c r="X170" s="3"/>
-      <c r="Y170" s="3"/>
-      <c r="Z170" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="171" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y170" s="4" t="str">
+        <f>IF(COUNTA(B170:X170)=0,"",AVERAGE(B170:X170))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="171" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A171" s="2"/>
       <c r="B171" s="3"/>
       <c r="C171" s="3"/>
@@ -12079,13 +11941,12 @@
       <c r="V171" s="3"/>
       <c r="W171" s="3"/>
       <c r="X171" s="3"/>
-      <c r="Y171" s="3"/>
-      <c r="Z171" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="172" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y171" s="4" t="str">
+        <f>IF(COUNTA(B171:X171)=0,"",AVERAGE(B171:X171))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="172" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A172" s="2"/>
       <c r="B172" s="3"/>
       <c r="C172" s="3"/>
@@ -12110,13 +11971,12 @@
       <c r="V172" s="3"/>
       <c r="W172" s="3"/>
       <c r="X172" s="3"/>
-      <c r="Y172" s="3"/>
-      <c r="Z172" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="173" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y172" s="4" t="str">
+        <f>IF(COUNTA(B172:X172)=0,"",AVERAGE(B172:X172))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="173" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A173" s="2"/>
       <c r="B173" s="3"/>
       <c r="C173" s="3"/>
@@ -12141,13 +12001,12 @@
       <c r="V173" s="3"/>
       <c r="W173" s="3"/>
       <c r="X173" s="3"/>
-      <c r="Y173" s="3"/>
-      <c r="Z173" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="174" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y173" s="4" t="str">
+        <f>IF(COUNTA(B173:X173)=0,"",AVERAGE(B173:X173))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="174" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A174" s="2"/>
       <c r="B174" s="3"/>
       <c r="C174" s="3"/>
@@ -12172,13 +12031,12 @@
       <c r="V174" s="3"/>
       <c r="W174" s="3"/>
       <c r="X174" s="3"/>
-      <c r="Y174" s="3"/>
-      <c r="Z174" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="175" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y174" s="4" t="str">
+        <f>IF(COUNTA(B174:X174)=0,"",AVERAGE(B174:X174))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="175" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A175" s="2"/>
       <c r="B175" s="3"/>
       <c r="C175" s="3"/>
@@ -12203,13 +12061,12 @@
       <c r="V175" s="3"/>
       <c r="W175" s="3"/>
       <c r="X175" s="3"/>
-      <c r="Y175" s="3"/>
-      <c r="Z175" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="176" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y175" s="4" t="str">
+        <f>IF(COUNTA(B175:X175)=0,"",AVERAGE(B175:X175))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="176" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A176" s="2"/>
       <c r="B176" s="3"/>
       <c r="C176" s="3"/>
@@ -12234,13 +12091,12 @@
       <c r="V176" s="3"/>
       <c r="W176" s="3"/>
       <c r="X176" s="3"/>
-      <c r="Y176" s="3"/>
-      <c r="Z176" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="177" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y176" s="4" t="str">
+        <f>IF(COUNTA(B176:X176)=0,"",AVERAGE(B176:X176))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="177" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A177" s="2"/>
       <c r="B177" s="3"/>
       <c r="C177" s="3"/>
@@ -12265,13 +12121,12 @@
       <c r="V177" s="3"/>
       <c r="W177" s="3"/>
       <c r="X177" s="3"/>
-      <c r="Y177" s="3"/>
-      <c r="Z177" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="178" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y177" s="4" t="str">
+        <f>IF(COUNTA(B177:X177)=0,"",AVERAGE(B177:X177))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="178" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A178" s="2"/>
       <c r="B178" s="3"/>
       <c r="C178" s="3"/>
@@ -12296,13 +12151,12 @@
       <c r="V178" s="3"/>
       <c r="W178" s="3"/>
       <c r="X178" s="3"/>
-      <c r="Y178" s="3"/>
-      <c r="Z178" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="179" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y178" s="4" t="str">
+        <f>IF(COUNTA(B178:X178)=0,"",AVERAGE(B178:X178))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="179" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A179" s="2"/>
       <c r="B179" s="3"/>
       <c r="C179" s="3"/>
@@ -12327,13 +12181,12 @@
       <c r="V179" s="3"/>
       <c r="W179" s="3"/>
       <c r="X179" s="3"/>
-      <c r="Y179" s="3"/>
-      <c r="Z179" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="180" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y179" s="4" t="str">
+        <f>IF(COUNTA(B179:X179)=0,"",AVERAGE(B179:X179))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="180" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A180" s="2"/>
       <c r="B180" s="3"/>
       <c r="C180" s="3"/>
@@ -12358,13 +12211,12 @@
       <c r="V180" s="3"/>
       <c r="W180" s="3"/>
       <c r="X180" s="3"/>
-      <c r="Y180" s="3"/>
-      <c r="Z180" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="181" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y180" s="4" t="str">
+        <f>IF(COUNTA(B180:X180)=0,"",AVERAGE(B180:X180))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="181" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A181" s="2"/>
       <c r="B181" s="3"/>
       <c r="C181" s="3"/>
@@ -12389,13 +12241,12 @@
       <c r="V181" s="3"/>
       <c r="W181" s="3"/>
       <c r="X181" s="3"/>
-      <c r="Y181" s="3"/>
-      <c r="Z181" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="182" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y181" s="4" t="str">
+        <f>IF(COUNTA(B181:X181)=0,"",AVERAGE(B181:X181))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="182" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A182" s="2"/>
       <c r="B182" s="3"/>
       <c r="C182" s="3"/>
@@ -12420,13 +12271,12 @@
       <c r="V182" s="3"/>
       <c r="W182" s="3"/>
       <c r="X182" s="3"/>
-      <c r="Y182" s="3"/>
-      <c r="Z182" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="183" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y182" s="4" t="str">
+        <f>IF(COUNTA(B182:X182)=0,"",AVERAGE(B182:X182))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="183" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A183" s="2"/>
       <c r="B183" s="3"/>
       <c r="C183" s="3"/>
@@ -12451,13 +12301,12 @@
       <c r="V183" s="3"/>
       <c r="W183" s="3"/>
       <c r="X183" s="3"/>
-      <c r="Y183" s="3"/>
-      <c r="Z183" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="184" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y183" s="4" t="str">
+        <f>IF(COUNTA(B183:X183)=0,"",AVERAGE(B183:X183))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="184" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A184" s="2"/>
       <c r="B184" s="3"/>
       <c r="C184" s="3"/>
@@ -12482,13 +12331,12 @@
       <c r="V184" s="3"/>
       <c r="W184" s="3"/>
       <c r="X184" s="3"/>
-      <c r="Y184" s="3"/>
-      <c r="Z184" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="185" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y184" s="4" t="str">
+        <f>IF(COUNTA(B184:X184)=0,"",AVERAGE(B184:X184))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="185" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A185" s="2"/>
       <c r="B185" s="3"/>
       <c r="C185" s="3"/>
@@ -12513,13 +12361,12 @@
       <c r="V185" s="3"/>
       <c r="W185" s="3"/>
       <c r="X185" s="3"/>
-      <c r="Y185" s="3"/>
-      <c r="Z185" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="186" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y185" s="4" t="str">
+        <f>IF(COUNTA(B185:X185)=0,"",AVERAGE(B185:X185))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="186" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A186" s="2"/>
       <c r="B186" s="3"/>
       <c r="C186" s="3"/>
@@ -12544,13 +12391,12 @@
       <c r="V186" s="3"/>
       <c r="W186" s="3"/>
       <c r="X186" s="3"/>
-      <c r="Y186" s="3"/>
-      <c r="Z186" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="187" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y186" s="4" t="str">
+        <f>IF(COUNTA(B186:X186)=0,"",AVERAGE(B186:X186))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="187" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A187" s="2"/>
       <c r="B187" s="3"/>
       <c r="C187" s="3"/>
@@ -12575,13 +12421,12 @@
       <c r="V187" s="3"/>
       <c r="W187" s="3"/>
       <c r="X187" s="3"/>
-      <c r="Y187" s="3"/>
-      <c r="Z187" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="188" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y187" s="4" t="str">
+        <f>IF(COUNTA(B187:X187)=0,"",AVERAGE(B187:X187))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="188" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A188" s="2"/>
       <c r="B188" s="3"/>
       <c r="C188" s="3"/>
@@ -12606,13 +12451,12 @@
       <c r="V188" s="3"/>
       <c r="W188" s="3"/>
       <c r="X188" s="3"/>
-      <c r="Y188" s="3"/>
-      <c r="Z188" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="189" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y188" s="4" t="str">
+        <f>IF(COUNTA(B188:X188)=0,"",AVERAGE(B188:X188))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="189" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A189" s="2"/>
       <c r="B189" s="3"/>
       <c r="C189" s="3"/>
@@ -12637,13 +12481,12 @@
       <c r="V189" s="3"/>
       <c r="W189" s="3"/>
       <c r="X189" s="3"/>
-      <c r="Y189" s="3"/>
-      <c r="Z189" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="190" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y189" s="4" t="str">
+        <f>IF(COUNTA(B189:X189)=0,"",AVERAGE(B189:X189))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="190" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A190" s="2"/>
       <c r="B190" s="3"/>
       <c r="C190" s="3"/>
@@ -12668,13 +12511,12 @@
       <c r="V190" s="3"/>
       <c r="W190" s="3"/>
       <c r="X190" s="3"/>
-      <c r="Y190" s="3"/>
-      <c r="Z190" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="191" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y190" s="4" t="str">
+        <f>IF(COUNTA(B190:X190)=0,"",AVERAGE(B190:X190))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="191" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A191" s="2"/>
       <c r="B191" s="3"/>
       <c r="C191" s="3"/>
@@ -12699,13 +12541,12 @@
       <c r="V191" s="3"/>
       <c r="W191" s="3"/>
       <c r="X191" s="3"/>
-      <c r="Y191" s="3"/>
-      <c r="Z191" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="192" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y191" s="4" t="str">
+        <f>IF(COUNTA(B191:X191)=0,"",AVERAGE(B191:X191))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="192" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A192" s="2"/>
       <c r="B192" s="3"/>
       <c r="C192" s="3"/>
@@ -12730,13 +12571,12 @@
       <c r="V192" s="3"/>
       <c r="W192" s="3"/>
       <c r="X192" s="3"/>
-      <c r="Y192" s="3"/>
-      <c r="Z192" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="193" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y192" s="4" t="str">
+        <f>IF(COUNTA(B192:X192)=0,"",AVERAGE(B192:X192))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="193" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A193" s="2"/>
       <c r="B193" s="3"/>
       <c r="C193" s="3"/>
@@ -12761,13 +12601,12 @@
       <c r="V193" s="3"/>
       <c r="W193" s="3"/>
       <c r="X193" s="3"/>
-      <c r="Y193" s="3"/>
-      <c r="Z193" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="194" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y193" s="4" t="str">
+        <f>IF(COUNTA(B193:X193)=0,"",AVERAGE(B193:X193))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="194" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A194" s="2"/>
       <c r="B194" s="3"/>
       <c r="C194" s="3"/>
@@ -12792,13 +12631,12 @@
       <c r="V194" s="3"/>
       <c r="W194" s="3"/>
       <c r="X194" s="3"/>
-      <c r="Y194" s="3"/>
-      <c r="Z194" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="195" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y194" s="4" t="str">
+        <f>IF(COUNTA(B194:X194)=0,"",AVERAGE(B194:X194))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="195" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A195" s="2"/>
       <c r="B195" s="3"/>
       <c r="C195" s="3"/>
@@ -12823,13 +12661,12 @@
       <c r="V195" s="3"/>
       <c r="W195" s="3"/>
       <c r="X195" s="3"/>
-      <c r="Y195" s="3"/>
-      <c r="Z195" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="196" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y195" s="4" t="str">
+        <f>IF(COUNTA(B195:X195)=0,"",AVERAGE(B195:X195))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="196" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A196" s="2"/>
       <c r="B196" s="3"/>
       <c r="C196" s="3"/>
@@ -12854,13 +12691,12 @@
       <c r="V196" s="3"/>
       <c r="W196" s="3"/>
       <c r="X196" s="3"/>
-      <c r="Y196" s="3"/>
-      <c r="Z196" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="197" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y196" s="4" t="str">
+        <f>IF(COUNTA(B196:X196)=0,"",AVERAGE(B196:X196))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="197" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A197" s="2"/>
       <c r="B197" s="3"/>
       <c r="C197" s="3"/>
@@ -12885,13 +12721,12 @@
       <c r="V197" s="3"/>
       <c r="W197" s="3"/>
       <c r="X197" s="3"/>
-      <c r="Y197" s="3"/>
-      <c r="Z197" s="4" t="str">
-        <f t="shared" ref="Z197:Z260" si="4">IF(COUNTA(B197:Y197)=0,"",AVERAGE(B197:Y197))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="198" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y197" s="4" t="str">
+        <f>IF(COUNTA(B197:X197)=0,"",AVERAGE(B197:X197))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="198" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A198" s="2"/>
       <c r="B198" s="3"/>
       <c r="C198" s="3"/>
@@ -12916,13 +12751,12 @@
       <c r="V198" s="3"/>
       <c r="W198" s="3"/>
       <c r="X198" s="3"/>
-      <c r="Y198" s="3"/>
-      <c r="Z198" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="199" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y198" s="4" t="str">
+        <f>IF(COUNTA(B198:X198)=0,"",AVERAGE(B198:X198))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="199" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A199" s="2"/>
       <c r="B199" s="3"/>
       <c r="C199" s="3"/>
@@ -12947,13 +12781,12 @@
       <c r="V199" s="3"/>
       <c r="W199" s="3"/>
       <c r="X199" s="3"/>
-      <c r="Y199" s="3"/>
-      <c r="Z199" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="200" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y199" s="4" t="str">
+        <f>IF(COUNTA(B199:X199)=0,"",AVERAGE(B199:X199))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="200" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A200" s="2"/>
       <c r="B200" s="3"/>
       <c r="C200" s="3"/>
@@ -12978,13 +12811,12 @@
       <c r="V200" s="3"/>
       <c r="W200" s="3"/>
       <c r="X200" s="3"/>
-      <c r="Y200" s="3"/>
-      <c r="Z200" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="201" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y200" s="4" t="str">
+        <f>IF(COUNTA(B200:X200)=0,"",AVERAGE(B200:X200))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="201" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A201" s="2"/>
       <c r="B201" s="3"/>
       <c r="C201" s="3"/>
@@ -13009,13 +12841,12 @@
       <c r="V201" s="3"/>
       <c r="W201" s="3"/>
       <c r="X201" s="3"/>
-      <c r="Y201" s="3"/>
-      <c r="Z201" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="202" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y201" s="4" t="str">
+        <f>IF(COUNTA(B201:X201)=0,"",AVERAGE(B201:X201))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="202" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A202" s="2"/>
       <c r="B202" s="3"/>
       <c r="C202" s="3"/>
@@ -13040,13 +12871,12 @@
       <c r="V202" s="3"/>
       <c r="W202" s="3"/>
       <c r="X202" s="3"/>
-      <c r="Y202" s="3"/>
-      <c r="Z202" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="203" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y202" s="4" t="str">
+        <f>IF(COUNTA(B202:X202)=0,"",AVERAGE(B202:X202))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="203" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A203" s="2"/>
       <c r="B203" s="3"/>
       <c r="C203" s="3"/>
@@ -13071,13 +12901,12 @@
       <c r="V203" s="3"/>
       <c r="W203" s="3"/>
       <c r="X203" s="3"/>
-      <c r="Y203" s="3"/>
-      <c r="Z203" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="204" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y203" s="4" t="str">
+        <f>IF(COUNTA(B203:X203)=0,"",AVERAGE(B203:X203))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="204" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A204" s="2"/>
       <c r="B204" s="3"/>
       <c r="C204" s="3"/>
@@ -13102,13 +12931,12 @@
       <c r="V204" s="3"/>
       <c r="W204" s="3"/>
       <c r="X204" s="3"/>
-      <c r="Y204" s="3"/>
-      <c r="Z204" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="205" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y204" s="4" t="str">
+        <f>IF(COUNTA(B204:X204)=0,"",AVERAGE(B204:X204))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="205" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A205" s="2"/>
       <c r="B205" s="3"/>
       <c r="C205" s="3"/>
@@ -13133,13 +12961,12 @@
       <c r="V205" s="3"/>
       <c r="W205" s="3"/>
       <c r="X205" s="3"/>
-      <c r="Y205" s="3"/>
-      <c r="Z205" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="206" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y205" s="4" t="str">
+        <f>IF(COUNTA(B205:X205)=0,"",AVERAGE(B205:X205))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="206" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A206" s="2"/>
       <c r="B206" s="3"/>
       <c r="C206" s="3"/>
@@ -13164,13 +12991,12 @@
       <c r="V206" s="3"/>
       <c r="W206" s="3"/>
       <c r="X206" s="3"/>
-      <c r="Y206" s="3"/>
-      <c r="Z206" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="207" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y206" s="4" t="str">
+        <f>IF(COUNTA(B206:X206)=0,"",AVERAGE(B206:X206))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="207" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A207" s="2"/>
       <c r="B207" s="3"/>
       <c r="C207" s="3"/>
@@ -13195,13 +13021,12 @@
       <c r="V207" s="3"/>
       <c r="W207" s="3"/>
       <c r="X207" s="3"/>
-      <c r="Y207" s="3"/>
-      <c r="Z207" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="208" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y207" s="4" t="str">
+        <f>IF(COUNTA(B207:X207)=0,"",AVERAGE(B207:X207))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="208" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A208" s="2"/>
       <c r="B208" s="3"/>
       <c r="C208" s="3"/>
@@ -13226,13 +13051,12 @@
       <c r="V208" s="3"/>
       <c r="W208" s="3"/>
       <c r="X208" s="3"/>
-      <c r="Y208" s="3"/>
-      <c r="Z208" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="209" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y208" s="4" t="str">
+        <f>IF(COUNTA(B208:X208)=0,"",AVERAGE(B208:X208))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="209" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A209" s="2"/>
       <c r="B209" s="3"/>
       <c r="C209" s="3"/>
@@ -13257,13 +13081,12 @@
       <c r="V209" s="3"/>
       <c r="W209" s="3"/>
       <c r="X209" s="3"/>
-      <c r="Y209" s="3"/>
-      <c r="Z209" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="210" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y209" s="4" t="str">
+        <f>IF(COUNTA(B209:X209)=0,"",AVERAGE(B209:X209))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="210" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A210" s="2"/>
       <c r="B210" s="3"/>
       <c r="C210" s="3"/>
@@ -13288,13 +13111,12 @@
       <c r="V210" s="3"/>
       <c r="W210" s="3"/>
       <c r="X210" s="3"/>
-      <c r="Y210" s="3"/>
-      <c r="Z210" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="211" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y210" s="4" t="str">
+        <f>IF(COUNTA(B210:X210)=0,"",AVERAGE(B210:X210))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="211" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A211" s="2"/>
       <c r="B211" s="3"/>
       <c r="C211" s="3"/>
@@ -13319,13 +13141,12 @@
       <c r="V211" s="3"/>
       <c r="W211" s="3"/>
       <c r="X211" s="3"/>
-      <c r="Y211" s="3"/>
-      <c r="Z211" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="212" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y211" s="4" t="str">
+        <f>IF(COUNTA(B211:X211)=0,"",AVERAGE(B211:X211))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="212" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A212" s="2"/>
       <c r="B212" s="3"/>
       <c r="C212" s="3"/>
@@ -13350,13 +13171,12 @@
       <c r="V212" s="3"/>
       <c r="W212" s="3"/>
       <c r="X212" s="3"/>
-      <c r="Y212" s="3"/>
-      <c r="Z212" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="213" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y212" s="4" t="str">
+        <f>IF(COUNTA(B212:X212)=0,"",AVERAGE(B212:X212))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="213" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A213" s="2"/>
       <c r="B213" s="3"/>
       <c r="C213" s="3"/>
@@ -13381,13 +13201,12 @@
       <c r="V213" s="3"/>
       <c r="W213" s="3"/>
       <c r="X213" s="3"/>
-      <c r="Y213" s="3"/>
-      <c r="Z213" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="214" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y213" s="4" t="str">
+        <f>IF(COUNTA(B213:X213)=0,"",AVERAGE(B213:X213))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="214" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A214" s="2"/>
       <c r="B214" s="3"/>
       <c r="C214" s="3"/>
@@ -13412,13 +13231,12 @@
       <c r="V214" s="3"/>
       <c r="W214" s="3"/>
       <c r="X214" s="3"/>
-      <c r="Y214" s="3"/>
-      <c r="Z214" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="215" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y214" s="4" t="str">
+        <f>IF(COUNTA(B214:X214)=0,"",AVERAGE(B214:X214))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="215" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A215" s="2"/>
       <c r="B215" s="3"/>
       <c r="C215" s="3"/>
@@ -13443,13 +13261,12 @@
       <c r="V215" s="3"/>
       <c r="W215" s="3"/>
       <c r="X215" s="3"/>
-      <c r="Y215" s="3"/>
-      <c r="Z215" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="216" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y215" s="4" t="str">
+        <f>IF(COUNTA(B215:X215)=0,"",AVERAGE(B215:X215))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="216" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A216" s="2"/>
       <c r="B216" s="3"/>
       <c r="C216" s="3"/>
@@ -13474,13 +13291,12 @@
       <c r="V216" s="3"/>
       <c r="W216" s="3"/>
       <c r="X216" s="3"/>
-      <c r="Y216" s="3"/>
-      <c r="Z216" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="217" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y216" s="4" t="str">
+        <f>IF(COUNTA(B216:X216)=0,"",AVERAGE(B216:X216))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="217" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A217" s="2"/>
       <c r="B217" s="3"/>
       <c r="C217" s="3"/>
@@ -13505,13 +13321,12 @@
       <c r="V217" s="3"/>
       <c r="W217" s="3"/>
       <c r="X217" s="3"/>
-      <c r="Y217" s="3"/>
-      <c r="Z217" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="218" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y217" s="4" t="str">
+        <f>IF(COUNTA(B217:X217)=0,"",AVERAGE(B217:X217))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="218" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A218" s="2"/>
       <c r="B218" s="3"/>
       <c r="C218" s="3"/>
@@ -13536,13 +13351,12 @@
       <c r="V218" s="3"/>
       <c r="W218" s="3"/>
       <c r="X218" s="3"/>
-      <c r="Y218" s="3"/>
-      <c r="Z218" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="219" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y218" s="4" t="str">
+        <f>IF(COUNTA(B218:X218)=0,"",AVERAGE(B218:X218))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="219" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A219" s="2"/>
       <c r="B219" s="3"/>
       <c r="C219" s="3"/>
@@ -13567,13 +13381,12 @@
       <c r="V219" s="3"/>
       <c r="W219" s="3"/>
       <c r="X219" s="3"/>
-      <c r="Y219" s="3"/>
-      <c r="Z219" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="220" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y219" s="4" t="str">
+        <f>IF(COUNTA(B219:X219)=0,"",AVERAGE(B219:X219))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="220" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A220" s="2"/>
       <c r="B220" s="3"/>
       <c r="C220" s="3"/>
@@ -13598,13 +13411,12 @@
       <c r="V220" s="3"/>
       <c r="W220" s="3"/>
       <c r="X220" s="3"/>
-      <c r="Y220" s="3"/>
-      <c r="Z220" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="221" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y220" s="4" t="str">
+        <f>IF(COUNTA(B220:X220)=0,"",AVERAGE(B220:X220))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="221" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A221" s="2"/>
       <c r="B221" s="3"/>
       <c r="C221" s="3"/>
@@ -13629,13 +13441,12 @@
       <c r="V221" s="3"/>
       <c r="W221" s="3"/>
       <c r="X221" s="3"/>
-      <c r="Y221" s="3"/>
-      <c r="Z221" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="222" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y221" s="4" t="str">
+        <f>IF(COUNTA(B221:X221)=0,"",AVERAGE(B221:X221))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="222" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A222" s="2"/>
       <c r="B222" s="3"/>
       <c r="C222" s="3"/>
@@ -13660,13 +13471,12 @@
       <c r="V222" s="3"/>
       <c r="W222" s="3"/>
       <c r="X222" s="3"/>
-      <c r="Y222" s="3"/>
-      <c r="Z222" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="223" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y222" s="4" t="str">
+        <f>IF(COUNTA(B222:X222)=0,"",AVERAGE(B222:X222))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="223" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A223" s="2"/>
       <c r="B223" s="3"/>
       <c r="C223" s="3"/>
@@ -13691,13 +13501,12 @@
       <c r="V223" s="3"/>
       <c r="W223" s="3"/>
       <c r="X223" s="3"/>
-      <c r="Y223" s="3"/>
-      <c r="Z223" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="224" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y223" s="4" t="str">
+        <f>IF(COUNTA(B223:X223)=0,"",AVERAGE(B223:X223))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="224" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A224" s="2"/>
       <c r="B224" s="3"/>
       <c r="C224" s="3"/>
@@ -13722,13 +13531,12 @@
       <c r="V224" s="3"/>
       <c r="W224" s="3"/>
       <c r="X224" s="3"/>
-      <c r="Y224" s="3"/>
-      <c r="Z224" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="225" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y224" s="4" t="str">
+        <f>IF(COUNTA(B224:X224)=0,"",AVERAGE(B224:X224))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="225" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A225" s="2"/>
       <c r="B225" s="3"/>
       <c r="C225" s="3"/>
@@ -13753,13 +13561,12 @@
       <c r="V225" s="3"/>
       <c r="W225" s="3"/>
       <c r="X225" s="3"/>
-      <c r="Y225" s="3"/>
-      <c r="Z225" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="226" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y225" s="4" t="str">
+        <f>IF(COUNTA(B225:X225)=0,"",AVERAGE(B225:X225))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="226" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A226" s="2"/>
       <c r="B226" s="3"/>
       <c r="C226" s="3"/>
@@ -13784,13 +13591,12 @@
       <c r="V226" s="3"/>
       <c r="W226" s="3"/>
       <c r="X226" s="3"/>
-      <c r="Y226" s="3"/>
-      <c r="Z226" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="227" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y226" s="4" t="str">
+        <f>IF(COUNTA(B226:X226)=0,"",AVERAGE(B226:X226))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="227" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A227" s="2"/>
       <c r="B227" s="3"/>
       <c r="C227" s="3"/>
@@ -13815,13 +13621,12 @@
       <c r="V227" s="3"/>
       <c r="W227" s="3"/>
       <c r="X227" s="3"/>
-      <c r="Y227" s="3"/>
-      <c r="Z227" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="228" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y227" s="4" t="str">
+        <f>IF(COUNTA(B227:X227)=0,"",AVERAGE(B227:X227))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="228" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A228" s="2"/>
       <c r="B228" s="3"/>
       <c r="C228" s="3"/>
@@ -13846,13 +13651,12 @@
       <c r="V228" s="3"/>
       <c r="W228" s="3"/>
       <c r="X228" s="3"/>
-      <c r="Y228" s="3"/>
-      <c r="Z228" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="229" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y228" s="4" t="str">
+        <f>IF(COUNTA(B228:X228)=0,"",AVERAGE(B228:X228))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="229" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A229" s="2"/>
       <c r="B229" s="3"/>
       <c r="C229" s="3"/>
@@ -13877,13 +13681,12 @@
       <c r="V229" s="3"/>
       <c r="W229" s="3"/>
       <c r="X229" s="3"/>
-      <c r="Y229" s="3"/>
-      <c r="Z229" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="230" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y229" s="4" t="str">
+        <f>IF(COUNTA(B229:X229)=0,"",AVERAGE(B229:X229))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="230" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A230" s="2"/>
       <c r="B230" s="3"/>
       <c r="C230" s="3"/>
@@ -13908,13 +13711,12 @@
       <c r="V230" s="3"/>
       <c r="W230" s="3"/>
       <c r="X230" s="3"/>
-      <c r="Y230" s="3"/>
-      <c r="Z230" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="231" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y230" s="4" t="str">
+        <f>IF(COUNTA(B230:X230)=0,"",AVERAGE(B230:X230))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="231" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A231" s="2"/>
       <c r="B231" s="3"/>
       <c r="C231" s="3"/>
@@ -13939,13 +13741,12 @@
       <c r="V231" s="3"/>
       <c r="W231" s="3"/>
       <c r="X231" s="3"/>
-      <c r="Y231" s="3"/>
-      <c r="Z231" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="232" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y231" s="4" t="str">
+        <f>IF(COUNTA(B231:X231)=0,"",AVERAGE(B231:X231))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="232" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A232" s="2"/>
       <c r="B232" s="3"/>
       <c r="C232" s="3"/>
@@ -13970,13 +13771,12 @@
       <c r="V232" s="3"/>
       <c r="W232" s="3"/>
       <c r="X232" s="3"/>
-      <c r="Y232" s="3"/>
-      <c r="Z232" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="233" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y232" s="4" t="str">
+        <f>IF(COUNTA(B232:X232)=0,"",AVERAGE(B232:X232))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="233" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A233" s="2"/>
       <c r="B233" s="3"/>
       <c r="C233" s="3"/>
@@ -14001,13 +13801,12 @@
       <c r="V233" s="3"/>
       <c r="W233" s="3"/>
       <c r="X233" s="3"/>
-      <c r="Y233" s="3"/>
-      <c r="Z233" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="234" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y233" s="4" t="str">
+        <f>IF(COUNTA(B233:X233)=0,"",AVERAGE(B233:X233))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="234" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A234" s="2"/>
       <c r="B234" s="3"/>
       <c r="C234" s="3"/>
@@ -14032,13 +13831,12 @@
       <c r="V234" s="3"/>
       <c r="W234" s="3"/>
       <c r="X234" s="3"/>
-      <c r="Y234" s="3"/>
-      <c r="Z234" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="235" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y234" s="4" t="str">
+        <f>IF(COUNTA(B234:X234)=0,"",AVERAGE(B234:X234))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="235" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A235" s="2"/>
       <c r="B235" s="3"/>
       <c r="C235" s="3"/>
@@ -14063,13 +13861,12 @@
       <c r="V235" s="3"/>
       <c r="W235" s="3"/>
       <c r="X235" s="3"/>
-      <c r="Y235" s="3"/>
-      <c r="Z235" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="236" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y235" s="4" t="str">
+        <f>IF(COUNTA(B235:X235)=0,"",AVERAGE(B235:X235))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="236" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A236" s="2"/>
       <c r="B236" s="3"/>
       <c r="C236" s="3"/>
@@ -14094,13 +13891,12 @@
       <c r="V236" s="3"/>
       <c r="W236" s="3"/>
       <c r="X236" s="3"/>
-      <c r="Y236" s="3"/>
-      <c r="Z236" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="237" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y236" s="4" t="str">
+        <f>IF(COUNTA(B236:X236)=0,"",AVERAGE(B236:X236))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="237" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A237" s="2"/>
       <c r="B237" s="3"/>
       <c r="C237" s="3"/>
@@ -14125,13 +13921,12 @@
       <c r="V237" s="3"/>
       <c r="W237" s="3"/>
       <c r="X237" s="3"/>
-      <c r="Y237" s="3"/>
-      <c r="Z237" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="238" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y237" s="4" t="str">
+        <f>IF(COUNTA(B237:X237)=0,"",AVERAGE(B237:X237))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="238" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A238" s="2"/>
       <c r="B238" s="3"/>
       <c r="C238" s="3"/>
@@ -14156,13 +13951,12 @@
       <c r="V238" s="3"/>
       <c r="W238" s="3"/>
       <c r="X238" s="3"/>
-      <c r="Y238" s="3"/>
-      <c r="Z238" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="239" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y238" s="4" t="str">
+        <f>IF(COUNTA(B238:X238)=0,"",AVERAGE(B238:X238))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="239" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A239" s="2"/>
       <c r="B239" s="3"/>
       <c r="C239" s="3"/>
@@ -14187,13 +13981,12 @@
       <c r="V239" s="3"/>
       <c r="W239" s="3"/>
       <c r="X239" s="3"/>
-      <c r="Y239" s="3"/>
-      <c r="Z239" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="240" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y239" s="4" t="str">
+        <f>IF(COUNTA(B239:X239)=0,"",AVERAGE(B239:X239))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="240" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A240" s="2"/>
       <c r="B240" s="3"/>
       <c r="C240" s="3"/>
@@ -14218,13 +14011,12 @@
       <c r="V240" s="3"/>
       <c r="W240" s="3"/>
       <c r="X240" s="3"/>
-      <c r="Y240" s="3"/>
-      <c r="Z240" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="241" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y240" s="4" t="str">
+        <f>IF(COUNTA(B240:X240)=0,"",AVERAGE(B240:X240))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="241" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A241" s="2"/>
       <c r="B241" s="3"/>
       <c r="C241" s="3"/>
@@ -14249,13 +14041,12 @@
       <c r="V241" s="3"/>
       <c r="W241" s="3"/>
       <c r="X241" s="3"/>
-      <c r="Y241" s="3"/>
-      <c r="Z241" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="242" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y241" s="4" t="str">
+        <f>IF(COUNTA(B241:X241)=0,"",AVERAGE(B241:X241))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="242" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A242" s="2"/>
       <c r="B242" s="3"/>
       <c r="C242" s="3"/>
@@ -14280,13 +14071,12 @@
       <c r="V242" s="3"/>
       <c r="W242" s="3"/>
       <c r="X242" s="3"/>
-      <c r="Y242" s="3"/>
-      <c r="Z242" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="243" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y242" s="4" t="str">
+        <f>IF(COUNTA(B242:X242)=0,"",AVERAGE(B242:X242))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="243" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A243" s="2"/>
       <c r="B243" s="3"/>
       <c r="C243" s="3"/>
@@ -14311,13 +14101,12 @@
       <c r="V243" s="3"/>
       <c r="W243" s="3"/>
       <c r="X243" s="3"/>
-      <c r="Y243" s="3"/>
-      <c r="Z243" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="244" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y243" s="4" t="str">
+        <f>IF(COUNTA(B243:X243)=0,"",AVERAGE(B243:X243))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="244" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A244" s="2"/>
       <c r="B244" s="3"/>
       <c r="C244" s="3"/>
@@ -14342,13 +14131,12 @@
       <c r="V244" s="3"/>
       <c r="W244" s="3"/>
       <c r="X244" s="3"/>
-      <c r="Y244" s="3"/>
-      <c r="Z244" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="245" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y244" s="4" t="str">
+        <f>IF(COUNTA(B244:X244)=0,"",AVERAGE(B244:X244))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="245" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A245" s="2"/>
       <c r="B245" s="3"/>
       <c r="C245" s="3"/>
@@ -14373,13 +14161,12 @@
       <c r="V245" s="3"/>
       <c r="W245" s="3"/>
       <c r="X245" s="3"/>
-      <c r="Y245" s="3"/>
-      <c r="Z245" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="246" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y245" s="4" t="str">
+        <f>IF(COUNTA(B245:X245)=0,"",AVERAGE(B245:X245))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="246" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A246" s="2"/>
       <c r="B246" s="3"/>
       <c r="C246" s="3"/>
@@ -14404,13 +14191,12 @@
       <c r="V246" s="3"/>
       <c r="W246" s="3"/>
       <c r="X246" s="3"/>
-      <c r="Y246" s="3"/>
-      <c r="Z246" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="247" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y246" s="4" t="str">
+        <f>IF(COUNTA(B246:X246)=0,"",AVERAGE(B246:X246))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="247" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A247" s="2"/>
       <c r="B247" s="3"/>
       <c r="C247" s="3"/>
@@ -14435,13 +14221,12 @@
       <c r="V247" s="3"/>
       <c r="W247" s="3"/>
       <c r="X247" s="3"/>
-      <c r="Y247" s="3"/>
-      <c r="Z247" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="248" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y247" s="4" t="str">
+        <f>IF(COUNTA(B247:X247)=0,"",AVERAGE(B247:X247))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="248" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A248" s="2"/>
       <c r="B248" s="3"/>
       <c r="C248" s="3"/>
@@ -14466,13 +14251,12 @@
       <c r="V248" s="3"/>
       <c r="W248" s="3"/>
       <c r="X248" s="3"/>
-      <c r="Y248" s="3"/>
-      <c r="Z248" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="249" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y248" s="4" t="str">
+        <f>IF(COUNTA(B248:X248)=0,"",AVERAGE(B248:X248))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="249" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A249" s="2"/>
       <c r="B249" s="3"/>
       <c r="C249" s="3"/>
@@ -14497,13 +14281,12 @@
       <c r="V249" s="3"/>
       <c r="W249" s="3"/>
       <c r="X249" s="3"/>
-      <c r="Y249" s="3"/>
-      <c r="Z249" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="250" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y249" s="4" t="str">
+        <f>IF(COUNTA(B249:X249)=0,"",AVERAGE(B249:X249))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="250" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A250" s="2"/>
       <c r="B250" s="3"/>
       <c r="C250" s="3"/>
@@ -14528,13 +14311,12 @@
       <c r="V250" s="3"/>
       <c r="W250" s="3"/>
       <c r="X250" s="3"/>
-      <c r="Y250" s="3"/>
-      <c r="Z250" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="251" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y250" s="4" t="str">
+        <f>IF(COUNTA(B250:X250)=0,"",AVERAGE(B250:X250))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="251" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A251" s="2"/>
       <c r="B251" s="3"/>
       <c r="C251" s="3"/>
@@ -14559,13 +14341,12 @@
       <c r="V251" s="3"/>
       <c r="W251" s="3"/>
       <c r="X251" s="3"/>
-      <c r="Y251" s="3"/>
-      <c r="Z251" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="252" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y251" s="4" t="str">
+        <f>IF(COUNTA(B251:X251)=0,"",AVERAGE(B251:X251))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="252" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A252" s="2"/>
       <c r="B252" s="3"/>
       <c r="C252" s="3"/>
@@ -14590,13 +14371,12 @@
       <c r="V252" s="3"/>
       <c r="W252" s="3"/>
       <c r="X252" s="3"/>
-      <c r="Y252" s="3"/>
-      <c r="Z252" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="253" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y252" s="4" t="str">
+        <f>IF(COUNTA(B252:X252)=0,"",AVERAGE(B252:X252))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="253" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A253" s="2"/>
       <c r="B253" s="3"/>
       <c r="C253" s="3"/>
@@ -14621,13 +14401,12 @@
       <c r="V253" s="3"/>
       <c r="W253" s="3"/>
       <c r="X253" s="3"/>
-      <c r="Y253" s="3"/>
-      <c r="Z253" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="254" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y253" s="4" t="str">
+        <f>IF(COUNTA(B253:X253)=0,"",AVERAGE(B253:X253))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="254" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A254" s="2"/>
       <c r="B254" s="3"/>
       <c r="C254" s="3"/>
@@ -14652,13 +14431,12 @@
       <c r="V254" s="3"/>
       <c r="W254" s="3"/>
       <c r="X254" s="3"/>
-      <c r="Y254" s="3"/>
-      <c r="Z254" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="255" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y254" s="4" t="str">
+        <f>IF(COUNTA(B254:X254)=0,"",AVERAGE(B254:X254))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="255" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A255" s="2"/>
       <c r="B255" s="3"/>
       <c r="C255" s="3"/>
@@ -14683,13 +14461,12 @@
       <c r="V255" s="3"/>
       <c r="W255" s="3"/>
       <c r="X255" s="3"/>
-      <c r="Y255" s="3"/>
-      <c r="Z255" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="256" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y255" s="4" t="str">
+        <f>IF(COUNTA(B255:X255)=0,"",AVERAGE(B255:X255))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="256" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A256" s="2"/>
       <c r="B256" s="3"/>
       <c r="C256" s="3"/>
@@ -14714,13 +14491,12 @@
       <c r="V256" s="3"/>
       <c r="W256" s="3"/>
       <c r="X256" s="3"/>
-      <c r="Y256" s="3"/>
-      <c r="Z256" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="257" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y256" s="4" t="str">
+        <f>IF(COUNTA(B256:X256)=0,"",AVERAGE(B256:X256))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="257" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A257" s="2"/>
       <c r="B257" s="3"/>
       <c r="C257" s="3"/>
@@ -14745,13 +14521,12 @@
       <c r="V257" s="3"/>
       <c r="W257" s="3"/>
       <c r="X257" s="3"/>
-      <c r="Y257" s="3"/>
-      <c r="Z257" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="258" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y257" s="4" t="str">
+        <f>IF(COUNTA(B257:X257)=0,"",AVERAGE(B257:X257))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="258" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A258" s="2"/>
       <c r="B258" s="3"/>
       <c r="C258" s="3"/>
@@ -14776,13 +14551,12 @@
       <c r="V258" s="3"/>
       <c r="W258" s="3"/>
       <c r="X258" s="3"/>
-      <c r="Y258" s="3"/>
-      <c r="Z258" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="259" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y258" s="4" t="str">
+        <f>IF(COUNTA(B258:X258)=0,"",AVERAGE(B258:X258))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="259" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A259" s="2"/>
       <c r="B259" s="3"/>
       <c r="C259" s="3"/>
@@ -14807,13 +14581,12 @@
       <c r="V259" s="3"/>
       <c r="W259" s="3"/>
       <c r="X259" s="3"/>
-      <c r="Y259" s="3"/>
-      <c r="Z259" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="260" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y259" s="4" t="str">
+        <f>IF(COUNTA(B259:X259)=0,"",AVERAGE(B259:X259))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="260" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A260" s="2"/>
       <c r="B260" s="3"/>
       <c r="C260" s="3"/>
@@ -14838,13 +14611,12 @@
       <c r="V260" s="3"/>
       <c r="W260" s="3"/>
       <c r="X260" s="3"/>
-      <c r="Y260" s="3"/>
-      <c r="Z260" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="261" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y260" s="4" t="str">
+        <f>IF(COUNTA(B260:X260)=0,"",AVERAGE(B260:X260))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="261" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A261" s="2"/>
       <c r="B261" s="3"/>
       <c r="C261" s="3"/>
@@ -14869,13 +14641,12 @@
       <c r="V261" s="3"/>
       <c r="W261" s="3"/>
       <c r="X261" s="3"/>
-      <c r="Y261" s="3"/>
-      <c r="Z261" s="4" t="str">
-        <f t="shared" ref="Z261:Z324" si="5">IF(COUNTA(B261:Y261)=0,"",AVERAGE(B261:Y261))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="262" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y261" s="4" t="str">
+        <f>IF(COUNTA(B261:X261)=0,"",AVERAGE(B261:X261))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="262" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A262" s="2"/>
       <c r="B262" s="3"/>
       <c r="C262" s="3"/>
@@ -14900,13 +14671,12 @@
       <c r="V262" s="3"/>
       <c r="W262" s="3"/>
       <c r="X262" s="3"/>
-      <c r="Y262" s="3"/>
-      <c r="Z262" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="263" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y262" s="4" t="str">
+        <f>IF(COUNTA(B262:X262)=0,"",AVERAGE(B262:X262))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="263" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A263" s="2"/>
       <c r="B263" s="3"/>
       <c r="C263" s="3"/>
@@ -14931,13 +14701,12 @@
       <c r="V263" s="3"/>
       <c r="W263" s="3"/>
       <c r="X263" s="3"/>
-      <c r="Y263" s="3"/>
-      <c r="Z263" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="264" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y263" s="4" t="str">
+        <f>IF(COUNTA(B263:X263)=0,"",AVERAGE(B263:X263))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="264" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A264" s="2"/>
       <c r="B264" s="3"/>
       <c r="C264" s="3"/>
@@ -14962,13 +14731,12 @@
       <c r="V264" s="3"/>
       <c r="W264" s="3"/>
       <c r="X264" s="3"/>
-      <c r="Y264" s="3"/>
-      <c r="Z264" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="265" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y264" s="4" t="str">
+        <f>IF(COUNTA(B264:X264)=0,"",AVERAGE(B264:X264))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="265" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A265" s="2"/>
       <c r="B265" s="3"/>
       <c r="C265" s="3"/>
@@ -14993,13 +14761,12 @@
       <c r="V265" s="3"/>
       <c r="W265" s="3"/>
       <c r="X265" s="3"/>
-      <c r="Y265" s="3"/>
-      <c r="Z265" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="266" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y265" s="4" t="str">
+        <f>IF(COUNTA(B265:X265)=0,"",AVERAGE(B265:X265))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="266" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A266" s="2"/>
       <c r="B266" s="3"/>
       <c r="C266" s="3"/>
@@ -15024,13 +14791,12 @@
       <c r="V266" s="3"/>
       <c r="W266" s="3"/>
       <c r="X266" s="3"/>
-      <c r="Y266" s="3"/>
-      <c r="Z266" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="267" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y266" s="4" t="str">
+        <f>IF(COUNTA(B266:X266)=0,"",AVERAGE(B266:X266))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="267" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A267" s="2"/>
       <c r="B267" s="3"/>
       <c r="C267" s="3"/>
@@ -15055,13 +14821,12 @@
       <c r="V267" s="3"/>
       <c r="W267" s="3"/>
       <c r="X267" s="3"/>
-      <c r="Y267" s="3"/>
-      <c r="Z267" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="268" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y267" s="4" t="str">
+        <f>IF(COUNTA(B267:X267)=0,"",AVERAGE(B267:X267))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="268" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A268" s="2"/>
       <c r="B268" s="3"/>
       <c r="C268" s="3"/>
@@ -15086,13 +14851,12 @@
       <c r="V268" s="3"/>
       <c r="W268" s="3"/>
       <c r="X268" s="3"/>
-      <c r="Y268" s="3"/>
-      <c r="Z268" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="269" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y268" s="4" t="str">
+        <f>IF(COUNTA(B268:X268)=0,"",AVERAGE(B268:X268))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="269" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A269" s="2"/>
       <c r="B269" s="3"/>
       <c r="C269" s="3"/>
@@ -15117,13 +14881,12 @@
       <c r="V269" s="3"/>
       <c r="W269" s="3"/>
       <c r="X269" s="3"/>
-      <c r="Y269" s="3"/>
-      <c r="Z269" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="270" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y269" s="4" t="str">
+        <f>IF(COUNTA(B269:X269)=0,"",AVERAGE(B269:X269))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="270" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A270" s="2"/>
       <c r="B270" s="3"/>
       <c r="C270" s="3"/>
@@ -15148,13 +14911,12 @@
       <c r="V270" s="3"/>
       <c r="W270" s="3"/>
       <c r="X270" s="3"/>
-      <c r="Y270" s="3"/>
-      <c r="Z270" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="271" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y270" s="4" t="str">
+        <f>IF(COUNTA(B270:X270)=0,"",AVERAGE(B270:X270))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="271" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A271" s="2"/>
       <c r="B271" s="3"/>
       <c r="C271" s="3"/>
@@ -15179,13 +14941,12 @@
       <c r="V271" s="3"/>
       <c r="W271" s="3"/>
       <c r="X271" s="3"/>
-      <c r="Y271" s="3"/>
-      <c r="Z271" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="272" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y271" s="4" t="str">
+        <f>IF(COUNTA(B271:X271)=0,"",AVERAGE(B271:X271))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="272" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A272" s="2"/>
       <c r="B272" s="3"/>
       <c r="C272" s="3"/>
@@ -15210,13 +14971,12 @@
       <c r="V272" s="3"/>
       <c r="W272" s="3"/>
       <c r="X272" s="3"/>
-      <c r="Y272" s="3"/>
-      <c r="Z272" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="273" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y272" s="4" t="str">
+        <f>IF(COUNTA(B272:X272)=0,"",AVERAGE(B272:X272))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="273" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A273" s="2"/>
       <c r="B273" s="3"/>
       <c r="C273" s="3"/>
@@ -15241,13 +15001,12 @@
       <c r="V273" s="3"/>
       <c r="W273" s="3"/>
       <c r="X273" s="3"/>
-      <c r="Y273" s="3"/>
-      <c r="Z273" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="274" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y273" s="4" t="str">
+        <f>IF(COUNTA(B273:X273)=0,"",AVERAGE(B273:X273))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="274" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A274" s="2"/>
       <c r="B274" s="3"/>
       <c r="C274" s="3"/>
@@ -15272,13 +15031,12 @@
       <c r="V274" s="3"/>
       <c r="W274" s="3"/>
       <c r="X274" s="3"/>
-      <c r="Y274" s="3"/>
-      <c r="Z274" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="275" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y274" s="4" t="str">
+        <f>IF(COUNTA(B274:X274)=0,"",AVERAGE(B274:X274))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="275" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A275" s="2"/>
       <c r="B275" s="3"/>
       <c r="C275" s="3"/>
@@ -15303,13 +15061,12 @@
       <c r="V275" s="3"/>
       <c r="W275" s="3"/>
       <c r="X275" s="3"/>
-      <c r="Y275" s="3"/>
-      <c r="Z275" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="276" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y275" s="4" t="str">
+        <f>IF(COUNTA(B275:X275)=0,"",AVERAGE(B275:X275))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="276" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A276" s="2"/>
       <c r="B276" s="3"/>
       <c r="C276" s="3"/>
@@ -15334,13 +15091,12 @@
       <c r="V276" s="3"/>
       <c r="W276" s="3"/>
       <c r="X276" s="3"/>
-      <c r="Y276" s="3"/>
-      <c r="Z276" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="277" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y276" s="4" t="str">
+        <f>IF(COUNTA(B276:X276)=0,"",AVERAGE(B276:X276))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="277" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A277" s="2"/>
       <c r="B277" s="3"/>
       <c r="C277" s="3"/>
@@ -15365,13 +15121,12 @@
       <c r="V277" s="3"/>
       <c r="W277" s="3"/>
       <c r="X277" s="3"/>
-      <c r="Y277" s="3"/>
-      <c r="Z277" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="278" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y277" s="4" t="str">
+        <f>IF(COUNTA(B277:X277)=0,"",AVERAGE(B277:X277))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="278" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A278" s="2"/>
       <c r="B278" s="3"/>
       <c r="C278" s="3"/>
@@ -15396,13 +15151,12 @@
       <c r="V278" s="3"/>
       <c r="W278" s="3"/>
       <c r="X278" s="3"/>
-      <c r="Y278" s="3"/>
-      <c r="Z278" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="279" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y278" s="4" t="str">
+        <f>IF(COUNTA(B278:X278)=0,"",AVERAGE(B278:X278))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="279" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A279" s="2"/>
       <c r="B279" s="3"/>
       <c r="C279" s="3"/>
@@ -15427,13 +15181,12 @@
       <c r="V279" s="3"/>
       <c r="W279" s="3"/>
       <c r="X279" s="3"/>
-      <c r="Y279" s="3"/>
-      <c r="Z279" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="280" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y279" s="4" t="str">
+        <f>IF(COUNTA(B279:X279)=0,"",AVERAGE(B279:X279))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="280" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A280" s="2"/>
       <c r="B280" s="3"/>
       <c r="C280" s="3"/>
@@ -15458,13 +15211,12 @@
       <c r="V280" s="3"/>
       <c r="W280" s="3"/>
       <c r="X280" s="3"/>
-      <c r="Y280" s="3"/>
-      <c r="Z280" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="281" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y280" s="4" t="str">
+        <f>IF(COUNTA(B280:X280)=0,"",AVERAGE(B280:X280))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="281" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A281" s="2"/>
       <c r="B281" s="3"/>
       <c r="C281" s="3"/>
@@ -15489,13 +15241,12 @@
       <c r="V281" s="3"/>
       <c r="W281" s="3"/>
       <c r="X281" s="3"/>
-      <c r="Y281" s="3"/>
-      <c r="Z281" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="282" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y281" s="4" t="str">
+        <f>IF(COUNTA(B281:X281)=0,"",AVERAGE(B281:X281))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="282" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A282" s="2"/>
       <c r="B282" s="3"/>
       <c r="C282" s="3"/>
@@ -15520,13 +15271,12 @@
       <c r="V282" s="3"/>
       <c r="W282" s="3"/>
       <c r="X282" s="3"/>
-      <c r="Y282" s="3"/>
-      <c r="Z282" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="283" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y282" s="4" t="str">
+        <f>IF(COUNTA(B282:X282)=0,"",AVERAGE(B282:X282))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="283" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A283" s="2"/>
       <c r="B283" s="3"/>
       <c r="C283" s="3"/>
@@ -15551,13 +15301,12 @@
       <c r="V283" s="3"/>
       <c r="W283" s="3"/>
       <c r="X283" s="3"/>
-      <c r="Y283" s="3"/>
-      <c r="Z283" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="284" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y283" s="4" t="str">
+        <f>IF(COUNTA(B283:X283)=0,"",AVERAGE(B283:X283))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="284" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A284" s="2"/>
       <c r="B284" s="3"/>
       <c r="C284" s="3"/>
@@ -15582,13 +15331,12 @@
       <c r="V284" s="3"/>
       <c r="W284" s="3"/>
       <c r="X284" s="3"/>
-      <c r="Y284" s="3"/>
-      <c r="Z284" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="285" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y284" s="4" t="str">
+        <f>IF(COUNTA(B284:X284)=0,"",AVERAGE(B284:X284))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="285" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A285" s="2"/>
       <c r="B285" s="3"/>
       <c r="C285" s="3"/>
@@ -15613,13 +15361,12 @@
       <c r="V285" s="3"/>
       <c r="W285" s="3"/>
       <c r="X285" s="3"/>
-      <c r="Y285" s="3"/>
-      <c r="Z285" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="286" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y285" s="4" t="str">
+        <f>IF(COUNTA(B285:X285)=0,"",AVERAGE(B285:X285))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="286" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A286" s="2"/>
       <c r="B286" s="3"/>
       <c r="C286" s="3"/>
@@ -15644,13 +15391,12 @@
       <c r="V286" s="3"/>
       <c r="W286" s="3"/>
       <c r="X286" s="3"/>
-      <c r="Y286" s="3"/>
-      <c r="Z286" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="287" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y286" s="4" t="str">
+        <f>IF(COUNTA(B286:X286)=0,"",AVERAGE(B286:X286))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="287" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A287" s="2"/>
       <c r="B287" s="3"/>
       <c r="C287" s="3"/>
@@ -15675,13 +15421,12 @@
       <c r="V287" s="3"/>
       <c r="W287" s="3"/>
       <c r="X287" s="3"/>
-      <c r="Y287" s="3"/>
-      <c r="Z287" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="288" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y287" s="4" t="str">
+        <f>IF(COUNTA(B287:X287)=0,"",AVERAGE(B287:X287))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="288" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A288" s="2"/>
       <c r="B288" s="3"/>
       <c r="C288" s="3"/>
@@ -15706,13 +15451,12 @@
       <c r="V288" s="3"/>
       <c r="W288" s="3"/>
       <c r="X288" s="3"/>
-      <c r="Y288" s="3"/>
-      <c r="Z288" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="289" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y288" s="4" t="str">
+        <f>IF(COUNTA(B288:X288)=0,"",AVERAGE(B288:X288))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="289" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A289" s="2"/>
       <c r="B289" s="3"/>
       <c r="C289" s="3"/>
@@ -15737,13 +15481,12 @@
       <c r="V289" s="3"/>
       <c r="W289" s="3"/>
       <c r="X289" s="3"/>
-      <c r="Y289" s="3"/>
-      <c r="Z289" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="290" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y289" s="4" t="str">
+        <f>IF(COUNTA(B289:X289)=0,"",AVERAGE(B289:X289))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="290" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A290" s="2"/>
       <c r="B290" s="3"/>
       <c r="C290" s="3"/>
@@ -15768,13 +15511,12 @@
       <c r="V290" s="3"/>
       <c r="W290" s="3"/>
       <c r="X290" s="3"/>
-      <c r="Y290" s="3"/>
-      <c r="Z290" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="291" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y290" s="4" t="str">
+        <f>IF(COUNTA(B290:X290)=0,"",AVERAGE(B290:X290))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="291" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A291" s="2"/>
       <c r="B291" s="3"/>
       <c r="C291" s="3"/>
@@ -15799,13 +15541,12 @@
       <c r="V291" s="3"/>
       <c r="W291" s="3"/>
       <c r="X291" s="3"/>
-      <c r="Y291" s="3"/>
-      <c r="Z291" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="292" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y291" s="4" t="str">
+        <f>IF(COUNTA(B291:X291)=0,"",AVERAGE(B291:X291))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="292" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A292" s="2"/>
       <c r="B292" s="3"/>
       <c r="C292" s="3"/>
@@ -15830,13 +15571,12 @@
       <c r="V292" s="3"/>
       <c r="W292" s="3"/>
       <c r="X292" s="3"/>
-      <c r="Y292" s="3"/>
-      <c r="Z292" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="293" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y292" s="4" t="str">
+        <f>IF(COUNTA(B292:X292)=0,"",AVERAGE(B292:X292))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="293" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A293" s="2"/>
       <c r="B293" s="3"/>
       <c r="C293" s="3"/>
@@ -15861,13 +15601,12 @@
       <c r="V293" s="3"/>
       <c r="W293" s="3"/>
       <c r="X293" s="3"/>
-      <c r="Y293" s="3"/>
-      <c r="Z293" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="294" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y293" s="4" t="str">
+        <f>IF(COUNTA(B293:X293)=0,"",AVERAGE(B293:X293))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="294" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A294" s="2"/>
       <c r="B294" s="3"/>
       <c r="C294" s="3"/>
@@ -15892,13 +15631,12 @@
       <c r="V294" s="3"/>
       <c r="W294" s="3"/>
       <c r="X294" s="3"/>
-      <c r="Y294" s="3"/>
-      <c r="Z294" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="295" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y294" s="4" t="str">
+        <f>IF(COUNTA(B294:X294)=0,"",AVERAGE(B294:X294))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="295" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A295" s="2"/>
       <c r="B295" s="3"/>
       <c r="C295" s="3"/>
@@ -15923,13 +15661,12 @@
       <c r="V295" s="3"/>
       <c r="W295" s="3"/>
       <c r="X295" s="3"/>
-      <c r="Y295" s="3"/>
-      <c r="Z295" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="296" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y295" s="4" t="str">
+        <f>IF(COUNTA(B295:X295)=0,"",AVERAGE(B295:X295))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="296" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A296" s="2"/>
       <c r="B296" s="3"/>
       <c r="C296" s="3"/>
@@ -15954,13 +15691,12 @@
       <c r="V296" s="3"/>
       <c r="W296" s="3"/>
       <c r="X296" s="3"/>
-      <c r="Y296" s="3"/>
-      <c r="Z296" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="297" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y296" s="4" t="str">
+        <f>IF(COUNTA(B296:X296)=0,"",AVERAGE(B296:X296))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="297" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A297" s="2"/>
       <c r="B297" s="3"/>
       <c r="C297" s="3"/>
@@ -15985,13 +15721,12 @@
       <c r="V297" s="3"/>
       <c r="W297" s="3"/>
       <c r="X297" s="3"/>
-      <c r="Y297" s="3"/>
-      <c r="Z297" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="298" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y297" s="4" t="str">
+        <f>IF(COUNTA(B297:X297)=0,"",AVERAGE(B297:X297))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="298" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A298" s="2"/>
       <c r="B298" s="3"/>
       <c r="C298" s="3"/>
@@ -16016,13 +15751,12 @@
       <c r="V298" s="3"/>
       <c r="W298" s="3"/>
       <c r="X298" s="3"/>
-      <c r="Y298" s="3"/>
-      <c r="Z298" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="299" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y298" s="4" t="str">
+        <f>IF(COUNTA(B298:X298)=0,"",AVERAGE(B298:X298))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="299" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A299" s="2"/>
       <c r="B299" s="3"/>
       <c r="C299" s="3"/>
@@ -16047,13 +15781,12 @@
       <c r="V299" s="3"/>
       <c r="W299" s="3"/>
       <c r="X299" s="3"/>
-      <c r="Y299" s="3"/>
-      <c r="Z299" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="300" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y299" s="4" t="str">
+        <f>IF(COUNTA(B299:X299)=0,"",AVERAGE(B299:X299))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="300" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A300" s="2"/>
       <c r="B300" s="3"/>
       <c r="C300" s="3"/>
@@ -16078,13 +15811,12 @@
       <c r="V300" s="3"/>
       <c r="W300" s="3"/>
       <c r="X300" s="3"/>
-      <c r="Y300" s="3"/>
-      <c r="Z300" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="301" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y300" s="4" t="str">
+        <f>IF(COUNTA(B300:X300)=0,"",AVERAGE(B300:X300))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="301" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A301" s="2"/>
       <c r="B301" s="3"/>
       <c r="C301" s="3"/>
@@ -16109,13 +15841,12 @@
       <c r="V301" s="3"/>
       <c r="W301" s="3"/>
       <c r="X301" s="3"/>
-      <c r="Y301" s="3"/>
-      <c r="Z301" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="302" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y301" s="4" t="str">
+        <f>IF(COUNTA(B301:X301)=0,"",AVERAGE(B301:X301))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="302" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A302" s="2"/>
       <c r="B302" s="3"/>
       <c r="C302" s="3"/>
@@ -16140,13 +15871,12 @@
       <c r="V302" s="3"/>
       <c r="W302" s="3"/>
       <c r="X302" s="3"/>
-      <c r="Y302" s="3"/>
-      <c r="Z302" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="303" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y302" s="4" t="str">
+        <f>IF(COUNTA(B302:X302)=0,"",AVERAGE(B302:X302))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="303" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A303" s="2"/>
       <c r="B303" s="3"/>
       <c r="C303" s="3"/>
@@ -16171,13 +15901,12 @@
       <c r="V303" s="3"/>
       <c r="W303" s="3"/>
       <c r="X303" s="3"/>
-      <c r="Y303" s="3"/>
-      <c r="Z303" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="304" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y303" s="4" t="str">
+        <f>IF(COUNTA(B303:X303)=0,"",AVERAGE(B303:X303))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="304" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A304" s="2"/>
       <c r="B304" s="3"/>
       <c r="C304" s="3"/>
@@ -16202,13 +15931,12 @@
       <c r="V304" s="3"/>
       <c r="W304" s="3"/>
       <c r="X304" s="3"/>
-      <c r="Y304" s="3"/>
-      <c r="Z304" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="305" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y304" s="4" t="str">
+        <f>IF(COUNTA(B304:X304)=0,"",AVERAGE(B304:X304))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="305" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A305" s="2"/>
       <c r="B305" s="3"/>
       <c r="C305" s="3"/>
@@ -16233,13 +15961,12 @@
       <c r="V305" s="3"/>
       <c r="W305" s="3"/>
       <c r="X305" s="3"/>
-      <c r="Y305" s="3"/>
-      <c r="Z305" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="306" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y305" s="4" t="str">
+        <f>IF(COUNTA(B305:X305)=0,"",AVERAGE(B305:X305))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="306" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A306" s="2"/>
       <c r="B306" s="3"/>
       <c r="C306" s="3"/>
@@ -16264,13 +15991,12 @@
       <c r="V306" s="3"/>
       <c r="W306" s="3"/>
       <c r="X306" s="3"/>
-      <c r="Y306" s="3"/>
-      <c r="Z306" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="307" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y306" s="4" t="str">
+        <f>IF(COUNTA(B306:X306)=0,"",AVERAGE(B306:X306))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="307" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A307" s="2"/>
       <c r="B307" s="3"/>
       <c r="C307" s="3"/>
@@ -16295,13 +16021,12 @@
       <c r="V307" s="3"/>
       <c r="W307" s="3"/>
       <c r="X307" s="3"/>
-      <c r="Y307" s="3"/>
-      <c r="Z307" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="308" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y307" s="4" t="str">
+        <f>IF(COUNTA(B307:X307)=0,"",AVERAGE(B307:X307))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="308" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A308" s="2"/>
       <c r="B308" s="3"/>
       <c r="C308" s="3"/>
@@ -16326,13 +16051,12 @@
       <c r="V308" s="3"/>
       <c r="W308" s="3"/>
       <c r="X308" s="3"/>
-      <c r="Y308" s="3"/>
-      <c r="Z308" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="309" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y308" s="4" t="str">
+        <f>IF(COUNTA(B308:X308)=0,"",AVERAGE(B308:X308))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="309" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A309" s="2"/>
       <c r="B309" s="3"/>
       <c r="C309" s="3"/>
@@ -16357,13 +16081,12 @@
       <c r="V309" s="3"/>
       <c r="W309" s="3"/>
       <c r="X309" s="3"/>
-      <c r="Y309" s="3"/>
-      <c r="Z309" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="310" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y309" s="4" t="str">
+        <f>IF(COUNTA(B309:X309)=0,"",AVERAGE(B309:X309))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="310" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A310" s="2"/>
       <c r="B310" s="3"/>
       <c r="C310" s="3"/>
@@ -16388,13 +16111,12 @@
       <c r="V310" s="3"/>
       <c r="W310" s="3"/>
       <c r="X310" s="3"/>
-      <c r="Y310" s="3"/>
-      <c r="Z310" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="311" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y310" s="4" t="str">
+        <f>IF(COUNTA(B310:X310)=0,"",AVERAGE(B310:X310))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="311" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A311" s="2"/>
       <c r="B311" s="3"/>
       <c r="C311" s="3"/>
@@ -16419,13 +16141,12 @@
       <c r="V311" s="3"/>
       <c r="W311" s="3"/>
       <c r="X311" s="3"/>
-      <c r="Y311" s="3"/>
-      <c r="Z311" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="312" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y311" s="4" t="str">
+        <f>IF(COUNTA(B311:X311)=0,"",AVERAGE(B311:X311))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="312" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A312" s="2"/>
       <c r="B312" s="3"/>
       <c r="C312" s="3"/>
@@ -16450,13 +16171,12 @@
       <c r="V312" s="3"/>
       <c r="W312" s="3"/>
       <c r="X312" s="3"/>
-      <c r="Y312" s="3"/>
-      <c r="Z312" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="313" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y312" s="4" t="str">
+        <f>IF(COUNTA(B312:X312)=0,"",AVERAGE(B312:X312))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="313" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A313" s="2"/>
       <c r="B313" s="3"/>
       <c r="C313" s="3"/>
@@ -16481,13 +16201,12 @@
       <c r="V313" s="3"/>
       <c r="W313" s="3"/>
       <c r="X313" s="3"/>
-      <c r="Y313" s="3"/>
-      <c r="Z313" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="314" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y313" s="4" t="str">
+        <f>IF(COUNTA(B313:X313)=0,"",AVERAGE(B313:X313))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="314" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A314" s="2"/>
       <c r="B314" s="3"/>
       <c r="C314" s="3"/>
@@ -16512,13 +16231,12 @@
       <c r="V314" s="3"/>
       <c r="W314" s="3"/>
       <c r="X314" s="3"/>
-      <c r="Y314" s="3"/>
-      <c r="Z314" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="315" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y314" s="4" t="str">
+        <f>IF(COUNTA(B314:X314)=0,"",AVERAGE(B314:X314))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="315" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A315" s="2"/>
       <c r="B315" s="3"/>
       <c r="C315" s="3"/>
@@ -16543,13 +16261,12 @@
       <c r="V315" s="3"/>
       <c r="W315" s="3"/>
       <c r="X315" s="3"/>
-      <c r="Y315" s="3"/>
-      <c r="Z315" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="316" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y315" s="4" t="str">
+        <f>IF(COUNTA(B315:X315)=0,"",AVERAGE(B315:X315))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="316" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A316" s="2"/>
       <c r="B316" s="3"/>
       <c r="C316" s="3"/>
@@ -16574,13 +16291,12 @@
       <c r="V316" s="3"/>
       <c r="W316" s="3"/>
       <c r="X316" s="3"/>
-      <c r="Y316" s="3"/>
-      <c r="Z316" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="317" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y316" s="4" t="str">
+        <f>IF(COUNTA(B316:X316)=0,"",AVERAGE(B316:X316))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="317" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A317" s="2"/>
       <c r="B317" s="3"/>
       <c r="C317" s="3"/>
@@ -16605,13 +16321,12 @@
       <c r="V317" s="3"/>
       <c r="W317" s="3"/>
       <c r="X317" s="3"/>
-      <c r="Y317" s="3"/>
-      <c r="Z317" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="318" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y317" s="4" t="str">
+        <f>IF(COUNTA(B317:X317)=0,"",AVERAGE(B317:X317))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="318" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A318" s="2"/>
       <c r="B318" s="3"/>
       <c r="C318" s="3"/>
@@ -16636,13 +16351,12 @@
       <c r="V318" s="3"/>
       <c r="W318" s="3"/>
       <c r="X318" s="3"/>
-      <c r="Y318" s="3"/>
-      <c r="Z318" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="319" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y318" s="4" t="str">
+        <f>IF(COUNTA(B318:X318)=0,"",AVERAGE(B318:X318))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="319" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A319" s="2"/>
       <c r="B319" s="3"/>
       <c r="C319" s="3"/>
@@ -16667,13 +16381,12 @@
       <c r="V319" s="3"/>
       <c r="W319" s="3"/>
       <c r="X319" s="3"/>
-      <c r="Y319" s="3"/>
-      <c r="Z319" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="320" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y319" s="4" t="str">
+        <f>IF(COUNTA(B319:X319)=0,"",AVERAGE(B319:X319))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="320" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A320" s="2"/>
       <c r="B320" s="3"/>
       <c r="C320" s="3"/>
@@ -16698,13 +16411,12 @@
       <c r="V320" s="3"/>
       <c r="W320" s="3"/>
       <c r="X320" s="3"/>
-      <c r="Y320" s="3"/>
-      <c r="Z320" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="321" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y320" s="4" t="str">
+        <f>IF(COUNTA(B320:X320)=0,"",AVERAGE(B320:X320))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="321" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A321" s="2"/>
       <c r="B321" s="3"/>
       <c r="C321" s="3"/>
@@ -16729,13 +16441,12 @@
       <c r="V321" s="3"/>
       <c r="W321" s="3"/>
       <c r="X321" s="3"/>
-      <c r="Y321" s="3"/>
-      <c r="Z321" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="322" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y321" s="4" t="str">
+        <f>IF(COUNTA(B321:X321)=0,"",AVERAGE(B321:X321))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="322" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A322" s="2"/>
       <c r="B322" s="3"/>
       <c r="C322" s="3"/>
@@ -16760,13 +16471,12 @@
       <c r="V322" s="3"/>
       <c r="W322" s="3"/>
       <c r="X322" s="3"/>
-      <c r="Y322" s="3"/>
-      <c r="Z322" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="323" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y322" s="4" t="str">
+        <f>IF(COUNTA(B322:X322)=0,"",AVERAGE(B322:X322))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="323" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A323" s="2"/>
       <c r="B323" s="3"/>
       <c r="C323" s="3"/>
@@ -16791,13 +16501,12 @@
       <c r="V323" s="3"/>
       <c r="W323" s="3"/>
       <c r="X323" s="3"/>
-      <c r="Y323" s="3"/>
-      <c r="Z323" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="324" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y323" s="4" t="str">
+        <f>IF(COUNTA(B323:X323)=0,"",AVERAGE(B323:X323))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="324" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A324" s="2"/>
       <c r="B324" s="3"/>
       <c r="C324" s="3"/>
@@ -16822,13 +16531,12 @@
       <c r="V324" s="3"/>
       <c r="W324" s="3"/>
       <c r="X324" s="3"/>
-      <c r="Y324" s="3"/>
-      <c r="Z324" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="325" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y324" s="4" t="str">
+        <f>IF(COUNTA(B324:X324)=0,"",AVERAGE(B324:X324))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="325" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A325" s="2"/>
       <c r="B325" s="3"/>
       <c r="C325" s="3"/>
@@ -16853,13 +16561,12 @@
       <c r="V325" s="3"/>
       <c r="W325" s="3"/>
       <c r="X325" s="3"/>
-      <c r="Y325" s="3"/>
-      <c r="Z325" s="4" t="str">
-        <f t="shared" ref="Z325:Z388" si="6">IF(COUNTA(B325:Y325)=0,"",AVERAGE(B325:Y325))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="326" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y325" s="4" t="str">
+        <f>IF(COUNTA(B325:X325)=0,"",AVERAGE(B325:X325))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="326" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A326" s="2"/>
       <c r="B326" s="3"/>
       <c r="C326" s="3"/>
@@ -16884,13 +16591,12 @@
       <c r="V326" s="3"/>
       <c r="W326" s="3"/>
       <c r="X326" s="3"/>
-      <c r="Y326" s="3"/>
-      <c r="Z326" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="327" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y326" s="4" t="str">
+        <f>IF(COUNTA(B326:X326)=0,"",AVERAGE(B326:X326))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="327" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A327" s="2"/>
       <c r="B327" s="3"/>
       <c r="C327" s="3"/>
@@ -16915,13 +16621,12 @@
       <c r="V327" s="3"/>
       <c r="W327" s="3"/>
       <c r="X327" s="3"/>
-      <c r="Y327" s="3"/>
-      <c r="Z327" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="328" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y327" s="4" t="str">
+        <f>IF(COUNTA(B327:X327)=0,"",AVERAGE(B327:X327))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="328" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A328" s="2"/>
       <c r="B328" s="3"/>
       <c r="C328" s="3"/>
@@ -16946,13 +16651,12 @@
       <c r="V328" s="3"/>
       <c r="W328" s="3"/>
       <c r="X328" s="3"/>
-      <c r="Y328" s="3"/>
-      <c r="Z328" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="329" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y328" s="4" t="str">
+        <f>IF(COUNTA(B328:X328)=0,"",AVERAGE(B328:X328))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="329" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A329" s="2"/>
       <c r="B329" s="3"/>
       <c r="C329" s="3"/>
@@ -16977,13 +16681,12 @@
       <c r="V329" s="3"/>
       <c r="W329" s="3"/>
       <c r="X329" s="3"/>
-      <c r="Y329" s="3"/>
-      <c r="Z329" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="330" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y329" s="4" t="str">
+        <f>IF(COUNTA(B329:X329)=0,"",AVERAGE(B329:X329))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="330" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A330" s="2"/>
       <c r="B330" s="3"/>
       <c r="C330" s="3"/>
@@ -17008,13 +16711,12 @@
       <c r="V330" s="3"/>
       <c r="W330" s="3"/>
       <c r="X330" s="3"/>
-      <c r="Y330" s="3"/>
-      <c r="Z330" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="331" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y330" s="4" t="str">
+        <f>IF(COUNTA(B330:X330)=0,"",AVERAGE(B330:X330))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="331" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A331" s="2"/>
       <c r="B331" s="3"/>
       <c r="C331" s="3"/>
@@ -17039,13 +16741,12 @@
       <c r="V331" s="3"/>
       <c r="W331" s="3"/>
       <c r="X331" s="3"/>
-      <c r="Y331" s="3"/>
-      <c r="Z331" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="332" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y331" s="4" t="str">
+        <f>IF(COUNTA(B331:X331)=0,"",AVERAGE(B331:X331))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="332" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A332" s="2"/>
       <c r="B332" s="3"/>
       <c r="C332" s="3"/>
@@ -17070,13 +16771,12 @@
       <c r="V332" s="3"/>
       <c r="W332" s="3"/>
       <c r="X332" s="3"/>
-      <c r="Y332" s="3"/>
-      <c r="Z332" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="333" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y332" s="4" t="str">
+        <f>IF(COUNTA(B332:X332)=0,"",AVERAGE(B332:X332))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="333" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A333" s="2"/>
       <c r="B333" s="3"/>
       <c r="C333" s="3"/>
@@ -17101,13 +16801,12 @@
       <c r="V333" s="3"/>
       <c r="W333" s="3"/>
       <c r="X333" s="3"/>
-      <c r="Y333" s="3"/>
-      <c r="Z333" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="334" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y333" s="4" t="str">
+        <f>IF(COUNTA(B333:X333)=0,"",AVERAGE(B333:X333))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="334" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A334" s="2"/>
       <c r="B334" s="3"/>
       <c r="C334" s="3"/>
@@ -17132,13 +16831,12 @@
       <c r="V334" s="3"/>
       <c r="W334" s="3"/>
       <c r="X334" s="3"/>
-      <c r="Y334" s="3"/>
-      <c r="Z334" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="335" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y334" s="4" t="str">
+        <f>IF(COUNTA(B334:X334)=0,"",AVERAGE(B334:X334))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="335" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A335" s="2"/>
       <c r="B335" s="3"/>
       <c r="C335" s="3"/>
@@ -17163,13 +16861,12 @@
       <c r="V335" s="3"/>
       <c r="W335" s="3"/>
       <c r="X335" s="3"/>
-      <c r="Y335" s="3"/>
-      <c r="Z335" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="336" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y335" s="4" t="str">
+        <f>IF(COUNTA(B335:X335)=0,"",AVERAGE(B335:X335))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="336" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A336" s="2"/>
       <c r="B336" s="3"/>
       <c r="C336" s="3"/>
@@ -17194,13 +16891,12 @@
       <c r="V336" s="3"/>
       <c r="W336" s="3"/>
       <c r="X336" s="3"/>
-      <c r="Y336" s="3"/>
-      <c r="Z336" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="337" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y336" s="4" t="str">
+        <f>IF(COUNTA(B336:X336)=0,"",AVERAGE(B336:X336))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="337" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A337" s="2"/>
       <c r="B337" s="3"/>
       <c r="C337" s="3"/>
@@ -17225,13 +16921,12 @@
       <c r="V337" s="3"/>
       <c r="W337" s="3"/>
       <c r="X337" s="3"/>
-      <c r="Y337" s="3"/>
-      <c r="Z337" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="338" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y337" s="4" t="str">
+        <f>IF(COUNTA(B337:X337)=0,"",AVERAGE(B337:X337))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="338" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A338" s="2"/>
       <c r="B338" s="3"/>
       <c r="C338" s="3"/>
@@ -17256,13 +16951,12 @@
       <c r="V338" s="3"/>
       <c r="W338" s="3"/>
       <c r="X338" s="3"/>
-      <c r="Y338" s="3"/>
-      <c r="Z338" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="339" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y338" s="4" t="str">
+        <f>IF(COUNTA(B338:X338)=0,"",AVERAGE(B338:X338))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="339" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A339" s="2"/>
       <c r="B339" s="3"/>
       <c r="C339" s="3"/>
@@ -17287,13 +16981,12 @@
       <c r="V339" s="3"/>
       <c r="W339" s="3"/>
       <c r="X339" s="3"/>
-      <c r="Y339" s="3"/>
-      <c r="Z339" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="340" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y339" s="4" t="str">
+        <f>IF(COUNTA(B339:X339)=0,"",AVERAGE(B339:X339))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="340" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A340" s="2"/>
       <c r="B340" s="3"/>
       <c r="C340" s="3"/>
@@ -17318,13 +17011,12 @@
       <c r="V340" s="3"/>
       <c r="W340" s="3"/>
       <c r="X340" s="3"/>
-      <c r="Y340" s="3"/>
-      <c r="Z340" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="341" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y340" s="4" t="str">
+        <f>IF(COUNTA(B340:X340)=0,"",AVERAGE(B340:X340))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="341" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A341" s="2"/>
       <c r="B341" s="3"/>
       <c r="C341" s="3"/>
@@ -17349,13 +17041,12 @@
       <c r="V341" s="3"/>
       <c r="W341" s="3"/>
       <c r="X341" s="3"/>
-      <c r="Y341" s="3"/>
-      <c r="Z341" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="342" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y341" s="4" t="str">
+        <f>IF(COUNTA(B341:X341)=0,"",AVERAGE(B341:X341))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="342" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A342" s="2"/>
       <c r="B342" s="3"/>
       <c r="C342" s="3"/>
@@ -17380,13 +17071,12 @@
       <c r="V342" s="3"/>
       <c r="W342" s="3"/>
       <c r="X342" s="3"/>
-      <c r="Y342" s="3"/>
-      <c r="Z342" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="343" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y342" s="4" t="str">
+        <f>IF(COUNTA(B342:X342)=0,"",AVERAGE(B342:X342))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="343" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A343" s="2"/>
       <c r="B343" s="3"/>
       <c r="C343" s="3"/>
@@ -17411,13 +17101,12 @@
       <c r="V343" s="3"/>
       <c r="W343" s="3"/>
       <c r="X343" s="3"/>
-      <c r="Y343" s="3"/>
-      <c r="Z343" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="344" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y343" s="4" t="str">
+        <f>IF(COUNTA(B343:X343)=0,"",AVERAGE(B343:X343))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="344" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A344" s="2"/>
       <c r="B344" s="3"/>
       <c r="C344" s="3"/>
@@ -17442,13 +17131,12 @@
       <c r="V344" s="3"/>
       <c r="W344" s="3"/>
       <c r="X344" s="3"/>
-      <c r="Y344" s="3"/>
-      <c r="Z344" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="345" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y344" s="4" t="str">
+        <f>IF(COUNTA(B344:X344)=0,"",AVERAGE(B344:X344))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="345" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A345" s="2"/>
       <c r="B345" s="3"/>
       <c r="C345" s="3"/>
@@ -17473,13 +17161,12 @@
       <c r="V345" s="3"/>
       <c r="W345" s="3"/>
       <c r="X345" s="3"/>
-      <c r="Y345" s="3"/>
-      <c r="Z345" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="346" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y345" s="4" t="str">
+        <f>IF(COUNTA(B345:X345)=0,"",AVERAGE(B345:X345))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="346" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A346" s="2"/>
       <c r="B346" s="3"/>
       <c r="C346" s="3"/>
@@ -17504,13 +17191,12 @@
       <c r="V346" s="3"/>
       <c r="W346" s="3"/>
       <c r="X346" s="3"/>
-      <c r="Y346" s="3"/>
-      <c r="Z346" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="347" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y346" s="4" t="str">
+        <f>IF(COUNTA(B346:X346)=0,"",AVERAGE(B346:X346))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="347" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A347" s="2"/>
       <c r="B347" s="3"/>
       <c r="C347" s="3"/>
@@ -17535,13 +17221,12 @@
       <c r="V347" s="3"/>
       <c r="W347" s="3"/>
       <c r="X347" s="3"/>
-      <c r="Y347" s="3"/>
-      <c r="Z347" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="348" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y347" s="4" t="str">
+        <f>IF(COUNTA(B347:X347)=0,"",AVERAGE(B347:X347))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="348" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A348" s="2"/>
       <c r="B348" s="3"/>
       <c r="C348" s="3"/>
@@ -17566,13 +17251,12 @@
       <c r="V348" s="3"/>
       <c r="W348" s="3"/>
       <c r="X348" s="3"/>
-      <c r="Y348" s="3"/>
-      <c r="Z348" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="349" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y348" s="4" t="str">
+        <f>IF(COUNTA(B348:X348)=0,"",AVERAGE(B348:X348))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="349" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A349" s="2"/>
       <c r="B349" s="3"/>
       <c r="C349" s="3"/>
@@ -17597,13 +17281,12 @@
       <c r="V349" s="3"/>
       <c r="W349" s="3"/>
       <c r="X349" s="3"/>
-      <c r="Y349" s="3"/>
-      <c r="Z349" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="350" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y349" s="4" t="str">
+        <f>IF(COUNTA(B349:X349)=0,"",AVERAGE(B349:X349))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="350" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A350" s="2"/>
       <c r="B350" s="3"/>
       <c r="C350" s="3"/>
@@ -17628,13 +17311,12 @@
       <c r="V350" s="3"/>
       <c r="W350" s="3"/>
       <c r="X350" s="3"/>
-      <c r="Y350" s="3"/>
-      <c r="Z350" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="351" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y350" s="4" t="str">
+        <f>IF(COUNTA(B350:X350)=0,"",AVERAGE(B350:X350))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="351" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A351" s="2"/>
       <c r="B351" s="3"/>
       <c r="C351" s="3"/>
@@ -17659,13 +17341,12 @@
       <c r="V351" s="3"/>
       <c r="W351" s="3"/>
       <c r="X351" s="3"/>
-      <c r="Y351" s="3"/>
-      <c r="Z351" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="352" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y351" s="4" t="str">
+        <f>IF(COUNTA(B351:X351)=0,"",AVERAGE(B351:X351))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="352" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A352" s="2"/>
       <c r="B352" s="3"/>
       <c r="C352" s="3"/>
@@ -17690,13 +17371,12 @@
       <c r="V352" s="3"/>
       <c r="W352" s="3"/>
       <c r="X352" s="3"/>
-      <c r="Y352" s="3"/>
-      <c r="Z352" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="353" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y352" s="4" t="str">
+        <f>IF(COUNTA(B352:X352)=0,"",AVERAGE(B352:X352))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="353" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A353" s="2"/>
       <c r="B353" s="3"/>
       <c r="C353" s="3"/>
@@ -17721,13 +17401,12 @@
       <c r="V353" s="3"/>
       <c r="W353" s="3"/>
       <c r="X353" s="3"/>
-      <c r="Y353" s="3"/>
-      <c r="Z353" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="354" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y353" s="4" t="str">
+        <f>IF(COUNTA(B353:X353)=0,"",AVERAGE(B353:X353))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="354" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A354" s="2"/>
       <c r="B354" s="3"/>
       <c r="C354" s="3"/>
@@ -17752,13 +17431,12 @@
       <c r="V354" s="3"/>
       <c r="W354" s="3"/>
       <c r="X354" s="3"/>
-      <c r="Y354" s="3"/>
-      <c r="Z354" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="355" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y354" s="4" t="str">
+        <f>IF(COUNTA(B354:X354)=0,"",AVERAGE(B354:X354))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="355" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A355" s="2"/>
       <c r="B355" s="3"/>
       <c r="C355" s="3"/>
@@ -17783,13 +17461,12 @@
       <c r="V355" s="3"/>
       <c r="W355" s="3"/>
       <c r="X355" s="3"/>
-      <c r="Y355" s="3"/>
-      <c r="Z355" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="356" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y355" s="4" t="str">
+        <f>IF(COUNTA(B355:X355)=0,"",AVERAGE(B355:X355))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="356" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A356" s="2"/>
       <c r="B356" s="3"/>
       <c r="C356" s="3"/>
@@ -17814,13 +17491,12 @@
       <c r="V356" s="3"/>
       <c r="W356" s="3"/>
       <c r="X356" s="3"/>
-      <c r="Y356" s="3"/>
-      <c r="Z356" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="357" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y356" s="4" t="str">
+        <f>IF(COUNTA(B356:X356)=0,"",AVERAGE(B356:X356))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="357" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A357" s="2"/>
       <c r="B357" s="3"/>
       <c r="C357" s="3"/>
@@ -17845,13 +17521,12 @@
       <c r="V357" s="3"/>
       <c r="W357" s="3"/>
       <c r="X357" s="3"/>
-      <c r="Y357" s="3"/>
-      <c r="Z357" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="358" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y357" s="4" t="str">
+        <f>IF(COUNTA(B357:X357)=0,"",AVERAGE(B357:X357))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="358" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A358" s="2"/>
       <c r="B358" s="3"/>
       <c r="C358" s="3"/>
@@ -17876,13 +17551,12 @@
       <c r="V358" s="3"/>
       <c r="W358" s="3"/>
       <c r="X358" s="3"/>
-      <c r="Y358" s="3"/>
-      <c r="Z358" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="359" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y358" s="4" t="str">
+        <f>IF(COUNTA(B358:X358)=0,"",AVERAGE(B358:X358))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="359" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A359" s="2"/>
       <c r="B359" s="3"/>
       <c r="C359" s="3"/>
@@ -17907,13 +17581,12 @@
       <c r="V359" s="3"/>
       <c r="W359" s="3"/>
       <c r="X359" s="3"/>
-      <c r="Y359" s="3"/>
-      <c r="Z359" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="360" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y359" s="4" t="str">
+        <f>IF(COUNTA(B359:X359)=0,"",AVERAGE(B359:X359))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="360" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A360" s="2"/>
       <c r="B360" s="3"/>
       <c r="C360" s="3"/>
@@ -17938,13 +17611,12 @@
       <c r="V360" s="3"/>
       <c r="W360" s="3"/>
       <c r="X360" s="3"/>
-      <c r="Y360" s="3"/>
-      <c r="Z360" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="361" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y360" s="4" t="str">
+        <f>IF(COUNTA(B360:X360)=0,"",AVERAGE(B360:X360))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="361" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A361" s="2"/>
       <c r="B361" s="3"/>
       <c r="C361" s="3"/>
@@ -17969,13 +17641,12 @@
       <c r="V361" s="3"/>
       <c r="W361" s="3"/>
       <c r="X361" s="3"/>
-      <c r="Y361" s="3"/>
-      <c r="Z361" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="362" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y361" s="4" t="str">
+        <f>IF(COUNTA(B361:X361)=0,"",AVERAGE(B361:X361))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="362" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A362" s="2"/>
       <c r="B362" s="3"/>
       <c r="C362" s="3"/>
@@ -18000,13 +17671,12 @@
       <c r="V362" s="3"/>
       <c r="W362" s="3"/>
       <c r="X362" s="3"/>
-      <c r="Y362" s="3"/>
-      <c r="Z362" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="363" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y362" s="4" t="str">
+        <f>IF(COUNTA(B362:X362)=0,"",AVERAGE(B362:X362))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="363" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A363" s="2"/>
       <c r="B363" s="3"/>
       <c r="C363" s="3"/>
@@ -18031,13 +17701,12 @@
       <c r="V363" s="3"/>
       <c r="W363" s="3"/>
       <c r="X363" s="3"/>
-      <c r="Y363" s="3"/>
-      <c r="Z363" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="364" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y363" s="4" t="str">
+        <f>IF(COUNTA(B363:X363)=0,"",AVERAGE(B363:X363))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="364" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A364" s="2"/>
       <c r="B364" s="3"/>
       <c r="C364" s="3"/>
@@ -18062,13 +17731,12 @@
       <c r="V364" s="3"/>
       <c r="W364" s="3"/>
       <c r="X364" s="3"/>
-      <c r="Y364" s="3"/>
-      <c r="Z364" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="365" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y364" s="4" t="str">
+        <f>IF(COUNTA(B364:X364)=0,"",AVERAGE(B364:X364))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="365" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A365" s="2"/>
       <c r="B365" s="3"/>
       <c r="C365" s="3"/>
@@ -18093,13 +17761,12 @@
       <c r="V365" s="3"/>
       <c r="W365" s="3"/>
       <c r="X365" s="3"/>
-      <c r="Y365" s="3"/>
-      <c r="Z365" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="366" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y365" s="4" t="str">
+        <f>IF(COUNTA(B365:X365)=0,"",AVERAGE(B365:X365))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="366" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A366" s="2"/>
       <c r="B366" s="3"/>
       <c r="C366" s="3"/>
@@ -18124,13 +17791,12 @@
       <c r="V366" s="3"/>
       <c r="W366" s="3"/>
       <c r="X366" s="3"/>
-      <c r="Y366" s="3"/>
-      <c r="Z366" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="367" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y366" s="4" t="str">
+        <f>IF(COUNTA(B366:X366)=0,"",AVERAGE(B366:X366))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="367" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A367" s="2"/>
       <c r="B367" s="3"/>
       <c r="C367" s="3"/>
@@ -18155,13 +17821,12 @@
       <c r="V367" s="3"/>
       <c r="W367" s="3"/>
       <c r="X367" s="3"/>
-      <c r="Y367" s="3"/>
-      <c r="Z367" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="368" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y367" s="4" t="str">
+        <f>IF(COUNTA(B367:X367)=0,"",AVERAGE(B367:X367))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="368" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A368" s="2"/>
       <c r="B368" s="3"/>
       <c r="C368" s="3"/>
@@ -18186,13 +17851,12 @@
       <c r="V368" s="3"/>
       <c r="W368" s="3"/>
       <c r="X368" s="3"/>
-      <c r="Y368" s="3"/>
-      <c r="Z368" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="369" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y368" s="4" t="str">
+        <f>IF(COUNTA(B368:X368)=0,"",AVERAGE(B368:X368))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="369" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A369" s="2"/>
       <c r="B369" s="3"/>
       <c r="C369" s="3"/>
@@ -18217,13 +17881,12 @@
       <c r="V369" s="3"/>
       <c r="W369" s="3"/>
       <c r="X369" s="3"/>
-      <c r="Y369" s="3"/>
-      <c r="Z369" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="370" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y369" s="4" t="str">
+        <f>IF(COUNTA(B369:X369)=0,"",AVERAGE(B369:X369))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="370" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A370" s="2"/>
       <c r="B370" s="3"/>
       <c r="C370" s="3"/>
@@ -18248,13 +17911,12 @@
       <c r="V370" s="3"/>
       <c r="W370" s="3"/>
       <c r="X370" s="3"/>
-      <c r="Y370" s="3"/>
-      <c r="Z370" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="371" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y370" s="4" t="str">
+        <f>IF(COUNTA(B370:X370)=0,"",AVERAGE(B370:X370))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="371" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A371" s="2"/>
       <c r="B371" s="3"/>
       <c r="C371" s="3"/>
@@ -18279,13 +17941,12 @@
       <c r="V371" s="3"/>
       <c r="W371" s="3"/>
       <c r="X371" s="3"/>
-      <c r="Y371" s="3"/>
-      <c r="Z371" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="372" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y371" s="4" t="str">
+        <f>IF(COUNTA(B371:X371)=0,"",AVERAGE(B371:X371))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="372" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A372" s="2"/>
       <c r="B372" s="3"/>
       <c r="C372" s="3"/>
@@ -18310,13 +17971,12 @@
       <c r="V372" s="3"/>
       <c r="W372" s="3"/>
       <c r="X372" s="3"/>
-      <c r="Y372" s="3"/>
-      <c r="Z372" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="373" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y372" s="4" t="str">
+        <f>IF(COUNTA(B372:X372)=0,"",AVERAGE(B372:X372))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="373" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A373" s="2"/>
       <c r="B373" s="3"/>
       <c r="C373" s="3"/>
@@ -18341,13 +18001,12 @@
       <c r="V373" s="3"/>
       <c r="W373" s="3"/>
       <c r="X373" s="3"/>
-      <c r="Y373" s="3"/>
-      <c r="Z373" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="374" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y373" s="4" t="str">
+        <f>IF(COUNTA(B373:X373)=0,"",AVERAGE(B373:X373))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="374" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A374" s="2"/>
       <c r="B374" s="3"/>
       <c r="C374" s="3"/>
@@ -18372,13 +18031,12 @@
       <c r="V374" s="3"/>
       <c r="W374" s="3"/>
       <c r="X374" s="3"/>
-      <c r="Y374" s="3"/>
-      <c r="Z374" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="375" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y374" s="4" t="str">
+        <f>IF(COUNTA(B374:X374)=0,"",AVERAGE(B374:X374))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="375" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A375" s="2"/>
       <c r="B375" s="3"/>
       <c r="C375" s="3"/>
@@ -18403,13 +18061,12 @@
       <c r="V375" s="3"/>
       <c r="W375" s="3"/>
       <c r="X375" s="3"/>
-      <c r="Y375" s="3"/>
-      <c r="Z375" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="376" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y375" s="4" t="str">
+        <f>IF(COUNTA(B375:X375)=0,"",AVERAGE(B375:X375))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="376" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A376" s="2"/>
       <c r="B376" s="3"/>
       <c r="C376" s="3"/>
@@ -18434,13 +18091,12 @@
       <c r="V376" s="3"/>
       <c r="W376" s="3"/>
       <c r="X376" s="3"/>
-      <c r="Y376" s="3"/>
-      <c r="Z376" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="377" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y376" s="4" t="str">
+        <f>IF(COUNTA(B376:X376)=0,"",AVERAGE(B376:X376))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="377" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A377" s="2"/>
       <c r="B377" s="3"/>
       <c r="C377" s="3"/>
@@ -18465,13 +18121,12 @@
       <c r="V377" s="3"/>
       <c r="W377" s="3"/>
       <c r="X377" s="3"/>
-      <c r="Y377" s="3"/>
-      <c r="Z377" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="378" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y377" s="4" t="str">
+        <f>IF(COUNTA(B377:X377)=0,"",AVERAGE(B377:X377))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="378" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A378" s="2"/>
       <c r="B378" s="3"/>
       <c r="C378" s="3"/>
@@ -18496,13 +18151,12 @@
       <c r="V378" s="3"/>
       <c r="W378" s="3"/>
       <c r="X378" s="3"/>
-      <c r="Y378" s="3"/>
-      <c r="Z378" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="379" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y378" s="4" t="str">
+        <f>IF(COUNTA(B378:X378)=0,"",AVERAGE(B378:X378))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="379" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A379" s="2"/>
       <c r="B379" s="3"/>
       <c r="C379" s="3"/>
@@ -18527,13 +18181,12 @@
       <c r="V379" s="3"/>
       <c r="W379" s="3"/>
       <c r="X379" s="3"/>
-      <c r="Y379" s="3"/>
-      <c r="Z379" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="380" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y379" s="4" t="str">
+        <f>IF(COUNTA(B379:X379)=0,"",AVERAGE(B379:X379))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="380" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A380" s="2"/>
       <c r="B380" s="3"/>
       <c r="C380" s="3"/>
@@ -18558,13 +18211,12 @@
       <c r="V380" s="3"/>
       <c r="W380" s="3"/>
       <c r="X380" s="3"/>
-      <c r="Y380" s="3"/>
-      <c r="Z380" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="381" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y380" s="4" t="str">
+        <f>IF(COUNTA(B380:X380)=0,"",AVERAGE(B380:X380))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="381" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A381" s="2"/>
       <c r="B381" s="3"/>
       <c r="C381" s="3"/>
@@ -18589,13 +18241,12 @@
       <c r="V381" s="3"/>
       <c r="W381" s="3"/>
       <c r="X381" s="3"/>
-      <c r="Y381" s="3"/>
-      <c r="Z381" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="382" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y381" s="4" t="str">
+        <f>IF(COUNTA(B381:X381)=0,"",AVERAGE(B381:X381))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="382" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A382" s="2"/>
       <c r="B382" s="3"/>
       <c r="C382" s="3"/>
@@ -18620,13 +18271,12 @@
       <c r="V382" s="3"/>
       <c r="W382" s="3"/>
       <c r="X382" s="3"/>
-      <c r="Y382" s="3"/>
-      <c r="Z382" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="383" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y382" s="4" t="str">
+        <f>IF(COUNTA(B382:X382)=0,"",AVERAGE(B382:X382))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="383" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A383" s="2"/>
       <c r="B383" s="3"/>
       <c r="C383" s="3"/>
@@ -18651,13 +18301,12 @@
       <c r="V383" s="3"/>
       <c r="W383" s="3"/>
       <c r="X383" s="3"/>
-      <c r="Y383" s="3"/>
-      <c r="Z383" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="384" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y383" s="4" t="str">
+        <f>IF(COUNTA(B383:X383)=0,"",AVERAGE(B383:X383))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="384" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A384" s="2"/>
       <c r="B384" s="3"/>
       <c r="C384" s="3"/>
@@ -18682,13 +18331,12 @@
       <c r="V384" s="3"/>
       <c r="W384" s="3"/>
       <c r="X384" s="3"/>
-      <c r="Y384" s="3"/>
-      <c r="Z384" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="385" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y384" s="4" t="str">
+        <f>IF(COUNTA(B384:X384)=0,"",AVERAGE(B384:X384))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="385" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A385" s="2"/>
       <c r="B385" s="3"/>
       <c r="C385" s="3"/>
@@ -18713,13 +18361,12 @@
       <c r="V385" s="3"/>
       <c r="W385" s="3"/>
       <c r="X385" s="3"/>
-      <c r="Y385" s="3"/>
-      <c r="Z385" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="386" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y385" s="4" t="str">
+        <f>IF(COUNTA(B385:X385)=0,"",AVERAGE(B385:X385))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="386" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A386" s="2"/>
       <c r="B386" s="3"/>
       <c r="C386" s="3"/>
@@ -18744,13 +18391,12 @@
       <c r="V386" s="3"/>
       <c r="W386" s="3"/>
       <c r="X386" s="3"/>
-      <c r="Y386" s="3"/>
-      <c r="Z386" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="387" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y386" s="4" t="str">
+        <f>IF(COUNTA(B386:X386)=0,"",AVERAGE(B386:X386))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="387" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A387" s="2"/>
       <c r="B387" s="3"/>
       <c r="C387" s="3"/>
@@ -18775,13 +18421,12 @@
       <c r="V387" s="3"/>
       <c r="W387" s="3"/>
       <c r="X387" s="3"/>
-      <c r="Y387" s="3"/>
-      <c r="Z387" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="388" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y387" s="4" t="str">
+        <f>IF(COUNTA(B387:X387)=0,"",AVERAGE(B387:X387))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="388" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A388" s="2"/>
       <c r="B388" s="3"/>
       <c r="C388" s="3"/>
@@ -18806,13 +18451,12 @@
       <c r="V388" s="3"/>
       <c r="W388" s="3"/>
       <c r="X388" s="3"/>
-      <c r="Y388" s="3"/>
-      <c r="Z388" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="389" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y388" s="4" t="str">
+        <f>IF(COUNTA(B388:X388)=0,"",AVERAGE(B388:X388))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="389" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A389" s="2"/>
       <c r="B389" s="3"/>
       <c r="C389" s="3"/>
@@ -18837,13 +18481,12 @@
       <c r="V389" s="3"/>
       <c r="W389" s="3"/>
       <c r="X389" s="3"/>
-      <c r="Y389" s="3"/>
-      <c r="Z389" s="4" t="str">
-        <f t="shared" ref="Z389:Z390" si="7">IF(COUNTA(B389:Y389)=0,"",AVERAGE(B389:Y389))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="390" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y389" s="4" t="str">
+        <f>IF(COUNTA(B389:X389)=0,"",AVERAGE(B389:X389))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="390" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A390" s="2"/>
       <c r="B390" s="3"/>
       <c r="C390" s="3"/>
@@ -18868,21 +18511,20 @@
       <c r="V390" s="3"/>
       <c r="W390" s="3"/>
       <c r="X390" s="3"/>
-      <c r="Y390" s="3"/>
-      <c r="Z390" s="4" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="392" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y390" s="4" t="str">
+        <f>IF(COUNTA(B390:X390)=0,"",AVERAGE(B390:X390))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="392" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A392" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A1:Z1"/>
-    <mergeCell ref="A2:Z2"/>
+    <mergeCell ref="A1:Y1"/>
+    <mergeCell ref="A2:Y2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing r:id="rId1"/>
@@ -18901,7 +18543,7 @@
   <sheetData>
     <row r="1" spans="1:21" ht="24" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="8" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B1" s="7"/>
       <c r="C1" s="7"/>
@@ -18957,7 +18599,7 @@
         <v>3</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>4</v>
@@ -18969,7 +18611,7 @@
         <v>7</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H4" s="1" t="s">
         <v>15</v>
@@ -18981,7 +18623,7 @@
         <v>11</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="L4" s="1" t="s">
         <v>19</v>
@@ -18990,28 +18632,28 @@
         <v>12</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O4" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="P4" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="P4" s="1" t="s">
+      <c r="Q4" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="Q4" s="1" t="s">
+      <c r="R4" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="S4" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="R4" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="S4" s="1" t="s">
-        <v>36</v>
-      </c>
       <c r="T4" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="U4" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5" spans="1:21" x14ac:dyDescent="0.25">
@@ -19807,29 +19449,69 @@
       </c>
     </row>
     <row r="17" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A17" s="2"/>
-      <c r="B17" s="3"/>
-      <c r="C17" s="3"/>
-      <c r="D17" s="3"/>
-      <c r="E17" s="3"/>
-      <c r="F17" s="3"/>
-      <c r="G17" s="3"/>
-      <c r="H17" s="3"/>
-      <c r="I17" s="3"/>
-      <c r="J17" s="3"/>
-      <c r="K17" s="3"/>
-      <c r="L17" s="3"/>
-      <c r="M17" s="3"/>
-      <c r="N17" s="3"/>
-      <c r="O17" s="3"/>
-      <c r="P17" s="3"/>
-      <c r="Q17" s="3"/>
-      <c r="R17" s="3"/>
-      <c r="S17" s="3"/>
-      <c r="T17" s="3"/>
-      <c r="U17" s="4" t="str">
+      <c r="A17" s="2">
+        <v>46141</v>
+      </c>
+      <c r="B17" s="3">
+        <v>4.29</v>
+      </c>
+      <c r="C17" s="3">
+        <v>3.95</v>
+      </c>
+      <c r="D17" s="3">
+        <v>2.4900000000000002</v>
+      </c>
+      <c r="E17" s="3">
+        <v>3.8</v>
+      </c>
+      <c r="F17" s="3">
+        <v>4.3099999999999996</v>
+      </c>
+      <c r="G17" s="3">
+        <v>3.99</v>
+      </c>
+      <c r="H17" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="I17" s="3">
+        <v>3.39</v>
+      </c>
+      <c r="J17" s="3">
+        <v>3.09</v>
+      </c>
+      <c r="K17" s="3">
+        <v>3.99</v>
+      </c>
+      <c r="L17" s="3">
+        <v>2.39</v>
+      </c>
+      <c r="M17" s="3">
+        <v>3.79</v>
+      </c>
+      <c r="N17" s="3">
+        <v>3.79</v>
+      </c>
+      <c r="O17" s="3">
+        <v>3.8</v>
+      </c>
+      <c r="P17" s="3">
+        <v>3.89</v>
+      </c>
+      <c r="Q17" s="3">
+        <v>4.03</v>
+      </c>
+      <c r="R17" s="3">
+        <v>3.79</v>
+      </c>
+      <c r="S17" s="3">
+        <v>3.99</v>
+      </c>
+      <c r="T17" s="3">
+        <v>1.99</v>
+      </c>
+      <c r="U17" s="4">
         <f t="shared" si="0"/>
-        <v/>
+        <v>3.5657894736842097</v>
       </c>
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.25">
@@ -29532,7 +29214,7 @@
     </row>
     <row r="392" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A392" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -29557,7 +29239,7 @@
   <sheetData>
     <row r="1" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="8" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B1" s="7"/>
       <c r="C1" s="7"/>
@@ -29596,28 +29278,28 @@
         <v>10</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>15</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G4" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H4" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="I4" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="J4" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="I4" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>36</v>
-      </c>
       <c r="K4" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
@@ -30053,19 +29735,39 @@
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A17" s="2"/>
-      <c r="B17" s="3"/>
-      <c r="C17" s="3"/>
-      <c r="D17" s="3"/>
-      <c r="E17" s="3"/>
-      <c r="F17" s="3"/>
-      <c r="G17" s="3"/>
-      <c r="H17" s="3"/>
-      <c r="I17" s="3"/>
-      <c r="J17" s="3"/>
-      <c r="K17" s="4" t="str">
+      <c r="A17" s="2">
+        <v>46141</v>
+      </c>
+      <c r="B17" s="3">
+        <v>2.85</v>
+      </c>
+      <c r="C17" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="D17" s="3">
+        <v>2.67</v>
+      </c>
+      <c r="E17" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="F17" s="3">
+        <v>2.8</v>
+      </c>
+      <c r="G17" s="3">
+        <v>2.96</v>
+      </c>
+      <c r="H17" s="3">
+        <v>2.63</v>
+      </c>
+      <c r="I17" s="3">
+        <v>2.79</v>
+      </c>
+      <c r="J17" s="3">
+        <v>2.59</v>
+      </c>
+      <c r="K17" s="4">
         <f t="shared" si="0"/>
-        <v/>
+        <v>2.8077777777777779</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.25">
@@ -36038,7 +35740,7 @@
     </row>
     <row r="392" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A392" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -36063,7 +35765,7 @@
   <sheetData>
     <row r="1" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B1" s="7"/>
       <c r="C1" s="7"/>
@@ -36101,34 +35803,34 @@
         <v>3</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E4" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="G4" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="F4" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="G4" s="1" t="s">
+      <c r="H4" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="J4" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="K4" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="I4" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>36</v>
-      </c>
       <c r="L4" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
@@ -36600,20 +36302,42 @@
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A17" s="2"/>
-      <c r="B17" s="3"/>
-      <c r="C17" s="3"/>
-      <c r="D17" s="3"/>
-      <c r="E17" s="3"/>
-      <c r="F17" s="3"/>
-      <c r="G17" s="3"/>
-      <c r="H17" s="3"/>
-      <c r="I17" s="3"/>
-      <c r="J17" s="3"/>
-      <c r="K17" s="3"/>
-      <c r="L17" s="4" t="str">
+      <c r="A17" s="2">
+        <v>46141</v>
+      </c>
+      <c r="B17" s="3">
+        <v>3.55</v>
+      </c>
+      <c r="C17" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="D17" s="3">
+        <v>3.15</v>
+      </c>
+      <c r="E17" s="3">
+        <v>3.35</v>
+      </c>
+      <c r="F17" s="3">
+        <v>3.43</v>
+      </c>
+      <c r="G17" s="3">
+        <v>3.69</v>
+      </c>
+      <c r="H17" s="3">
+        <v>3.11</v>
+      </c>
+      <c r="I17" s="3">
+        <v>3.29</v>
+      </c>
+      <c r="J17" s="3">
+        <v>3.55</v>
+      </c>
+      <c r="K17" s="3">
+        <v>3.29</v>
+      </c>
+      <c r="L17" s="4">
         <f t="shared" si="0"/>
-        <v/>
+        <v>3.34</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
@@ -42959,7 +42683,7 @@
     </row>
     <row r="392" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A392" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>

--- a/app/mevduat-kredi-faizleri/data/hoca-ile-borsa-faiz-takip-sablonu-guncel.xlsx
+++ b/app/mevduat-kredi-faizleri/data/hoca-ile-borsa-faiz-takip-sablonu-guncel.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projeler\hoca-ile-borsa\app\mevduat-kredi-faizleri\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D41AB2A-B838-48C7-B0D5-2E0245BBCDEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{797B09B7-FE21-4512-88A1-CE5DCAF2271E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="18915" yWindow="5565" windowWidth="19665" windowHeight="15345" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="18735" yWindow="5535" windowWidth="19665" windowHeight="15345" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Mevduat" sheetId="1" r:id="rId1"/>
@@ -377,6 +377,9 @@
                 <c:pt idx="12">
                   <c:v>46141</c:v>
                 </c:pt>
+                <c:pt idx="13">
+                  <c:v>46142</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -426,7 +429,7 @@
                   <c:v>43.383478260869566</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0</c:v>
+                  <c:v>43.383478260869566</c:v>
                 </c:pt>
                 <c:pt idx="14">
                   <c:v>0</c:v>
@@ -1742,6 +1745,9 @@
                 <c:pt idx="12">
                   <c:v>46141</c:v>
                 </c:pt>
+                <c:pt idx="13">
+                  <c:v>46142</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1791,7 +1797,7 @@
                   <c:v>3.5657894736842097</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0</c:v>
+                  <c:v>3.5578947368421048</c:v>
                 </c:pt>
                 <c:pt idx="14">
                   <c:v>0</c:v>
@@ -3107,6 +3113,9 @@
                 <c:pt idx="12">
                   <c:v>46141</c:v>
                 </c:pt>
+                <c:pt idx="13">
+                  <c:v>46142</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3156,7 +3165,7 @@
                   <c:v>2.8077777777777779</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0</c:v>
+                  <c:v>2.8077777777777779</c:v>
                 </c:pt>
                 <c:pt idx="14">
                   <c:v>0</c:v>
@@ -4472,6 +4481,9 @@
                 <c:pt idx="12">
                   <c:v>46141</c:v>
                 </c:pt>
+                <c:pt idx="13">
+                  <c:v>46142</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -4521,7 +4533,7 @@
                   <c:v>3.34</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0</c:v>
+                  <c:v>3.34</c:v>
                 </c:pt>
                 <c:pt idx="14">
                   <c:v>0</c:v>
@@ -6386,7 +6398,7 @@
         <v>45.25</v>
       </c>
       <c r="Y5" s="4">
-        <f>IF(COUNTA(B5:X5)=0,"",AVERAGE(B5:X5))</f>
+        <f t="shared" ref="Y5:Y68" si="0">IF(COUNTA(B5:X5)=0,"",AVERAGE(B5:X5))</f>
         <v>43.078695652173913</v>
       </c>
     </row>
@@ -6464,7 +6476,7 @@
         <v>45.25</v>
       </c>
       <c r="Y6" s="4">
-        <f>IF(COUNTA(B6:X6)=0,"",AVERAGE(B6:X6))</f>
+        <f t="shared" si="0"/>
         <v>43.078695652173913</v>
       </c>
     </row>
@@ -6542,7 +6554,7 @@
         <v>45.25</v>
       </c>
       <c r="Y7" s="4">
-        <f>IF(COUNTA(B7:X7)=0,"",AVERAGE(B7:X7))</f>
+        <f t="shared" si="0"/>
         <v>43.078695652173913</v>
       </c>
     </row>
@@ -6620,7 +6632,7 @@
         <v>45.25</v>
       </c>
       <c r="Y8" s="4">
-        <f>IF(COUNTA(B8:X8)=0,"",AVERAGE(B8:X8))</f>
+        <f t="shared" si="0"/>
         <v>43.52</v>
       </c>
     </row>
@@ -6698,7 +6710,7 @@
         <v>45.25</v>
       </c>
       <c r="Y9" s="4">
-        <f>IF(COUNTA(B9:X9)=0,"",AVERAGE(B9:X9))</f>
+        <f t="shared" si="0"/>
         <v>43.35</v>
       </c>
     </row>
@@ -6776,7 +6788,7 @@
         <v>45.25</v>
       </c>
       <c r="Y10" s="4">
-        <f>IF(COUNTA(B10:X10)=0,"",AVERAGE(B10:X10))</f>
+        <f t="shared" si="0"/>
         <v>43.393478260869564</v>
       </c>
     </row>
@@ -6854,7 +6866,7 @@
         <v>45.25</v>
       </c>
       <c r="Y11" s="4">
-        <f>IF(COUNTA(B11:X11)=0,"",AVERAGE(B11:X11))</f>
+        <f t="shared" si="0"/>
         <v>43.35</v>
       </c>
     </row>
@@ -6932,7 +6944,7 @@
         <v>45.25</v>
       </c>
       <c r="Y12" s="4">
-        <f>IF(COUNTA(B12:X12)=0,"",AVERAGE(B12:X12))</f>
+        <f t="shared" si="0"/>
         <v>43.343043478260867</v>
       </c>
     </row>
@@ -7010,7 +7022,7 @@
         <v>45.25</v>
       </c>
       <c r="Y13" s="4">
-        <f>IF(COUNTA(B13:X13)=0,"",AVERAGE(B13:X13))</f>
+        <f t="shared" si="0"/>
         <v>43.375652173913046</v>
       </c>
     </row>
@@ -7088,7 +7100,7 @@
         <v>45.25</v>
       </c>
       <c r="Y14" s="4">
-        <f>IF(COUNTA(B14:X14)=0,"",AVERAGE(B14:X14))</f>
+        <f t="shared" si="0"/>
         <v>43.375652173913046</v>
       </c>
     </row>
@@ -7166,7 +7178,7 @@
         <v>45.25</v>
       </c>
       <c r="Y15" s="4">
-        <f>IF(COUNTA(B15:X15)=0,"",AVERAGE(B15:X15))</f>
+        <f t="shared" si="0"/>
         <v>43.364782608695648</v>
       </c>
     </row>
@@ -7244,7 +7256,7 @@
         <v>45.25</v>
       </c>
       <c r="Y16" s="4">
-        <f>IF(COUNTA(B16:X16)=0,"",AVERAGE(B16:X16))</f>
+        <f t="shared" si="0"/>
         <v>43.416086956521738</v>
       </c>
     </row>
@@ -7322,38 +7334,86 @@
         <v>45.25</v>
       </c>
       <c r="Y17" s="4">
-        <f>IF(COUNTA(B17:X17)=0,"",AVERAGE(B17:X17))</f>
+        <f t="shared" si="0"/>
         <v>43.383478260869566</v>
       </c>
     </row>
     <row r="18" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A18" s="2"/>
-      <c r="B18" s="3"/>
-      <c r="C18" s="3"/>
-      <c r="D18" s="3"/>
-      <c r="E18" s="3"/>
-      <c r="F18" s="3"/>
-      <c r="G18" s="3"/>
-      <c r="H18" s="3"/>
-      <c r="I18" s="3"/>
-      <c r="J18" s="3"/>
-      <c r="K18" s="3"/>
-      <c r="L18" s="3"/>
-      <c r="M18" s="3"/>
-      <c r="N18" s="3"/>
-      <c r="O18" s="3"/>
-      <c r="P18" s="3"/>
-      <c r="Q18" s="3"/>
-      <c r="R18" s="3"/>
-      <c r="S18" s="3"/>
-      <c r="T18" s="3"/>
-      <c r="U18" s="3"/>
-      <c r="V18" s="3"/>
-      <c r="W18" s="3"/>
-      <c r="X18" s="3"/>
-      <c r="Y18" s="4" t="str">
-        <f>IF(COUNTA(B18:X18)=0,"",AVERAGE(B18:X18))</f>
-        <v/>
+      <c r="A18" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B18" s="3">
+        <v>42</v>
+      </c>
+      <c r="C18" s="3">
+        <v>46</v>
+      </c>
+      <c r="D18" s="3">
+        <v>45</v>
+      </c>
+      <c r="E18" s="3">
+        <v>45</v>
+      </c>
+      <c r="F18" s="3">
+        <v>43.5</v>
+      </c>
+      <c r="G18" s="3">
+        <v>41.5</v>
+      </c>
+      <c r="H18" s="3">
+        <v>46</v>
+      </c>
+      <c r="I18" s="3">
+        <v>41.5</v>
+      </c>
+      <c r="J18" s="3">
+        <v>43</v>
+      </c>
+      <c r="K18" s="3">
+        <v>41</v>
+      </c>
+      <c r="L18" s="3">
+        <v>36</v>
+      </c>
+      <c r="M18" s="3">
+        <v>44</v>
+      </c>
+      <c r="N18" s="3">
+        <v>45</v>
+      </c>
+      <c r="O18" s="3">
+        <v>42.57</v>
+      </c>
+      <c r="P18" s="3">
+        <v>40</v>
+      </c>
+      <c r="Q18" s="3">
+        <v>45</v>
+      </c>
+      <c r="R18" s="3">
+        <v>45</v>
+      </c>
+      <c r="S18" s="3">
+        <v>45</v>
+      </c>
+      <c r="T18" s="3">
+        <v>43</v>
+      </c>
+      <c r="U18" s="3">
+        <v>43.5</v>
+      </c>
+      <c r="V18" s="3">
+        <v>42</v>
+      </c>
+      <c r="W18" s="3">
+        <v>47</v>
+      </c>
+      <c r="X18" s="3">
+        <v>45.25</v>
+      </c>
+      <c r="Y18" s="4">
+        <f t="shared" si="0"/>
+        <v>43.383478260869566</v>
       </c>
     </row>
     <row r="19" spans="1:25" x14ac:dyDescent="0.25">
@@ -7382,7 +7442,7 @@
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
       <c r="Y19" s="4" t="str">
-        <f>IF(COUNTA(B19:X19)=0,"",AVERAGE(B19:X19))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -7412,7 +7472,7 @@
       <c r="W20" s="3"/>
       <c r="X20" s="3"/>
       <c r="Y20" s="4" t="str">
-        <f>IF(COUNTA(B20:X20)=0,"",AVERAGE(B20:X20))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -7442,7 +7502,7 @@
       <c r="W21" s="3"/>
       <c r="X21" s="3"/>
       <c r="Y21" s="4" t="str">
-        <f>IF(COUNTA(B21:X21)=0,"",AVERAGE(B21:X21))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -7472,7 +7532,7 @@
       <c r="W22" s="3"/>
       <c r="X22" s="3"/>
       <c r="Y22" s="4" t="str">
-        <f>IF(COUNTA(B22:X22)=0,"",AVERAGE(B22:X22))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -7502,7 +7562,7 @@
       <c r="W23" s="3"/>
       <c r="X23" s="3"/>
       <c r="Y23" s="4" t="str">
-        <f>IF(COUNTA(B23:X23)=0,"",AVERAGE(B23:X23))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -7532,7 +7592,7 @@
       <c r="W24" s="3"/>
       <c r="X24" s="3"/>
       <c r="Y24" s="4" t="str">
-        <f>IF(COUNTA(B24:X24)=0,"",AVERAGE(B24:X24))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -7562,7 +7622,7 @@
       <c r="W25" s="3"/>
       <c r="X25" s="3"/>
       <c r="Y25" s="4" t="str">
-        <f>IF(COUNTA(B25:X25)=0,"",AVERAGE(B25:X25))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -7592,7 +7652,7 @@
       <c r="W26" s="3"/>
       <c r="X26" s="3"/>
       <c r="Y26" s="4" t="str">
-        <f>IF(COUNTA(B26:X26)=0,"",AVERAGE(B26:X26))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -7622,7 +7682,7 @@
       <c r="W27" s="3"/>
       <c r="X27" s="3"/>
       <c r="Y27" s="4" t="str">
-        <f>IF(COUNTA(B27:X27)=0,"",AVERAGE(B27:X27))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -7652,7 +7712,7 @@
       <c r="W28" s="3"/>
       <c r="X28" s="3"/>
       <c r="Y28" s="4" t="str">
-        <f>IF(COUNTA(B28:X28)=0,"",AVERAGE(B28:X28))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -7682,7 +7742,7 @@
       <c r="W29" s="3"/>
       <c r="X29" s="3"/>
       <c r="Y29" s="4" t="str">
-        <f>IF(COUNTA(B29:X29)=0,"",AVERAGE(B29:X29))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -7712,7 +7772,7 @@
       <c r="W30" s="3"/>
       <c r="X30" s="3"/>
       <c r="Y30" s="4" t="str">
-        <f>IF(COUNTA(B30:X30)=0,"",AVERAGE(B30:X30))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -7742,7 +7802,7 @@
       <c r="W31" s="3"/>
       <c r="X31" s="3"/>
       <c r="Y31" s="4" t="str">
-        <f>IF(COUNTA(B31:X31)=0,"",AVERAGE(B31:X31))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -7772,7 +7832,7 @@
       <c r="W32" s="3"/>
       <c r="X32" s="3"/>
       <c r="Y32" s="4" t="str">
-        <f>IF(COUNTA(B32:X32)=0,"",AVERAGE(B32:X32))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -7802,7 +7862,7 @@
       <c r="W33" s="3"/>
       <c r="X33" s="3"/>
       <c r="Y33" s="4" t="str">
-        <f>IF(COUNTA(B33:X33)=0,"",AVERAGE(B33:X33))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -7832,7 +7892,7 @@
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="4" t="str">
-        <f>IF(COUNTA(B34:X34)=0,"",AVERAGE(B34:X34))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -7862,7 +7922,7 @@
       <c r="W35" s="3"/>
       <c r="X35" s="3"/>
       <c r="Y35" s="4" t="str">
-        <f>IF(COUNTA(B35:X35)=0,"",AVERAGE(B35:X35))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -7892,7 +7952,7 @@
       <c r="W36" s="3"/>
       <c r="X36" s="3"/>
       <c r="Y36" s="4" t="str">
-        <f>IF(COUNTA(B36:X36)=0,"",AVERAGE(B36:X36))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -7922,7 +7982,7 @@
       <c r="W37" s="3"/>
       <c r="X37" s="3"/>
       <c r="Y37" s="4" t="str">
-        <f>IF(COUNTA(B37:X37)=0,"",AVERAGE(B37:X37))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -7952,7 +8012,7 @@
       <c r="W38" s="3"/>
       <c r="X38" s="3"/>
       <c r="Y38" s="4" t="str">
-        <f>IF(COUNTA(B38:X38)=0,"",AVERAGE(B38:X38))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -7982,7 +8042,7 @@
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
       <c r="Y39" s="4" t="str">
-        <f>IF(COUNTA(B39:X39)=0,"",AVERAGE(B39:X39))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -8012,7 +8072,7 @@
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
       <c r="Y40" s="4" t="str">
-        <f>IF(COUNTA(B40:X40)=0,"",AVERAGE(B40:X40))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -8042,7 +8102,7 @@
       <c r="W41" s="3"/>
       <c r="X41" s="3"/>
       <c r="Y41" s="4" t="str">
-        <f>IF(COUNTA(B41:X41)=0,"",AVERAGE(B41:X41))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -8072,7 +8132,7 @@
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
       <c r="Y42" s="4" t="str">
-        <f>IF(COUNTA(B42:X42)=0,"",AVERAGE(B42:X42))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -8102,7 +8162,7 @@
       <c r="W43" s="3"/>
       <c r="X43" s="3"/>
       <c r="Y43" s="4" t="str">
-        <f>IF(COUNTA(B43:X43)=0,"",AVERAGE(B43:X43))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -8132,7 +8192,7 @@
       <c r="W44" s="3"/>
       <c r="X44" s="3"/>
       <c r="Y44" s="4" t="str">
-        <f>IF(COUNTA(B44:X44)=0,"",AVERAGE(B44:X44))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -8162,7 +8222,7 @@
       <c r="W45" s="3"/>
       <c r="X45" s="3"/>
       <c r="Y45" s="4" t="str">
-        <f>IF(COUNTA(B45:X45)=0,"",AVERAGE(B45:X45))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -8192,7 +8252,7 @@
       <c r="W46" s="3"/>
       <c r="X46" s="3"/>
       <c r="Y46" s="4" t="str">
-        <f>IF(COUNTA(B46:X46)=0,"",AVERAGE(B46:X46))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -8222,7 +8282,7 @@
       <c r="W47" s="3"/>
       <c r="X47" s="3"/>
       <c r="Y47" s="4" t="str">
-        <f>IF(COUNTA(B47:X47)=0,"",AVERAGE(B47:X47))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -8252,7 +8312,7 @@
       <c r="W48" s="3"/>
       <c r="X48" s="3"/>
       <c r="Y48" s="4" t="str">
-        <f>IF(COUNTA(B48:X48)=0,"",AVERAGE(B48:X48))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -8282,7 +8342,7 @@
       <c r="W49" s="3"/>
       <c r="X49" s="3"/>
       <c r="Y49" s="4" t="str">
-        <f>IF(COUNTA(B49:X49)=0,"",AVERAGE(B49:X49))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -8312,7 +8372,7 @@
       <c r="W50" s="3"/>
       <c r="X50" s="3"/>
       <c r="Y50" s="4" t="str">
-        <f>IF(COUNTA(B50:X50)=0,"",AVERAGE(B50:X50))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -8342,7 +8402,7 @@
       <c r="W51" s="3"/>
       <c r="X51" s="3"/>
       <c r="Y51" s="4" t="str">
-        <f>IF(COUNTA(B51:X51)=0,"",AVERAGE(B51:X51))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -8372,7 +8432,7 @@
       <c r="W52" s="3"/>
       <c r="X52" s="3"/>
       <c r="Y52" s="4" t="str">
-        <f>IF(COUNTA(B52:X52)=0,"",AVERAGE(B52:X52))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -8402,7 +8462,7 @@
       <c r="W53" s="3"/>
       <c r="X53" s="3"/>
       <c r="Y53" s="4" t="str">
-        <f>IF(COUNTA(B53:X53)=0,"",AVERAGE(B53:X53))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -8432,7 +8492,7 @@
       <c r="W54" s="3"/>
       <c r="X54" s="3"/>
       <c r="Y54" s="4" t="str">
-        <f>IF(COUNTA(B54:X54)=0,"",AVERAGE(B54:X54))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -8462,7 +8522,7 @@
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
       <c r="Y55" s="4" t="str">
-        <f>IF(COUNTA(B55:X55)=0,"",AVERAGE(B55:X55))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -8492,7 +8552,7 @@
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
       <c r="Y56" s="4" t="str">
-        <f>IF(COUNTA(B56:X56)=0,"",AVERAGE(B56:X56))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -8522,7 +8582,7 @@
       <c r="W57" s="3"/>
       <c r="X57" s="3"/>
       <c r="Y57" s="4" t="str">
-        <f>IF(COUNTA(B57:X57)=0,"",AVERAGE(B57:X57))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -8552,7 +8612,7 @@
       <c r="W58" s="3"/>
       <c r="X58" s="3"/>
       <c r="Y58" s="4" t="str">
-        <f>IF(COUNTA(B58:X58)=0,"",AVERAGE(B58:X58))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -8582,7 +8642,7 @@
       <c r="W59" s="3"/>
       <c r="X59" s="3"/>
       <c r="Y59" s="4" t="str">
-        <f>IF(COUNTA(B59:X59)=0,"",AVERAGE(B59:X59))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -8612,7 +8672,7 @@
       <c r="W60" s="3"/>
       <c r="X60" s="3"/>
       <c r="Y60" s="4" t="str">
-        <f>IF(COUNTA(B60:X60)=0,"",AVERAGE(B60:X60))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -8642,7 +8702,7 @@
       <c r="W61" s="3"/>
       <c r="X61" s="3"/>
       <c r="Y61" s="4" t="str">
-        <f>IF(COUNTA(B61:X61)=0,"",AVERAGE(B61:X61))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -8672,7 +8732,7 @@
       <c r="W62" s="3"/>
       <c r="X62" s="3"/>
       <c r="Y62" s="4" t="str">
-        <f>IF(COUNTA(B62:X62)=0,"",AVERAGE(B62:X62))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -8702,7 +8762,7 @@
       <c r="W63" s="3"/>
       <c r="X63" s="3"/>
       <c r="Y63" s="4" t="str">
-        <f>IF(COUNTA(B63:X63)=0,"",AVERAGE(B63:X63))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -8732,7 +8792,7 @@
       <c r="W64" s="3"/>
       <c r="X64" s="3"/>
       <c r="Y64" s="4" t="str">
-        <f>IF(COUNTA(B64:X64)=0,"",AVERAGE(B64:X64))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -8762,7 +8822,7 @@
       <c r="W65" s="3"/>
       <c r="X65" s="3"/>
       <c r="Y65" s="4" t="str">
-        <f>IF(COUNTA(B65:X65)=0,"",AVERAGE(B65:X65))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -8792,7 +8852,7 @@
       <c r="W66" s="3"/>
       <c r="X66" s="3"/>
       <c r="Y66" s="4" t="str">
-        <f>IF(COUNTA(B66:X66)=0,"",AVERAGE(B66:X66))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -8822,7 +8882,7 @@
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
       <c r="Y67" s="4" t="str">
-        <f>IF(COUNTA(B67:X67)=0,"",AVERAGE(B67:X67))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -8852,7 +8912,7 @@
       <c r="W68" s="3"/>
       <c r="X68" s="3"/>
       <c r="Y68" s="4" t="str">
-        <f>IF(COUNTA(B68:X68)=0,"",AVERAGE(B68:X68))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -8882,7 +8942,7 @@
       <c r="W69" s="3"/>
       <c r="X69" s="3"/>
       <c r="Y69" s="4" t="str">
-        <f>IF(COUNTA(B69:X69)=0,"",AVERAGE(B69:X69))</f>
+        <f t="shared" ref="Y69:Y132" si="1">IF(COUNTA(B69:X69)=0,"",AVERAGE(B69:X69))</f>
         <v/>
       </c>
     </row>
@@ -8912,7 +8972,7 @@
       <c r="W70" s="3"/>
       <c r="X70" s="3"/>
       <c r="Y70" s="4" t="str">
-        <f>IF(COUNTA(B70:X70)=0,"",AVERAGE(B70:X70))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -8942,7 +9002,7 @@
       <c r="W71" s="3"/>
       <c r="X71" s="3"/>
       <c r="Y71" s="4" t="str">
-        <f>IF(COUNTA(B71:X71)=0,"",AVERAGE(B71:X71))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -8972,7 +9032,7 @@
       <c r="W72" s="3"/>
       <c r="X72" s="3"/>
       <c r="Y72" s="4" t="str">
-        <f>IF(COUNTA(B72:X72)=0,"",AVERAGE(B72:X72))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -9002,7 +9062,7 @@
       <c r="W73" s="3"/>
       <c r="X73" s="3"/>
       <c r="Y73" s="4" t="str">
-        <f>IF(COUNTA(B73:X73)=0,"",AVERAGE(B73:X73))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -9032,7 +9092,7 @@
       <c r="W74" s="3"/>
       <c r="X74" s="3"/>
       <c r="Y74" s="4" t="str">
-        <f>IF(COUNTA(B74:X74)=0,"",AVERAGE(B74:X74))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -9062,7 +9122,7 @@
       <c r="W75" s="3"/>
       <c r="X75" s="3"/>
       <c r="Y75" s="4" t="str">
-        <f>IF(COUNTA(B75:X75)=0,"",AVERAGE(B75:X75))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -9092,7 +9152,7 @@
       <c r="W76" s="3"/>
       <c r="X76" s="3"/>
       <c r="Y76" s="4" t="str">
-        <f>IF(COUNTA(B76:X76)=0,"",AVERAGE(B76:X76))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -9122,7 +9182,7 @@
       <c r="W77" s="3"/>
       <c r="X77" s="3"/>
       <c r="Y77" s="4" t="str">
-        <f>IF(COUNTA(B77:X77)=0,"",AVERAGE(B77:X77))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -9152,7 +9212,7 @@
       <c r="W78" s="3"/>
       <c r="X78" s="3"/>
       <c r="Y78" s="4" t="str">
-        <f>IF(COUNTA(B78:X78)=0,"",AVERAGE(B78:X78))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -9182,7 +9242,7 @@
       <c r="W79" s="3"/>
       <c r="X79" s="3"/>
       <c r="Y79" s="4" t="str">
-        <f>IF(COUNTA(B79:X79)=0,"",AVERAGE(B79:X79))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -9212,7 +9272,7 @@
       <c r="W80" s="3"/>
       <c r="X80" s="3"/>
       <c r="Y80" s="4" t="str">
-        <f>IF(COUNTA(B80:X80)=0,"",AVERAGE(B80:X80))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -9242,7 +9302,7 @@
       <c r="W81" s="3"/>
       <c r="X81" s="3"/>
       <c r="Y81" s="4" t="str">
-        <f>IF(COUNTA(B81:X81)=0,"",AVERAGE(B81:X81))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -9272,7 +9332,7 @@
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
       <c r="Y82" s="4" t="str">
-        <f>IF(COUNTA(B82:X82)=0,"",AVERAGE(B82:X82))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -9302,7 +9362,7 @@
       <c r="W83" s="3"/>
       <c r="X83" s="3"/>
       <c r="Y83" s="4" t="str">
-        <f>IF(COUNTA(B83:X83)=0,"",AVERAGE(B83:X83))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -9332,7 +9392,7 @@
       <c r="W84" s="3"/>
       <c r="X84" s="3"/>
       <c r="Y84" s="4" t="str">
-        <f>IF(COUNTA(B84:X84)=0,"",AVERAGE(B84:X84))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -9362,7 +9422,7 @@
       <c r="W85" s="3"/>
       <c r="X85" s="3"/>
       <c r="Y85" s="4" t="str">
-        <f>IF(COUNTA(B85:X85)=0,"",AVERAGE(B85:X85))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -9392,7 +9452,7 @@
       <c r="W86" s="3"/>
       <c r="X86" s="3"/>
       <c r="Y86" s="4" t="str">
-        <f>IF(COUNTA(B86:X86)=0,"",AVERAGE(B86:X86))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -9422,7 +9482,7 @@
       <c r="W87" s="3"/>
       <c r="X87" s="3"/>
       <c r="Y87" s="4" t="str">
-        <f>IF(COUNTA(B87:X87)=0,"",AVERAGE(B87:X87))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -9452,7 +9512,7 @@
       <c r="W88" s="3"/>
       <c r="X88" s="3"/>
       <c r="Y88" s="4" t="str">
-        <f>IF(COUNTA(B88:X88)=0,"",AVERAGE(B88:X88))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -9482,7 +9542,7 @@
       <c r="W89" s="3"/>
       <c r="X89" s="3"/>
       <c r="Y89" s="4" t="str">
-        <f>IF(COUNTA(B89:X89)=0,"",AVERAGE(B89:X89))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -9512,7 +9572,7 @@
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
       <c r="Y90" s="4" t="str">
-        <f>IF(COUNTA(B90:X90)=0,"",AVERAGE(B90:X90))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -9542,7 +9602,7 @@
       <c r="W91" s="3"/>
       <c r="X91" s="3"/>
       <c r="Y91" s="4" t="str">
-        <f>IF(COUNTA(B91:X91)=0,"",AVERAGE(B91:X91))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -9572,7 +9632,7 @@
       <c r="W92" s="3"/>
       <c r="X92" s="3"/>
       <c r="Y92" s="4" t="str">
-        <f>IF(COUNTA(B92:X92)=0,"",AVERAGE(B92:X92))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -9602,7 +9662,7 @@
       <c r="W93" s="3"/>
       <c r="X93" s="3"/>
       <c r="Y93" s="4" t="str">
-        <f>IF(COUNTA(B93:X93)=0,"",AVERAGE(B93:X93))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -9632,7 +9692,7 @@
       <c r="W94" s="3"/>
       <c r="X94" s="3"/>
       <c r="Y94" s="4" t="str">
-        <f>IF(COUNTA(B94:X94)=0,"",AVERAGE(B94:X94))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -9662,7 +9722,7 @@
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
       <c r="Y95" s="4" t="str">
-        <f>IF(COUNTA(B95:X95)=0,"",AVERAGE(B95:X95))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -9692,7 +9752,7 @@
       <c r="W96" s="3"/>
       <c r="X96" s="3"/>
       <c r="Y96" s="4" t="str">
-        <f>IF(COUNTA(B96:X96)=0,"",AVERAGE(B96:X96))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -9722,7 +9782,7 @@
       <c r="W97" s="3"/>
       <c r="X97" s="3"/>
       <c r="Y97" s="4" t="str">
-        <f>IF(COUNTA(B97:X97)=0,"",AVERAGE(B97:X97))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -9752,7 +9812,7 @@
       <c r="W98" s="3"/>
       <c r="X98" s="3"/>
       <c r="Y98" s="4" t="str">
-        <f>IF(COUNTA(B98:X98)=0,"",AVERAGE(B98:X98))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -9782,7 +9842,7 @@
       <c r="W99" s="3"/>
       <c r="X99" s="3"/>
       <c r="Y99" s="4" t="str">
-        <f>IF(COUNTA(B99:X99)=0,"",AVERAGE(B99:X99))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -9812,7 +9872,7 @@
       <c r="W100" s="3"/>
       <c r="X100" s="3"/>
       <c r="Y100" s="4" t="str">
-        <f>IF(COUNTA(B100:X100)=0,"",AVERAGE(B100:X100))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -9842,7 +9902,7 @@
       <c r="W101" s="3"/>
       <c r="X101" s="3"/>
       <c r="Y101" s="4" t="str">
-        <f>IF(COUNTA(B101:X101)=0,"",AVERAGE(B101:X101))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -9872,7 +9932,7 @@
       <c r="W102" s="3"/>
       <c r="X102" s="3"/>
       <c r="Y102" s="4" t="str">
-        <f>IF(COUNTA(B102:X102)=0,"",AVERAGE(B102:X102))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -9902,7 +9962,7 @@
       <c r="W103" s="3"/>
       <c r="X103" s="3"/>
       <c r="Y103" s="4" t="str">
-        <f>IF(COUNTA(B103:X103)=0,"",AVERAGE(B103:X103))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -9932,7 +9992,7 @@
       <c r="W104" s="3"/>
       <c r="X104" s="3"/>
       <c r="Y104" s="4" t="str">
-        <f>IF(COUNTA(B104:X104)=0,"",AVERAGE(B104:X104))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -9962,7 +10022,7 @@
       <c r="W105" s="3"/>
       <c r="X105" s="3"/>
       <c r="Y105" s="4" t="str">
-        <f>IF(COUNTA(B105:X105)=0,"",AVERAGE(B105:X105))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -9992,7 +10052,7 @@
       <c r="W106" s="3"/>
       <c r="X106" s="3"/>
       <c r="Y106" s="4" t="str">
-        <f>IF(COUNTA(B106:X106)=0,"",AVERAGE(B106:X106))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -10022,7 +10082,7 @@
       <c r="W107" s="3"/>
       <c r="X107" s="3"/>
       <c r="Y107" s="4" t="str">
-        <f>IF(COUNTA(B107:X107)=0,"",AVERAGE(B107:X107))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -10052,7 +10112,7 @@
       <c r="W108" s="3"/>
       <c r="X108" s="3"/>
       <c r="Y108" s="4" t="str">
-        <f>IF(COUNTA(B108:X108)=0,"",AVERAGE(B108:X108))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -10082,7 +10142,7 @@
       <c r="W109" s="3"/>
       <c r="X109" s="3"/>
       <c r="Y109" s="4" t="str">
-        <f>IF(COUNTA(B109:X109)=0,"",AVERAGE(B109:X109))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -10112,7 +10172,7 @@
       <c r="W110" s="3"/>
       <c r="X110" s="3"/>
       <c r="Y110" s="4" t="str">
-        <f>IF(COUNTA(B110:X110)=0,"",AVERAGE(B110:X110))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -10142,7 +10202,7 @@
       <c r="W111" s="3"/>
       <c r="X111" s="3"/>
       <c r="Y111" s="4" t="str">
-        <f>IF(COUNTA(B111:X111)=0,"",AVERAGE(B111:X111))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -10172,7 +10232,7 @@
       <c r="W112" s="3"/>
       <c r="X112" s="3"/>
       <c r="Y112" s="4" t="str">
-        <f>IF(COUNTA(B112:X112)=0,"",AVERAGE(B112:X112))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -10202,7 +10262,7 @@
       <c r="W113" s="3"/>
       <c r="X113" s="3"/>
       <c r="Y113" s="4" t="str">
-        <f>IF(COUNTA(B113:X113)=0,"",AVERAGE(B113:X113))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -10232,7 +10292,7 @@
       <c r="W114" s="3"/>
       <c r="X114" s="3"/>
       <c r="Y114" s="4" t="str">
-        <f>IF(COUNTA(B114:X114)=0,"",AVERAGE(B114:X114))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -10262,7 +10322,7 @@
       <c r="W115" s="3"/>
       <c r="X115" s="3"/>
       <c r="Y115" s="4" t="str">
-        <f>IF(COUNTA(B115:X115)=0,"",AVERAGE(B115:X115))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -10292,7 +10352,7 @@
       <c r="W116" s="3"/>
       <c r="X116" s="3"/>
       <c r="Y116" s="4" t="str">
-        <f>IF(COUNTA(B116:X116)=0,"",AVERAGE(B116:X116))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -10322,7 +10382,7 @@
       <c r="W117" s="3"/>
       <c r="X117" s="3"/>
       <c r="Y117" s="4" t="str">
-        <f>IF(COUNTA(B117:X117)=0,"",AVERAGE(B117:X117))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -10352,7 +10412,7 @@
       <c r="W118" s="3"/>
       <c r="X118" s="3"/>
       <c r="Y118" s="4" t="str">
-        <f>IF(COUNTA(B118:X118)=0,"",AVERAGE(B118:X118))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -10382,7 +10442,7 @@
       <c r="W119" s="3"/>
       <c r="X119" s="3"/>
       <c r="Y119" s="4" t="str">
-        <f>IF(COUNTA(B119:X119)=0,"",AVERAGE(B119:X119))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -10412,7 +10472,7 @@
       <c r="W120" s="3"/>
       <c r="X120" s="3"/>
       <c r="Y120" s="4" t="str">
-        <f>IF(COUNTA(B120:X120)=0,"",AVERAGE(B120:X120))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -10442,7 +10502,7 @@
       <c r="W121" s="3"/>
       <c r="X121" s="3"/>
       <c r="Y121" s="4" t="str">
-        <f>IF(COUNTA(B121:X121)=0,"",AVERAGE(B121:X121))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -10472,7 +10532,7 @@
       <c r="W122" s="3"/>
       <c r="X122" s="3"/>
       <c r="Y122" s="4" t="str">
-        <f>IF(COUNTA(B122:X122)=0,"",AVERAGE(B122:X122))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -10502,7 +10562,7 @@
       <c r="W123" s="3"/>
       <c r="X123" s="3"/>
       <c r="Y123" s="4" t="str">
-        <f>IF(COUNTA(B123:X123)=0,"",AVERAGE(B123:X123))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -10532,7 +10592,7 @@
       <c r="W124" s="3"/>
       <c r="X124" s="3"/>
       <c r="Y124" s="4" t="str">
-        <f>IF(COUNTA(B124:X124)=0,"",AVERAGE(B124:X124))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -10562,7 +10622,7 @@
       <c r="W125" s="3"/>
       <c r="X125" s="3"/>
       <c r="Y125" s="4" t="str">
-        <f>IF(COUNTA(B125:X125)=0,"",AVERAGE(B125:X125))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -10592,7 +10652,7 @@
       <c r="W126" s="3"/>
       <c r="X126" s="3"/>
       <c r="Y126" s="4" t="str">
-        <f>IF(COUNTA(B126:X126)=0,"",AVERAGE(B126:X126))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -10622,7 +10682,7 @@
       <c r="W127" s="3"/>
       <c r="X127" s="3"/>
       <c r="Y127" s="4" t="str">
-        <f>IF(COUNTA(B127:X127)=0,"",AVERAGE(B127:X127))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -10652,7 +10712,7 @@
       <c r="W128" s="3"/>
       <c r="X128" s="3"/>
       <c r="Y128" s="4" t="str">
-        <f>IF(COUNTA(B128:X128)=0,"",AVERAGE(B128:X128))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -10682,7 +10742,7 @@
       <c r="W129" s="3"/>
       <c r="X129" s="3"/>
       <c r="Y129" s="4" t="str">
-        <f>IF(COUNTA(B129:X129)=0,"",AVERAGE(B129:X129))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -10712,7 +10772,7 @@
       <c r="W130" s="3"/>
       <c r="X130" s="3"/>
       <c r="Y130" s="4" t="str">
-        <f>IF(COUNTA(B130:X130)=0,"",AVERAGE(B130:X130))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -10742,7 +10802,7 @@
       <c r="W131" s="3"/>
       <c r="X131" s="3"/>
       <c r="Y131" s="4" t="str">
-        <f>IF(COUNTA(B131:X131)=0,"",AVERAGE(B131:X131))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -10772,7 +10832,7 @@
       <c r="W132" s="3"/>
       <c r="X132" s="3"/>
       <c r="Y132" s="4" t="str">
-        <f>IF(COUNTA(B132:X132)=0,"",AVERAGE(B132:X132))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -10802,7 +10862,7 @@
       <c r="W133" s="3"/>
       <c r="X133" s="3"/>
       <c r="Y133" s="4" t="str">
-        <f>IF(COUNTA(B133:X133)=0,"",AVERAGE(B133:X133))</f>
+        <f t="shared" ref="Y133:Y196" si="2">IF(COUNTA(B133:X133)=0,"",AVERAGE(B133:X133))</f>
         <v/>
       </c>
     </row>
@@ -10832,7 +10892,7 @@
       <c r="W134" s="3"/>
       <c r="X134" s="3"/>
       <c r="Y134" s="4" t="str">
-        <f>IF(COUNTA(B134:X134)=0,"",AVERAGE(B134:X134))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -10862,7 +10922,7 @@
       <c r="W135" s="3"/>
       <c r="X135" s="3"/>
       <c r="Y135" s="4" t="str">
-        <f>IF(COUNTA(B135:X135)=0,"",AVERAGE(B135:X135))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -10892,7 +10952,7 @@
       <c r="W136" s="3"/>
       <c r="X136" s="3"/>
       <c r="Y136" s="4" t="str">
-        <f>IF(COUNTA(B136:X136)=0,"",AVERAGE(B136:X136))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -10922,7 +10982,7 @@
       <c r="W137" s="3"/>
       <c r="X137" s="3"/>
       <c r="Y137" s="4" t="str">
-        <f>IF(COUNTA(B137:X137)=0,"",AVERAGE(B137:X137))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -10952,7 +11012,7 @@
       <c r="W138" s="3"/>
       <c r="X138" s="3"/>
       <c r="Y138" s="4" t="str">
-        <f>IF(COUNTA(B138:X138)=0,"",AVERAGE(B138:X138))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -10982,7 +11042,7 @@
       <c r="W139" s="3"/>
       <c r="X139" s="3"/>
       <c r="Y139" s="4" t="str">
-        <f>IF(COUNTA(B139:X139)=0,"",AVERAGE(B139:X139))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -11012,7 +11072,7 @@
       <c r="W140" s="3"/>
       <c r="X140" s="3"/>
       <c r="Y140" s="4" t="str">
-        <f>IF(COUNTA(B140:X140)=0,"",AVERAGE(B140:X140))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -11042,7 +11102,7 @@
       <c r="W141" s="3"/>
       <c r="X141" s="3"/>
       <c r="Y141" s="4" t="str">
-        <f>IF(COUNTA(B141:X141)=0,"",AVERAGE(B141:X141))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -11072,7 +11132,7 @@
       <c r="W142" s="3"/>
       <c r="X142" s="3"/>
       <c r="Y142" s="4" t="str">
-        <f>IF(COUNTA(B142:X142)=0,"",AVERAGE(B142:X142))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -11102,7 +11162,7 @@
       <c r="W143" s="3"/>
       <c r="X143" s="3"/>
       <c r="Y143" s="4" t="str">
-        <f>IF(COUNTA(B143:X143)=0,"",AVERAGE(B143:X143))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -11132,7 +11192,7 @@
       <c r="W144" s="3"/>
       <c r="X144" s="3"/>
       <c r="Y144" s="4" t="str">
-        <f>IF(COUNTA(B144:X144)=0,"",AVERAGE(B144:X144))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -11162,7 +11222,7 @@
       <c r="W145" s="3"/>
       <c r="X145" s="3"/>
       <c r="Y145" s="4" t="str">
-        <f>IF(COUNTA(B145:X145)=0,"",AVERAGE(B145:X145))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -11192,7 +11252,7 @@
       <c r="W146" s="3"/>
       <c r="X146" s="3"/>
       <c r="Y146" s="4" t="str">
-        <f>IF(COUNTA(B146:X146)=0,"",AVERAGE(B146:X146))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -11222,7 +11282,7 @@
       <c r="W147" s="3"/>
       <c r="X147" s="3"/>
       <c r="Y147" s="4" t="str">
-        <f>IF(COUNTA(B147:X147)=0,"",AVERAGE(B147:X147))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -11252,7 +11312,7 @@
       <c r="W148" s="3"/>
       <c r="X148" s="3"/>
       <c r="Y148" s="4" t="str">
-        <f>IF(COUNTA(B148:X148)=0,"",AVERAGE(B148:X148))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -11282,7 +11342,7 @@
       <c r="W149" s="3"/>
       <c r="X149" s="3"/>
       <c r="Y149" s="4" t="str">
-        <f>IF(COUNTA(B149:X149)=0,"",AVERAGE(B149:X149))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -11312,7 +11372,7 @@
       <c r="W150" s="3"/>
       <c r="X150" s="3"/>
       <c r="Y150" s="4" t="str">
-        <f>IF(COUNTA(B150:X150)=0,"",AVERAGE(B150:X150))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -11342,7 +11402,7 @@
       <c r="W151" s="3"/>
       <c r="X151" s="3"/>
       <c r="Y151" s="4" t="str">
-        <f>IF(COUNTA(B151:X151)=0,"",AVERAGE(B151:X151))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -11372,7 +11432,7 @@
       <c r="W152" s="3"/>
       <c r="X152" s="3"/>
       <c r="Y152" s="4" t="str">
-        <f>IF(COUNTA(B152:X152)=0,"",AVERAGE(B152:X152))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -11402,7 +11462,7 @@
       <c r="W153" s="3"/>
       <c r="X153" s="3"/>
       <c r="Y153" s="4" t="str">
-        <f>IF(COUNTA(B153:X153)=0,"",AVERAGE(B153:X153))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -11432,7 +11492,7 @@
       <c r="W154" s="3"/>
       <c r="X154" s="3"/>
       <c r="Y154" s="4" t="str">
-        <f>IF(COUNTA(B154:X154)=0,"",AVERAGE(B154:X154))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -11462,7 +11522,7 @@
       <c r="W155" s="3"/>
       <c r="X155" s="3"/>
       <c r="Y155" s="4" t="str">
-        <f>IF(COUNTA(B155:X155)=0,"",AVERAGE(B155:X155))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -11492,7 +11552,7 @@
       <c r="W156" s="3"/>
       <c r="X156" s="3"/>
       <c r="Y156" s="4" t="str">
-        <f>IF(COUNTA(B156:X156)=0,"",AVERAGE(B156:X156))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -11522,7 +11582,7 @@
       <c r="W157" s="3"/>
       <c r="X157" s="3"/>
       <c r="Y157" s="4" t="str">
-        <f>IF(COUNTA(B157:X157)=0,"",AVERAGE(B157:X157))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -11552,7 +11612,7 @@
       <c r="W158" s="3"/>
       <c r="X158" s="3"/>
       <c r="Y158" s="4" t="str">
-        <f>IF(COUNTA(B158:X158)=0,"",AVERAGE(B158:X158))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -11582,7 +11642,7 @@
       <c r="W159" s="3"/>
       <c r="X159" s="3"/>
       <c r="Y159" s="4" t="str">
-        <f>IF(COUNTA(B159:X159)=0,"",AVERAGE(B159:X159))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -11612,7 +11672,7 @@
       <c r="W160" s="3"/>
       <c r="X160" s="3"/>
       <c r="Y160" s="4" t="str">
-        <f>IF(COUNTA(B160:X160)=0,"",AVERAGE(B160:X160))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -11642,7 +11702,7 @@
       <c r="W161" s="3"/>
       <c r="X161" s="3"/>
       <c r="Y161" s="4" t="str">
-        <f>IF(COUNTA(B161:X161)=0,"",AVERAGE(B161:X161))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -11672,7 +11732,7 @@
       <c r="W162" s="3"/>
       <c r="X162" s="3"/>
       <c r="Y162" s="4" t="str">
-        <f>IF(COUNTA(B162:X162)=0,"",AVERAGE(B162:X162))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -11702,7 +11762,7 @@
       <c r="W163" s="3"/>
       <c r="X163" s="3"/>
       <c r="Y163" s="4" t="str">
-        <f>IF(COUNTA(B163:X163)=0,"",AVERAGE(B163:X163))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -11732,7 +11792,7 @@
       <c r="W164" s="3"/>
       <c r="X164" s="3"/>
       <c r="Y164" s="4" t="str">
-        <f>IF(COUNTA(B164:X164)=0,"",AVERAGE(B164:X164))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -11762,7 +11822,7 @@
       <c r="W165" s="3"/>
       <c r="X165" s="3"/>
       <c r="Y165" s="4" t="str">
-        <f>IF(COUNTA(B165:X165)=0,"",AVERAGE(B165:X165))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -11792,7 +11852,7 @@
       <c r="W166" s="3"/>
       <c r="X166" s="3"/>
       <c r="Y166" s="4" t="str">
-        <f>IF(COUNTA(B166:X166)=0,"",AVERAGE(B166:X166))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -11822,7 +11882,7 @@
       <c r="W167" s="3"/>
       <c r="X167" s="3"/>
       <c r="Y167" s="4" t="str">
-        <f>IF(COUNTA(B167:X167)=0,"",AVERAGE(B167:X167))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -11852,7 +11912,7 @@
       <c r="W168" s="3"/>
       <c r="X168" s="3"/>
       <c r="Y168" s="4" t="str">
-        <f>IF(COUNTA(B168:X168)=0,"",AVERAGE(B168:X168))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -11882,7 +11942,7 @@
       <c r="W169" s="3"/>
       <c r="X169" s="3"/>
       <c r="Y169" s="4" t="str">
-        <f>IF(COUNTA(B169:X169)=0,"",AVERAGE(B169:X169))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -11912,7 +11972,7 @@
       <c r="W170" s="3"/>
       <c r="X170" s="3"/>
       <c r="Y170" s="4" t="str">
-        <f>IF(COUNTA(B170:X170)=0,"",AVERAGE(B170:X170))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -11942,7 +12002,7 @@
       <c r="W171" s="3"/>
       <c r="X171" s="3"/>
       <c r="Y171" s="4" t="str">
-        <f>IF(COUNTA(B171:X171)=0,"",AVERAGE(B171:X171))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -11972,7 +12032,7 @@
       <c r="W172" s="3"/>
       <c r="X172" s="3"/>
       <c r="Y172" s="4" t="str">
-        <f>IF(COUNTA(B172:X172)=0,"",AVERAGE(B172:X172))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -12002,7 +12062,7 @@
       <c r="W173" s="3"/>
       <c r="X173" s="3"/>
       <c r="Y173" s="4" t="str">
-        <f>IF(COUNTA(B173:X173)=0,"",AVERAGE(B173:X173))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -12032,7 +12092,7 @@
       <c r="W174" s="3"/>
       <c r="X174" s="3"/>
       <c r="Y174" s="4" t="str">
-        <f>IF(COUNTA(B174:X174)=0,"",AVERAGE(B174:X174))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -12062,7 +12122,7 @@
       <c r="W175" s="3"/>
       <c r="X175" s="3"/>
       <c r="Y175" s="4" t="str">
-        <f>IF(COUNTA(B175:X175)=0,"",AVERAGE(B175:X175))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -12092,7 +12152,7 @@
       <c r="W176" s="3"/>
       <c r="X176" s="3"/>
       <c r="Y176" s="4" t="str">
-        <f>IF(COUNTA(B176:X176)=0,"",AVERAGE(B176:X176))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -12122,7 +12182,7 @@
       <c r="W177" s="3"/>
       <c r="X177" s="3"/>
       <c r="Y177" s="4" t="str">
-        <f>IF(COUNTA(B177:X177)=0,"",AVERAGE(B177:X177))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -12152,7 +12212,7 @@
       <c r="W178" s="3"/>
       <c r="X178" s="3"/>
       <c r="Y178" s="4" t="str">
-        <f>IF(COUNTA(B178:X178)=0,"",AVERAGE(B178:X178))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -12182,7 +12242,7 @@
       <c r="W179" s="3"/>
       <c r="X179" s="3"/>
       <c r="Y179" s="4" t="str">
-        <f>IF(COUNTA(B179:X179)=0,"",AVERAGE(B179:X179))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -12212,7 +12272,7 @@
       <c r="W180" s="3"/>
       <c r="X180" s="3"/>
       <c r="Y180" s="4" t="str">
-        <f>IF(COUNTA(B180:X180)=0,"",AVERAGE(B180:X180))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -12242,7 +12302,7 @@
       <c r="W181" s="3"/>
       <c r="X181" s="3"/>
       <c r="Y181" s="4" t="str">
-        <f>IF(COUNTA(B181:X181)=0,"",AVERAGE(B181:X181))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -12272,7 +12332,7 @@
       <c r="W182" s="3"/>
       <c r="X182" s="3"/>
       <c r="Y182" s="4" t="str">
-        <f>IF(COUNTA(B182:X182)=0,"",AVERAGE(B182:X182))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -12302,7 +12362,7 @@
       <c r="W183" s="3"/>
       <c r="X183" s="3"/>
       <c r="Y183" s="4" t="str">
-        <f>IF(COUNTA(B183:X183)=0,"",AVERAGE(B183:X183))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -12332,7 +12392,7 @@
       <c r="W184" s="3"/>
       <c r="X184" s="3"/>
       <c r="Y184" s="4" t="str">
-        <f>IF(COUNTA(B184:X184)=0,"",AVERAGE(B184:X184))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -12362,7 +12422,7 @@
       <c r="W185" s="3"/>
       <c r="X185" s="3"/>
       <c r="Y185" s="4" t="str">
-        <f>IF(COUNTA(B185:X185)=0,"",AVERAGE(B185:X185))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -12392,7 +12452,7 @@
       <c r="W186" s="3"/>
       <c r="X186" s="3"/>
       <c r="Y186" s="4" t="str">
-        <f>IF(COUNTA(B186:X186)=0,"",AVERAGE(B186:X186))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -12422,7 +12482,7 @@
       <c r="W187" s="3"/>
       <c r="X187" s="3"/>
       <c r="Y187" s="4" t="str">
-        <f>IF(COUNTA(B187:X187)=0,"",AVERAGE(B187:X187))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -12452,7 +12512,7 @@
       <c r="W188" s="3"/>
       <c r="X188" s="3"/>
       <c r="Y188" s="4" t="str">
-        <f>IF(COUNTA(B188:X188)=0,"",AVERAGE(B188:X188))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -12482,7 +12542,7 @@
       <c r="W189" s="3"/>
       <c r="X189" s="3"/>
       <c r="Y189" s="4" t="str">
-        <f>IF(COUNTA(B189:X189)=0,"",AVERAGE(B189:X189))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -12512,7 +12572,7 @@
       <c r="W190" s="3"/>
       <c r="X190" s="3"/>
       <c r="Y190" s="4" t="str">
-        <f>IF(COUNTA(B190:X190)=0,"",AVERAGE(B190:X190))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -12542,7 +12602,7 @@
       <c r="W191" s="3"/>
       <c r="X191" s="3"/>
       <c r="Y191" s="4" t="str">
-        <f>IF(COUNTA(B191:X191)=0,"",AVERAGE(B191:X191))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -12572,7 +12632,7 @@
       <c r="W192" s="3"/>
       <c r="X192" s="3"/>
       <c r="Y192" s="4" t="str">
-        <f>IF(COUNTA(B192:X192)=0,"",AVERAGE(B192:X192))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -12602,7 +12662,7 @@
       <c r="W193" s="3"/>
       <c r="X193" s="3"/>
       <c r="Y193" s="4" t="str">
-        <f>IF(COUNTA(B193:X193)=0,"",AVERAGE(B193:X193))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -12632,7 +12692,7 @@
       <c r="W194" s="3"/>
       <c r="X194" s="3"/>
       <c r="Y194" s="4" t="str">
-        <f>IF(COUNTA(B194:X194)=0,"",AVERAGE(B194:X194))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -12662,7 +12722,7 @@
       <c r="W195" s="3"/>
       <c r="X195" s="3"/>
       <c r="Y195" s="4" t="str">
-        <f>IF(COUNTA(B195:X195)=0,"",AVERAGE(B195:X195))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -12692,7 +12752,7 @@
       <c r="W196" s="3"/>
       <c r="X196" s="3"/>
       <c r="Y196" s="4" t="str">
-        <f>IF(COUNTA(B196:X196)=0,"",AVERAGE(B196:X196))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -12722,7 +12782,7 @@
       <c r="W197" s="3"/>
       <c r="X197" s="3"/>
       <c r="Y197" s="4" t="str">
-        <f>IF(COUNTA(B197:X197)=0,"",AVERAGE(B197:X197))</f>
+        <f t="shared" ref="Y197:Y260" si="3">IF(COUNTA(B197:X197)=0,"",AVERAGE(B197:X197))</f>
         <v/>
       </c>
     </row>
@@ -12752,7 +12812,7 @@
       <c r="W198" s="3"/>
       <c r="X198" s="3"/>
       <c r="Y198" s="4" t="str">
-        <f>IF(COUNTA(B198:X198)=0,"",AVERAGE(B198:X198))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -12782,7 +12842,7 @@
       <c r="W199" s="3"/>
       <c r="X199" s="3"/>
       <c r="Y199" s="4" t="str">
-        <f>IF(COUNTA(B199:X199)=0,"",AVERAGE(B199:X199))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -12812,7 +12872,7 @@
       <c r="W200" s="3"/>
       <c r="X200" s="3"/>
       <c r="Y200" s="4" t="str">
-        <f>IF(COUNTA(B200:X200)=0,"",AVERAGE(B200:X200))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -12842,7 +12902,7 @@
       <c r="W201" s="3"/>
       <c r="X201" s="3"/>
       <c r="Y201" s="4" t="str">
-        <f>IF(COUNTA(B201:X201)=0,"",AVERAGE(B201:X201))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -12872,7 +12932,7 @@
       <c r="W202" s="3"/>
       <c r="X202" s="3"/>
       <c r="Y202" s="4" t="str">
-        <f>IF(COUNTA(B202:X202)=0,"",AVERAGE(B202:X202))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -12902,7 +12962,7 @@
       <c r="W203" s="3"/>
       <c r="X203" s="3"/>
       <c r="Y203" s="4" t="str">
-        <f>IF(COUNTA(B203:X203)=0,"",AVERAGE(B203:X203))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -12932,7 +12992,7 @@
       <c r="W204" s="3"/>
       <c r="X204" s="3"/>
       <c r="Y204" s="4" t="str">
-        <f>IF(COUNTA(B204:X204)=0,"",AVERAGE(B204:X204))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -12962,7 +13022,7 @@
       <c r="W205" s="3"/>
       <c r="X205" s="3"/>
       <c r="Y205" s="4" t="str">
-        <f>IF(COUNTA(B205:X205)=0,"",AVERAGE(B205:X205))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -12992,7 +13052,7 @@
       <c r="W206" s="3"/>
       <c r="X206" s="3"/>
       <c r="Y206" s="4" t="str">
-        <f>IF(COUNTA(B206:X206)=0,"",AVERAGE(B206:X206))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -13022,7 +13082,7 @@
       <c r="W207" s="3"/>
       <c r="X207" s="3"/>
       <c r="Y207" s="4" t="str">
-        <f>IF(COUNTA(B207:X207)=0,"",AVERAGE(B207:X207))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -13052,7 +13112,7 @@
       <c r="W208" s="3"/>
       <c r="X208" s="3"/>
       <c r="Y208" s="4" t="str">
-        <f>IF(COUNTA(B208:X208)=0,"",AVERAGE(B208:X208))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -13082,7 +13142,7 @@
       <c r="W209" s="3"/>
       <c r="X209" s="3"/>
       <c r="Y209" s="4" t="str">
-        <f>IF(COUNTA(B209:X209)=0,"",AVERAGE(B209:X209))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -13112,7 +13172,7 @@
       <c r="W210" s="3"/>
       <c r="X210" s="3"/>
       <c r="Y210" s="4" t="str">
-        <f>IF(COUNTA(B210:X210)=0,"",AVERAGE(B210:X210))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -13142,7 +13202,7 @@
       <c r="W211" s="3"/>
       <c r="X211" s="3"/>
       <c r="Y211" s="4" t="str">
-        <f>IF(COUNTA(B211:X211)=0,"",AVERAGE(B211:X211))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -13172,7 +13232,7 @@
       <c r="W212" s="3"/>
       <c r="X212" s="3"/>
       <c r="Y212" s="4" t="str">
-        <f>IF(COUNTA(B212:X212)=0,"",AVERAGE(B212:X212))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -13202,7 +13262,7 @@
       <c r="W213" s="3"/>
       <c r="X213" s="3"/>
       <c r="Y213" s="4" t="str">
-        <f>IF(COUNTA(B213:X213)=0,"",AVERAGE(B213:X213))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -13232,7 +13292,7 @@
       <c r="W214" s="3"/>
       <c r="X214" s="3"/>
       <c r="Y214" s="4" t="str">
-        <f>IF(COUNTA(B214:X214)=0,"",AVERAGE(B214:X214))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -13262,7 +13322,7 @@
       <c r="W215" s="3"/>
       <c r="X215" s="3"/>
       <c r="Y215" s="4" t="str">
-        <f>IF(COUNTA(B215:X215)=0,"",AVERAGE(B215:X215))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -13292,7 +13352,7 @@
       <c r="W216" s="3"/>
       <c r="X216" s="3"/>
       <c r="Y216" s="4" t="str">
-        <f>IF(COUNTA(B216:X216)=0,"",AVERAGE(B216:X216))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -13322,7 +13382,7 @@
       <c r="W217" s="3"/>
       <c r="X217" s="3"/>
       <c r="Y217" s="4" t="str">
-        <f>IF(COUNTA(B217:X217)=0,"",AVERAGE(B217:X217))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -13352,7 +13412,7 @@
       <c r="W218" s="3"/>
       <c r="X218" s="3"/>
       <c r="Y218" s="4" t="str">
-        <f>IF(COUNTA(B218:X218)=0,"",AVERAGE(B218:X218))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -13382,7 +13442,7 @@
       <c r="W219" s="3"/>
       <c r="X219" s="3"/>
       <c r="Y219" s="4" t="str">
-        <f>IF(COUNTA(B219:X219)=0,"",AVERAGE(B219:X219))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -13412,7 +13472,7 @@
       <c r="W220" s="3"/>
       <c r="X220" s="3"/>
       <c r="Y220" s="4" t="str">
-        <f>IF(COUNTA(B220:X220)=0,"",AVERAGE(B220:X220))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -13442,7 +13502,7 @@
       <c r="W221" s="3"/>
       <c r="X221" s="3"/>
       <c r="Y221" s="4" t="str">
-        <f>IF(COUNTA(B221:X221)=0,"",AVERAGE(B221:X221))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -13472,7 +13532,7 @@
       <c r="W222" s="3"/>
       <c r="X222" s="3"/>
       <c r="Y222" s="4" t="str">
-        <f>IF(COUNTA(B222:X222)=0,"",AVERAGE(B222:X222))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -13502,7 +13562,7 @@
       <c r="W223" s="3"/>
       <c r="X223" s="3"/>
       <c r="Y223" s="4" t="str">
-        <f>IF(COUNTA(B223:X223)=0,"",AVERAGE(B223:X223))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -13532,7 +13592,7 @@
       <c r="W224" s="3"/>
       <c r="X224" s="3"/>
       <c r="Y224" s="4" t="str">
-        <f>IF(COUNTA(B224:X224)=0,"",AVERAGE(B224:X224))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -13562,7 +13622,7 @@
       <c r="W225" s="3"/>
       <c r="X225" s="3"/>
       <c r="Y225" s="4" t="str">
-        <f>IF(COUNTA(B225:X225)=0,"",AVERAGE(B225:X225))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -13592,7 +13652,7 @@
       <c r="W226" s="3"/>
       <c r="X226" s="3"/>
       <c r="Y226" s="4" t="str">
-        <f>IF(COUNTA(B226:X226)=0,"",AVERAGE(B226:X226))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -13622,7 +13682,7 @@
       <c r="W227" s="3"/>
       <c r="X227" s="3"/>
       <c r="Y227" s="4" t="str">
-        <f>IF(COUNTA(B227:X227)=0,"",AVERAGE(B227:X227))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -13652,7 +13712,7 @@
       <c r="W228" s="3"/>
       <c r="X228" s="3"/>
       <c r="Y228" s="4" t="str">
-        <f>IF(COUNTA(B228:X228)=0,"",AVERAGE(B228:X228))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -13682,7 +13742,7 @@
       <c r="W229" s="3"/>
       <c r="X229" s="3"/>
       <c r="Y229" s="4" t="str">
-        <f>IF(COUNTA(B229:X229)=0,"",AVERAGE(B229:X229))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -13712,7 +13772,7 @@
       <c r="W230" s="3"/>
       <c r="X230" s="3"/>
       <c r="Y230" s="4" t="str">
-        <f>IF(COUNTA(B230:X230)=0,"",AVERAGE(B230:X230))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -13742,7 +13802,7 @@
       <c r="W231" s="3"/>
       <c r="X231" s="3"/>
       <c r="Y231" s="4" t="str">
-        <f>IF(COUNTA(B231:X231)=0,"",AVERAGE(B231:X231))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -13772,7 +13832,7 @@
       <c r="W232" s="3"/>
       <c r="X232" s="3"/>
       <c r="Y232" s="4" t="str">
-        <f>IF(COUNTA(B232:X232)=0,"",AVERAGE(B232:X232))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -13802,7 +13862,7 @@
       <c r="W233" s="3"/>
       <c r="X233" s="3"/>
       <c r="Y233" s="4" t="str">
-        <f>IF(COUNTA(B233:X233)=0,"",AVERAGE(B233:X233))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -13832,7 +13892,7 @@
       <c r="W234" s="3"/>
       <c r="X234" s="3"/>
       <c r="Y234" s="4" t="str">
-        <f>IF(COUNTA(B234:X234)=0,"",AVERAGE(B234:X234))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -13862,7 +13922,7 @@
       <c r="W235" s="3"/>
       <c r="X235" s="3"/>
       <c r="Y235" s="4" t="str">
-        <f>IF(COUNTA(B235:X235)=0,"",AVERAGE(B235:X235))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -13892,7 +13952,7 @@
       <c r="W236" s="3"/>
       <c r="X236" s="3"/>
       <c r="Y236" s="4" t="str">
-        <f>IF(COUNTA(B236:X236)=0,"",AVERAGE(B236:X236))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -13922,7 +13982,7 @@
       <c r="W237" s="3"/>
       <c r="X237" s="3"/>
       <c r="Y237" s="4" t="str">
-        <f>IF(COUNTA(B237:X237)=0,"",AVERAGE(B237:X237))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -13952,7 +14012,7 @@
       <c r="W238" s="3"/>
       <c r="X238" s="3"/>
       <c r="Y238" s="4" t="str">
-        <f>IF(COUNTA(B238:X238)=0,"",AVERAGE(B238:X238))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -13982,7 +14042,7 @@
       <c r="W239" s="3"/>
       <c r="X239" s="3"/>
       <c r="Y239" s="4" t="str">
-        <f>IF(COUNTA(B239:X239)=0,"",AVERAGE(B239:X239))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -14012,7 +14072,7 @@
       <c r="W240" s="3"/>
       <c r="X240" s="3"/>
       <c r="Y240" s="4" t="str">
-        <f>IF(COUNTA(B240:X240)=0,"",AVERAGE(B240:X240))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -14042,7 +14102,7 @@
       <c r="W241" s="3"/>
       <c r="X241" s="3"/>
       <c r="Y241" s="4" t="str">
-        <f>IF(COUNTA(B241:X241)=0,"",AVERAGE(B241:X241))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -14072,7 +14132,7 @@
       <c r="W242" s="3"/>
       <c r="X242" s="3"/>
       <c r="Y242" s="4" t="str">
-        <f>IF(COUNTA(B242:X242)=0,"",AVERAGE(B242:X242))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -14102,7 +14162,7 @@
       <c r="W243" s="3"/>
       <c r="X243" s="3"/>
       <c r="Y243" s="4" t="str">
-        <f>IF(COUNTA(B243:X243)=0,"",AVERAGE(B243:X243))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -14132,7 +14192,7 @@
       <c r="W244" s="3"/>
       <c r="X244" s="3"/>
       <c r="Y244" s="4" t="str">
-        <f>IF(COUNTA(B244:X244)=0,"",AVERAGE(B244:X244))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -14162,7 +14222,7 @@
       <c r="W245" s="3"/>
       <c r="X245" s="3"/>
       <c r="Y245" s="4" t="str">
-        <f>IF(COUNTA(B245:X245)=0,"",AVERAGE(B245:X245))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -14192,7 +14252,7 @@
       <c r="W246" s="3"/>
       <c r="X246" s="3"/>
       <c r="Y246" s="4" t="str">
-        <f>IF(COUNTA(B246:X246)=0,"",AVERAGE(B246:X246))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -14222,7 +14282,7 @@
       <c r="W247" s="3"/>
       <c r="X247" s="3"/>
       <c r="Y247" s="4" t="str">
-        <f>IF(COUNTA(B247:X247)=0,"",AVERAGE(B247:X247))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -14252,7 +14312,7 @@
       <c r="W248" s="3"/>
       <c r="X248" s="3"/>
       <c r="Y248" s="4" t="str">
-        <f>IF(COUNTA(B248:X248)=0,"",AVERAGE(B248:X248))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -14282,7 +14342,7 @@
       <c r="W249" s="3"/>
       <c r="X249" s="3"/>
       <c r="Y249" s="4" t="str">
-        <f>IF(COUNTA(B249:X249)=0,"",AVERAGE(B249:X249))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -14312,7 +14372,7 @@
       <c r="W250" s="3"/>
       <c r="X250" s="3"/>
       <c r="Y250" s="4" t="str">
-        <f>IF(COUNTA(B250:X250)=0,"",AVERAGE(B250:X250))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -14342,7 +14402,7 @@
       <c r="W251" s="3"/>
       <c r="X251" s="3"/>
       <c r="Y251" s="4" t="str">
-        <f>IF(COUNTA(B251:X251)=0,"",AVERAGE(B251:X251))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -14372,7 +14432,7 @@
       <c r="W252" s="3"/>
       <c r="X252" s="3"/>
       <c r="Y252" s="4" t="str">
-        <f>IF(COUNTA(B252:X252)=0,"",AVERAGE(B252:X252))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -14402,7 +14462,7 @@
       <c r="W253" s="3"/>
       <c r="X253" s="3"/>
       <c r="Y253" s="4" t="str">
-        <f>IF(COUNTA(B253:X253)=0,"",AVERAGE(B253:X253))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -14432,7 +14492,7 @@
       <c r="W254" s="3"/>
       <c r="X254" s="3"/>
       <c r="Y254" s="4" t="str">
-        <f>IF(COUNTA(B254:X254)=0,"",AVERAGE(B254:X254))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -14462,7 +14522,7 @@
       <c r="W255" s="3"/>
       <c r="X255" s="3"/>
       <c r="Y255" s="4" t="str">
-        <f>IF(COUNTA(B255:X255)=0,"",AVERAGE(B255:X255))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -14492,7 +14552,7 @@
       <c r="W256" s="3"/>
       <c r="X256" s="3"/>
       <c r="Y256" s="4" t="str">
-        <f>IF(COUNTA(B256:X256)=0,"",AVERAGE(B256:X256))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -14522,7 +14582,7 @@
       <c r="W257" s="3"/>
       <c r="X257" s="3"/>
       <c r="Y257" s="4" t="str">
-        <f>IF(COUNTA(B257:X257)=0,"",AVERAGE(B257:X257))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -14552,7 +14612,7 @@
       <c r="W258" s="3"/>
       <c r="X258" s="3"/>
       <c r="Y258" s="4" t="str">
-        <f>IF(COUNTA(B258:X258)=0,"",AVERAGE(B258:X258))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -14582,7 +14642,7 @@
       <c r="W259" s="3"/>
       <c r="X259" s="3"/>
       <c r="Y259" s="4" t="str">
-        <f>IF(COUNTA(B259:X259)=0,"",AVERAGE(B259:X259))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -14612,7 +14672,7 @@
       <c r="W260" s="3"/>
       <c r="X260" s="3"/>
       <c r="Y260" s="4" t="str">
-        <f>IF(COUNTA(B260:X260)=0,"",AVERAGE(B260:X260))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -14642,7 +14702,7 @@
       <c r="W261" s="3"/>
       <c r="X261" s="3"/>
       <c r="Y261" s="4" t="str">
-        <f>IF(COUNTA(B261:X261)=0,"",AVERAGE(B261:X261))</f>
+        <f t="shared" ref="Y261:Y324" si="4">IF(COUNTA(B261:X261)=0,"",AVERAGE(B261:X261))</f>
         <v/>
       </c>
     </row>
@@ -14672,7 +14732,7 @@
       <c r="W262" s="3"/>
       <c r="X262" s="3"/>
       <c r="Y262" s="4" t="str">
-        <f>IF(COUNTA(B262:X262)=0,"",AVERAGE(B262:X262))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
@@ -14702,7 +14762,7 @@
       <c r="W263" s="3"/>
       <c r="X263" s="3"/>
       <c r="Y263" s="4" t="str">
-        <f>IF(COUNTA(B263:X263)=0,"",AVERAGE(B263:X263))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
@@ -14732,7 +14792,7 @@
       <c r="W264" s="3"/>
       <c r="X264" s="3"/>
       <c r="Y264" s="4" t="str">
-        <f>IF(COUNTA(B264:X264)=0,"",AVERAGE(B264:X264))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
@@ -14762,7 +14822,7 @@
       <c r="W265" s="3"/>
       <c r="X265" s="3"/>
       <c r="Y265" s="4" t="str">
-        <f>IF(COUNTA(B265:X265)=0,"",AVERAGE(B265:X265))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
@@ -14792,7 +14852,7 @@
       <c r="W266" s="3"/>
       <c r="X266" s="3"/>
       <c r="Y266" s="4" t="str">
-        <f>IF(COUNTA(B266:X266)=0,"",AVERAGE(B266:X266))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
@@ -14822,7 +14882,7 @@
       <c r="W267" s="3"/>
       <c r="X267" s="3"/>
       <c r="Y267" s="4" t="str">
-        <f>IF(COUNTA(B267:X267)=0,"",AVERAGE(B267:X267))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
@@ -14852,7 +14912,7 @@
       <c r="W268" s="3"/>
       <c r="X268" s="3"/>
       <c r="Y268" s="4" t="str">
-        <f>IF(COUNTA(B268:X268)=0,"",AVERAGE(B268:X268))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
@@ -14882,7 +14942,7 @@
       <c r="W269" s="3"/>
       <c r="X269" s="3"/>
       <c r="Y269" s="4" t="str">
-        <f>IF(COUNTA(B269:X269)=0,"",AVERAGE(B269:X269))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
@@ -14912,7 +14972,7 @@
       <c r="W270" s="3"/>
       <c r="X270" s="3"/>
       <c r="Y270" s="4" t="str">
-        <f>IF(COUNTA(B270:X270)=0,"",AVERAGE(B270:X270))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
@@ -14942,7 +15002,7 @@
       <c r="W271" s="3"/>
       <c r="X271" s="3"/>
       <c r="Y271" s="4" t="str">
-        <f>IF(COUNTA(B271:X271)=0,"",AVERAGE(B271:X271))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
@@ -14972,7 +15032,7 @@
       <c r="W272" s="3"/>
       <c r="X272" s="3"/>
       <c r="Y272" s="4" t="str">
-        <f>IF(COUNTA(B272:X272)=0,"",AVERAGE(B272:X272))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
@@ -15002,7 +15062,7 @@
       <c r="W273" s="3"/>
       <c r="X273" s="3"/>
       <c r="Y273" s="4" t="str">
-        <f>IF(COUNTA(B273:X273)=0,"",AVERAGE(B273:X273))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
@@ -15032,7 +15092,7 @@
       <c r="W274" s="3"/>
       <c r="X274" s="3"/>
       <c r="Y274" s="4" t="str">
-        <f>IF(COUNTA(B274:X274)=0,"",AVERAGE(B274:X274))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
@@ -15062,7 +15122,7 @@
       <c r="W275" s="3"/>
       <c r="X275" s="3"/>
       <c r="Y275" s="4" t="str">
-        <f>IF(COUNTA(B275:X275)=0,"",AVERAGE(B275:X275))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
@@ -15092,7 +15152,7 @@
       <c r="W276" s="3"/>
       <c r="X276" s="3"/>
       <c r="Y276" s="4" t="str">
-        <f>IF(COUNTA(B276:X276)=0,"",AVERAGE(B276:X276))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
@@ -15122,7 +15182,7 @@
       <c r="W277" s="3"/>
       <c r="X277" s="3"/>
       <c r="Y277" s="4" t="str">
-        <f>IF(COUNTA(B277:X277)=0,"",AVERAGE(B277:X277))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
@@ -15152,7 +15212,7 @@
       <c r="W278" s="3"/>
       <c r="X278" s="3"/>
       <c r="Y278" s="4" t="str">
-        <f>IF(COUNTA(B278:X278)=0,"",AVERAGE(B278:X278))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
@@ -15182,7 +15242,7 @@
       <c r="W279" s="3"/>
       <c r="X279" s="3"/>
       <c r="Y279" s="4" t="str">
-        <f>IF(COUNTA(B279:X279)=0,"",AVERAGE(B279:X279))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
@@ -15212,7 +15272,7 @@
       <c r="W280" s="3"/>
       <c r="X280" s="3"/>
       <c r="Y280" s="4" t="str">
-        <f>IF(COUNTA(B280:X280)=0,"",AVERAGE(B280:X280))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
@@ -15242,7 +15302,7 @@
       <c r="W281" s="3"/>
       <c r="X281" s="3"/>
       <c r="Y281" s="4" t="str">
-        <f>IF(COUNTA(B281:X281)=0,"",AVERAGE(B281:X281))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
@@ -15272,7 +15332,7 @@
       <c r="W282" s="3"/>
       <c r="X282" s="3"/>
       <c r="Y282" s="4" t="str">
-        <f>IF(COUNTA(B282:X282)=0,"",AVERAGE(B282:X282))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
@@ -15302,7 +15362,7 @@
       <c r="W283" s="3"/>
       <c r="X283" s="3"/>
       <c r="Y283" s="4" t="str">
-        <f>IF(COUNTA(B283:X283)=0,"",AVERAGE(B283:X283))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
@@ -15332,7 +15392,7 @@
       <c r="W284" s="3"/>
       <c r="X284" s="3"/>
       <c r="Y284" s="4" t="str">
-        <f>IF(COUNTA(B284:X284)=0,"",AVERAGE(B284:X284))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
@@ -15362,7 +15422,7 @@
       <c r="W285" s="3"/>
       <c r="X285" s="3"/>
       <c r="Y285" s="4" t="str">
-        <f>IF(COUNTA(B285:X285)=0,"",AVERAGE(B285:X285))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
@@ -15392,7 +15452,7 @@
       <c r="W286" s="3"/>
       <c r="X286" s="3"/>
       <c r="Y286" s="4" t="str">
-        <f>IF(COUNTA(B286:X286)=0,"",AVERAGE(B286:X286))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
@@ -15422,7 +15482,7 @@
       <c r="W287" s="3"/>
       <c r="X287" s="3"/>
       <c r="Y287" s="4" t="str">
-        <f>IF(COUNTA(B287:X287)=0,"",AVERAGE(B287:X287))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
@@ -15452,7 +15512,7 @@
       <c r="W288" s="3"/>
       <c r="X288" s="3"/>
       <c r="Y288" s="4" t="str">
-        <f>IF(COUNTA(B288:X288)=0,"",AVERAGE(B288:X288))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
@@ -15482,7 +15542,7 @@
       <c r="W289" s="3"/>
       <c r="X289" s="3"/>
       <c r="Y289" s="4" t="str">
-        <f>IF(COUNTA(B289:X289)=0,"",AVERAGE(B289:X289))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
@@ -15512,7 +15572,7 @@
       <c r="W290" s="3"/>
       <c r="X290" s="3"/>
       <c r="Y290" s="4" t="str">
-        <f>IF(COUNTA(B290:X290)=0,"",AVERAGE(B290:X290))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
@@ -15542,7 +15602,7 @@
       <c r="W291" s="3"/>
       <c r="X291" s="3"/>
       <c r="Y291" s="4" t="str">
-        <f>IF(COUNTA(B291:X291)=0,"",AVERAGE(B291:X291))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
@@ -15572,7 +15632,7 @@
       <c r="W292" s="3"/>
       <c r="X292" s="3"/>
       <c r="Y292" s="4" t="str">
-        <f>IF(COUNTA(B292:X292)=0,"",AVERAGE(B292:X292))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
@@ -15602,7 +15662,7 @@
       <c r="W293" s="3"/>
       <c r="X293" s="3"/>
       <c r="Y293" s="4" t="str">
-        <f>IF(COUNTA(B293:X293)=0,"",AVERAGE(B293:X293))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
@@ -15632,7 +15692,7 @@
       <c r="W294" s="3"/>
       <c r="X294" s="3"/>
       <c r="Y294" s="4" t="str">
-        <f>IF(COUNTA(B294:X294)=0,"",AVERAGE(B294:X294))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
@@ -15662,7 +15722,7 @@
       <c r="W295" s="3"/>
       <c r="X295" s="3"/>
       <c r="Y295" s="4" t="str">
-        <f>IF(COUNTA(B295:X295)=0,"",AVERAGE(B295:X295))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
@@ -15692,7 +15752,7 @@
       <c r="W296" s="3"/>
       <c r="X296" s="3"/>
       <c r="Y296" s="4" t="str">
-        <f>IF(COUNTA(B296:X296)=0,"",AVERAGE(B296:X296))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
@@ -15722,7 +15782,7 @@
       <c r="W297" s="3"/>
       <c r="X297" s="3"/>
       <c r="Y297" s="4" t="str">
-        <f>IF(COUNTA(B297:X297)=0,"",AVERAGE(B297:X297))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
@@ -15752,7 +15812,7 @@
       <c r="W298" s="3"/>
       <c r="X298" s="3"/>
       <c r="Y298" s="4" t="str">
-        <f>IF(COUNTA(B298:X298)=0,"",AVERAGE(B298:X298))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
@@ -15782,7 +15842,7 @@
       <c r="W299" s="3"/>
       <c r="X299" s="3"/>
       <c r="Y299" s="4" t="str">
-        <f>IF(COUNTA(B299:X299)=0,"",AVERAGE(B299:X299))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
@@ -15812,7 +15872,7 @@
       <c r="W300" s="3"/>
       <c r="X300" s="3"/>
       <c r="Y300" s="4" t="str">
-        <f>IF(COUNTA(B300:X300)=0,"",AVERAGE(B300:X300))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
@@ -15842,7 +15902,7 @@
       <c r="W301" s="3"/>
       <c r="X301" s="3"/>
       <c r="Y301" s="4" t="str">
-        <f>IF(COUNTA(B301:X301)=0,"",AVERAGE(B301:X301))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
@@ -15872,7 +15932,7 @@
       <c r="W302" s="3"/>
       <c r="X302" s="3"/>
       <c r="Y302" s="4" t="str">
-        <f>IF(COUNTA(B302:X302)=0,"",AVERAGE(B302:X302))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
@@ -15902,7 +15962,7 @@
       <c r="W303" s="3"/>
       <c r="X303" s="3"/>
       <c r="Y303" s="4" t="str">
-        <f>IF(COUNTA(B303:X303)=0,"",AVERAGE(B303:X303))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
@@ -15932,7 +15992,7 @@
       <c r="W304" s="3"/>
       <c r="X304" s="3"/>
       <c r="Y304" s="4" t="str">
-        <f>IF(COUNTA(B304:X304)=0,"",AVERAGE(B304:X304))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
@@ -15962,7 +16022,7 @@
       <c r="W305" s="3"/>
       <c r="X305" s="3"/>
       <c r="Y305" s="4" t="str">
-        <f>IF(COUNTA(B305:X305)=0,"",AVERAGE(B305:X305))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
@@ -15992,7 +16052,7 @@
       <c r="W306" s="3"/>
       <c r="X306" s="3"/>
       <c r="Y306" s="4" t="str">
-        <f>IF(COUNTA(B306:X306)=0,"",AVERAGE(B306:X306))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
@@ -16022,7 +16082,7 @@
       <c r="W307" s="3"/>
       <c r="X307" s="3"/>
       <c r="Y307" s="4" t="str">
-        <f>IF(COUNTA(B307:X307)=0,"",AVERAGE(B307:X307))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
@@ -16052,7 +16112,7 @@
       <c r="W308" s="3"/>
       <c r="X308" s="3"/>
       <c r="Y308" s="4" t="str">
-        <f>IF(COUNTA(B308:X308)=0,"",AVERAGE(B308:X308))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
@@ -16082,7 +16142,7 @@
       <c r="W309" s="3"/>
       <c r="X309" s="3"/>
       <c r="Y309" s="4" t="str">
-        <f>IF(COUNTA(B309:X309)=0,"",AVERAGE(B309:X309))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
@@ -16112,7 +16172,7 @@
       <c r="W310" s="3"/>
       <c r="X310" s="3"/>
       <c r="Y310" s="4" t="str">
-        <f>IF(COUNTA(B310:X310)=0,"",AVERAGE(B310:X310))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
@@ -16142,7 +16202,7 @@
       <c r="W311" s="3"/>
       <c r="X311" s="3"/>
       <c r="Y311" s="4" t="str">
-        <f>IF(COUNTA(B311:X311)=0,"",AVERAGE(B311:X311))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
@@ -16172,7 +16232,7 @@
       <c r="W312" s="3"/>
       <c r="X312" s="3"/>
       <c r="Y312" s="4" t="str">
-        <f>IF(COUNTA(B312:X312)=0,"",AVERAGE(B312:X312))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
@@ -16202,7 +16262,7 @@
       <c r="W313" s="3"/>
       <c r="X313" s="3"/>
       <c r="Y313" s="4" t="str">
-        <f>IF(COUNTA(B313:X313)=0,"",AVERAGE(B313:X313))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
@@ -16232,7 +16292,7 @@
       <c r="W314" s="3"/>
       <c r="X314" s="3"/>
       <c r="Y314" s="4" t="str">
-        <f>IF(COUNTA(B314:X314)=0,"",AVERAGE(B314:X314))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
@@ -16262,7 +16322,7 @@
       <c r="W315" s="3"/>
       <c r="X315" s="3"/>
       <c r="Y315" s="4" t="str">
-        <f>IF(COUNTA(B315:X315)=0,"",AVERAGE(B315:X315))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
@@ -16292,7 +16352,7 @@
       <c r="W316" s="3"/>
       <c r="X316" s="3"/>
       <c r="Y316" s="4" t="str">
-        <f>IF(COUNTA(B316:X316)=0,"",AVERAGE(B316:X316))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
@@ -16322,7 +16382,7 @@
       <c r="W317" s="3"/>
       <c r="X317" s="3"/>
       <c r="Y317" s="4" t="str">
-        <f>IF(COUNTA(B317:X317)=0,"",AVERAGE(B317:X317))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
@@ -16352,7 +16412,7 @@
       <c r="W318" s="3"/>
       <c r="X318" s="3"/>
       <c r="Y318" s="4" t="str">
-        <f>IF(COUNTA(B318:X318)=0,"",AVERAGE(B318:X318))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
@@ -16382,7 +16442,7 @@
       <c r="W319" s="3"/>
       <c r="X319" s="3"/>
       <c r="Y319" s="4" t="str">
-        <f>IF(COUNTA(B319:X319)=0,"",AVERAGE(B319:X319))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
@@ -16412,7 +16472,7 @@
       <c r="W320" s="3"/>
       <c r="X320" s="3"/>
       <c r="Y320" s="4" t="str">
-        <f>IF(COUNTA(B320:X320)=0,"",AVERAGE(B320:X320))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
@@ -16442,7 +16502,7 @@
       <c r="W321" s="3"/>
       <c r="X321" s="3"/>
       <c r="Y321" s="4" t="str">
-        <f>IF(COUNTA(B321:X321)=0,"",AVERAGE(B321:X321))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
@@ -16472,7 +16532,7 @@
       <c r="W322" s="3"/>
       <c r="X322" s="3"/>
       <c r="Y322" s="4" t="str">
-        <f>IF(COUNTA(B322:X322)=0,"",AVERAGE(B322:X322))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
@@ -16502,7 +16562,7 @@
       <c r="W323" s="3"/>
       <c r="X323" s="3"/>
       <c r="Y323" s="4" t="str">
-        <f>IF(COUNTA(B323:X323)=0,"",AVERAGE(B323:X323))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
@@ -16532,7 +16592,7 @@
       <c r="W324" s="3"/>
       <c r="X324" s="3"/>
       <c r="Y324" s="4" t="str">
-        <f>IF(COUNTA(B324:X324)=0,"",AVERAGE(B324:X324))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
@@ -16562,7 +16622,7 @@
       <c r="W325" s="3"/>
       <c r="X325" s="3"/>
       <c r="Y325" s="4" t="str">
-        <f>IF(COUNTA(B325:X325)=0,"",AVERAGE(B325:X325))</f>
+        <f t="shared" ref="Y325:Y388" si="5">IF(COUNTA(B325:X325)=0,"",AVERAGE(B325:X325))</f>
         <v/>
       </c>
     </row>
@@ -16592,7 +16652,7 @@
       <c r="W326" s="3"/>
       <c r="X326" s="3"/>
       <c r="Y326" s="4" t="str">
-        <f>IF(COUNTA(B326:X326)=0,"",AVERAGE(B326:X326))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -16622,7 +16682,7 @@
       <c r="W327" s="3"/>
       <c r="X327" s="3"/>
       <c r="Y327" s="4" t="str">
-        <f>IF(COUNTA(B327:X327)=0,"",AVERAGE(B327:X327))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -16652,7 +16712,7 @@
       <c r="W328" s="3"/>
       <c r="X328" s="3"/>
       <c r="Y328" s="4" t="str">
-        <f>IF(COUNTA(B328:X328)=0,"",AVERAGE(B328:X328))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -16682,7 +16742,7 @@
       <c r="W329" s="3"/>
       <c r="X329" s="3"/>
       <c r="Y329" s="4" t="str">
-        <f>IF(COUNTA(B329:X329)=0,"",AVERAGE(B329:X329))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -16712,7 +16772,7 @@
       <c r="W330" s="3"/>
       <c r="X330" s="3"/>
       <c r="Y330" s="4" t="str">
-        <f>IF(COUNTA(B330:X330)=0,"",AVERAGE(B330:X330))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -16742,7 +16802,7 @@
       <c r="W331" s="3"/>
       <c r="X331" s="3"/>
       <c r="Y331" s="4" t="str">
-        <f>IF(COUNTA(B331:X331)=0,"",AVERAGE(B331:X331))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -16772,7 +16832,7 @@
       <c r="W332" s="3"/>
       <c r="X332" s="3"/>
       <c r="Y332" s="4" t="str">
-        <f>IF(COUNTA(B332:X332)=0,"",AVERAGE(B332:X332))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -16802,7 +16862,7 @@
       <c r="W333" s="3"/>
       <c r="X333" s="3"/>
       <c r="Y333" s="4" t="str">
-        <f>IF(COUNTA(B333:X333)=0,"",AVERAGE(B333:X333))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -16832,7 +16892,7 @@
       <c r="W334" s="3"/>
       <c r="X334" s="3"/>
       <c r="Y334" s="4" t="str">
-        <f>IF(COUNTA(B334:X334)=0,"",AVERAGE(B334:X334))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -16862,7 +16922,7 @@
       <c r="W335" s="3"/>
       <c r="X335" s="3"/>
       <c r="Y335" s="4" t="str">
-        <f>IF(COUNTA(B335:X335)=0,"",AVERAGE(B335:X335))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -16892,7 +16952,7 @@
       <c r="W336" s="3"/>
       <c r="X336" s="3"/>
       <c r="Y336" s="4" t="str">
-        <f>IF(COUNTA(B336:X336)=0,"",AVERAGE(B336:X336))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -16922,7 +16982,7 @@
       <c r="W337" s="3"/>
       <c r="X337" s="3"/>
       <c r="Y337" s="4" t="str">
-        <f>IF(COUNTA(B337:X337)=0,"",AVERAGE(B337:X337))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -16952,7 +17012,7 @@
       <c r="W338" s="3"/>
       <c r="X338" s="3"/>
       <c r="Y338" s="4" t="str">
-        <f>IF(COUNTA(B338:X338)=0,"",AVERAGE(B338:X338))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -16982,7 +17042,7 @@
       <c r="W339" s="3"/>
       <c r="X339" s="3"/>
       <c r="Y339" s="4" t="str">
-        <f>IF(COUNTA(B339:X339)=0,"",AVERAGE(B339:X339))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -17012,7 +17072,7 @@
       <c r="W340" s="3"/>
       <c r="X340" s="3"/>
       <c r="Y340" s="4" t="str">
-        <f>IF(COUNTA(B340:X340)=0,"",AVERAGE(B340:X340))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -17042,7 +17102,7 @@
       <c r="W341" s="3"/>
       <c r="X341" s="3"/>
       <c r="Y341" s="4" t="str">
-        <f>IF(COUNTA(B341:X341)=0,"",AVERAGE(B341:X341))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -17072,7 +17132,7 @@
       <c r="W342" s="3"/>
       <c r="X342" s="3"/>
       <c r="Y342" s="4" t="str">
-        <f>IF(COUNTA(B342:X342)=0,"",AVERAGE(B342:X342))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -17102,7 +17162,7 @@
       <c r="W343" s="3"/>
       <c r="X343" s="3"/>
       <c r="Y343" s="4" t="str">
-        <f>IF(COUNTA(B343:X343)=0,"",AVERAGE(B343:X343))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -17132,7 +17192,7 @@
       <c r="W344" s="3"/>
       <c r="X344" s="3"/>
       <c r="Y344" s="4" t="str">
-        <f>IF(COUNTA(B344:X344)=0,"",AVERAGE(B344:X344))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -17162,7 +17222,7 @@
       <c r="W345" s="3"/>
       <c r="X345" s="3"/>
       <c r="Y345" s="4" t="str">
-        <f>IF(COUNTA(B345:X345)=0,"",AVERAGE(B345:X345))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -17192,7 +17252,7 @@
       <c r="W346" s="3"/>
       <c r="X346" s="3"/>
       <c r="Y346" s="4" t="str">
-        <f>IF(COUNTA(B346:X346)=0,"",AVERAGE(B346:X346))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -17222,7 +17282,7 @@
       <c r="W347" s="3"/>
       <c r="X347" s="3"/>
       <c r="Y347" s="4" t="str">
-        <f>IF(COUNTA(B347:X347)=0,"",AVERAGE(B347:X347))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -17252,7 +17312,7 @@
       <c r="W348" s="3"/>
       <c r="X348" s="3"/>
       <c r="Y348" s="4" t="str">
-        <f>IF(COUNTA(B348:X348)=0,"",AVERAGE(B348:X348))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -17282,7 +17342,7 @@
       <c r="W349" s="3"/>
       <c r="X349" s="3"/>
       <c r="Y349" s="4" t="str">
-        <f>IF(COUNTA(B349:X349)=0,"",AVERAGE(B349:X349))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -17312,7 +17372,7 @@
       <c r="W350" s="3"/>
       <c r="X350" s="3"/>
       <c r="Y350" s="4" t="str">
-        <f>IF(COUNTA(B350:X350)=0,"",AVERAGE(B350:X350))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -17342,7 +17402,7 @@
       <c r="W351" s="3"/>
       <c r="X351" s="3"/>
       <c r="Y351" s="4" t="str">
-        <f>IF(COUNTA(B351:X351)=0,"",AVERAGE(B351:X351))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -17372,7 +17432,7 @@
       <c r="W352" s="3"/>
       <c r="X352" s="3"/>
       <c r="Y352" s="4" t="str">
-        <f>IF(COUNTA(B352:X352)=0,"",AVERAGE(B352:X352))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -17402,7 +17462,7 @@
       <c r="W353" s="3"/>
       <c r="X353" s="3"/>
       <c r="Y353" s="4" t="str">
-        <f>IF(COUNTA(B353:X353)=0,"",AVERAGE(B353:X353))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -17432,7 +17492,7 @@
       <c r="W354" s="3"/>
       <c r="X354" s="3"/>
       <c r="Y354" s="4" t="str">
-        <f>IF(COUNTA(B354:X354)=0,"",AVERAGE(B354:X354))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -17462,7 +17522,7 @@
       <c r="W355" s="3"/>
       <c r="X355" s="3"/>
       <c r="Y355" s="4" t="str">
-        <f>IF(COUNTA(B355:X355)=0,"",AVERAGE(B355:X355))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -17492,7 +17552,7 @@
       <c r="W356" s="3"/>
       <c r="X356" s="3"/>
       <c r="Y356" s="4" t="str">
-        <f>IF(COUNTA(B356:X356)=0,"",AVERAGE(B356:X356))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -17522,7 +17582,7 @@
       <c r="W357" s="3"/>
       <c r="X357" s="3"/>
       <c r="Y357" s="4" t="str">
-        <f>IF(COUNTA(B357:X357)=0,"",AVERAGE(B357:X357))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -17552,7 +17612,7 @@
       <c r="W358" s="3"/>
       <c r="X358" s="3"/>
       <c r="Y358" s="4" t="str">
-        <f>IF(COUNTA(B358:X358)=0,"",AVERAGE(B358:X358))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -17582,7 +17642,7 @@
       <c r="W359" s="3"/>
       <c r="X359" s="3"/>
       <c r="Y359" s="4" t="str">
-        <f>IF(COUNTA(B359:X359)=0,"",AVERAGE(B359:X359))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -17612,7 +17672,7 @@
       <c r="W360" s="3"/>
       <c r="X360" s="3"/>
       <c r="Y360" s="4" t="str">
-        <f>IF(COUNTA(B360:X360)=0,"",AVERAGE(B360:X360))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -17642,7 +17702,7 @@
       <c r="W361" s="3"/>
       <c r="X361" s="3"/>
       <c r="Y361" s="4" t="str">
-        <f>IF(COUNTA(B361:X361)=0,"",AVERAGE(B361:X361))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -17672,7 +17732,7 @@
       <c r="W362" s="3"/>
       <c r="X362" s="3"/>
       <c r="Y362" s="4" t="str">
-        <f>IF(COUNTA(B362:X362)=0,"",AVERAGE(B362:X362))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -17702,7 +17762,7 @@
       <c r="W363" s="3"/>
       <c r="X363" s="3"/>
       <c r="Y363" s="4" t="str">
-        <f>IF(COUNTA(B363:X363)=0,"",AVERAGE(B363:X363))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -17732,7 +17792,7 @@
       <c r="W364" s="3"/>
       <c r="X364" s="3"/>
       <c r="Y364" s="4" t="str">
-        <f>IF(COUNTA(B364:X364)=0,"",AVERAGE(B364:X364))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -17762,7 +17822,7 @@
       <c r="W365" s="3"/>
       <c r="X365" s="3"/>
       <c r="Y365" s="4" t="str">
-        <f>IF(COUNTA(B365:X365)=0,"",AVERAGE(B365:X365))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -17792,7 +17852,7 @@
       <c r="W366" s="3"/>
       <c r="X366" s="3"/>
       <c r="Y366" s="4" t="str">
-        <f>IF(COUNTA(B366:X366)=0,"",AVERAGE(B366:X366))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -17822,7 +17882,7 @@
       <c r="W367" s="3"/>
       <c r="X367" s="3"/>
       <c r="Y367" s="4" t="str">
-        <f>IF(COUNTA(B367:X367)=0,"",AVERAGE(B367:X367))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -17852,7 +17912,7 @@
       <c r="W368" s="3"/>
       <c r="X368" s="3"/>
       <c r="Y368" s="4" t="str">
-        <f>IF(COUNTA(B368:X368)=0,"",AVERAGE(B368:X368))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -17882,7 +17942,7 @@
       <c r="W369" s="3"/>
       <c r="X369" s="3"/>
       <c r="Y369" s="4" t="str">
-        <f>IF(COUNTA(B369:X369)=0,"",AVERAGE(B369:X369))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -17912,7 +17972,7 @@
       <c r="W370" s="3"/>
       <c r="X370" s="3"/>
       <c r="Y370" s="4" t="str">
-        <f>IF(COUNTA(B370:X370)=0,"",AVERAGE(B370:X370))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -17942,7 +18002,7 @@
       <c r="W371" s="3"/>
       <c r="X371" s="3"/>
       <c r="Y371" s="4" t="str">
-        <f>IF(COUNTA(B371:X371)=0,"",AVERAGE(B371:X371))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -17972,7 +18032,7 @@
       <c r="W372" s="3"/>
       <c r="X372" s="3"/>
       <c r="Y372" s="4" t="str">
-        <f>IF(COUNTA(B372:X372)=0,"",AVERAGE(B372:X372))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -18002,7 +18062,7 @@
       <c r="W373" s="3"/>
       <c r="X373" s="3"/>
       <c r="Y373" s="4" t="str">
-        <f>IF(COUNTA(B373:X373)=0,"",AVERAGE(B373:X373))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -18032,7 +18092,7 @@
       <c r="W374" s="3"/>
       <c r="X374" s="3"/>
       <c r="Y374" s="4" t="str">
-        <f>IF(COUNTA(B374:X374)=0,"",AVERAGE(B374:X374))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -18062,7 +18122,7 @@
       <c r="W375" s="3"/>
       <c r="X375" s="3"/>
       <c r="Y375" s="4" t="str">
-        <f>IF(COUNTA(B375:X375)=0,"",AVERAGE(B375:X375))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -18092,7 +18152,7 @@
       <c r="W376" s="3"/>
       <c r="X376" s="3"/>
       <c r="Y376" s="4" t="str">
-        <f>IF(COUNTA(B376:X376)=0,"",AVERAGE(B376:X376))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -18122,7 +18182,7 @@
       <c r="W377" s="3"/>
       <c r="X377" s="3"/>
       <c r="Y377" s="4" t="str">
-        <f>IF(COUNTA(B377:X377)=0,"",AVERAGE(B377:X377))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -18152,7 +18212,7 @@
       <c r="W378" s="3"/>
       <c r="X378" s="3"/>
       <c r="Y378" s="4" t="str">
-        <f>IF(COUNTA(B378:X378)=0,"",AVERAGE(B378:X378))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -18182,7 +18242,7 @@
       <c r="W379" s="3"/>
       <c r="X379" s="3"/>
       <c r="Y379" s="4" t="str">
-        <f>IF(COUNTA(B379:X379)=0,"",AVERAGE(B379:X379))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -18212,7 +18272,7 @@
       <c r="W380" s="3"/>
       <c r="X380" s="3"/>
       <c r="Y380" s="4" t="str">
-        <f>IF(COUNTA(B380:X380)=0,"",AVERAGE(B380:X380))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -18242,7 +18302,7 @@
       <c r="W381" s="3"/>
       <c r="X381" s="3"/>
       <c r="Y381" s="4" t="str">
-        <f>IF(COUNTA(B381:X381)=0,"",AVERAGE(B381:X381))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -18272,7 +18332,7 @@
       <c r="W382" s="3"/>
       <c r="X382" s="3"/>
       <c r="Y382" s="4" t="str">
-        <f>IF(COUNTA(B382:X382)=0,"",AVERAGE(B382:X382))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -18302,7 +18362,7 @@
       <c r="W383" s="3"/>
       <c r="X383" s="3"/>
       <c r="Y383" s="4" t="str">
-        <f>IF(COUNTA(B383:X383)=0,"",AVERAGE(B383:X383))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -18332,7 +18392,7 @@
       <c r="W384" s="3"/>
       <c r="X384" s="3"/>
       <c r="Y384" s="4" t="str">
-        <f>IF(COUNTA(B384:X384)=0,"",AVERAGE(B384:X384))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -18362,7 +18422,7 @@
       <c r="W385" s="3"/>
       <c r="X385" s="3"/>
       <c r="Y385" s="4" t="str">
-        <f>IF(COUNTA(B385:X385)=0,"",AVERAGE(B385:X385))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -18392,7 +18452,7 @@
       <c r="W386" s="3"/>
       <c r="X386" s="3"/>
       <c r="Y386" s="4" t="str">
-        <f>IF(COUNTA(B386:X386)=0,"",AVERAGE(B386:X386))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -18422,7 +18482,7 @@
       <c r="W387" s="3"/>
       <c r="X387" s="3"/>
       <c r="Y387" s="4" t="str">
-        <f>IF(COUNTA(B387:X387)=0,"",AVERAGE(B387:X387))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -18452,7 +18512,7 @@
       <c r="W388" s="3"/>
       <c r="X388" s="3"/>
       <c r="Y388" s="4" t="str">
-        <f>IF(COUNTA(B388:X388)=0,"",AVERAGE(B388:X388))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -18482,7 +18542,7 @@
       <c r="W389" s="3"/>
       <c r="X389" s="3"/>
       <c r="Y389" s="4" t="str">
-        <f>IF(COUNTA(B389:X389)=0,"",AVERAGE(B389:X389))</f>
+        <f t="shared" ref="Y389:Y452" si="6">IF(COUNTA(B389:X389)=0,"",AVERAGE(B389:X389))</f>
         <v/>
       </c>
     </row>
@@ -18512,7 +18572,7 @@
       <c r="W390" s="3"/>
       <c r="X390" s="3"/>
       <c r="Y390" s="4" t="str">
-        <f>IF(COUNTA(B390:X390)=0,"",AVERAGE(B390:X390))</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
@@ -19515,29 +19575,69 @@
       </c>
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A18" s="2"/>
-      <c r="B18" s="3"/>
-      <c r="C18" s="3"/>
-      <c r="D18" s="3"/>
-      <c r="E18" s="3"/>
-      <c r="F18" s="3"/>
-      <c r="G18" s="3"/>
-      <c r="H18" s="3"/>
-      <c r="I18" s="3"/>
-      <c r="J18" s="3"/>
-      <c r="K18" s="3"/>
-      <c r="L18" s="3"/>
-      <c r="M18" s="3"/>
-      <c r="N18" s="3"/>
-      <c r="O18" s="3"/>
-      <c r="P18" s="3"/>
-      <c r="Q18" s="3"/>
-      <c r="R18" s="3"/>
-      <c r="S18" s="3"/>
-      <c r="T18" s="3"/>
-      <c r="U18" s="4" t="str">
+      <c r="A18" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B18" s="3">
+        <v>4.29</v>
+      </c>
+      <c r="C18" s="3">
+        <v>3.95</v>
+      </c>
+      <c r="D18" s="3">
+        <v>2.4900000000000002</v>
+      </c>
+      <c r="E18" s="3">
+        <v>3.8</v>
+      </c>
+      <c r="F18" s="3">
+        <v>4.3099999999999996</v>
+      </c>
+      <c r="G18" s="3">
+        <v>3.99</v>
+      </c>
+      <c r="H18" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="I18" s="3">
+        <v>3.39</v>
+      </c>
+      <c r="J18" s="3">
+        <v>3.09</v>
+      </c>
+      <c r="K18" s="3">
+        <v>3.99</v>
+      </c>
+      <c r="L18" s="3">
+        <v>2.39</v>
+      </c>
+      <c r="M18" s="3">
+        <v>3.79</v>
+      </c>
+      <c r="N18" s="3">
+        <v>3.79</v>
+      </c>
+      <c r="O18" s="3">
+        <v>3.8</v>
+      </c>
+      <c r="P18" s="3">
+        <v>3.74</v>
+      </c>
+      <c r="Q18" s="3">
+        <v>4.03</v>
+      </c>
+      <c r="R18" s="3">
+        <v>3.79</v>
+      </c>
+      <c r="S18" s="3">
+        <v>3.99</v>
+      </c>
+      <c r="T18" s="3">
+        <v>1.99</v>
+      </c>
+      <c r="U18" s="4">
         <f t="shared" si="0"/>
-        <v/>
+        <v>3.5578947368421048</v>
       </c>
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
@@ -29771,19 +29871,39 @@
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A18" s="2"/>
-      <c r="B18" s="3"/>
-      <c r="C18" s="3"/>
-      <c r="D18" s="3"/>
-      <c r="E18" s="3"/>
-      <c r="F18" s="3"/>
-      <c r="G18" s="3"/>
-      <c r="H18" s="3"/>
-      <c r="I18" s="3"/>
-      <c r="J18" s="3"/>
-      <c r="K18" s="4" t="str">
+      <c r="A18" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B18" s="3">
+        <v>2.85</v>
+      </c>
+      <c r="C18" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="D18" s="3">
+        <v>2.67</v>
+      </c>
+      <c r="E18" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="F18" s="3">
+        <v>2.8</v>
+      </c>
+      <c r="G18" s="3">
+        <v>2.96</v>
+      </c>
+      <c r="H18" s="3">
+        <v>2.63</v>
+      </c>
+      <c r="I18" s="3">
+        <v>2.79</v>
+      </c>
+      <c r="J18" s="3">
+        <v>2.59</v>
+      </c>
+      <c r="K18" s="4">
         <f t="shared" si="0"/>
-        <v/>
+        <v>2.8077777777777779</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.25">
@@ -36341,20 +36461,42 @@
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A18" s="2"/>
-      <c r="B18" s="3"/>
-      <c r="C18" s="3"/>
-      <c r="D18" s="3"/>
-      <c r="E18" s="3"/>
-      <c r="F18" s="3"/>
-      <c r="G18" s="3"/>
-      <c r="H18" s="3"/>
-      <c r="I18" s="3"/>
-      <c r="J18" s="3"/>
-      <c r="K18" s="3"/>
-      <c r="L18" s="4" t="str">
+      <c r="A18" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B18" s="3">
+        <v>3.55</v>
+      </c>
+      <c r="C18" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="D18" s="3">
+        <v>3.15</v>
+      </c>
+      <c r="E18" s="3">
+        <v>3.35</v>
+      </c>
+      <c r="F18" s="3">
+        <v>3.43</v>
+      </c>
+      <c r="G18" s="3">
+        <v>3.69</v>
+      </c>
+      <c r="H18" s="3">
+        <v>3.11</v>
+      </c>
+      <c r="I18" s="3">
+        <v>3.29</v>
+      </c>
+      <c r="J18" s="3">
+        <v>3.55</v>
+      </c>
+      <c r="K18" s="3">
+        <v>3.29</v>
+      </c>
+      <c r="L18" s="4">
         <f t="shared" si="0"/>
-        <v/>
+        <v>3.34</v>
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">

--- a/app/mevduat-kredi-faizleri/data/hoca-ile-borsa-faiz-takip-sablonu-guncel.xlsx
+++ b/app/mevduat-kredi-faizleri/data/hoca-ile-borsa-faiz-takip-sablonu-guncel.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projeler\hoca-ile-borsa\app\mevduat-kredi-faizleri\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{797B09B7-FE21-4512-88A1-CE5DCAF2271E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28E31E67-BFBB-4460-87DA-FCAFA7B97D70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="18735" yWindow="5535" windowWidth="19665" windowHeight="15345" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="24240" yWindow="3540" windowWidth="14025" windowHeight="15345" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Mevduat" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="40">
   <si>
     <t>Mevduat Günlük Oran Takip Şablonu</t>
   </si>
@@ -97,6 +97,9 @@
   </si>
   <si>
     <t>TEB - Türk Ekonomi Bankası</t>
+  </si>
+  <si>
+    <t>Şekerbank</t>
   </si>
   <si>
     <t>Yapı Kredi</t>
@@ -315,7 +318,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Mevduat!$Y$4</c:f>
+              <c:f>Mevduat!$Z$4</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -380,59 +383,62 @@
                 <c:pt idx="13">
                   <c:v>46142</c:v>
                 </c:pt>
+                <c:pt idx="14">
+                  <c:v>46146</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Mevduat!$Y$5:$Y$390</c:f>
+              <c:f>Mevduat!$Z$5:$Z$390</c:f>
               <c:numCache>
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="386"/>
                 <c:pt idx="0">
-                  <c:v>43.078695652173913</c:v>
+                  <c:v>42.825416666666662</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>43.078695652173913</c:v>
+                  <c:v>42.825416666666662</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>43.078695652173913</c:v>
+                  <c:v>42.825416666666662</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>43.52</c:v>
+                  <c:v>43.248333333333335</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>43.35</c:v>
+                  <c:v>43.085416666666667</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>43.393478260869564</c:v>
+                  <c:v>43.127083333333331</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>43.35</c:v>
+                  <c:v>43.085416666666667</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>43.343043478260867</c:v>
+                  <c:v>43.078749999999992</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>43.375652173913046</c:v>
+                  <c:v>43.109999999999992</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>43.375652173913046</c:v>
+                  <c:v>43.109999999999992</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>43.364782608695648</c:v>
+                  <c:v>43.099583333333328</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>43.416086956521738</c:v>
+                  <c:v>43.148750000000007</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>43.383478260869566</c:v>
+                  <c:v>43.117500000000007</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>43.383478260869566</c:v>
+                  <c:v>43.117500000000007</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0</c:v>
+                  <c:v>43.534166666666671</c:v>
                 </c:pt>
                 <c:pt idx="15">
                   <c:v>0</c:v>
@@ -1748,6 +1754,9 @@
                 <c:pt idx="13">
                   <c:v>46142</c:v>
                 </c:pt>
+                <c:pt idx="14">
+                  <c:v>46146</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1800,7 +1809,7 @@
                   <c:v>3.5578947368421048</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0</c:v>
+                  <c:v>3.5789473684210527</c:v>
                 </c:pt>
                 <c:pt idx="15">
                   <c:v>0</c:v>
@@ -3116,6 +3125,9 @@
                 <c:pt idx="13">
                   <c:v>46142</c:v>
                 </c:pt>
+                <c:pt idx="14">
+                  <c:v>46146</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3168,7 +3180,7 @@
                   <c:v>2.8077777777777779</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0</c:v>
+                  <c:v>2.8077777777777779</c:v>
                 </c:pt>
                 <c:pt idx="15">
                   <c:v>0</c:v>
@@ -4484,6 +4496,9 @@
                 <c:pt idx="13">
                   <c:v>46142</c:v>
                 </c:pt>
+                <c:pt idx="14">
+                  <c:v>46146</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -4536,7 +4551,7 @@
                   <c:v>3.34</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0</c:v>
+                  <c:v>3.34</c:v>
                 </c:pt>
                 <c:pt idx="15">
                   <c:v>0</c:v>
@@ -6181,15 +6196,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Y392"/>
+  <dimension ref="A1:Z392"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
-    <col min="2" max="24" width="18" customWidth="1"/>
-    <col min="25" max="25" width="16" customWidth="1"/>
+    <col min="2" max="25" width="18" customWidth="1"/>
+    <col min="26" max="26" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:26" ht="24" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
@@ -6217,8 +6232,9 @@
       <c r="W1" s="7"/>
       <c r="X1" s="7"/>
       <c r="Y1" s="7"/>
-    </row>
-    <row r="2" spans="1:25" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z1" s="7"/>
+    </row>
+    <row r="2" spans="1:26" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
         <v>1</v>
       </c>
@@ -6246,8 +6262,9 @@
       <c r="W2" s="7"/>
       <c r="X2" s="7"/>
       <c r="Y2" s="7"/>
-    </row>
-    <row r="4" spans="1:25" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z2" s="7"/>
+    </row>
+    <row r="4" spans="1:26" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
@@ -6323,8 +6340,11 @@
       <c r="Y4" s="1" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z4" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="5" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>46123</v>
       </c>
@@ -6383,26 +6403,29 @@
         <v>37</v>
       </c>
       <c r="T5" s="3">
+        <v>37</v>
+      </c>
+      <c r="U5" s="3">
         <v>43</v>
       </c>
-      <c r="U5" s="3">
+      <c r="V5" s="3">
         <v>44.5</v>
       </c>
-      <c r="V5" s="3">
+      <c r="W5" s="3">
         <v>42</v>
       </c>
-      <c r="W5" s="3">
+      <c r="X5" s="3">
         <v>46</v>
       </c>
-      <c r="X5" s="3">
+      <c r="Y5" s="3">
         <v>45.25</v>
       </c>
-      <c r="Y5" s="4">
-        <f t="shared" ref="Y5:Y68" si="0">IF(COUNTA(B5:X5)=0,"",AVERAGE(B5:X5))</f>
-        <v>43.078695652173913</v>
-      </c>
-    </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z5" s="4">
+        <f t="shared" ref="Z5:Z68" si="0">IF(COUNTA(B5:Y5)=0,"",AVERAGE(B5:Y5))</f>
+        <v>42.825416666666662</v>
+      </c>
+    </row>
+    <row r="6" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>46125</v>
       </c>
@@ -6461,26 +6484,29 @@
         <v>37</v>
       </c>
       <c r="T6" s="3">
+        <v>37</v>
+      </c>
+      <c r="U6" s="3">
         <v>43</v>
       </c>
-      <c r="U6" s="3">
+      <c r="V6" s="3">
         <v>44.5</v>
       </c>
-      <c r="V6" s="3">
+      <c r="W6" s="3">
         <v>42</v>
       </c>
-      <c r="W6" s="3">
+      <c r="X6" s="3">
         <v>46</v>
       </c>
-      <c r="X6" s="3">
+      <c r="Y6" s="3">
         <v>45.25</v>
       </c>
-      <c r="Y6" s="4">
-        <f t="shared" si="0"/>
-        <v>43.078695652173913</v>
-      </c>
-    </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z6" s="4">
+        <f t="shared" ref="Z6" si="1">IF(COUNTA(B6:Y6)=0,"",AVERAGE(B6:Y6))</f>
+        <v>42.825416666666662</v>
+      </c>
+    </row>
+    <row r="7" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>46126</v>
       </c>
@@ -6539,26 +6565,29 @@
         <v>37</v>
       </c>
       <c r="T7" s="3">
+        <v>37</v>
+      </c>
+      <c r="U7" s="3">
         <v>43</v>
       </c>
-      <c r="U7" s="3">
+      <c r="V7" s="3">
         <v>44.5</v>
       </c>
-      <c r="V7" s="3">
+      <c r="W7" s="3">
         <v>42</v>
       </c>
-      <c r="W7" s="3">
+      <c r="X7" s="3">
         <v>46</v>
       </c>
-      <c r="X7" s="3">
+      <c r="Y7" s="3">
         <v>45.25</v>
       </c>
-      <c r="Y7" s="4">
+      <c r="Z7" s="4">
         <f t="shared" si="0"/>
-        <v>43.078695652173913</v>
-      </c>
-    </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.25">
+        <v>42.825416666666662</v>
+      </c>
+    </row>
+    <row r="8" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>46127</v>
       </c>
@@ -6617,26 +6646,29 @@
         <v>45</v>
       </c>
       <c r="T8" s="3">
+        <v>37</v>
+      </c>
+      <c r="U8" s="3">
         <v>43</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>44.5</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>42</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>46</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>45.25</v>
       </c>
-      <c r="Y8" s="4">
+      <c r="Z8" s="4">
         <f t="shared" si="0"/>
-        <v>43.52</v>
-      </c>
-    </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.25">
+        <v>43.248333333333335</v>
+      </c>
+    </row>
+    <row r="9" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>46128</v>
       </c>
@@ -6695,26 +6727,29 @@
         <v>45</v>
       </c>
       <c r="T9" s="3">
+        <v>37</v>
+      </c>
+      <c r="U9" s="3">
         <v>43</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>44.5</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>42</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>46</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>45.25</v>
       </c>
-      <c r="Y9" s="4">
+      <c r="Z9" s="4">
         <f t="shared" si="0"/>
-        <v>43.35</v>
-      </c>
-    </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.25">
+        <v>43.085416666666667</v>
+      </c>
+    </row>
+    <row r="10" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>46129</v>
       </c>
@@ -6773,26 +6808,29 @@
         <v>45</v>
       </c>
       <c r="T10" s="3">
+        <v>37</v>
+      </c>
+      <c r="U10" s="3">
         <v>43</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>44.5</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>42</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>46</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>45.25</v>
       </c>
-      <c r="Y10" s="4">
+      <c r="Z10" s="4">
         <f t="shared" si="0"/>
-        <v>43.393478260869564</v>
-      </c>
-    </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.25">
+        <v>43.127083333333331</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <v>46132</v>
       </c>
@@ -6851,26 +6889,29 @@
         <v>45</v>
       </c>
       <c r="T11" s="3">
+        <v>37</v>
+      </c>
+      <c r="U11" s="3">
         <v>43</v>
       </c>
-      <c r="U11" s="3">
+      <c r="V11" s="3">
         <v>44.5</v>
       </c>
-      <c r="V11" s="3">
+      <c r="W11" s="3">
         <v>42</v>
       </c>
-      <c r="W11" s="3">
+      <c r="X11" s="3">
         <v>46</v>
       </c>
-      <c r="X11" s="3">
+      <c r="Y11" s="3">
         <v>45.25</v>
       </c>
-      <c r="Y11" s="4">
+      <c r="Z11" s="4">
         <f t="shared" si="0"/>
-        <v>43.35</v>
-      </c>
-    </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.25">
+        <v>43.085416666666667</v>
+      </c>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <v>46133</v>
       </c>
@@ -6929,26 +6970,29 @@
         <v>45</v>
       </c>
       <c r="T12" s="3">
+        <v>37</v>
+      </c>
+      <c r="U12" s="3">
         <v>43</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>44.25</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>42</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>46</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>45.25</v>
       </c>
-      <c r="Y12" s="4">
+      <c r="Z12" s="4">
         <f t="shared" si="0"/>
-        <v>43.343043478260867</v>
-      </c>
-    </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.25">
+        <v>43.078749999999992</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
         <v>46134</v>
       </c>
@@ -7007,26 +7051,29 @@
         <v>45</v>
       </c>
       <c r="T13" s="3">
+        <v>37</v>
+      </c>
+      <c r="U13" s="3">
         <v>43</v>
       </c>
-      <c r="U13" s="3">
+      <c r="V13" s="3">
         <v>43.75</v>
       </c>
-      <c r="V13" s="3">
+      <c r="W13" s="3">
         <v>42</v>
       </c>
-      <c r="W13" s="3">
+      <c r="X13" s="3">
         <v>46</v>
       </c>
-      <c r="X13" s="3">
+      <c r="Y13" s="3">
         <v>45.25</v>
       </c>
-      <c r="Y13" s="4">
+      <c r="Z13" s="4">
         <f t="shared" si="0"/>
-        <v>43.375652173913046</v>
-      </c>
-    </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.25">
+        <v>43.109999999999992</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
         <v>46136</v>
       </c>
@@ -7085,26 +7132,29 @@
         <v>45</v>
       </c>
       <c r="T14" s="3">
+        <v>37</v>
+      </c>
+      <c r="U14" s="3">
         <v>43</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>43.75</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>42</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>46</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>45.25</v>
       </c>
-      <c r="Y14" s="4">
+      <c r="Z14" s="4">
         <f t="shared" si="0"/>
-        <v>43.375652173913046</v>
-      </c>
-    </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.25">
+        <v>43.109999999999992</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
         <v>46139</v>
       </c>
@@ -7163,26 +7213,29 @@
         <v>45</v>
       </c>
       <c r="T15" s="3">
+        <v>37</v>
+      </c>
+      <c r="U15" s="3">
         <v>43</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>43.5</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>42</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>46</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>45.25</v>
       </c>
-      <c r="Y15" s="4">
+      <c r="Z15" s="4">
         <f t="shared" si="0"/>
-        <v>43.364782608695648</v>
-      </c>
-    </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.25">
+        <v>43.099583333333328</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
         <v>46140</v>
       </c>
@@ -7241,26 +7294,29 @@
         <v>45</v>
       </c>
       <c r="T16" s="3">
+        <v>37</v>
+      </c>
+      <c r="U16" s="3">
         <v>43</v>
       </c>
-      <c r="U16" s="3">
+      <c r="V16" s="3">
         <v>43.5</v>
       </c>
-      <c r="V16" s="3">
+      <c r="W16" s="3">
         <v>42</v>
       </c>
-      <c r="W16" s="3">
+      <c r="X16" s="3">
         <v>47</v>
       </c>
-      <c r="X16" s="3">
+      <c r="Y16" s="3">
         <v>45.25</v>
       </c>
-      <c r="Y16" s="4">
+      <c r="Z16" s="4">
         <f t="shared" si="0"/>
-        <v>43.416086956521738</v>
-      </c>
-    </row>
-    <row r="17" spans="1:25" x14ac:dyDescent="0.25">
+        <v>43.148750000000007</v>
+      </c>
+    </row>
+    <row r="17" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
         <v>46141</v>
       </c>
@@ -7319,26 +7375,29 @@
         <v>45</v>
       </c>
       <c r="T17" s="3">
+        <v>37</v>
+      </c>
+      <c r="U17" s="3">
         <v>43</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>43.5</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>42</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>47</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>45.25</v>
       </c>
-      <c r="Y17" s="4">
+      <c r="Z17" s="4">
         <f t="shared" si="0"/>
-        <v>43.383478260869566</v>
-      </c>
-    </row>
-    <row r="18" spans="1:25" x14ac:dyDescent="0.25">
+        <v>43.117500000000007</v>
+      </c>
+    </row>
+    <row r="18" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
         <v>46142</v>
       </c>
@@ -7397,56 +7456,110 @@
         <v>45</v>
       </c>
       <c r="T18" s="3">
+        <v>37</v>
+      </c>
+      <c r="U18" s="3">
         <v>43</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>43.5</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>42</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>47</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>45.25</v>
       </c>
-      <c r="Y18" s="4">
+      <c r="Z18" s="4">
         <f t="shared" si="0"/>
-        <v>43.383478260869566</v>
-      </c>
-    </row>
-    <row r="19" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A19" s="2"/>
-      <c r="B19" s="3"/>
-      <c r="C19" s="3"/>
-      <c r="D19" s="3"/>
-      <c r="E19" s="3"/>
-      <c r="F19" s="3"/>
-      <c r="G19" s="3"/>
-      <c r="H19" s="3"/>
-      <c r="I19" s="3"/>
-      <c r="J19" s="3"/>
-      <c r="K19" s="3"/>
-      <c r="L19" s="3"/>
-      <c r="M19" s="3"/>
-      <c r="N19" s="3"/>
-      <c r="O19" s="3"/>
-      <c r="P19" s="3"/>
-      <c r="Q19" s="3"/>
-      <c r="R19" s="3"/>
-      <c r="S19" s="3"/>
-      <c r="T19" s="3"/>
-      <c r="U19" s="3"/>
-      <c r="V19" s="3"/>
-      <c r="W19" s="3"/>
-      <c r="X19" s="3"/>
-      <c r="Y19" s="4" t="str">
+        <v>43.117500000000007</v>
+      </c>
+    </row>
+    <row r="19" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A19" s="2">
+        <v>46146</v>
+      </c>
+      <c r="B19" s="3">
+        <v>42</v>
+      </c>
+      <c r="C19" s="3">
+        <v>46</v>
+      </c>
+      <c r="D19" s="3">
+        <v>45</v>
+      </c>
+      <c r="E19" s="3">
+        <v>45</v>
+      </c>
+      <c r="F19" s="3">
+        <v>43.5</v>
+      </c>
+      <c r="G19" s="3">
+        <v>41.5</v>
+      </c>
+      <c r="H19" s="3">
+        <v>46</v>
+      </c>
+      <c r="I19" s="3">
+        <v>41.5</v>
+      </c>
+      <c r="J19" s="3">
+        <v>43</v>
+      </c>
+      <c r="K19" s="3">
+        <v>41</v>
+      </c>
+      <c r="L19" s="3">
+        <v>36</v>
+      </c>
+      <c r="M19" s="3">
+        <v>44</v>
+      </c>
+      <c r="N19" s="3">
+        <v>45</v>
+      </c>
+      <c r="O19" s="3">
+        <v>42.57</v>
+      </c>
+      <c r="P19" s="3">
+        <v>40</v>
+      </c>
+      <c r="Q19" s="3">
+        <v>45</v>
+      </c>
+      <c r="R19" s="3">
+        <v>45</v>
+      </c>
+      <c r="S19" s="3">
+        <v>45</v>
+      </c>
+      <c r="T19" s="3">
+        <v>45</v>
+      </c>
+      <c r="U19" s="3">
+        <v>43.5</v>
+      </c>
+      <c r="V19" s="3">
+        <v>45</v>
+      </c>
+      <c r="W19" s="3">
+        <v>42</v>
+      </c>
+      <c r="X19" s="3">
+        <v>47</v>
+      </c>
+      <c r="Y19" s="3">
+        <v>45.25</v>
+      </c>
+      <c r="Z19" s="4">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="20" spans="1:25" x14ac:dyDescent="0.25">
+        <v>43.534166666666671</v>
+      </c>
+    </row>
+    <row r="20" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A20" s="2"/>
       <c r="B20" s="3"/>
       <c r="C20" s="3"/>
@@ -7471,12 +7584,13 @@
       <c r="V20" s="3"/>
       <c r="W20" s="3"/>
       <c r="X20" s="3"/>
-      <c r="Y20" s="4" t="str">
+      <c r="Y20" s="3"/>
+      <c r="Z20" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="21" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A21" s="2"/>
       <c r="B21" s="3"/>
       <c r="C21" s="3"/>
@@ -7501,12 +7615,13 @@
       <c r="V21" s="3"/>
       <c r="W21" s="3"/>
       <c r="X21" s="3"/>
-      <c r="Y21" s="4" t="str">
+      <c r="Y21" s="3"/>
+      <c r="Z21" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="22" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A22" s="2"/>
       <c r="B22" s="3"/>
       <c r="C22" s="3"/>
@@ -7531,12 +7646,13 @@
       <c r="V22" s="3"/>
       <c r="W22" s="3"/>
       <c r="X22" s="3"/>
-      <c r="Y22" s="4" t="str">
+      <c r="Y22" s="3"/>
+      <c r="Z22" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="23" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A23" s="2"/>
       <c r="B23" s="3"/>
       <c r="C23" s="3"/>
@@ -7561,12 +7677,13 @@
       <c r="V23" s="3"/>
       <c r="W23" s="3"/>
       <c r="X23" s="3"/>
-      <c r="Y23" s="4" t="str">
+      <c r="Y23" s="3"/>
+      <c r="Z23" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A24" s="2"/>
       <c r="B24" s="3"/>
       <c r="C24" s="3"/>
@@ -7591,12 +7708,13 @@
       <c r="V24" s="3"/>
       <c r="W24" s="3"/>
       <c r="X24" s="3"/>
-      <c r="Y24" s="4" t="str">
+      <c r="Y24" s="3"/>
+      <c r="Z24" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A25" s="2"/>
       <c r="B25" s="3"/>
       <c r="C25" s="3"/>
@@ -7621,12 +7739,13 @@
       <c r="V25" s="3"/>
       <c r="W25" s="3"/>
       <c r="X25" s="3"/>
-      <c r="Y25" s="4" t="str">
+      <c r="Y25" s="3"/>
+      <c r="Z25" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="26" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A26" s="2"/>
       <c r="B26" s="3"/>
       <c r="C26" s="3"/>
@@ -7651,12 +7770,13 @@
       <c r="V26" s="3"/>
       <c r="W26" s="3"/>
       <c r="X26" s="3"/>
-      <c r="Y26" s="4" t="str">
+      <c r="Y26" s="3"/>
+      <c r="Z26" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="27" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A27" s="2"/>
       <c r="B27" s="3"/>
       <c r="C27" s="3"/>
@@ -7681,12 +7801,13 @@
       <c r="V27" s="3"/>
       <c r="W27" s="3"/>
       <c r="X27" s="3"/>
-      <c r="Y27" s="4" t="str">
+      <c r="Y27" s="3"/>
+      <c r="Z27" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="28" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A28" s="2"/>
       <c r="B28" s="3"/>
       <c r="C28" s="3"/>
@@ -7711,12 +7832,13 @@
       <c r="V28" s="3"/>
       <c r="W28" s="3"/>
       <c r="X28" s="3"/>
-      <c r="Y28" s="4" t="str">
+      <c r="Y28" s="3"/>
+      <c r="Z28" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="29" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A29" s="2"/>
       <c r="B29" s="3"/>
       <c r="C29" s="3"/>
@@ -7741,12 +7863,13 @@
       <c r="V29" s="3"/>
       <c r="W29" s="3"/>
       <c r="X29" s="3"/>
-      <c r="Y29" s="4" t="str">
+      <c r="Y29" s="3"/>
+      <c r="Z29" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="30" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A30" s="2"/>
       <c r="B30" s="3"/>
       <c r="C30" s="3"/>
@@ -7771,12 +7894,13 @@
       <c r="V30" s="3"/>
       <c r="W30" s="3"/>
       <c r="X30" s="3"/>
-      <c r="Y30" s="4" t="str">
+      <c r="Y30" s="3"/>
+      <c r="Z30" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="31" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A31" s="2"/>
       <c r="B31" s="3"/>
       <c r="C31" s="3"/>
@@ -7801,12 +7925,13 @@
       <c r="V31" s="3"/>
       <c r="W31" s="3"/>
       <c r="X31" s="3"/>
-      <c r="Y31" s="4" t="str">
+      <c r="Y31" s="3"/>
+      <c r="Z31" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="32" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A32" s="2"/>
       <c r="B32" s="3"/>
       <c r="C32" s="3"/>
@@ -7831,12 +7956,13 @@
       <c r="V32" s="3"/>
       <c r="W32" s="3"/>
       <c r="X32" s="3"/>
-      <c r="Y32" s="4" t="str">
+      <c r="Y32" s="3"/>
+      <c r="Z32" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="33" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A33" s="2"/>
       <c r="B33" s="3"/>
       <c r="C33" s="3"/>
@@ -7861,12 +7987,13 @@
       <c r="V33" s="3"/>
       <c r="W33" s="3"/>
       <c r="X33" s="3"/>
-      <c r="Y33" s="4" t="str">
+      <c r="Y33" s="3"/>
+      <c r="Z33" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="34" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A34" s="2"/>
       <c r="B34" s="3"/>
       <c r="C34" s="3"/>
@@ -7891,12 +8018,13 @@
       <c r="V34" s="3"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
-      <c r="Y34" s="4" t="str">
+      <c r="Y34" s="3"/>
+      <c r="Z34" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="35" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A35" s="2"/>
       <c r="B35" s="3"/>
       <c r="C35" s="3"/>
@@ -7921,12 +8049,13 @@
       <c r="V35" s="3"/>
       <c r="W35" s="3"/>
       <c r="X35" s="3"/>
-      <c r="Y35" s="4" t="str">
+      <c r="Y35" s="3"/>
+      <c r="Z35" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="36" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A36" s="2"/>
       <c r="B36" s="3"/>
       <c r="C36" s="3"/>
@@ -7951,12 +8080,13 @@
       <c r="V36" s="3"/>
       <c r="W36" s="3"/>
       <c r="X36" s="3"/>
-      <c r="Y36" s="4" t="str">
+      <c r="Y36" s="3"/>
+      <c r="Z36" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="37" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A37" s="2"/>
       <c r="B37" s="3"/>
       <c r="C37" s="3"/>
@@ -7981,12 +8111,13 @@
       <c r="V37" s="3"/>
       <c r="W37" s="3"/>
       <c r="X37" s="3"/>
-      <c r="Y37" s="4" t="str">
+      <c r="Y37" s="3"/>
+      <c r="Z37" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="38" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A38" s="2"/>
       <c r="B38" s="3"/>
       <c r="C38" s="3"/>
@@ -8011,12 +8142,13 @@
       <c r="V38" s="3"/>
       <c r="W38" s="3"/>
       <c r="X38" s="3"/>
-      <c r="Y38" s="4" t="str">
+      <c r="Y38" s="3"/>
+      <c r="Z38" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="39" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A39" s="2"/>
       <c r="B39" s="3"/>
       <c r="C39" s="3"/>
@@ -8041,12 +8173,13 @@
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
-      <c r="Y39" s="4" t="str">
+      <c r="Y39" s="3"/>
+      <c r="Z39" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="40" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A40" s="2"/>
       <c r="B40" s="3"/>
       <c r="C40" s="3"/>
@@ -8071,12 +8204,13 @@
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
-      <c r="Y40" s="4" t="str">
+      <c r="Y40" s="3"/>
+      <c r="Z40" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="41" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A41" s="2"/>
       <c r="B41" s="3"/>
       <c r="C41" s="3"/>
@@ -8101,12 +8235,13 @@
       <c r="V41" s="3"/>
       <c r="W41" s="3"/>
       <c r="X41" s="3"/>
-      <c r="Y41" s="4" t="str">
+      <c r="Y41" s="3"/>
+      <c r="Z41" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="42" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A42" s="2"/>
       <c r="B42" s="3"/>
       <c r="C42" s="3"/>
@@ -8131,12 +8266,13 @@
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
-      <c r="Y42" s="4" t="str">
+      <c r="Y42" s="3"/>
+      <c r="Z42" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="43" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A43" s="2"/>
       <c r="B43" s="3"/>
       <c r="C43" s="3"/>
@@ -8161,12 +8297,13 @@
       <c r="V43" s="3"/>
       <c r="W43" s="3"/>
       <c r="X43" s="3"/>
-      <c r="Y43" s="4" t="str">
+      <c r="Y43" s="3"/>
+      <c r="Z43" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="44" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A44" s="2"/>
       <c r="B44" s="3"/>
       <c r="C44" s="3"/>
@@ -8191,12 +8328,13 @@
       <c r="V44" s="3"/>
       <c r="W44" s="3"/>
       <c r="X44" s="3"/>
-      <c r="Y44" s="4" t="str">
+      <c r="Y44" s="3"/>
+      <c r="Z44" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="45" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A45" s="2"/>
       <c r="B45" s="3"/>
       <c r="C45" s="3"/>
@@ -8221,12 +8359,13 @@
       <c r="V45" s="3"/>
       <c r="W45" s="3"/>
       <c r="X45" s="3"/>
-      <c r="Y45" s="4" t="str">
+      <c r="Y45" s="3"/>
+      <c r="Z45" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="46" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A46" s="2"/>
       <c r="B46" s="3"/>
       <c r="C46" s="3"/>
@@ -8251,12 +8390,13 @@
       <c r="V46" s="3"/>
       <c r="W46" s="3"/>
       <c r="X46" s="3"/>
-      <c r="Y46" s="4" t="str">
+      <c r="Y46" s="3"/>
+      <c r="Z46" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="47" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A47" s="2"/>
       <c r="B47" s="3"/>
       <c r="C47" s="3"/>
@@ -8281,12 +8421,13 @@
       <c r="V47" s="3"/>
       <c r="W47" s="3"/>
       <c r="X47" s="3"/>
-      <c r="Y47" s="4" t="str">
+      <c r="Y47" s="3"/>
+      <c r="Z47" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="48" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A48" s="2"/>
       <c r="B48" s="3"/>
       <c r="C48" s="3"/>
@@ -8311,12 +8452,13 @@
       <c r="V48" s="3"/>
       <c r="W48" s="3"/>
       <c r="X48" s="3"/>
-      <c r="Y48" s="4" t="str">
+      <c r="Y48" s="3"/>
+      <c r="Z48" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="49" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A49" s="2"/>
       <c r="B49" s="3"/>
       <c r="C49" s="3"/>
@@ -8341,12 +8483,13 @@
       <c r="V49" s="3"/>
       <c r="W49" s="3"/>
       <c r="X49" s="3"/>
-      <c r="Y49" s="4" t="str">
+      <c r="Y49" s="3"/>
+      <c r="Z49" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="50" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A50" s="2"/>
       <c r="B50" s="3"/>
       <c r="C50" s="3"/>
@@ -8371,12 +8514,13 @@
       <c r="V50" s="3"/>
       <c r="W50" s="3"/>
       <c r="X50" s="3"/>
-      <c r="Y50" s="4" t="str">
+      <c r="Y50" s="3"/>
+      <c r="Z50" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="51" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A51" s="2"/>
       <c r="B51" s="3"/>
       <c r="C51" s="3"/>
@@ -8401,12 +8545,13 @@
       <c r="V51" s="3"/>
       <c r="W51" s="3"/>
       <c r="X51" s="3"/>
-      <c r="Y51" s="4" t="str">
+      <c r="Y51" s="3"/>
+      <c r="Z51" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="52" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A52" s="2"/>
       <c r="B52" s="3"/>
       <c r="C52" s="3"/>
@@ -8431,12 +8576,13 @@
       <c r="V52" s="3"/>
       <c r="W52" s="3"/>
       <c r="X52" s="3"/>
-      <c r="Y52" s="4" t="str">
+      <c r="Y52" s="3"/>
+      <c r="Z52" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="53" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A53" s="2"/>
       <c r="B53" s="3"/>
       <c r="C53" s="3"/>
@@ -8461,12 +8607,13 @@
       <c r="V53" s="3"/>
       <c r="W53" s="3"/>
       <c r="X53" s="3"/>
-      <c r="Y53" s="4" t="str">
+      <c r="Y53" s="3"/>
+      <c r="Z53" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="54" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A54" s="2"/>
       <c r="B54" s="3"/>
       <c r="C54" s="3"/>
@@ -8491,12 +8638,13 @@
       <c r="V54" s="3"/>
       <c r="W54" s="3"/>
       <c r="X54" s="3"/>
-      <c r="Y54" s="4" t="str">
+      <c r="Y54" s="3"/>
+      <c r="Z54" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="55" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A55" s="2"/>
       <c r="B55" s="3"/>
       <c r="C55" s="3"/>
@@ -8521,12 +8669,13 @@
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
-      <c r="Y55" s="4" t="str">
+      <c r="Y55" s="3"/>
+      <c r="Z55" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="56" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A56" s="2"/>
       <c r="B56" s="3"/>
       <c r="C56" s="3"/>
@@ -8551,12 +8700,13 @@
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
-      <c r="Y56" s="4" t="str">
+      <c r="Y56" s="3"/>
+      <c r="Z56" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="57" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A57" s="2"/>
       <c r="B57" s="3"/>
       <c r="C57" s="3"/>
@@ -8581,12 +8731,13 @@
       <c r="V57" s="3"/>
       <c r="W57" s="3"/>
       <c r="X57" s="3"/>
-      <c r="Y57" s="4" t="str">
+      <c r="Y57" s="3"/>
+      <c r="Z57" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="58" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A58" s="2"/>
       <c r="B58" s="3"/>
       <c r="C58" s="3"/>
@@ -8611,12 +8762,13 @@
       <c r="V58" s="3"/>
       <c r="W58" s="3"/>
       <c r="X58" s="3"/>
-      <c r="Y58" s="4" t="str">
+      <c r="Y58" s="3"/>
+      <c r="Z58" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="59" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A59" s="2"/>
       <c r="B59" s="3"/>
       <c r="C59" s="3"/>
@@ -8641,12 +8793,13 @@
       <c r="V59" s="3"/>
       <c r="W59" s="3"/>
       <c r="X59" s="3"/>
-      <c r="Y59" s="4" t="str">
+      <c r="Y59" s="3"/>
+      <c r="Z59" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="60" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A60" s="2"/>
       <c r="B60" s="3"/>
       <c r="C60" s="3"/>
@@ -8671,12 +8824,13 @@
       <c r="V60" s="3"/>
       <c r="W60" s="3"/>
       <c r="X60" s="3"/>
-      <c r="Y60" s="4" t="str">
+      <c r="Y60" s="3"/>
+      <c r="Z60" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="61" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A61" s="2"/>
       <c r="B61" s="3"/>
       <c r="C61" s="3"/>
@@ -8701,12 +8855,13 @@
       <c r="V61" s="3"/>
       <c r="W61" s="3"/>
       <c r="X61" s="3"/>
-      <c r="Y61" s="4" t="str">
+      <c r="Y61" s="3"/>
+      <c r="Z61" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="62" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A62" s="2"/>
       <c r="B62" s="3"/>
       <c r="C62" s="3"/>
@@ -8731,12 +8886,13 @@
       <c r="V62" s="3"/>
       <c r="W62" s="3"/>
       <c r="X62" s="3"/>
-      <c r="Y62" s="4" t="str">
+      <c r="Y62" s="3"/>
+      <c r="Z62" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="63" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A63" s="2"/>
       <c r="B63" s="3"/>
       <c r="C63" s="3"/>
@@ -8761,12 +8917,13 @@
       <c r="V63" s="3"/>
       <c r="W63" s="3"/>
       <c r="X63" s="3"/>
-      <c r="Y63" s="4" t="str">
+      <c r="Y63" s="3"/>
+      <c r="Z63" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="64" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A64" s="2"/>
       <c r="B64" s="3"/>
       <c r="C64" s="3"/>
@@ -8791,12 +8948,13 @@
       <c r="V64" s="3"/>
       <c r="W64" s="3"/>
       <c r="X64" s="3"/>
-      <c r="Y64" s="4" t="str">
+      <c r="Y64" s="3"/>
+      <c r="Z64" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="65" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A65" s="2"/>
       <c r="B65" s="3"/>
       <c r="C65" s="3"/>
@@ -8821,12 +8979,13 @@
       <c r="V65" s="3"/>
       <c r="W65" s="3"/>
       <c r="X65" s="3"/>
-      <c r="Y65" s="4" t="str">
+      <c r="Y65" s="3"/>
+      <c r="Z65" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="66" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A66" s="2"/>
       <c r="B66" s="3"/>
       <c r="C66" s="3"/>
@@ -8851,12 +9010,13 @@
       <c r="V66" s="3"/>
       <c r="W66" s="3"/>
       <c r="X66" s="3"/>
-      <c r="Y66" s="4" t="str">
+      <c r="Y66" s="3"/>
+      <c r="Z66" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="67" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A67" s="2"/>
       <c r="B67" s="3"/>
       <c r="C67" s="3"/>
@@ -8881,12 +9041,13 @@
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
-      <c r="Y67" s="4" t="str">
+      <c r="Y67" s="3"/>
+      <c r="Z67" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="68" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A68" s="2"/>
       <c r="B68" s="3"/>
       <c r="C68" s="3"/>
@@ -8911,12 +9072,13 @@
       <c r="V68" s="3"/>
       <c r="W68" s="3"/>
       <c r="X68" s="3"/>
-      <c r="Y68" s="4" t="str">
+      <c r="Y68" s="3"/>
+      <c r="Z68" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="69" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A69" s="2"/>
       <c r="B69" s="3"/>
       <c r="C69" s="3"/>
@@ -8941,12 +9103,13 @@
       <c r="V69" s="3"/>
       <c r="W69" s="3"/>
       <c r="X69" s="3"/>
-      <c r="Y69" s="4" t="str">
-        <f t="shared" ref="Y69:Y132" si="1">IF(COUNTA(B69:X69)=0,"",AVERAGE(B69:X69))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="70" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y69" s="3"/>
+      <c r="Z69" s="4" t="str">
+        <f t="shared" ref="Z69:Z132" si="2">IF(COUNTA(B69:Y69)=0,"",AVERAGE(B69:Y69))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="70" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A70" s="2"/>
       <c r="B70" s="3"/>
       <c r="C70" s="3"/>
@@ -8971,12 +9134,13 @@
       <c r="V70" s="3"/>
       <c r="W70" s="3"/>
       <c r="X70" s="3"/>
-      <c r="Y70" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="71" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y70" s="3"/>
+      <c r="Z70" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="71" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A71" s="2"/>
       <c r="B71" s="3"/>
       <c r="C71" s="3"/>
@@ -9001,12 +9165,13 @@
       <c r="V71" s="3"/>
       <c r="W71" s="3"/>
       <c r="X71" s="3"/>
-      <c r="Y71" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="72" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y71" s="3"/>
+      <c r="Z71" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="72" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A72" s="2"/>
       <c r="B72" s="3"/>
       <c r="C72" s="3"/>
@@ -9031,12 +9196,13 @@
       <c r="V72" s="3"/>
       <c r="W72" s="3"/>
       <c r="X72" s="3"/>
-      <c r="Y72" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="73" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y72" s="3"/>
+      <c r="Z72" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="73" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A73" s="2"/>
       <c r="B73" s="3"/>
       <c r="C73" s="3"/>
@@ -9061,12 +9227,13 @@
       <c r="V73" s="3"/>
       <c r="W73" s="3"/>
       <c r="X73" s="3"/>
-      <c r="Y73" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="74" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y73" s="3"/>
+      <c r="Z73" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="74" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A74" s="2"/>
       <c r="B74" s="3"/>
       <c r="C74" s="3"/>
@@ -9091,12 +9258,13 @@
       <c r="V74" s="3"/>
       <c r="W74" s="3"/>
       <c r="X74" s="3"/>
-      <c r="Y74" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="75" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y74" s="3"/>
+      <c r="Z74" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="75" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A75" s="2"/>
       <c r="B75" s="3"/>
       <c r="C75" s="3"/>
@@ -9121,12 +9289,13 @@
       <c r="V75" s="3"/>
       <c r="W75" s="3"/>
       <c r="X75" s="3"/>
-      <c r="Y75" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="76" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y75" s="3"/>
+      <c r="Z75" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="76" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A76" s="2"/>
       <c r="B76" s="3"/>
       <c r="C76" s="3"/>
@@ -9151,12 +9320,13 @@
       <c r="V76" s="3"/>
       <c r="W76" s="3"/>
       <c r="X76" s="3"/>
-      <c r="Y76" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="77" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y76" s="3"/>
+      <c r="Z76" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="77" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A77" s="2"/>
       <c r="B77" s="3"/>
       <c r="C77" s="3"/>
@@ -9181,12 +9351,13 @@
       <c r="V77" s="3"/>
       <c r="W77" s="3"/>
       <c r="X77" s="3"/>
-      <c r="Y77" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="78" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y77" s="3"/>
+      <c r="Z77" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="78" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A78" s="2"/>
       <c r="B78" s="3"/>
       <c r="C78" s="3"/>
@@ -9211,12 +9382,13 @@
       <c r="V78" s="3"/>
       <c r="W78" s="3"/>
       <c r="X78" s="3"/>
-      <c r="Y78" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="79" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y78" s="3"/>
+      <c r="Z78" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="79" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A79" s="2"/>
       <c r="B79" s="3"/>
       <c r="C79" s="3"/>
@@ -9241,12 +9413,13 @@
       <c r="V79" s="3"/>
       <c r="W79" s="3"/>
       <c r="X79" s="3"/>
-      <c r="Y79" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="80" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y79" s="3"/>
+      <c r="Z79" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="80" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A80" s="2"/>
       <c r="B80" s="3"/>
       <c r="C80" s="3"/>
@@ -9271,12 +9444,13 @@
       <c r="V80" s="3"/>
       <c r="W80" s="3"/>
       <c r="X80" s="3"/>
-      <c r="Y80" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="81" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y80" s="3"/>
+      <c r="Z80" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="81" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A81" s="2"/>
       <c r="B81" s="3"/>
       <c r="C81" s="3"/>
@@ -9301,12 +9475,13 @@
       <c r="V81" s="3"/>
       <c r="W81" s="3"/>
       <c r="X81" s="3"/>
-      <c r="Y81" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="82" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y81" s="3"/>
+      <c r="Z81" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="82" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A82" s="2"/>
       <c r="B82" s="3"/>
       <c r="C82" s="3"/>
@@ -9331,12 +9506,13 @@
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
-      <c r="Y82" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="83" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y82" s="3"/>
+      <c r="Z82" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="83" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A83" s="2"/>
       <c r="B83" s="3"/>
       <c r="C83" s="3"/>
@@ -9361,12 +9537,13 @@
       <c r="V83" s="3"/>
       <c r="W83" s="3"/>
       <c r="X83" s="3"/>
-      <c r="Y83" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="84" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y83" s="3"/>
+      <c r="Z83" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="84" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A84" s="2"/>
       <c r="B84" s="3"/>
       <c r="C84" s="3"/>
@@ -9391,12 +9568,13 @@
       <c r="V84" s="3"/>
       <c r="W84" s="3"/>
       <c r="X84" s="3"/>
-      <c r="Y84" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="85" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y84" s="3"/>
+      <c r="Z84" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="85" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A85" s="2"/>
       <c r="B85" s="3"/>
       <c r="C85" s="3"/>
@@ -9421,12 +9599,13 @@
       <c r="V85" s="3"/>
       <c r="W85" s="3"/>
       <c r="X85" s="3"/>
-      <c r="Y85" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="86" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y85" s="3"/>
+      <c r="Z85" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="86" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A86" s="2"/>
       <c r="B86" s="3"/>
       <c r="C86" s="3"/>
@@ -9451,12 +9630,13 @@
       <c r="V86" s="3"/>
       <c r="W86" s="3"/>
       <c r="X86" s="3"/>
-      <c r="Y86" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="87" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y86" s="3"/>
+      <c r="Z86" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="87" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A87" s="2"/>
       <c r="B87" s="3"/>
       <c r="C87" s="3"/>
@@ -9481,12 +9661,13 @@
       <c r="V87" s="3"/>
       <c r="W87" s="3"/>
       <c r="X87" s="3"/>
-      <c r="Y87" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="88" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y87" s="3"/>
+      <c r="Z87" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="88" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A88" s="2"/>
       <c r="B88" s="3"/>
       <c r="C88" s="3"/>
@@ -9511,12 +9692,13 @@
       <c r="V88" s="3"/>
       <c r="W88" s="3"/>
       <c r="X88" s="3"/>
-      <c r="Y88" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="89" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y88" s="3"/>
+      <c r="Z88" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="89" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A89" s="2"/>
       <c r="B89" s="3"/>
       <c r="C89" s="3"/>
@@ -9541,12 +9723,13 @@
       <c r="V89" s="3"/>
       <c r="W89" s="3"/>
       <c r="X89" s="3"/>
-      <c r="Y89" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="90" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y89" s="3"/>
+      <c r="Z89" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="90" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A90" s="2"/>
       <c r="B90" s="3"/>
       <c r="C90" s="3"/>
@@ -9571,12 +9754,13 @@
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
-      <c r="Y90" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="91" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y90" s="3"/>
+      <c r="Z90" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="91" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A91" s="2"/>
       <c r="B91" s="3"/>
       <c r="C91" s="3"/>
@@ -9601,12 +9785,13 @@
       <c r="V91" s="3"/>
       <c r="W91" s="3"/>
       <c r="X91" s="3"/>
-      <c r="Y91" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="92" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y91" s="3"/>
+      <c r="Z91" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="92" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A92" s="2"/>
       <c r="B92" s="3"/>
       <c r="C92" s="3"/>
@@ -9631,12 +9816,13 @@
       <c r="V92" s="3"/>
       <c r="W92" s="3"/>
       <c r="X92" s="3"/>
-      <c r="Y92" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="93" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y92" s="3"/>
+      <c r="Z92" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="93" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A93" s="2"/>
       <c r="B93" s="3"/>
       <c r="C93" s="3"/>
@@ -9661,12 +9847,13 @@
       <c r="V93" s="3"/>
       <c r="W93" s="3"/>
       <c r="X93" s="3"/>
-      <c r="Y93" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="94" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y93" s="3"/>
+      <c r="Z93" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="94" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A94" s="2"/>
       <c r="B94" s="3"/>
       <c r="C94" s="3"/>
@@ -9691,12 +9878,13 @@
       <c r="V94" s="3"/>
       <c r="W94" s="3"/>
       <c r="X94" s="3"/>
-      <c r="Y94" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="95" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y94" s="3"/>
+      <c r="Z94" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="95" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A95" s="2"/>
       <c r="B95" s="3"/>
       <c r="C95" s="3"/>
@@ -9721,12 +9909,13 @@
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
-      <c r="Y95" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="96" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y95" s="3"/>
+      <c r="Z95" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="96" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A96" s="2"/>
       <c r="B96" s="3"/>
       <c r="C96" s="3"/>
@@ -9751,12 +9940,13 @@
       <c r="V96" s="3"/>
       <c r="W96" s="3"/>
       <c r="X96" s="3"/>
-      <c r="Y96" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="97" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y96" s="3"/>
+      <c r="Z96" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="97" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A97" s="2"/>
       <c r="B97" s="3"/>
       <c r="C97" s="3"/>
@@ -9781,12 +9971,13 @@
       <c r="V97" s="3"/>
       <c r="W97" s="3"/>
       <c r="X97" s="3"/>
-      <c r="Y97" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="98" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y97" s="3"/>
+      <c r="Z97" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="98" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A98" s="2"/>
       <c r="B98" s="3"/>
       <c r="C98" s="3"/>
@@ -9811,12 +10002,13 @@
       <c r="V98" s="3"/>
       <c r="W98" s="3"/>
       <c r="X98" s="3"/>
-      <c r="Y98" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="99" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y98" s="3"/>
+      <c r="Z98" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="99" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A99" s="2"/>
       <c r="B99" s="3"/>
       <c r="C99" s="3"/>
@@ -9841,12 +10033,13 @@
       <c r="V99" s="3"/>
       <c r="W99" s="3"/>
       <c r="X99" s="3"/>
-      <c r="Y99" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="100" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y99" s="3"/>
+      <c r="Z99" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="100" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A100" s="2"/>
       <c r="B100" s="3"/>
       <c r="C100" s="3"/>
@@ -9871,12 +10064,13 @@
       <c r="V100" s="3"/>
       <c r="W100" s="3"/>
       <c r="X100" s="3"/>
-      <c r="Y100" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="101" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y100" s="3"/>
+      <c r="Z100" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="101" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A101" s="2"/>
       <c r="B101" s="3"/>
       <c r="C101" s="3"/>
@@ -9901,12 +10095,13 @@
       <c r="V101" s="3"/>
       <c r="W101" s="3"/>
       <c r="X101" s="3"/>
-      <c r="Y101" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="102" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y101" s="3"/>
+      <c r="Z101" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="102" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A102" s="2"/>
       <c r="B102" s="3"/>
       <c r="C102" s="3"/>
@@ -9931,12 +10126,13 @@
       <c r="V102" s="3"/>
       <c r="W102" s="3"/>
       <c r="X102" s="3"/>
-      <c r="Y102" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="103" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y102" s="3"/>
+      <c r="Z102" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="103" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A103" s="2"/>
       <c r="B103" s="3"/>
       <c r="C103" s="3"/>
@@ -9961,12 +10157,13 @@
       <c r="V103" s="3"/>
       <c r="W103" s="3"/>
       <c r="X103" s="3"/>
-      <c r="Y103" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="104" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y103" s="3"/>
+      <c r="Z103" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="104" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A104" s="2"/>
       <c r="B104" s="3"/>
       <c r="C104" s="3"/>
@@ -9991,12 +10188,13 @@
       <c r="V104" s="3"/>
       <c r="W104" s="3"/>
       <c r="X104" s="3"/>
-      <c r="Y104" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="105" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y104" s="3"/>
+      <c r="Z104" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="105" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A105" s="2"/>
       <c r="B105" s="3"/>
       <c r="C105" s="3"/>
@@ -10021,12 +10219,13 @@
       <c r="V105" s="3"/>
       <c r="W105" s="3"/>
       <c r="X105" s="3"/>
-      <c r="Y105" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="106" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y105" s="3"/>
+      <c r="Z105" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="106" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A106" s="2"/>
       <c r="B106" s="3"/>
       <c r="C106" s="3"/>
@@ -10051,12 +10250,13 @@
       <c r="V106" s="3"/>
       <c r="W106" s="3"/>
       <c r="X106" s="3"/>
-      <c r="Y106" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="107" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y106" s="3"/>
+      <c r="Z106" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="107" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A107" s="2"/>
       <c r="B107" s="3"/>
       <c r="C107" s="3"/>
@@ -10081,12 +10281,13 @@
       <c r="V107" s="3"/>
       <c r="W107" s="3"/>
       <c r="X107" s="3"/>
-      <c r="Y107" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="108" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y107" s="3"/>
+      <c r="Z107" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="108" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A108" s="2"/>
       <c r="B108" s="3"/>
       <c r="C108" s="3"/>
@@ -10111,12 +10312,13 @@
       <c r="V108" s="3"/>
       <c r="W108" s="3"/>
       <c r="X108" s="3"/>
-      <c r="Y108" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="109" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y108" s="3"/>
+      <c r="Z108" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="109" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A109" s="2"/>
       <c r="B109" s="3"/>
       <c r="C109" s="3"/>
@@ -10141,12 +10343,13 @@
       <c r="V109" s="3"/>
       <c r="W109" s="3"/>
       <c r="X109" s="3"/>
-      <c r="Y109" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="110" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y109" s="3"/>
+      <c r="Z109" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="110" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A110" s="2"/>
       <c r="B110" s="3"/>
       <c r="C110" s="3"/>
@@ -10171,12 +10374,13 @@
       <c r="V110" s="3"/>
       <c r="W110" s="3"/>
       <c r="X110" s="3"/>
-      <c r="Y110" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="111" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y110" s="3"/>
+      <c r="Z110" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="111" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A111" s="2"/>
       <c r="B111" s="3"/>
       <c r="C111" s="3"/>
@@ -10201,12 +10405,13 @@
       <c r="V111" s="3"/>
       <c r="W111" s="3"/>
       <c r="X111" s="3"/>
-      <c r="Y111" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="112" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y111" s="3"/>
+      <c r="Z111" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="112" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A112" s="2"/>
       <c r="B112" s="3"/>
       <c r="C112" s="3"/>
@@ -10231,12 +10436,13 @@
       <c r="V112" s="3"/>
       <c r="W112" s="3"/>
       <c r="X112" s="3"/>
-      <c r="Y112" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="113" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y112" s="3"/>
+      <c r="Z112" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="113" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A113" s="2"/>
       <c r="B113" s="3"/>
       <c r="C113" s="3"/>
@@ -10261,12 +10467,13 @@
       <c r="V113" s="3"/>
       <c r="W113" s="3"/>
       <c r="X113" s="3"/>
-      <c r="Y113" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="114" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y113" s="3"/>
+      <c r="Z113" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="114" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A114" s="2"/>
       <c r="B114" s="3"/>
       <c r="C114" s="3"/>
@@ -10291,12 +10498,13 @@
       <c r="V114" s="3"/>
       <c r="W114" s="3"/>
       <c r="X114" s="3"/>
-      <c r="Y114" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="115" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y114" s="3"/>
+      <c r="Z114" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="115" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A115" s="2"/>
       <c r="B115" s="3"/>
       <c r="C115" s="3"/>
@@ -10321,12 +10529,13 @@
       <c r="V115" s="3"/>
       <c r="W115" s="3"/>
       <c r="X115" s="3"/>
-      <c r="Y115" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="116" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y115" s="3"/>
+      <c r="Z115" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="116" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A116" s="2"/>
       <c r="B116" s="3"/>
       <c r="C116" s="3"/>
@@ -10351,12 +10560,13 @@
       <c r="V116" s="3"/>
       <c r="W116" s="3"/>
       <c r="X116" s="3"/>
-      <c r="Y116" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="117" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y116" s="3"/>
+      <c r="Z116" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="117" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A117" s="2"/>
       <c r="B117" s="3"/>
       <c r="C117" s="3"/>
@@ -10381,12 +10591,13 @@
       <c r="V117" s="3"/>
       <c r="W117" s="3"/>
       <c r="X117" s="3"/>
-      <c r="Y117" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="118" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y117" s="3"/>
+      <c r="Z117" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="118" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A118" s="2"/>
       <c r="B118" s="3"/>
       <c r="C118" s="3"/>
@@ -10411,12 +10622,13 @@
       <c r="V118" s="3"/>
       <c r="W118" s="3"/>
       <c r="X118" s="3"/>
-      <c r="Y118" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="119" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y118" s="3"/>
+      <c r="Z118" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="119" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A119" s="2"/>
       <c r="B119" s="3"/>
       <c r="C119" s="3"/>
@@ -10441,12 +10653,13 @@
       <c r="V119" s="3"/>
       <c r="W119" s="3"/>
       <c r="X119" s="3"/>
-      <c r="Y119" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="120" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y119" s="3"/>
+      <c r="Z119" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="120" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A120" s="2"/>
       <c r="B120" s="3"/>
       <c r="C120" s="3"/>
@@ -10471,12 +10684,13 @@
       <c r="V120" s="3"/>
       <c r="W120" s="3"/>
       <c r="X120" s="3"/>
-      <c r="Y120" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="121" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y120" s="3"/>
+      <c r="Z120" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="121" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A121" s="2"/>
       <c r="B121" s="3"/>
       <c r="C121" s="3"/>
@@ -10501,12 +10715,13 @@
       <c r="V121" s="3"/>
       <c r="W121" s="3"/>
       <c r="X121" s="3"/>
-      <c r="Y121" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="122" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y121" s="3"/>
+      <c r="Z121" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="122" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A122" s="2"/>
       <c r="B122" s="3"/>
       <c r="C122" s="3"/>
@@ -10531,12 +10746,13 @@
       <c r="V122" s="3"/>
       <c r="W122" s="3"/>
       <c r="X122" s="3"/>
-      <c r="Y122" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="123" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y122" s="3"/>
+      <c r="Z122" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="123" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A123" s="2"/>
       <c r="B123" s="3"/>
       <c r="C123" s="3"/>
@@ -10561,12 +10777,13 @@
       <c r="V123" s="3"/>
       <c r="W123" s="3"/>
       <c r="X123" s="3"/>
-      <c r="Y123" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="124" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y123" s="3"/>
+      <c r="Z123" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="124" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A124" s="2"/>
       <c r="B124" s="3"/>
       <c r="C124" s="3"/>
@@ -10591,12 +10808,13 @@
       <c r="V124" s="3"/>
       <c r="W124" s="3"/>
       <c r="X124" s="3"/>
-      <c r="Y124" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="125" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y124" s="3"/>
+      <c r="Z124" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="125" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A125" s="2"/>
       <c r="B125" s="3"/>
       <c r="C125" s="3"/>
@@ -10621,12 +10839,13 @@
       <c r="V125" s="3"/>
       <c r="W125" s="3"/>
       <c r="X125" s="3"/>
-      <c r="Y125" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="126" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y125" s="3"/>
+      <c r="Z125" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="126" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A126" s="2"/>
       <c r="B126" s="3"/>
       <c r="C126" s="3"/>
@@ -10651,12 +10870,13 @@
       <c r="V126" s="3"/>
       <c r="W126" s="3"/>
       <c r="X126" s="3"/>
-      <c r="Y126" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="127" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y126" s="3"/>
+      <c r="Z126" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="127" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A127" s="2"/>
       <c r="B127" s="3"/>
       <c r="C127" s="3"/>
@@ -10681,12 +10901,13 @@
       <c r="V127" s="3"/>
       <c r="W127" s="3"/>
       <c r="X127" s="3"/>
-      <c r="Y127" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="128" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y127" s="3"/>
+      <c r="Z127" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="128" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A128" s="2"/>
       <c r="B128" s="3"/>
       <c r="C128" s="3"/>
@@ -10711,12 +10932,13 @@
       <c r="V128" s="3"/>
       <c r="W128" s="3"/>
       <c r="X128" s="3"/>
-      <c r="Y128" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="129" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y128" s="3"/>
+      <c r="Z128" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="129" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A129" s="2"/>
       <c r="B129" s="3"/>
       <c r="C129" s="3"/>
@@ -10741,12 +10963,13 @@
       <c r="V129" s="3"/>
       <c r="W129" s="3"/>
       <c r="X129" s="3"/>
-      <c r="Y129" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="130" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y129" s="3"/>
+      <c r="Z129" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="130" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A130" s="2"/>
       <c r="B130" s="3"/>
       <c r="C130" s="3"/>
@@ -10771,12 +10994,13 @@
       <c r="V130" s="3"/>
       <c r="W130" s="3"/>
       <c r="X130" s="3"/>
-      <c r="Y130" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="131" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y130" s="3"/>
+      <c r="Z130" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="131" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A131" s="2"/>
       <c r="B131" s="3"/>
       <c r="C131" s="3"/>
@@ -10801,12 +11025,13 @@
       <c r="V131" s="3"/>
       <c r="W131" s="3"/>
       <c r="X131" s="3"/>
-      <c r="Y131" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="132" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y131" s="3"/>
+      <c r="Z131" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="132" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A132" s="2"/>
       <c r="B132" s="3"/>
       <c r="C132" s="3"/>
@@ -10831,12 +11056,13 @@
       <c r="V132" s="3"/>
       <c r="W132" s="3"/>
       <c r="X132" s="3"/>
-      <c r="Y132" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="133" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y132" s="3"/>
+      <c r="Z132" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="133" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A133" s="2"/>
       <c r="B133" s="3"/>
       <c r="C133" s="3"/>
@@ -10861,12 +11087,13 @@
       <c r="V133" s="3"/>
       <c r="W133" s="3"/>
       <c r="X133" s="3"/>
-      <c r="Y133" s="4" t="str">
-        <f t="shared" ref="Y133:Y196" si="2">IF(COUNTA(B133:X133)=0,"",AVERAGE(B133:X133))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="134" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y133" s="3"/>
+      <c r="Z133" s="4" t="str">
+        <f t="shared" ref="Z133:Z196" si="3">IF(COUNTA(B133:Y133)=0,"",AVERAGE(B133:Y133))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="134" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A134" s="2"/>
       <c r="B134" s="3"/>
       <c r="C134" s="3"/>
@@ -10891,12 +11118,13 @@
       <c r="V134" s="3"/>
       <c r="W134" s="3"/>
       <c r="X134" s="3"/>
-      <c r="Y134" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="135" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y134" s="3"/>
+      <c r="Z134" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="135" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A135" s="2"/>
       <c r="B135" s="3"/>
       <c r="C135" s="3"/>
@@ -10921,12 +11149,13 @@
       <c r="V135" s="3"/>
       <c r="W135" s="3"/>
       <c r="X135" s="3"/>
-      <c r="Y135" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="136" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y135" s="3"/>
+      <c r="Z135" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="136" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A136" s="2"/>
       <c r="B136" s="3"/>
       <c r="C136" s="3"/>
@@ -10951,12 +11180,13 @@
       <c r="V136" s="3"/>
       <c r="W136" s="3"/>
       <c r="X136" s="3"/>
-      <c r="Y136" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="137" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y136" s="3"/>
+      <c r="Z136" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="137" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A137" s="2"/>
       <c r="B137" s="3"/>
       <c r="C137" s="3"/>
@@ -10981,12 +11211,13 @@
       <c r="V137" s="3"/>
       <c r="W137" s="3"/>
       <c r="X137" s="3"/>
-      <c r="Y137" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="138" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y137" s="3"/>
+      <c r="Z137" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="138" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A138" s="2"/>
       <c r="B138" s="3"/>
       <c r="C138" s="3"/>
@@ -11011,12 +11242,13 @@
       <c r="V138" s="3"/>
       <c r="W138" s="3"/>
       <c r="X138" s="3"/>
-      <c r="Y138" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="139" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y138" s="3"/>
+      <c r="Z138" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="139" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A139" s="2"/>
       <c r="B139" s="3"/>
       <c r="C139" s="3"/>
@@ -11041,12 +11273,13 @@
       <c r="V139" s="3"/>
       <c r="W139" s="3"/>
       <c r="X139" s="3"/>
-      <c r="Y139" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="140" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y139" s="3"/>
+      <c r="Z139" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="140" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A140" s="2"/>
       <c r="B140" s="3"/>
       <c r="C140" s="3"/>
@@ -11071,12 +11304,13 @@
       <c r="V140" s="3"/>
       <c r="W140" s="3"/>
       <c r="X140" s="3"/>
-      <c r="Y140" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="141" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y140" s="3"/>
+      <c r="Z140" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="141" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A141" s="2"/>
       <c r="B141" s="3"/>
       <c r="C141" s="3"/>
@@ -11101,12 +11335,13 @@
       <c r="V141" s="3"/>
       <c r="W141" s="3"/>
       <c r="X141" s="3"/>
-      <c r="Y141" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="142" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y141" s="3"/>
+      <c r="Z141" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="142" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A142" s="2"/>
       <c r="B142" s="3"/>
       <c r="C142" s="3"/>
@@ -11131,12 +11366,13 @@
       <c r="V142" s="3"/>
       <c r="W142" s="3"/>
       <c r="X142" s="3"/>
-      <c r="Y142" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="143" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y142" s="3"/>
+      <c r="Z142" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="143" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A143" s="2"/>
       <c r="B143" s="3"/>
       <c r="C143" s="3"/>
@@ -11161,12 +11397,13 @@
       <c r="V143" s="3"/>
       <c r="W143" s="3"/>
       <c r="X143" s="3"/>
-      <c r="Y143" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="144" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y143" s="3"/>
+      <c r="Z143" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="144" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A144" s="2"/>
       <c r="B144" s="3"/>
       <c r="C144" s="3"/>
@@ -11191,12 +11428,13 @@
       <c r="V144" s="3"/>
       <c r="W144" s="3"/>
       <c r="X144" s="3"/>
-      <c r="Y144" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="145" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y144" s="3"/>
+      <c r="Z144" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="145" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A145" s="2"/>
       <c r="B145" s="3"/>
       <c r="C145" s="3"/>
@@ -11221,12 +11459,13 @@
       <c r="V145" s="3"/>
       <c r="W145" s="3"/>
       <c r="X145" s="3"/>
-      <c r="Y145" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="146" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y145" s="3"/>
+      <c r="Z145" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="146" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A146" s="2"/>
       <c r="B146" s="3"/>
       <c r="C146" s="3"/>
@@ -11251,12 +11490,13 @@
       <c r="V146" s="3"/>
       <c r="W146" s="3"/>
       <c r="X146" s="3"/>
-      <c r="Y146" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="147" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y146" s="3"/>
+      <c r="Z146" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="147" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A147" s="2"/>
       <c r="B147" s="3"/>
       <c r="C147" s="3"/>
@@ -11281,12 +11521,13 @@
       <c r="V147" s="3"/>
       <c r="W147" s="3"/>
       <c r="X147" s="3"/>
-      <c r="Y147" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="148" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y147" s="3"/>
+      <c r="Z147" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="148" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A148" s="2"/>
       <c r="B148" s="3"/>
       <c r="C148" s="3"/>
@@ -11311,12 +11552,13 @@
       <c r="V148" s="3"/>
       <c r="W148" s="3"/>
       <c r="X148" s="3"/>
-      <c r="Y148" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="149" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y148" s="3"/>
+      <c r="Z148" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="149" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A149" s="2"/>
       <c r="B149" s="3"/>
       <c r="C149" s="3"/>
@@ -11341,12 +11583,13 @@
       <c r="V149" s="3"/>
       <c r="W149" s="3"/>
       <c r="X149" s="3"/>
-      <c r="Y149" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="150" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y149" s="3"/>
+      <c r="Z149" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="150" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A150" s="2"/>
       <c r="B150" s="3"/>
       <c r="C150" s="3"/>
@@ -11371,12 +11614,13 @@
       <c r="V150" s="3"/>
       <c r="W150" s="3"/>
       <c r="X150" s="3"/>
-      <c r="Y150" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="151" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y150" s="3"/>
+      <c r="Z150" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="151" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A151" s="2"/>
       <c r="B151" s="3"/>
       <c r="C151" s="3"/>
@@ -11401,12 +11645,13 @@
       <c r="V151" s="3"/>
       <c r="W151" s="3"/>
       <c r="X151" s="3"/>
-      <c r="Y151" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="152" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y151" s="3"/>
+      <c r="Z151" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="152" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A152" s="2"/>
       <c r="B152" s="3"/>
       <c r="C152" s="3"/>
@@ -11431,12 +11676,13 @@
       <c r="V152" s="3"/>
       <c r="W152" s="3"/>
       <c r="X152" s="3"/>
-      <c r="Y152" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="153" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y152" s="3"/>
+      <c r="Z152" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="153" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A153" s="2"/>
       <c r="B153" s="3"/>
       <c r="C153" s="3"/>
@@ -11461,12 +11707,13 @@
       <c r="V153" s="3"/>
       <c r="W153" s="3"/>
       <c r="X153" s="3"/>
-      <c r="Y153" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="154" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y153" s="3"/>
+      <c r="Z153" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="154" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A154" s="2"/>
       <c r="B154" s="3"/>
       <c r="C154" s="3"/>
@@ -11491,12 +11738,13 @@
       <c r="V154" s="3"/>
       <c r="W154" s="3"/>
       <c r="X154" s="3"/>
-      <c r="Y154" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="155" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y154" s="3"/>
+      <c r="Z154" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="155" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A155" s="2"/>
       <c r="B155" s="3"/>
       <c r="C155" s="3"/>
@@ -11521,12 +11769,13 @@
       <c r="V155" s="3"/>
       <c r="W155" s="3"/>
       <c r="X155" s="3"/>
-      <c r="Y155" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="156" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y155" s="3"/>
+      <c r="Z155" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="156" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A156" s="2"/>
       <c r="B156" s="3"/>
       <c r="C156" s="3"/>
@@ -11551,12 +11800,13 @@
       <c r="V156" s="3"/>
       <c r="W156" s="3"/>
       <c r="X156" s="3"/>
-      <c r="Y156" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="157" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y156" s="3"/>
+      <c r="Z156" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="157" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A157" s="2"/>
       <c r="B157" s="3"/>
       <c r="C157" s="3"/>
@@ -11581,12 +11831,13 @@
       <c r="V157" s="3"/>
       <c r="W157" s="3"/>
       <c r="X157" s="3"/>
-      <c r="Y157" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="158" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y157" s="3"/>
+      <c r="Z157" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="158" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A158" s="2"/>
       <c r="B158" s="3"/>
       <c r="C158" s="3"/>
@@ -11611,12 +11862,13 @@
       <c r="V158" s="3"/>
       <c r="W158" s="3"/>
       <c r="X158" s="3"/>
-      <c r="Y158" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="159" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y158" s="3"/>
+      <c r="Z158" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="159" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A159" s="2"/>
       <c r="B159" s="3"/>
       <c r="C159" s="3"/>
@@ -11641,12 +11893,13 @@
       <c r="V159" s="3"/>
       <c r="W159" s="3"/>
       <c r="X159" s="3"/>
-      <c r="Y159" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="160" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y159" s="3"/>
+      <c r="Z159" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="160" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A160" s="2"/>
       <c r="B160" s="3"/>
       <c r="C160" s="3"/>
@@ -11671,12 +11924,13 @@
       <c r="V160" s="3"/>
       <c r="W160" s="3"/>
       <c r="X160" s="3"/>
-      <c r="Y160" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="161" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y160" s="3"/>
+      <c r="Z160" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="161" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A161" s="2"/>
       <c r="B161" s="3"/>
       <c r="C161" s="3"/>
@@ -11701,12 +11955,13 @@
       <c r="V161" s="3"/>
       <c r="W161" s="3"/>
       <c r="X161" s="3"/>
-      <c r="Y161" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="162" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y161" s="3"/>
+      <c r="Z161" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="162" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A162" s="2"/>
       <c r="B162" s="3"/>
       <c r="C162" s="3"/>
@@ -11731,12 +11986,13 @@
       <c r="V162" s="3"/>
       <c r="W162" s="3"/>
       <c r="X162" s="3"/>
-      <c r="Y162" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="163" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y162" s="3"/>
+      <c r="Z162" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="163" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A163" s="2"/>
       <c r="B163" s="3"/>
       <c r="C163" s="3"/>
@@ -11761,12 +12017,13 @@
       <c r="V163" s="3"/>
       <c r="W163" s="3"/>
       <c r="X163" s="3"/>
-      <c r="Y163" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="164" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y163" s="3"/>
+      <c r="Z163" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="164" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A164" s="2"/>
       <c r="B164" s="3"/>
       <c r="C164" s="3"/>
@@ -11791,12 +12048,13 @@
       <c r="V164" s="3"/>
       <c r="W164" s="3"/>
       <c r="X164" s="3"/>
-      <c r="Y164" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="165" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y164" s="3"/>
+      <c r="Z164" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="165" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A165" s="2"/>
       <c r="B165" s="3"/>
       <c r="C165" s="3"/>
@@ -11821,12 +12079,13 @@
       <c r="V165" s="3"/>
       <c r="W165" s="3"/>
       <c r="X165" s="3"/>
-      <c r="Y165" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="166" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y165" s="3"/>
+      <c r="Z165" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="166" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A166" s="2"/>
       <c r="B166" s="3"/>
       <c r="C166" s="3"/>
@@ -11851,12 +12110,13 @@
       <c r="V166" s="3"/>
       <c r="W166" s="3"/>
       <c r="X166" s="3"/>
-      <c r="Y166" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="167" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y166" s="3"/>
+      <c r="Z166" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="167" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A167" s="2"/>
       <c r="B167" s="3"/>
       <c r="C167" s="3"/>
@@ -11881,12 +12141,13 @@
       <c r="V167" s="3"/>
       <c r="W167" s="3"/>
       <c r="X167" s="3"/>
-      <c r="Y167" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="168" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y167" s="3"/>
+      <c r="Z167" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="168" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A168" s="2"/>
       <c r="B168" s="3"/>
       <c r="C168" s="3"/>
@@ -11911,12 +12172,13 @@
       <c r="V168" s="3"/>
       <c r="W168" s="3"/>
       <c r="X168" s="3"/>
-      <c r="Y168" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="169" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y168" s="3"/>
+      <c r="Z168" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="169" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A169" s="2"/>
       <c r="B169" s="3"/>
       <c r="C169" s="3"/>
@@ -11941,12 +12203,13 @@
       <c r="V169" s="3"/>
       <c r="W169" s="3"/>
       <c r="X169" s="3"/>
-      <c r="Y169" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="170" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y169" s="3"/>
+      <c r="Z169" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="170" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A170" s="2"/>
       <c r="B170" s="3"/>
       <c r="C170" s="3"/>
@@ -11971,12 +12234,13 @@
       <c r="V170" s="3"/>
       <c r="W170" s="3"/>
       <c r="X170" s="3"/>
-      <c r="Y170" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="171" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y170" s="3"/>
+      <c r="Z170" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="171" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A171" s="2"/>
       <c r="B171" s="3"/>
       <c r="C171" s="3"/>
@@ -12001,12 +12265,13 @@
       <c r="V171" s="3"/>
       <c r="W171" s="3"/>
       <c r="X171" s="3"/>
-      <c r="Y171" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="172" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y171" s="3"/>
+      <c r="Z171" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="172" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A172" s="2"/>
       <c r="B172" s="3"/>
       <c r="C172" s="3"/>
@@ -12031,12 +12296,13 @@
       <c r="V172" s="3"/>
       <c r="W172" s="3"/>
       <c r="X172" s="3"/>
-      <c r="Y172" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="173" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y172" s="3"/>
+      <c r="Z172" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="173" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A173" s="2"/>
       <c r="B173" s="3"/>
       <c r="C173" s="3"/>
@@ -12061,12 +12327,13 @@
       <c r="V173" s="3"/>
       <c r="W173" s="3"/>
       <c r="X173" s="3"/>
-      <c r="Y173" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="174" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y173" s="3"/>
+      <c r="Z173" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="174" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A174" s="2"/>
       <c r="B174" s="3"/>
       <c r="C174" s="3"/>
@@ -12091,12 +12358,13 @@
       <c r="V174" s="3"/>
       <c r="W174" s="3"/>
       <c r="X174" s="3"/>
-      <c r="Y174" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="175" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y174" s="3"/>
+      <c r="Z174" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="175" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A175" s="2"/>
       <c r="B175" s="3"/>
       <c r="C175" s="3"/>
@@ -12121,12 +12389,13 @@
       <c r="V175" s="3"/>
       <c r="W175" s="3"/>
       <c r="X175" s="3"/>
-      <c r="Y175" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="176" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y175" s="3"/>
+      <c r="Z175" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="176" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A176" s="2"/>
       <c r="B176" s="3"/>
       <c r="C176" s="3"/>
@@ -12151,12 +12420,13 @@
       <c r="V176" s="3"/>
       <c r="W176" s="3"/>
       <c r="X176" s="3"/>
-      <c r="Y176" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="177" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y176" s="3"/>
+      <c r="Z176" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="177" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A177" s="2"/>
       <c r="B177" s="3"/>
       <c r="C177" s="3"/>
@@ -12181,12 +12451,13 @@
       <c r="V177" s="3"/>
       <c r="W177" s="3"/>
       <c r="X177" s="3"/>
-      <c r="Y177" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="178" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y177" s="3"/>
+      <c r="Z177" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="178" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A178" s="2"/>
       <c r="B178" s="3"/>
       <c r="C178" s="3"/>
@@ -12211,12 +12482,13 @@
       <c r="V178" s="3"/>
       <c r="W178" s="3"/>
       <c r="X178" s="3"/>
-      <c r="Y178" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="179" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y178" s="3"/>
+      <c r="Z178" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="179" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A179" s="2"/>
       <c r="B179" s="3"/>
       <c r="C179" s="3"/>
@@ -12241,12 +12513,13 @@
       <c r="V179" s="3"/>
       <c r="W179" s="3"/>
       <c r="X179" s="3"/>
-      <c r="Y179" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="180" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y179" s="3"/>
+      <c r="Z179" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="180" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A180" s="2"/>
       <c r="B180" s="3"/>
       <c r="C180" s="3"/>
@@ -12271,12 +12544,13 @@
       <c r="V180" s="3"/>
       <c r="W180" s="3"/>
       <c r="X180" s="3"/>
-      <c r="Y180" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="181" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y180" s="3"/>
+      <c r="Z180" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="181" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A181" s="2"/>
       <c r="B181" s="3"/>
       <c r="C181" s="3"/>
@@ -12301,12 +12575,13 @@
       <c r="V181" s="3"/>
       <c r="W181" s="3"/>
       <c r="X181" s="3"/>
-      <c r="Y181" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="182" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y181" s="3"/>
+      <c r="Z181" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="182" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A182" s="2"/>
       <c r="B182" s="3"/>
       <c r="C182" s="3"/>
@@ -12331,12 +12606,13 @@
       <c r="V182" s="3"/>
       <c r="W182" s="3"/>
       <c r="X182" s="3"/>
-      <c r="Y182" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="183" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y182" s="3"/>
+      <c r="Z182" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="183" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A183" s="2"/>
       <c r="B183" s="3"/>
       <c r="C183" s="3"/>
@@ -12361,12 +12637,13 @@
       <c r="V183" s="3"/>
       <c r="W183" s="3"/>
       <c r="X183" s="3"/>
-      <c r="Y183" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="184" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y183" s="3"/>
+      <c r="Z183" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="184" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A184" s="2"/>
       <c r="B184" s="3"/>
       <c r="C184" s="3"/>
@@ -12391,12 +12668,13 @@
       <c r="V184" s="3"/>
       <c r="W184" s="3"/>
       <c r="X184" s="3"/>
-      <c r="Y184" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="185" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y184" s="3"/>
+      <c r="Z184" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="185" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A185" s="2"/>
       <c r="B185" s="3"/>
       <c r="C185" s="3"/>
@@ -12421,12 +12699,13 @@
       <c r="V185" s="3"/>
       <c r="W185" s="3"/>
       <c r="X185" s="3"/>
-      <c r="Y185" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="186" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y185" s="3"/>
+      <c r="Z185" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="186" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A186" s="2"/>
       <c r="B186" s="3"/>
       <c r="C186" s="3"/>
@@ -12451,12 +12730,13 @@
       <c r="V186" s="3"/>
       <c r="W186" s="3"/>
       <c r="X186" s="3"/>
-      <c r="Y186" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="187" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y186" s="3"/>
+      <c r="Z186" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="187" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A187" s="2"/>
       <c r="B187" s="3"/>
       <c r="C187" s="3"/>
@@ -12481,12 +12761,13 @@
       <c r="V187" s="3"/>
       <c r="W187" s="3"/>
       <c r="X187" s="3"/>
-      <c r="Y187" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="188" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y187" s="3"/>
+      <c r="Z187" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="188" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A188" s="2"/>
       <c r="B188" s="3"/>
       <c r="C188" s="3"/>
@@ -12511,12 +12792,13 @@
       <c r="V188" s="3"/>
       <c r="W188" s="3"/>
       <c r="X188" s="3"/>
-      <c r="Y188" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="189" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y188" s="3"/>
+      <c r="Z188" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="189" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A189" s="2"/>
       <c r="B189" s="3"/>
       <c r="C189" s="3"/>
@@ -12541,12 +12823,13 @@
       <c r="V189" s="3"/>
       <c r="W189" s="3"/>
       <c r="X189" s="3"/>
-      <c r="Y189" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="190" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y189" s="3"/>
+      <c r="Z189" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="190" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A190" s="2"/>
       <c r="B190" s="3"/>
       <c r="C190" s="3"/>
@@ -12571,12 +12854,13 @@
       <c r="V190" s="3"/>
       <c r="W190" s="3"/>
       <c r="X190" s="3"/>
-      <c r="Y190" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="191" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y190" s="3"/>
+      <c r="Z190" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="191" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A191" s="2"/>
       <c r="B191" s="3"/>
       <c r="C191" s="3"/>
@@ -12601,12 +12885,13 @@
       <c r="V191" s="3"/>
       <c r="W191" s="3"/>
       <c r="X191" s="3"/>
-      <c r="Y191" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="192" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y191" s="3"/>
+      <c r="Z191" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="192" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A192" s="2"/>
       <c r="B192" s="3"/>
       <c r="C192" s="3"/>
@@ -12631,12 +12916,13 @@
       <c r="V192" s="3"/>
       <c r="W192" s="3"/>
       <c r="X192" s="3"/>
-      <c r="Y192" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="193" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y192" s="3"/>
+      <c r="Z192" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="193" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A193" s="2"/>
       <c r="B193" s="3"/>
       <c r="C193" s="3"/>
@@ -12661,12 +12947,13 @@
       <c r="V193" s="3"/>
       <c r="W193" s="3"/>
       <c r="X193" s="3"/>
-      <c r="Y193" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="194" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y193" s="3"/>
+      <c r="Z193" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="194" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A194" s="2"/>
       <c r="B194" s="3"/>
       <c r="C194" s="3"/>
@@ -12691,12 +12978,13 @@
       <c r="V194" s="3"/>
       <c r="W194" s="3"/>
       <c r="X194" s="3"/>
-      <c r="Y194" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="195" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y194" s="3"/>
+      <c r="Z194" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="195" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A195" s="2"/>
       <c r="B195" s="3"/>
       <c r="C195" s="3"/>
@@ -12721,12 +13009,13 @@
       <c r="V195" s="3"/>
       <c r="W195" s="3"/>
       <c r="X195" s="3"/>
-      <c r="Y195" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="196" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y195" s="3"/>
+      <c r="Z195" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="196" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A196" s="2"/>
       <c r="B196" s="3"/>
       <c r="C196" s="3"/>
@@ -12751,12 +13040,13 @@
       <c r="V196" s="3"/>
       <c r="W196" s="3"/>
       <c r="X196" s="3"/>
-      <c r="Y196" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="197" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y196" s="3"/>
+      <c r="Z196" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="197" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A197" s="2"/>
       <c r="B197" s="3"/>
       <c r="C197" s="3"/>
@@ -12781,12 +13071,13 @@
       <c r="V197" s="3"/>
       <c r="W197" s="3"/>
       <c r="X197" s="3"/>
-      <c r="Y197" s="4" t="str">
-        <f t="shared" ref="Y197:Y260" si="3">IF(COUNTA(B197:X197)=0,"",AVERAGE(B197:X197))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="198" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y197" s="3"/>
+      <c r="Z197" s="4" t="str">
+        <f t="shared" ref="Z197:Z260" si="4">IF(COUNTA(B197:Y197)=0,"",AVERAGE(B197:Y197))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="198" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A198" s="2"/>
       <c r="B198" s="3"/>
       <c r="C198" s="3"/>
@@ -12811,12 +13102,13 @@
       <c r="V198" s="3"/>
       <c r="W198" s="3"/>
       <c r="X198" s="3"/>
-      <c r="Y198" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="199" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y198" s="3"/>
+      <c r="Z198" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="199" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A199" s="2"/>
       <c r="B199" s="3"/>
       <c r="C199" s="3"/>
@@ -12841,12 +13133,13 @@
       <c r="V199" s="3"/>
       <c r="W199" s="3"/>
       <c r="X199" s="3"/>
-      <c r="Y199" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="200" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y199" s="3"/>
+      <c r="Z199" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="200" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A200" s="2"/>
       <c r="B200" s="3"/>
       <c r="C200" s="3"/>
@@ -12871,12 +13164,13 @@
       <c r="V200" s="3"/>
       <c r="W200" s="3"/>
       <c r="X200" s="3"/>
-      <c r="Y200" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="201" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y200" s="3"/>
+      <c r="Z200" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="201" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A201" s="2"/>
       <c r="B201" s="3"/>
       <c r="C201" s="3"/>
@@ -12901,12 +13195,13 @@
       <c r="V201" s="3"/>
       <c r="W201" s="3"/>
       <c r="X201" s="3"/>
-      <c r="Y201" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="202" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y201" s="3"/>
+      <c r="Z201" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="202" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A202" s="2"/>
       <c r="B202" s="3"/>
       <c r="C202" s="3"/>
@@ -12931,12 +13226,13 @@
       <c r="V202" s="3"/>
       <c r="W202" s="3"/>
       <c r="X202" s="3"/>
-      <c r="Y202" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="203" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y202" s="3"/>
+      <c r="Z202" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="203" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A203" s="2"/>
       <c r="B203" s="3"/>
       <c r="C203" s="3"/>
@@ -12961,12 +13257,13 @@
       <c r="V203" s="3"/>
       <c r="W203" s="3"/>
       <c r="X203" s="3"/>
-      <c r="Y203" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="204" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y203" s="3"/>
+      <c r="Z203" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="204" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A204" s="2"/>
       <c r="B204" s="3"/>
       <c r="C204" s="3"/>
@@ -12991,12 +13288,13 @@
       <c r="V204" s="3"/>
       <c r="W204" s="3"/>
       <c r="X204" s="3"/>
-      <c r="Y204" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="205" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y204" s="3"/>
+      <c r="Z204" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="205" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A205" s="2"/>
       <c r="B205" s="3"/>
       <c r="C205" s="3"/>
@@ -13021,12 +13319,13 @@
       <c r="V205" s="3"/>
       <c r="W205" s="3"/>
       <c r="X205" s="3"/>
-      <c r="Y205" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="206" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y205" s="3"/>
+      <c r="Z205" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="206" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A206" s="2"/>
       <c r="B206" s="3"/>
       <c r="C206" s="3"/>
@@ -13051,12 +13350,13 @@
       <c r="V206" s="3"/>
       <c r="W206" s="3"/>
       <c r="X206" s="3"/>
-      <c r="Y206" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="207" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y206" s="3"/>
+      <c r="Z206" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="207" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A207" s="2"/>
       <c r="B207" s="3"/>
       <c r="C207" s="3"/>
@@ -13081,12 +13381,13 @@
       <c r="V207" s="3"/>
       <c r="W207" s="3"/>
       <c r="X207" s="3"/>
-      <c r="Y207" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="208" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y207" s="3"/>
+      <c r="Z207" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="208" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A208" s="2"/>
       <c r="B208" s="3"/>
       <c r="C208" s="3"/>
@@ -13111,12 +13412,13 @@
       <c r="V208" s="3"/>
       <c r="W208" s="3"/>
       <c r="X208" s="3"/>
-      <c r="Y208" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="209" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y208" s="3"/>
+      <c r="Z208" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="209" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A209" s="2"/>
       <c r="B209" s="3"/>
       <c r="C209" s="3"/>
@@ -13141,12 +13443,13 @@
       <c r="V209" s="3"/>
       <c r="W209" s="3"/>
       <c r="X209" s="3"/>
-      <c r="Y209" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="210" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y209" s="3"/>
+      <c r="Z209" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="210" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A210" s="2"/>
       <c r="B210" s="3"/>
       <c r="C210" s="3"/>
@@ -13171,12 +13474,13 @@
       <c r="V210" s="3"/>
       <c r="W210" s="3"/>
       <c r="X210" s="3"/>
-      <c r="Y210" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="211" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y210" s="3"/>
+      <c r="Z210" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="211" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A211" s="2"/>
       <c r="B211" s="3"/>
       <c r="C211" s="3"/>
@@ -13201,12 +13505,13 @@
       <c r="V211" s="3"/>
       <c r="W211" s="3"/>
       <c r="X211" s="3"/>
-      <c r="Y211" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="212" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y211" s="3"/>
+      <c r="Z211" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="212" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A212" s="2"/>
       <c r="B212" s="3"/>
       <c r="C212" s="3"/>
@@ -13231,12 +13536,13 @@
       <c r="V212" s="3"/>
       <c r="W212" s="3"/>
       <c r="X212" s="3"/>
-      <c r="Y212" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="213" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y212" s="3"/>
+      <c r="Z212" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="213" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A213" s="2"/>
       <c r="B213" s="3"/>
       <c r="C213" s="3"/>
@@ -13261,12 +13567,13 @@
       <c r="V213" s="3"/>
       <c r="W213" s="3"/>
       <c r="X213" s="3"/>
-      <c r="Y213" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="214" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y213" s="3"/>
+      <c r="Z213" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="214" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A214" s="2"/>
       <c r="B214" s="3"/>
       <c r="C214" s="3"/>
@@ -13291,12 +13598,13 @@
       <c r="V214" s="3"/>
       <c r="W214" s="3"/>
       <c r="X214" s="3"/>
-      <c r="Y214" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="215" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y214" s="3"/>
+      <c r="Z214" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="215" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A215" s="2"/>
       <c r="B215" s="3"/>
       <c r="C215" s="3"/>
@@ -13321,12 +13629,13 @@
       <c r="V215" s="3"/>
       <c r="W215" s="3"/>
       <c r="X215" s="3"/>
-      <c r="Y215" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="216" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y215" s="3"/>
+      <c r="Z215" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="216" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A216" s="2"/>
       <c r="B216" s="3"/>
       <c r="C216" s="3"/>
@@ -13351,12 +13660,13 @@
       <c r="V216" s="3"/>
       <c r="W216" s="3"/>
       <c r="X216" s="3"/>
-      <c r="Y216" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="217" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y216" s="3"/>
+      <c r="Z216" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="217" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A217" s="2"/>
       <c r="B217" s="3"/>
       <c r="C217" s="3"/>
@@ -13381,12 +13691,13 @@
       <c r="V217" s="3"/>
       <c r="W217" s="3"/>
       <c r="X217" s="3"/>
-      <c r="Y217" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="218" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y217" s="3"/>
+      <c r="Z217" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="218" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A218" s="2"/>
       <c r="B218" s="3"/>
       <c r="C218" s="3"/>
@@ -13411,12 +13722,13 @@
       <c r="V218" s="3"/>
       <c r="W218" s="3"/>
       <c r="X218" s="3"/>
-      <c r="Y218" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="219" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y218" s="3"/>
+      <c r="Z218" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="219" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A219" s="2"/>
       <c r="B219" s="3"/>
       <c r="C219" s="3"/>
@@ -13441,12 +13753,13 @@
       <c r="V219" s="3"/>
       <c r="W219" s="3"/>
       <c r="X219" s="3"/>
-      <c r="Y219" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="220" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y219" s="3"/>
+      <c r="Z219" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="220" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A220" s="2"/>
       <c r="B220" s="3"/>
       <c r="C220" s="3"/>
@@ -13471,12 +13784,13 @@
       <c r="V220" s="3"/>
       <c r="W220" s="3"/>
       <c r="X220" s="3"/>
-      <c r="Y220" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="221" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y220" s="3"/>
+      <c r="Z220" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="221" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A221" s="2"/>
       <c r="B221" s="3"/>
       <c r="C221" s="3"/>
@@ -13501,12 +13815,13 @@
       <c r="V221" s="3"/>
       <c r="W221" s="3"/>
       <c r="X221" s="3"/>
-      <c r="Y221" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="222" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y221" s="3"/>
+      <c r="Z221" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="222" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A222" s="2"/>
       <c r="B222" s="3"/>
       <c r="C222" s="3"/>
@@ -13531,12 +13846,13 @@
       <c r="V222" s="3"/>
       <c r="W222" s="3"/>
       <c r="X222" s="3"/>
-      <c r="Y222" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="223" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y222" s="3"/>
+      <c r="Z222" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="223" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A223" s="2"/>
       <c r="B223" s="3"/>
       <c r="C223" s="3"/>
@@ -13561,12 +13877,13 @@
       <c r="V223" s="3"/>
       <c r="W223" s="3"/>
       <c r="X223" s="3"/>
-      <c r="Y223" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="224" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y223" s="3"/>
+      <c r="Z223" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="224" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A224" s="2"/>
       <c r="B224" s="3"/>
       <c r="C224" s="3"/>
@@ -13591,12 +13908,13 @@
       <c r="V224" s="3"/>
       <c r="W224" s="3"/>
       <c r="X224" s="3"/>
-      <c r="Y224" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="225" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y224" s="3"/>
+      <c r="Z224" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="225" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A225" s="2"/>
       <c r="B225" s="3"/>
       <c r="C225" s="3"/>
@@ -13621,12 +13939,13 @@
       <c r="V225" s="3"/>
       <c r="W225" s="3"/>
       <c r="X225" s="3"/>
-      <c r="Y225" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="226" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y225" s="3"/>
+      <c r="Z225" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="226" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A226" s="2"/>
       <c r="B226" s="3"/>
       <c r="C226" s="3"/>
@@ -13651,12 +13970,13 @@
       <c r="V226" s="3"/>
       <c r="W226" s="3"/>
       <c r="X226" s="3"/>
-      <c r="Y226" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="227" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y226" s="3"/>
+      <c r="Z226" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="227" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A227" s="2"/>
       <c r="B227" s="3"/>
       <c r="C227" s="3"/>
@@ -13681,12 +14001,13 @@
       <c r="V227" s="3"/>
       <c r="W227" s="3"/>
       <c r="X227" s="3"/>
-      <c r="Y227" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="228" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y227" s="3"/>
+      <c r="Z227" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="228" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A228" s="2"/>
       <c r="B228" s="3"/>
       <c r="C228" s="3"/>
@@ -13711,12 +14032,13 @@
       <c r="V228" s="3"/>
       <c r="W228" s="3"/>
       <c r="X228" s="3"/>
-      <c r="Y228" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="229" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y228" s="3"/>
+      <c r="Z228" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="229" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A229" s="2"/>
       <c r="B229" s="3"/>
       <c r="C229" s="3"/>
@@ -13741,12 +14063,13 @@
       <c r="V229" s="3"/>
       <c r="W229" s="3"/>
       <c r="X229" s="3"/>
-      <c r="Y229" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="230" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y229" s="3"/>
+      <c r="Z229" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="230" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A230" s="2"/>
       <c r="B230" s="3"/>
       <c r="C230" s="3"/>
@@ -13771,12 +14094,13 @@
       <c r="V230" s="3"/>
       <c r="W230" s="3"/>
       <c r="X230" s="3"/>
-      <c r="Y230" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="231" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y230" s="3"/>
+      <c r="Z230" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="231" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A231" s="2"/>
       <c r="B231" s="3"/>
       <c r="C231" s="3"/>
@@ -13801,12 +14125,13 @@
       <c r="V231" s="3"/>
       <c r="W231" s="3"/>
       <c r="X231" s="3"/>
-      <c r="Y231" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="232" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y231" s="3"/>
+      <c r="Z231" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="232" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A232" s="2"/>
       <c r="B232" s="3"/>
       <c r="C232" s="3"/>
@@ -13831,12 +14156,13 @@
       <c r="V232" s="3"/>
       <c r="W232" s="3"/>
       <c r="X232" s="3"/>
-      <c r="Y232" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="233" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y232" s="3"/>
+      <c r="Z232" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="233" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A233" s="2"/>
       <c r="B233" s="3"/>
       <c r="C233" s="3"/>
@@ -13861,12 +14187,13 @@
       <c r="V233" s="3"/>
       <c r="W233" s="3"/>
       <c r="X233" s="3"/>
-      <c r="Y233" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="234" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y233" s="3"/>
+      <c r="Z233" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="234" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A234" s="2"/>
       <c r="B234" s="3"/>
       <c r="C234" s="3"/>
@@ -13891,12 +14218,13 @@
       <c r="V234" s="3"/>
       <c r="W234" s="3"/>
       <c r="X234" s="3"/>
-      <c r="Y234" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="235" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y234" s="3"/>
+      <c r="Z234" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="235" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A235" s="2"/>
       <c r="B235" s="3"/>
       <c r="C235" s="3"/>
@@ -13921,12 +14249,13 @@
       <c r="V235" s="3"/>
       <c r="W235" s="3"/>
       <c r="X235" s="3"/>
-      <c r="Y235" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="236" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y235" s="3"/>
+      <c r="Z235" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="236" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A236" s="2"/>
       <c r="B236" s="3"/>
       <c r="C236" s="3"/>
@@ -13951,12 +14280,13 @@
       <c r="V236" s="3"/>
       <c r="W236" s="3"/>
       <c r="X236" s="3"/>
-      <c r="Y236" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="237" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y236" s="3"/>
+      <c r="Z236" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="237" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A237" s="2"/>
       <c r="B237" s="3"/>
       <c r="C237" s="3"/>
@@ -13981,12 +14311,13 @@
       <c r="V237" s="3"/>
       <c r="W237" s="3"/>
       <c r="X237" s="3"/>
-      <c r="Y237" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="238" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y237" s="3"/>
+      <c r="Z237" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="238" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A238" s="2"/>
       <c r="B238" s="3"/>
       <c r="C238" s="3"/>
@@ -14011,12 +14342,13 @@
       <c r="V238" s="3"/>
       <c r="W238" s="3"/>
       <c r="X238" s="3"/>
-      <c r="Y238" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="239" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y238" s="3"/>
+      <c r="Z238" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="239" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A239" s="2"/>
       <c r="B239" s="3"/>
       <c r="C239" s="3"/>
@@ -14041,12 +14373,13 @@
       <c r="V239" s="3"/>
       <c r="W239" s="3"/>
       <c r="X239" s="3"/>
-      <c r="Y239" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="240" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y239" s="3"/>
+      <c r="Z239" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="240" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A240" s="2"/>
       <c r="B240" s="3"/>
       <c r="C240" s="3"/>
@@ -14071,12 +14404,13 @@
       <c r="V240" s="3"/>
       <c r="W240" s="3"/>
       <c r="X240" s="3"/>
-      <c r="Y240" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="241" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y240" s="3"/>
+      <c r="Z240" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="241" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A241" s="2"/>
       <c r="B241" s="3"/>
       <c r="C241" s="3"/>
@@ -14101,12 +14435,13 @@
       <c r="V241" s="3"/>
       <c r="W241" s="3"/>
       <c r="X241" s="3"/>
-      <c r="Y241" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="242" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y241" s="3"/>
+      <c r="Z241" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="242" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A242" s="2"/>
       <c r="B242" s="3"/>
       <c r="C242" s="3"/>
@@ -14131,12 +14466,13 @@
       <c r="V242" s="3"/>
       <c r="W242" s="3"/>
       <c r="X242" s="3"/>
-      <c r="Y242" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="243" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y242" s="3"/>
+      <c r="Z242" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="243" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A243" s="2"/>
       <c r="B243" s="3"/>
       <c r="C243" s="3"/>
@@ -14161,12 +14497,13 @@
       <c r="V243" s="3"/>
       <c r="W243" s="3"/>
       <c r="X243" s="3"/>
-      <c r="Y243" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="244" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y243" s="3"/>
+      <c r="Z243" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="244" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A244" s="2"/>
       <c r="B244" s="3"/>
       <c r="C244" s="3"/>
@@ -14191,12 +14528,13 @@
       <c r="V244" s="3"/>
       <c r="W244" s="3"/>
       <c r="X244" s="3"/>
-      <c r="Y244" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="245" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y244" s="3"/>
+      <c r="Z244" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="245" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A245" s="2"/>
       <c r="B245" s="3"/>
       <c r="C245" s="3"/>
@@ -14221,12 +14559,13 @@
       <c r="V245" s="3"/>
       <c r="W245" s="3"/>
       <c r="X245" s="3"/>
-      <c r="Y245" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="246" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y245" s="3"/>
+      <c r="Z245" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="246" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A246" s="2"/>
       <c r="B246" s="3"/>
       <c r="C246" s="3"/>
@@ -14251,12 +14590,13 @@
       <c r="V246" s="3"/>
       <c r="W246" s="3"/>
       <c r="X246" s="3"/>
-      <c r="Y246" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="247" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y246" s="3"/>
+      <c r="Z246" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="247" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A247" s="2"/>
       <c r="B247" s="3"/>
       <c r="C247" s="3"/>
@@ -14281,12 +14621,13 @@
       <c r="V247" s="3"/>
       <c r="W247" s="3"/>
       <c r="X247" s="3"/>
-      <c r="Y247" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="248" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y247" s="3"/>
+      <c r="Z247" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="248" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A248" s="2"/>
       <c r="B248" s="3"/>
       <c r="C248" s="3"/>
@@ -14311,12 +14652,13 @@
       <c r="V248" s="3"/>
       <c r="W248" s="3"/>
       <c r="X248" s="3"/>
-      <c r="Y248" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="249" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y248" s="3"/>
+      <c r="Z248" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="249" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A249" s="2"/>
       <c r="B249" s="3"/>
       <c r="C249" s="3"/>
@@ -14341,12 +14683,13 @@
       <c r="V249" s="3"/>
       <c r="W249" s="3"/>
       <c r="X249" s="3"/>
-      <c r="Y249" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="250" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y249" s="3"/>
+      <c r="Z249" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="250" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A250" s="2"/>
       <c r="B250" s="3"/>
       <c r="C250" s="3"/>
@@ -14371,12 +14714,13 @@
       <c r="V250" s="3"/>
       <c r="W250" s="3"/>
       <c r="X250" s="3"/>
-      <c r="Y250" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="251" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y250" s="3"/>
+      <c r="Z250" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="251" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A251" s="2"/>
       <c r="B251" s="3"/>
       <c r="C251" s="3"/>
@@ -14401,12 +14745,13 @@
       <c r="V251" s="3"/>
       <c r="W251" s="3"/>
       <c r="X251" s="3"/>
-      <c r="Y251" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="252" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y251" s="3"/>
+      <c r="Z251" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="252" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A252" s="2"/>
       <c r="B252" s="3"/>
       <c r="C252" s="3"/>
@@ -14431,12 +14776,13 @@
       <c r="V252" s="3"/>
       <c r="W252" s="3"/>
       <c r="X252" s="3"/>
-      <c r="Y252" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="253" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y252" s="3"/>
+      <c r="Z252" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="253" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A253" s="2"/>
       <c r="B253" s="3"/>
       <c r="C253" s="3"/>
@@ -14461,12 +14807,13 @@
       <c r="V253" s="3"/>
       <c r="W253" s="3"/>
       <c r="X253" s="3"/>
-      <c r="Y253" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="254" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y253" s="3"/>
+      <c r="Z253" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="254" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A254" s="2"/>
       <c r="B254" s="3"/>
       <c r="C254" s="3"/>
@@ -14491,12 +14838,13 @@
       <c r="V254" s="3"/>
       <c r="W254" s="3"/>
       <c r="X254" s="3"/>
-      <c r="Y254" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="255" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y254" s="3"/>
+      <c r="Z254" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="255" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A255" s="2"/>
       <c r="B255" s="3"/>
       <c r="C255" s="3"/>
@@ -14521,12 +14869,13 @@
       <c r="V255" s="3"/>
       <c r="W255" s="3"/>
       <c r="X255" s="3"/>
-      <c r="Y255" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="256" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y255" s="3"/>
+      <c r="Z255" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="256" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A256" s="2"/>
       <c r="B256" s="3"/>
       <c r="C256" s="3"/>
@@ -14551,12 +14900,13 @@
       <c r="V256" s="3"/>
       <c r="W256" s="3"/>
       <c r="X256" s="3"/>
-      <c r="Y256" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="257" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y256" s="3"/>
+      <c r="Z256" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="257" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A257" s="2"/>
       <c r="B257" s="3"/>
       <c r="C257" s="3"/>
@@ -14581,12 +14931,13 @@
       <c r="V257" s="3"/>
       <c r="W257" s="3"/>
       <c r="X257" s="3"/>
-      <c r="Y257" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="258" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y257" s="3"/>
+      <c r="Z257" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="258" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A258" s="2"/>
       <c r="B258" s="3"/>
       <c r="C258" s="3"/>
@@ -14611,12 +14962,13 @@
       <c r="V258" s="3"/>
       <c r="W258" s="3"/>
       <c r="X258" s="3"/>
-      <c r="Y258" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="259" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y258" s="3"/>
+      <c r="Z258" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="259" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A259" s="2"/>
       <c r="B259" s="3"/>
       <c r="C259" s="3"/>
@@ -14641,12 +14993,13 @@
       <c r="V259" s="3"/>
       <c r="W259" s="3"/>
       <c r="X259" s="3"/>
-      <c r="Y259" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="260" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y259" s="3"/>
+      <c r="Z259" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="260" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A260" s="2"/>
       <c r="B260" s="3"/>
       <c r="C260" s="3"/>
@@ -14671,12 +15024,13 @@
       <c r="V260" s="3"/>
       <c r="W260" s="3"/>
       <c r="X260" s="3"/>
-      <c r="Y260" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="261" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y260" s="3"/>
+      <c r="Z260" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="261" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A261" s="2"/>
       <c r="B261" s="3"/>
       <c r="C261" s="3"/>
@@ -14701,12 +15055,13 @@
       <c r="V261" s="3"/>
       <c r="W261" s="3"/>
       <c r="X261" s="3"/>
-      <c r="Y261" s="4" t="str">
-        <f t="shared" ref="Y261:Y324" si="4">IF(COUNTA(B261:X261)=0,"",AVERAGE(B261:X261))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="262" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y261" s="3"/>
+      <c r="Z261" s="4" t="str">
+        <f t="shared" ref="Z261:Z324" si="5">IF(COUNTA(B261:Y261)=0,"",AVERAGE(B261:Y261))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="262" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A262" s="2"/>
       <c r="B262" s="3"/>
       <c r="C262" s="3"/>
@@ -14731,12 +15086,13 @@
       <c r="V262" s="3"/>
       <c r="W262" s="3"/>
       <c r="X262" s="3"/>
-      <c r="Y262" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="263" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y262" s="3"/>
+      <c r="Z262" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="263" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A263" s="2"/>
       <c r="B263" s="3"/>
       <c r="C263" s="3"/>
@@ -14761,12 +15117,13 @@
       <c r="V263" s="3"/>
       <c r="W263" s="3"/>
       <c r="X263" s="3"/>
-      <c r="Y263" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="264" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y263" s="3"/>
+      <c r="Z263" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="264" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A264" s="2"/>
       <c r="B264" s="3"/>
       <c r="C264" s="3"/>
@@ -14791,12 +15148,13 @@
       <c r="V264" s="3"/>
       <c r="W264" s="3"/>
       <c r="X264" s="3"/>
-      <c r="Y264" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="265" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y264" s="3"/>
+      <c r="Z264" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="265" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A265" s="2"/>
       <c r="B265" s="3"/>
       <c r="C265" s="3"/>
@@ -14821,12 +15179,13 @@
       <c r="V265" s="3"/>
       <c r="W265" s="3"/>
       <c r="X265" s="3"/>
-      <c r="Y265" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="266" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y265" s="3"/>
+      <c r="Z265" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="266" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A266" s="2"/>
       <c r="B266" s="3"/>
       <c r="C266" s="3"/>
@@ -14851,12 +15210,13 @@
       <c r="V266" s="3"/>
       <c r="W266" s="3"/>
       <c r="X266" s="3"/>
-      <c r="Y266" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="267" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y266" s="3"/>
+      <c r="Z266" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="267" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A267" s="2"/>
       <c r="B267" s="3"/>
       <c r="C267" s="3"/>
@@ -14881,12 +15241,13 @@
       <c r="V267" s="3"/>
       <c r="W267" s="3"/>
       <c r="X267" s="3"/>
-      <c r="Y267" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="268" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y267" s="3"/>
+      <c r="Z267" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="268" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A268" s="2"/>
       <c r="B268" s="3"/>
       <c r="C268" s="3"/>
@@ -14911,12 +15272,13 @@
       <c r="V268" s="3"/>
       <c r="W268" s="3"/>
       <c r="X268" s="3"/>
-      <c r="Y268" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="269" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y268" s="3"/>
+      <c r="Z268" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="269" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A269" s="2"/>
       <c r="B269" s="3"/>
       <c r="C269" s="3"/>
@@ -14941,12 +15303,13 @@
       <c r="V269" s="3"/>
       <c r="W269" s="3"/>
       <c r="X269" s="3"/>
-      <c r="Y269" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="270" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y269" s="3"/>
+      <c r="Z269" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="270" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A270" s="2"/>
       <c r="B270" s="3"/>
       <c r="C270" s="3"/>
@@ -14971,12 +15334,13 @@
       <c r="V270" s="3"/>
       <c r="W270" s="3"/>
       <c r="X270" s="3"/>
-      <c r="Y270" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="271" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y270" s="3"/>
+      <c r="Z270" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="271" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A271" s="2"/>
       <c r="B271" s="3"/>
       <c r="C271" s="3"/>
@@ -15001,12 +15365,13 @@
       <c r="V271" s="3"/>
       <c r="W271" s="3"/>
       <c r="X271" s="3"/>
-      <c r="Y271" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="272" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y271" s="3"/>
+      <c r="Z271" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="272" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A272" s="2"/>
       <c r="B272" s="3"/>
       <c r="C272" s="3"/>
@@ -15031,12 +15396,13 @@
       <c r="V272" s="3"/>
       <c r="W272" s="3"/>
       <c r="X272" s="3"/>
-      <c r="Y272" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="273" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y272" s="3"/>
+      <c r="Z272" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="273" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A273" s="2"/>
       <c r="B273" s="3"/>
       <c r="C273" s="3"/>
@@ -15061,12 +15427,13 @@
       <c r="V273" s="3"/>
       <c r="W273" s="3"/>
       <c r="X273" s="3"/>
-      <c r="Y273" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="274" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y273" s="3"/>
+      <c r="Z273" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="274" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A274" s="2"/>
       <c r="B274" s="3"/>
       <c r="C274" s="3"/>
@@ -15091,12 +15458,13 @@
       <c r="V274" s="3"/>
       <c r="W274" s="3"/>
       <c r="X274" s="3"/>
-      <c r="Y274" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="275" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y274" s="3"/>
+      <c r="Z274" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="275" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A275" s="2"/>
       <c r="B275" s="3"/>
       <c r="C275" s="3"/>
@@ -15121,12 +15489,13 @@
       <c r="V275" s="3"/>
       <c r="W275" s="3"/>
       <c r="X275" s="3"/>
-      <c r="Y275" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="276" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y275" s="3"/>
+      <c r="Z275" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="276" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A276" s="2"/>
       <c r="B276" s="3"/>
       <c r="C276" s="3"/>
@@ -15151,12 +15520,13 @@
       <c r="V276" s="3"/>
       <c r="W276" s="3"/>
       <c r="X276" s="3"/>
-      <c r="Y276" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="277" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y276" s="3"/>
+      <c r="Z276" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="277" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A277" s="2"/>
       <c r="B277" s="3"/>
       <c r="C277" s="3"/>
@@ -15181,12 +15551,13 @@
       <c r="V277" s="3"/>
       <c r="W277" s="3"/>
       <c r="X277" s="3"/>
-      <c r="Y277" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="278" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y277" s="3"/>
+      <c r="Z277" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="278" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A278" s="2"/>
       <c r="B278" s="3"/>
       <c r="C278" s="3"/>
@@ -15211,12 +15582,13 @@
       <c r="V278" s="3"/>
       <c r="W278" s="3"/>
       <c r="X278" s="3"/>
-      <c r="Y278" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="279" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y278" s="3"/>
+      <c r="Z278" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="279" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A279" s="2"/>
       <c r="B279" s="3"/>
       <c r="C279" s="3"/>
@@ -15241,12 +15613,13 @@
       <c r="V279" s="3"/>
       <c r="W279" s="3"/>
       <c r="X279" s="3"/>
-      <c r="Y279" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="280" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y279" s="3"/>
+      <c r="Z279" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="280" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A280" s="2"/>
       <c r="B280" s="3"/>
       <c r="C280" s="3"/>
@@ -15271,12 +15644,13 @@
       <c r="V280" s="3"/>
       <c r="W280" s="3"/>
       <c r="X280" s="3"/>
-      <c r="Y280" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="281" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y280" s="3"/>
+      <c r="Z280" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="281" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A281" s="2"/>
       <c r="B281" s="3"/>
       <c r="C281" s="3"/>
@@ -15301,12 +15675,13 @@
       <c r="V281" s="3"/>
       <c r="W281" s="3"/>
       <c r="X281" s="3"/>
-      <c r="Y281" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="282" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y281" s="3"/>
+      <c r="Z281" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="282" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A282" s="2"/>
       <c r="B282" s="3"/>
       <c r="C282" s="3"/>
@@ -15331,12 +15706,13 @@
       <c r="V282" s="3"/>
       <c r="W282" s="3"/>
       <c r="X282" s="3"/>
-      <c r="Y282" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="283" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y282" s="3"/>
+      <c r="Z282" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="283" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A283" s="2"/>
       <c r="B283" s="3"/>
       <c r="C283" s="3"/>
@@ -15361,12 +15737,13 @@
       <c r="V283" s="3"/>
       <c r="W283" s="3"/>
       <c r="X283" s="3"/>
-      <c r="Y283" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="284" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y283" s="3"/>
+      <c r="Z283" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="284" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A284" s="2"/>
       <c r="B284" s="3"/>
       <c r="C284" s="3"/>
@@ -15391,12 +15768,13 @@
       <c r="V284" s="3"/>
       <c r="W284" s="3"/>
       <c r="X284" s="3"/>
-      <c r="Y284" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="285" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y284" s="3"/>
+      <c r="Z284" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="285" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A285" s="2"/>
       <c r="B285" s="3"/>
       <c r="C285" s="3"/>
@@ -15421,12 +15799,13 @@
       <c r="V285" s="3"/>
       <c r="W285" s="3"/>
       <c r="X285" s="3"/>
-      <c r="Y285" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="286" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y285" s="3"/>
+      <c r="Z285" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="286" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A286" s="2"/>
       <c r="B286" s="3"/>
       <c r="C286" s="3"/>
@@ -15451,12 +15830,13 @@
       <c r="V286" s="3"/>
       <c r="W286" s="3"/>
       <c r="X286" s="3"/>
-      <c r="Y286" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="287" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y286" s="3"/>
+      <c r="Z286" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="287" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A287" s="2"/>
       <c r="B287" s="3"/>
       <c r="C287" s="3"/>
@@ -15481,12 +15861,13 @@
       <c r="V287" s="3"/>
       <c r="W287" s="3"/>
       <c r="X287" s="3"/>
-      <c r="Y287" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="288" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y287" s="3"/>
+      <c r="Z287" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="288" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A288" s="2"/>
       <c r="B288" s="3"/>
       <c r="C288" s="3"/>
@@ -15511,12 +15892,13 @@
       <c r="V288" s="3"/>
       <c r="W288" s="3"/>
       <c r="X288" s="3"/>
-      <c r="Y288" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="289" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y288" s="3"/>
+      <c r="Z288" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="289" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A289" s="2"/>
       <c r="B289" s="3"/>
       <c r="C289" s="3"/>
@@ -15541,12 +15923,13 @@
       <c r="V289" s="3"/>
       <c r="W289" s="3"/>
       <c r="X289" s="3"/>
-      <c r="Y289" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="290" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y289" s="3"/>
+      <c r="Z289" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="290" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A290" s="2"/>
       <c r="B290" s="3"/>
       <c r="C290" s="3"/>
@@ -15571,12 +15954,13 @@
       <c r="V290" s="3"/>
       <c r="W290" s="3"/>
       <c r="X290" s="3"/>
-      <c r="Y290" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="291" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y290" s="3"/>
+      <c r="Z290" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="291" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A291" s="2"/>
       <c r="B291" s="3"/>
       <c r="C291" s="3"/>
@@ -15601,12 +15985,13 @@
       <c r="V291" s="3"/>
       <c r="W291" s="3"/>
       <c r="X291" s="3"/>
-      <c r="Y291" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="292" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y291" s="3"/>
+      <c r="Z291" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="292" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A292" s="2"/>
       <c r="B292" s="3"/>
       <c r="C292" s="3"/>
@@ -15631,12 +16016,13 @@
       <c r="V292" s="3"/>
       <c r="W292" s="3"/>
       <c r="X292" s="3"/>
-      <c r="Y292" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="293" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y292" s="3"/>
+      <c r="Z292" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="293" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A293" s="2"/>
       <c r="B293" s="3"/>
       <c r="C293" s="3"/>
@@ -15661,12 +16047,13 @@
       <c r="V293" s="3"/>
       <c r="W293" s="3"/>
       <c r="X293" s="3"/>
-      <c r="Y293" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="294" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y293" s="3"/>
+      <c r="Z293" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="294" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A294" s="2"/>
       <c r="B294" s="3"/>
       <c r="C294" s="3"/>
@@ -15691,12 +16078,13 @@
       <c r="V294" s="3"/>
       <c r="W294" s="3"/>
       <c r="X294" s="3"/>
-      <c r="Y294" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="295" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y294" s="3"/>
+      <c r="Z294" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="295" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A295" s="2"/>
       <c r="B295" s="3"/>
       <c r="C295" s="3"/>
@@ -15721,12 +16109,13 @@
       <c r="V295" s="3"/>
       <c r="W295" s="3"/>
       <c r="X295" s="3"/>
-      <c r="Y295" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="296" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y295" s="3"/>
+      <c r="Z295" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="296" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A296" s="2"/>
       <c r="B296" s="3"/>
       <c r="C296" s="3"/>
@@ -15751,12 +16140,13 @@
       <c r="V296" s="3"/>
       <c r="W296" s="3"/>
       <c r="X296" s="3"/>
-      <c r="Y296" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="297" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y296" s="3"/>
+      <c r="Z296" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="297" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A297" s="2"/>
       <c r="B297" s="3"/>
       <c r="C297" s="3"/>
@@ -15781,12 +16171,13 @@
       <c r="V297" s="3"/>
       <c r="W297" s="3"/>
       <c r="X297" s="3"/>
-      <c r="Y297" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="298" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y297" s="3"/>
+      <c r="Z297" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="298" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A298" s="2"/>
       <c r="B298" s="3"/>
       <c r="C298" s="3"/>
@@ -15811,12 +16202,13 @@
       <c r="V298" s="3"/>
       <c r="W298" s="3"/>
       <c r="X298" s="3"/>
-      <c r="Y298" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="299" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y298" s="3"/>
+      <c r="Z298" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="299" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A299" s="2"/>
       <c r="B299" s="3"/>
       <c r="C299" s="3"/>
@@ -15841,12 +16233,13 @@
       <c r="V299" s="3"/>
       <c r="W299" s="3"/>
       <c r="X299" s="3"/>
-      <c r="Y299" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="300" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y299" s="3"/>
+      <c r="Z299" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="300" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A300" s="2"/>
       <c r="B300" s="3"/>
       <c r="C300" s="3"/>
@@ -15871,12 +16264,13 @@
       <c r="V300" s="3"/>
       <c r="W300" s="3"/>
       <c r="X300" s="3"/>
-      <c r="Y300" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="301" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y300" s="3"/>
+      <c r="Z300" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="301" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A301" s="2"/>
       <c r="B301" s="3"/>
       <c r="C301" s="3"/>
@@ -15901,12 +16295,13 @@
       <c r="V301" s="3"/>
       <c r="W301" s="3"/>
       <c r="X301" s="3"/>
-      <c r="Y301" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="302" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y301" s="3"/>
+      <c r="Z301" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="302" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A302" s="2"/>
       <c r="B302" s="3"/>
       <c r="C302" s="3"/>
@@ -15931,12 +16326,13 @@
       <c r="V302" s="3"/>
       <c r="W302" s="3"/>
       <c r="X302" s="3"/>
-      <c r="Y302" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="303" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y302" s="3"/>
+      <c r="Z302" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="303" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A303" s="2"/>
       <c r="B303" s="3"/>
       <c r="C303" s="3"/>
@@ -15961,12 +16357,13 @@
       <c r="V303" s="3"/>
       <c r="W303" s="3"/>
       <c r="X303" s="3"/>
-      <c r="Y303" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="304" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y303" s="3"/>
+      <c r="Z303" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="304" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A304" s="2"/>
       <c r="B304" s="3"/>
       <c r="C304" s="3"/>
@@ -15991,12 +16388,13 @@
       <c r="V304" s="3"/>
       <c r="W304" s="3"/>
       <c r="X304" s="3"/>
-      <c r="Y304" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="305" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y304" s="3"/>
+      <c r="Z304" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="305" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A305" s="2"/>
       <c r="B305" s="3"/>
       <c r="C305" s="3"/>
@@ -16021,12 +16419,13 @@
       <c r="V305" s="3"/>
       <c r="W305" s="3"/>
       <c r="X305" s="3"/>
-      <c r="Y305" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="306" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y305" s="3"/>
+      <c r="Z305" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="306" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A306" s="2"/>
       <c r="B306" s="3"/>
       <c r="C306" s="3"/>
@@ -16051,12 +16450,13 @@
       <c r="V306" s="3"/>
       <c r="W306" s="3"/>
       <c r="X306" s="3"/>
-      <c r="Y306" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="307" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y306" s="3"/>
+      <c r="Z306" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="307" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A307" s="2"/>
       <c r="B307" s="3"/>
       <c r="C307" s="3"/>
@@ -16081,12 +16481,13 @@
       <c r="V307" s="3"/>
       <c r="W307" s="3"/>
       <c r="X307" s="3"/>
-      <c r="Y307" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="308" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y307" s="3"/>
+      <c r="Z307" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="308" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A308" s="2"/>
       <c r="B308" s="3"/>
       <c r="C308" s="3"/>
@@ -16111,12 +16512,13 @@
       <c r="V308" s="3"/>
       <c r="W308" s="3"/>
       <c r="X308" s="3"/>
-      <c r="Y308" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="309" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y308" s="3"/>
+      <c r="Z308" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="309" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A309" s="2"/>
       <c r="B309" s="3"/>
       <c r="C309" s="3"/>
@@ -16141,12 +16543,13 @@
       <c r="V309" s="3"/>
       <c r="W309" s="3"/>
       <c r="X309" s="3"/>
-      <c r="Y309" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="310" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y309" s="3"/>
+      <c r="Z309" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="310" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A310" s="2"/>
       <c r="B310" s="3"/>
       <c r="C310" s="3"/>
@@ -16171,12 +16574,13 @@
       <c r="V310" s="3"/>
       <c r="W310" s="3"/>
       <c r="X310" s="3"/>
-      <c r="Y310" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="311" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y310" s="3"/>
+      <c r="Z310" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="311" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A311" s="2"/>
       <c r="B311" s="3"/>
       <c r="C311" s="3"/>
@@ -16201,12 +16605,13 @@
       <c r="V311" s="3"/>
       <c r="W311" s="3"/>
       <c r="X311" s="3"/>
-      <c r="Y311" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="312" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y311" s="3"/>
+      <c r="Z311" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="312" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A312" s="2"/>
       <c r="B312" s="3"/>
       <c r="C312" s="3"/>
@@ -16231,12 +16636,13 @@
       <c r="V312" s="3"/>
       <c r="W312" s="3"/>
       <c r="X312" s="3"/>
-      <c r="Y312" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="313" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y312" s="3"/>
+      <c r="Z312" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="313" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A313" s="2"/>
       <c r="B313" s="3"/>
       <c r="C313" s="3"/>
@@ -16261,12 +16667,13 @@
       <c r="V313" s="3"/>
       <c r="W313" s="3"/>
       <c r="X313" s="3"/>
-      <c r="Y313" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="314" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y313" s="3"/>
+      <c r="Z313" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="314" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A314" s="2"/>
       <c r="B314" s="3"/>
       <c r="C314" s="3"/>
@@ -16291,12 +16698,13 @@
       <c r="V314" s="3"/>
       <c r="W314" s="3"/>
       <c r="X314" s="3"/>
-      <c r="Y314" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="315" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y314" s="3"/>
+      <c r="Z314" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="315" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A315" s="2"/>
       <c r="B315" s="3"/>
       <c r="C315" s="3"/>
@@ -16321,12 +16729,13 @@
       <c r="V315" s="3"/>
       <c r="W315" s="3"/>
       <c r="X315" s="3"/>
-      <c r="Y315" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="316" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y315" s="3"/>
+      <c r="Z315" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="316" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A316" s="2"/>
       <c r="B316" s="3"/>
       <c r="C316" s="3"/>
@@ -16351,12 +16760,13 @@
       <c r="V316" s="3"/>
       <c r="W316" s="3"/>
       <c r="X316" s="3"/>
-      <c r="Y316" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="317" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y316" s="3"/>
+      <c r="Z316" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="317" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A317" s="2"/>
       <c r="B317" s="3"/>
       <c r="C317" s="3"/>
@@ -16381,12 +16791,13 @@
       <c r="V317" s="3"/>
       <c r="W317" s="3"/>
       <c r="X317" s="3"/>
-      <c r="Y317" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="318" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y317" s="3"/>
+      <c r="Z317" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="318" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A318" s="2"/>
       <c r="B318" s="3"/>
       <c r="C318" s="3"/>
@@ -16411,12 +16822,13 @@
       <c r="V318" s="3"/>
       <c r="W318" s="3"/>
       <c r="X318" s="3"/>
-      <c r="Y318" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="319" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y318" s="3"/>
+      <c r="Z318" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="319" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A319" s="2"/>
       <c r="B319" s="3"/>
       <c r="C319" s="3"/>
@@ -16441,12 +16853,13 @@
       <c r="V319" s="3"/>
       <c r="W319" s="3"/>
       <c r="X319" s="3"/>
-      <c r="Y319" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="320" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y319" s="3"/>
+      <c r="Z319" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="320" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A320" s="2"/>
       <c r="B320" s="3"/>
       <c r="C320" s="3"/>
@@ -16471,12 +16884,13 @@
       <c r="V320" s="3"/>
       <c r="W320" s="3"/>
       <c r="X320" s="3"/>
-      <c r="Y320" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="321" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y320" s="3"/>
+      <c r="Z320" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="321" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A321" s="2"/>
       <c r="B321" s="3"/>
       <c r="C321" s="3"/>
@@ -16501,12 +16915,13 @@
       <c r="V321" s="3"/>
       <c r="W321" s="3"/>
       <c r="X321" s="3"/>
-      <c r="Y321" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="322" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y321" s="3"/>
+      <c r="Z321" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="322" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A322" s="2"/>
       <c r="B322" s="3"/>
       <c r="C322" s="3"/>
@@ -16531,12 +16946,13 @@
       <c r="V322" s="3"/>
       <c r="W322" s="3"/>
       <c r="X322" s="3"/>
-      <c r="Y322" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="323" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y322" s="3"/>
+      <c r="Z322" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="323" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A323" s="2"/>
       <c r="B323" s="3"/>
       <c r="C323" s="3"/>
@@ -16561,12 +16977,13 @@
       <c r="V323" s="3"/>
       <c r="W323" s="3"/>
       <c r="X323" s="3"/>
-      <c r="Y323" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="324" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y323" s="3"/>
+      <c r="Z323" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="324" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A324" s="2"/>
       <c r="B324" s="3"/>
       <c r="C324" s="3"/>
@@ -16591,12 +17008,13 @@
       <c r="V324" s="3"/>
       <c r="W324" s="3"/>
       <c r="X324" s="3"/>
-      <c r="Y324" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="325" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y324" s="3"/>
+      <c r="Z324" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="325" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A325" s="2"/>
       <c r="B325" s="3"/>
       <c r="C325" s="3"/>
@@ -16621,12 +17039,13 @@
       <c r="V325" s="3"/>
       <c r="W325" s="3"/>
       <c r="X325" s="3"/>
-      <c r="Y325" s="4" t="str">
-        <f t="shared" ref="Y325:Y388" si="5">IF(COUNTA(B325:X325)=0,"",AVERAGE(B325:X325))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="326" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y325" s="3"/>
+      <c r="Z325" s="4" t="str">
+        <f t="shared" ref="Z325:Z388" si="6">IF(COUNTA(B325:Y325)=0,"",AVERAGE(B325:Y325))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="326" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A326" s="2"/>
       <c r="B326" s="3"/>
       <c r="C326" s="3"/>
@@ -16651,12 +17070,13 @@
       <c r="V326" s="3"/>
       <c r="W326" s="3"/>
       <c r="X326" s="3"/>
-      <c r="Y326" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="327" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y326" s="3"/>
+      <c r="Z326" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="327" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A327" s="2"/>
       <c r="B327" s="3"/>
       <c r="C327" s="3"/>
@@ -16681,12 +17101,13 @@
       <c r="V327" s="3"/>
       <c r="W327" s="3"/>
       <c r="X327" s="3"/>
-      <c r="Y327" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="328" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y327" s="3"/>
+      <c r="Z327" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="328" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A328" s="2"/>
       <c r="B328" s="3"/>
       <c r="C328" s="3"/>
@@ -16711,12 +17132,13 @@
       <c r="V328" s="3"/>
       <c r="W328" s="3"/>
       <c r="X328" s="3"/>
-      <c r="Y328" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="329" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y328" s="3"/>
+      <c r="Z328" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="329" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A329" s="2"/>
       <c r="B329" s="3"/>
       <c r="C329" s="3"/>
@@ -16741,12 +17163,13 @@
       <c r="V329" s="3"/>
       <c r="W329" s="3"/>
       <c r="X329" s="3"/>
-      <c r="Y329" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="330" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y329" s="3"/>
+      <c r="Z329" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="330" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A330" s="2"/>
       <c r="B330" s="3"/>
       <c r="C330" s="3"/>
@@ -16771,12 +17194,13 @@
       <c r="V330" s="3"/>
       <c r="W330" s="3"/>
       <c r="X330" s="3"/>
-      <c r="Y330" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="331" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y330" s="3"/>
+      <c r="Z330" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="331" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A331" s="2"/>
       <c r="B331" s="3"/>
       <c r="C331" s="3"/>
@@ -16801,12 +17225,13 @@
       <c r="V331" s="3"/>
       <c r="W331" s="3"/>
       <c r="X331" s="3"/>
-      <c r="Y331" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="332" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y331" s="3"/>
+      <c r="Z331" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="332" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A332" s="2"/>
       <c r="B332" s="3"/>
       <c r="C332" s="3"/>
@@ -16831,12 +17256,13 @@
       <c r="V332" s="3"/>
       <c r="W332" s="3"/>
       <c r="X332" s="3"/>
-      <c r="Y332" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="333" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y332" s="3"/>
+      <c r="Z332" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="333" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A333" s="2"/>
       <c r="B333" s="3"/>
       <c r="C333" s="3"/>
@@ -16861,12 +17287,13 @@
       <c r="V333" s="3"/>
       <c r="W333" s="3"/>
       <c r="X333" s="3"/>
-      <c r="Y333" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="334" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y333" s="3"/>
+      <c r="Z333" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="334" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A334" s="2"/>
       <c r="B334" s="3"/>
       <c r="C334" s="3"/>
@@ -16891,12 +17318,13 @@
       <c r="V334" s="3"/>
       <c r="W334" s="3"/>
       <c r="X334" s="3"/>
-      <c r="Y334" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="335" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y334" s="3"/>
+      <c r="Z334" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="335" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A335" s="2"/>
       <c r="B335" s="3"/>
       <c r="C335" s="3"/>
@@ -16921,12 +17349,13 @@
       <c r="V335" s="3"/>
       <c r="W335" s="3"/>
       <c r="X335" s="3"/>
-      <c r="Y335" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="336" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y335" s="3"/>
+      <c r="Z335" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="336" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A336" s="2"/>
       <c r="B336" s="3"/>
       <c r="C336" s="3"/>
@@ -16951,12 +17380,13 @@
       <c r="V336" s="3"/>
       <c r="W336" s="3"/>
       <c r="X336" s="3"/>
-      <c r="Y336" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="337" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y336" s="3"/>
+      <c r="Z336" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="337" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A337" s="2"/>
       <c r="B337" s="3"/>
       <c r="C337" s="3"/>
@@ -16981,12 +17411,13 @@
       <c r="V337" s="3"/>
       <c r="W337" s="3"/>
       <c r="X337" s="3"/>
-      <c r="Y337" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="338" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y337" s="3"/>
+      <c r="Z337" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="338" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A338" s="2"/>
       <c r="B338" s="3"/>
       <c r="C338" s="3"/>
@@ -17011,12 +17442,13 @@
       <c r="V338" s="3"/>
       <c r="W338" s="3"/>
       <c r="X338" s="3"/>
-      <c r="Y338" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="339" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y338" s="3"/>
+      <c r="Z338" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="339" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A339" s="2"/>
       <c r="B339" s="3"/>
       <c r="C339" s="3"/>
@@ -17041,12 +17473,13 @@
       <c r="V339" s="3"/>
       <c r="W339" s="3"/>
       <c r="X339" s="3"/>
-      <c r="Y339" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="340" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y339" s="3"/>
+      <c r="Z339" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="340" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A340" s="2"/>
       <c r="B340" s="3"/>
       <c r="C340" s="3"/>
@@ -17071,12 +17504,13 @@
       <c r="V340" s="3"/>
       <c r="W340" s="3"/>
       <c r="X340" s="3"/>
-      <c r="Y340" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="341" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y340" s="3"/>
+      <c r="Z340" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="341" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A341" s="2"/>
       <c r="B341" s="3"/>
       <c r="C341" s="3"/>
@@ -17101,12 +17535,13 @@
       <c r="V341" s="3"/>
       <c r="W341" s="3"/>
       <c r="X341" s="3"/>
-      <c r="Y341" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="342" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y341" s="3"/>
+      <c r="Z341" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="342" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A342" s="2"/>
       <c r="B342" s="3"/>
       <c r="C342" s="3"/>
@@ -17131,12 +17566,13 @@
       <c r="V342" s="3"/>
       <c r="W342" s="3"/>
       <c r="X342" s="3"/>
-      <c r="Y342" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="343" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y342" s="3"/>
+      <c r="Z342" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="343" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A343" s="2"/>
       <c r="B343" s="3"/>
       <c r="C343" s="3"/>
@@ -17161,12 +17597,13 @@
       <c r="V343" s="3"/>
       <c r="W343" s="3"/>
       <c r="X343" s="3"/>
-      <c r="Y343" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="344" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y343" s="3"/>
+      <c r="Z343" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="344" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A344" s="2"/>
       <c r="B344" s="3"/>
       <c r="C344" s="3"/>
@@ -17191,12 +17628,13 @@
       <c r="V344" s="3"/>
       <c r="W344" s="3"/>
       <c r="X344" s="3"/>
-      <c r="Y344" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="345" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y344" s="3"/>
+      <c r="Z344" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="345" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A345" s="2"/>
       <c r="B345" s="3"/>
       <c r="C345" s="3"/>
@@ -17221,12 +17659,13 @@
       <c r="V345" s="3"/>
       <c r="W345" s="3"/>
       <c r="X345" s="3"/>
-      <c r="Y345" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="346" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y345" s="3"/>
+      <c r="Z345" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="346" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A346" s="2"/>
       <c r="B346" s="3"/>
       <c r="C346" s="3"/>
@@ -17251,12 +17690,13 @@
       <c r="V346" s="3"/>
       <c r="W346" s="3"/>
       <c r="X346" s="3"/>
-      <c r="Y346" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="347" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y346" s="3"/>
+      <c r="Z346" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="347" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A347" s="2"/>
       <c r="B347" s="3"/>
       <c r="C347" s="3"/>
@@ -17281,12 +17721,13 @@
       <c r="V347" s="3"/>
       <c r="W347" s="3"/>
       <c r="X347" s="3"/>
-      <c r="Y347" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="348" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y347" s="3"/>
+      <c r="Z347" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="348" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A348" s="2"/>
       <c r="B348" s="3"/>
       <c r="C348" s="3"/>
@@ -17311,12 +17752,13 @@
       <c r="V348" s="3"/>
       <c r="W348" s="3"/>
       <c r="X348" s="3"/>
-      <c r="Y348" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="349" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y348" s="3"/>
+      <c r="Z348" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="349" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A349" s="2"/>
       <c r="B349" s="3"/>
       <c r="C349" s="3"/>
@@ -17341,12 +17783,13 @@
       <c r="V349" s="3"/>
       <c r="W349" s="3"/>
       <c r="X349" s="3"/>
-      <c r="Y349" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="350" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y349" s="3"/>
+      <c r="Z349" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="350" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A350" s="2"/>
       <c r="B350" s="3"/>
       <c r="C350" s="3"/>
@@ -17371,12 +17814,13 @@
       <c r="V350" s="3"/>
       <c r="W350" s="3"/>
       <c r="X350" s="3"/>
-      <c r="Y350" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="351" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y350" s="3"/>
+      <c r="Z350" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="351" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A351" s="2"/>
       <c r="B351" s="3"/>
       <c r="C351" s="3"/>
@@ -17401,12 +17845,13 @@
       <c r="V351" s="3"/>
       <c r="W351" s="3"/>
       <c r="X351" s="3"/>
-      <c r="Y351" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="352" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y351" s="3"/>
+      <c r="Z351" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="352" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A352" s="2"/>
       <c r="B352" s="3"/>
       <c r="C352" s="3"/>
@@ -17431,12 +17876,13 @@
       <c r="V352" s="3"/>
       <c r="W352" s="3"/>
       <c r="X352" s="3"/>
-      <c r="Y352" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="353" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y352" s="3"/>
+      <c r="Z352" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="353" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A353" s="2"/>
       <c r="B353" s="3"/>
       <c r="C353" s="3"/>
@@ -17461,12 +17907,13 @@
       <c r="V353" s="3"/>
       <c r="W353" s="3"/>
       <c r="X353" s="3"/>
-      <c r="Y353" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="354" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y353" s="3"/>
+      <c r="Z353" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="354" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A354" s="2"/>
       <c r="B354" s="3"/>
       <c r="C354" s="3"/>
@@ -17491,12 +17938,13 @@
       <c r="V354" s="3"/>
       <c r="W354" s="3"/>
       <c r="X354" s="3"/>
-      <c r="Y354" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="355" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y354" s="3"/>
+      <c r="Z354" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="355" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A355" s="2"/>
       <c r="B355" s="3"/>
       <c r="C355" s="3"/>
@@ -17521,12 +17969,13 @@
       <c r="V355" s="3"/>
       <c r="W355" s="3"/>
       <c r="X355" s="3"/>
-      <c r="Y355" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="356" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y355" s="3"/>
+      <c r="Z355" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="356" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A356" s="2"/>
       <c r="B356" s="3"/>
       <c r="C356" s="3"/>
@@ -17551,12 +18000,13 @@
       <c r="V356" s="3"/>
       <c r="W356" s="3"/>
       <c r="X356" s="3"/>
-      <c r="Y356" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="357" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y356" s="3"/>
+      <c r="Z356" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="357" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A357" s="2"/>
       <c r="B357" s="3"/>
       <c r="C357" s="3"/>
@@ -17581,12 +18031,13 @@
       <c r="V357" s="3"/>
       <c r="W357" s="3"/>
       <c r="X357" s="3"/>
-      <c r="Y357" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="358" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y357" s="3"/>
+      <c r="Z357" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="358" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A358" s="2"/>
       <c r="B358" s="3"/>
       <c r="C358" s="3"/>
@@ -17611,12 +18062,13 @@
       <c r="V358" s="3"/>
       <c r="W358" s="3"/>
       <c r="X358" s="3"/>
-      <c r="Y358" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="359" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y358" s="3"/>
+      <c r="Z358" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="359" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A359" s="2"/>
       <c r="B359" s="3"/>
       <c r="C359" s="3"/>
@@ -17641,12 +18093,13 @@
       <c r="V359" s="3"/>
       <c r="W359" s="3"/>
       <c r="X359" s="3"/>
-      <c r="Y359" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="360" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y359" s="3"/>
+      <c r="Z359" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="360" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A360" s="2"/>
       <c r="B360" s="3"/>
       <c r="C360" s="3"/>
@@ -17671,12 +18124,13 @@
       <c r="V360" s="3"/>
       <c r="W360" s="3"/>
       <c r="X360" s="3"/>
-      <c r="Y360" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="361" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y360" s="3"/>
+      <c r="Z360" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="361" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A361" s="2"/>
       <c r="B361" s="3"/>
       <c r="C361" s="3"/>
@@ -17701,12 +18155,13 @@
       <c r="V361" s="3"/>
       <c r="W361" s="3"/>
       <c r="X361" s="3"/>
-      <c r="Y361" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="362" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y361" s="3"/>
+      <c r="Z361" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="362" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A362" s="2"/>
       <c r="B362" s="3"/>
       <c r="C362" s="3"/>
@@ -17731,12 +18186,13 @@
       <c r="V362" s="3"/>
       <c r="W362" s="3"/>
       <c r="X362" s="3"/>
-      <c r="Y362" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="363" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y362" s="3"/>
+      <c r="Z362" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="363" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A363" s="2"/>
       <c r="B363" s="3"/>
       <c r="C363" s="3"/>
@@ -17761,12 +18217,13 @@
       <c r="V363" s="3"/>
       <c r="W363" s="3"/>
       <c r="X363" s="3"/>
-      <c r="Y363" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="364" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y363" s="3"/>
+      <c r="Z363" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="364" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A364" s="2"/>
       <c r="B364" s="3"/>
       <c r="C364" s="3"/>
@@ -17791,12 +18248,13 @@
       <c r="V364" s="3"/>
       <c r="W364" s="3"/>
       <c r="X364" s="3"/>
-      <c r="Y364" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="365" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y364" s="3"/>
+      <c r="Z364" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="365" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A365" s="2"/>
       <c r="B365" s="3"/>
       <c r="C365" s="3"/>
@@ -17821,12 +18279,13 @@
       <c r="V365" s="3"/>
       <c r="W365" s="3"/>
       <c r="X365" s="3"/>
-      <c r="Y365" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="366" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y365" s="3"/>
+      <c r="Z365" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="366" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A366" s="2"/>
       <c r="B366" s="3"/>
       <c r="C366" s="3"/>
@@ -17851,12 +18310,13 @@
       <c r="V366" s="3"/>
       <c r="W366" s="3"/>
       <c r="X366" s="3"/>
-      <c r="Y366" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="367" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y366" s="3"/>
+      <c r="Z366" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="367" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A367" s="2"/>
       <c r="B367" s="3"/>
       <c r="C367" s="3"/>
@@ -17881,12 +18341,13 @@
       <c r="V367" s="3"/>
       <c r="W367" s="3"/>
       <c r="X367" s="3"/>
-      <c r="Y367" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="368" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y367" s="3"/>
+      <c r="Z367" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="368" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A368" s="2"/>
       <c r="B368" s="3"/>
       <c r="C368" s="3"/>
@@ -17911,12 +18372,13 @@
       <c r="V368" s="3"/>
       <c r="W368" s="3"/>
       <c r="X368" s="3"/>
-      <c r="Y368" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="369" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y368" s="3"/>
+      <c r="Z368" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="369" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A369" s="2"/>
       <c r="B369" s="3"/>
       <c r="C369" s="3"/>
@@ -17941,12 +18403,13 @@
       <c r="V369" s="3"/>
       <c r="W369" s="3"/>
       <c r="X369" s="3"/>
-      <c r="Y369" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="370" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y369" s="3"/>
+      <c r="Z369" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="370" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A370" s="2"/>
       <c r="B370" s="3"/>
       <c r="C370" s="3"/>
@@ -17971,12 +18434,13 @@
       <c r="V370" s="3"/>
       <c r="W370" s="3"/>
       <c r="X370" s="3"/>
-      <c r="Y370" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="371" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y370" s="3"/>
+      <c r="Z370" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="371" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A371" s="2"/>
       <c r="B371" s="3"/>
       <c r="C371" s="3"/>
@@ -18001,12 +18465,13 @@
       <c r="V371" s="3"/>
       <c r="W371" s="3"/>
       <c r="X371" s="3"/>
-      <c r="Y371" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="372" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y371" s="3"/>
+      <c r="Z371" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="372" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A372" s="2"/>
       <c r="B372" s="3"/>
       <c r="C372" s="3"/>
@@ -18031,12 +18496,13 @@
       <c r="V372" s="3"/>
       <c r="W372" s="3"/>
       <c r="X372" s="3"/>
-      <c r="Y372" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="373" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y372" s="3"/>
+      <c r="Z372" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="373" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A373" s="2"/>
       <c r="B373" s="3"/>
       <c r="C373" s="3"/>
@@ -18061,12 +18527,13 @@
       <c r="V373" s="3"/>
       <c r="W373" s="3"/>
       <c r="X373" s="3"/>
-      <c r="Y373" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="374" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y373" s="3"/>
+      <c r="Z373" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="374" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A374" s="2"/>
       <c r="B374" s="3"/>
       <c r="C374" s="3"/>
@@ -18091,12 +18558,13 @@
       <c r="V374" s="3"/>
       <c r="W374" s="3"/>
       <c r="X374" s="3"/>
-      <c r="Y374" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="375" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y374" s="3"/>
+      <c r="Z374" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="375" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A375" s="2"/>
       <c r="B375" s="3"/>
       <c r="C375" s="3"/>
@@ -18121,12 +18589,13 @@
       <c r="V375" s="3"/>
       <c r="W375" s="3"/>
       <c r="X375" s="3"/>
-      <c r="Y375" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="376" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y375" s="3"/>
+      <c r="Z375" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="376" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A376" s="2"/>
       <c r="B376" s="3"/>
       <c r="C376" s="3"/>
@@ -18151,12 +18620,13 @@
       <c r="V376" s="3"/>
       <c r="W376" s="3"/>
       <c r="X376" s="3"/>
-      <c r="Y376" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="377" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y376" s="3"/>
+      <c r="Z376" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="377" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A377" s="2"/>
       <c r="B377" s="3"/>
       <c r="C377" s="3"/>
@@ -18181,12 +18651,13 @@
       <c r="V377" s="3"/>
       <c r="W377" s="3"/>
       <c r="X377" s="3"/>
-      <c r="Y377" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="378" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y377" s="3"/>
+      <c r="Z377" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="378" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A378" s="2"/>
       <c r="B378" s="3"/>
       <c r="C378" s="3"/>
@@ -18211,12 +18682,13 @@
       <c r="V378" s="3"/>
       <c r="W378" s="3"/>
       <c r="X378" s="3"/>
-      <c r="Y378" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="379" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y378" s="3"/>
+      <c r="Z378" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="379" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A379" s="2"/>
       <c r="B379" s="3"/>
       <c r="C379" s="3"/>
@@ -18241,12 +18713,13 @@
       <c r="V379" s="3"/>
       <c r="W379" s="3"/>
       <c r="X379" s="3"/>
-      <c r="Y379" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="380" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y379" s="3"/>
+      <c r="Z379" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="380" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A380" s="2"/>
       <c r="B380" s="3"/>
       <c r="C380" s="3"/>
@@ -18271,12 +18744,13 @@
       <c r="V380" s="3"/>
       <c r="W380" s="3"/>
       <c r="X380" s="3"/>
-      <c r="Y380" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="381" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y380" s="3"/>
+      <c r="Z380" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="381" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A381" s="2"/>
       <c r="B381" s="3"/>
       <c r="C381" s="3"/>
@@ -18301,12 +18775,13 @@
       <c r="V381" s="3"/>
       <c r="W381" s="3"/>
       <c r="X381" s="3"/>
-      <c r="Y381" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="382" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y381" s="3"/>
+      <c r="Z381" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="382" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A382" s="2"/>
       <c r="B382" s="3"/>
       <c r="C382" s="3"/>
@@ -18331,12 +18806,13 @@
       <c r="V382" s="3"/>
       <c r="W382" s="3"/>
       <c r="X382" s="3"/>
-      <c r="Y382" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="383" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y382" s="3"/>
+      <c r="Z382" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="383" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A383" s="2"/>
       <c r="B383" s="3"/>
       <c r="C383" s="3"/>
@@ -18361,12 +18837,13 @@
       <c r="V383" s="3"/>
       <c r="W383" s="3"/>
       <c r="X383" s="3"/>
-      <c r="Y383" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="384" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y383" s="3"/>
+      <c r="Z383" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="384" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A384" s="2"/>
       <c r="B384" s="3"/>
       <c r="C384" s="3"/>
@@ -18391,12 +18868,13 @@
       <c r="V384" s="3"/>
       <c r="W384" s="3"/>
       <c r="X384" s="3"/>
-      <c r="Y384" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="385" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y384" s="3"/>
+      <c r="Z384" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="385" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A385" s="2"/>
       <c r="B385" s="3"/>
       <c r="C385" s="3"/>
@@ -18421,12 +18899,13 @@
       <c r="V385" s="3"/>
       <c r="W385" s="3"/>
       <c r="X385" s="3"/>
-      <c r="Y385" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="386" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y385" s="3"/>
+      <c r="Z385" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="386" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A386" s="2"/>
       <c r="B386" s="3"/>
       <c r="C386" s="3"/>
@@ -18451,12 +18930,13 @@
       <c r="V386" s="3"/>
       <c r="W386" s="3"/>
       <c r="X386" s="3"/>
-      <c r="Y386" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="387" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y386" s="3"/>
+      <c r="Z386" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="387" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A387" s="2"/>
       <c r="B387" s="3"/>
       <c r="C387" s="3"/>
@@ -18481,12 +18961,13 @@
       <c r="V387" s="3"/>
       <c r="W387" s="3"/>
       <c r="X387" s="3"/>
-      <c r="Y387" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="388" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y387" s="3"/>
+      <c r="Z387" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="388" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A388" s="2"/>
       <c r="B388" s="3"/>
       <c r="C388" s="3"/>
@@ -18511,12 +18992,13 @@
       <c r="V388" s="3"/>
       <c r="W388" s="3"/>
       <c r="X388" s="3"/>
-      <c r="Y388" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="389" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y388" s="3"/>
+      <c r="Z388" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="389" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A389" s="2"/>
       <c r="B389" s="3"/>
       <c r="C389" s="3"/>
@@ -18541,12 +19023,13 @@
       <c r="V389" s="3"/>
       <c r="W389" s="3"/>
       <c r="X389" s="3"/>
-      <c r="Y389" s="4" t="str">
-        <f t="shared" ref="Y389:Y452" si="6">IF(COUNTA(B389:X389)=0,"",AVERAGE(B389:X389))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="390" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y389" s="3"/>
+      <c r="Z389" s="4" t="str">
+        <f t="shared" ref="Z389:Z390" si="7">IF(COUNTA(B389:Y389)=0,"",AVERAGE(B389:Y389))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="390" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A390" s="2"/>
       <c r="B390" s="3"/>
       <c r="C390" s="3"/>
@@ -18571,20 +19054,21 @@
       <c r="V390" s="3"/>
       <c r="W390" s="3"/>
       <c r="X390" s="3"/>
-      <c r="Y390" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="392" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y390" s="3"/>
+      <c r="Z390" s="4" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+    </row>
+    <row r="392" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A392" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A1:Y1"/>
-    <mergeCell ref="A2:Y2"/>
+    <mergeCell ref="A1:Z1"/>
+    <mergeCell ref="A2:Z2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing r:id="rId1"/>
@@ -18603,7 +19087,7 @@
   <sheetData>
     <row r="1" spans="1:21" ht="24" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B1" s="7"/>
       <c r="C1" s="7"/>
@@ -18659,7 +19143,7 @@
         <v>3</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>4</v>
@@ -18671,7 +19155,7 @@
         <v>7</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H4" s="1" t="s">
         <v>15</v>
@@ -18683,7 +19167,7 @@
         <v>11</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L4" s="1" t="s">
         <v>19</v>
@@ -18692,28 +19176,28 @@
         <v>12</v>
       </c>
       <c r="N4" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="O4" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="P4" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q4" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="R4" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="O4" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="P4" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q4" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="R4" s="1" t="s">
-        <v>21</v>
-      </c>
       <c r="S4" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="T4" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="U4" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5" spans="1:21" x14ac:dyDescent="0.25">
@@ -19641,29 +20125,69 @@
       </c>
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A19" s="2"/>
-      <c r="B19" s="3"/>
-      <c r="C19" s="3"/>
-      <c r="D19" s="3"/>
-      <c r="E19" s="3"/>
-      <c r="F19" s="3"/>
-      <c r="G19" s="3"/>
-      <c r="H19" s="3"/>
-      <c r="I19" s="3"/>
-      <c r="J19" s="3"/>
-      <c r="K19" s="3"/>
-      <c r="L19" s="3"/>
-      <c r="M19" s="3"/>
-      <c r="N19" s="3"/>
-      <c r="O19" s="3"/>
-      <c r="P19" s="3"/>
-      <c r="Q19" s="3"/>
-      <c r="R19" s="3"/>
-      <c r="S19" s="3"/>
-      <c r="T19" s="3"/>
-      <c r="U19" s="4" t="str">
+      <c r="A19" s="2">
+        <v>46146</v>
+      </c>
+      <c r="B19" s="3">
+        <v>4.29</v>
+      </c>
+      <c r="C19" s="3">
+        <v>3.95</v>
+      </c>
+      <c r="D19" s="3">
+        <v>3.39</v>
+      </c>
+      <c r="E19" s="3">
+        <v>3.8</v>
+      </c>
+      <c r="F19" s="3">
+        <v>4.3099999999999996</v>
+      </c>
+      <c r="G19" s="3">
+        <v>3.99</v>
+      </c>
+      <c r="H19" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="I19" s="3">
+        <v>3.39</v>
+      </c>
+      <c r="J19" s="3">
+        <v>3.09</v>
+      </c>
+      <c r="K19" s="3">
+        <v>3.99</v>
+      </c>
+      <c r="L19" s="3">
+        <v>3.19</v>
+      </c>
+      <c r="M19" s="3">
+        <v>3.79</v>
+      </c>
+      <c r="N19" s="3">
+        <v>2.4900000000000002</v>
+      </c>
+      <c r="O19" s="3">
+        <v>3.8</v>
+      </c>
+      <c r="P19" s="3">
+        <v>3.74</v>
+      </c>
+      <c r="Q19" s="3">
+        <v>4.03</v>
+      </c>
+      <c r="R19" s="3">
+        <v>3.79</v>
+      </c>
+      <c r="S19" s="3">
+        <v>3.99</v>
+      </c>
+      <c r="T19" s="3">
+        <v>1.99</v>
+      </c>
+      <c r="U19" s="4">
         <f t="shared" si="0"/>
-        <v/>
+        <v>3.5789473684210527</v>
       </c>
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
@@ -29314,7 +29838,7 @@
     </row>
     <row r="392" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A392" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -29339,7 +29863,7 @@
   <sheetData>
     <row r="1" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="8" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B1" s="7"/>
       <c r="C1" s="7"/>
@@ -29378,28 +29902,28 @@
         <v>10</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>15</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
@@ -29907,19 +30431,39 @@
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A19" s="2"/>
-      <c r="B19" s="3"/>
-      <c r="C19" s="3"/>
-      <c r="D19" s="3"/>
-      <c r="E19" s="3"/>
-      <c r="F19" s="3"/>
-      <c r="G19" s="3"/>
-      <c r="H19" s="3"/>
-      <c r="I19" s="3"/>
-      <c r="J19" s="3"/>
-      <c r="K19" s="4" t="str">
+      <c r="A19" s="2">
+        <v>46146</v>
+      </c>
+      <c r="B19" s="3">
+        <v>2.85</v>
+      </c>
+      <c r="C19" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="D19" s="3">
+        <v>2.67</v>
+      </c>
+      <c r="E19" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="F19" s="3">
+        <v>2.8</v>
+      </c>
+      <c r="G19" s="3">
+        <v>2.96</v>
+      </c>
+      <c r="H19" s="3">
+        <v>2.63</v>
+      </c>
+      <c r="I19" s="3">
+        <v>2.79</v>
+      </c>
+      <c r="J19" s="3">
+        <v>2.59</v>
+      </c>
+      <c r="K19" s="4">
         <f t="shared" si="0"/>
-        <v/>
+        <v>2.8077777777777779</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.25">
@@ -35860,7 +36404,7 @@
     </row>
     <row r="392" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A392" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -35885,7 +36429,7 @@
   <sheetData>
     <row r="1" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="8" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B1" s="7"/>
       <c r="C1" s="7"/>
@@ -35923,34 +36467,34 @@
         <v>3</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E4" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="I4" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F4" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="H4" s="1" t="s">
+      <c r="J4" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="I4" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>33</v>
-      </c>
       <c r="K4" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
@@ -36500,20 +37044,42 @@
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A19" s="2"/>
-      <c r="B19" s="3"/>
-      <c r="C19" s="3"/>
-      <c r="D19" s="3"/>
-      <c r="E19" s="3"/>
-      <c r="F19" s="3"/>
-      <c r="G19" s="3"/>
-      <c r="H19" s="3"/>
-      <c r="I19" s="3"/>
-      <c r="J19" s="3"/>
-      <c r="K19" s="3"/>
-      <c r="L19" s="4" t="str">
+      <c r="A19" s="2">
+        <v>46146</v>
+      </c>
+      <c r="B19" s="3">
+        <v>3.55</v>
+      </c>
+      <c r="C19" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="D19" s="3">
+        <v>3.15</v>
+      </c>
+      <c r="E19" s="3">
+        <v>3.35</v>
+      </c>
+      <c r="F19" s="3">
+        <v>3.43</v>
+      </c>
+      <c r="G19" s="3">
+        <v>3.69</v>
+      </c>
+      <c r="H19" s="3">
+        <v>3.11</v>
+      </c>
+      <c r="I19" s="3">
+        <v>3.29</v>
+      </c>
+      <c r="J19" s="3">
+        <v>3.55</v>
+      </c>
+      <c r="K19" s="3">
+        <v>3.29</v>
+      </c>
+      <c r="L19" s="4">
         <f t="shared" si="0"/>
-        <v/>
+        <v>3.34</v>
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.25">
@@ -42825,7 +43391,7 @@
     </row>
     <row r="392" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A392" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>

--- a/app/mevduat-kredi-faizleri/data/hoca-ile-borsa-faiz-takip-sablonu-guncel.xlsx
+++ b/app/mevduat-kredi-faizleri/data/hoca-ile-borsa-faiz-takip-sablonu-guncel.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projeler\hoca-ile-borsa\app\mevduat-kredi-faizleri\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28E31E67-BFBB-4460-87DA-FCAFA7B97D70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13B9ED6B-512E-47DB-ACC7-7149410C8908}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="24240" yWindow="3540" windowWidth="14025" windowHeight="15345" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="16410" yWindow="3540" windowWidth="21855" windowHeight="15345" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Mevduat" sheetId="1" r:id="rId1"/>
@@ -386,6 +386,9 @@
                 <c:pt idx="14">
                   <c:v>46146</c:v>
                 </c:pt>
+                <c:pt idx="15">
+                  <c:v>46147</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -441,7 +444,7 @@
                   <c:v>43.534166666666671</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0</c:v>
+                  <c:v>43.502083333333331</c:v>
                 </c:pt>
                 <c:pt idx="16">
                   <c:v>0</c:v>
@@ -1757,6 +1760,9 @@
                 <c:pt idx="14">
                   <c:v>46146</c:v>
                 </c:pt>
+                <c:pt idx="15">
+                  <c:v>46147</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1812,7 +1818,7 @@
                   <c:v>3.5789473684210527</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0</c:v>
+                  <c:v>3.5684210526315789</c:v>
                 </c:pt>
                 <c:pt idx="16">
                   <c:v>0</c:v>
@@ -3128,6 +3134,9 @@
                 <c:pt idx="14">
                   <c:v>46146</c:v>
                 </c:pt>
+                <c:pt idx="15">
+                  <c:v>46147</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3183,7 +3192,7 @@
                   <c:v>2.8077777777777779</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0</c:v>
+                  <c:v>2.8077777777777779</c:v>
                 </c:pt>
                 <c:pt idx="16">
                   <c:v>0</c:v>
@@ -4499,6 +4508,9 @@
                 <c:pt idx="14">
                   <c:v>46146</c:v>
                 </c:pt>
+                <c:pt idx="15">
+                  <c:v>46147</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -4554,7 +4566,7 @@
                   <c:v>3.34</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0</c:v>
+                  <c:v>3.34</c:v>
                 </c:pt>
                 <c:pt idx="16">
                   <c:v>0</c:v>
@@ -7560,34 +7572,84 @@
       </c>
     </row>
     <row r="20" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A20" s="2"/>
-      <c r="B20" s="3"/>
-      <c r="C20" s="3"/>
-      <c r="D20" s="3"/>
-      <c r="E20" s="3"/>
-      <c r="F20" s="3"/>
-      <c r="G20" s="3"/>
-      <c r="H20" s="3"/>
-      <c r="I20" s="3"/>
-      <c r="J20" s="3"/>
-      <c r="K20" s="3"/>
-      <c r="L20" s="3"/>
-      <c r="M20" s="3"/>
-      <c r="N20" s="3"/>
-      <c r="O20" s="3"/>
-      <c r="P20" s="3"/>
-      <c r="Q20" s="3"/>
-      <c r="R20" s="3"/>
-      <c r="S20" s="3"/>
-      <c r="T20" s="3"/>
-      <c r="U20" s="3"/>
-      <c r="V20" s="3"/>
-      <c r="W20" s="3"/>
-      <c r="X20" s="3"/>
-      <c r="Y20" s="3"/>
-      <c r="Z20" s="4" t="str">
+      <c r="A20" s="2">
+        <v>46147</v>
+      </c>
+      <c r="B20" s="3">
+        <v>42</v>
+      </c>
+      <c r="C20" s="3">
+        <v>46</v>
+      </c>
+      <c r="D20" s="3">
+        <v>45</v>
+      </c>
+      <c r="E20" s="3">
+        <v>45</v>
+      </c>
+      <c r="F20" s="3">
+        <v>43.5</v>
+      </c>
+      <c r="G20" s="3">
+        <v>41.5</v>
+      </c>
+      <c r="H20" s="3">
+        <v>46</v>
+      </c>
+      <c r="I20" s="3">
+        <v>41.5</v>
+      </c>
+      <c r="J20" s="3">
+        <v>43</v>
+      </c>
+      <c r="K20" s="3">
+        <v>41</v>
+      </c>
+      <c r="L20" s="3">
+        <v>36</v>
+      </c>
+      <c r="M20" s="3">
+        <v>44</v>
+      </c>
+      <c r="N20" s="3">
+        <v>45</v>
+      </c>
+      <c r="O20" s="3">
+        <v>42.8</v>
+      </c>
+      <c r="P20" s="3">
+        <v>40</v>
+      </c>
+      <c r="Q20" s="3">
+        <v>45</v>
+      </c>
+      <c r="R20" s="3">
+        <v>45</v>
+      </c>
+      <c r="S20" s="3">
+        <v>45</v>
+      </c>
+      <c r="T20" s="3">
+        <v>45</v>
+      </c>
+      <c r="U20" s="3">
+        <v>43.5</v>
+      </c>
+      <c r="V20" s="3">
+        <v>44</v>
+      </c>
+      <c r="W20" s="3">
+        <v>42</v>
+      </c>
+      <c r="X20" s="3">
+        <v>47</v>
+      </c>
+      <c r="Y20" s="3">
+        <v>45.25</v>
+      </c>
+      <c r="Z20" s="4">
         <f t="shared" si="0"/>
-        <v/>
+        <v>43.502083333333331</v>
       </c>
     </row>
     <row r="21" spans="1:26" x14ac:dyDescent="0.25">
@@ -20191,29 +20253,69 @@
       </c>
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A20" s="2"/>
-      <c r="B20" s="3"/>
-      <c r="C20" s="3"/>
-      <c r="D20" s="3"/>
-      <c r="E20" s="3"/>
-      <c r="F20" s="3"/>
-      <c r="G20" s="3"/>
-      <c r="H20" s="3"/>
-      <c r="I20" s="3"/>
-      <c r="J20" s="3"/>
-      <c r="K20" s="3"/>
-      <c r="L20" s="3"/>
-      <c r="M20" s="3"/>
-      <c r="N20" s="3"/>
-      <c r="O20" s="3"/>
-      <c r="P20" s="3"/>
-      <c r="Q20" s="3"/>
-      <c r="R20" s="3"/>
-      <c r="S20" s="3"/>
-      <c r="T20" s="3"/>
-      <c r="U20" s="4" t="str">
+      <c r="A20" s="2">
+        <v>46147</v>
+      </c>
+      <c r="B20" s="3">
+        <v>4.29</v>
+      </c>
+      <c r="C20" s="3">
+        <v>3.95</v>
+      </c>
+      <c r="D20" s="3">
+        <v>3.39</v>
+      </c>
+      <c r="E20" s="3">
+        <v>3.8</v>
+      </c>
+      <c r="F20" s="3">
+        <v>4.3099999999999996</v>
+      </c>
+      <c r="G20" s="3">
+        <v>3.99</v>
+      </c>
+      <c r="H20" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="I20" s="3">
+        <v>3.39</v>
+      </c>
+      <c r="J20" s="3">
+        <v>3.09</v>
+      </c>
+      <c r="K20" s="3">
+        <v>3.99</v>
+      </c>
+      <c r="L20" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="M20" s="3">
+        <v>3.79</v>
+      </c>
+      <c r="N20" s="3">
+        <v>2.4900000000000002</v>
+      </c>
+      <c r="O20" s="3">
+        <v>3.8</v>
+      </c>
+      <c r="P20" s="3">
+        <v>3.74</v>
+      </c>
+      <c r="Q20" s="3">
+        <v>4.03</v>
+      </c>
+      <c r="R20" s="3">
+        <v>3.79</v>
+      </c>
+      <c r="S20" s="3">
+        <v>3.99</v>
+      </c>
+      <c r="T20" s="3">
+        <v>1.99</v>
+      </c>
+      <c r="U20" s="4">
         <f t="shared" si="0"/>
-        <v/>
+        <v>3.5684210526315789</v>
       </c>
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
@@ -30467,19 +30569,39 @@
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A20" s="2"/>
-      <c r="B20" s="3"/>
-      <c r="C20" s="3"/>
-      <c r="D20" s="3"/>
-      <c r="E20" s="3"/>
-      <c r="F20" s="3"/>
-      <c r="G20" s="3"/>
-      <c r="H20" s="3"/>
-      <c r="I20" s="3"/>
-      <c r="J20" s="3"/>
-      <c r="K20" s="4" t="str">
+      <c r="A20" s="2">
+        <v>46147</v>
+      </c>
+      <c r="B20" s="3">
+        <v>2.85</v>
+      </c>
+      <c r="C20" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="D20" s="3">
+        <v>2.67</v>
+      </c>
+      <c r="E20" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="F20" s="3">
+        <v>2.8</v>
+      </c>
+      <c r="G20" s="3">
+        <v>2.96</v>
+      </c>
+      <c r="H20" s="3">
+        <v>2.63</v>
+      </c>
+      <c r="I20" s="3">
+        <v>2.79</v>
+      </c>
+      <c r="J20" s="3">
+        <v>2.59</v>
+      </c>
+      <c r="K20" s="4">
         <f t="shared" si="0"/>
-        <v/>
+        <v>2.8077777777777779</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.25">
@@ -37083,20 +37205,42 @@
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A20" s="2"/>
-      <c r="B20" s="3"/>
-      <c r="C20" s="3"/>
-      <c r="D20" s="3"/>
-      <c r="E20" s="3"/>
-      <c r="F20" s="3"/>
-      <c r="G20" s="3"/>
-      <c r="H20" s="3"/>
-      <c r="I20" s="3"/>
-      <c r="J20" s="3"/>
-      <c r="K20" s="3"/>
-      <c r="L20" s="4" t="str">
+      <c r="A20" s="2">
+        <v>46147</v>
+      </c>
+      <c r="B20" s="3">
+        <v>3.55</v>
+      </c>
+      <c r="C20" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="D20" s="3">
+        <v>3.15</v>
+      </c>
+      <c r="E20" s="3">
+        <v>3.35</v>
+      </c>
+      <c r="F20" s="3">
+        <v>3.43</v>
+      </c>
+      <c r="G20" s="3">
+        <v>3.69</v>
+      </c>
+      <c r="H20" s="3">
+        <v>3.11</v>
+      </c>
+      <c r="I20" s="3">
+        <v>3.29</v>
+      </c>
+      <c r="J20" s="3">
+        <v>3.55</v>
+      </c>
+      <c r="K20" s="3">
+        <v>3.29</v>
+      </c>
+      <c r="L20" s="4">
         <f t="shared" si="0"/>
-        <v/>
+        <v>3.34</v>
       </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">

--- a/app/mevduat-kredi-faizleri/data/hoca-ile-borsa-faiz-takip-sablonu-guncel.xlsx
+++ b/app/mevduat-kredi-faizleri/data/hoca-ile-borsa-faiz-takip-sablonu-guncel.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projeler\hoca-ile-borsa\app\mevduat-kredi-faizleri\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13B9ED6B-512E-47DB-ACC7-7149410C8908}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5C2727B-AED6-4F1B-BB0A-0880CCF419D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="16410" yWindow="3540" windowWidth="21855" windowHeight="15345" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19350" yWindow="3540" windowWidth="18915" windowHeight="15345" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Mevduat" sheetId="1" r:id="rId1"/>
@@ -389,6 +389,9 @@
                 <c:pt idx="15">
                   <c:v>46147</c:v>
                 </c:pt>
+                <c:pt idx="16">
+                  <c:v>46148</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -447,7 +450,7 @@
                   <c:v>43.502083333333331</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0</c:v>
+                  <c:v>43.491666666666667</c:v>
                 </c:pt>
                 <c:pt idx="17">
                   <c:v>0</c:v>
@@ -1763,6 +1766,9 @@
                 <c:pt idx="15">
                   <c:v>46147</c:v>
                 </c:pt>
+                <c:pt idx="16">
+                  <c:v>46148</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1821,7 +1827,7 @@
                   <c:v>3.5684210526315789</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0</c:v>
+                  <c:v>3.513157894736842</c:v>
                 </c:pt>
                 <c:pt idx="17">
                   <c:v>0</c:v>
@@ -3137,6 +3143,9 @@
                 <c:pt idx="15">
                   <c:v>46147</c:v>
                 </c:pt>
+                <c:pt idx="16">
+                  <c:v>46148</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3195,7 +3204,7 @@
                   <c:v>2.8077777777777779</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0</c:v>
+                  <c:v>2.8077777777777779</c:v>
                 </c:pt>
                 <c:pt idx="17">
                   <c:v>0</c:v>
@@ -4511,6 +4520,9 @@
                 <c:pt idx="15">
                   <c:v>46147</c:v>
                 </c:pt>
+                <c:pt idx="16">
+                  <c:v>46148</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -4569,7 +4581,7 @@
                   <c:v>3.34</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0</c:v>
+                  <c:v>3.34</c:v>
                 </c:pt>
                 <c:pt idx="17">
                   <c:v>0</c:v>
@@ -7653,34 +7665,84 @@
       </c>
     </row>
     <row r="21" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A21" s="2"/>
-      <c r="B21" s="3"/>
-      <c r="C21" s="3"/>
-      <c r="D21" s="3"/>
-      <c r="E21" s="3"/>
-      <c r="F21" s="3"/>
-      <c r="G21" s="3"/>
-      <c r="H21" s="3"/>
-      <c r="I21" s="3"/>
-      <c r="J21" s="3"/>
-      <c r="K21" s="3"/>
-      <c r="L21" s="3"/>
-      <c r="M21" s="3"/>
-      <c r="N21" s="3"/>
-      <c r="O21" s="3"/>
-      <c r="P21" s="3"/>
-      <c r="Q21" s="3"/>
-      <c r="R21" s="3"/>
-      <c r="S21" s="3"/>
-      <c r="T21" s="3"/>
-      <c r="U21" s="3"/>
-      <c r="V21" s="3"/>
-      <c r="W21" s="3"/>
-      <c r="X21" s="3"/>
-      <c r="Y21" s="3"/>
-      <c r="Z21" s="4" t="str">
+      <c r="A21" s="2">
+        <v>46148</v>
+      </c>
+      <c r="B21" s="3">
+        <v>42</v>
+      </c>
+      <c r="C21" s="3">
+        <v>46</v>
+      </c>
+      <c r="D21" s="3">
+        <v>45</v>
+      </c>
+      <c r="E21" s="3">
+        <v>45</v>
+      </c>
+      <c r="F21" s="3">
+        <v>43.5</v>
+      </c>
+      <c r="G21" s="3">
+        <v>41.5</v>
+      </c>
+      <c r="H21" s="3">
+        <v>46</v>
+      </c>
+      <c r="I21" s="3">
+        <v>41.5</v>
+      </c>
+      <c r="J21" s="3">
+        <v>43</v>
+      </c>
+      <c r="K21" s="3">
+        <v>41</v>
+      </c>
+      <c r="L21" s="3">
+        <v>36</v>
+      </c>
+      <c r="M21" s="3">
+        <v>44</v>
+      </c>
+      <c r="N21" s="3">
+        <v>45</v>
+      </c>
+      <c r="O21" s="3">
+        <v>42.8</v>
+      </c>
+      <c r="P21" s="3">
+        <v>40</v>
+      </c>
+      <c r="Q21" s="3">
+        <v>45</v>
+      </c>
+      <c r="R21" s="3">
+        <v>45</v>
+      </c>
+      <c r="S21" s="3">
+        <v>45</v>
+      </c>
+      <c r="T21" s="3">
+        <v>45</v>
+      </c>
+      <c r="U21" s="3">
+        <v>43.5</v>
+      </c>
+      <c r="V21" s="3">
+        <v>43.75</v>
+      </c>
+      <c r="W21" s="3">
+        <v>42</v>
+      </c>
+      <c r="X21" s="3">
+        <v>47</v>
+      </c>
+      <c r="Y21" s="3">
+        <v>45.25</v>
+      </c>
+      <c r="Z21" s="4">
         <f t="shared" si="0"/>
-        <v/>
+        <v>43.491666666666667</v>
       </c>
     </row>
     <row r="22" spans="1:26" x14ac:dyDescent="0.25">
@@ -20319,29 +20381,69 @@
       </c>
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A21" s="2"/>
-      <c r="B21" s="3"/>
-      <c r="C21" s="3"/>
-      <c r="D21" s="3"/>
-      <c r="E21" s="3"/>
-      <c r="F21" s="3"/>
-      <c r="G21" s="3"/>
-      <c r="H21" s="3"/>
-      <c r="I21" s="3"/>
-      <c r="J21" s="3"/>
-      <c r="K21" s="3"/>
-      <c r="L21" s="3"/>
-      <c r="M21" s="3"/>
-      <c r="N21" s="3"/>
-      <c r="O21" s="3"/>
-      <c r="P21" s="3"/>
-      <c r="Q21" s="3"/>
-      <c r="R21" s="3"/>
-      <c r="S21" s="3"/>
-      <c r="T21" s="3"/>
-      <c r="U21" s="4" t="str">
+      <c r="A21" s="2">
+        <v>46148</v>
+      </c>
+      <c r="B21" s="3">
+        <v>3.64</v>
+      </c>
+      <c r="C21" s="3">
+        <v>3.95</v>
+      </c>
+      <c r="D21" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="E21" s="3">
+        <v>3.8</v>
+      </c>
+      <c r="F21" s="3">
+        <v>4.3099999999999996</v>
+      </c>
+      <c r="G21" s="3">
+        <v>3.99</v>
+      </c>
+      <c r="H21" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="I21" s="3">
+        <v>3.39</v>
+      </c>
+      <c r="J21" s="3">
+        <v>3.09</v>
+      </c>
+      <c r="K21" s="3">
+        <v>3.99</v>
+      </c>
+      <c r="L21" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="M21" s="3">
+        <v>3.79</v>
+      </c>
+      <c r="N21" s="3">
+        <v>2.4900000000000002</v>
+      </c>
+      <c r="O21" s="3">
+        <v>3.8</v>
+      </c>
+      <c r="P21" s="3">
+        <v>3.74</v>
+      </c>
+      <c r="Q21" s="3">
+        <v>4.03</v>
+      </c>
+      <c r="R21" s="3">
+        <v>3.79</v>
+      </c>
+      <c r="S21" s="3">
+        <v>3.99</v>
+      </c>
+      <c r="T21" s="3">
+        <v>1.99</v>
+      </c>
+      <c r="U21" s="4">
         <f t="shared" si="0"/>
-        <v/>
+        <v>3.513157894736842</v>
       </c>
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
@@ -30605,19 +30707,39 @@
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A21" s="2"/>
-      <c r="B21" s="3"/>
-      <c r="C21" s="3"/>
-      <c r="D21" s="3"/>
-      <c r="E21" s="3"/>
-      <c r="F21" s="3"/>
-      <c r="G21" s="3"/>
-      <c r="H21" s="3"/>
-      <c r="I21" s="3"/>
-      <c r="J21" s="3"/>
-      <c r="K21" s="4" t="str">
+      <c r="A21" s="2">
+        <v>46148</v>
+      </c>
+      <c r="B21" s="3">
+        <v>2.85</v>
+      </c>
+      <c r="C21" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="D21" s="3">
+        <v>2.67</v>
+      </c>
+      <c r="E21" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="F21" s="3">
+        <v>2.8</v>
+      </c>
+      <c r="G21" s="3">
+        <v>2.96</v>
+      </c>
+      <c r="H21" s="3">
+        <v>2.63</v>
+      </c>
+      <c r="I21" s="3">
+        <v>2.79</v>
+      </c>
+      <c r="J21" s="3">
+        <v>2.59</v>
+      </c>
+      <c r="K21" s="4">
         <f t="shared" si="0"/>
-        <v/>
+        <v>2.8077777777777779</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.25">
@@ -37244,20 +37366,42 @@
       </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A21" s="2"/>
-      <c r="B21" s="3"/>
-      <c r="C21" s="3"/>
-      <c r="D21" s="3"/>
-      <c r="E21" s="3"/>
-      <c r="F21" s="3"/>
-      <c r="G21" s="3"/>
-      <c r="H21" s="3"/>
-      <c r="I21" s="3"/>
-      <c r="J21" s="3"/>
-      <c r="K21" s="3"/>
-      <c r="L21" s="4" t="str">
+      <c r="A21" s="2">
+        <v>46148</v>
+      </c>
+      <c r="B21" s="3">
+        <v>3.55</v>
+      </c>
+      <c r="C21" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="D21" s="3">
+        <v>3.15</v>
+      </c>
+      <c r="E21" s="3">
+        <v>3.35</v>
+      </c>
+      <c r="F21" s="3">
+        <v>3.43</v>
+      </c>
+      <c r="G21" s="3">
+        <v>3.69</v>
+      </c>
+      <c r="H21" s="3">
+        <v>3.11</v>
+      </c>
+      <c r="I21" s="3">
+        <v>3.29</v>
+      </c>
+      <c r="J21" s="3">
+        <v>3.55</v>
+      </c>
+      <c r="K21" s="3">
+        <v>3.29</v>
+      </c>
+      <c r="L21" s="4">
         <f t="shared" si="0"/>
-        <v/>
+        <v>3.34</v>
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">

--- a/app/mevduat-kredi-faizleri/data/hoca-ile-borsa-faiz-takip-sablonu-guncel.xlsx
+++ b/app/mevduat-kredi-faizleri/data/hoca-ile-borsa-faiz-takip-sablonu-guncel.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projeler\hoca-ile-borsa\app\mevduat-kredi-faizleri\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5C2727B-AED6-4F1B-BB0A-0880CCF419D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E31C2742-86B9-465E-9355-28584FDC7A18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="19350" yWindow="3540" windowWidth="18915" windowHeight="15345" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -392,6 +392,9 @@
                 <c:pt idx="16">
                   <c:v>46148</c:v>
                 </c:pt>
+                <c:pt idx="17">
+                  <c:v>46149</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -453,7 +456,7 @@
                   <c:v>43.491666666666667</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0</c:v>
+                  <c:v>43.460416666666667</c:v>
                 </c:pt>
                 <c:pt idx="18">
                   <c:v>0</c:v>
@@ -1769,6 +1772,9 @@
                 <c:pt idx="16">
                   <c:v>46148</c:v>
                 </c:pt>
+                <c:pt idx="17">
+                  <c:v>46149</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1830,7 +1836,7 @@
                   <c:v>3.513157894736842</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0</c:v>
+                  <c:v>3.5105263157894737</c:v>
                 </c:pt>
                 <c:pt idx="18">
                   <c:v>0</c:v>
@@ -3146,6 +3152,9 @@
                 <c:pt idx="16">
                   <c:v>46148</c:v>
                 </c:pt>
+                <c:pt idx="17">
+                  <c:v>46149</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3207,7 +3216,7 @@
                   <c:v>2.8077777777777779</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0</c:v>
+                  <c:v>2.8111111111111109</c:v>
                 </c:pt>
                 <c:pt idx="18">
                   <c:v>0</c:v>
@@ -4523,6 +4532,9 @@
                 <c:pt idx="16">
                   <c:v>46148</c:v>
                 </c:pt>
+                <c:pt idx="17">
+                  <c:v>46149</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -4584,7 +4596,7 @@
                   <c:v>3.34</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0</c:v>
+                  <c:v>3.3289999999999997</c:v>
                 </c:pt>
                 <c:pt idx="18">
                   <c:v>0</c:v>
@@ -7746,34 +7758,84 @@
       </c>
     </row>
     <row r="22" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A22" s="2"/>
-      <c r="B22" s="3"/>
-      <c r="C22" s="3"/>
-      <c r="D22" s="3"/>
-      <c r="E22" s="3"/>
-      <c r="F22" s="3"/>
-      <c r="G22" s="3"/>
-      <c r="H22" s="3"/>
-      <c r="I22" s="3"/>
-      <c r="J22" s="3"/>
-      <c r="K22" s="3"/>
-      <c r="L22" s="3"/>
-      <c r="M22" s="3"/>
-      <c r="N22" s="3"/>
-      <c r="O22" s="3"/>
-      <c r="P22" s="3"/>
-      <c r="Q22" s="3"/>
-      <c r="R22" s="3"/>
-      <c r="S22" s="3"/>
-      <c r="T22" s="3"/>
-      <c r="U22" s="3"/>
-      <c r="V22" s="3"/>
-      <c r="W22" s="3"/>
-      <c r="X22" s="3"/>
-      <c r="Y22" s="3"/>
-      <c r="Z22" s="4" t="str">
+      <c r="A22" s="2">
+        <v>46149</v>
+      </c>
+      <c r="B22" s="3">
+        <v>42</v>
+      </c>
+      <c r="C22" s="3">
+        <v>46</v>
+      </c>
+      <c r="D22" s="3">
+        <v>45</v>
+      </c>
+      <c r="E22" s="3">
+        <v>45</v>
+      </c>
+      <c r="F22" s="3">
+        <v>43.5</v>
+      </c>
+      <c r="G22" s="3">
+        <v>41.5</v>
+      </c>
+      <c r="H22" s="3">
+        <v>46</v>
+      </c>
+      <c r="I22" s="3">
+        <v>41.25</v>
+      </c>
+      <c r="J22" s="3">
+        <v>43</v>
+      </c>
+      <c r="K22" s="3">
+        <v>41</v>
+      </c>
+      <c r="L22" s="3">
+        <v>36</v>
+      </c>
+      <c r="M22" s="3">
+        <v>44</v>
+      </c>
+      <c r="N22" s="3">
+        <v>45</v>
+      </c>
+      <c r="O22" s="3">
+        <v>42.8</v>
+      </c>
+      <c r="P22" s="3">
+        <v>40</v>
+      </c>
+      <c r="Q22" s="3">
+        <v>45</v>
+      </c>
+      <c r="R22" s="3">
+        <v>45</v>
+      </c>
+      <c r="S22" s="3">
+        <v>45</v>
+      </c>
+      <c r="T22" s="3">
+        <v>45</v>
+      </c>
+      <c r="U22" s="3">
+        <v>43.5</v>
+      </c>
+      <c r="V22" s="3">
+        <v>43.25</v>
+      </c>
+      <c r="W22" s="3">
+        <v>42</v>
+      </c>
+      <c r="X22" s="3">
+        <v>47</v>
+      </c>
+      <c r="Y22" s="3">
+        <v>45.25</v>
+      </c>
+      <c r="Z22" s="4">
         <f t="shared" si="0"/>
-        <v/>
+        <v>43.460416666666667</v>
       </c>
     </row>
     <row r="23" spans="1:26" x14ac:dyDescent="0.25">
@@ -20447,29 +20509,69 @@
       </c>
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A22" s="2"/>
-      <c r="B22" s="3"/>
-      <c r="C22" s="3"/>
-      <c r="D22" s="3"/>
-      <c r="E22" s="3"/>
-      <c r="F22" s="3"/>
-      <c r="G22" s="3"/>
-      <c r="H22" s="3"/>
-      <c r="I22" s="3"/>
-      <c r="J22" s="3"/>
-      <c r="K22" s="3"/>
-      <c r="L22" s="3"/>
-      <c r="M22" s="3"/>
-      <c r="N22" s="3"/>
-      <c r="O22" s="3"/>
-      <c r="P22" s="3"/>
-      <c r="Q22" s="3"/>
-      <c r="R22" s="3"/>
-      <c r="S22" s="3"/>
-      <c r="T22" s="3"/>
-      <c r="U22" s="4" t="str">
+      <c r="A22" s="2">
+        <v>46149</v>
+      </c>
+      <c r="B22" s="3">
+        <v>3.64</v>
+      </c>
+      <c r="C22" s="3">
+        <v>3.95</v>
+      </c>
+      <c r="D22" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="E22" s="3">
+        <v>3.8</v>
+      </c>
+      <c r="F22" s="3">
+        <v>4.3099999999999996</v>
+      </c>
+      <c r="G22" s="3">
+        <v>3.99</v>
+      </c>
+      <c r="H22" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="I22" s="3">
+        <v>3.39</v>
+      </c>
+      <c r="J22" s="3">
+        <v>3.09</v>
+      </c>
+      <c r="K22" s="3">
+        <v>3.99</v>
+      </c>
+      <c r="L22" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="M22" s="3">
+        <v>3.59</v>
+      </c>
+      <c r="N22" s="3">
+        <v>2.4900000000000002</v>
+      </c>
+      <c r="O22" s="3">
+        <v>3.8</v>
+      </c>
+      <c r="P22" s="3">
+        <v>3.89</v>
+      </c>
+      <c r="Q22" s="3">
+        <v>4.03</v>
+      </c>
+      <c r="R22" s="3">
+        <v>3.79</v>
+      </c>
+      <c r="S22" s="3">
+        <v>3.99</v>
+      </c>
+      <c r="T22" s="3">
+        <v>1.99</v>
+      </c>
+      <c r="U22" s="4">
         <f t="shared" si="0"/>
-        <v/>
+        <v>3.5105263157894737</v>
       </c>
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
@@ -30743,19 +30845,39 @@
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A22" s="2"/>
-      <c r="B22" s="3"/>
-      <c r="C22" s="3"/>
-      <c r="D22" s="3"/>
-      <c r="E22" s="3"/>
-      <c r="F22" s="3"/>
-      <c r="G22" s="3"/>
-      <c r="H22" s="3"/>
-      <c r="I22" s="3"/>
-      <c r="J22" s="3"/>
-      <c r="K22" s="4" t="str">
+      <c r="A22" s="2">
+        <v>46149</v>
+      </c>
+      <c r="B22" s="3">
+        <v>2.85</v>
+      </c>
+      <c r="C22" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="D22" s="3">
+        <v>2.67</v>
+      </c>
+      <c r="E22" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="F22" s="3">
+        <v>2.8</v>
+      </c>
+      <c r="G22" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="H22" s="3">
+        <v>2.63</v>
+      </c>
+      <c r="I22" s="3">
+        <v>2.79</v>
+      </c>
+      <c r="J22" s="3">
+        <v>2.59</v>
+      </c>
+      <c r="K22" s="4">
         <f t="shared" si="0"/>
-        <v/>
+        <v>2.8111111111111109</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.25">
@@ -37405,20 +37527,42 @@
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A22" s="2"/>
-      <c r="B22" s="3"/>
-      <c r="C22" s="3"/>
-      <c r="D22" s="3"/>
-      <c r="E22" s="3"/>
-      <c r="F22" s="3"/>
-      <c r="G22" s="3"/>
-      <c r="H22" s="3"/>
-      <c r="I22" s="3"/>
-      <c r="J22" s="3"/>
-      <c r="K22" s="3"/>
-      <c r="L22" s="4" t="str">
+      <c r="A22" s="2">
+        <v>46149</v>
+      </c>
+      <c r="B22" s="3">
+        <v>3.55</v>
+      </c>
+      <c r="C22" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="D22" s="3">
+        <v>3.15</v>
+      </c>
+      <c r="E22" s="3">
+        <v>3.35</v>
+      </c>
+      <c r="F22" s="3">
+        <v>3.43</v>
+      </c>
+      <c r="G22" s="3">
+        <v>3.69</v>
+      </c>
+      <c r="H22" s="3">
+        <v>3.11</v>
+      </c>
+      <c r="I22" s="3">
+        <v>3.29</v>
+      </c>
+      <c r="J22" s="3">
+        <v>3.44</v>
+      </c>
+      <c r="K22" s="3">
+        <v>3.29</v>
+      </c>
+      <c r="L22" s="4">
         <f t="shared" si="0"/>
-        <v/>
+        <v>3.3289999999999997</v>
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">

--- a/app/mevduat-kredi-faizleri/data/hoca-ile-borsa-faiz-takip-sablonu-guncel.xlsx
+++ b/app/mevduat-kredi-faizleri/data/hoca-ile-borsa-faiz-takip-sablonu-guncel.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projeler\hoca-ile-borsa\app\mevduat-kredi-faizleri\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E31C2742-86B9-465E-9355-28584FDC7A18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B27109F9-1957-4BA5-8770-AA0C65E9991A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="19350" yWindow="3540" windowWidth="18915" windowHeight="15345" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -395,6 +395,9 @@
                 <c:pt idx="17">
                   <c:v>46149</c:v>
                 </c:pt>
+                <c:pt idx="18">
+                  <c:v>46150</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -459,7 +462,7 @@
                   <c:v>43.460416666666667</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0</c:v>
+                  <c:v>43.449999999999996</c:v>
                 </c:pt>
                 <c:pt idx="19">
                   <c:v>0</c:v>
@@ -1775,6 +1778,9 @@
                 <c:pt idx="17">
                   <c:v>46149</c:v>
                 </c:pt>
+                <c:pt idx="18">
+                  <c:v>46150</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1839,7 +1845,7 @@
                   <c:v>3.5105263157894737</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0</c:v>
+                  <c:v>3.5105263157894737</c:v>
                 </c:pt>
                 <c:pt idx="19">
                   <c:v>0</c:v>
@@ -3155,6 +3161,9 @@
                 <c:pt idx="17">
                   <c:v>46149</c:v>
                 </c:pt>
+                <c:pt idx="18">
+                  <c:v>46150</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3219,7 +3228,7 @@
                   <c:v>2.8111111111111109</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0</c:v>
+                  <c:v>2.8111111111111109</c:v>
                 </c:pt>
                 <c:pt idx="19">
                   <c:v>0</c:v>
@@ -4535,6 +4544,9 @@
                 <c:pt idx="17">
                   <c:v>46149</c:v>
                 </c:pt>
+                <c:pt idx="18">
+                  <c:v>46150</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -4599,7 +4611,7 @@
                   <c:v>3.3289999999999997</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0</c:v>
+                  <c:v>3.3289999999999997</c:v>
                 </c:pt>
                 <c:pt idx="19">
                   <c:v>0</c:v>
@@ -7839,34 +7851,84 @@
       </c>
     </row>
     <row r="23" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A23" s="2"/>
-      <c r="B23" s="3"/>
-      <c r="C23" s="3"/>
-      <c r="D23" s="3"/>
-      <c r="E23" s="3"/>
-      <c r="F23" s="3"/>
-      <c r="G23" s="3"/>
-      <c r="H23" s="3"/>
-      <c r="I23" s="3"/>
-      <c r="J23" s="3"/>
-      <c r="K23" s="3"/>
-      <c r="L23" s="3"/>
-      <c r="M23" s="3"/>
-      <c r="N23" s="3"/>
-      <c r="O23" s="3"/>
-      <c r="P23" s="3"/>
-      <c r="Q23" s="3"/>
-      <c r="R23" s="3"/>
-      <c r="S23" s="3"/>
-      <c r="T23" s="3"/>
-      <c r="U23" s="3"/>
-      <c r="V23" s="3"/>
-      <c r="W23" s="3"/>
-      <c r="X23" s="3"/>
-      <c r="Y23" s="3"/>
-      <c r="Z23" s="4" t="str">
+      <c r="A23" s="2">
+        <v>46150</v>
+      </c>
+      <c r="B23" s="3">
+        <v>42</v>
+      </c>
+      <c r="C23" s="3">
+        <v>46</v>
+      </c>
+      <c r="D23" s="3">
+        <v>45</v>
+      </c>
+      <c r="E23" s="3">
+        <v>45</v>
+      </c>
+      <c r="F23" s="3">
+        <v>43.5</v>
+      </c>
+      <c r="G23" s="3">
+        <v>41.5</v>
+      </c>
+      <c r="H23" s="3">
+        <v>46</v>
+      </c>
+      <c r="I23" s="3">
+        <v>41.25</v>
+      </c>
+      <c r="J23" s="3">
+        <v>43</v>
+      </c>
+      <c r="K23" s="3">
+        <v>41</v>
+      </c>
+      <c r="L23" s="3">
+        <v>36</v>
+      </c>
+      <c r="M23" s="3">
+        <v>44</v>
+      </c>
+      <c r="N23" s="3">
+        <v>45</v>
+      </c>
+      <c r="O23" s="3">
+        <v>42.8</v>
+      </c>
+      <c r="P23" s="3">
+        <v>40</v>
+      </c>
+      <c r="Q23" s="3">
+        <v>45</v>
+      </c>
+      <c r="R23" s="3">
+        <v>45</v>
+      </c>
+      <c r="S23" s="3">
+        <v>45</v>
+      </c>
+      <c r="T23" s="3">
+        <v>45</v>
+      </c>
+      <c r="U23" s="3">
+        <v>43.5</v>
+      </c>
+      <c r="V23" s="3">
+        <v>43</v>
+      </c>
+      <c r="W23" s="3">
+        <v>42</v>
+      </c>
+      <c r="X23" s="3">
+        <v>47</v>
+      </c>
+      <c r="Y23" s="3">
+        <v>45.25</v>
+      </c>
+      <c r="Z23" s="4">
         <f t="shared" si="0"/>
-        <v/>
+        <v>43.449999999999996</v>
       </c>
     </row>
     <row r="24" spans="1:26" x14ac:dyDescent="0.25">
@@ -20575,29 +20637,69 @@
       </c>
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A23" s="2"/>
-      <c r="B23" s="3"/>
-      <c r="C23" s="3"/>
-      <c r="D23" s="3"/>
-      <c r="E23" s="3"/>
-      <c r="F23" s="3"/>
-      <c r="G23" s="3"/>
-      <c r="H23" s="3"/>
-      <c r="I23" s="3"/>
-      <c r="J23" s="3"/>
-      <c r="K23" s="3"/>
-      <c r="L23" s="3"/>
-      <c r="M23" s="3"/>
-      <c r="N23" s="3"/>
-      <c r="O23" s="3"/>
-      <c r="P23" s="3"/>
-      <c r="Q23" s="3"/>
-      <c r="R23" s="3"/>
-      <c r="S23" s="3"/>
-      <c r="T23" s="3"/>
-      <c r="U23" s="4" t="str">
+      <c r="A23" s="2">
+        <v>46150</v>
+      </c>
+      <c r="B23" s="3">
+        <v>3.64</v>
+      </c>
+      <c r="C23" s="3">
+        <v>3.95</v>
+      </c>
+      <c r="D23" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="E23" s="3">
+        <v>3.8</v>
+      </c>
+      <c r="F23" s="3">
+        <v>4.3099999999999996</v>
+      </c>
+      <c r="G23" s="3">
+        <v>3.99</v>
+      </c>
+      <c r="H23" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="I23" s="3">
+        <v>3.39</v>
+      </c>
+      <c r="J23" s="3">
+        <v>3.09</v>
+      </c>
+      <c r="K23" s="3">
+        <v>3.99</v>
+      </c>
+      <c r="L23" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="M23" s="3">
+        <v>3.59</v>
+      </c>
+      <c r="N23" s="3">
+        <v>2.4900000000000002</v>
+      </c>
+      <c r="O23" s="3">
+        <v>3.8</v>
+      </c>
+      <c r="P23" s="3">
+        <v>3.89</v>
+      </c>
+      <c r="Q23" s="3">
+        <v>4.03</v>
+      </c>
+      <c r="R23" s="3">
+        <v>3.79</v>
+      </c>
+      <c r="S23" s="3">
+        <v>3.99</v>
+      </c>
+      <c r="T23" s="3">
+        <v>1.99</v>
+      </c>
+      <c r="U23" s="4">
         <f t="shared" si="0"/>
-        <v/>
+        <v>3.5105263157894737</v>
       </c>
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
@@ -30881,19 +30983,39 @@
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A23" s="2"/>
-      <c r="B23" s="3"/>
-      <c r="C23" s="3"/>
-      <c r="D23" s="3"/>
-      <c r="E23" s="3"/>
-      <c r="F23" s="3"/>
-      <c r="G23" s="3"/>
-      <c r="H23" s="3"/>
-      <c r="I23" s="3"/>
-      <c r="J23" s="3"/>
-      <c r="K23" s="4" t="str">
+      <c r="A23" s="2">
+        <v>46150</v>
+      </c>
+      <c r="B23" s="3">
+        <v>2.85</v>
+      </c>
+      <c r="C23" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="D23" s="3">
+        <v>2.67</v>
+      </c>
+      <c r="E23" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="F23" s="3">
+        <v>2.8</v>
+      </c>
+      <c r="G23" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="H23" s="3">
+        <v>2.63</v>
+      </c>
+      <c r="I23" s="3">
+        <v>2.79</v>
+      </c>
+      <c r="J23" s="3">
+        <v>2.59</v>
+      </c>
+      <c r="K23" s="4">
         <f t="shared" si="0"/>
-        <v/>
+        <v>2.8111111111111109</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
@@ -37566,20 +37688,42 @@
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A23" s="2"/>
-      <c r="B23" s="3"/>
-      <c r="C23" s="3"/>
-      <c r="D23" s="3"/>
-      <c r="E23" s="3"/>
-      <c r="F23" s="3"/>
-      <c r="G23" s="3"/>
-      <c r="H23" s="3"/>
-      <c r="I23" s="3"/>
-      <c r="J23" s="3"/>
-      <c r="K23" s="3"/>
-      <c r="L23" s="4" t="str">
+      <c r="A23" s="2">
+        <v>46150</v>
+      </c>
+      <c r="B23" s="3">
+        <v>3.55</v>
+      </c>
+      <c r="C23" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="D23" s="3">
+        <v>3.15</v>
+      </c>
+      <c r="E23" s="3">
+        <v>3.35</v>
+      </c>
+      <c r="F23" s="3">
+        <v>3.43</v>
+      </c>
+      <c r="G23" s="3">
+        <v>3.69</v>
+      </c>
+      <c r="H23" s="3">
+        <v>3.11</v>
+      </c>
+      <c r="I23" s="3">
+        <v>3.29</v>
+      </c>
+      <c r="J23" s="3">
+        <v>3.44</v>
+      </c>
+      <c r="K23" s="3">
+        <v>3.29</v>
+      </c>
+      <c r="L23" s="4">
         <f t="shared" si="0"/>
-        <v/>
+        <v>3.3289999999999997</v>
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.25">

--- a/app/mevduat-kredi-faizleri/data/hoca-ile-borsa-faiz-takip-sablonu-guncel.xlsx
+++ b/app/mevduat-kredi-faizleri/data/hoca-ile-borsa-faiz-takip-sablonu-guncel.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projeler\hoca-ile-borsa\app\mevduat-kredi-faizleri\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B27109F9-1957-4BA5-8770-AA0C65E9991A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF2FA475-B135-4D1B-A590-7F8565718E7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19350" yWindow="3540" windowWidth="18915" windowHeight="15345" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Mevduat" sheetId="1" r:id="rId1"/>
@@ -398,6 +398,9 @@
                 <c:pt idx="18">
                   <c:v>46150</c:v>
                 </c:pt>
+                <c:pt idx="19">
+                  <c:v>46153</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -465,7 +468,7 @@
                   <c:v>43.449999999999996</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0</c:v>
+                  <c:v>43.449999999999996</c:v>
                 </c:pt>
                 <c:pt idx="20">
                   <c:v>0</c:v>
@@ -1781,6 +1784,9 @@
                 <c:pt idx="18">
                   <c:v>46150</c:v>
                 </c:pt>
+                <c:pt idx="19">
+                  <c:v>46153</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1848,7 +1854,7 @@
                   <c:v>3.5105263157894737</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0</c:v>
+                  <c:v>3.4842105263157888</c:v>
                 </c:pt>
                 <c:pt idx="20">
                   <c:v>0</c:v>
@@ -3164,6 +3170,9 @@
                 <c:pt idx="18">
                   <c:v>46150</c:v>
                 </c:pt>
+                <c:pt idx="19">
+                  <c:v>46153</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3231,7 +3240,7 @@
                   <c:v>2.8111111111111109</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0</c:v>
+                  <c:v>2.8111111111111109</c:v>
                 </c:pt>
                 <c:pt idx="20">
                   <c:v>0</c:v>
@@ -4547,6 +4556,9 @@
                 <c:pt idx="18">
                   <c:v>46150</c:v>
                 </c:pt>
+                <c:pt idx="19">
+                  <c:v>46153</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -4614,7 +4626,7 @@
                   <c:v>3.3289999999999997</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0</c:v>
+                  <c:v>3.3289999999999997</c:v>
                 </c:pt>
                 <c:pt idx="20">
                   <c:v>0</c:v>
@@ -7932,34 +7944,84 @@
       </c>
     </row>
     <row r="24" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A24" s="2"/>
-      <c r="B24" s="3"/>
-      <c r="C24" s="3"/>
-      <c r="D24" s="3"/>
-      <c r="E24" s="3"/>
-      <c r="F24" s="3"/>
-      <c r="G24" s="3"/>
-      <c r="H24" s="3"/>
-      <c r="I24" s="3"/>
-      <c r="J24" s="3"/>
-      <c r="K24" s="3"/>
-      <c r="L24" s="3"/>
-      <c r="M24" s="3"/>
-      <c r="N24" s="3"/>
-      <c r="O24" s="3"/>
-      <c r="P24" s="3"/>
-      <c r="Q24" s="3"/>
-      <c r="R24" s="3"/>
-      <c r="S24" s="3"/>
-      <c r="T24" s="3"/>
-      <c r="U24" s="3"/>
-      <c r="V24" s="3"/>
-      <c r="W24" s="3"/>
-      <c r="X24" s="3"/>
-      <c r="Y24" s="3"/>
-      <c r="Z24" s="4" t="str">
+      <c r="A24" s="2">
+        <v>46153</v>
+      </c>
+      <c r="B24" s="3">
+        <v>42</v>
+      </c>
+      <c r="C24" s="3">
+        <v>46</v>
+      </c>
+      <c r="D24" s="3">
+        <v>45</v>
+      </c>
+      <c r="E24" s="3">
+        <v>45</v>
+      </c>
+      <c r="F24" s="3">
+        <v>43.5</v>
+      </c>
+      <c r="G24" s="3">
+        <v>41.5</v>
+      </c>
+      <c r="H24" s="3">
+        <v>46</v>
+      </c>
+      <c r="I24" s="3">
+        <v>41.25</v>
+      </c>
+      <c r="J24" s="3">
+        <v>43</v>
+      </c>
+      <c r="K24" s="3">
+        <v>41</v>
+      </c>
+      <c r="L24" s="3">
+        <v>36</v>
+      </c>
+      <c r="M24" s="3">
+        <v>44</v>
+      </c>
+      <c r="N24" s="3">
+        <v>45</v>
+      </c>
+      <c r="O24" s="3">
+        <v>42.8</v>
+      </c>
+      <c r="P24" s="3">
+        <v>40</v>
+      </c>
+      <c r="Q24" s="3">
+        <v>45</v>
+      </c>
+      <c r="R24" s="3">
+        <v>45</v>
+      </c>
+      <c r="S24" s="3">
+        <v>45</v>
+      </c>
+      <c r="T24" s="3">
+        <v>45</v>
+      </c>
+      <c r="U24" s="3">
+        <v>43.5</v>
+      </c>
+      <c r="V24" s="3">
+        <v>43</v>
+      </c>
+      <c r="W24" s="3">
+        <v>42</v>
+      </c>
+      <c r="X24" s="3">
+        <v>47</v>
+      </c>
+      <c r="Y24" s="3">
+        <v>45.25</v>
+      </c>
+      <c r="Z24" s="4">
         <f t="shared" si="0"/>
-        <v/>
+        <v>43.449999999999996</v>
       </c>
     </row>
     <row r="25" spans="1:26" x14ac:dyDescent="0.25">
@@ -20703,29 +20765,69 @@
       </c>
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A24" s="2"/>
-      <c r="B24" s="3"/>
-      <c r="C24" s="3"/>
-      <c r="D24" s="3"/>
-      <c r="E24" s="3"/>
-      <c r="F24" s="3"/>
-      <c r="G24" s="3"/>
-      <c r="H24" s="3"/>
-      <c r="I24" s="3"/>
-      <c r="J24" s="3"/>
-      <c r="K24" s="3"/>
-      <c r="L24" s="3"/>
-      <c r="M24" s="3"/>
-      <c r="N24" s="3"/>
-      <c r="O24" s="3"/>
-      <c r="P24" s="3"/>
-      <c r="Q24" s="3"/>
-      <c r="R24" s="3"/>
-      <c r="S24" s="3"/>
-      <c r="T24" s="3"/>
-      <c r="U24" s="4" t="str">
+      <c r="A24" s="2">
+        <v>46153</v>
+      </c>
+      <c r="B24" s="3">
+        <v>3.64</v>
+      </c>
+      <c r="C24" s="3">
+        <v>3.95</v>
+      </c>
+      <c r="D24" s="3">
+        <v>2.4900000000000002</v>
+      </c>
+      <c r="E24" s="3">
+        <v>3.8</v>
+      </c>
+      <c r="F24" s="3">
+        <v>4.3099999999999996</v>
+      </c>
+      <c r="G24" s="3">
+        <v>3.99</v>
+      </c>
+      <c r="H24" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="I24" s="3">
+        <v>3.39</v>
+      </c>
+      <c r="J24" s="3">
+        <v>3.09</v>
+      </c>
+      <c r="K24" s="3">
+        <v>3.99</v>
+      </c>
+      <c r="L24" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="M24" s="3">
+        <v>3.59</v>
+      </c>
+      <c r="N24" s="3">
+        <v>2.4900000000000002</v>
+      </c>
+      <c r="O24" s="3">
+        <v>3.8</v>
+      </c>
+      <c r="P24" s="3">
+        <v>3.89</v>
+      </c>
+      <c r="Q24" s="3">
+        <v>4.03</v>
+      </c>
+      <c r="R24" s="3">
+        <v>3.79</v>
+      </c>
+      <c r="S24" s="3">
+        <v>3.99</v>
+      </c>
+      <c r="T24" s="3">
+        <v>1.99</v>
+      </c>
+      <c r="U24" s="4">
         <f t="shared" si="0"/>
-        <v/>
+        <v>3.4842105263157888</v>
       </c>
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
@@ -31019,19 +31121,39 @@
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A24" s="2"/>
-      <c r="B24" s="3"/>
-      <c r="C24" s="3"/>
-      <c r="D24" s="3"/>
-      <c r="E24" s="3"/>
-      <c r="F24" s="3"/>
-      <c r="G24" s="3"/>
-      <c r="H24" s="3"/>
-      <c r="I24" s="3"/>
-      <c r="J24" s="3"/>
-      <c r="K24" s="4" t="str">
+      <c r="A24" s="2">
+        <v>46153</v>
+      </c>
+      <c r="B24" s="3">
+        <v>2.85</v>
+      </c>
+      <c r="C24" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="D24" s="3">
+        <v>2.67</v>
+      </c>
+      <c r="E24" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="F24" s="3">
+        <v>2.8</v>
+      </c>
+      <c r="G24" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="H24" s="3">
+        <v>2.63</v>
+      </c>
+      <c r="I24" s="3">
+        <v>2.79</v>
+      </c>
+      <c r="J24" s="3">
+        <v>2.59</v>
+      </c>
+      <c r="K24" s="4">
         <f t="shared" si="0"/>
-        <v/>
+        <v>2.8111111111111109</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
@@ -37727,20 +37849,42 @@
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A24" s="2"/>
-      <c r="B24" s="3"/>
-      <c r="C24" s="3"/>
-      <c r="D24" s="3"/>
-      <c r="E24" s="3"/>
-      <c r="F24" s="3"/>
-      <c r="G24" s="3"/>
-      <c r="H24" s="3"/>
-      <c r="I24" s="3"/>
-      <c r="J24" s="3"/>
-      <c r="K24" s="3"/>
-      <c r="L24" s="4" t="str">
+      <c r="A24" s="2">
+        <v>46153</v>
+      </c>
+      <c r="B24" s="3">
+        <v>3.55</v>
+      </c>
+      <c r="C24" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="D24" s="3">
+        <v>3.15</v>
+      </c>
+      <c r="E24" s="3">
+        <v>3.35</v>
+      </c>
+      <c r="F24" s="3">
+        <v>3.43</v>
+      </c>
+      <c r="G24" s="3">
+        <v>3.69</v>
+      </c>
+      <c r="H24" s="3">
+        <v>3.11</v>
+      </c>
+      <c r="I24" s="3">
+        <v>3.29</v>
+      </c>
+      <c r="J24" s="3">
+        <v>3.44</v>
+      </c>
+      <c r="K24" s="3">
+        <v>3.29</v>
+      </c>
+      <c r="L24" s="4">
         <f t="shared" si="0"/>
-        <v/>
+        <v>3.3289999999999997</v>
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.25">

--- a/app/mevduat-kredi-faizleri/data/hoca-ile-borsa-faiz-takip-sablonu-guncel.xlsx
+++ b/app/mevduat-kredi-faizleri/data/hoca-ile-borsa-faiz-takip-sablonu-guncel.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projeler\hoca-ile-borsa\app\mevduat-kredi-faizleri\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF2FA475-B135-4D1B-A590-7F8565718E7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C627094F-EC5B-41D7-B5B4-4E69A8DDFC0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4860" yWindow="1275" windowWidth="28800" windowHeight="17535" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Mevduat" sheetId="1" r:id="rId1"/>
@@ -401,6 +401,9 @@
                 <c:pt idx="19">
                   <c:v>46153</c:v>
                 </c:pt>
+                <c:pt idx="20">
+                  <c:v>46154</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -471,7 +474,7 @@
                   <c:v>43.449999999999996</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0</c:v>
+                  <c:v>43.439583333333331</c:v>
                 </c:pt>
                 <c:pt idx="21">
                   <c:v>0</c:v>
@@ -1787,6 +1790,9 @@
                 <c:pt idx="19">
                   <c:v>46153</c:v>
                 </c:pt>
+                <c:pt idx="20">
+                  <c:v>46154</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1857,7 +1863,7 @@
                   <c:v>3.4842105263157888</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0</c:v>
+                  <c:v>3.4842105263157888</c:v>
                 </c:pt>
                 <c:pt idx="21">
                   <c:v>0</c:v>
@@ -3173,6 +3179,9 @@
                 <c:pt idx="19">
                   <c:v>46153</c:v>
                 </c:pt>
+                <c:pt idx="20">
+                  <c:v>46154</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3243,7 +3252,7 @@
                   <c:v>2.8111111111111109</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0</c:v>
+                  <c:v>2.8111111111111109</c:v>
                 </c:pt>
                 <c:pt idx="21">
                   <c:v>0</c:v>
@@ -4559,6 +4568,9 @@
                 <c:pt idx="19">
                   <c:v>46153</c:v>
                 </c:pt>
+                <c:pt idx="20">
+                  <c:v>46154</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -4629,7 +4641,7 @@
                   <c:v>3.3289999999999997</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0</c:v>
+                  <c:v>3.3289999999999997</c:v>
                 </c:pt>
                 <c:pt idx="21">
                   <c:v>0</c:v>
@@ -8025,34 +8037,84 @@
       </c>
     </row>
     <row r="25" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A25" s="2"/>
-      <c r="B25" s="3"/>
-      <c r="C25" s="3"/>
-      <c r="D25" s="3"/>
-      <c r="E25" s="3"/>
-      <c r="F25" s="3"/>
-      <c r="G25" s="3"/>
-      <c r="H25" s="3"/>
-      <c r="I25" s="3"/>
-      <c r="J25" s="3"/>
-      <c r="K25" s="3"/>
-      <c r="L25" s="3"/>
-      <c r="M25" s="3"/>
-      <c r="N25" s="3"/>
-      <c r="O25" s="3"/>
-      <c r="P25" s="3"/>
-      <c r="Q25" s="3"/>
-      <c r="R25" s="3"/>
-      <c r="S25" s="3"/>
-      <c r="T25" s="3"/>
-      <c r="U25" s="3"/>
-      <c r="V25" s="3"/>
-      <c r="W25" s="3"/>
-      <c r="X25" s="3"/>
-      <c r="Y25" s="3"/>
-      <c r="Z25" s="4" t="str">
+      <c r="A25" s="2">
+        <v>46154</v>
+      </c>
+      <c r="B25" s="3">
+        <v>42</v>
+      </c>
+      <c r="C25" s="3">
+        <v>46</v>
+      </c>
+      <c r="D25" s="3">
+        <v>45</v>
+      </c>
+      <c r="E25" s="3">
+        <v>45</v>
+      </c>
+      <c r="F25" s="3">
+        <v>43.5</v>
+      </c>
+      <c r="G25" s="3">
+        <v>41.5</v>
+      </c>
+      <c r="H25" s="3">
+        <v>46</v>
+      </c>
+      <c r="I25" s="3">
+        <v>41</v>
+      </c>
+      <c r="J25" s="3">
+        <v>43</v>
+      </c>
+      <c r="K25" s="3">
+        <v>41</v>
+      </c>
+      <c r="L25" s="3">
+        <v>36</v>
+      </c>
+      <c r="M25" s="3">
+        <v>44</v>
+      </c>
+      <c r="N25" s="3">
+        <v>45</v>
+      </c>
+      <c r="O25" s="3">
+        <v>42.8</v>
+      </c>
+      <c r="P25" s="3">
+        <v>40</v>
+      </c>
+      <c r="Q25" s="3">
+        <v>45</v>
+      </c>
+      <c r="R25" s="3">
+        <v>45</v>
+      </c>
+      <c r="S25" s="3">
+        <v>45</v>
+      </c>
+      <c r="T25" s="3">
+        <v>45</v>
+      </c>
+      <c r="U25" s="3">
+        <v>43.5</v>
+      </c>
+      <c r="V25" s="3">
+        <v>43</v>
+      </c>
+      <c r="W25" s="3">
+        <v>42</v>
+      </c>
+      <c r="X25" s="3">
+        <v>47</v>
+      </c>
+      <c r="Y25" s="3">
+        <v>45.25</v>
+      </c>
+      <c r="Z25" s="4">
         <f t="shared" si="0"/>
-        <v/>
+        <v>43.439583333333331</v>
       </c>
     </row>
     <row r="26" spans="1:26" x14ac:dyDescent="0.25">
@@ -20831,29 +20893,69 @@
       </c>
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A25" s="2"/>
-      <c r="B25" s="3"/>
-      <c r="C25" s="3"/>
-      <c r="D25" s="3"/>
-      <c r="E25" s="3"/>
-      <c r="F25" s="3"/>
-      <c r="G25" s="3"/>
-      <c r="H25" s="3"/>
-      <c r="I25" s="3"/>
-      <c r="J25" s="3"/>
-      <c r="K25" s="3"/>
-      <c r="L25" s="3"/>
-      <c r="M25" s="3"/>
-      <c r="N25" s="3"/>
-      <c r="O25" s="3"/>
-      <c r="P25" s="3"/>
-      <c r="Q25" s="3"/>
-      <c r="R25" s="3"/>
-      <c r="S25" s="3"/>
-      <c r="T25" s="3"/>
-      <c r="U25" s="4" t="str">
+      <c r="A25" s="2">
+        <v>46154</v>
+      </c>
+      <c r="B25" s="3">
+        <v>3.64</v>
+      </c>
+      <c r="C25" s="3">
+        <v>3.95</v>
+      </c>
+      <c r="D25" s="3">
+        <v>2.4900000000000002</v>
+      </c>
+      <c r="E25" s="3">
+        <v>3.8</v>
+      </c>
+      <c r="F25" s="3">
+        <v>4.3099999999999996</v>
+      </c>
+      <c r="G25" s="3">
+        <v>3.99</v>
+      </c>
+      <c r="H25" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="I25" s="3">
+        <v>3.39</v>
+      </c>
+      <c r="J25" s="3">
+        <v>3.09</v>
+      </c>
+      <c r="K25" s="3">
+        <v>3.99</v>
+      </c>
+      <c r="L25" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="M25" s="3">
+        <v>3.59</v>
+      </c>
+      <c r="N25" s="3">
+        <v>2.4900000000000002</v>
+      </c>
+      <c r="O25" s="3">
+        <v>3.8</v>
+      </c>
+      <c r="P25" s="3">
+        <v>3.89</v>
+      </c>
+      <c r="Q25" s="3">
+        <v>4.03</v>
+      </c>
+      <c r="R25" s="3">
+        <v>3.79</v>
+      </c>
+      <c r="S25" s="3">
+        <v>3.99</v>
+      </c>
+      <c r="T25" s="3">
+        <v>1.99</v>
+      </c>
+      <c r="U25" s="4">
         <f t="shared" si="0"/>
-        <v/>
+        <v>3.4842105263157888</v>
       </c>
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
@@ -31157,19 +31259,39 @@
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A25" s="2"/>
-      <c r="B25" s="3"/>
-      <c r="C25" s="3"/>
-      <c r="D25" s="3"/>
-      <c r="E25" s="3"/>
-      <c r="F25" s="3"/>
-      <c r="G25" s="3"/>
-      <c r="H25" s="3"/>
-      <c r="I25" s="3"/>
-      <c r="J25" s="3"/>
-      <c r="K25" s="4" t="str">
+      <c r="A25" s="2">
+        <v>46154</v>
+      </c>
+      <c r="B25" s="3">
+        <v>2.85</v>
+      </c>
+      <c r="C25" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="D25" s="3">
+        <v>2.67</v>
+      </c>
+      <c r="E25" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="F25" s="3">
+        <v>2.8</v>
+      </c>
+      <c r="G25" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="H25" s="3">
+        <v>2.63</v>
+      </c>
+      <c r="I25" s="3">
+        <v>2.79</v>
+      </c>
+      <c r="J25" s="3">
+        <v>2.59</v>
+      </c>
+      <c r="K25" s="4">
         <f t="shared" si="0"/>
-        <v/>
+        <v>2.8111111111111109</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
@@ -37888,20 +38010,42 @@
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A25" s="2"/>
-      <c r="B25" s="3"/>
-      <c r="C25" s="3"/>
-      <c r="D25" s="3"/>
-      <c r="E25" s="3"/>
-      <c r="F25" s="3"/>
-      <c r="G25" s="3"/>
-      <c r="H25" s="3"/>
-      <c r="I25" s="3"/>
-      <c r="J25" s="3"/>
-      <c r="K25" s="3"/>
-      <c r="L25" s="4" t="str">
+      <c r="A25" s="2">
+        <v>46154</v>
+      </c>
+      <c r="B25" s="3">
+        <v>3.55</v>
+      </c>
+      <c r="C25" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="D25" s="3">
+        <v>3.15</v>
+      </c>
+      <c r="E25" s="3">
+        <v>3.35</v>
+      </c>
+      <c r="F25" s="3">
+        <v>3.43</v>
+      </c>
+      <c r="G25" s="3">
+        <v>3.69</v>
+      </c>
+      <c r="H25" s="3">
+        <v>3.11</v>
+      </c>
+      <c r="I25" s="3">
+        <v>3.29</v>
+      </c>
+      <c r="J25" s="3">
+        <v>3.44</v>
+      </c>
+      <c r="K25" s="3">
+        <v>3.29</v>
+      </c>
+      <c r="L25" s="4">
         <f t="shared" si="0"/>
-        <v/>
+        <v>3.3289999999999997</v>
       </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">

--- a/app/mevduat-kredi-faizleri/data/hoca-ile-borsa-faiz-takip-sablonu-guncel.xlsx
+++ b/app/mevduat-kredi-faizleri/data/hoca-ile-borsa-faiz-takip-sablonu-guncel.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projeler\hoca-ile-borsa\app\mevduat-kredi-faizleri\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C627094F-EC5B-41D7-B5B4-4E69A8DDFC0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C789561-21CF-4A5B-9769-CD940C88105F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4860" yWindow="1275" windowWidth="28800" windowHeight="17535" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4860" yWindow="1275" windowWidth="28800" windowHeight="18630" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Mevduat" sheetId="1" r:id="rId1"/>
@@ -404,6 +404,9 @@
                 <c:pt idx="20">
                   <c:v>46154</c:v>
                 </c:pt>
+                <c:pt idx="21">
+                  <c:v>46155</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -477,7 +480,7 @@
                   <c:v>43.439583333333331</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0</c:v>
+                  <c:v>43.455000000000005</c:v>
                 </c:pt>
                 <c:pt idx="22">
                   <c:v>0</c:v>
@@ -1793,6 +1796,9 @@
                 <c:pt idx="20">
                   <c:v>46154</c:v>
                 </c:pt>
+                <c:pt idx="21">
+                  <c:v>46155</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1866,7 +1872,7 @@
                   <c:v>3.4842105263157888</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0</c:v>
+                  <c:v>3.430526315789475</c:v>
                 </c:pt>
                 <c:pt idx="22">
                   <c:v>0</c:v>
@@ -3182,6 +3188,9 @@
                 <c:pt idx="20">
                   <c:v>46154</c:v>
                 </c:pt>
+                <c:pt idx="21">
+                  <c:v>46155</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3255,7 +3264,7 @@
                   <c:v>2.8111111111111109</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0</c:v>
+                  <c:v>2.8111111111111113</c:v>
                 </c:pt>
                 <c:pt idx="22">
                   <c:v>0</c:v>
@@ -4571,6 +4580,9 @@
                 <c:pt idx="20">
                   <c:v>46154</c:v>
                 </c:pt>
+                <c:pt idx="21">
+                  <c:v>46155</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -4644,7 +4656,7 @@
                   <c:v>3.3289999999999997</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0</c:v>
+                  <c:v>3.3380000000000001</c:v>
                 </c:pt>
                 <c:pt idx="22">
                   <c:v>0</c:v>
@@ -8118,34 +8130,84 @@
       </c>
     </row>
     <row r="26" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A26" s="2"/>
-      <c r="B26" s="3"/>
-      <c r="C26" s="3"/>
-      <c r="D26" s="3"/>
-      <c r="E26" s="3"/>
-      <c r="F26" s="3"/>
-      <c r="G26" s="3"/>
-      <c r="H26" s="3"/>
-      <c r="I26" s="3"/>
-      <c r="J26" s="3"/>
-      <c r="K26" s="3"/>
-      <c r="L26" s="3"/>
-      <c r="M26" s="3"/>
-      <c r="N26" s="3"/>
-      <c r="O26" s="3"/>
-      <c r="P26" s="3"/>
-      <c r="Q26" s="3"/>
-      <c r="R26" s="3"/>
-      <c r="S26" s="3"/>
-      <c r="T26" s="3"/>
-      <c r="U26" s="3"/>
-      <c r="V26" s="3"/>
-      <c r="W26" s="3"/>
-      <c r="X26" s="3"/>
-      <c r="Y26" s="3"/>
-      <c r="Z26" s="4" t="str">
+      <c r="A26" s="2">
+        <v>46155</v>
+      </c>
+      <c r="B26" s="3">
+        <v>42</v>
+      </c>
+      <c r="C26" s="3">
+        <v>46</v>
+      </c>
+      <c r="D26" s="3">
+        <v>45</v>
+      </c>
+      <c r="E26" s="3">
+        <v>45</v>
+      </c>
+      <c r="F26" s="3">
+        <v>43.5</v>
+      </c>
+      <c r="G26" s="3">
+        <v>41.5</v>
+      </c>
+      <c r="H26" s="3">
+        <v>46</v>
+      </c>
+      <c r="I26" s="3">
+        <v>41</v>
+      </c>
+      <c r="J26" s="3">
+        <v>43</v>
+      </c>
+      <c r="K26" s="3">
+        <v>41</v>
+      </c>
+      <c r="L26" s="3">
+        <v>36</v>
+      </c>
+      <c r="M26" s="3">
+        <v>44</v>
+      </c>
+      <c r="N26" s="3">
+        <v>45</v>
+      </c>
+      <c r="O26" s="3">
+        <v>42.67</v>
+      </c>
+      <c r="P26" s="3">
+        <v>40</v>
+      </c>
+      <c r="Q26" s="3">
+        <v>45</v>
+      </c>
+      <c r="R26" s="3">
+        <v>45</v>
+      </c>
+      <c r="S26" s="3">
+        <v>45</v>
+      </c>
+      <c r="T26" s="3">
+        <v>45</v>
+      </c>
+      <c r="U26" s="3">
+        <v>43.5</v>
+      </c>
+      <c r="V26" s="3">
+        <v>43.5</v>
+      </c>
+      <c r="W26" s="3">
+        <v>42</v>
+      </c>
+      <c r="X26" s="3">
+        <v>47</v>
+      </c>
+      <c r="Y26" s="3">
+        <v>45.25</v>
+      </c>
+      <c r="Z26" s="4">
         <f t="shared" si="0"/>
-        <v/>
+        <v>43.455000000000005</v>
       </c>
     </row>
     <row r="27" spans="1:26" x14ac:dyDescent="0.25">
@@ -20959,29 +21021,69 @@
       </c>
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A26" s="2"/>
-      <c r="B26" s="3"/>
-      <c r="C26" s="3"/>
-      <c r="D26" s="3"/>
-      <c r="E26" s="3"/>
-      <c r="F26" s="3"/>
-      <c r="G26" s="3"/>
-      <c r="H26" s="3"/>
-      <c r="I26" s="3"/>
-      <c r="J26" s="3"/>
-      <c r="K26" s="3"/>
-      <c r="L26" s="3"/>
-      <c r="M26" s="3"/>
-      <c r="N26" s="3"/>
-      <c r="O26" s="3"/>
-      <c r="P26" s="3"/>
-      <c r="Q26" s="3"/>
-      <c r="R26" s="3"/>
-      <c r="S26" s="3"/>
-      <c r="T26" s="3"/>
-      <c r="U26" s="4" t="str">
+      <c r="A26" s="2">
+        <v>46155</v>
+      </c>
+      <c r="B26" s="3">
+        <v>3.64</v>
+      </c>
+      <c r="C26" s="3">
+        <v>3.95</v>
+      </c>
+      <c r="D26" s="3">
+        <v>2.4900000000000002</v>
+      </c>
+      <c r="E26" s="3">
+        <v>3.39</v>
+      </c>
+      <c r="F26" s="3">
+        <v>4.3099999999999996</v>
+      </c>
+      <c r="G26" s="3">
+        <v>3.99</v>
+      </c>
+      <c r="H26" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="I26" s="3">
+        <v>3.39</v>
+      </c>
+      <c r="J26" s="3">
+        <v>2.89</v>
+      </c>
+      <c r="K26" s="3">
+        <v>3.99</v>
+      </c>
+      <c r="L26" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="M26" s="3">
+        <v>3.59</v>
+      </c>
+      <c r="N26" s="3">
+        <v>2.4900000000000002</v>
+      </c>
+      <c r="O26" s="3">
+        <v>3.39</v>
+      </c>
+      <c r="P26" s="3">
+        <v>3.89</v>
+      </c>
+      <c r="Q26" s="3">
+        <v>4.03</v>
+      </c>
+      <c r="R26" s="3">
+        <v>3.79</v>
+      </c>
+      <c r="S26" s="3">
+        <v>3.99</v>
+      </c>
+      <c r="T26" s="3">
+        <v>1.99</v>
+      </c>
+      <c r="U26" s="4">
         <f t="shared" si="0"/>
-        <v/>
+        <v>3.430526315789475</v>
       </c>
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
@@ -31295,19 +31397,39 @@
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A26" s="2"/>
-      <c r="B26" s="3"/>
-      <c r="C26" s="3"/>
-      <c r="D26" s="3"/>
-      <c r="E26" s="3"/>
-      <c r="F26" s="3"/>
-      <c r="G26" s="3"/>
-      <c r="H26" s="3"/>
-      <c r="I26" s="3"/>
-      <c r="J26" s="3"/>
-      <c r="K26" s="4" t="str">
+      <c r="A26" s="2">
+        <v>46155</v>
+      </c>
+      <c r="B26" s="3">
+        <v>2.85</v>
+      </c>
+      <c r="C26" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="D26" s="3">
+        <v>2.72</v>
+      </c>
+      <c r="E26" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="F26" s="3">
+        <v>2.8</v>
+      </c>
+      <c r="G26" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="H26" s="3">
+        <v>2.63</v>
+      </c>
+      <c r="I26" s="3">
+        <v>2.74</v>
+      </c>
+      <c r="J26" s="3">
+        <v>2.59</v>
+      </c>
+      <c r="K26" s="4">
         <f t="shared" si="0"/>
-        <v/>
+        <v>2.8111111111111113</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.25">
@@ -38049,20 +38171,42 @@
       </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A26" s="2"/>
-      <c r="B26" s="3"/>
-      <c r="C26" s="3"/>
-      <c r="D26" s="3"/>
-      <c r="E26" s="3"/>
-      <c r="F26" s="3"/>
-      <c r="G26" s="3"/>
-      <c r="H26" s="3"/>
-      <c r="I26" s="3"/>
-      <c r="J26" s="3"/>
-      <c r="K26" s="3"/>
-      <c r="L26" s="4" t="str">
+      <c r="A26" s="2">
+        <v>46155</v>
+      </c>
+      <c r="B26" s="3">
+        <v>3.55</v>
+      </c>
+      <c r="C26" s="3">
+        <v>3.08</v>
+      </c>
+      <c r="D26" s="3">
+        <v>3.15</v>
+      </c>
+      <c r="E26" s="3">
+        <v>3.35</v>
+      </c>
+      <c r="F26" s="3">
+        <v>3.43</v>
+      </c>
+      <c r="G26" s="3">
+        <v>3.69</v>
+      </c>
+      <c r="H26" s="3">
+        <v>3.11</v>
+      </c>
+      <c r="I26" s="3">
+        <v>3.29</v>
+      </c>
+      <c r="J26" s="3">
+        <v>3.44</v>
+      </c>
+      <c r="K26" s="3">
+        <v>3.29</v>
+      </c>
+      <c r="L26" s="4">
         <f t="shared" si="0"/>
-        <v/>
+        <v>3.3380000000000001</v>
       </c>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.25">

--- a/app/mevduat-kredi-faizleri/data/hoca-ile-borsa-faiz-takip-sablonu-guncel.xlsx
+++ b/app/mevduat-kredi-faizleri/data/hoca-ile-borsa-faiz-takip-sablonu-guncel.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projeler\hoca-ile-borsa\app\mevduat-kredi-faizleri\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C789561-21CF-4A5B-9769-CD940C88105F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A3785E8-2176-41A7-A732-0E8332DB421E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4860" yWindow="1275" windowWidth="28800" windowHeight="18630" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Mevduat" sheetId="1" r:id="rId1"/>
@@ -407,6 +407,9 @@
                 <c:pt idx="21">
                   <c:v>46155</c:v>
                 </c:pt>
+                <c:pt idx="22">
+                  <c:v>46156</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -483,7 +486,7 @@
                   <c:v>43.455000000000005</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>0</c:v>
+                  <c:v>43.344347826086953</c:v>
                 </c:pt>
                 <c:pt idx="23">
                   <c:v>0</c:v>
@@ -1799,6 +1802,9 @@
                 <c:pt idx="21">
                   <c:v>46155</c:v>
                 </c:pt>
+                <c:pt idx="22">
+                  <c:v>46156</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1875,7 +1881,7 @@
                   <c:v>3.430526315789475</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>0</c:v>
+                  <c:v>3.430526315789475</c:v>
                 </c:pt>
                 <c:pt idx="23">
                   <c:v>0</c:v>
@@ -3191,6 +3197,9 @@
                 <c:pt idx="21">
                   <c:v>46155</c:v>
                 </c:pt>
+                <c:pt idx="22">
+                  <c:v>46156</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3267,7 +3276,7 @@
                   <c:v>2.8111111111111113</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>0</c:v>
+                  <c:v>2.8111111111111113</c:v>
                 </c:pt>
                 <c:pt idx="23">
                   <c:v>0</c:v>
@@ -4583,6 +4592,9 @@
                 <c:pt idx="21">
                   <c:v>46155</c:v>
                 </c:pt>
+                <c:pt idx="22">
+                  <c:v>46156</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -4659,7 +4671,7 @@
                   <c:v>3.3380000000000001</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>0</c:v>
+                  <c:v>3.3380000000000001</c:v>
                 </c:pt>
                 <c:pt idx="23">
                   <c:v>0</c:v>
@@ -8211,34 +8223,82 @@
       </c>
     </row>
     <row r="27" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A27" s="2"/>
-      <c r="B27" s="3"/>
-      <c r="C27" s="3"/>
-      <c r="D27" s="3"/>
-      <c r="E27" s="3"/>
-      <c r="F27" s="3"/>
-      <c r="G27" s="3"/>
-      <c r="H27" s="3"/>
-      <c r="I27" s="3"/>
-      <c r="J27" s="3"/>
-      <c r="K27" s="3"/>
-      <c r="L27" s="3"/>
-      <c r="M27" s="3"/>
-      <c r="N27" s="3"/>
-      <c r="O27" s="3"/>
-      <c r="P27" s="3"/>
-      <c r="Q27" s="3"/>
+      <c r="A27" s="2">
+        <v>46156</v>
+      </c>
+      <c r="B27" s="3">
+        <v>42</v>
+      </c>
+      <c r="C27" s="3">
+        <v>46</v>
+      </c>
+      <c r="D27" s="3">
+        <v>45</v>
+      </c>
+      <c r="E27" s="3">
+        <v>45</v>
+      </c>
+      <c r="F27" s="3">
+        <v>43.5</v>
+      </c>
+      <c r="G27" s="3">
+        <v>41.5</v>
+      </c>
+      <c r="H27" s="3">
+        <v>46</v>
+      </c>
+      <c r="I27" s="3">
+        <v>41</v>
+      </c>
+      <c r="J27" s="3">
+        <v>43</v>
+      </c>
+      <c r="K27" s="3">
+        <v>41</v>
+      </c>
+      <c r="L27" s="3">
+        <v>36</v>
+      </c>
+      <c r="M27" s="3">
+        <v>44</v>
+      </c>
+      <c r="N27" s="3">
+        <v>45</v>
+      </c>
+      <c r="O27" s="3">
+        <v>42.67</v>
+      </c>
+      <c r="P27" s="3">
+        <v>39</v>
+      </c>
+      <c r="Q27" s="3">
+        <v>45</v>
+      </c>
       <c r="R27" s="3"/>
-      <c r="S27" s="3"/>
-      <c r="T27" s="3"/>
-      <c r="U27" s="3"/>
-      <c r="V27" s="3"/>
-      <c r="W27" s="3"/>
-      <c r="X27" s="3"/>
-      <c r="Y27" s="3"/>
-      <c r="Z27" s="4" t="str">
+      <c r="S27" s="3">
+        <v>45</v>
+      </c>
+      <c r="T27" s="3">
+        <v>45</v>
+      </c>
+      <c r="U27" s="3">
+        <v>43.5</v>
+      </c>
+      <c r="V27" s="3">
+        <v>43.5</v>
+      </c>
+      <c r="W27" s="3">
+        <v>42</v>
+      </c>
+      <c r="X27" s="3">
+        <v>47</v>
+      </c>
+      <c r="Y27" s="3">
+        <v>45.25</v>
+      </c>
+      <c r="Z27" s="4">
         <f t="shared" si="0"/>
-        <v/>
+        <v>43.344347826086953</v>
       </c>
     </row>
     <row r="28" spans="1:26" x14ac:dyDescent="0.25">
@@ -21087,29 +21147,69 @@
       </c>
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A27" s="2"/>
-      <c r="B27" s="3"/>
-      <c r="C27" s="3"/>
-      <c r="D27" s="3"/>
-      <c r="E27" s="3"/>
-      <c r="F27" s="3"/>
-      <c r="G27" s="3"/>
-      <c r="H27" s="3"/>
-      <c r="I27" s="3"/>
-      <c r="J27" s="3"/>
-      <c r="K27" s="3"/>
-      <c r="L27" s="3"/>
-      <c r="M27" s="3"/>
-      <c r="N27" s="3"/>
-      <c r="O27" s="3"/>
-      <c r="P27" s="3"/>
-      <c r="Q27" s="3"/>
-      <c r="R27" s="3"/>
-      <c r="S27" s="3"/>
-      <c r="T27" s="3"/>
-      <c r="U27" s="4" t="str">
+      <c r="A27" s="2">
+        <v>46156</v>
+      </c>
+      <c r="B27" s="3">
+        <v>3.64</v>
+      </c>
+      <c r="C27" s="3">
+        <v>3.95</v>
+      </c>
+      <c r="D27" s="3">
+        <v>2.4900000000000002</v>
+      </c>
+      <c r="E27" s="3">
+        <v>3.39</v>
+      </c>
+      <c r="F27" s="3">
+        <v>4.3099999999999996</v>
+      </c>
+      <c r="G27" s="3">
+        <v>3.99</v>
+      </c>
+      <c r="H27" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="I27" s="3">
+        <v>3.39</v>
+      </c>
+      <c r="J27" s="3">
+        <v>2.89</v>
+      </c>
+      <c r="K27" s="3">
+        <v>3.99</v>
+      </c>
+      <c r="L27" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="M27" s="3">
+        <v>3.59</v>
+      </c>
+      <c r="N27" s="3">
+        <v>2.4900000000000002</v>
+      </c>
+      <c r="O27" s="3">
+        <v>3.39</v>
+      </c>
+      <c r="P27" s="3">
+        <v>3.89</v>
+      </c>
+      <c r="Q27" s="3">
+        <v>4.03</v>
+      </c>
+      <c r="R27" s="3">
+        <v>3.79</v>
+      </c>
+      <c r="S27" s="3">
+        <v>3.99</v>
+      </c>
+      <c r="T27" s="3">
+        <v>1.99</v>
+      </c>
+      <c r="U27" s="4">
         <f t="shared" si="0"/>
-        <v/>
+        <v>3.430526315789475</v>
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
@@ -31433,19 +31533,39 @@
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A27" s="2"/>
-      <c r="B27" s="3"/>
-      <c r="C27" s="3"/>
-      <c r="D27" s="3"/>
-      <c r="E27" s="3"/>
-      <c r="F27" s="3"/>
-      <c r="G27" s="3"/>
-      <c r="H27" s="3"/>
-      <c r="I27" s="3"/>
-      <c r="J27" s="3"/>
-      <c r="K27" s="4" t="str">
+      <c r="A27" s="2">
+        <v>46156</v>
+      </c>
+      <c r="B27" s="3">
+        <v>2.85</v>
+      </c>
+      <c r="C27" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="D27" s="3">
+        <v>2.72</v>
+      </c>
+      <c r="E27" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="F27" s="3">
+        <v>2.8</v>
+      </c>
+      <c r="G27" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="H27" s="3">
+        <v>2.63</v>
+      </c>
+      <c r="I27" s="3">
+        <v>2.74</v>
+      </c>
+      <c r="J27" s="3">
+        <v>2.59</v>
+      </c>
+      <c r="K27" s="4">
         <f t="shared" si="0"/>
-        <v/>
+        <v>2.8111111111111113</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
@@ -38210,20 +38330,42 @@
       </c>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A27" s="2"/>
-      <c r="B27" s="3"/>
-      <c r="C27" s="3"/>
-      <c r="D27" s="3"/>
-      <c r="E27" s="3"/>
-      <c r="F27" s="3"/>
-      <c r="G27" s="3"/>
-      <c r="H27" s="3"/>
-      <c r="I27" s="3"/>
-      <c r="J27" s="3"/>
-      <c r="K27" s="3"/>
-      <c r="L27" s="4" t="str">
+      <c r="A27" s="2">
+        <v>46156</v>
+      </c>
+      <c r="B27" s="3">
+        <v>3.55</v>
+      </c>
+      <c r="C27" s="3">
+        <v>3.08</v>
+      </c>
+      <c r="D27" s="3">
+        <v>3.15</v>
+      </c>
+      <c r="E27" s="3">
+        <v>3.35</v>
+      </c>
+      <c r="F27" s="3">
+        <v>3.43</v>
+      </c>
+      <c r="G27" s="3">
+        <v>3.69</v>
+      </c>
+      <c r="H27" s="3">
+        <v>3.11</v>
+      </c>
+      <c r="I27" s="3">
+        <v>3.29</v>
+      </c>
+      <c r="J27" s="3">
+        <v>3.44</v>
+      </c>
+      <c r="K27" s="3">
+        <v>3.29</v>
+      </c>
+      <c r="L27" s="4">
         <f t="shared" si="0"/>
-        <v/>
+        <v>3.3380000000000001</v>
       </c>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.25">

--- a/app/mevduat-kredi-faizleri/data/hoca-ile-borsa-faiz-takip-sablonu-guncel.xlsx
+++ b/app/mevduat-kredi-faizleri/data/hoca-ile-borsa-faiz-takip-sablonu-guncel.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projeler\hoca-ile-borsa\app\mevduat-kredi-faizleri\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A3785E8-2176-41A7-A732-0E8332DB421E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C4D1EE2-A48F-48E6-A03B-1F4BDE7EE55A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -410,6 +410,9 @@
                 <c:pt idx="22">
                   <c:v>46156</c:v>
                 </c:pt>
+                <c:pt idx="23">
+                  <c:v>46157</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -486,10 +489,10 @@
                   <c:v>43.455000000000005</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>43.344347826086953</c:v>
+                  <c:v>43.413333333333334</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>0</c:v>
+                  <c:v>43.413333333333334</c:v>
                 </c:pt>
                 <c:pt idx="24">
                   <c:v>0</c:v>
@@ -1805,6 +1808,9 @@
                 <c:pt idx="22">
                   <c:v>46156</c:v>
                 </c:pt>
+                <c:pt idx="23">
+                  <c:v>46157</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1884,7 +1890,7 @@
                   <c:v>3.430526315789475</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>0</c:v>
+                  <c:v>3.4384210526315795</c:v>
                 </c:pt>
                 <c:pt idx="24">
                   <c:v>0</c:v>
@@ -3200,6 +3206,9 @@
                 <c:pt idx="22">
                   <c:v>46156</c:v>
                 </c:pt>
+                <c:pt idx="23">
+                  <c:v>46157</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3279,7 +3288,7 @@
                   <c:v>2.8111111111111113</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>0</c:v>
+                  <c:v>2.8111111111111113</c:v>
                 </c:pt>
                 <c:pt idx="24">
                   <c:v>0</c:v>
@@ -4595,6 +4604,9 @@
                 <c:pt idx="22">
                   <c:v>46156</c:v>
                 </c:pt>
+                <c:pt idx="23">
+                  <c:v>46157</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -4674,7 +4686,7 @@
                   <c:v>3.3380000000000001</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>0</c:v>
+                  <c:v>3.3319999999999999</c:v>
                 </c:pt>
                 <c:pt idx="24">
                   <c:v>0</c:v>
@@ -8274,7 +8286,9 @@
       <c r="Q27" s="3">
         <v>45</v>
       </c>
-      <c r="R27" s="3"/>
+      <c r="R27" s="3">
+        <v>45</v>
+      </c>
       <c r="S27" s="3">
         <v>45</v>
       </c>
@@ -8298,38 +8312,88 @@
       </c>
       <c r="Z27" s="4">
         <f t="shared" si="0"/>
-        <v>43.344347826086953</v>
+        <v>43.413333333333334</v>
       </c>
     </row>
     <row r="28" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A28" s="2"/>
-      <c r="B28" s="3"/>
-      <c r="C28" s="3"/>
-      <c r="D28" s="3"/>
-      <c r="E28" s="3"/>
-      <c r="F28" s="3"/>
-      <c r="G28" s="3"/>
-      <c r="H28" s="3"/>
-      <c r="I28" s="3"/>
-      <c r="J28" s="3"/>
-      <c r="K28" s="3"/>
-      <c r="L28" s="3"/>
-      <c r="M28" s="3"/>
-      <c r="N28" s="3"/>
-      <c r="O28" s="3"/>
-      <c r="P28" s="3"/>
-      <c r="Q28" s="3"/>
-      <c r="R28" s="3"/>
-      <c r="S28" s="3"/>
-      <c r="T28" s="3"/>
-      <c r="U28" s="3"/>
-      <c r="V28" s="3"/>
-      <c r="W28" s="3"/>
-      <c r="X28" s="3"/>
-      <c r="Y28" s="3"/>
-      <c r="Z28" s="4" t="str">
+      <c r="A28" s="2">
+        <v>46157</v>
+      </c>
+      <c r="B28" s="3">
+        <v>42</v>
+      </c>
+      <c r="C28" s="3">
+        <v>46</v>
+      </c>
+      <c r="D28" s="3">
+        <v>45</v>
+      </c>
+      <c r="E28" s="3">
+        <v>45</v>
+      </c>
+      <c r="F28" s="3">
+        <v>43.5</v>
+      </c>
+      <c r="G28" s="3">
+        <v>41.5</v>
+      </c>
+      <c r="H28" s="3">
+        <v>46</v>
+      </c>
+      <c r="I28" s="3">
+        <v>41</v>
+      </c>
+      <c r="J28" s="3">
+        <v>43</v>
+      </c>
+      <c r="K28" s="3">
+        <v>41</v>
+      </c>
+      <c r="L28" s="3">
+        <v>36</v>
+      </c>
+      <c r="M28" s="3">
+        <v>44</v>
+      </c>
+      <c r="N28" s="3">
+        <v>45</v>
+      </c>
+      <c r="O28" s="3">
+        <v>42.67</v>
+      </c>
+      <c r="P28" s="3">
+        <v>39</v>
+      </c>
+      <c r="Q28" s="3">
+        <v>45</v>
+      </c>
+      <c r="R28" s="3">
+        <v>45</v>
+      </c>
+      <c r="S28" s="3">
+        <v>45</v>
+      </c>
+      <c r="T28" s="3">
+        <v>45</v>
+      </c>
+      <c r="U28" s="3">
+        <v>43.5</v>
+      </c>
+      <c r="V28" s="3">
+        <v>43.5</v>
+      </c>
+      <c r="W28" s="3">
+        <v>42</v>
+      </c>
+      <c r="X28" s="3">
+        <v>47</v>
+      </c>
+      <c r="Y28" s="3">
+        <v>45.25</v>
+      </c>
+      <c r="Z28" s="4">
         <f t="shared" si="0"/>
-        <v/>
+        <v>43.413333333333334</v>
       </c>
     </row>
     <row r="29" spans="1:26" x14ac:dyDescent="0.25">
@@ -21213,29 +21277,69 @@
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A28" s="2"/>
-      <c r="B28" s="3"/>
-      <c r="C28" s="3"/>
-      <c r="D28" s="3"/>
-      <c r="E28" s="3"/>
-      <c r="F28" s="3"/>
-      <c r="G28" s="3"/>
-      <c r="H28" s="3"/>
-      <c r="I28" s="3"/>
-      <c r="J28" s="3"/>
-      <c r="K28" s="3"/>
-      <c r="L28" s="3"/>
-      <c r="M28" s="3"/>
-      <c r="N28" s="3"/>
-      <c r="O28" s="3"/>
-      <c r="P28" s="3"/>
-      <c r="Q28" s="3"/>
-      <c r="R28" s="3"/>
-      <c r="S28" s="3"/>
-      <c r="T28" s="3"/>
-      <c r="U28" s="4" t="str">
+      <c r="A28" s="2">
+        <v>46157</v>
+      </c>
+      <c r="B28" s="3">
+        <v>3.89</v>
+      </c>
+      <c r="C28" s="3">
+        <v>3.95</v>
+      </c>
+      <c r="D28" s="3">
+        <v>2.4900000000000002</v>
+      </c>
+      <c r="E28" s="3">
+        <v>3.39</v>
+      </c>
+      <c r="F28" s="3">
+        <v>4.3099999999999996</v>
+      </c>
+      <c r="G28" s="3">
+        <v>3.99</v>
+      </c>
+      <c r="H28" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="I28" s="3">
+        <v>3.39</v>
+      </c>
+      <c r="J28" s="3">
+        <v>2.89</v>
+      </c>
+      <c r="K28" s="3">
+        <v>3.99</v>
+      </c>
+      <c r="L28" s="3">
+        <v>2.89</v>
+      </c>
+      <c r="M28" s="3">
+        <v>3.59</v>
+      </c>
+      <c r="N28" s="3">
+        <v>2.4900000000000002</v>
+      </c>
+      <c r="O28" s="3">
+        <v>3.39</v>
+      </c>
+      <c r="P28" s="3">
+        <v>3.89</v>
+      </c>
+      <c r="Q28" s="3">
+        <v>4.03</v>
+      </c>
+      <c r="R28" s="3">
+        <v>3.79</v>
+      </c>
+      <c r="S28" s="3">
+        <v>3.99</v>
+      </c>
+      <c r="T28" s="3">
+        <v>1.99</v>
+      </c>
+      <c r="U28" s="4">
         <f t="shared" si="0"/>
-        <v/>
+        <v>3.4384210526315795</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
@@ -31569,19 +31673,39 @@
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A28" s="2"/>
-      <c r="B28" s="3"/>
-      <c r="C28" s="3"/>
-      <c r="D28" s="3"/>
-      <c r="E28" s="3"/>
-      <c r="F28" s="3"/>
-      <c r="G28" s="3"/>
-      <c r="H28" s="3"/>
-      <c r="I28" s="3"/>
-      <c r="J28" s="3"/>
-      <c r="K28" s="4" t="str">
+      <c r="A28" s="2">
+        <v>46157</v>
+      </c>
+      <c r="B28" s="3">
+        <v>2.85</v>
+      </c>
+      <c r="C28" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="D28" s="3">
+        <v>2.72</v>
+      </c>
+      <c r="E28" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="F28" s="3">
+        <v>2.8</v>
+      </c>
+      <c r="G28" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="H28" s="3">
+        <v>2.63</v>
+      </c>
+      <c r="I28" s="3">
+        <v>2.74</v>
+      </c>
+      <c r="J28" s="3">
+        <v>2.59</v>
+      </c>
+      <c r="K28" s="4">
         <f t="shared" si="0"/>
-        <v/>
+        <v>2.8111111111111113</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.25">
@@ -38369,20 +38493,42 @@
       </c>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A28" s="2"/>
-      <c r="B28" s="3"/>
-      <c r="C28" s="3"/>
-      <c r="D28" s="3"/>
-      <c r="E28" s="3"/>
-      <c r="F28" s="3"/>
-      <c r="G28" s="3"/>
-      <c r="H28" s="3"/>
-      <c r="I28" s="3"/>
-      <c r="J28" s="3"/>
-      <c r="K28" s="3"/>
-      <c r="L28" s="4" t="str">
+      <c r="A28" s="2">
+        <v>46157</v>
+      </c>
+      <c r="B28" s="3">
+        <v>3.49</v>
+      </c>
+      <c r="C28" s="3">
+        <v>3.08</v>
+      </c>
+      <c r="D28" s="3">
+        <v>3.15</v>
+      </c>
+      <c r="E28" s="3">
+        <v>3.35</v>
+      </c>
+      <c r="F28" s="3">
+        <v>3.43</v>
+      </c>
+      <c r="G28" s="3">
+        <v>3.69</v>
+      </c>
+      <c r="H28" s="3">
+        <v>3.11</v>
+      </c>
+      <c r="I28" s="3">
+        <v>3.29</v>
+      </c>
+      <c r="J28" s="3">
+        <v>3.44</v>
+      </c>
+      <c r="K28" s="3">
+        <v>3.29</v>
+      </c>
+      <c r="L28" s="4">
         <f t="shared" si="0"/>
-        <v/>
+        <v>3.3319999999999999</v>
       </c>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.25">

--- a/app/mevduat-kredi-faizleri/data/hoca-ile-borsa-faiz-takip-sablonu-guncel.xlsx
+++ b/app/mevduat-kredi-faizleri/data/hoca-ile-borsa-faiz-takip-sablonu-guncel.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projeler\hoca-ile-borsa\app\mevduat-kredi-faizleri\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C4D1EE2-A48F-48E6-A03B-1F4BDE7EE55A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FD70EA0-8FA5-453D-9810-D87B8CD732B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -413,6 +413,9 @@
                 <c:pt idx="23">
                   <c:v>46157</c:v>
                 </c:pt>
+                <c:pt idx="24">
+                  <c:v>46160</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -495,7 +498,7 @@
                   <c:v>43.413333333333334</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>0</c:v>
+                  <c:v>43.413333333333334</c:v>
                 </c:pt>
                 <c:pt idx="25">
                   <c:v>0</c:v>
@@ -1811,6 +1814,9 @@
                 <c:pt idx="23">
                   <c:v>46157</c:v>
                 </c:pt>
+                <c:pt idx="24">
+                  <c:v>46160</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1893,7 +1899,7 @@
                   <c:v>3.4384210526315795</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>0</c:v>
+                  <c:v>3.5226315789473679</c:v>
                 </c:pt>
                 <c:pt idx="25">
                   <c:v>0</c:v>
@@ -3209,6 +3215,9 @@
                 <c:pt idx="23">
                   <c:v>46157</c:v>
                 </c:pt>
+                <c:pt idx="24">
+                  <c:v>46160</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3291,7 +3300,7 @@
                   <c:v>2.8111111111111113</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>0</c:v>
+                  <c:v>2.8111111111111113</c:v>
                 </c:pt>
                 <c:pt idx="25">
                   <c:v>0</c:v>
@@ -4607,6 +4616,9 @@
                 <c:pt idx="23">
                   <c:v>46157</c:v>
                 </c:pt>
+                <c:pt idx="24">
+                  <c:v>46160</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -4689,7 +4701,7 @@
                   <c:v>3.3319999999999999</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>0</c:v>
+                  <c:v>3.3319999999999999</c:v>
                 </c:pt>
                 <c:pt idx="25">
                   <c:v>0</c:v>
@@ -8397,34 +8409,84 @@
       </c>
     </row>
     <row r="29" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A29" s="2"/>
-      <c r="B29" s="3"/>
-      <c r="C29" s="3"/>
-      <c r="D29" s="3"/>
-      <c r="E29" s="3"/>
-      <c r="F29" s="3"/>
-      <c r="G29" s="3"/>
-      <c r="H29" s="3"/>
-      <c r="I29" s="3"/>
-      <c r="J29" s="3"/>
-      <c r="K29" s="3"/>
-      <c r="L29" s="3"/>
-      <c r="M29" s="3"/>
-      <c r="N29" s="3"/>
-      <c r="O29" s="3"/>
-      <c r="P29" s="3"/>
-      <c r="Q29" s="3"/>
-      <c r="R29" s="3"/>
-      <c r="S29" s="3"/>
-      <c r="T29" s="3"/>
-      <c r="U29" s="3"/>
-      <c r="V29" s="3"/>
-      <c r="W29" s="3"/>
-      <c r="X29" s="3"/>
-      <c r="Y29" s="3"/>
-      <c r="Z29" s="4" t="str">
+      <c r="A29" s="2">
+        <v>46160</v>
+      </c>
+      <c r="B29" s="3">
+        <v>42</v>
+      </c>
+      <c r="C29" s="3">
+        <v>46</v>
+      </c>
+      <c r="D29" s="3">
+        <v>45</v>
+      </c>
+      <c r="E29" s="3">
+        <v>45</v>
+      </c>
+      <c r="F29" s="3">
+        <v>43.5</v>
+      </c>
+      <c r="G29" s="3">
+        <v>41.5</v>
+      </c>
+      <c r="H29" s="3">
+        <v>46</v>
+      </c>
+      <c r="I29" s="3">
+        <v>41</v>
+      </c>
+      <c r="J29" s="3">
+        <v>43</v>
+      </c>
+      <c r="K29" s="3">
+        <v>41</v>
+      </c>
+      <c r="L29" s="3">
+        <v>36</v>
+      </c>
+      <c r="M29" s="3">
+        <v>44</v>
+      </c>
+      <c r="N29" s="3">
+        <v>45</v>
+      </c>
+      <c r="O29" s="3">
+        <v>42.67</v>
+      </c>
+      <c r="P29" s="3">
+        <v>39</v>
+      </c>
+      <c r="Q29" s="3">
+        <v>45</v>
+      </c>
+      <c r="R29" s="3">
+        <v>45</v>
+      </c>
+      <c r="S29" s="3">
+        <v>45</v>
+      </c>
+      <c r="T29" s="3">
+        <v>45</v>
+      </c>
+      <c r="U29" s="3">
+        <v>43.5</v>
+      </c>
+      <c r="V29" s="3">
+        <v>43.5</v>
+      </c>
+      <c r="W29" s="3">
+        <v>42</v>
+      </c>
+      <c r="X29" s="3">
+        <v>47</v>
+      </c>
+      <c r="Y29" s="3">
+        <v>45.25</v>
+      </c>
+      <c r="Z29" s="4">
         <f t="shared" si="0"/>
-        <v/>
+        <v>43.413333333333334</v>
       </c>
     </row>
     <row r="30" spans="1:26" x14ac:dyDescent="0.25">
@@ -21343,29 +21405,69 @@
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A29" s="2"/>
-      <c r="B29" s="3"/>
-      <c r="C29" s="3"/>
-      <c r="D29" s="3"/>
-      <c r="E29" s="3"/>
-      <c r="F29" s="3"/>
-      <c r="G29" s="3"/>
-      <c r="H29" s="3"/>
-      <c r="I29" s="3"/>
-      <c r="J29" s="3"/>
-      <c r="K29" s="3"/>
-      <c r="L29" s="3"/>
-      <c r="M29" s="3"/>
-      <c r="N29" s="3"/>
-      <c r="O29" s="3"/>
-      <c r="P29" s="3"/>
-      <c r="Q29" s="3"/>
-      <c r="R29" s="3"/>
-      <c r="S29" s="3"/>
-      <c r="T29" s="3"/>
-      <c r="U29" s="4" t="str">
+      <c r="A29" s="2">
+        <v>46160</v>
+      </c>
+      <c r="B29" s="3">
+        <v>3.89</v>
+      </c>
+      <c r="C29" s="3">
+        <v>3.95</v>
+      </c>
+      <c r="D29" s="3">
+        <v>2.4900000000000002</v>
+      </c>
+      <c r="E29" s="3">
+        <v>3.49</v>
+      </c>
+      <c r="F29" s="3">
+        <v>4.3099999999999996</v>
+      </c>
+      <c r="G29" s="3">
+        <v>3.99</v>
+      </c>
+      <c r="H29" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="I29" s="3">
+        <v>3.39</v>
+      </c>
+      <c r="J29" s="3">
+        <v>3.09</v>
+      </c>
+      <c r="K29" s="3">
+        <v>3.99</v>
+      </c>
+      <c r="L29" s="3">
+        <v>2.89</v>
+      </c>
+      <c r="M29" s="3">
+        <v>3.59</v>
+      </c>
+      <c r="N29" s="3">
+        <v>3.69</v>
+      </c>
+      <c r="O29" s="3">
+        <v>3.49</v>
+      </c>
+      <c r="P29" s="3">
+        <v>3.89</v>
+      </c>
+      <c r="Q29" s="3">
+        <v>4.03</v>
+      </c>
+      <c r="R29" s="3">
+        <v>3.79</v>
+      </c>
+      <c r="S29" s="3">
+        <v>3.99</v>
+      </c>
+      <c r="T29" s="3">
+        <v>1.99</v>
+      </c>
+      <c r="U29" s="4">
         <f t="shared" si="0"/>
-        <v/>
+        <v>3.5226315789473679</v>
       </c>
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
@@ -31709,19 +31811,39 @@
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A29" s="2"/>
-      <c r="B29" s="3"/>
-      <c r="C29" s="3"/>
-      <c r="D29" s="3"/>
-      <c r="E29" s="3"/>
-      <c r="F29" s="3"/>
-      <c r="G29" s="3"/>
-      <c r="H29" s="3"/>
-      <c r="I29" s="3"/>
-      <c r="J29" s="3"/>
-      <c r="K29" s="4" t="str">
+      <c r="A29" s="2">
+        <v>46160</v>
+      </c>
+      <c r="B29" s="3">
+        <v>2.85</v>
+      </c>
+      <c r="C29" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="D29" s="3">
+        <v>2.72</v>
+      </c>
+      <c r="E29" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="F29" s="3">
+        <v>2.8</v>
+      </c>
+      <c r="G29" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="H29" s="3">
+        <v>2.63</v>
+      </c>
+      <c r="I29" s="3">
+        <v>2.74</v>
+      </c>
+      <c r="J29" s="3">
+        <v>2.59</v>
+      </c>
+      <c r="K29" s="4">
         <f t="shared" si="0"/>
-        <v/>
+        <v>2.8111111111111113</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
@@ -38532,20 +38654,42 @@
       </c>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A29" s="2"/>
-      <c r="B29" s="3"/>
-      <c r="C29" s="3"/>
-      <c r="D29" s="3"/>
-      <c r="E29" s="3"/>
-      <c r="F29" s="3"/>
-      <c r="G29" s="3"/>
-      <c r="H29" s="3"/>
-      <c r="I29" s="3"/>
-      <c r="J29" s="3"/>
-      <c r="K29" s="3"/>
-      <c r="L29" s="4" t="str">
+      <c r="A29" s="2">
+        <v>46160</v>
+      </c>
+      <c r="B29" s="3">
+        <v>3.49</v>
+      </c>
+      <c r="C29" s="3">
+        <v>3.08</v>
+      </c>
+      <c r="D29" s="3">
+        <v>3.15</v>
+      </c>
+      <c r="E29" s="3">
+        <v>3.35</v>
+      </c>
+      <c r="F29" s="3">
+        <v>3.43</v>
+      </c>
+      <c r="G29" s="3">
+        <v>3.69</v>
+      </c>
+      <c r="H29" s="3">
+        <v>3.11</v>
+      </c>
+      <c r="I29" s="3">
+        <v>3.29</v>
+      </c>
+      <c r="J29" s="3">
+        <v>3.44</v>
+      </c>
+      <c r="K29" s="3">
+        <v>3.29</v>
+      </c>
+      <c r="L29" s="4">
         <f t="shared" si="0"/>
-        <v/>
+        <v>3.3319999999999999</v>
       </c>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.25">

--- a/app/mevduat-kredi-faizleri/data/hoca-ile-borsa-faiz-takip-sablonu-guncel.xlsx
+++ b/app/mevduat-kredi-faizleri/data/hoca-ile-borsa-faiz-takip-sablonu-guncel.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projeler\hoca-ile-borsa\app\mevduat-kredi-faizleri\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FD70EA0-8FA5-453D-9810-D87B8CD732B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2DD77EE-9C63-4927-90CF-23B47A5E3DF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Mevduat" sheetId="1" r:id="rId1"/>
@@ -416,6 +416,9 @@
                 <c:pt idx="24">
                   <c:v>46160</c:v>
                 </c:pt>
+                <c:pt idx="25">
+                  <c:v>46162</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -501,7 +504,7 @@
                   <c:v>43.413333333333334</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>0</c:v>
+                  <c:v>43.455000000000005</c:v>
                 </c:pt>
                 <c:pt idx="26">
                   <c:v>0</c:v>
@@ -1817,6 +1820,9 @@
                 <c:pt idx="24">
                   <c:v>46160</c:v>
                 </c:pt>
+                <c:pt idx="25">
+                  <c:v>46162</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1902,7 +1908,7 @@
                   <c:v>3.5226315789473679</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>0</c:v>
+                  <c:v>3.5226315789473679</c:v>
                 </c:pt>
                 <c:pt idx="26">
                   <c:v>0</c:v>
@@ -3218,6 +3224,9 @@
                 <c:pt idx="24">
                   <c:v>46160</c:v>
                 </c:pt>
+                <c:pt idx="25">
+                  <c:v>46162</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3303,7 +3312,7 @@
                   <c:v>2.8111111111111113</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>0</c:v>
+                  <c:v>2.8222222222222224</c:v>
                 </c:pt>
                 <c:pt idx="26">
                   <c:v>0</c:v>
@@ -4619,6 +4628,9 @@
                 <c:pt idx="24">
                   <c:v>46160</c:v>
                 </c:pt>
+                <c:pt idx="25">
+                  <c:v>46162</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -4704,7 +4716,7 @@
                   <c:v>3.3319999999999999</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>0</c:v>
+                  <c:v>3.3319999999999999</c:v>
                 </c:pt>
                 <c:pt idx="26">
                   <c:v>0</c:v>
@@ -8490,34 +8502,84 @@
       </c>
     </row>
     <row r="30" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A30" s="2"/>
-      <c r="B30" s="3"/>
-      <c r="C30" s="3"/>
-      <c r="D30" s="3"/>
-      <c r="E30" s="3"/>
-      <c r="F30" s="3"/>
-      <c r="G30" s="3"/>
-      <c r="H30" s="3"/>
-      <c r="I30" s="3"/>
-      <c r="J30" s="3"/>
-      <c r="K30" s="3"/>
-      <c r="L30" s="3"/>
-      <c r="M30" s="3"/>
-      <c r="N30" s="3"/>
-      <c r="O30" s="3"/>
-      <c r="P30" s="3"/>
-      <c r="Q30" s="3"/>
-      <c r="R30" s="3"/>
-      <c r="S30" s="3"/>
-      <c r="T30" s="3"/>
-      <c r="U30" s="3"/>
-      <c r="V30" s="3"/>
-      <c r="W30" s="3"/>
-      <c r="X30" s="3"/>
-      <c r="Y30" s="3"/>
-      <c r="Z30" s="4" t="str">
+      <c r="A30" s="2">
+        <v>46162</v>
+      </c>
+      <c r="B30" s="3">
+        <v>42</v>
+      </c>
+      <c r="C30" s="3">
+        <v>46</v>
+      </c>
+      <c r="D30" s="3">
+        <v>45</v>
+      </c>
+      <c r="E30" s="3">
+        <v>45</v>
+      </c>
+      <c r="F30" s="3">
+        <v>43.5</v>
+      </c>
+      <c r="G30" s="3">
+        <v>41.5</v>
+      </c>
+      <c r="H30" s="3">
+        <v>46</v>
+      </c>
+      <c r="I30" s="3">
+        <v>41</v>
+      </c>
+      <c r="J30" s="3">
+        <v>43</v>
+      </c>
+      <c r="K30" s="3">
+        <v>41</v>
+      </c>
+      <c r="L30" s="3">
+        <v>36</v>
+      </c>
+      <c r="M30" s="3">
+        <v>44</v>
+      </c>
+      <c r="N30" s="3">
+        <v>45</v>
+      </c>
+      <c r="O30" s="3">
+        <v>42.67</v>
+      </c>
+      <c r="P30" s="3">
+        <v>39</v>
+      </c>
+      <c r="Q30" s="3">
+        <v>45</v>
+      </c>
+      <c r="R30" s="3">
+        <v>45</v>
+      </c>
+      <c r="S30" s="3">
+        <v>45</v>
+      </c>
+      <c r="T30" s="3">
+        <v>45</v>
+      </c>
+      <c r="U30" s="3">
+        <v>43.5</v>
+      </c>
+      <c r="V30" s="3">
+        <v>44.5</v>
+      </c>
+      <c r="W30" s="3">
+        <v>42</v>
+      </c>
+      <c r="X30" s="3">
+        <v>47</v>
+      </c>
+      <c r="Y30" s="3">
+        <v>45.25</v>
+      </c>
+      <c r="Z30" s="4">
         <f t="shared" si="0"/>
-        <v/>
+        <v>43.455000000000005</v>
       </c>
     </row>
     <row r="31" spans="1:26" x14ac:dyDescent="0.25">
@@ -21471,29 +21533,69 @@
       </c>
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A30" s="2"/>
-      <c r="B30" s="3"/>
-      <c r="C30" s="3"/>
-      <c r="D30" s="3"/>
-      <c r="E30" s="3"/>
-      <c r="F30" s="3"/>
-      <c r="G30" s="3"/>
-      <c r="H30" s="3"/>
-      <c r="I30" s="3"/>
-      <c r="J30" s="3"/>
-      <c r="K30" s="3"/>
-      <c r="L30" s="3"/>
-      <c r="M30" s="3"/>
-      <c r="N30" s="3"/>
-      <c r="O30" s="3"/>
-      <c r="P30" s="3"/>
-      <c r="Q30" s="3"/>
-      <c r="R30" s="3"/>
-      <c r="S30" s="3"/>
-      <c r="T30" s="3"/>
-      <c r="U30" s="4" t="str">
+      <c r="A30" s="2">
+        <v>46162</v>
+      </c>
+      <c r="B30" s="3">
+        <v>3.89</v>
+      </c>
+      <c r="C30" s="3">
+        <v>3.95</v>
+      </c>
+      <c r="D30" s="3">
+        <v>2.4900000000000002</v>
+      </c>
+      <c r="E30" s="3">
+        <v>3.49</v>
+      </c>
+      <c r="F30" s="3">
+        <v>4.3099999999999996</v>
+      </c>
+      <c r="G30" s="3">
+        <v>3.99</v>
+      </c>
+      <c r="H30" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="I30" s="3">
+        <v>3.39</v>
+      </c>
+      <c r="J30" s="3">
+        <v>3.09</v>
+      </c>
+      <c r="K30" s="3">
+        <v>3.99</v>
+      </c>
+      <c r="L30" s="3">
+        <v>2.89</v>
+      </c>
+      <c r="M30" s="3">
+        <v>3.59</v>
+      </c>
+      <c r="N30" s="3">
+        <v>3.69</v>
+      </c>
+      <c r="O30" s="3">
+        <v>3.49</v>
+      </c>
+      <c r="P30" s="3">
+        <v>3.89</v>
+      </c>
+      <c r="Q30" s="3">
+        <v>4.03</v>
+      </c>
+      <c r="R30" s="3">
+        <v>3.79</v>
+      </c>
+      <c r="S30" s="3">
+        <v>3.99</v>
+      </c>
+      <c r="T30" s="3">
+        <v>1.99</v>
+      </c>
+      <c r="U30" s="4">
         <f t="shared" si="0"/>
-        <v/>
+        <v>3.5226315789473679</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
@@ -31847,19 +31949,39 @@
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A30" s="2"/>
-      <c r="B30" s="3"/>
-      <c r="C30" s="3"/>
-      <c r="D30" s="3"/>
-      <c r="E30" s="3"/>
-      <c r="F30" s="3"/>
-      <c r="G30" s="3"/>
-      <c r="H30" s="3"/>
-      <c r="I30" s="3"/>
-      <c r="J30" s="3"/>
-      <c r="K30" s="4" t="str">
+      <c r="A30" s="2">
+        <v>46162</v>
+      </c>
+      <c r="B30" s="3">
+        <v>2.85</v>
+      </c>
+      <c r="C30" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="D30" s="3">
+        <v>2.72</v>
+      </c>
+      <c r="E30" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="F30" s="3">
+        <v>2.8</v>
+      </c>
+      <c r="G30" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="H30" s="3">
+        <v>2.63</v>
+      </c>
+      <c r="I30" s="3">
+        <v>2.74</v>
+      </c>
+      <c r="J30" s="3">
+        <v>2.69</v>
+      </c>
+      <c r="K30" s="4">
         <f t="shared" si="0"/>
-        <v/>
+        <v>2.8222222222222224</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
@@ -38693,20 +38815,42 @@
       </c>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A30" s="2"/>
-      <c r="B30" s="3"/>
-      <c r="C30" s="3"/>
-      <c r="D30" s="3"/>
-      <c r="E30" s="3"/>
-      <c r="F30" s="3"/>
-      <c r="G30" s="3"/>
-      <c r="H30" s="3"/>
-      <c r="I30" s="3"/>
-      <c r="J30" s="3"/>
-      <c r="K30" s="3"/>
-      <c r="L30" s="4" t="str">
+      <c r="A30" s="2">
+        <v>46162</v>
+      </c>
+      <c r="B30" s="3">
+        <v>3.49</v>
+      </c>
+      <c r="C30" s="3">
+        <v>3.08</v>
+      </c>
+      <c r="D30" s="3">
+        <v>3.15</v>
+      </c>
+      <c r="E30" s="3">
+        <v>3.35</v>
+      </c>
+      <c r="F30" s="3">
+        <v>3.43</v>
+      </c>
+      <c r="G30" s="3">
+        <v>3.69</v>
+      </c>
+      <c r="H30" s="3">
+        <v>3.11</v>
+      </c>
+      <c r="I30" s="3">
+        <v>3.29</v>
+      </c>
+      <c r="J30" s="3">
+        <v>3.44</v>
+      </c>
+      <c r="K30" s="3">
+        <v>3.29</v>
+      </c>
+      <c r="L30" s="4">
         <f t="shared" si="0"/>
-        <v/>
+        <v>3.3319999999999999</v>
       </c>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.25">

--- a/app/mevduat-kredi-faizleri/data/hoca-ile-borsa-faiz-takip-sablonu-guncel.xlsx
+++ b/app/mevduat-kredi-faizleri/data/hoca-ile-borsa-faiz-takip-sablonu-guncel.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projeler\hoca-ile-borsa\app\mevduat-kredi-faizleri\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2DD77EE-9C63-4927-90CF-23B47A5E3DF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B904A67-03CC-4E1A-A37F-A3C79E9DB088}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Mevduat" sheetId="1" r:id="rId1"/>
@@ -259,12 +259,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -419,6 +419,9 @@
                 <c:pt idx="25">
                   <c:v>46162</c:v>
                 </c:pt>
+                <c:pt idx="26">
+                  <c:v>46163</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -507,7 +510,7 @@
                   <c:v>43.455000000000005</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>0</c:v>
+                  <c:v>43.434583333333329</c:v>
                 </c:pt>
                 <c:pt idx="27">
                   <c:v>0</c:v>
@@ -1823,6 +1826,9 @@
                 <c:pt idx="25">
                   <c:v>46162</c:v>
                 </c:pt>
+                <c:pt idx="26">
+                  <c:v>46163</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1911,7 +1917,7 @@
                   <c:v>3.5226315789473679</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>0</c:v>
+                  <c:v>3.5278947368421054</c:v>
                 </c:pt>
                 <c:pt idx="27">
                   <c:v>0</c:v>
@@ -3227,6 +3233,9 @@
                 <c:pt idx="25">
                   <c:v>46162</c:v>
                 </c:pt>
+                <c:pt idx="26">
+                  <c:v>46163</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3315,7 +3324,7 @@
                   <c:v>2.8222222222222224</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>0</c:v>
+                  <c:v>2.8111111111111113</c:v>
                 </c:pt>
                 <c:pt idx="27">
                   <c:v>0</c:v>
@@ -4631,6 +4640,9 @@
                 <c:pt idx="25">
                   <c:v>46162</c:v>
                 </c:pt>
+                <c:pt idx="26">
+                  <c:v>46163</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -4719,7 +4731,7 @@
                   <c:v>3.3319999999999999</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>0</c:v>
+                  <c:v>3.3319999999999999</c:v>
                 </c:pt>
                 <c:pt idx="27">
                   <c:v>0</c:v>
@@ -6337,7 +6349,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="7"/>
@@ -6367,7 +6379,7 @@
       <c r="Z1" s="7"/>
     </row>
     <row r="2" spans="1:26" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="8" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="7"/>
@@ -8583,34 +8595,84 @@
       </c>
     </row>
     <row r="31" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A31" s="2"/>
-      <c r="B31" s="3"/>
-      <c r="C31" s="3"/>
-      <c r="D31" s="3"/>
-      <c r="E31" s="3"/>
-      <c r="F31" s="3"/>
-      <c r="G31" s="3"/>
-      <c r="H31" s="3"/>
-      <c r="I31" s="3"/>
-      <c r="J31" s="3"/>
-      <c r="K31" s="3"/>
-      <c r="L31" s="3"/>
-      <c r="M31" s="3"/>
-      <c r="N31" s="3"/>
-      <c r="O31" s="3"/>
-      <c r="P31" s="3"/>
-      <c r="Q31" s="3"/>
-      <c r="R31" s="3"/>
-      <c r="S31" s="3"/>
-      <c r="T31" s="3"/>
-      <c r="U31" s="3"/>
-      <c r="V31" s="3"/>
-      <c r="W31" s="3"/>
-      <c r="X31" s="3"/>
-      <c r="Y31" s="3"/>
-      <c r="Z31" s="4" t="str">
+      <c r="A31" s="2">
+        <v>46163</v>
+      </c>
+      <c r="B31" s="3">
+        <v>42</v>
+      </c>
+      <c r="C31" s="3">
+        <v>46</v>
+      </c>
+      <c r="D31" s="3">
+        <v>45</v>
+      </c>
+      <c r="E31" s="3">
+        <v>45</v>
+      </c>
+      <c r="F31" s="3">
+        <v>43.5</v>
+      </c>
+      <c r="G31" s="3">
+        <v>41.5</v>
+      </c>
+      <c r="H31" s="3">
+        <v>46</v>
+      </c>
+      <c r="I31" s="3">
+        <v>41</v>
+      </c>
+      <c r="J31" s="3">
+        <v>43</v>
+      </c>
+      <c r="K31" s="3">
+        <v>41</v>
+      </c>
+      <c r="L31" s="3">
+        <v>36</v>
+      </c>
+      <c r="M31" s="3">
+        <v>44</v>
+      </c>
+      <c r="N31" s="3">
+        <v>45</v>
+      </c>
+      <c r="O31" s="3">
+        <v>42.18</v>
+      </c>
+      <c r="P31" s="3">
+        <v>39</v>
+      </c>
+      <c r="Q31" s="3">
+        <v>45</v>
+      </c>
+      <c r="R31" s="3">
+        <v>45</v>
+      </c>
+      <c r="S31" s="3">
+        <v>45</v>
+      </c>
+      <c r="T31" s="3">
+        <v>45</v>
+      </c>
+      <c r="U31" s="3">
+        <v>43.5</v>
+      </c>
+      <c r="V31" s="3">
+        <v>44.5</v>
+      </c>
+      <c r="W31" s="3">
+        <v>42</v>
+      </c>
+      <c r="X31" s="3">
+        <v>47</v>
+      </c>
+      <c r="Y31" s="3">
+        <v>45.25</v>
+      </c>
+      <c r="Z31" s="4">
         <f t="shared" si="0"/>
-        <v/>
+        <v>43.434583333333329</v>
       </c>
     </row>
     <row r="32" spans="1:26" x14ac:dyDescent="0.25">
@@ -19768,7 +19830,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="6" t="s">
         <v>29</v>
       </c>
       <c r="B1" s="7"/>
@@ -19793,7 +19855,7 @@
       <c r="U1" s="7"/>
     </row>
     <row r="2" spans="1:21" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="8" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="7"/>
@@ -21599,29 +21661,69 @@
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A31" s="2"/>
-      <c r="B31" s="3"/>
-      <c r="C31" s="3"/>
-      <c r="D31" s="3"/>
-      <c r="E31" s="3"/>
-      <c r="F31" s="3"/>
-      <c r="G31" s="3"/>
-      <c r="H31" s="3"/>
-      <c r="I31" s="3"/>
-      <c r="J31" s="3"/>
-      <c r="K31" s="3"/>
-      <c r="L31" s="3"/>
-      <c r="M31" s="3"/>
-      <c r="N31" s="3"/>
-      <c r="O31" s="3"/>
-      <c r="P31" s="3"/>
-      <c r="Q31" s="3"/>
-      <c r="R31" s="3"/>
-      <c r="S31" s="3"/>
-      <c r="T31" s="3"/>
-      <c r="U31" s="4" t="str">
+      <c r="A31" s="2">
+        <v>46163</v>
+      </c>
+      <c r="B31" s="3">
+        <v>3.89</v>
+      </c>
+      <c r="C31" s="3">
+        <v>3.95</v>
+      </c>
+      <c r="D31" s="3">
+        <v>2.4900000000000002</v>
+      </c>
+      <c r="E31" s="3">
+        <v>3.49</v>
+      </c>
+      <c r="F31" s="3">
+        <v>4.3099999999999996</v>
+      </c>
+      <c r="G31" s="3">
+        <v>3.99</v>
+      </c>
+      <c r="H31" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="I31" s="3">
+        <v>3.39</v>
+      </c>
+      <c r="J31" s="3">
+        <v>3.09</v>
+      </c>
+      <c r="K31" s="3">
+        <v>3.99</v>
+      </c>
+      <c r="L31" s="3">
+        <v>2.89</v>
+      </c>
+      <c r="M31" s="3">
+        <v>3.59</v>
+      </c>
+      <c r="N31" s="3">
+        <v>3.69</v>
+      </c>
+      <c r="O31" s="3">
+        <v>3.49</v>
+      </c>
+      <c r="P31" s="3">
+        <v>3.89</v>
+      </c>
+      <c r="Q31" s="3">
+        <v>4.03</v>
+      </c>
+      <c r="R31" s="3">
+        <v>3.89</v>
+      </c>
+      <c r="S31" s="3">
+        <v>3.99</v>
+      </c>
+      <c r="T31" s="3">
+        <v>1.99</v>
+      </c>
+      <c r="U31" s="4">
         <f t="shared" si="0"/>
-        <v/>
+        <v>3.5278947368421054</v>
       </c>
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
@@ -30984,7 +31086,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="6" t="s">
         <v>37</v>
       </c>
       <c r="B1" s="7"/>
@@ -30999,7 +31101,7 @@
       <c r="K1" s="7"/>
     </row>
     <row r="2" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="8" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="7"/>
@@ -31985,19 +32087,39 @@
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A31" s="2"/>
-      <c r="B31" s="3"/>
-      <c r="C31" s="3"/>
-      <c r="D31" s="3"/>
-      <c r="E31" s="3"/>
-      <c r="F31" s="3"/>
-      <c r="G31" s="3"/>
-      <c r="H31" s="3"/>
-      <c r="I31" s="3"/>
-      <c r="J31" s="3"/>
-      <c r="K31" s="4" t="str">
+      <c r="A31" s="2">
+        <v>46163</v>
+      </c>
+      <c r="B31" s="3">
+        <v>2.85</v>
+      </c>
+      <c r="C31" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="D31" s="3">
+        <v>2.72</v>
+      </c>
+      <c r="E31" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="F31" s="3">
+        <v>2.8</v>
+      </c>
+      <c r="G31" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="H31" s="3">
+        <v>2.63</v>
+      </c>
+      <c r="I31" s="3">
+        <v>2.74</v>
+      </c>
+      <c r="J31" s="3">
+        <v>2.59</v>
+      </c>
+      <c r="K31" s="4">
         <f t="shared" si="0"/>
-        <v/>
+        <v>2.8111111111111113</v>
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.25">
@@ -37770,7 +37892,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="6" t="s">
         <v>39</v>
       </c>
       <c r="B1" s="7"/>
@@ -37786,7 +37908,7 @@
       <c r="L1" s="7"/>
     </row>
     <row r="2" spans="1:12" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="8" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="7"/>
@@ -38854,20 +38976,42 @@
       </c>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A31" s="2"/>
-      <c r="B31" s="3"/>
-      <c r="C31" s="3"/>
-      <c r="D31" s="3"/>
-      <c r="E31" s="3"/>
-      <c r="F31" s="3"/>
-      <c r="G31" s="3"/>
-      <c r="H31" s="3"/>
-      <c r="I31" s="3"/>
-      <c r="J31" s="3"/>
-      <c r="K31" s="3"/>
-      <c r="L31" s="4" t="str">
+      <c r="A31" s="2">
+        <v>46163</v>
+      </c>
+      <c r="B31" s="3">
+        <v>3.49</v>
+      </c>
+      <c r="C31" s="3">
+        <v>3.08</v>
+      </c>
+      <c r="D31" s="3">
+        <v>3.15</v>
+      </c>
+      <c r="E31" s="3">
+        <v>3.35</v>
+      </c>
+      <c r="F31" s="3">
+        <v>3.43</v>
+      </c>
+      <c r="G31" s="3">
+        <v>3.69</v>
+      </c>
+      <c r="H31" s="3">
+        <v>3.11</v>
+      </c>
+      <c r="I31" s="3">
+        <v>3.29</v>
+      </c>
+      <c r="J31" s="3">
+        <v>3.44</v>
+      </c>
+      <c r="K31" s="3">
+        <v>3.29</v>
+      </c>
+      <c r="L31" s="4">
         <f t="shared" si="0"/>
-        <v/>
+        <v>3.3319999999999999</v>
       </c>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.25">

--- a/app/mevduat-kredi-faizleri/data/hoca-ile-borsa-faiz-takip-sablonu-guncel.xlsx
+++ b/app/mevduat-kredi-faizleri/data/hoca-ile-borsa-faiz-takip-sablonu-guncel.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projeler\hoca-ile-borsa\app\mevduat-kredi-faizleri\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{852BD5C7-F3CB-4F85-B4FA-7D9B469C4838}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEF36469-A229-4F41-B35D-A1E337A0F6FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -425,6 +425,9 @@
                 <c:pt idx="27">
                   <c:v>46164</c:v>
                 </c:pt>
+                <c:pt idx="28">
+                  <c:v>46167</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -519,7 +522,7 @@
                   <c:v>43.434583333333329</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>0</c:v>
+                  <c:v>43.476249999999993</c:v>
                 </c:pt>
                 <c:pt idx="29">
                   <c:v>0</c:v>
@@ -1835,6 +1838,9 @@
                 <c:pt idx="27">
                   <c:v>46164</c:v>
                 </c:pt>
+                <c:pt idx="28">
+                  <c:v>46167</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1929,7 +1935,7 @@
                   <c:v>3.5278947368421054</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>0</c:v>
+                  <c:v>3.6568421052631579</c:v>
                 </c:pt>
                 <c:pt idx="29">
                   <c:v>0</c:v>
@@ -3245,6 +3251,9 @@
                 <c:pt idx="27">
                   <c:v>46164</c:v>
                 </c:pt>
+                <c:pt idx="28">
+                  <c:v>46167</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3339,7 +3348,7 @@
                   <c:v>2.8111111111111113</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>0</c:v>
+                  <c:v>2.838888888888889</c:v>
                 </c:pt>
                 <c:pt idx="29">
                   <c:v>0</c:v>
@@ -4655,6 +4664,9 @@
                 <c:pt idx="27">
                   <c:v>46164</c:v>
                 </c:pt>
+                <c:pt idx="28">
+                  <c:v>46167</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -4749,7 +4761,7 @@
                   <c:v>3.3319999999999999</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>0</c:v>
+                  <c:v>3.3530000000000002</c:v>
                 </c:pt>
                 <c:pt idx="29">
                   <c:v>0</c:v>
@@ -8769,34 +8781,84 @@
       </c>
     </row>
     <row r="33" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A33" s="2"/>
-      <c r="B33" s="3"/>
-      <c r="C33" s="3"/>
-      <c r="D33" s="3"/>
-      <c r="E33" s="3"/>
-      <c r="F33" s="3"/>
-      <c r="G33" s="3"/>
-      <c r="H33" s="3"/>
-      <c r="I33" s="3"/>
-      <c r="J33" s="3"/>
-      <c r="K33" s="3"/>
-      <c r="L33" s="3"/>
-      <c r="M33" s="3"/>
-      <c r="N33" s="3"/>
-      <c r="O33" s="3"/>
-      <c r="P33" s="3"/>
-      <c r="Q33" s="3"/>
-      <c r="R33" s="3"/>
-      <c r="S33" s="3"/>
-      <c r="T33" s="3"/>
-      <c r="U33" s="3"/>
-      <c r="V33" s="3"/>
-      <c r="W33" s="3"/>
-      <c r="X33" s="3"/>
-      <c r="Y33" s="3"/>
-      <c r="Z33" s="4" t="str">
+      <c r="A33" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B33" s="3">
+        <v>42.5</v>
+      </c>
+      <c r="C33" s="3">
+        <v>46</v>
+      </c>
+      <c r="D33" s="3">
+        <v>45</v>
+      </c>
+      <c r="E33" s="3">
+        <v>45</v>
+      </c>
+      <c r="F33" s="3">
+        <v>43.5</v>
+      </c>
+      <c r="G33" s="3">
+        <v>41.5</v>
+      </c>
+      <c r="H33" s="3">
+        <v>46</v>
+      </c>
+      <c r="I33" s="3">
+        <v>41</v>
+      </c>
+      <c r="J33" s="3">
+        <v>43</v>
+      </c>
+      <c r="K33" s="3">
+        <v>41</v>
+      </c>
+      <c r="L33" s="3">
+        <v>36</v>
+      </c>
+      <c r="M33" s="3">
+        <v>44</v>
+      </c>
+      <c r="N33" s="3">
+        <v>45</v>
+      </c>
+      <c r="O33" s="3">
+        <v>42.18</v>
+      </c>
+      <c r="P33" s="3">
+        <v>39</v>
+      </c>
+      <c r="Q33" s="3">
+        <v>45</v>
+      </c>
+      <c r="R33" s="3">
+        <v>45</v>
+      </c>
+      <c r="S33" s="3">
+        <v>45</v>
+      </c>
+      <c r="T33" s="3">
+        <v>45</v>
+      </c>
+      <c r="U33" s="3">
+        <v>43.5</v>
+      </c>
+      <c r="V33" s="3">
+        <v>45</v>
+      </c>
+      <c r="W33" s="3">
+        <v>42</v>
+      </c>
+      <c r="X33" s="3">
+        <v>47</v>
+      </c>
+      <c r="Y33" s="3">
+        <v>45.25</v>
+      </c>
+      <c r="Z33" s="4">
         <f t="shared" si="0"/>
-        <v/>
+        <v>43.476249999999993</v>
       </c>
     </row>
     <row r="34" spans="1:26" x14ac:dyDescent="0.25">
@@ -21855,29 +21917,69 @@
       </c>
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A33" s="2"/>
-      <c r="B33" s="3"/>
-      <c r="C33" s="3"/>
-      <c r="D33" s="3"/>
-      <c r="E33" s="3"/>
-      <c r="F33" s="3"/>
-      <c r="G33" s="3"/>
-      <c r="H33" s="3"/>
-      <c r="I33" s="3"/>
-      <c r="J33" s="3"/>
-      <c r="K33" s="3"/>
-      <c r="L33" s="3"/>
-      <c r="M33" s="3"/>
-      <c r="N33" s="3"/>
-      <c r="O33" s="3"/>
-      <c r="P33" s="3"/>
-      <c r="Q33" s="3"/>
-      <c r="R33" s="3"/>
-      <c r="S33" s="3"/>
-      <c r="T33" s="3"/>
-      <c r="U33" s="4" t="str">
+      <c r="A33" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B33" s="3">
+        <v>4.29</v>
+      </c>
+      <c r="C33" s="3">
+        <v>3.95</v>
+      </c>
+      <c r="D33" s="3">
+        <v>2.4900000000000002</v>
+      </c>
+      <c r="E33" s="3">
+        <v>3.99</v>
+      </c>
+      <c r="F33" s="3">
+        <v>4.3099999999999996</v>
+      </c>
+      <c r="G33" s="3">
+        <v>3.99</v>
+      </c>
+      <c r="H33" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="I33" s="3">
+        <v>3.39</v>
+      </c>
+      <c r="J33" s="3">
+        <v>3.09</v>
+      </c>
+      <c r="K33" s="3">
+        <v>4.1399999999999997</v>
+      </c>
+      <c r="L33" s="3">
+        <v>3.79</v>
+      </c>
+      <c r="M33" s="3">
+        <v>3.59</v>
+      </c>
+      <c r="N33" s="3">
+        <v>3.69</v>
+      </c>
+      <c r="O33" s="3">
+        <v>3.99</v>
+      </c>
+      <c r="P33" s="3">
+        <v>3.89</v>
+      </c>
+      <c r="Q33" s="3">
+        <v>4.03</v>
+      </c>
+      <c r="R33" s="3">
+        <v>3.89</v>
+      </c>
+      <c r="S33" s="3">
+        <v>3.99</v>
+      </c>
+      <c r="T33" s="3">
+        <v>1.99</v>
+      </c>
+      <c r="U33" s="4">
         <f t="shared" si="0"/>
-        <v/>
+        <v>3.6568421052631579</v>
       </c>
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
@@ -32261,19 +32363,39 @@
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A33" s="2"/>
-      <c r="B33" s="3"/>
-      <c r="C33" s="3"/>
-      <c r="D33" s="3"/>
-      <c r="E33" s="3"/>
-      <c r="F33" s="3"/>
-      <c r="G33" s="3"/>
-      <c r="H33" s="3"/>
-      <c r="I33" s="3"/>
-      <c r="J33" s="3"/>
-      <c r="K33" s="4" t="str">
+      <c r="A33" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B33" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="C33" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="D33" s="3">
+        <v>2.83</v>
+      </c>
+      <c r="E33" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="F33" s="3">
+        <v>2.8</v>
+      </c>
+      <c r="G33" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="H33" s="3">
+        <v>2.63</v>
+      </c>
+      <c r="I33" s="3">
+        <v>2.74</v>
+      </c>
+      <c r="J33" s="3">
+        <v>2.59</v>
+      </c>
+      <c r="K33" s="4">
         <f t="shared" si="0"/>
-        <v/>
+        <v>2.838888888888889</v>
       </c>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.25">
@@ -39176,20 +39298,42 @@
       </c>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A33" s="2"/>
-      <c r="B33" s="3"/>
-      <c r="C33" s="3"/>
-      <c r="D33" s="3"/>
-      <c r="E33" s="3"/>
-      <c r="F33" s="3"/>
-      <c r="G33" s="3"/>
-      <c r="H33" s="3"/>
-      <c r="I33" s="3"/>
-      <c r="J33" s="3"/>
-      <c r="K33" s="3"/>
-      <c r="L33" s="4" t="str">
+      <c r="A33" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B33" s="3">
+        <v>3.59</v>
+      </c>
+      <c r="C33" s="3">
+        <v>3.19</v>
+      </c>
+      <c r="D33" s="3">
+        <v>3.15</v>
+      </c>
+      <c r="E33" s="3">
+        <v>3.35</v>
+      </c>
+      <c r="F33" s="3">
+        <v>3.43</v>
+      </c>
+      <c r="G33" s="3">
+        <v>3.69</v>
+      </c>
+      <c r="H33" s="3">
+        <v>3.11</v>
+      </c>
+      <c r="I33" s="3">
+        <v>3.29</v>
+      </c>
+      <c r="J33" s="3">
+        <v>3.44</v>
+      </c>
+      <c r="K33" s="3">
+        <v>3.29</v>
+      </c>
+      <c r="L33" s="4">
         <f t="shared" si="0"/>
-        <v/>
+        <v>3.3530000000000002</v>
       </c>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.25">

--- a/app/mevduat-kredi-faizleri/data/hoca-ile-borsa-faiz-takip-sablonu-guncel.xlsx
+++ b/app/mevduat-kredi-faizleri/data/hoca-ile-borsa-faiz-takip-sablonu-guncel.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projeler\hoca-ile-borsa\app\mevduat-kredi-faizleri\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A153DB52-B09A-4933-ADD1-2DCD323129B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93966EA7-CD4C-4315-A33E-0F0450579D66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Mevduat" sheetId="1" r:id="rId1"/>
@@ -19,17 +19,6 @@
     <sheet name="Taşıt Kredisi" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
@@ -434,6 +423,9 @@
                 <c:pt idx="30">
                   <c:v>46174</c:v>
                 </c:pt>
+                <c:pt idx="31">
+                  <c:v>46175</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -537,7 +529,7 @@
                   <c:v>43.476249999999993</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>0</c:v>
+                  <c:v>43.472500000000004</c:v>
                 </c:pt>
                 <c:pt idx="32">
                   <c:v>0</c:v>
@@ -1853,6 +1845,9 @@
                 <c:pt idx="30">
                   <c:v>46174</c:v>
                 </c:pt>
+                <c:pt idx="31">
+                  <c:v>46175</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1956,7 +1951,7 @@
                   <c:v>3.6568421052631579</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>0</c:v>
+                  <c:v>3.7305263157894726</c:v>
                 </c:pt>
                 <c:pt idx="32">
                   <c:v>0</c:v>
@@ -3272,6 +3267,9 @@
                 <c:pt idx="30">
                   <c:v>46174</c:v>
                 </c:pt>
+                <c:pt idx="31">
+                  <c:v>46175</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3375,7 +3373,7 @@
                   <c:v>2.838888888888889</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>0</c:v>
+                  <c:v>2.8555555555555556</c:v>
                 </c:pt>
                 <c:pt idx="32">
                   <c:v>0</c:v>
@@ -4691,6 +4689,9 @@
                 <c:pt idx="30">
                   <c:v>46174</c:v>
                 </c:pt>
+                <c:pt idx="31">
+                  <c:v>46175</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -4794,7 +4795,7 @@
                   <c:v>3.3530000000000002</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>0</c:v>
+                  <c:v>3.399</c:v>
                 </c:pt>
                 <c:pt idx="32">
                   <c:v>0</c:v>
@@ -9048,34 +9049,84 @@
       </c>
     </row>
     <row r="36" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A36" s="2"/>
-      <c r="B36" s="3"/>
-      <c r="C36" s="3"/>
-      <c r="D36" s="3"/>
-      <c r="E36" s="3"/>
-      <c r="F36" s="3"/>
-      <c r="G36" s="3"/>
-      <c r="H36" s="3"/>
-      <c r="I36" s="3"/>
-      <c r="J36" s="3"/>
-      <c r="K36" s="3"/>
-      <c r="L36" s="3"/>
-      <c r="M36" s="3"/>
-      <c r="N36" s="3"/>
-      <c r="O36" s="3"/>
-      <c r="P36" s="3"/>
-      <c r="Q36" s="3"/>
-      <c r="R36" s="3"/>
-      <c r="S36" s="3"/>
-      <c r="T36" s="3"/>
-      <c r="U36" s="3"/>
-      <c r="V36" s="3"/>
-      <c r="W36" s="3"/>
-      <c r="X36" s="3"/>
-      <c r="Y36" s="3"/>
-      <c r="Z36" s="4" t="str">
+      <c r="A36" s="2">
+        <v>46175</v>
+      </c>
+      <c r="B36" s="3">
+        <v>42.5</v>
+      </c>
+      <c r="C36" s="3">
+        <v>46</v>
+      </c>
+      <c r="D36" s="3">
+        <v>45</v>
+      </c>
+      <c r="E36" s="3">
+        <v>45</v>
+      </c>
+      <c r="F36" s="3">
+        <v>43.5</v>
+      </c>
+      <c r="G36" s="3">
+        <v>41.5</v>
+      </c>
+      <c r="H36" s="3">
+        <v>46</v>
+      </c>
+      <c r="I36" s="3">
+        <v>41</v>
+      </c>
+      <c r="J36" s="3">
+        <v>43</v>
+      </c>
+      <c r="K36" s="3">
+        <v>41</v>
+      </c>
+      <c r="L36" s="3">
+        <v>36</v>
+      </c>
+      <c r="M36" s="3">
+        <v>44</v>
+      </c>
+      <c r="N36" s="3">
+        <v>45</v>
+      </c>
+      <c r="O36" s="3">
+        <v>42.59</v>
+      </c>
+      <c r="P36" s="3">
+        <v>39</v>
+      </c>
+      <c r="Q36" s="3">
+        <v>45</v>
+      </c>
+      <c r="R36" s="3">
+        <v>45</v>
+      </c>
+      <c r="S36" s="3">
+        <v>45</v>
+      </c>
+      <c r="T36" s="3">
+        <v>45</v>
+      </c>
+      <c r="U36" s="3">
+        <v>43.5</v>
+      </c>
+      <c r="V36" s="3">
+        <v>44.5</v>
+      </c>
+      <c r="W36" s="3">
+        <v>42</v>
+      </c>
+      <c r="X36" s="3">
+        <v>47</v>
+      </c>
+      <c r="Y36" s="3">
+        <v>45.25</v>
+      </c>
+      <c r="Z36" s="4">
         <f t="shared" si="0"/>
-        <v/>
+        <v>43.472500000000004</v>
       </c>
     </row>
     <row r="37" spans="1:26" x14ac:dyDescent="0.25">
@@ -22239,29 +22290,69 @@
       </c>
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A36" s="2"/>
-      <c r="B36" s="3"/>
-      <c r="C36" s="3"/>
-      <c r="D36" s="3"/>
-      <c r="E36" s="3"/>
-      <c r="F36" s="3"/>
-      <c r="G36" s="3"/>
-      <c r="H36" s="3"/>
-      <c r="I36" s="3"/>
-      <c r="J36" s="3"/>
-      <c r="K36" s="3"/>
-      <c r="L36" s="3"/>
-      <c r="M36" s="3"/>
-      <c r="N36" s="3"/>
-      <c r="O36" s="3"/>
-      <c r="P36" s="3"/>
-      <c r="Q36" s="3"/>
-      <c r="R36" s="3"/>
-      <c r="S36" s="3"/>
-      <c r="T36" s="3"/>
-      <c r="U36" s="4" t="str">
+      <c r="A36" s="2">
+        <v>46175</v>
+      </c>
+      <c r="B36" s="3">
+        <v>4.29</v>
+      </c>
+      <c r="C36" s="3">
+        <v>3.95</v>
+      </c>
+      <c r="D36" s="3">
+        <v>3.49</v>
+      </c>
+      <c r="E36" s="3">
+        <v>4.1900000000000004</v>
+      </c>
+      <c r="F36" s="3">
+        <v>4.3099999999999996</v>
+      </c>
+      <c r="G36" s="3">
+        <v>3.99</v>
+      </c>
+      <c r="H36" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="I36" s="3">
+        <v>3.39</v>
+      </c>
+      <c r="J36" s="3">
+        <v>3.09</v>
+      </c>
+      <c r="K36" s="3">
+        <v>4.1399999999999997</v>
+      </c>
+      <c r="L36" s="3">
+        <v>3.79</v>
+      </c>
+      <c r="M36" s="3">
+        <v>3.59</v>
+      </c>
+      <c r="N36" s="3">
+        <v>3.69</v>
+      </c>
+      <c r="O36" s="3">
+        <v>4.1900000000000004</v>
+      </c>
+      <c r="P36" s="3">
+        <v>3.89</v>
+      </c>
+      <c r="Q36" s="3">
+        <v>4.03</v>
+      </c>
+      <c r="R36" s="3">
+        <v>3.89</v>
+      </c>
+      <c r="S36" s="3">
+        <v>3.99</v>
+      </c>
+      <c r="T36" s="3">
+        <v>1.99</v>
+      </c>
+      <c r="U36" s="4">
         <f t="shared" si="0"/>
-        <v/>
+        <v>3.7305263157894726</v>
       </c>
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
@@ -32675,19 +32766,39 @@
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A36" s="2"/>
-      <c r="B36" s="3"/>
-      <c r="C36" s="3"/>
-      <c r="D36" s="3"/>
-      <c r="E36" s="3"/>
-      <c r="F36" s="3"/>
-      <c r="G36" s="3"/>
-      <c r="H36" s="3"/>
-      <c r="I36" s="3"/>
-      <c r="J36" s="3"/>
-      <c r="K36" s="4" t="str">
+      <c r="A36" s="2">
+        <v>46175</v>
+      </c>
+      <c r="B36" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="C36" s="3">
+        <v>3.14</v>
+      </c>
+      <c r="D36" s="3">
+        <v>2.83</v>
+      </c>
+      <c r="E36" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="F36" s="3">
+        <v>2.8</v>
+      </c>
+      <c r="G36" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="H36" s="3">
+        <v>2.63</v>
+      </c>
+      <c r="I36" s="3">
+        <v>2.74</v>
+      </c>
+      <c r="J36" s="3">
+        <v>2.59</v>
+      </c>
+      <c r="K36" s="4">
         <f t="shared" si="0"/>
-        <v/>
+        <v>2.8555555555555556</v>
       </c>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.25">
@@ -39659,20 +39770,42 @@
       </c>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A36" s="2"/>
-      <c r="B36" s="3"/>
-      <c r="C36" s="3"/>
-      <c r="D36" s="3"/>
-      <c r="E36" s="3"/>
-      <c r="F36" s="3"/>
-      <c r="G36" s="3"/>
-      <c r="H36" s="3"/>
-      <c r="I36" s="3"/>
-      <c r="J36" s="3"/>
-      <c r="K36" s="3"/>
-      <c r="L36" s="4" t="str">
+      <c r="A36" s="2">
+        <v>46175</v>
+      </c>
+      <c r="B36" s="3">
+        <v>3.59</v>
+      </c>
+      <c r="C36" s="3">
+        <v>3.19</v>
+      </c>
+      <c r="D36" s="3">
+        <v>3.59</v>
+      </c>
+      <c r="E36" s="3">
+        <v>3.35</v>
+      </c>
+      <c r="F36" s="3">
+        <v>3.43</v>
+      </c>
+      <c r="G36" s="3">
+        <v>3.69</v>
+      </c>
+      <c r="H36" s="3">
+        <v>3.11</v>
+      </c>
+      <c r="I36" s="3">
+        <v>3.29</v>
+      </c>
+      <c r="J36" s="3">
+        <v>3.46</v>
+      </c>
+      <c r="K36" s="3">
+        <v>3.29</v>
+      </c>
+      <c r="L36" s="4">
         <f t="shared" si="0"/>
-        <v/>
+        <v>3.399</v>
       </c>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.25">

--- a/app/mevduat-kredi-faizleri/data/hoca-ile-borsa-faiz-takip-sablonu-guncel.xlsx
+++ b/app/mevduat-kredi-faizleri/data/hoca-ile-borsa-faiz-takip-sablonu-guncel.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projeler\hoca-ile-borsa\app\mevduat-kredi-faizleri\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFF7B334-319B-48E9-80E1-599E237B36EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{460F093C-9AD3-448A-807A-6368CF891E59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-60" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Mevduat" sheetId="1" r:id="rId1"/>
@@ -259,12 +259,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -443,6 +443,9 @@
                 <c:pt idx="33">
                   <c:v>46177</c:v>
                 </c:pt>
+                <c:pt idx="34">
+                  <c:v>46178</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -555,7 +558,7 @@
                   <c:v>43.472500000000004</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>0</c:v>
+                  <c:v>43.472500000000004</c:v>
                 </c:pt>
                 <c:pt idx="35">
                   <c:v>0</c:v>
@@ -1871,6 +1874,9 @@
                 <c:pt idx="33">
                   <c:v>46177</c:v>
                 </c:pt>
+                <c:pt idx="34">
+                  <c:v>46178</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1983,7 +1989,7 @@
                   <c:v>3.7305263157894726</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>0</c:v>
+                  <c:v>3.7305263157894726</c:v>
                 </c:pt>
                 <c:pt idx="35">
                   <c:v>0</c:v>
@@ -3299,6 +3305,9 @@
                 <c:pt idx="33">
                   <c:v>46177</c:v>
                 </c:pt>
+                <c:pt idx="34">
+                  <c:v>46178</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3411,7 +3420,7 @@
                   <c:v>2.8555555555555556</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>0</c:v>
+                  <c:v>2.8555555555555556</c:v>
                 </c:pt>
                 <c:pt idx="35">
                   <c:v>0</c:v>
@@ -4727,6 +4736,9 @@
                 <c:pt idx="33">
                   <c:v>46177</c:v>
                 </c:pt>
+                <c:pt idx="34">
+                  <c:v>46178</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -4839,7 +4851,7 @@
                   <c:v>3.399</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>0</c:v>
+                  <c:v>3.399</c:v>
                 </c:pt>
                 <c:pt idx="35">
                   <c:v>0</c:v>
@@ -6433,7 +6445,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="7"/>
@@ -6463,7 +6475,7 @@
       <c r="Z1" s="7"/>
     </row>
     <row r="2" spans="1:26" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="8" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="7"/>
@@ -9327,34 +9339,84 @@
       </c>
     </row>
     <row r="39" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A39" s="2"/>
-      <c r="B39" s="3"/>
-      <c r="C39" s="3"/>
-      <c r="D39" s="3"/>
-      <c r="E39" s="3"/>
-      <c r="F39" s="3"/>
-      <c r="G39" s="3"/>
-      <c r="H39" s="3"/>
-      <c r="I39" s="3"/>
-      <c r="J39" s="3"/>
-      <c r="K39" s="3"/>
-      <c r="L39" s="3"/>
-      <c r="M39" s="3"/>
-      <c r="N39" s="3"/>
-      <c r="O39" s="3"/>
-      <c r="P39" s="3"/>
-      <c r="Q39" s="3"/>
-      <c r="R39" s="3"/>
-      <c r="S39" s="3"/>
-      <c r="T39" s="3"/>
-      <c r="U39" s="3"/>
-      <c r="V39" s="3"/>
-      <c r="W39" s="3"/>
-      <c r="X39" s="3"/>
-      <c r="Y39" s="3"/>
-      <c r="Z39" s="4" t="str">
+      <c r="A39" s="2">
+        <v>46178</v>
+      </c>
+      <c r="B39" s="3">
+        <v>42.5</v>
+      </c>
+      <c r="C39" s="3">
+        <v>46</v>
+      </c>
+      <c r="D39" s="3">
+        <v>45</v>
+      </c>
+      <c r="E39" s="3">
+        <v>45</v>
+      </c>
+      <c r="F39" s="3">
+        <v>43.5</v>
+      </c>
+      <c r="G39" s="3">
+        <v>41</v>
+      </c>
+      <c r="H39" s="3">
+        <v>46</v>
+      </c>
+      <c r="I39" s="3">
+        <v>41.5</v>
+      </c>
+      <c r="J39" s="3">
+        <v>43</v>
+      </c>
+      <c r="K39" s="3">
+        <v>41</v>
+      </c>
+      <c r="L39" s="3">
+        <v>36</v>
+      </c>
+      <c r="M39" s="3">
+        <v>44</v>
+      </c>
+      <c r="N39" s="3">
+        <v>45</v>
+      </c>
+      <c r="O39" s="3">
+        <v>42.59</v>
+      </c>
+      <c r="P39" s="3">
+        <v>39</v>
+      </c>
+      <c r="Q39" s="3">
+        <v>45</v>
+      </c>
+      <c r="R39" s="3">
+        <v>45</v>
+      </c>
+      <c r="S39" s="3">
+        <v>45</v>
+      </c>
+      <c r="T39" s="3">
+        <v>45</v>
+      </c>
+      <c r="U39" s="3">
+        <v>43.5</v>
+      </c>
+      <c r="V39" s="3">
+        <v>44.5</v>
+      </c>
+      <c r="W39" s="3">
+        <v>42</v>
+      </c>
+      <c r="X39" s="3">
+        <v>47</v>
+      </c>
+      <c r="Y39" s="3">
+        <v>45.25</v>
+      </c>
+      <c r="Z39" s="4">
         <f t="shared" si="0"/>
-        <v/>
+        <v>43.472500000000004</v>
       </c>
     </row>
     <row r="40" spans="1:26" x14ac:dyDescent="0.25">
@@ -20264,7 +20326,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="6" t="s">
         <v>29</v>
       </c>
       <c r="B1" s="7"/>
@@ -20289,7 +20351,7 @@
       <c r="U1" s="7"/>
     </row>
     <row r="2" spans="1:21" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="8" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="7"/>
@@ -22623,29 +22685,69 @@
       </c>
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A39" s="2"/>
-      <c r="B39" s="3"/>
-      <c r="C39" s="3"/>
-      <c r="D39" s="3"/>
-      <c r="E39" s="3"/>
-      <c r="F39" s="3"/>
-      <c r="G39" s="3"/>
-      <c r="H39" s="3"/>
-      <c r="I39" s="3"/>
-      <c r="J39" s="3"/>
-      <c r="K39" s="3"/>
-      <c r="L39" s="3"/>
-      <c r="M39" s="3"/>
-      <c r="N39" s="3"/>
-      <c r="O39" s="3"/>
-      <c r="P39" s="3"/>
-      <c r="Q39" s="3"/>
-      <c r="R39" s="3"/>
-      <c r="S39" s="3"/>
-      <c r="T39" s="3"/>
-      <c r="U39" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
+      <c r="A39" s="2">
+        <v>46178</v>
+      </c>
+      <c r="B39" s="3">
+        <v>4.29</v>
+      </c>
+      <c r="C39" s="3">
+        <v>3.95</v>
+      </c>
+      <c r="D39" s="3">
+        <v>3.49</v>
+      </c>
+      <c r="E39" s="3">
+        <v>4.1900000000000004</v>
+      </c>
+      <c r="F39" s="3">
+        <v>4.3099999999999996</v>
+      </c>
+      <c r="G39" s="3">
+        <v>3.99</v>
+      </c>
+      <c r="H39" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="I39" s="3">
+        <v>3.39</v>
+      </c>
+      <c r="J39" s="3">
+        <v>3.09</v>
+      </c>
+      <c r="K39" s="3">
+        <v>4.1399999999999997</v>
+      </c>
+      <c r="L39" s="3">
+        <v>3.79</v>
+      </c>
+      <c r="M39" s="3">
+        <v>3.59</v>
+      </c>
+      <c r="N39" s="3">
+        <v>3.69</v>
+      </c>
+      <c r="O39" s="3">
+        <v>4.1900000000000004</v>
+      </c>
+      <c r="P39" s="3">
+        <v>3.89</v>
+      </c>
+      <c r="Q39" s="3">
+        <v>4.03</v>
+      </c>
+      <c r="R39" s="3">
+        <v>3.89</v>
+      </c>
+      <c r="S39" s="3">
+        <v>3.99</v>
+      </c>
+      <c r="T39" s="3">
+        <v>1.99</v>
+      </c>
+      <c r="U39" s="4">
+        <f t="shared" ref="U39" si="7">IF(COUNTA(B39:T39)=0,"",AVERAGE(B39:T39))</f>
+        <v>3.7305263157894726</v>
       </c>
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
@@ -23424,7 +23526,7 @@
       <c r="S69" s="3"/>
       <c r="T69" s="3"/>
       <c r="U69" s="4" t="str">
-        <f t="shared" ref="U69:U132" si="7">IF(COUNTA(B69:T69)=0,"",AVERAGE(B69:T69))</f>
+        <f t="shared" ref="U69:U132" si="8">IF(COUNTA(B69:T69)=0,"",AVERAGE(B69:T69))</f>
         <v/>
       </c>
     </row>
@@ -23450,7 +23552,7 @@
       <c r="S70" s="3"/>
       <c r="T70" s="3"/>
       <c r="U70" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -23476,7 +23578,7 @@
       <c r="S71" s="3"/>
       <c r="T71" s="3"/>
       <c r="U71" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -23502,7 +23604,7 @@
       <c r="S72" s="3"/>
       <c r="T72" s="3"/>
       <c r="U72" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -23528,7 +23630,7 @@
       <c r="S73" s="3"/>
       <c r="T73" s="3"/>
       <c r="U73" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -23554,7 +23656,7 @@
       <c r="S74" s="3"/>
       <c r="T74" s="3"/>
       <c r="U74" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -23580,7 +23682,7 @@
       <c r="S75" s="3"/>
       <c r="T75" s="3"/>
       <c r="U75" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -23606,7 +23708,7 @@
       <c r="S76" s="3"/>
       <c r="T76" s="3"/>
       <c r="U76" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -23632,7 +23734,7 @@
       <c r="S77" s="3"/>
       <c r="T77" s="3"/>
       <c r="U77" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -23658,7 +23760,7 @@
       <c r="S78" s="3"/>
       <c r="T78" s="3"/>
       <c r="U78" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -23684,7 +23786,7 @@
       <c r="S79" s="3"/>
       <c r="T79" s="3"/>
       <c r="U79" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -23710,7 +23812,7 @@
       <c r="S80" s="3"/>
       <c r="T80" s="3"/>
       <c r="U80" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -23736,7 +23838,7 @@
       <c r="S81" s="3"/>
       <c r="T81" s="3"/>
       <c r="U81" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -23762,7 +23864,7 @@
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
       <c r="U82" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -23788,7 +23890,7 @@
       <c r="S83" s="3"/>
       <c r="T83" s="3"/>
       <c r="U83" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -23814,7 +23916,7 @@
       <c r="S84" s="3"/>
       <c r="T84" s="3"/>
       <c r="U84" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -23840,7 +23942,7 @@
       <c r="S85" s="3"/>
       <c r="T85" s="3"/>
       <c r="U85" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -23866,7 +23968,7 @@
       <c r="S86" s="3"/>
       <c r="T86" s="3"/>
       <c r="U86" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -23892,7 +23994,7 @@
       <c r="S87" s="3"/>
       <c r="T87" s="3"/>
       <c r="U87" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -23918,7 +24020,7 @@
       <c r="S88" s="3"/>
       <c r="T88" s="3"/>
       <c r="U88" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -23944,7 +24046,7 @@
       <c r="S89" s="3"/>
       <c r="T89" s="3"/>
       <c r="U89" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -23970,7 +24072,7 @@
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
       <c r="U90" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -23996,7 +24098,7 @@
       <c r="S91" s="3"/>
       <c r="T91" s="3"/>
       <c r="U91" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -24022,7 +24124,7 @@
       <c r="S92" s="3"/>
       <c r="T92" s="3"/>
       <c r="U92" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -24048,7 +24150,7 @@
       <c r="S93" s="3"/>
       <c r="T93" s="3"/>
       <c r="U93" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -24074,7 +24176,7 @@
       <c r="S94" s="3"/>
       <c r="T94" s="3"/>
       <c r="U94" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -24100,7 +24202,7 @@
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
       <c r="U95" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -24126,7 +24228,7 @@
       <c r="S96" s="3"/>
       <c r="T96" s="3"/>
       <c r="U96" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -24152,7 +24254,7 @@
       <c r="S97" s="3"/>
       <c r="T97" s="3"/>
       <c r="U97" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -24178,7 +24280,7 @@
       <c r="S98" s="3"/>
       <c r="T98" s="3"/>
       <c r="U98" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -24204,7 +24306,7 @@
       <c r="S99" s="3"/>
       <c r="T99" s="3"/>
       <c r="U99" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -24230,7 +24332,7 @@
       <c r="S100" s="3"/>
       <c r="T100" s="3"/>
       <c r="U100" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -24256,7 +24358,7 @@
       <c r="S101" s="3"/>
       <c r="T101" s="3"/>
       <c r="U101" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -24282,7 +24384,7 @@
       <c r="S102" s="3"/>
       <c r="T102" s="3"/>
       <c r="U102" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -24308,7 +24410,7 @@
       <c r="S103" s="3"/>
       <c r="T103" s="3"/>
       <c r="U103" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -24334,7 +24436,7 @@
       <c r="S104" s="3"/>
       <c r="T104" s="3"/>
       <c r="U104" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -24360,7 +24462,7 @@
       <c r="S105" s="3"/>
       <c r="T105" s="3"/>
       <c r="U105" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -24386,7 +24488,7 @@
       <c r="S106" s="3"/>
       <c r="T106" s="3"/>
       <c r="U106" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -24412,7 +24514,7 @@
       <c r="S107" s="3"/>
       <c r="T107" s="3"/>
       <c r="U107" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -24438,7 +24540,7 @@
       <c r="S108" s="3"/>
       <c r="T108" s="3"/>
       <c r="U108" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -24464,7 +24566,7 @@
       <c r="S109" s="3"/>
       <c r="T109" s="3"/>
       <c r="U109" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -24490,7 +24592,7 @@
       <c r="S110" s="3"/>
       <c r="T110" s="3"/>
       <c r="U110" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -24516,7 +24618,7 @@
       <c r="S111" s="3"/>
       <c r="T111" s="3"/>
       <c r="U111" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -24542,7 +24644,7 @@
       <c r="S112" s="3"/>
       <c r="T112" s="3"/>
       <c r="U112" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -24568,7 +24670,7 @@
       <c r="S113" s="3"/>
       <c r="T113" s="3"/>
       <c r="U113" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -24594,7 +24696,7 @@
       <c r="S114" s="3"/>
       <c r="T114" s="3"/>
       <c r="U114" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -24620,7 +24722,7 @@
       <c r="S115" s="3"/>
       <c r="T115" s="3"/>
       <c r="U115" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -24646,7 +24748,7 @@
       <c r="S116" s="3"/>
       <c r="T116" s="3"/>
       <c r="U116" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -24672,7 +24774,7 @@
       <c r="S117" s="3"/>
       <c r="T117" s="3"/>
       <c r="U117" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -24698,7 +24800,7 @@
       <c r="S118" s="3"/>
       <c r="T118" s="3"/>
       <c r="U118" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -24724,7 +24826,7 @@
       <c r="S119" s="3"/>
       <c r="T119" s="3"/>
       <c r="U119" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -24750,7 +24852,7 @@
       <c r="S120" s="3"/>
       <c r="T120" s="3"/>
       <c r="U120" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -24776,7 +24878,7 @@
       <c r="S121" s="3"/>
       <c r="T121" s="3"/>
       <c r="U121" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -24802,7 +24904,7 @@
       <c r="S122" s="3"/>
       <c r="T122" s="3"/>
       <c r="U122" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -24828,7 +24930,7 @@
       <c r="S123" s="3"/>
       <c r="T123" s="3"/>
       <c r="U123" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -24854,7 +24956,7 @@
       <c r="S124" s="3"/>
       <c r="T124" s="3"/>
       <c r="U124" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -24880,7 +24982,7 @@
       <c r="S125" s="3"/>
       <c r="T125" s="3"/>
       <c r="U125" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -24906,7 +25008,7 @@
       <c r="S126" s="3"/>
       <c r="T126" s="3"/>
       <c r="U126" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -24932,7 +25034,7 @@
       <c r="S127" s="3"/>
       <c r="T127" s="3"/>
       <c r="U127" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -24958,7 +25060,7 @@
       <c r="S128" s="3"/>
       <c r="T128" s="3"/>
       <c r="U128" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -24984,7 +25086,7 @@
       <c r="S129" s="3"/>
       <c r="T129" s="3"/>
       <c r="U129" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -25010,7 +25112,7 @@
       <c r="S130" s="3"/>
       <c r="T130" s="3"/>
       <c r="U130" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -25036,7 +25138,7 @@
       <c r="S131" s="3"/>
       <c r="T131" s="3"/>
       <c r="U131" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -25062,7 +25164,7 @@
       <c r="S132" s="3"/>
       <c r="T132" s="3"/>
       <c r="U132" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -25088,7 +25190,7 @@
       <c r="S133" s="3"/>
       <c r="T133" s="3"/>
       <c r="U133" s="4" t="str">
-        <f t="shared" ref="U133:U196" si="8">IF(COUNTA(B133:T133)=0,"",AVERAGE(B133:T133))</f>
+        <f t="shared" ref="U133:U196" si="9">IF(COUNTA(B133:T133)=0,"",AVERAGE(B133:T133))</f>
         <v/>
       </c>
     </row>
@@ -25114,7 +25216,7 @@
       <c r="S134" s="3"/>
       <c r="T134" s="3"/>
       <c r="U134" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -25140,7 +25242,7 @@
       <c r="S135" s="3"/>
       <c r="T135" s="3"/>
       <c r="U135" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -25166,7 +25268,7 @@
       <c r="S136" s="3"/>
       <c r="T136" s="3"/>
       <c r="U136" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -25192,7 +25294,7 @@
       <c r="S137" s="3"/>
       <c r="T137" s="3"/>
       <c r="U137" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -25218,7 +25320,7 @@
       <c r="S138" s="3"/>
       <c r="T138" s="3"/>
       <c r="U138" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -25244,7 +25346,7 @@
       <c r="S139" s="3"/>
       <c r="T139" s="3"/>
       <c r="U139" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -25270,7 +25372,7 @@
       <c r="S140" s="3"/>
       <c r="T140" s="3"/>
       <c r="U140" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -25296,7 +25398,7 @@
       <c r="S141" s="3"/>
       <c r="T141" s="3"/>
       <c r="U141" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -25322,7 +25424,7 @@
       <c r="S142" s="3"/>
       <c r="T142" s="3"/>
       <c r="U142" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -25348,7 +25450,7 @@
       <c r="S143" s="3"/>
       <c r="T143" s="3"/>
       <c r="U143" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -25374,7 +25476,7 @@
       <c r="S144" s="3"/>
       <c r="T144" s="3"/>
       <c r="U144" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -25400,7 +25502,7 @@
       <c r="S145" s="3"/>
       <c r="T145" s="3"/>
       <c r="U145" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -25426,7 +25528,7 @@
       <c r="S146" s="3"/>
       <c r="T146" s="3"/>
       <c r="U146" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -25452,7 +25554,7 @@
       <c r="S147" s="3"/>
       <c r="T147" s="3"/>
       <c r="U147" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -25478,7 +25580,7 @@
       <c r="S148" s="3"/>
       <c r="T148" s="3"/>
       <c r="U148" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -25504,7 +25606,7 @@
       <c r="S149" s="3"/>
       <c r="T149" s="3"/>
       <c r="U149" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -25530,7 +25632,7 @@
       <c r="S150" s="3"/>
       <c r="T150" s="3"/>
       <c r="U150" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -25556,7 +25658,7 @@
       <c r="S151" s="3"/>
       <c r="T151" s="3"/>
       <c r="U151" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -25582,7 +25684,7 @@
       <c r="S152" s="3"/>
       <c r="T152" s="3"/>
       <c r="U152" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -25608,7 +25710,7 @@
       <c r="S153" s="3"/>
       <c r="T153" s="3"/>
       <c r="U153" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -25634,7 +25736,7 @@
       <c r="S154" s="3"/>
       <c r="T154" s="3"/>
       <c r="U154" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -25660,7 +25762,7 @@
       <c r="S155" s="3"/>
       <c r="T155" s="3"/>
       <c r="U155" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -25686,7 +25788,7 @@
       <c r="S156" s="3"/>
       <c r="T156" s="3"/>
       <c r="U156" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -25712,7 +25814,7 @@
       <c r="S157" s="3"/>
       <c r="T157" s="3"/>
       <c r="U157" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -25738,7 +25840,7 @@
       <c r="S158" s="3"/>
       <c r="T158" s="3"/>
       <c r="U158" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -25764,7 +25866,7 @@
       <c r="S159" s="3"/>
       <c r="T159" s="3"/>
       <c r="U159" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -25790,7 +25892,7 @@
       <c r="S160" s="3"/>
       <c r="T160" s="3"/>
       <c r="U160" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -25816,7 +25918,7 @@
       <c r="S161" s="3"/>
       <c r="T161" s="3"/>
       <c r="U161" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -25842,7 +25944,7 @@
       <c r="S162" s="3"/>
       <c r="T162" s="3"/>
       <c r="U162" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -25868,7 +25970,7 @@
       <c r="S163" s="3"/>
       <c r="T163" s="3"/>
       <c r="U163" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -25894,7 +25996,7 @@
       <c r="S164" s="3"/>
       <c r="T164" s="3"/>
       <c r="U164" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -25920,7 +26022,7 @@
       <c r="S165" s="3"/>
       <c r="T165" s="3"/>
       <c r="U165" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -25946,7 +26048,7 @@
       <c r="S166" s="3"/>
       <c r="T166" s="3"/>
       <c r="U166" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -25972,7 +26074,7 @@
       <c r="S167" s="3"/>
       <c r="T167" s="3"/>
       <c r="U167" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -25998,7 +26100,7 @@
       <c r="S168" s="3"/>
       <c r="T168" s="3"/>
       <c r="U168" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -26024,7 +26126,7 @@
       <c r="S169" s="3"/>
       <c r="T169" s="3"/>
       <c r="U169" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -26050,7 +26152,7 @@
       <c r="S170" s="3"/>
       <c r="T170" s="3"/>
       <c r="U170" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -26076,7 +26178,7 @@
       <c r="S171" s="3"/>
       <c r="T171" s="3"/>
       <c r="U171" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -26102,7 +26204,7 @@
       <c r="S172" s="3"/>
       <c r="T172" s="3"/>
       <c r="U172" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -26128,7 +26230,7 @@
       <c r="S173" s="3"/>
       <c r="T173" s="3"/>
       <c r="U173" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -26154,7 +26256,7 @@
       <c r="S174" s="3"/>
       <c r="T174" s="3"/>
       <c r="U174" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -26180,7 +26282,7 @@
       <c r="S175" s="3"/>
       <c r="T175" s="3"/>
       <c r="U175" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -26206,7 +26308,7 @@
       <c r="S176" s="3"/>
       <c r="T176" s="3"/>
       <c r="U176" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -26232,7 +26334,7 @@
       <c r="S177" s="3"/>
       <c r="T177" s="3"/>
       <c r="U177" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -26258,7 +26360,7 @@
       <c r="S178" s="3"/>
       <c r="T178" s="3"/>
       <c r="U178" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -26284,7 +26386,7 @@
       <c r="S179" s="3"/>
       <c r="T179" s="3"/>
       <c r="U179" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -26310,7 +26412,7 @@
       <c r="S180" s="3"/>
       <c r="T180" s="3"/>
       <c r="U180" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -26336,7 +26438,7 @@
       <c r="S181" s="3"/>
       <c r="T181" s="3"/>
       <c r="U181" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -26362,7 +26464,7 @@
       <c r="S182" s="3"/>
       <c r="T182" s="3"/>
       <c r="U182" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -26388,7 +26490,7 @@
       <c r="S183" s="3"/>
       <c r="T183" s="3"/>
       <c r="U183" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -26414,7 +26516,7 @@
       <c r="S184" s="3"/>
       <c r="T184" s="3"/>
       <c r="U184" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -26440,7 +26542,7 @@
       <c r="S185" s="3"/>
       <c r="T185" s="3"/>
       <c r="U185" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -26466,7 +26568,7 @@
       <c r="S186" s="3"/>
       <c r="T186" s="3"/>
       <c r="U186" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -26492,7 +26594,7 @@
       <c r="S187" s="3"/>
       <c r="T187" s="3"/>
       <c r="U187" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -26518,7 +26620,7 @@
       <c r="S188" s="3"/>
       <c r="T188" s="3"/>
       <c r="U188" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -26544,7 +26646,7 @@
       <c r="S189" s="3"/>
       <c r="T189" s="3"/>
       <c r="U189" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -26570,7 +26672,7 @@
       <c r="S190" s="3"/>
       <c r="T190" s="3"/>
       <c r="U190" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -26596,7 +26698,7 @@
       <c r="S191" s="3"/>
       <c r="T191" s="3"/>
       <c r="U191" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -26622,7 +26724,7 @@
       <c r="S192" s="3"/>
       <c r="T192" s="3"/>
       <c r="U192" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -26648,7 +26750,7 @@
       <c r="S193" s="3"/>
       <c r="T193" s="3"/>
       <c r="U193" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -26674,7 +26776,7 @@
       <c r="S194" s="3"/>
       <c r="T194" s="3"/>
       <c r="U194" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -26700,7 +26802,7 @@
       <c r="S195" s="3"/>
       <c r="T195" s="3"/>
       <c r="U195" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -26726,7 +26828,7 @@
       <c r="S196" s="3"/>
       <c r="T196" s="3"/>
       <c r="U196" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -26752,7 +26854,7 @@
       <c r="S197" s="3"/>
       <c r="T197" s="3"/>
       <c r="U197" s="4" t="str">
-        <f t="shared" ref="U197:U260" si="9">IF(COUNTA(B197:T197)=0,"",AVERAGE(B197:T197))</f>
+        <f t="shared" ref="U197:U260" si="10">IF(COUNTA(B197:T197)=0,"",AVERAGE(B197:T197))</f>
         <v/>
       </c>
     </row>
@@ -26778,7 +26880,7 @@
       <c r="S198" s="3"/>
       <c r="T198" s="3"/>
       <c r="U198" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -26804,7 +26906,7 @@
       <c r="S199" s="3"/>
       <c r="T199" s="3"/>
       <c r="U199" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -26830,7 +26932,7 @@
       <c r="S200" s="3"/>
       <c r="T200" s="3"/>
       <c r="U200" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -26856,7 +26958,7 @@
       <c r="S201" s="3"/>
       <c r="T201" s="3"/>
       <c r="U201" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -26882,7 +26984,7 @@
       <c r="S202" s="3"/>
       <c r="T202" s="3"/>
       <c r="U202" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -26908,7 +27010,7 @@
       <c r="S203" s="3"/>
       <c r="T203" s="3"/>
       <c r="U203" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -26934,7 +27036,7 @@
       <c r="S204" s="3"/>
       <c r="T204" s="3"/>
       <c r="U204" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -26960,7 +27062,7 @@
       <c r="S205" s="3"/>
       <c r="T205" s="3"/>
       <c r="U205" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -26986,7 +27088,7 @@
       <c r="S206" s="3"/>
       <c r="T206" s="3"/>
       <c r="U206" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -27012,7 +27114,7 @@
       <c r="S207" s="3"/>
       <c r="T207" s="3"/>
       <c r="U207" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -27038,7 +27140,7 @@
       <c r="S208" s="3"/>
       <c r="T208" s="3"/>
       <c r="U208" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -27064,7 +27166,7 @@
       <c r="S209" s="3"/>
       <c r="T209" s="3"/>
       <c r="U209" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -27090,7 +27192,7 @@
       <c r="S210" s="3"/>
       <c r="T210" s="3"/>
       <c r="U210" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -27116,7 +27218,7 @@
       <c r="S211" s="3"/>
       <c r="T211" s="3"/>
       <c r="U211" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -27142,7 +27244,7 @@
       <c r="S212" s="3"/>
       <c r="T212" s="3"/>
       <c r="U212" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -27168,7 +27270,7 @@
       <c r="S213" s="3"/>
       <c r="T213" s="3"/>
       <c r="U213" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -27194,7 +27296,7 @@
       <c r="S214" s="3"/>
       <c r="T214" s="3"/>
       <c r="U214" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -27220,7 +27322,7 @@
       <c r="S215" s="3"/>
       <c r="T215" s="3"/>
       <c r="U215" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -27246,7 +27348,7 @@
       <c r="S216" s="3"/>
       <c r="T216" s="3"/>
       <c r="U216" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -27272,7 +27374,7 @@
       <c r="S217" s="3"/>
       <c r="T217" s="3"/>
       <c r="U217" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -27298,7 +27400,7 @@
       <c r="S218" s="3"/>
       <c r="T218" s="3"/>
       <c r="U218" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -27324,7 +27426,7 @@
       <c r="S219" s="3"/>
       <c r="T219" s="3"/>
       <c r="U219" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -27350,7 +27452,7 @@
       <c r="S220" s="3"/>
       <c r="T220" s="3"/>
       <c r="U220" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -27376,7 +27478,7 @@
       <c r="S221" s="3"/>
       <c r="T221" s="3"/>
       <c r="U221" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -27402,7 +27504,7 @@
       <c r="S222" s="3"/>
       <c r="T222" s="3"/>
       <c r="U222" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -27428,7 +27530,7 @@
       <c r="S223" s="3"/>
       <c r="T223" s="3"/>
       <c r="U223" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -27454,7 +27556,7 @@
       <c r="S224" s="3"/>
       <c r="T224" s="3"/>
       <c r="U224" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -27480,7 +27582,7 @@
       <c r="S225" s="3"/>
       <c r="T225" s="3"/>
       <c r="U225" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -27506,7 +27608,7 @@
       <c r="S226" s="3"/>
       <c r="T226" s="3"/>
       <c r="U226" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -27532,7 +27634,7 @@
       <c r="S227" s="3"/>
       <c r="T227" s="3"/>
       <c r="U227" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -27558,7 +27660,7 @@
       <c r="S228" s="3"/>
       <c r="T228" s="3"/>
       <c r="U228" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -27584,7 +27686,7 @@
       <c r="S229" s="3"/>
       <c r="T229" s="3"/>
       <c r="U229" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -27610,7 +27712,7 @@
       <c r="S230" s="3"/>
       <c r="T230" s="3"/>
       <c r="U230" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -27636,7 +27738,7 @@
       <c r="S231" s="3"/>
       <c r="T231" s="3"/>
       <c r="U231" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -27662,7 +27764,7 @@
       <c r="S232" s="3"/>
       <c r="T232" s="3"/>
       <c r="U232" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -27688,7 +27790,7 @@
       <c r="S233" s="3"/>
       <c r="T233" s="3"/>
       <c r="U233" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -27714,7 +27816,7 @@
       <c r="S234" s="3"/>
       <c r="T234" s="3"/>
       <c r="U234" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -27740,7 +27842,7 @@
       <c r="S235" s="3"/>
       <c r="T235" s="3"/>
       <c r="U235" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -27766,7 +27868,7 @@
       <c r="S236" s="3"/>
       <c r="T236" s="3"/>
       <c r="U236" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -27792,7 +27894,7 @@
       <c r="S237" s="3"/>
       <c r="T237" s="3"/>
       <c r="U237" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -27818,7 +27920,7 @@
       <c r="S238" s="3"/>
       <c r="T238" s="3"/>
       <c r="U238" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -27844,7 +27946,7 @@
       <c r="S239" s="3"/>
       <c r="T239" s="3"/>
       <c r="U239" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -27870,7 +27972,7 @@
       <c r="S240" s="3"/>
       <c r="T240" s="3"/>
       <c r="U240" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -27896,7 +27998,7 @@
       <c r="S241" s="3"/>
       <c r="T241" s="3"/>
       <c r="U241" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -27922,7 +28024,7 @@
       <c r="S242" s="3"/>
       <c r="T242" s="3"/>
       <c r="U242" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -27948,7 +28050,7 @@
       <c r="S243" s="3"/>
       <c r="T243" s="3"/>
       <c r="U243" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -27974,7 +28076,7 @@
       <c r="S244" s="3"/>
       <c r="T244" s="3"/>
       <c r="U244" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -28000,7 +28102,7 @@
       <c r="S245" s="3"/>
       <c r="T245" s="3"/>
       <c r="U245" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -28026,7 +28128,7 @@
       <c r="S246" s="3"/>
       <c r="T246" s="3"/>
       <c r="U246" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -28052,7 +28154,7 @@
       <c r="S247" s="3"/>
       <c r="T247" s="3"/>
       <c r="U247" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -28078,7 +28180,7 @@
       <c r="S248" s="3"/>
       <c r="T248" s="3"/>
       <c r="U248" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -28104,7 +28206,7 @@
       <c r="S249" s="3"/>
       <c r="T249" s="3"/>
       <c r="U249" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -28130,7 +28232,7 @@
       <c r="S250" s="3"/>
       <c r="T250" s="3"/>
       <c r="U250" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -28156,7 +28258,7 @@
       <c r="S251" s="3"/>
       <c r="T251" s="3"/>
       <c r="U251" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -28182,7 +28284,7 @@
       <c r="S252" s="3"/>
       <c r="T252" s="3"/>
       <c r="U252" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -28208,7 +28310,7 @@
       <c r="S253" s="3"/>
       <c r="T253" s="3"/>
       <c r="U253" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -28234,7 +28336,7 @@
       <c r="S254" s="3"/>
       <c r="T254" s="3"/>
       <c r="U254" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -28260,7 +28362,7 @@
       <c r="S255" s="3"/>
       <c r="T255" s="3"/>
       <c r="U255" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -28286,7 +28388,7 @@
       <c r="S256" s="3"/>
       <c r="T256" s="3"/>
       <c r="U256" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -28312,7 +28414,7 @@
       <c r="S257" s="3"/>
       <c r="T257" s="3"/>
       <c r="U257" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -28338,7 +28440,7 @@
       <c r="S258" s="3"/>
       <c r="T258" s="3"/>
       <c r="U258" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -28364,7 +28466,7 @@
       <c r="S259" s="3"/>
       <c r="T259" s="3"/>
       <c r="U259" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -28390,7 +28492,7 @@
       <c r="S260" s="3"/>
       <c r="T260" s="3"/>
       <c r="U260" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -28416,7 +28518,7 @@
       <c r="S261" s="3"/>
       <c r="T261" s="3"/>
       <c r="U261" s="4" t="str">
-        <f t="shared" ref="U261:U324" si="10">IF(COUNTA(B261:T261)=0,"",AVERAGE(B261:T261))</f>
+        <f t="shared" ref="U261:U324" si="11">IF(COUNTA(B261:T261)=0,"",AVERAGE(B261:T261))</f>
         <v/>
       </c>
     </row>
@@ -28442,7 +28544,7 @@
       <c r="S262" s="3"/>
       <c r="T262" s="3"/>
       <c r="U262" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -28468,7 +28570,7 @@
       <c r="S263" s="3"/>
       <c r="T263" s="3"/>
       <c r="U263" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -28494,7 +28596,7 @@
       <c r="S264" s="3"/>
       <c r="T264" s="3"/>
       <c r="U264" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -28520,7 +28622,7 @@
       <c r="S265" s="3"/>
       <c r="T265" s="3"/>
       <c r="U265" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -28546,7 +28648,7 @@
       <c r="S266" s="3"/>
       <c r="T266" s="3"/>
       <c r="U266" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -28572,7 +28674,7 @@
       <c r="S267" s="3"/>
       <c r="T267" s="3"/>
       <c r="U267" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -28598,7 +28700,7 @@
       <c r="S268" s="3"/>
       <c r="T268" s="3"/>
       <c r="U268" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -28624,7 +28726,7 @@
       <c r="S269" s="3"/>
       <c r="T269" s="3"/>
       <c r="U269" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -28650,7 +28752,7 @@
       <c r="S270" s="3"/>
       <c r="T270" s="3"/>
       <c r="U270" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -28676,7 +28778,7 @@
       <c r="S271" s="3"/>
       <c r="T271" s="3"/>
       <c r="U271" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -28702,7 +28804,7 @@
       <c r="S272" s="3"/>
       <c r="T272" s="3"/>
       <c r="U272" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -28728,7 +28830,7 @@
       <c r="S273" s="3"/>
       <c r="T273" s="3"/>
       <c r="U273" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -28754,7 +28856,7 @@
       <c r="S274" s="3"/>
       <c r="T274" s="3"/>
       <c r="U274" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -28780,7 +28882,7 @@
       <c r="S275" s="3"/>
       <c r="T275" s="3"/>
       <c r="U275" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -28806,7 +28908,7 @@
       <c r="S276" s="3"/>
       <c r="T276" s="3"/>
       <c r="U276" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -28832,7 +28934,7 @@
       <c r="S277" s="3"/>
       <c r="T277" s="3"/>
       <c r="U277" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -28858,7 +28960,7 @@
       <c r="S278" s="3"/>
       <c r="T278" s="3"/>
       <c r="U278" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -28884,7 +28986,7 @@
       <c r="S279" s="3"/>
       <c r="T279" s="3"/>
       <c r="U279" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -28910,7 +29012,7 @@
       <c r="S280" s="3"/>
       <c r="T280" s="3"/>
       <c r="U280" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -28936,7 +29038,7 @@
       <c r="S281" s="3"/>
       <c r="T281" s="3"/>
       <c r="U281" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -28962,7 +29064,7 @@
       <c r="S282" s="3"/>
       <c r="T282" s="3"/>
       <c r="U282" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -28988,7 +29090,7 @@
       <c r="S283" s="3"/>
       <c r="T283" s="3"/>
       <c r="U283" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -29014,7 +29116,7 @@
       <c r="S284" s="3"/>
       <c r="T284" s="3"/>
       <c r="U284" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -29040,7 +29142,7 @@
       <c r="S285" s="3"/>
       <c r="T285" s="3"/>
       <c r="U285" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -29066,7 +29168,7 @@
       <c r="S286" s="3"/>
       <c r="T286" s="3"/>
       <c r="U286" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -29092,7 +29194,7 @@
       <c r="S287" s="3"/>
       <c r="T287" s="3"/>
       <c r="U287" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -29118,7 +29220,7 @@
       <c r="S288" s="3"/>
       <c r="T288" s="3"/>
       <c r="U288" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -29144,7 +29246,7 @@
       <c r="S289" s="3"/>
       <c r="T289" s="3"/>
       <c r="U289" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -29170,7 +29272,7 @@
       <c r="S290" s="3"/>
       <c r="T290" s="3"/>
       <c r="U290" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -29196,7 +29298,7 @@
       <c r="S291" s="3"/>
       <c r="T291" s="3"/>
       <c r="U291" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -29222,7 +29324,7 @@
       <c r="S292" s="3"/>
       <c r="T292" s="3"/>
       <c r="U292" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -29248,7 +29350,7 @@
       <c r="S293" s="3"/>
       <c r="T293" s="3"/>
       <c r="U293" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -29274,7 +29376,7 @@
       <c r="S294" s="3"/>
       <c r="T294" s="3"/>
       <c r="U294" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -29300,7 +29402,7 @@
       <c r="S295" s="3"/>
       <c r="T295" s="3"/>
       <c r="U295" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -29326,7 +29428,7 @@
       <c r="S296" s="3"/>
       <c r="T296" s="3"/>
       <c r="U296" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -29352,7 +29454,7 @@
       <c r="S297" s="3"/>
       <c r="T297" s="3"/>
       <c r="U297" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -29378,7 +29480,7 @@
       <c r="S298" s="3"/>
       <c r="T298" s="3"/>
       <c r="U298" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -29404,7 +29506,7 @@
       <c r="S299" s="3"/>
       <c r="T299" s="3"/>
       <c r="U299" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -29430,7 +29532,7 @@
       <c r="S300" s="3"/>
       <c r="T300" s="3"/>
       <c r="U300" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -29456,7 +29558,7 @@
       <c r="S301" s="3"/>
       <c r="T301" s="3"/>
       <c r="U301" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -29482,7 +29584,7 @@
       <c r="S302" s="3"/>
       <c r="T302" s="3"/>
       <c r="U302" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -29508,7 +29610,7 @@
       <c r="S303" s="3"/>
       <c r="T303" s="3"/>
       <c r="U303" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -29534,7 +29636,7 @@
       <c r="S304" s="3"/>
       <c r="T304" s="3"/>
       <c r="U304" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -29560,7 +29662,7 @@
       <c r="S305" s="3"/>
       <c r="T305" s="3"/>
       <c r="U305" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -29586,7 +29688,7 @@
       <c r="S306" s="3"/>
       <c r="T306" s="3"/>
       <c r="U306" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -29612,7 +29714,7 @@
       <c r="S307" s="3"/>
       <c r="T307" s="3"/>
       <c r="U307" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -29638,7 +29740,7 @@
       <c r="S308" s="3"/>
       <c r="T308" s="3"/>
       <c r="U308" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -29664,7 +29766,7 @@
       <c r="S309" s="3"/>
       <c r="T309" s="3"/>
       <c r="U309" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -29690,7 +29792,7 @@
       <c r="S310" s="3"/>
       <c r="T310" s="3"/>
       <c r="U310" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -29716,7 +29818,7 @@
       <c r="S311" s="3"/>
       <c r="T311" s="3"/>
       <c r="U311" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -29742,7 +29844,7 @@
       <c r="S312" s="3"/>
       <c r="T312" s="3"/>
       <c r="U312" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -29768,7 +29870,7 @@
       <c r="S313" s="3"/>
       <c r="T313" s="3"/>
       <c r="U313" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -29794,7 +29896,7 @@
       <c r="S314" s="3"/>
       <c r="T314" s="3"/>
       <c r="U314" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -29820,7 +29922,7 @@
       <c r="S315" s="3"/>
       <c r="T315" s="3"/>
       <c r="U315" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -29846,7 +29948,7 @@
       <c r="S316" s="3"/>
       <c r="T316" s="3"/>
       <c r="U316" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -29872,7 +29974,7 @@
       <c r="S317" s="3"/>
       <c r="T317" s="3"/>
       <c r="U317" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -29898,7 +30000,7 @@
       <c r="S318" s="3"/>
       <c r="T318" s="3"/>
       <c r="U318" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -29924,7 +30026,7 @@
       <c r="S319" s="3"/>
       <c r="T319" s="3"/>
       <c r="U319" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -29950,7 +30052,7 @@
       <c r="S320" s="3"/>
       <c r="T320" s="3"/>
       <c r="U320" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -29976,7 +30078,7 @@
       <c r="S321" s="3"/>
       <c r="T321" s="3"/>
       <c r="U321" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -30002,7 +30104,7 @@
       <c r="S322" s="3"/>
       <c r="T322" s="3"/>
       <c r="U322" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -30028,7 +30130,7 @@
       <c r="S323" s="3"/>
       <c r="T323" s="3"/>
       <c r="U323" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -30054,7 +30156,7 @@
       <c r="S324" s="3"/>
       <c r="T324" s="3"/>
       <c r="U324" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -30080,7 +30182,7 @@
       <c r="S325" s="3"/>
       <c r="T325" s="3"/>
       <c r="U325" s="4" t="str">
-        <f t="shared" ref="U325:U388" si="11">IF(COUNTA(B325:T325)=0,"",AVERAGE(B325:T325))</f>
+        <f t="shared" ref="U325:U388" si="12">IF(COUNTA(B325:T325)=0,"",AVERAGE(B325:T325))</f>
         <v/>
       </c>
     </row>
@@ -30106,7 +30208,7 @@
       <c r="S326" s="3"/>
       <c r="T326" s="3"/>
       <c r="U326" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -30132,7 +30234,7 @@
       <c r="S327" s="3"/>
       <c r="T327" s="3"/>
       <c r="U327" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -30158,7 +30260,7 @@
       <c r="S328" s="3"/>
       <c r="T328" s="3"/>
       <c r="U328" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -30184,7 +30286,7 @@
       <c r="S329" s="3"/>
       <c r="T329" s="3"/>
       <c r="U329" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -30210,7 +30312,7 @@
       <c r="S330" s="3"/>
       <c r="T330" s="3"/>
       <c r="U330" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -30236,7 +30338,7 @@
       <c r="S331" s="3"/>
       <c r="T331" s="3"/>
       <c r="U331" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -30262,7 +30364,7 @@
       <c r="S332" s="3"/>
       <c r="T332" s="3"/>
       <c r="U332" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -30288,7 +30390,7 @@
       <c r="S333" s="3"/>
       <c r="T333" s="3"/>
       <c r="U333" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -30314,7 +30416,7 @@
       <c r="S334" s="3"/>
       <c r="T334" s="3"/>
       <c r="U334" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -30340,7 +30442,7 @@
       <c r="S335" s="3"/>
       <c r="T335" s="3"/>
       <c r="U335" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -30366,7 +30468,7 @@
       <c r="S336" s="3"/>
       <c r="T336" s="3"/>
       <c r="U336" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -30392,7 +30494,7 @@
       <c r="S337" s="3"/>
       <c r="T337" s="3"/>
       <c r="U337" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -30418,7 +30520,7 @@
       <c r="S338" s="3"/>
       <c r="T338" s="3"/>
       <c r="U338" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -30444,7 +30546,7 @@
       <c r="S339" s="3"/>
       <c r="T339" s="3"/>
       <c r="U339" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -30470,7 +30572,7 @@
       <c r="S340" s="3"/>
       <c r="T340" s="3"/>
       <c r="U340" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -30496,7 +30598,7 @@
       <c r="S341" s="3"/>
       <c r="T341" s="3"/>
       <c r="U341" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -30522,7 +30624,7 @@
       <c r="S342" s="3"/>
       <c r="T342" s="3"/>
       <c r="U342" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -30548,7 +30650,7 @@
       <c r="S343" s="3"/>
       <c r="T343" s="3"/>
       <c r="U343" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -30574,7 +30676,7 @@
       <c r="S344" s="3"/>
       <c r="T344" s="3"/>
       <c r="U344" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -30600,7 +30702,7 @@
       <c r="S345" s="3"/>
       <c r="T345" s="3"/>
       <c r="U345" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -30626,7 +30728,7 @@
       <c r="S346" s="3"/>
       <c r="T346" s="3"/>
       <c r="U346" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -30652,7 +30754,7 @@
       <c r="S347" s="3"/>
       <c r="T347" s="3"/>
       <c r="U347" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -30678,7 +30780,7 @@
       <c r="S348" s="3"/>
       <c r="T348" s="3"/>
       <c r="U348" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -30704,7 +30806,7 @@
       <c r="S349" s="3"/>
       <c r="T349" s="3"/>
       <c r="U349" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -30730,7 +30832,7 @@
       <c r="S350" s="3"/>
       <c r="T350" s="3"/>
       <c r="U350" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -30756,7 +30858,7 @@
       <c r="S351" s="3"/>
       <c r="T351" s="3"/>
       <c r="U351" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -30782,7 +30884,7 @@
       <c r="S352" s="3"/>
       <c r="T352" s="3"/>
       <c r="U352" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -30808,7 +30910,7 @@
       <c r="S353" s="3"/>
       <c r="T353" s="3"/>
       <c r="U353" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -30834,7 +30936,7 @@
       <c r="S354" s="3"/>
       <c r="T354" s="3"/>
       <c r="U354" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -30860,7 +30962,7 @@
       <c r="S355" s="3"/>
       <c r="T355" s="3"/>
       <c r="U355" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -30886,7 +30988,7 @@
       <c r="S356" s="3"/>
       <c r="T356" s="3"/>
       <c r="U356" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -30912,7 +31014,7 @@
       <c r="S357" s="3"/>
       <c r="T357" s="3"/>
       <c r="U357" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -30938,7 +31040,7 @@
       <c r="S358" s="3"/>
       <c r="T358" s="3"/>
       <c r="U358" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -30964,7 +31066,7 @@
       <c r="S359" s="3"/>
       <c r="T359" s="3"/>
       <c r="U359" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -30990,7 +31092,7 @@
       <c r="S360" s="3"/>
       <c r="T360" s="3"/>
       <c r="U360" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -31016,7 +31118,7 @@
       <c r="S361" s="3"/>
       <c r="T361" s="3"/>
       <c r="U361" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -31042,7 +31144,7 @@
       <c r="S362" s="3"/>
       <c r="T362" s="3"/>
       <c r="U362" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -31068,7 +31170,7 @@
       <c r="S363" s="3"/>
       <c r="T363" s="3"/>
       <c r="U363" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -31094,7 +31196,7 @@
       <c r="S364" s="3"/>
       <c r="T364" s="3"/>
       <c r="U364" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -31120,7 +31222,7 @@
       <c r="S365" s="3"/>
       <c r="T365" s="3"/>
       <c r="U365" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -31146,7 +31248,7 @@
       <c r="S366" s="3"/>
       <c r="T366" s="3"/>
       <c r="U366" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -31172,7 +31274,7 @@
       <c r="S367" s="3"/>
       <c r="T367" s="3"/>
       <c r="U367" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -31198,7 +31300,7 @@
       <c r="S368" s="3"/>
       <c r="T368" s="3"/>
       <c r="U368" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -31224,7 +31326,7 @@
       <c r="S369" s="3"/>
       <c r="T369" s="3"/>
       <c r="U369" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -31250,7 +31352,7 @@
       <c r="S370" s="3"/>
       <c r="T370" s="3"/>
       <c r="U370" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -31276,7 +31378,7 @@
       <c r="S371" s="3"/>
       <c r="T371" s="3"/>
       <c r="U371" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -31302,7 +31404,7 @@
       <c r="S372" s="3"/>
       <c r="T372" s="3"/>
       <c r="U372" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -31328,7 +31430,7 @@
       <c r="S373" s="3"/>
       <c r="T373" s="3"/>
       <c r="U373" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -31354,7 +31456,7 @@
       <c r="S374" s="3"/>
       <c r="T374" s="3"/>
       <c r="U374" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -31380,7 +31482,7 @@
       <c r="S375" s="3"/>
       <c r="T375" s="3"/>
       <c r="U375" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -31406,7 +31508,7 @@
       <c r="S376" s="3"/>
       <c r="T376" s="3"/>
       <c r="U376" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -31432,7 +31534,7 @@
       <c r="S377" s="3"/>
       <c r="T377" s="3"/>
       <c r="U377" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -31458,7 +31560,7 @@
       <c r="S378" s="3"/>
       <c r="T378" s="3"/>
       <c r="U378" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -31484,7 +31586,7 @@
       <c r="S379" s="3"/>
       <c r="T379" s="3"/>
       <c r="U379" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -31510,7 +31612,7 @@
       <c r="S380" s="3"/>
       <c r="T380" s="3"/>
       <c r="U380" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -31536,7 +31638,7 @@
       <c r="S381" s="3"/>
       <c r="T381" s="3"/>
       <c r="U381" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -31562,7 +31664,7 @@
       <c r="S382" s="3"/>
       <c r="T382" s="3"/>
       <c r="U382" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -31588,7 +31690,7 @@
       <c r="S383" s="3"/>
       <c r="T383" s="3"/>
       <c r="U383" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -31614,7 +31716,7 @@
       <c r="S384" s="3"/>
       <c r="T384" s="3"/>
       <c r="U384" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -31640,7 +31742,7 @@
       <c r="S385" s="3"/>
       <c r="T385" s="3"/>
       <c r="U385" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -31666,7 +31768,7 @@
       <c r="S386" s="3"/>
       <c r="T386" s="3"/>
       <c r="U386" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -31692,7 +31794,7 @@
       <c r="S387" s="3"/>
       <c r="T387" s="3"/>
       <c r="U387" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -31718,7 +31820,7 @@
       <c r="S388" s="3"/>
       <c r="T388" s="3"/>
       <c r="U388" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -31744,7 +31846,7 @@
       <c r="S389" s="3"/>
       <c r="T389" s="3"/>
       <c r="U389" s="4" t="str">
-        <f t="shared" ref="U389:U390" si="12">IF(COUNTA(B389:T389)=0,"",AVERAGE(B389:T389))</f>
+        <f t="shared" ref="U389:U390" si="13">IF(COUNTA(B389:T389)=0,"",AVERAGE(B389:T389))</f>
         <v/>
       </c>
     </row>
@@ -31770,7 +31872,7 @@
       <c r="S390" s="3"/>
       <c r="T390" s="3"/>
       <c r="U390" s="4" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -31800,7 +31902,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="6" t="s">
         <v>37</v>
       </c>
       <c r="B1" s="7"/>
@@ -31815,7 +31917,7 @@
       <c r="K1" s="7"/>
     </row>
     <row r="2" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="8" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="7"/>
@@ -33089,19 +33191,39 @@
       </c>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A39" s="2"/>
-      <c r="B39" s="3"/>
-      <c r="C39" s="3"/>
-      <c r="D39" s="3"/>
-      <c r="E39" s="3"/>
-      <c r="F39" s="3"/>
-      <c r="G39" s="3"/>
-      <c r="H39" s="3"/>
-      <c r="I39" s="3"/>
-      <c r="J39" s="3"/>
-      <c r="K39" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
+      <c r="A39" s="2">
+        <v>46178</v>
+      </c>
+      <c r="B39" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="C39" s="3">
+        <v>3.14</v>
+      </c>
+      <c r="D39" s="3">
+        <v>2.83</v>
+      </c>
+      <c r="E39" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="F39" s="3">
+        <v>2.8</v>
+      </c>
+      <c r="G39" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="H39" s="3">
+        <v>2.63</v>
+      </c>
+      <c r="I39" s="3">
+        <v>2.74</v>
+      </c>
+      <c r="J39" s="3">
+        <v>2.59</v>
+      </c>
+      <c r="K39" s="4">
+        <f t="shared" ref="K39" si="7">IF(COUNTA(B39:J39)=0,"",AVERAGE(B39:J39))</f>
+        <v>2.8555555555555556</v>
       </c>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.25">
@@ -33580,7 +33702,7 @@
       <c r="I69" s="3"/>
       <c r="J69" s="3"/>
       <c r="K69" s="4" t="str">
-        <f t="shared" ref="K69:K132" si="7">IF(COUNTA(B69:J69)=0,"",AVERAGE(B69:J69))</f>
+        <f t="shared" ref="K69:K132" si="8">IF(COUNTA(B69:J69)=0,"",AVERAGE(B69:J69))</f>
         <v/>
       </c>
     </row>
@@ -33596,7 +33718,7 @@
       <c r="I70" s="3"/>
       <c r="J70" s="3"/>
       <c r="K70" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -33612,7 +33734,7 @@
       <c r="I71" s="3"/>
       <c r="J71" s="3"/>
       <c r="K71" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -33628,7 +33750,7 @@
       <c r="I72" s="3"/>
       <c r="J72" s="3"/>
       <c r="K72" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -33644,7 +33766,7 @@
       <c r="I73" s="3"/>
       <c r="J73" s="3"/>
       <c r="K73" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -33660,7 +33782,7 @@
       <c r="I74" s="3"/>
       <c r="J74" s="3"/>
       <c r="K74" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -33676,7 +33798,7 @@
       <c r="I75" s="3"/>
       <c r="J75" s="3"/>
       <c r="K75" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -33692,7 +33814,7 @@
       <c r="I76" s="3"/>
       <c r="J76" s="3"/>
       <c r="K76" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -33708,7 +33830,7 @@
       <c r="I77" s="3"/>
       <c r="J77" s="3"/>
       <c r="K77" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -33724,7 +33846,7 @@
       <c r="I78" s="3"/>
       <c r="J78" s="3"/>
       <c r="K78" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -33740,7 +33862,7 @@
       <c r="I79" s="3"/>
       <c r="J79" s="3"/>
       <c r="K79" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -33756,7 +33878,7 @@
       <c r="I80" s="3"/>
       <c r="J80" s="3"/>
       <c r="K80" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -33772,7 +33894,7 @@
       <c r="I81" s="3"/>
       <c r="J81" s="3"/>
       <c r="K81" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -33788,7 +33910,7 @@
       <c r="I82" s="3"/>
       <c r="J82" s="3"/>
       <c r="K82" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -33804,7 +33926,7 @@
       <c r="I83" s="3"/>
       <c r="J83" s="3"/>
       <c r="K83" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -33820,7 +33942,7 @@
       <c r="I84" s="3"/>
       <c r="J84" s="3"/>
       <c r="K84" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -33836,7 +33958,7 @@
       <c r="I85" s="3"/>
       <c r="J85" s="3"/>
       <c r="K85" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -33852,7 +33974,7 @@
       <c r="I86" s="3"/>
       <c r="J86" s="3"/>
       <c r="K86" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -33868,7 +33990,7 @@
       <c r="I87" s="3"/>
       <c r="J87" s="3"/>
       <c r="K87" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -33884,7 +34006,7 @@
       <c r="I88" s="3"/>
       <c r="J88" s="3"/>
       <c r="K88" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -33900,7 +34022,7 @@
       <c r="I89" s="3"/>
       <c r="J89" s="3"/>
       <c r="K89" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -33916,7 +34038,7 @@
       <c r="I90" s="3"/>
       <c r="J90" s="3"/>
       <c r="K90" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -33932,7 +34054,7 @@
       <c r="I91" s="3"/>
       <c r="J91" s="3"/>
       <c r="K91" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -33948,7 +34070,7 @@
       <c r="I92" s="3"/>
       <c r="J92" s="3"/>
       <c r="K92" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -33964,7 +34086,7 @@
       <c r="I93" s="3"/>
       <c r="J93" s="3"/>
       <c r="K93" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -33980,7 +34102,7 @@
       <c r="I94" s="3"/>
       <c r="J94" s="3"/>
       <c r="K94" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -33996,7 +34118,7 @@
       <c r="I95" s="3"/>
       <c r="J95" s="3"/>
       <c r="K95" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -34012,7 +34134,7 @@
       <c r="I96" s="3"/>
       <c r="J96" s="3"/>
       <c r="K96" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -34028,7 +34150,7 @@
       <c r="I97" s="3"/>
       <c r="J97" s="3"/>
       <c r="K97" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -34044,7 +34166,7 @@
       <c r="I98" s="3"/>
       <c r="J98" s="3"/>
       <c r="K98" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -34060,7 +34182,7 @@
       <c r="I99" s="3"/>
       <c r="J99" s="3"/>
       <c r="K99" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -34076,7 +34198,7 @@
       <c r="I100" s="3"/>
       <c r="J100" s="3"/>
       <c r="K100" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -34092,7 +34214,7 @@
       <c r="I101" s="3"/>
       <c r="J101" s="3"/>
       <c r="K101" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -34108,7 +34230,7 @@
       <c r="I102" s="3"/>
       <c r="J102" s="3"/>
       <c r="K102" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -34124,7 +34246,7 @@
       <c r="I103" s="3"/>
       <c r="J103" s="3"/>
       <c r="K103" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -34140,7 +34262,7 @@
       <c r="I104" s="3"/>
       <c r="J104" s="3"/>
       <c r="K104" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -34156,7 +34278,7 @@
       <c r="I105" s="3"/>
       <c r="J105" s="3"/>
       <c r="K105" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -34172,7 +34294,7 @@
       <c r="I106" s="3"/>
       <c r="J106" s="3"/>
       <c r="K106" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -34188,7 +34310,7 @@
       <c r="I107" s="3"/>
       <c r="J107" s="3"/>
       <c r="K107" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -34204,7 +34326,7 @@
       <c r="I108" s="3"/>
       <c r="J108" s="3"/>
       <c r="K108" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -34220,7 +34342,7 @@
       <c r="I109" s="3"/>
       <c r="J109" s="3"/>
       <c r="K109" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -34236,7 +34358,7 @@
       <c r="I110" s="3"/>
       <c r="J110" s="3"/>
       <c r="K110" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -34252,7 +34374,7 @@
       <c r="I111" s="3"/>
       <c r="J111" s="3"/>
       <c r="K111" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -34268,7 +34390,7 @@
       <c r="I112" s="3"/>
       <c r="J112" s="3"/>
       <c r="K112" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -34284,7 +34406,7 @@
       <c r="I113" s="3"/>
       <c r="J113" s="3"/>
       <c r="K113" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -34300,7 +34422,7 @@
       <c r="I114" s="3"/>
       <c r="J114" s="3"/>
       <c r="K114" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -34316,7 +34438,7 @@
       <c r="I115" s="3"/>
       <c r="J115" s="3"/>
       <c r="K115" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -34332,7 +34454,7 @@
       <c r="I116" s="3"/>
       <c r="J116" s="3"/>
       <c r="K116" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -34348,7 +34470,7 @@
       <c r="I117" s="3"/>
       <c r="J117" s="3"/>
       <c r="K117" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -34364,7 +34486,7 @@
       <c r="I118" s="3"/>
       <c r="J118" s="3"/>
       <c r="K118" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -34380,7 +34502,7 @@
       <c r="I119" s="3"/>
       <c r="J119" s="3"/>
       <c r="K119" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -34396,7 +34518,7 @@
       <c r="I120" s="3"/>
       <c r="J120" s="3"/>
       <c r="K120" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -34412,7 +34534,7 @@
       <c r="I121" s="3"/>
       <c r="J121" s="3"/>
       <c r="K121" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -34428,7 +34550,7 @@
       <c r="I122" s="3"/>
       <c r="J122" s="3"/>
       <c r="K122" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -34444,7 +34566,7 @@
       <c r="I123" s="3"/>
       <c r="J123" s="3"/>
       <c r="K123" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -34460,7 +34582,7 @@
       <c r="I124" s="3"/>
       <c r="J124" s="3"/>
       <c r="K124" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -34476,7 +34598,7 @@
       <c r="I125" s="3"/>
       <c r="J125" s="3"/>
       <c r="K125" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -34492,7 +34614,7 @@
       <c r="I126" s="3"/>
       <c r="J126" s="3"/>
       <c r="K126" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -34508,7 +34630,7 @@
       <c r="I127" s="3"/>
       <c r="J127" s="3"/>
       <c r="K127" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -34524,7 +34646,7 @@
       <c r="I128" s="3"/>
       <c r="J128" s="3"/>
       <c r="K128" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -34540,7 +34662,7 @@
       <c r="I129" s="3"/>
       <c r="J129" s="3"/>
       <c r="K129" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -34556,7 +34678,7 @@
       <c r="I130" s="3"/>
       <c r="J130" s="3"/>
       <c r="K130" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -34572,7 +34694,7 @@
       <c r="I131" s="3"/>
       <c r="J131" s="3"/>
       <c r="K131" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -34588,7 +34710,7 @@
       <c r="I132" s="3"/>
       <c r="J132" s="3"/>
       <c r="K132" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -34604,7 +34726,7 @@
       <c r="I133" s="3"/>
       <c r="J133" s="3"/>
       <c r="K133" s="4" t="str">
-        <f t="shared" ref="K133:K196" si="8">IF(COUNTA(B133:J133)=0,"",AVERAGE(B133:J133))</f>
+        <f t="shared" ref="K133:K196" si="9">IF(COUNTA(B133:J133)=0,"",AVERAGE(B133:J133))</f>
         <v/>
       </c>
     </row>
@@ -34620,7 +34742,7 @@
       <c r="I134" s="3"/>
       <c r="J134" s="3"/>
       <c r="K134" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -34636,7 +34758,7 @@
       <c r="I135" s="3"/>
       <c r="J135" s="3"/>
       <c r="K135" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -34652,7 +34774,7 @@
       <c r="I136" s="3"/>
       <c r="J136" s="3"/>
       <c r="K136" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -34668,7 +34790,7 @@
       <c r="I137" s="3"/>
       <c r="J137" s="3"/>
       <c r="K137" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -34684,7 +34806,7 @@
       <c r="I138" s="3"/>
       <c r="J138" s="3"/>
       <c r="K138" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -34700,7 +34822,7 @@
       <c r="I139" s="3"/>
       <c r="J139" s="3"/>
       <c r="K139" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -34716,7 +34838,7 @@
       <c r="I140" s="3"/>
       <c r="J140" s="3"/>
       <c r="K140" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -34732,7 +34854,7 @@
       <c r="I141" s="3"/>
       <c r="J141" s="3"/>
       <c r="K141" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -34748,7 +34870,7 @@
       <c r="I142" s="3"/>
       <c r="J142" s="3"/>
       <c r="K142" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -34764,7 +34886,7 @@
       <c r="I143" s="3"/>
       <c r="J143" s="3"/>
       <c r="K143" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -34780,7 +34902,7 @@
       <c r="I144" s="3"/>
       <c r="J144" s="3"/>
       <c r="K144" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -34796,7 +34918,7 @@
       <c r="I145" s="3"/>
       <c r="J145" s="3"/>
       <c r="K145" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -34812,7 +34934,7 @@
       <c r="I146" s="3"/>
       <c r="J146" s="3"/>
       <c r="K146" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -34828,7 +34950,7 @@
       <c r="I147" s="3"/>
       <c r="J147" s="3"/>
       <c r="K147" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -34844,7 +34966,7 @@
       <c r="I148" s="3"/>
       <c r="J148" s="3"/>
       <c r="K148" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -34860,7 +34982,7 @@
       <c r="I149" s="3"/>
       <c r="J149" s="3"/>
       <c r="K149" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -34876,7 +34998,7 @@
       <c r="I150" s="3"/>
       <c r="J150" s="3"/>
       <c r="K150" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -34892,7 +35014,7 @@
       <c r="I151" s="3"/>
       <c r="J151" s="3"/>
       <c r="K151" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -34908,7 +35030,7 @@
       <c r="I152" s="3"/>
       <c r="J152" s="3"/>
       <c r="K152" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -34924,7 +35046,7 @@
       <c r="I153" s="3"/>
       <c r="J153" s="3"/>
       <c r="K153" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -34940,7 +35062,7 @@
       <c r="I154" s="3"/>
       <c r="J154" s="3"/>
       <c r="K154" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -34956,7 +35078,7 @@
       <c r="I155" s="3"/>
       <c r="J155" s="3"/>
       <c r="K155" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -34972,7 +35094,7 @@
       <c r="I156" s="3"/>
       <c r="J156" s="3"/>
       <c r="K156" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -34988,7 +35110,7 @@
       <c r="I157" s="3"/>
       <c r="J157" s="3"/>
       <c r="K157" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -35004,7 +35126,7 @@
       <c r="I158" s="3"/>
       <c r="J158" s="3"/>
       <c r="K158" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -35020,7 +35142,7 @@
       <c r="I159" s="3"/>
       <c r="J159" s="3"/>
       <c r="K159" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -35036,7 +35158,7 @@
       <c r="I160" s="3"/>
       <c r="J160" s="3"/>
       <c r="K160" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -35052,7 +35174,7 @@
       <c r="I161" s="3"/>
       <c r="J161" s="3"/>
       <c r="K161" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -35068,7 +35190,7 @@
       <c r="I162" s="3"/>
       <c r="J162" s="3"/>
       <c r="K162" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -35084,7 +35206,7 @@
       <c r="I163" s="3"/>
       <c r="J163" s="3"/>
       <c r="K163" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -35100,7 +35222,7 @@
       <c r="I164" s="3"/>
       <c r="J164" s="3"/>
       <c r="K164" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -35116,7 +35238,7 @@
       <c r="I165" s="3"/>
       <c r="J165" s="3"/>
       <c r="K165" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -35132,7 +35254,7 @@
       <c r="I166" s="3"/>
       <c r="J166" s="3"/>
       <c r="K166" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -35148,7 +35270,7 @@
       <c r="I167" s="3"/>
       <c r="J167" s="3"/>
       <c r="K167" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -35164,7 +35286,7 @@
       <c r="I168" s="3"/>
       <c r="J168" s="3"/>
       <c r="K168" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -35180,7 +35302,7 @@
       <c r="I169" s="3"/>
       <c r="J169" s="3"/>
       <c r="K169" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -35196,7 +35318,7 @@
       <c r="I170" s="3"/>
       <c r="J170" s="3"/>
       <c r="K170" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -35212,7 +35334,7 @@
       <c r="I171" s="3"/>
       <c r="J171" s="3"/>
       <c r="K171" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -35228,7 +35350,7 @@
       <c r="I172" s="3"/>
       <c r="J172" s="3"/>
       <c r="K172" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -35244,7 +35366,7 @@
       <c r="I173" s="3"/>
       <c r="J173" s="3"/>
       <c r="K173" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -35260,7 +35382,7 @@
       <c r="I174" s="3"/>
       <c r="J174" s="3"/>
       <c r="K174" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -35276,7 +35398,7 @@
       <c r="I175" s="3"/>
       <c r="J175" s="3"/>
       <c r="K175" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -35292,7 +35414,7 @@
       <c r="I176" s="3"/>
       <c r="J176" s="3"/>
       <c r="K176" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -35308,7 +35430,7 @@
       <c r="I177" s="3"/>
       <c r="J177" s="3"/>
       <c r="K177" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -35324,7 +35446,7 @@
       <c r="I178" s="3"/>
       <c r="J178" s="3"/>
       <c r="K178" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -35340,7 +35462,7 @@
       <c r="I179" s="3"/>
       <c r="J179" s="3"/>
       <c r="K179" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -35356,7 +35478,7 @@
       <c r="I180" s="3"/>
       <c r="J180" s="3"/>
       <c r="K180" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -35372,7 +35494,7 @@
       <c r="I181" s="3"/>
       <c r="J181" s="3"/>
       <c r="K181" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -35388,7 +35510,7 @@
       <c r="I182" s="3"/>
       <c r="J182" s="3"/>
       <c r="K182" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -35404,7 +35526,7 @@
       <c r="I183" s="3"/>
       <c r="J183" s="3"/>
       <c r="K183" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -35420,7 +35542,7 @@
       <c r="I184" s="3"/>
       <c r="J184" s="3"/>
       <c r="K184" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -35436,7 +35558,7 @@
       <c r="I185" s="3"/>
       <c r="J185" s="3"/>
       <c r="K185" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -35452,7 +35574,7 @@
       <c r="I186" s="3"/>
       <c r="J186" s="3"/>
       <c r="K186" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -35468,7 +35590,7 @@
       <c r="I187" s="3"/>
       <c r="J187" s="3"/>
       <c r="K187" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -35484,7 +35606,7 @@
       <c r="I188" s="3"/>
       <c r="J188" s="3"/>
       <c r="K188" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -35500,7 +35622,7 @@
       <c r="I189" s="3"/>
       <c r="J189" s="3"/>
       <c r="K189" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -35516,7 +35638,7 @@
       <c r="I190" s="3"/>
       <c r="J190" s="3"/>
       <c r="K190" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -35532,7 +35654,7 @@
       <c r="I191" s="3"/>
       <c r="J191" s="3"/>
       <c r="K191" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -35548,7 +35670,7 @@
       <c r="I192" s="3"/>
       <c r="J192" s="3"/>
       <c r="K192" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -35564,7 +35686,7 @@
       <c r="I193" s="3"/>
       <c r="J193" s="3"/>
       <c r="K193" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -35580,7 +35702,7 @@
       <c r="I194" s="3"/>
       <c r="J194" s="3"/>
       <c r="K194" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -35596,7 +35718,7 @@
       <c r="I195" s="3"/>
       <c r="J195" s="3"/>
       <c r="K195" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -35612,7 +35734,7 @@
       <c r="I196" s="3"/>
       <c r="J196" s="3"/>
       <c r="K196" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -35628,7 +35750,7 @@
       <c r="I197" s="3"/>
       <c r="J197" s="3"/>
       <c r="K197" s="4" t="str">
-        <f t="shared" ref="K197:K260" si="9">IF(COUNTA(B197:J197)=0,"",AVERAGE(B197:J197))</f>
+        <f t="shared" ref="K197:K260" si="10">IF(COUNTA(B197:J197)=0,"",AVERAGE(B197:J197))</f>
         <v/>
       </c>
     </row>
@@ -35644,7 +35766,7 @@
       <c r="I198" s="3"/>
       <c r="J198" s="3"/>
       <c r="K198" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -35660,7 +35782,7 @@
       <c r="I199" s="3"/>
       <c r="J199" s="3"/>
       <c r="K199" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -35676,7 +35798,7 @@
       <c r="I200" s="3"/>
       <c r="J200" s="3"/>
       <c r="K200" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -35692,7 +35814,7 @@
       <c r="I201" s="3"/>
       <c r="J201" s="3"/>
       <c r="K201" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -35708,7 +35830,7 @@
       <c r="I202" s="3"/>
       <c r="J202" s="3"/>
       <c r="K202" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -35724,7 +35846,7 @@
       <c r="I203" s="3"/>
       <c r="J203" s="3"/>
       <c r="K203" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -35740,7 +35862,7 @@
       <c r="I204" s="3"/>
       <c r="J204" s="3"/>
       <c r="K204" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -35756,7 +35878,7 @@
       <c r="I205" s="3"/>
       <c r="J205" s="3"/>
       <c r="K205" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -35772,7 +35894,7 @@
       <c r="I206" s="3"/>
       <c r="J206" s="3"/>
       <c r="K206" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -35788,7 +35910,7 @@
       <c r="I207" s="3"/>
       <c r="J207" s="3"/>
       <c r="K207" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -35804,7 +35926,7 @@
       <c r="I208" s="3"/>
       <c r="J208" s="3"/>
       <c r="K208" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -35820,7 +35942,7 @@
       <c r="I209" s="3"/>
       <c r="J209" s="3"/>
       <c r="K209" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -35836,7 +35958,7 @@
       <c r="I210" s="3"/>
       <c r="J210" s="3"/>
       <c r="K210" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -35852,7 +35974,7 @@
       <c r="I211" s="3"/>
       <c r="J211" s="3"/>
       <c r="K211" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -35868,7 +35990,7 @@
       <c r="I212" s="3"/>
       <c r="J212" s="3"/>
       <c r="K212" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -35884,7 +36006,7 @@
       <c r="I213" s="3"/>
       <c r="J213" s="3"/>
       <c r="K213" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -35900,7 +36022,7 @@
       <c r="I214" s="3"/>
       <c r="J214" s="3"/>
       <c r="K214" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -35916,7 +36038,7 @@
       <c r="I215" s="3"/>
       <c r="J215" s="3"/>
       <c r="K215" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -35932,7 +36054,7 @@
       <c r="I216" s="3"/>
       <c r="J216" s="3"/>
       <c r="K216" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -35948,7 +36070,7 @@
       <c r="I217" s="3"/>
       <c r="J217" s="3"/>
       <c r="K217" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -35964,7 +36086,7 @@
       <c r="I218" s="3"/>
       <c r="J218" s="3"/>
       <c r="K218" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -35980,7 +36102,7 @@
       <c r="I219" s="3"/>
       <c r="J219" s="3"/>
       <c r="K219" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -35996,7 +36118,7 @@
       <c r="I220" s="3"/>
       <c r="J220" s="3"/>
       <c r="K220" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -36012,7 +36134,7 @@
       <c r="I221" s="3"/>
       <c r="J221" s="3"/>
       <c r="K221" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -36028,7 +36150,7 @@
       <c r="I222" s="3"/>
       <c r="J222" s="3"/>
       <c r="K222" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -36044,7 +36166,7 @@
       <c r="I223" s="3"/>
       <c r="J223" s="3"/>
       <c r="K223" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -36060,7 +36182,7 @@
       <c r="I224" s="3"/>
       <c r="J224" s="3"/>
       <c r="K224" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -36076,7 +36198,7 @@
       <c r="I225" s="3"/>
       <c r="J225" s="3"/>
       <c r="K225" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -36092,7 +36214,7 @@
       <c r="I226" s="3"/>
       <c r="J226" s="3"/>
       <c r="K226" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -36108,7 +36230,7 @@
       <c r="I227" s="3"/>
       <c r="J227" s="3"/>
       <c r="K227" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -36124,7 +36246,7 @@
       <c r="I228" s="3"/>
       <c r="J228" s="3"/>
       <c r="K228" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -36140,7 +36262,7 @@
       <c r="I229" s="3"/>
       <c r="J229" s="3"/>
       <c r="K229" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -36156,7 +36278,7 @@
       <c r="I230" s="3"/>
       <c r="J230" s="3"/>
       <c r="K230" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -36172,7 +36294,7 @@
       <c r="I231" s="3"/>
       <c r="J231" s="3"/>
       <c r="K231" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -36188,7 +36310,7 @@
       <c r="I232" s="3"/>
       <c r="J232" s="3"/>
       <c r="K232" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -36204,7 +36326,7 @@
       <c r="I233" s="3"/>
       <c r="J233" s="3"/>
       <c r="K233" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -36220,7 +36342,7 @@
       <c r="I234" s="3"/>
       <c r="J234" s="3"/>
       <c r="K234" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -36236,7 +36358,7 @@
       <c r="I235" s="3"/>
       <c r="J235" s="3"/>
       <c r="K235" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -36252,7 +36374,7 @@
       <c r="I236" s="3"/>
       <c r="J236" s="3"/>
       <c r="K236" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -36268,7 +36390,7 @@
       <c r="I237" s="3"/>
       <c r="J237" s="3"/>
       <c r="K237" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -36284,7 +36406,7 @@
       <c r="I238" s="3"/>
       <c r="J238" s="3"/>
       <c r="K238" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -36300,7 +36422,7 @@
       <c r="I239" s="3"/>
       <c r="J239" s="3"/>
       <c r="K239" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -36316,7 +36438,7 @@
       <c r="I240" s="3"/>
       <c r="J240" s="3"/>
       <c r="K240" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -36332,7 +36454,7 @@
       <c r="I241" s="3"/>
       <c r="J241" s="3"/>
       <c r="K241" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -36348,7 +36470,7 @@
       <c r="I242" s="3"/>
       <c r="J242" s="3"/>
       <c r="K242" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -36364,7 +36486,7 @@
       <c r="I243" s="3"/>
       <c r="J243" s="3"/>
       <c r="K243" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -36380,7 +36502,7 @@
       <c r="I244" s="3"/>
       <c r="J244" s="3"/>
       <c r="K244" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -36396,7 +36518,7 @@
       <c r="I245" s="3"/>
       <c r="J245" s="3"/>
       <c r="K245" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -36412,7 +36534,7 @@
       <c r="I246" s="3"/>
       <c r="J246" s="3"/>
       <c r="K246" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -36428,7 +36550,7 @@
       <c r="I247" s="3"/>
       <c r="J247" s="3"/>
       <c r="K247" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -36444,7 +36566,7 @@
       <c r="I248" s="3"/>
       <c r="J248" s="3"/>
       <c r="K248" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -36460,7 +36582,7 @@
       <c r="I249" s="3"/>
       <c r="J249" s="3"/>
       <c r="K249" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -36476,7 +36598,7 @@
       <c r="I250" s="3"/>
       <c r="J250" s="3"/>
       <c r="K250" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -36492,7 +36614,7 @@
       <c r="I251" s="3"/>
       <c r="J251" s="3"/>
       <c r="K251" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -36508,7 +36630,7 @@
       <c r="I252" s="3"/>
       <c r="J252" s="3"/>
       <c r="K252" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -36524,7 +36646,7 @@
       <c r="I253" s="3"/>
       <c r="J253" s="3"/>
       <c r="K253" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -36540,7 +36662,7 @@
       <c r="I254" s="3"/>
       <c r="J254" s="3"/>
       <c r="K254" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -36556,7 +36678,7 @@
       <c r="I255" s="3"/>
       <c r="J255" s="3"/>
       <c r="K255" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -36572,7 +36694,7 @@
       <c r="I256" s="3"/>
       <c r="J256" s="3"/>
       <c r="K256" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -36588,7 +36710,7 @@
       <c r="I257" s="3"/>
       <c r="J257" s="3"/>
       <c r="K257" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -36604,7 +36726,7 @@
       <c r="I258" s="3"/>
       <c r="J258" s="3"/>
       <c r="K258" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -36620,7 +36742,7 @@
       <c r="I259" s="3"/>
       <c r="J259" s="3"/>
       <c r="K259" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -36636,7 +36758,7 @@
       <c r="I260" s="3"/>
       <c r="J260" s="3"/>
       <c r="K260" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -36652,7 +36774,7 @@
       <c r="I261" s="3"/>
       <c r="J261" s="3"/>
       <c r="K261" s="4" t="str">
-        <f t="shared" ref="K261:K324" si="10">IF(COUNTA(B261:J261)=0,"",AVERAGE(B261:J261))</f>
+        <f t="shared" ref="K261:K324" si="11">IF(COUNTA(B261:J261)=0,"",AVERAGE(B261:J261))</f>
         <v/>
       </c>
     </row>
@@ -36668,7 +36790,7 @@
       <c r="I262" s="3"/>
       <c r="J262" s="3"/>
       <c r="K262" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -36684,7 +36806,7 @@
       <c r="I263" s="3"/>
       <c r="J263" s="3"/>
       <c r="K263" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -36700,7 +36822,7 @@
       <c r="I264" s="3"/>
       <c r="J264" s="3"/>
       <c r="K264" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -36716,7 +36838,7 @@
       <c r="I265" s="3"/>
       <c r="J265" s="3"/>
       <c r="K265" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -36732,7 +36854,7 @@
       <c r="I266" s="3"/>
       <c r="J266" s="3"/>
       <c r="K266" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -36748,7 +36870,7 @@
       <c r="I267" s="3"/>
       <c r="J267" s="3"/>
       <c r="K267" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -36764,7 +36886,7 @@
       <c r="I268" s="3"/>
       <c r="J268" s="3"/>
       <c r="K268" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -36780,7 +36902,7 @@
       <c r="I269" s="3"/>
       <c r="J269" s="3"/>
       <c r="K269" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -36796,7 +36918,7 @@
       <c r="I270" s="3"/>
       <c r="J270" s="3"/>
       <c r="K270" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -36812,7 +36934,7 @@
       <c r="I271" s="3"/>
       <c r="J271" s="3"/>
       <c r="K271" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -36828,7 +36950,7 @@
       <c r="I272" s="3"/>
       <c r="J272" s="3"/>
       <c r="K272" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -36844,7 +36966,7 @@
       <c r="I273" s="3"/>
       <c r="J273" s="3"/>
       <c r="K273" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -36860,7 +36982,7 @@
       <c r="I274" s="3"/>
       <c r="J274" s="3"/>
       <c r="K274" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -36876,7 +36998,7 @@
       <c r="I275" s="3"/>
       <c r="J275" s="3"/>
       <c r="K275" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -36892,7 +37014,7 @@
       <c r="I276" s="3"/>
       <c r="J276" s="3"/>
       <c r="K276" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -36908,7 +37030,7 @@
       <c r="I277" s="3"/>
       <c r="J277" s="3"/>
       <c r="K277" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -36924,7 +37046,7 @@
       <c r="I278" s="3"/>
       <c r="J278" s="3"/>
       <c r="K278" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -36940,7 +37062,7 @@
       <c r="I279" s="3"/>
       <c r="J279" s="3"/>
       <c r="K279" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -36956,7 +37078,7 @@
       <c r="I280" s="3"/>
       <c r="J280" s="3"/>
       <c r="K280" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -36972,7 +37094,7 @@
       <c r="I281" s="3"/>
       <c r="J281" s="3"/>
       <c r="K281" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -36988,7 +37110,7 @@
       <c r="I282" s="3"/>
       <c r="J282" s="3"/>
       <c r="K282" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -37004,7 +37126,7 @@
       <c r="I283" s="3"/>
       <c r="J283" s="3"/>
       <c r="K283" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -37020,7 +37142,7 @@
       <c r="I284" s="3"/>
       <c r="J284" s="3"/>
       <c r="K284" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -37036,7 +37158,7 @@
       <c r="I285" s="3"/>
       <c r="J285" s="3"/>
       <c r="K285" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -37052,7 +37174,7 @@
       <c r="I286" s="3"/>
       <c r="J286" s="3"/>
       <c r="K286" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -37068,7 +37190,7 @@
       <c r="I287" s="3"/>
       <c r="J287" s="3"/>
       <c r="K287" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -37084,7 +37206,7 @@
       <c r="I288" s="3"/>
       <c r="J288" s="3"/>
       <c r="K288" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -37100,7 +37222,7 @@
       <c r="I289" s="3"/>
       <c r="J289" s="3"/>
       <c r="K289" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -37116,7 +37238,7 @@
       <c r="I290" s="3"/>
       <c r="J290" s="3"/>
       <c r="K290" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -37132,7 +37254,7 @@
       <c r="I291" s="3"/>
       <c r="J291" s="3"/>
       <c r="K291" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -37148,7 +37270,7 @@
       <c r="I292" s="3"/>
       <c r="J292" s="3"/>
       <c r="K292" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -37164,7 +37286,7 @@
       <c r="I293" s="3"/>
       <c r="J293" s="3"/>
       <c r="K293" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -37180,7 +37302,7 @@
       <c r="I294" s="3"/>
       <c r="J294" s="3"/>
       <c r="K294" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -37196,7 +37318,7 @@
       <c r="I295" s="3"/>
       <c r="J295" s="3"/>
       <c r="K295" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -37212,7 +37334,7 @@
       <c r="I296" s="3"/>
       <c r="J296" s="3"/>
       <c r="K296" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -37228,7 +37350,7 @@
       <c r="I297" s="3"/>
       <c r="J297" s="3"/>
       <c r="K297" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -37244,7 +37366,7 @@
       <c r="I298" s="3"/>
       <c r="J298" s="3"/>
       <c r="K298" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -37260,7 +37382,7 @@
       <c r="I299" s="3"/>
       <c r="J299" s="3"/>
       <c r="K299" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -37276,7 +37398,7 @@
       <c r="I300" s="3"/>
       <c r="J300" s="3"/>
       <c r="K300" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -37292,7 +37414,7 @@
       <c r="I301" s="3"/>
       <c r="J301" s="3"/>
       <c r="K301" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -37308,7 +37430,7 @@
       <c r="I302" s="3"/>
       <c r="J302" s="3"/>
       <c r="K302" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -37324,7 +37446,7 @@
       <c r="I303" s="3"/>
       <c r="J303" s="3"/>
       <c r="K303" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -37340,7 +37462,7 @@
       <c r="I304" s="3"/>
       <c r="J304" s="3"/>
       <c r="K304" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -37356,7 +37478,7 @@
       <c r="I305" s="3"/>
       <c r="J305" s="3"/>
       <c r="K305" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -37372,7 +37494,7 @@
       <c r="I306" s="3"/>
       <c r="J306" s="3"/>
       <c r="K306" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -37388,7 +37510,7 @@
       <c r="I307" s="3"/>
       <c r="J307" s="3"/>
       <c r="K307" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -37404,7 +37526,7 @@
       <c r="I308" s="3"/>
       <c r="J308" s="3"/>
       <c r="K308" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -37420,7 +37542,7 @@
       <c r="I309" s="3"/>
       <c r="J309" s="3"/>
       <c r="K309" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -37436,7 +37558,7 @@
       <c r="I310" s="3"/>
       <c r="J310" s="3"/>
       <c r="K310" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -37452,7 +37574,7 @@
       <c r="I311" s="3"/>
       <c r="J311" s="3"/>
       <c r="K311" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -37468,7 +37590,7 @@
       <c r="I312" s="3"/>
       <c r="J312" s="3"/>
       <c r="K312" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -37484,7 +37606,7 @@
       <c r="I313" s="3"/>
       <c r="J313" s="3"/>
       <c r="K313" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -37500,7 +37622,7 @@
       <c r="I314" s="3"/>
       <c r="J314" s="3"/>
       <c r="K314" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -37516,7 +37638,7 @@
       <c r="I315" s="3"/>
       <c r="J315" s="3"/>
       <c r="K315" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -37532,7 +37654,7 @@
       <c r="I316" s="3"/>
       <c r="J316" s="3"/>
       <c r="K316" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -37548,7 +37670,7 @@
       <c r="I317" s="3"/>
       <c r="J317" s="3"/>
       <c r="K317" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -37564,7 +37686,7 @@
       <c r="I318" s="3"/>
       <c r="J318" s="3"/>
       <c r="K318" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -37580,7 +37702,7 @@
       <c r="I319" s="3"/>
       <c r="J319" s="3"/>
       <c r="K319" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -37596,7 +37718,7 @@
       <c r="I320" s="3"/>
       <c r="J320" s="3"/>
       <c r="K320" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -37612,7 +37734,7 @@
       <c r="I321" s="3"/>
       <c r="J321" s="3"/>
       <c r="K321" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -37628,7 +37750,7 @@
       <c r="I322" s="3"/>
       <c r="J322" s="3"/>
       <c r="K322" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -37644,7 +37766,7 @@
       <c r="I323" s="3"/>
       <c r="J323" s="3"/>
       <c r="K323" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -37660,7 +37782,7 @@
       <c r="I324" s="3"/>
       <c r="J324" s="3"/>
       <c r="K324" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -37676,7 +37798,7 @@
       <c r="I325" s="3"/>
       <c r="J325" s="3"/>
       <c r="K325" s="4" t="str">
-        <f t="shared" ref="K325:K388" si="11">IF(COUNTA(B325:J325)=0,"",AVERAGE(B325:J325))</f>
+        <f t="shared" ref="K325:K388" si="12">IF(COUNTA(B325:J325)=0,"",AVERAGE(B325:J325))</f>
         <v/>
       </c>
     </row>
@@ -37692,7 +37814,7 @@
       <c r="I326" s="3"/>
       <c r="J326" s="3"/>
       <c r="K326" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -37708,7 +37830,7 @@
       <c r="I327" s="3"/>
       <c r="J327" s="3"/>
       <c r="K327" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -37724,7 +37846,7 @@
       <c r="I328" s="3"/>
       <c r="J328" s="3"/>
       <c r="K328" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -37740,7 +37862,7 @@
       <c r="I329" s="3"/>
       <c r="J329" s="3"/>
       <c r="K329" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -37756,7 +37878,7 @@
       <c r="I330" s="3"/>
       <c r="J330" s="3"/>
       <c r="K330" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -37772,7 +37894,7 @@
       <c r="I331" s="3"/>
       <c r="J331" s="3"/>
       <c r="K331" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -37788,7 +37910,7 @@
       <c r="I332" s="3"/>
       <c r="J332" s="3"/>
       <c r="K332" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -37804,7 +37926,7 @@
       <c r="I333" s="3"/>
       <c r="J333" s="3"/>
       <c r="K333" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -37820,7 +37942,7 @@
       <c r="I334" s="3"/>
       <c r="J334" s="3"/>
       <c r="K334" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -37836,7 +37958,7 @@
       <c r="I335" s="3"/>
       <c r="J335" s="3"/>
       <c r="K335" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -37852,7 +37974,7 @@
       <c r="I336" s="3"/>
       <c r="J336" s="3"/>
       <c r="K336" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -37868,7 +37990,7 @@
       <c r="I337" s="3"/>
       <c r="J337" s="3"/>
       <c r="K337" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -37884,7 +38006,7 @@
       <c r="I338" s="3"/>
       <c r="J338" s="3"/>
       <c r="K338" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -37900,7 +38022,7 @@
       <c r="I339" s="3"/>
       <c r="J339" s="3"/>
       <c r="K339" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -37916,7 +38038,7 @@
       <c r="I340" s="3"/>
       <c r="J340" s="3"/>
       <c r="K340" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -37932,7 +38054,7 @@
       <c r="I341" s="3"/>
       <c r="J341" s="3"/>
       <c r="K341" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -37948,7 +38070,7 @@
       <c r="I342" s="3"/>
       <c r="J342" s="3"/>
       <c r="K342" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -37964,7 +38086,7 @@
       <c r="I343" s="3"/>
       <c r="J343" s="3"/>
       <c r="K343" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -37980,7 +38102,7 @@
       <c r="I344" s="3"/>
       <c r="J344" s="3"/>
       <c r="K344" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -37996,7 +38118,7 @@
       <c r="I345" s="3"/>
       <c r="J345" s="3"/>
       <c r="K345" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -38012,7 +38134,7 @@
       <c r="I346" s="3"/>
       <c r="J346" s="3"/>
       <c r="K346" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -38028,7 +38150,7 @@
       <c r="I347" s="3"/>
       <c r="J347" s="3"/>
       <c r="K347" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -38044,7 +38166,7 @@
       <c r="I348" s="3"/>
       <c r="J348" s="3"/>
       <c r="K348" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -38060,7 +38182,7 @@
       <c r="I349" s="3"/>
       <c r="J349" s="3"/>
       <c r="K349" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -38076,7 +38198,7 @@
       <c r="I350" s="3"/>
       <c r="J350" s="3"/>
       <c r="K350" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -38092,7 +38214,7 @@
       <c r="I351" s="3"/>
       <c r="J351" s="3"/>
       <c r="K351" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -38108,7 +38230,7 @@
       <c r="I352" s="3"/>
       <c r="J352" s="3"/>
       <c r="K352" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -38124,7 +38246,7 @@
       <c r="I353" s="3"/>
       <c r="J353" s="3"/>
       <c r="K353" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -38140,7 +38262,7 @@
       <c r="I354" s="3"/>
       <c r="J354" s="3"/>
       <c r="K354" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -38156,7 +38278,7 @@
       <c r="I355" s="3"/>
       <c r="J355" s="3"/>
       <c r="K355" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -38172,7 +38294,7 @@
       <c r="I356" s="3"/>
       <c r="J356" s="3"/>
       <c r="K356" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -38188,7 +38310,7 @@
       <c r="I357" s="3"/>
       <c r="J357" s="3"/>
       <c r="K357" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -38204,7 +38326,7 @@
       <c r="I358" s="3"/>
       <c r="J358" s="3"/>
       <c r="K358" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -38220,7 +38342,7 @@
       <c r="I359" s="3"/>
       <c r="J359" s="3"/>
       <c r="K359" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -38236,7 +38358,7 @@
       <c r="I360" s="3"/>
       <c r="J360" s="3"/>
       <c r="K360" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -38252,7 +38374,7 @@
       <c r="I361" s="3"/>
       <c r="J361" s="3"/>
       <c r="K361" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -38268,7 +38390,7 @@
       <c r="I362" s="3"/>
       <c r="J362" s="3"/>
       <c r="K362" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -38284,7 +38406,7 @@
       <c r="I363" s="3"/>
       <c r="J363" s="3"/>
       <c r="K363" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -38300,7 +38422,7 @@
       <c r="I364" s="3"/>
       <c r="J364" s="3"/>
       <c r="K364" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -38316,7 +38438,7 @@
       <c r="I365" s="3"/>
       <c r="J365" s="3"/>
       <c r="K365" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -38332,7 +38454,7 @@
       <c r="I366" s="3"/>
       <c r="J366" s="3"/>
       <c r="K366" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -38348,7 +38470,7 @@
       <c r="I367" s="3"/>
       <c r="J367" s="3"/>
       <c r="K367" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -38364,7 +38486,7 @@
       <c r="I368" s="3"/>
       <c r="J368" s="3"/>
       <c r="K368" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -38380,7 +38502,7 @@
       <c r="I369" s="3"/>
       <c r="J369" s="3"/>
       <c r="K369" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -38396,7 +38518,7 @@
       <c r="I370" s="3"/>
       <c r="J370" s="3"/>
       <c r="K370" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -38412,7 +38534,7 @@
       <c r="I371" s="3"/>
       <c r="J371" s="3"/>
       <c r="K371" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -38428,7 +38550,7 @@
       <c r="I372" s="3"/>
       <c r="J372" s="3"/>
       <c r="K372" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -38444,7 +38566,7 @@
       <c r="I373" s="3"/>
       <c r="J373" s="3"/>
       <c r="K373" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -38460,7 +38582,7 @@
       <c r="I374" s="3"/>
       <c r="J374" s="3"/>
       <c r="K374" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -38476,7 +38598,7 @@
       <c r="I375" s="3"/>
       <c r="J375" s="3"/>
       <c r="K375" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -38492,7 +38614,7 @@
       <c r="I376" s="3"/>
       <c r="J376" s="3"/>
       <c r="K376" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -38508,7 +38630,7 @@
       <c r="I377" s="3"/>
       <c r="J377" s="3"/>
       <c r="K377" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -38524,7 +38646,7 @@
       <c r="I378" s="3"/>
       <c r="J378" s="3"/>
       <c r="K378" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -38540,7 +38662,7 @@
       <c r="I379" s="3"/>
       <c r="J379" s="3"/>
       <c r="K379" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -38556,7 +38678,7 @@
       <c r="I380" s="3"/>
       <c r="J380" s="3"/>
       <c r="K380" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -38572,7 +38694,7 @@
       <c r="I381" s="3"/>
       <c r="J381" s="3"/>
       <c r="K381" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -38588,7 +38710,7 @@
       <c r="I382" s="3"/>
       <c r="J382" s="3"/>
       <c r="K382" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -38604,7 +38726,7 @@
       <c r="I383" s="3"/>
       <c r="J383" s="3"/>
       <c r="K383" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -38620,7 +38742,7 @@
       <c r="I384" s="3"/>
       <c r="J384" s="3"/>
       <c r="K384" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -38636,7 +38758,7 @@
       <c r="I385" s="3"/>
       <c r="J385" s="3"/>
       <c r="K385" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -38652,7 +38774,7 @@
       <c r="I386" s="3"/>
       <c r="J386" s="3"/>
       <c r="K386" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -38668,7 +38790,7 @@
       <c r="I387" s="3"/>
       <c r="J387" s="3"/>
       <c r="K387" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -38684,7 +38806,7 @@
       <c r="I388" s="3"/>
       <c r="J388" s="3"/>
       <c r="K388" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -38700,7 +38822,7 @@
       <c r="I389" s="3"/>
       <c r="J389" s="3"/>
       <c r="K389" s="4" t="str">
-        <f t="shared" ref="K389:K390" si="12">IF(COUNTA(B389:J389)=0,"",AVERAGE(B389:J389))</f>
+        <f t="shared" ref="K389:K390" si="13">IF(COUNTA(B389:J389)=0,"",AVERAGE(B389:J389))</f>
         <v/>
       </c>
     </row>
@@ -38716,7 +38838,7 @@
       <c r="I390" s="3"/>
       <c r="J390" s="3"/>
       <c r="K390" s="4" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -38746,7 +38868,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="6" t="s">
         <v>39</v>
       </c>
       <c r="B1" s="7"/>
@@ -38762,7 +38884,7 @@
       <c r="L1" s="7"/>
     </row>
     <row r="2" spans="1:12" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="8" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="7"/>
@@ -40142,20 +40264,42 @@
       </c>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A39" s="2"/>
-      <c r="B39" s="3"/>
-      <c r="C39" s="3"/>
-      <c r="D39" s="3"/>
-      <c r="E39" s="3"/>
-      <c r="F39" s="3"/>
-      <c r="G39" s="3"/>
-      <c r="H39" s="3"/>
-      <c r="I39" s="3"/>
-      <c r="J39" s="3"/>
-      <c r="K39" s="3"/>
-      <c r="L39" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
+      <c r="A39" s="2">
+        <v>46178</v>
+      </c>
+      <c r="B39" s="3">
+        <v>3.59</v>
+      </c>
+      <c r="C39" s="3">
+        <v>3.19</v>
+      </c>
+      <c r="D39" s="3">
+        <v>3.59</v>
+      </c>
+      <c r="E39" s="3">
+        <v>3.35</v>
+      </c>
+      <c r="F39" s="3">
+        <v>3.43</v>
+      </c>
+      <c r="G39" s="3">
+        <v>3.69</v>
+      </c>
+      <c r="H39" s="3">
+        <v>3.11</v>
+      </c>
+      <c r="I39" s="3">
+        <v>3.29</v>
+      </c>
+      <c r="J39" s="3">
+        <v>3.46</v>
+      </c>
+      <c r="K39" s="3">
+        <v>3.29</v>
+      </c>
+      <c r="L39" s="4">
+        <f t="shared" ref="L39" si="7">IF(COUNTA(B39:K39)=0,"",AVERAGE(B39:K39))</f>
+        <v>3.399</v>
       </c>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.25">
@@ -40664,7 +40808,7 @@
       <c r="J69" s="3"/>
       <c r="K69" s="3"/>
       <c r="L69" s="4" t="str">
-        <f t="shared" ref="L69:L132" si="7">IF(COUNTA(B69:K69)=0,"",AVERAGE(B69:K69))</f>
+        <f t="shared" ref="L69:L132" si="8">IF(COUNTA(B69:K69)=0,"",AVERAGE(B69:K69))</f>
         <v/>
       </c>
     </row>
@@ -40681,7 +40825,7 @@
       <c r="J70" s="3"/>
       <c r="K70" s="3"/>
       <c r="L70" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -40698,7 +40842,7 @@
       <c r="J71" s="3"/>
       <c r="K71" s="3"/>
       <c r="L71" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -40715,7 +40859,7 @@
       <c r="J72" s="3"/>
       <c r="K72" s="3"/>
       <c r="L72" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -40732,7 +40876,7 @@
       <c r="J73" s="3"/>
       <c r="K73" s="3"/>
       <c r="L73" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -40749,7 +40893,7 @@
       <c r="J74" s="3"/>
       <c r="K74" s="3"/>
       <c r="L74" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -40766,7 +40910,7 @@
       <c r="J75" s="3"/>
       <c r="K75" s="3"/>
       <c r="L75" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -40783,7 +40927,7 @@
       <c r="J76" s="3"/>
       <c r="K76" s="3"/>
       <c r="L76" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -40800,7 +40944,7 @@
       <c r="J77" s="3"/>
       <c r="K77" s="3"/>
       <c r="L77" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -40817,7 +40961,7 @@
       <c r="J78" s="3"/>
       <c r="K78" s="3"/>
       <c r="L78" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -40834,7 +40978,7 @@
       <c r="J79" s="3"/>
       <c r="K79" s="3"/>
       <c r="L79" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -40851,7 +40995,7 @@
       <c r="J80" s="3"/>
       <c r="K80" s="3"/>
       <c r="L80" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -40868,7 +41012,7 @@
       <c r="J81" s="3"/>
       <c r="K81" s="3"/>
       <c r="L81" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -40885,7 +41029,7 @@
       <c r="J82" s="3"/>
       <c r="K82" s="3"/>
       <c r="L82" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -40902,7 +41046,7 @@
       <c r="J83" s="3"/>
       <c r="K83" s="3"/>
       <c r="L83" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -40919,7 +41063,7 @@
       <c r="J84" s="3"/>
       <c r="K84" s="3"/>
       <c r="L84" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -40936,7 +41080,7 @@
       <c r="J85" s="3"/>
       <c r="K85" s="3"/>
       <c r="L85" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -40953,7 +41097,7 @@
       <c r="J86" s="3"/>
       <c r="K86" s="3"/>
       <c r="L86" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -40970,7 +41114,7 @@
       <c r="J87" s="3"/>
       <c r="K87" s="3"/>
       <c r="L87" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -40987,7 +41131,7 @@
       <c r="J88" s="3"/>
       <c r="K88" s="3"/>
       <c r="L88" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -41004,7 +41148,7 @@
       <c r="J89" s="3"/>
       <c r="K89" s="3"/>
       <c r="L89" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -41021,7 +41165,7 @@
       <c r="J90" s="3"/>
       <c r="K90" s="3"/>
       <c r="L90" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -41038,7 +41182,7 @@
       <c r="J91" s="3"/>
       <c r="K91" s="3"/>
       <c r="L91" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -41055,7 +41199,7 @@
       <c r="J92" s="3"/>
       <c r="K92" s="3"/>
       <c r="L92" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -41072,7 +41216,7 @@
       <c r="J93" s="3"/>
       <c r="K93" s="3"/>
       <c r="L93" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -41089,7 +41233,7 @@
       <c r="J94" s="3"/>
       <c r="K94" s="3"/>
       <c r="L94" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -41106,7 +41250,7 @@
       <c r="J95" s="3"/>
       <c r="K95" s="3"/>
       <c r="L95" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -41123,7 +41267,7 @@
       <c r="J96" s="3"/>
       <c r="K96" s="3"/>
       <c r="L96" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -41140,7 +41284,7 @@
       <c r="J97" s="3"/>
       <c r="K97" s="3"/>
       <c r="L97" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -41157,7 +41301,7 @@
       <c r="J98" s="3"/>
       <c r="K98" s="3"/>
       <c r="L98" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -41174,7 +41318,7 @@
       <c r="J99" s="3"/>
       <c r="K99" s="3"/>
       <c r="L99" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -41191,7 +41335,7 @@
       <c r="J100" s="3"/>
       <c r="K100" s="3"/>
       <c r="L100" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -41208,7 +41352,7 @@
       <c r="J101" s="3"/>
       <c r="K101" s="3"/>
       <c r="L101" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -41225,7 +41369,7 @@
       <c r="J102" s="3"/>
       <c r="K102" s="3"/>
       <c r="L102" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -41242,7 +41386,7 @@
       <c r="J103" s="3"/>
       <c r="K103" s="3"/>
       <c r="L103" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -41259,7 +41403,7 @@
       <c r="J104" s="3"/>
       <c r="K104" s="3"/>
       <c r="L104" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -41276,7 +41420,7 @@
       <c r="J105" s="3"/>
       <c r="K105" s="3"/>
       <c r="L105" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -41293,7 +41437,7 @@
       <c r="J106" s="3"/>
       <c r="K106" s="3"/>
       <c r="L106" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -41310,7 +41454,7 @@
       <c r="J107" s="3"/>
       <c r="K107" s="3"/>
       <c r="L107" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -41327,7 +41471,7 @@
       <c r="J108" s="3"/>
       <c r="K108" s="3"/>
       <c r="L108" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -41344,7 +41488,7 @@
       <c r="J109" s="3"/>
       <c r="K109" s="3"/>
       <c r="L109" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -41361,7 +41505,7 @@
       <c r="J110" s="3"/>
       <c r="K110" s="3"/>
       <c r="L110" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -41378,7 +41522,7 @@
       <c r="J111" s="3"/>
       <c r="K111" s="3"/>
       <c r="L111" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -41395,7 +41539,7 @@
       <c r="J112" s="3"/>
       <c r="K112" s="3"/>
       <c r="L112" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -41412,7 +41556,7 @@
       <c r="J113" s="3"/>
       <c r="K113" s="3"/>
       <c r="L113" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -41429,7 +41573,7 @@
       <c r="J114" s="3"/>
       <c r="K114" s="3"/>
       <c r="L114" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -41446,7 +41590,7 @@
       <c r="J115" s="3"/>
       <c r="K115" s="3"/>
       <c r="L115" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -41463,7 +41607,7 @@
       <c r="J116" s="3"/>
       <c r="K116" s="3"/>
       <c r="L116" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -41480,7 +41624,7 @@
       <c r="J117" s="3"/>
       <c r="K117" s="3"/>
       <c r="L117" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -41497,7 +41641,7 @@
       <c r="J118" s="3"/>
       <c r="K118" s="3"/>
       <c r="L118" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -41514,7 +41658,7 @@
       <c r="J119" s="3"/>
       <c r="K119" s="3"/>
       <c r="L119" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -41531,7 +41675,7 @@
       <c r="J120" s="3"/>
       <c r="K120" s="3"/>
       <c r="L120" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -41548,7 +41692,7 @@
       <c r="J121" s="3"/>
       <c r="K121" s="3"/>
       <c r="L121" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -41565,7 +41709,7 @@
       <c r="J122" s="3"/>
       <c r="K122" s="3"/>
       <c r="L122" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -41582,7 +41726,7 @@
       <c r="J123" s="3"/>
       <c r="K123" s="3"/>
       <c r="L123" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -41599,7 +41743,7 @@
       <c r="J124" s="3"/>
       <c r="K124" s="3"/>
       <c r="L124" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -41616,7 +41760,7 @@
       <c r="J125" s="3"/>
       <c r="K125" s="3"/>
       <c r="L125" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -41633,7 +41777,7 @@
       <c r="J126" s="3"/>
       <c r="K126" s="3"/>
       <c r="L126" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -41650,7 +41794,7 @@
       <c r="J127" s="3"/>
       <c r="K127" s="3"/>
       <c r="L127" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -41667,7 +41811,7 @@
       <c r="J128" s="3"/>
       <c r="K128" s="3"/>
       <c r="L128" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -41684,7 +41828,7 @@
       <c r="J129" s="3"/>
       <c r="K129" s="3"/>
       <c r="L129" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -41701,7 +41845,7 @@
       <c r="J130" s="3"/>
       <c r="K130" s="3"/>
       <c r="L130" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -41718,7 +41862,7 @@
       <c r="J131" s="3"/>
       <c r="K131" s="3"/>
       <c r="L131" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -41735,7 +41879,7 @@
       <c r="J132" s="3"/>
       <c r="K132" s="3"/>
       <c r="L132" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -41752,7 +41896,7 @@
       <c r="J133" s="3"/>
       <c r="K133" s="3"/>
       <c r="L133" s="4" t="str">
-        <f t="shared" ref="L133:L196" si="8">IF(COUNTA(B133:K133)=0,"",AVERAGE(B133:K133))</f>
+        <f t="shared" ref="L133:L196" si="9">IF(COUNTA(B133:K133)=0,"",AVERAGE(B133:K133))</f>
         <v/>
       </c>
     </row>
@@ -41769,7 +41913,7 @@
       <c r="J134" s="3"/>
       <c r="K134" s="3"/>
       <c r="L134" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -41786,7 +41930,7 @@
       <c r="J135" s="3"/>
       <c r="K135" s="3"/>
       <c r="L135" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -41803,7 +41947,7 @@
       <c r="J136" s="3"/>
       <c r="K136" s="3"/>
       <c r="L136" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -41820,7 +41964,7 @@
       <c r="J137" s="3"/>
       <c r="K137" s="3"/>
       <c r="L137" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -41837,7 +41981,7 @@
       <c r="J138" s="3"/>
       <c r="K138" s="3"/>
       <c r="L138" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -41854,7 +41998,7 @@
       <c r="J139" s="3"/>
       <c r="K139" s="3"/>
       <c r="L139" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -41871,7 +42015,7 @@
       <c r="J140" s="3"/>
       <c r="K140" s="3"/>
       <c r="L140" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -41888,7 +42032,7 @@
       <c r="J141" s="3"/>
       <c r="K141" s="3"/>
       <c r="L141" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -41905,7 +42049,7 @@
       <c r="J142" s="3"/>
       <c r="K142" s="3"/>
       <c r="L142" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -41922,7 +42066,7 @@
       <c r="J143" s="3"/>
       <c r="K143" s="3"/>
       <c r="L143" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -41939,7 +42083,7 @@
       <c r="J144" s="3"/>
       <c r="K144" s="3"/>
       <c r="L144" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -41956,7 +42100,7 @@
       <c r="J145" s="3"/>
       <c r="K145" s="3"/>
       <c r="L145" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -41973,7 +42117,7 @@
       <c r="J146" s="3"/>
       <c r="K146" s="3"/>
       <c r="L146" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -41990,7 +42134,7 @@
       <c r="J147" s="3"/>
       <c r="K147" s="3"/>
       <c r="L147" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -42007,7 +42151,7 @@
       <c r="J148" s="3"/>
       <c r="K148" s="3"/>
       <c r="L148" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -42024,7 +42168,7 @@
       <c r="J149" s="3"/>
       <c r="K149" s="3"/>
       <c r="L149" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -42041,7 +42185,7 @@
       <c r="J150" s="3"/>
       <c r="K150" s="3"/>
       <c r="L150" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -42058,7 +42202,7 @@
       <c r="J151" s="3"/>
       <c r="K151" s="3"/>
       <c r="L151" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -42075,7 +42219,7 @@
       <c r="J152" s="3"/>
       <c r="K152" s="3"/>
       <c r="L152" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -42092,7 +42236,7 @@
       <c r="J153" s="3"/>
       <c r="K153" s="3"/>
       <c r="L153" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -42109,7 +42253,7 @@
       <c r="J154" s="3"/>
       <c r="K154" s="3"/>
       <c r="L154" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -42126,7 +42270,7 @@
       <c r="J155" s="3"/>
       <c r="K155" s="3"/>
       <c r="L155" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -42143,7 +42287,7 @@
       <c r="J156" s="3"/>
       <c r="K156" s="3"/>
       <c r="L156" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -42160,7 +42304,7 @@
       <c r="J157" s="3"/>
       <c r="K157" s="3"/>
       <c r="L157" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -42177,7 +42321,7 @@
       <c r="J158" s="3"/>
       <c r="K158" s="3"/>
       <c r="L158" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -42194,7 +42338,7 @@
       <c r="J159" s="3"/>
       <c r="K159" s="3"/>
       <c r="L159" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -42211,7 +42355,7 @@
       <c r="J160" s="3"/>
       <c r="K160" s="3"/>
       <c r="L160" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -42228,7 +42372,7 @@
       <c r="J161" s="3"/>
       <c r="K161" s="3"/>
       <c r="L161" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -42245,7 +42389,7 @@
       <c r="J162" s="3"/>
       <c r="K162" s="3"/>
       <c r="L162" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -42262,7 +42406,7 @@
       <c r="J163" s="3"/>
       <c r="K163" s="3"/>
       <c r="L163" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -42279,7 +42423,7 @@
       <c r="J164" s="3"/>
       <c r="K164" s="3"/>
       <c r="L164" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -42296,7 +42440,7 @@
       <c r="J165" s="3"/>
       <c r="K165" s="3"/>
       <c r="L165" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -42313,7 +42457,7 @@
       <c r="J166" s="3"/>
       <c r="K166" s="3"/>
       <c r="L166" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -42330,7 +42474,7 @@
       <c r="J167" s="3"/>
       <c r="K167" s="3"/>
       <c r="L167" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -42347,7 +42491,7 @@
       <c r="J168" s="3"/>
       <c r="K168" s="3"/>
       <c r="L168" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -42364,7 +42508,7 @@
       <c r="J169" s="3"/>
       <c r="K169" s="3"/>
       <c r="L169" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -42381,7 +42525,7 @@
       <c r="J170" s="3"/>
       <c r="K170" s="3"/>
       <c r="L170" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -42398,7 +42542,7 @@
       <c r="J171" s="3"/>
       <c r="K171" s="3"/>
       <c r="L171" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -42415,7 +42559,7 @@
       <c r="J172" s="3"/>
       <c r="K172" s="3"/>
       <c r="L172" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -42432,7 +42576,7 @@
       <c r="J173" s="3"/>
       <c r="K173" s="3"/>
       <c r="L173" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -42449,7 +42593,7 @@
       <c r="J174" s="3"/>
       <c r="K174" s="3"/>
       <c r="L174" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -42466,7 +42610,7 @@
       <c r="J175" s="3"/>
       <c r="K175" s="3"/>
       <c r="L175" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -42483,7 +42627,7 @@
       <c r="J176" s="3"/>
       <c r="K176" s="3"/>
       <c r="L176" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -42500,7 +42644,7 @@
       <c r="J177" s="3"/>
       <c r="K177" s="3"/>
       <c r="L177" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -42517,7 +42661,7 @@
       <c r="J178" s="3"/>
       <c r="K178" s="3"/>
       <c r="L178" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -42534,7 +42678,7 @@
       <c r="J179" s="3"/>
       <c r="K179" s="3"/>
       <c r="L179" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -42551,7 +42695,7 @@
       <c r="J180" s="3"/>
       <c r="K180" s="3"/>
       <c r="L180" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -42568,7 +42712,7 @@
       <c r="J181" s="3"/>
       <c r="K181" s="3"/>
       <c r="L181" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -42585,7 +42729,7 @@
       <c r="J182" s="3"/>
       <c r="K182" s="3"/>
       <c r="L182" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -42602,7 +42746,7 @@
       <c r="J183" s="3"/>
       <c r="K183" s="3"/>
       <c r="L183" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -42619,7 +42763,7 @@
       <c r="J184" s="3"/>
       <c r="K184" s="3"/>
       <c r="L184" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -42636,7 +42780,7 @@
       <c r="J185" s="3"/>
       <c r="K185" s="3"/>
       <c r="L185" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -42653,7 +42797,7 @@
       <c r="J186" s="3"/>
       <c r="K186" s="3"/>
       <c r="L186" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -42670,7 +42814,7 @@
       <c r="J187" s="3"/>
       <c r="K187" s="3"/>
       <c r="L187" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -42687,7 +42831,7 @@
       <c r="J188" s="3"/>
       <c r="K188" s="3"/>
       <c r="L188" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -42704,7 +42848,7 @@
       <c r="J189" s="3"/>
       <c r="K189" s="3"/>
       <c r="L189" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -42721,7 +42865,7 @@
       <c r="J190" s="3"/>
       <c r="K190" s="3"/>
       <c r="L190" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -42738,7 +42882,7 @@
       <c r="J191" s="3"/>
       <c r="K191" s="3"/>
       <c r="L191" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -42755,7 +42899,7 @@
       <c r="J192" s="3"/>
       <c r="K192" s="3"/>
       <c r="L192" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -42772,7 +42916,7 @@
       <c r="J193" s="3"/>
       <c r="K193" s="3"/>
       <c r="L193" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -42789,7 +42933,7 @@
       <c r="J194" s="3"/>
       <c r="K194" s="3"/>
       <c r="L194" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -42806,7 +42950,7 @@
       <c r="J195" s="3"/>
       <c r="K195" s="3"/>
       <c r="L195" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -42823,7 +42967,7 @@
       <c r="J196" s="3"/>
       <c r="K196" s="3"/>
       <c r="L196" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -42840,7 +42984,7 @@
       <c r="J197" s="3"/>
       <c r="K197" s="3"/>
       <c r="L197" s="4" t="str">
-        <f t="shared" ref="L197:L260" si="9">IF(COUNTA(B197:K197)=0,"",AVERAGE(B197:K197))</f>
+        <f t="shared" ref="L197:L260" si="10">IF(COUNTA(B197:K197)=0,"",AVERAGE(B197:K197))</f>
         <v/>
       </c>
     </row>
@@ -42857,7 +43001,7 @@
       <c r="J198" s="3"/>
       <c r="K198" s="3"/>
       <c r="L198" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -42874,7 +43018,7 @@
       <c r="J199" s="3"/>
       <c r="K199" s="3"/>
       <c r="L199" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -42891,7 +43035,7 @@
       <c r="J200" s="3"/>
       <c r="K200" s="3"/>
       <c r="L200" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -42908,7 +43052,7 @@
       <c r="J201" s="3"/>
       <c r="K201" s="3"/>
       <c r="L201" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -42925,7 +43069,7 @@
       <c r="J202" s="3"/>
       <c r="K202" s="3"/>
       <c r="L202" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -42942,7 +43086,7 @@
       <c r="J203" s="3"/>
       <c r="K203" s="3"/>
       <c r="L203" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -42959,7 +43103,7 @@
       <c r="J204" s="3"/>
       <c r="K204" s="3"/>
       <c r="L204" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -42976,7 +43120,7 @@
       <c r="J205" s="3"/>
       <c r="K205" s="3"/>
       <c r="L205" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -42993,7 +43137,7 @@
       <c r="J206" s="3"/>
       <c r="K206" s="3"/>
       <c r="L206" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -43010,7 +43154,7 @@
       <c r="J207" s="3"/>
       <c r="K207" s="3"/>
       <c r="L207" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -43027,7 +43171,7 @@
       <c r="J208" s="3"/>
       <c r="K208" s="3"/>
       <c r="L208" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -43044,7 +43188,7 @@
       <c r="J209" s="3"/>
       <c r="K209" s="3"/>
       <c r="L209" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -43061,7 +43205,7 @@
       <c r="J210" s="3"/>
       <c r="K210" s="3"/>
       <c r="L210" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -43078,7 +43222,7 @@
       <c r="J211" s="3"/>
       <c r="K211" s="3"/>
       <c r="L211" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -43095,7 +43239,7 @@
       <c r="J212" s="3"/>
       <c r="K212" s="3"/>
       <c r="L212" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -43112,7 +43256,7 @@
       <c r="J213" s="3"/>
       <c r="K213" s="3"/>
       <c r="L213" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -43129,7 +43273,7 @@
       <c r="J214" s="3"/>
       <c r="K214" s="3"/>
       <c r="L214" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -43146,7 +43290,7 @@
       <c r="J215" s="3"/>
       <c r="K215" s="3"/>
       <c r="L215" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -43163,7 +43307,7 @@
       <c r="J216" s="3"/>
       <c r="K216" s="3"/>
       <c r="L216" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -43180,7 +43324,7 @@
       <c r="J217" s="3"/>
       <c r="K217" s="3"/>
       <c r="L217" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -43197,7 +43341,7 @@
       <c r="J218" s="3"/>
       <c r="K218" s="3"/>
       <c r="L218" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -43214,7 +43358,7 @@
       <c r="J219" s="3"/>
       <c r="K219" s="3"/>
       <c r="L219" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -43231,7 +43375,7 @@
       <c r="J220" s="3"/>
       <c r="K220" s="3"/>
       <c r="L220" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -43248,7 +43392,7 @@
       <c r="J221" s="3"/>
       <c r="K221" s="3"/>
       <c r="L221" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -43265,7 +43409,7 @@
       <c r="J222" s="3"/>
       <c r="K222" s="3"/>
       <c r="L222" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -43282,7 +43426,7 @@
       <c r="J223" s="3"/>
       <c r="K223" s="3"/>
       <c r="L223" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -43299,7 +43443,7 @@
       <c r="J224" s="3"/>
       <c r="K224" s="3"/>
       <c r="L224" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -43316,7 +43460,7 @@
       <c r="J225" s="3"/>
       <c r="K225" s="3"/>
       <c r="L225" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -43333,7 +43477,7 @@
       <c r="J226" s="3"/>
       <c r="K226" s="3"/>
       <c r="L226" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -43350,7 +43494,7 @@
       <c r="J227" s="3"/>
       <c r="K227" s="3"/>
       <c r="L227" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -43367,7 +43511,7 @@
       <c r="J228" s="3"/>
       <c r="K228" s="3"/>
       <c r="L228" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -43384,7 +43528,7 @@
       <c r="J229" s="3"/>
       <c r="K229" s="3"/>
       <c r="L229" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -43401,7 +43545,7 @@
       <c r="J230" s="3"/>
       <c r="K230" s="3"/>
       <c r="L230" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -43418,7 +43562,7 @@
       <c r="J231" s="3"/>
       <c r="K231" s="3"/>
       <c r="L231" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -43435,7 +43579,7 @@
       <c r="J232" s="3"/>
       <c r="K232" s="3"/>
       <c r="L232" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -43452,7 +43596,7 @@
       <c r="J233" s="3"/>
       <c r="K233" s="3"/>
       <c r="L233" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -43469,7 +43613,7 @@
       <c r="J234" s="3"/>
       <c r="K234" s="3"/>
       <c r="L234" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -43486,7 +43630,7 @@
       <c r="J235" s="3"/>
       <c r="K235" s="3"/>
       <c r="L235" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -43503,7 +43647,7 @@
       <c r="J236" s="3"/>
       <c r="K236" s="3"/>
       <c r="L236" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -43520,7 +43664,7 @@
       <c r="J237" s="3"/>
       <c r="K237" s="3"/>
       <c r="L237" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -43537,7 +43681,7 @@
       <c r="J238" s="3"/>
       <c r="K238" s="3"/>
       <c r="L238" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -43554,7 +43698,7 @@
       <c r="J239" s="3"/>
       <c r="K239" s="3"/>
       <c r="L239" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -43571,7 +43715,7 @@
       <c r="J240" s="3"/>
       <c r="K240" s="3"/>
       <c r="L240" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -43588,7 +43732,7 @@
       <c r="J241" s="3"/>
       <c r="K241" s="3"/>
       <c r="L241" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -43605,7 +43749,7 @@
       <c r="J242" s="3"/>
       <c r="K242" s="3"/>
       <c r="L242" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -43622,7 +43766,7 @@
       <c r="J243" s="3"/>
       <c r="K243" s="3"/>
       <c r="L243" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -43639,7 +43783,7 @@
       <c r="J244" s="3"/>
       <c r="K244" s="3"/>
       <c r="L244" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -43656,7 +43800,7 @@
       <c r="J245" s="3"/>
       <c r="K245" s="3"/>
       <c r="L245" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -43673,7 +43817,7 @@
       <c r="J246" s="3"/>
       <c r="K246" s="3"/>
       <c r="L246" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -43690,7 +43834,7 @@
       <c r="J247" s="3"/>
       <c r="K247" s="3"/>
       <c r="L247" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -43707,7 +43851,7 @@
       <c r="J248" s="3"/>
       <c r="K248" s="3"/>
       <c r="L248" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -43724,7 +43868,7 @@
       <c r="J249" s="3"/>
       <c r="K249" s="3"/>
       <c r="L249" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -43741,7 +43885,7 @@
       <c r="J250" s="3"/>
       <c r="K250" s="3"/>
       <c r="L250" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -43758,7 +43902,7 @@
       <c r="J251" s="3"/>
       <c r="K251" s="3"/>
       <c r="L251" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -43775,7 +43919,7 @@
       <c r="J252" s="3"/>
       <c r="K252" s="3"/>
       <c r="L252" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -43792,7 +43936,7 @@
       <c r="J253" s="3"/>
       <c r="K253" s="3"/>
       <c r="L253" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -43809,7 +43953,7 @@
       <c r="J254" s="3"/>
       <c r="K254" s="3"/>
       <c r="L254" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -43826,7 +43970,7 @@
       <c r="J255" s="3"/>
       <c r="K255" s="3"/>
       <c r="L255" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -43843,7 +43987,7 @@
       <c r="J256" s="3"/>
       <c r="K256" s="3"/>
       <c r="L256" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -43860,7 +44004,7 @@
       <c r="J257" s="3"/>
       <c r="K257" s="3"/>
       <c r="L257" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -43877,7 +44021,7 @@
       <c r="J258" s="3"/>
       <c r="K258" s="3"/>
       <c r="L258" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -43894,7 +44038,7 @@
       <c r="J259" s="3"/>
       <c r="K259" s="3"/>
       <c r="L259" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -43911,7 +44055,7 @@
       <c r="J260" s="3"/>
       <c r="K260" s="3"/>
       <c r="L260" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -43928,7 +44072,7 @@
       <c r="J261" s="3"/>
       <c r="K261" s="3"/>
       <c r="L261" s="4" t="str">
-        <f t="shared" ref="L261:L324" si="10">IF(COUNTA(B261:K261)=0,"",AVERAGE(B261:K261))</f>
+        <f t="shared" ref="L261:L324" si="11">IF(COUNTA(B261:K261)=0,"",AVERAGE(B261:K261))</f>
         <v/>
       </c>
     </row>
@@ -43945,7 +44089,7 @@
       <c r="J262" s="3"/>
       <c r="K262" s="3"/>
       <c r="L262" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -43962,7 +44106,7 @@
       <c r="J263" s="3"/>
       <c r="K263" s="3"/>
       <c r="L263" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -43979,7 +44123,7 @@
       <c r="J264" s="3"/>
       <c r="K264" s="3"/>
       <c r="L264" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -43996,7 +44140,7 @@
       <c r="J265" s="3"/>
       <c r="K265" s="3"/>
       <c r="L265" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -44013,7 +44157,7 @@
       <c r="J266" s="3"/>
       <c r="K266" s="3"/>
       <c r="L266" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -44030,7 +44174,7 @@
       <c r="J267" s="3"/>
       <c r="K267" s="3"/>
       <c r="L267" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -44047,7 +44191,7 @@
       <c r="J268" s="3"/>
       <c r="K268" s="3"/>
       <c r="L268" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -44064,7 +44208,7 @@
       <c r="J269" s="3"/>
       <c r="K269" s="3"/>
       <c r="L269" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -44081,7 +44225,7 @@
       <c r="J270" s="3"/>
       <c r="K270" s="3"/>
       <c r="L270" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -44098,7 +44242,7 @@
       <c r="J271" s="3"/>
       <c r="K271" s="3"/>
       <c r="L271" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -44115,7 +44259,7 @@
       <c r="J272" s="3"/>
       <c r="K272" s="3"/>
       <c r="L272" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -44132,7 +44276,7 @@
       <c r="J273" s="3"/>
       <c r="K273" s="3"/>
       <c r="L273" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -44149,7 +44293,7 @@
       <c r="J274" s="3"/>
       <c r="K274" s="3"/>
       <c r="L274" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -44166,7 +44310,7 @@
       <c r="J275" s="3"/>
       <c r="K275" s="3"/>
       <c r="L275" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -44183,7 +44327,7 @@
       <c r="J276" s="3"/>
       <c r="K276" s="3"/>
       <c r="L276" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -44200,7 +44344,7 @@
       <c r="J277" s="3"/>
       <c r="K277" s="3"/>
       <c r="L277" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -44217,7 +44361,7 @@
       <c r="J278" s="3"/>
       <c r="K278" s="3"/>
       <c r="L278" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -44234,7 +44378,7 @@
       <c r="J279" s="3"/>
       <c r="K279" s="3"/>
       <c r="L279" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -44251,7 +44395,7 @@
       <c r="J280" s="3"/>
       <c r="K280" s="3"/>
       <c r="L280" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -44268,7 +44412,7 @@
       <c r="J281" s="3"/>
       <c r="K281" s="3"/>
       <c r="L281" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -44285,7 +44429,7 @@
       <c r="J282" s="3"/>
       <c r="K282" s="3"/>
       <c r="L282" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -44302,7 +44446,7 @@
       <c r="J283" s="3"/>
       <c r="K283" s="3"/>
       <c r="L283" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -44319,7 +44463,7 @@
       <c r="J284" s="3"/>
       <c r="K284" s="3"/>
       <c r="L284" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -44336,7 +44480,7 @@
       <c r="J285" s="3"/>
       <c r="K285" s="3"/>
       <c r="L285" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -44353,7 +44497,7 @@
       <c r="J286" s="3"/>
       <c r="K286" s="3"/>
       <c r="L286" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -44370,7 +44514,7 @@
       <c r="J287" s="3"/>
       <c r="K287" s="3"/>
       <c r="L287" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -44387,7 +44531,7 @@
       <c r="J288" s="3"/>
       <c r="K288" s="3"/>
       <c r="L288" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -44404,7 +44548,7 @@
       <c r="J289" s="3"/>
       <c r="K289" s="3"/>
       <c r="L289" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -44421,7 +44565,7 @@
       <c r="J290" s="3"/>
       <c r="K290" s="3"/>
       <c r="L290" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -44438,7 +44582,7 @@
       <c r="J291" s="3"/>
       <c r="K291" s="3"/>
       <c r="L291" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -44455,7 +44599,7 @@
       <c r="J292" s="3"/>
       <c r="K292" s="3"/>
       <c r="L292" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -44472,7 +44616,7 @@
       <c r="J293" s="3"/>
       <c r="K293" s="3"/>
       <c r="L293" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -44489,7 +44633,7 @@
       <c r="J294" s="3"/>
       <c r="K294" s="3"/>
       <c r="L294" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -44506,7 +44650,7 @@
       <c r="J295" s="3"/>
       <c r="K295" s="3"/>
       <c r="L295" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -44523,7 +44667,7 @@
       <c r="J296" s="3"/>
       <c r="K296" s="3"/>
       <c r="L296" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -44540,7 +44684,7 @@
       <c r="J297" s="3"/>
       <c r="K297" s="3"/>
       <c r="L297" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -44557,7 +44701,7 @@
       <c r="J298" s="3"/>
       <c r="K298" s="3"/>
       <c r="L298" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -44574,7 +44718,7 @@
       <c r="J299" s="3"/>
       <c r="K299" s="3"/>
       <c r="L299" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -44591,7 +44735,7 @@
       <c r="J300" s="3"/>
       <c r="K300" s="3"/>
       <c r="L300" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -44608,7 +44752,7 @@
       <c r="J301" s="3"/>
       <c r="K301" s="3"/>
       <c r="L301" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -44625,7 +44769,7 @@
       <c r="J302" s="3"/>
       <c r="K302" s="3"/>
       <c r="L302" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -44642,7 +44786,7 @@
       <c r="J303" s="3"/>
       <c r="K303" s="3"/>
       <c r="L303" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -44659,7 +44803,7 @@
       <c r="J304" s="3"/>
       <c r="K304" s="3"/>
       <c r="L304" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -44676,7 +44820,7 @@
       <c r="J305" s="3"/>
       <c r="K305" s="3"/>
       <c r="L305" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -44693,7 +44837,7 @@
       <c r="J306" s="3"/>
       <c r="K306" s="3"/>
       <c r="L306" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -44710,7 +44854,7 @@
       <c r="J307" s="3"/>
       <c r="K307" s="3"/>
       <c r="L307" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -44727,7 +44871,7 @@
       <c r="J308" s="3"/>
       <c r="K308" s="3"/>
       <c r="L308" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -44744,7 +44888,7 @@
       <c r="J309" s="3"/>
       <c r="K309" s="3"/>
       <c r="L309" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -44761,7 +44905,7 @@
       <c r="J310" s="3"/>
       <c r="K310" s="3"/>
       <c r="L310" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -44778,7 +44922,7 @@
       <c r="J311" s="3"/>
       <c r="K311" s="3"/>
       <c r="L311" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -44795,7 +44939,7 @@
       <c r="J312" s="3"/>
       <c r="K312" s="3"/>
       <c r="L312" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -44812,7 +44956,7 @@
       <c r="J313" s="3"/>
       <c r="K313" s="3"/>
       <c r="L313" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -44829,7 +44973,7 @@
       <c r="J314" s="3"/>
       <c r="K314" s="3"/>
       <c r="L314" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -44846,7 +44990,7 @@
       <c r="J315" s="3"/>
       <c r="K315" s="3"/>
       <c r="L315" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -44863,7 +45007,7 @@
       <c r="J316" s="3"/>
       <c r="K316" s="3"/>
       <c r="L316" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -44880,7 +45024,7 @@
       <c r="J317" s="3"/>
       <c r="K317" s="3"/>
       <c r="L317" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -44897,7 +45041,7 @@
       <c r="J318" s="3"/>
       <c r="K318" s="3"/>
       <c r="L318" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -44914,7 +45058,7 @@
       <c r="J319" s="3"/>
       <c r="K319" s="3"/>
       <c r="L319" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -44931,7 +45075,7 @@
       <c r="J320" s="3"/>
       <c r="K320" s="3"/>
       <c r="L320" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -44948,7 +45092,7 @@
       <c r="J321" s="3"/>
       <c r="K321" s="3"/>
       <c r="L321" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -44965,7 +45109,7 @@
       <c r="J322" s="3"/>
       <c r="K322" s="3"/>
       <c r="L322" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -44982,7 +45126,7 @@
       <c r="J323" s="3"/>
       <c r="K323" s="3"/>
       <c r="L323" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -44999,7 +45143,7 @@
       <c r="J324" s="3"/>
       <c r="K324" s="3"/>
       <c r="L324" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -45016,7 +45160,7 @@
       <c r="J325" s="3"/>
       <c r="K325" s="3"/>
       <c r="L325" s="4" t="str">
-        <f t="shared" ref="L325:L388" si="11">IF(COUNTA(B325:K325)=0,"",AVERAGE(B325:K325))</f>
+        <f t="shared" ref="L325:L388" si="12">IF(COUNTA(B325:K325)=0,"",AVERAGE(B325:K325))</f>
         <v/>
       </c>
     </row>
@@ -45033,7 +45177,7 @@
       <c r="J326" s="3"/>
       <c r="K326" s="3"/>
       <c r="L326" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -45050,7 +45194,7 @@
       <c r="J327" s="3"/>
       <c r="K327" s="3"/>
       <c r="L327" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -45067,7 +45211,7 @@
       <c r="J328" s="3"/>
       <c r="K328" s="3"/>
       <c r="L328" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -45084,7 +45228,7 @@
       <c r="J329" s="3"/>
       <c r="K329" s="3"/>
       <c r="L329" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -45101,7 +45245,7 @@
       <c r="J330" s="3"/>
       <c r="K330" s="3"/>
       <c r="L330" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -45118,7 +45262,7 @@
       <c r="J331" s="3"/>
       <c r="K331" s="3"/>
       <c r="L331" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -45135,7 +45279,7 @@
       <c r="J332" s="3"/>
       <c r="K332" s="3"/>
       <c r="L332" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -45152,7 +45296,7 @@
       <c r="J333" s="3"/>
       <c r="K333" s="3"/>
       <c r="L333" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -45169,7 +45313,7 @@
       <c r="J334" s="3"/>
       <c r="K334" s="3"/>
       <c r="L334" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -45186,7 +45330,7 @@
       <c r="J335" s="3"/>
       <c r="K335" s="3"/>
       <c r="L335" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -45203,7 +45347,7 @@
       <c r="J336" s="3"/>
       <c r="K336" s="3"/>
       <c r="L336" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -45220,7 +45364,7 @@
       <c r="J337" s="3"/>
       <c r="K337" s="3"/>
       <c r="L337" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -45237,7 +45381,7 @@
       <c r="J338" s="3"/>
       <c r="K338" s="3"/>
       <c r="L338" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -45254,7 +45398,7 @@
       <c r="J339" s="3"/>
       <c r="K339" s="3"/>
       <c r="L339" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -45271,7 +45415,7 @@
       <c r="J340" s="3"/>
       <c r="K340" s="3"/>
       <c r="L340" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -45288,7 +45432,7 @@
       <c r="J341" s="3"/>
       <c r="K341" s="3"/>
       <c r="L341" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -45305,7 +45449,7 @@
       <c r="J342" s="3"/>
       <c r="K342" s="3"/>
       <c r="L342" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -45322,7 +45466,7 @@
       <c r="J343" s="3"/>
       <c r="K343" s="3"/>
       <c r="L343" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -45339,7 +45483,7 @@
       <c r="J344" s="3"/>
       <c r="K344" s="3"/>
       <c r="L344" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -45356,7 +45500,7 @@
       <c r="J345" s="3"/>
       <c r="K345" s="3"/>
       <c r="L345" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -45373,7 +45517,7 @@
       <c r="J346" s="3"/>
       <c r="K346" s="3"/>
       <c r="L346" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -45390,7 +45534,7 @@
       <c r="J347" s="3"/>
       <c r="K347" s="3"/>
       <c r="L347" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -45407,7 +45551,7 @@
       <c r="J348" s="3"/>
       <c r="K348" s="3"/>
       <c r="L348" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -45424,7 +45568,7 @@
       <c r="J349" s="3"/>
       <c r="K349" s="3"/>
       <c r="L349" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -45441,7 +45585,7 @@
       <c r="J350" s="3"/>
       <c r="K350" s="3"/>
       <c r="L350" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -45458,7 +45602,7 @@
       <c r="J351" s="3"/>
       <c r="K351" s="3"/>
       <c r="L351" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -45475,7 +45619,7 @@
       <c r="J352" s="3"/>
       <c r="K352" s="3"/>
       <c r="L352" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -45492,7 +45636,7 @@
       <c r="J353" s="3"/>
       <c r="K353" s="3"/>
       <c r="L353" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -45509,7 +45653,7 @@
       <c r="J354" s="3"/>
       <c r="K354" s="3"/>
       <c r="L354" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -45526,7 +45670,7 @@
       <c r="J355" s="3"/>
       <c r="K355" s="3"/>
       <c r="L355" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -45543,7 +45687,7 @@
       <c r="J356" s="3"/>
       <c r="K356" s="3"/>
       <c r="L356" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -45560,7 +45704,7 @@
       <c r="J357" s="3"/>
       <c r="K357" s="3"/>
       <c r="L357" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -45577,7 +45721,7 @@
       <c r="J358" s="3"/>
       <c r="K358" s="3"/>
       <c r="L358" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -45594,7 +45738,7 @@
       <c r="J359" s="3"/>
       <c r="K359" s="3"/>
       <c r="L359" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -45611,7 +45755,7 @@
       <c r="J360" s="3"/>
       <c r="K360" s="3"/>
       <c r="L360" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -45628,7 +45772,7 @@
       <c r="J361" s="3"/>
       <c r="K361" s="3"/>
       <c r="L361" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -45645,7 +45789,7 @@
       <c r="J362" s="3"/>
       <c r="K362" s="3"/>
       <c r="L362" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -45662,7 +45806,7 @@
       <c r="J363" s="3"/>
       <c r="K363" s="3"/>
       <c r="L363" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -45679,7 +45823,7 @@
       <c r="J364" s="3"/>
       <c r="K364" s="3"/>
       <c r="L364" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -45696,7 +45840,7 @@
       <c r="J365" s="3"/>
       <c r="K365" s="3"/>
       <c r="L365" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -45713,7 +45857,7 @@
       <c r="J366" s="3"/>
       <c r="K366" s="3"/>
       <c r="L366" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -45730,7 +45874,7 @@
       <c r="J367" s="3"/>
       <c r="K367" s="3"/>
       <c r="L367" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -45747,7 +45891,7 @@
       <c r="J368" s="3"/>
       <c r="K368" s="3"/>
       <c r="L368" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -45764,7 +45908,7 @@
       <c r="J369" s="3"/>
       <c r="K369" s="3"/>
       <c r="L369" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -45781,7 +45925,7 @@
       <c r="J370" s="3"/>
       <c r="K370" s="3"/>
       <c r="L370" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -45798,7 +45942,7 @@
       <c r="J371" s="3"/>
       <c r="K371" s="3"/>
       <c r="L371" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -45815,7 +45959,7 @@
       <c r="J372" s="3"/>
       <c r="K372" s="3"/>
       <c r="L372" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -45832,7 +45976,7 @@
       <c r="J373" s="3"/>
       <c r="K373" s="3"/>
       <c r="L373" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -45849,7 +45993,7 @@
       <c r="J374" s="3"/>
       <c r="K374" s="3"/>
       <c r="L374" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -45866,7 +46010,7 @@
       <c r="J375" s="3"/>
       <c r="K375" s="3"/>
       <c r="L375" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -45883,7 +46027,7 @@
       <c r="J376" s="3"/>
       <c r="K376" s="3"/>
       <c r="L376" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -45900,7 +46044,7 @@
       <c r="J377" s="3"/>
       <c r="K377" s="3"/>
       <c r="L377" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -45917,7 +46061,7 @@
       <c r="J378" s="3"/>
       <c r="K378" s="3"/>
       <c r="L378" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -45934,7 +46078,7 @@
       <c r="J379" s="3"/>
       <c r="K379" s="3"/>
       <c r="L379" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -45951,7 +46095,7 @@
       <c r="J380" s="3"/>
       <c r="K380" s="3"/>
       <c r="L380" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -45968,7 +46112,7 @@
       <c r="J381" s="3"/>
       <c r="K381" s="3"/>
       <c r="L381" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -45985,7 +46129,7 @@
       <c r="J382" s="3"/>
       <c r="K382" s="3"/>
       <c r="L382" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -46002,7 +46146,7 @@
       <c r="J383" s="3"/>
       <c r="K383" s="3"/>
       <c r="L383" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -46019,7 +46163,7 @@
       <c r="J384" s="3"/>
       <c r="K384" s="3"/>
       <c r="L384" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -46036,7 +46180,7 @@
       <c r="J385" s="3"/>
       <c r="K385" s="3"/>
       <c r="L385" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -46053,7 +46197,7 @@
       <c r="J386" s="3"/>
       <c r="K386" s="3"/>
       <c r="L386" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -46070,7 +46214,7 @@
       <c r="J387" s="3"/>
       <c r="K387" s="3"/>
       <c r="L387" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -46087,7 +46231,7 @@
       <c r="J388" s="3"/>
       <c r="K388" s="3"/>
       <c r="L388" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -46104,7 +46248,7 @@
       <c r="J389" s="3"/>
       <c r="K389" s="3"/>
       <c r="L389" s="4" t="str">
-        <f t="shared" ref="L389:L390" si="12">IF(COUNTA(B389:K389)=0,"",AVERAGE(B389:K389))</f>
+        <f t="shared" ref="L389:L390" si="13">IF(COUNTA(B389:K389)=0,"",AVERAGE(B389:K389))</f>
         <v/>
       </c>
     </row>
@@ -46121,7 +46265,7 @@
       <c r="J390" s="3"/>
       <c r="K390" s="3"/>
       <c r="L390" s="4" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>

--- a/app/mevduat-kredi-faizleri/data/hoca-ile-borsa-faiz-takip-sablonu-guncel.xlsx
+++ b/app/mevduat-kredi-faizleri/data/hoca-ile-borsa-faiz-takip-sablonu-guncel.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projeler\hoca-ile-borsa\app\mevduat-kredi-faizleri\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{460F093C-9AD3-448A-807A-6368CF891E59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8731FC9E-F9E1-41C4-A7FD-044A4A8BE587}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -259,12 +259,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -446,6 +446,9 @@
                 <c:pt idx="34">
                   <c:v>46178</c:v>
                 </c:pt>
+                <c:pt idx="35">
+                  <c:v>46181</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -561,7 +564,7 @@
                   <c:v>43.472500000000004</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>0</c:v>
+                  <c:v>43.472500000000004</c:v>
                 </c:pt>
                 <c:pt idx="36">
                   <c:v>0</c:v>
@@ -1877,6 +1880,9 @@
                 <c:pt idx="34">
                   <c:v>46178</c:v>
                 </c:pt>
+                <c:pt idx="35">
+                  <c:v>46181</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1992,7 +1998,7 @@
                   <c:v>3.7305263157894726</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>0</c:v>
+                  <c:v>3.7305263157894726</c:v>
                 </c:pt>
                 <c:pt idx="36">
                   <c:v>0</c:v>
@@ -3308,6 +3314,9 @@
                 <c:pt idx="34">
                   <c:v>46178</c:v>
                 </c:pt>
+                <c:pt idx="35">
+                  <c:v>46181</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3423,7 +3432,7 @@
                   <c:v>2.8555555555555556</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>0</c:v>
+                  <c:v>2.8555555555555556</c:v>
                 </c:pt>
                 <c:pt idx="36">
                   <c:v>0</c:v>
@@ -4739,6 +4748,9 @@
                 <c:pt idx="34">
                   <c:v>46178</c:v>
                 </c:pt>
+                <c:pt idx="35">
+                  <c:v>46181</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -4854,7 +4866,7 @@
                   <c:v>3.399</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>0</c:v>
+                  <c:v>3.399</c:v>
                 </c:pt>
                 <c:pt idx="36">
                   <c:v>0</c:v>
@@ -6445,7 +6457,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="7"/>
@@ -6475,7 +6487,7 @@
       <c r="Z1" s="7"/>
     </row>
     <row r="2" spans="1:26" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="6" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="7"/>
@@ -9420,34 +9432,84 @@
       </c>
     </row>
     <row r="40" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A40" s="2"/>
-      <c r="B40" s="3"/>
-      <c r="C40" s="3"/>
-      <c r="D40" s="3"/>
-      <c r="E40" s="3"/>
-      <c r="F40" s="3"/>
-      <c r="G40" s="3"/>
-      <c r="H40" s="3"/>
-      <c r="I40" s="3"/>
-      <c r="J40" s="3"/>
-      <c r="K40" s="3"/>
-      <c r="L40" s="3"/>
-      <c r="M40" s="3"/>
-      <c r="N40" s="3"/>
-      <c r="O40" s="3"/>
-      <c r="P40" s="3"/>
-      <c r="Q40" s="3"/>
-      <c r="R40" s="3"/>
-      <c r="S40" s="3"/>
-      <c r="T40" s="3"/>
-      <c r="U40" s="3"/>
-      <c r="V40" s="3"/>
-      <c r="W40" s="3"/>
-      <c r="X40" s="3"/>
-      <c r="Y40" s="3"/>
-      <c r="Z40" s="4" t="str">
+      <c r="A40" s="2">
+        <v>46181</v>
+      </c>
+      <c r="B40" s="3">
+        <v>42.5</v>
+      </c>
+      <c r="C40" s="3">
+        <v>46</v>
+      </c>
+      <c r="D40" s="3">
+        <v>45</v>
+      </c>
+      <c r="E40" s="3">
+        <v>45</v>
+      </c>
+      <c r="F40" s="3">
+        <v>43.5</v>
+      </c>
+      <c r="G40" s="3">
+        <v>41</v>
+      </c>
+      <c r="H40" s="3">
+        <v>46</v>
+      </c>
+      <c r="I40" s="3">
+        <v>41.5</v>
+      </c>
+      <c r="J40" s="3">
+        <v>43</v>
+      </c>
+      <c r="K40" s="3">
+        <v>41</v>
+      </c>
+      <c r="L40" s="3">
+        <v>36</v>
+      </c>
+      <c r="M40" s="3">
+        <v>44</v>
+      </c>
+      <c r="N40" s="3">
+        <v>45</v>
+      </c>
+      <c r="O40" s="3">
+        <v>42.59</v>
+      </c>
+      <c r="P40" s="3">
+        <v>39</v>
+      </c>
+      <c r="Q40" s="3">
+        <v>45</v>
+      </c>
+      <c r="R40" s="3">
+        <v>45</v>
+      </c>
+      <c r="S40" s="3">
+        <v>45</v>
+      </c>
+      <c r="T40" s="3">
+        <v>45</v>
+      </c>
+      <c r="U40" s="3">
+        <v>43.5</v>
+      </c>
+      <c r="V40" s="3">
+        <v>44.5</v>
+      </c>
+      <c r="W40" s="3">
+        <v>42</v>
+      </c>
+      <c r="X40" s="3">
+        <v>47</v>
+      </c>
+      <c r="Y40" s="3">
+        <v>45.25</v>
+      </c>
+      <c r="Z40" s="4">
         <f t="shared" si="0"/>
-        <v/>
+        <v>43.472500000000004</v>
       </c>
     </row>
     <row r="41" spans="1:26" x14ac:dyDescent="0.25">
@@ -20326,7 +20388,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="8" t="s">
         <v>29</v>
       </c>
       <c r="B1" s="7"/>
@@ -20351,7 +20413,7 @@
       <c r="U1" s="7"/>
     </row>
     <row r="2" spans="1:21" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="6" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="7"/>
@@ -22751,29 +22813,69 @@
       </c>
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A40" s="2"/>
-      <c r="B40" s="3"/>
-      <c r="C40" s="3"/>
-      <c r="D40" s="3"/>
-      <c r="E40" s="3"/>
-      <c r="F40" s="3"/>
-      <c r="G40" s="3"/>
-      <c r="H40" s="3"/>
-      <c r="I40" s="3"/>
-      <c r="J40" s="3"/>
-      <c r="K40" s="3"/>
-      <c r="L40" s="3"/>
-      <c r="M40" s="3"/>
-      <c r="N40" s="3"/>
-      <c r="O40" s="3"/>
-      <c r="P40" s="3"/>
-      <c r="Q40" s="3"/>
-      <c r="R40" s="3"/>
-      <c r="S40" s="3"/>
-      <c r="T40" s="3"/>
-      <c r="U40" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
+      <c r="A40" s="2">
+        <v>46181</v>
+      </c>
+      <c r="B40" s="3">
+        <v>4.29</v>
+      </c>
+      <c r="C40" s="3">
+        <v>3.95</v>
+      </c>
+      <c r="D40" s="3">
+        <v>3.49</v>
+      </c>
+      <c r="E40" s="3">
+        <v>4.1900000000000004</v>
+      </c>
+      <c r="F40" s="3">
+        <v>4.3099999999999996</v>
+      </c>
+      <c r="G40" s="3">
+        <v>3.99</v>
+      </c>
+      <c r="H40" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="I40" s="3">
+        <v>3.39</v>
+      </c>
+      <c r="J40" s="3">
+        <v>3.09</v>
+      </c>
+      <c r="K40" s="3">
+        <v>4.1399999999999997</v>
+      </c>
+      <c r="L40" s="3">
+        <v>3.79</v>
+      </c>
+      <c r="M40" s="3">
+        <v>3.59</v>
+      </c>
+      <c r="N40" s="3">
+        <v>3.69</v>
+      </c>
+      <c r="O40" s="3">
+        <v>4.1900000000000004</v>
+      </c>
+      <c r="P40" s="3">
+        <v>3.89</v>
+      </c>
+      <c r="Q40" s="3">
+        <v>4.03</v>
+      </c>
+      <c r="R40" s="3">
+        <v>3.89</v>
+      </c>
+      <c r="S40" s="3">
+        <v>3.99</v>
+      </c>
+      <c r="T40" s="3">
+        <v>1.99</v>
+      </c>
+      <c r="U40" s="4">
+        <f t="shared" ref="U40" si="8">IF(COUNTA(B40:T40)=0,"",AVERAGE(B40:T40))</f>
+        <v>3.7305263157894726</v>
       </c>
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
@@ -23526,7 +23628,7 @@
       <c r="S69" s="3"/>
       <c r="T69" s="3"/>
       <c r="U69" s="4" t="str">
-        <f t="shared" ref="U69:U132" si="8">IF(COUNTA(B69:T69)=0,"",AVERAGE(B69:T69))</f>
+        <f t="shared" ref="U69:U132" si="9">IF(COUNTA(B69:T69)=0,"",AVERAGE(B69:T69))</f>
         <v/>
       </c>
     </row>
@@ -23552,7 +23654,7 @@
       <c r="S70" s="3"/>
       <c r="T70" s="3"/>
       <c r="U70" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -23578,7 +23680,7 @@
       <c r="S71" s="3"/>
       <c r="T71" s="3"/>
       <c r="U71" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -23604,7 +23706,7 @@
       <c r="S72" s="3"/>
       <c r="T72" s="3"/>
       <c r="U72" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -23630,7 +23732,7 @@
       <c r="S73" s="3"/>
       <c r="T73" s="3"/>
       <c r="U73" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -23656,7 +23758,7 @@
       <c r="S74" s="3"/>
       <c r="T74" s="3"/>
       <c r="U74" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -23682,7 +23784,7 @@
       <c r="S75" s="3"/>
       <c r="T75" s="3"/>
       <c r="U75" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -23708,7 +23810,7 @@
       <c r="S76" s="3"/>
       <c r="T76" s="3"/>
       <c r="U76" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -23734,7 +23836,7 @@
       <c r="S77" s="3"/>
       <c r="T77" s="3"/>
       <c r="U77" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -23760,7 +23862,7 @@
       <c r="S78" s="3"/>
       <c r="T78" s="3"/>
       <c r="U78" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -23786,7 +23888,7 @@
       <c r="S79" s="3"/>
       <c r="T79" s="3"/>
       <c r="U79" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -23812,7 +23914,7 @@
       <c r="S80" s="3"/>
       <c r="T80" s="3"/>
       <c r="U80" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -23838,7 +23940,7 @@
       <c r="S81" s="3"/>
       <c r="T81" s="3"/>
       <c r="U81" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -23864,7 +23966,7 @@
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
       <c r="U82" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -23890,7 +23992,7 @@
       <c r="S83" s="3"/>
       <c r="T83" s="3"/>
       <c r="U83" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -23916,7 +24018,7 @@
       <c r="S84" s="3"/>
       <c r="T84" s="3"/>
       <c r="U84" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -23942,7 +24044,7 @@
       <c r="S85" s="3"/>
       <c r="T85" s="3"/>
       <c r="U85" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -23968,7 +24070,7 @@
       <c r="S86" s="3"/>
       <c r="T86" s="3"/>
       <c r="U86" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -23994,7 +24096,7 @@
       <c r="S87" s="3"/>
       <c r="T87" s="3"/>
       <c r="U87" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -24020,7 +24122,7 @@
       <c r="S88" s="3"/>
       <c r="T88" s="3"/>
       <c r="U88" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -24046,7 +24148,7 @@
       <c r="S89" s="3"/>
       <c r="T89" s="3"/>
       <c r="U89" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -24072,7 +24174,7 @@
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
       <c r="U90" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -24098,7 +24200,7 @@
       <c r="S91" s="3"/>
       <c r="T91" s="3"/>
       <c r="U91" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -24124,7 +24226,7 @@
       <c r="S92" s="3"/>
       <c r="T92" s="3"/>
       <c r="U92" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -24150,7 +24252,7 @@
       <c r="S93" s="3"/>
       <c r="T93" s="3"/>
       <c r="U93" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -24176,7 +24278,7 @@
       <c r="S94" s="3"/>
       <c r="T94" s="3"/>
       <c r="U94" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -24202,7 +24304,7 @@
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
       <c r="U95" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -24228,7 +24330,7 @@
       <c r="S96" s="3"/>
       <c r="T96" s="3"/>
       <c r="U96" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -24254,7 +24356,7 @@
       <c r="S97" s="3"/>
       <c r="T97" s="3"/>
       <c r="U97" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -24280,7 +24382,7 @@
       <c r="S98" s="3"/>
       <c r="T98" s="3"/>
       <c r="U98" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -24306,7 +24408,7 @@
       <c r="S99" s="3"/>
       <c r="T99" s="3"/>
       <c r="U99" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -24332,7 +24434,7 @@
       <c r="S100" s="3"/>
       <c r="T100" s="3"/>
       <c r="U100" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -24358,7 +24460,7 @@
       <c r="S101" s="3"/>
       <c r="T101" s="3"/>
       <c r="U101" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -24384,7 +24486,7 @@
       <c r="S102" s="3"/>
       <c r="T102" s="3"/>
       <c r="U102" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -24410,7 +24512,7 @@
       <c r="S103" s="3"/>
       <c r="T103" s="3"/>
       <c r="U103" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -24436,7 +24538,7 @@
       <c r="S104" s="3"/>
       <c r="T104" s="3"/>
       <c r="U104" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -24462,7 +24564,7 @@
       <c r="S105" s="3"/>
       <c r="T105" s="3"/>
       <c r="U105" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -24488,7 +24590,7 @@
       <c r="S106" s="3"/>
       <c r="T106" s="3"/>
       <c r="U106" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -24514,7 +24616,7 @@
       <c r="S107" s="3"/>
       <c r="T107" s="3"/>
       <c r="U107" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -24540,7 +24642,7 @@
       <c r="S108" s="3"/>
       <c r="T108" s="3"/>
       <c r="U108" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -24566,7 +24668,7 @@
       <c r="S109" s="3"/>
       <c r="T109" s="3"/>
       <c r="U109" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -24592,7 +24694,7 @@
       <c r="S110" s="3"/>
       <c r="T110" s="3"/>
       <c r="U110" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -24618,7 +24720,7 @@
       <c r="S111" s="3"/>
       <c r="T111" s="3"/>
       <c r="U111" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -24644,7 +24746,7 @@
       <c r="S112" s="3"/>
       <c r="T112" s="3"/>
       <c r="U112" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -24670,7 +24772,7 @@
       <c r="S113" s="3"/>
       <c r="T113" s="3"/>
       <c r="U113" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -24696,7 +24798,7 @@
       <c r="S114" s="3"/>
       <c r="T114" s="3"/>
       <c r="U114" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -24722,7 +24824,7 @@
       <c r="S115" s="3"/>
       <c r="T115" s="3"/>
       <c r="U115" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -24748,7 +24850,7 @@
       <c r="S116" s="3"/>
       <c r="T116" s="3"/>
       <c r="U116" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -24774,7 +24876,7 @@
       <c r="S117" s="3"/>
       <c r="T117" s="3"/>
       <c r="U117" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -24800,7 +24902,7 @@
       <c r="S118" s="3"/>
       <c r="T118" s="3"/>
       <c r="U118" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -24826,7 +24928,7 @@
       <c r="S119" s="3"/>
       <c r="T119" s="3"/>
       <c r="U119" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -24852,7 +24954,7 @@
       <c r="S120" s="3"/>
       <c r="T120" s="3"/>
       <c r="U120" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -24878,7 +24980,7 @@
       <c r="S121" s="3"/>
       <c r="T121" s="3"/>
       <c r="U121" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -24904,7 +25006,7 @@
       <c r="S122" s="3"/>
       <c r="T122" s="3"/>
       <c r="U122" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -24930,7 +25032,7 @@
       <c r="S123" s="3"/>
       <c r="T123" s="3"/>
       <c r="U123" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -24956,7 +25058,7 @@
       <c r="S124" s="3"/>
       <c r="T124" s="3"/>
       <c r="U124" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -24982,7 +25084,7 @@
       <c r="S125" s="3"/>
       <c r="T125" s="3"/>
       <c r="U125" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -25008,7 +25110,7 @@
       <c r="S126" s="3"/>
       <c r="T126" s="3"/>
       <c r="U126" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -25034,7 +25136,7 @@
       <c r="S127" s="3"/>
       <c r="T127" s="3"/>
       <c r="U127" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -25060,7 +25162,7 @@
       <c r="S128" s="3"/>
       <c r="T128" s="3"/>
       <c r="U128" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -25086,7 +25188,7 @@
       <c r="S129" s="3"/>
       <c r="T129" s="3"/>
       <c r="U129" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -25112,7 +25214,7 @@
       <c r="S130" s="3"/>
       <c r="T130" s="3"/>
       <c r="U130" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -25138,7 +25240,7 @@
       <c r="S131" s="3"/>
       <c r="T131" s="3"/>
       <c r="U131" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -25164,7 +25266,7 @@
       <c r="S132" s="3"/>
       <c r="T132" s="3"/>
       <c r="U132" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -25190,7 +25292,7 @@
       <c r="S133" s="3"/>
       <c r="T133" s="3"/>
       <c r="U133" s="4" t="str">
-        <f t="shared" ref="U133:U196" si="9">IF(COUNTA(B133:T133)=0,"",AVERAGE(B133:T133))</f>
+        <f t="shared" ref="U133:U196" si="10">IF(COUNTA(B133:T133)=0,"",AVERAGE(B133:T133))</f>
         <v/>
       </c>
     </row>
@@ -25216,7 +25318,7 @@
       <c r="S134" s="3"/>
       <c r="T134" s="3"/>
       <c r="U134" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -25242,7 +25344,7 @@
       <c r="S135" s="3"/>
       <c r="T135" s="3"/>
       <c r="U135" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -25268,7 +25370,7 @@
       <c r="S136" s="3"/>
       <c r="T136" s="3"/>
       <c r="U136" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -25294,7 +25396,7 @@
       <c r="S137" s="3"/>
       <c r="T137" s="3"/>
       <c r="U137" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -25320,7 +25422,7 @@
       <c r="S138" s="3"/>
       <c r="T138" s="3"/>
       <c r="U138" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -25346,7 +25448,7 @@
       <c r="S139" s="3"/>
       <c r="T139" s="3"/>
       <c r="U139" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -25372,7 +25474,7 @@
       <c r="S140" s="3"/>
       <c r="T140" s="3"/>
       <c r="U140" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -25398,7 +25500,7 @@
       <c r="S141" s="3"/>
       <c r="T141" s="3"/>
       <c r="U141" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -25424,7 +25526,7 @@
       <c r="S142" s="3"/>
       <c r="T142" s="3"/>
       <c r="U142" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -25450,7 +25552,7 @@
       <c r="S143" s="3"/>
       <c r="T143" s="3"/>
       <c r="U143" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -25476,7 +25578,7 @@
       <c r="S144" s="3"/>
       <c r="T144" s="3"/>
       <c r="U144" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -25502,7 +25604,7 @@
       <c r="S145" s="3"/>
       <c r="T145" s="3"/>
       <c r="U145" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -25528,7 +25630,7 @@
       <c r="S146" s="3"/>
       <c r="T146" s="3"/>
       <c r="U146" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -25554,7 +25656,7 @@
       <c r="S147" s="3"/>
       <c r="T147" s="3"/>
       <c r="U147" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -25580,7 +25682,7 @@
       <c r="S148" s="3"/>
       <c r="T148" s="3"/>
       <c r="U148" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -25606,7 +25708,7 @@
       <c r="S149" s="3"/>
       <c r="T149" s="3"/>
       <c r="U149" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -25632,7 +25734,7 @@
       <c r="S150" s="3"/>
       <c r="T150" s="3"/>
       <c r="U150" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -25658,7 +25760,7 @@
       <c r="S151" s="3"/>
       <c r="T151" s="3"/>
       <c r="U151" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -25684,7 +25786,7 @@
       <c r="S152" s="3"/>
       <c r="T152" s="3"/>
       <c r="U152" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -25710,7 +25812,7 @@
       <c r="S153" s="3"/>
       <c r="T153" s="3"/>
       <c r="U153" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -25736,7 +25838,7 @@
       <c r="S154" s="3"/>
       <c r="T154" s="3"/>
       <c r="U154" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -25762,7 +25864,7 @@
       <c r="S155" s="3"/>
       <c r="T155" s="3"/>
       <c r="U155" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -25788,7 +25890,7 @@
       <c r="S156" s="3"/>
       <c r="T156" s="3"/>
       <c r="U156" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -25814,7 +25916,7 @@
       <c r="S157" s="3"/>
       <c r="T157" s="3"/>
       <c r="U157" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -25840,7 +25942,7 @@
       <c r="S158" s="3"/>
       <c r="T158" s="3"/>
       <c r="U158" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -25866,7 +25968,7 @@
       <c r="S159" s="3"/>
       <c r="T159" s="3"/>
       <c r="U159" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -25892,7 +25994,7 @@
       <c r="S160" s="3"/>
       <c r="T160" s="3"/>
       <c r="U160" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -25918,7 +26020,7 @@
       <c r="S161" s="3"/>
       <c r="T161" s="3"/>
       <c r="U161" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -25944,7 +26046,7 @@
       <c r="S162" s="3"/>
       <c r="T162" s="3"/>
       <c r="U162" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -25970,7 +26072,7 @@
       <c r="S163" s="3"/>
       <c r="T163" s="3"/>
       <c r="U163" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -25996,7 +26098,7 @@
       <c r="S164" s="3"/>
       <c r="T164" s="3"/>
       <c r="U164" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -26022,7 +26124,7 @@
       <c r="S165" s="3"/>
       <c r="T165" s="3"/>
       <c r="U165" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -26048,7 +26150,7 @@
       <c r="S166" s="3"/>
       <c r="T166" s="3"/>
       <c r="U166" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -26074,7 +26176,7 @@
       <c r="S167" s="3"/>
       <c r="T167" s="3"/>
       <c r="U167" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -26100,7 +26202,7 @@
       <c r="S168" s="3"/>
       <c r="T168" s="3"/>
       <c r="U168" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -26126,7 +26228,7 @@
       <c r="S169" s="3"/>
       <c r="T169" s="3"/>
       <c r="U169" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -26152,7 +26254,7 @@
       <c r="S170" s="3"/>
       <c r="T170" s="3"/>
       <c r="U170" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -26178,7 +26280,7 @@
       <c r="S171" s="3"/>
       <c r="T171" s="3"/>
       <c r="U171" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -26204,7 +26306,7 @@
       <c r="S172" s="3"/>
       <c r="T172" s="3"/>
       <c r="U172" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -26230,7 +26332,7 @@
       <c r="S173" s="3"/>
       <c r="T173" s="3"/>
       <c r="U173" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -26256,7 +26358,7 @@
       <c r="S174" s="3"/>
       <c r="T174" s="3"/>
       <c r="U174" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -26282,7 +26384,7 @@
       <c r="S175" s="3"/>
       <c r="T175" s="3"/>
       <c r="U175" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -26308,7 +26410,7 @@
       <c r="S176" s="3"/>
       <c r="T176" s="3"/>
       <c r="U176" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -26334,7 +26436,7 @@
       <c r="S177" s="3"/>
       <c r="T177" s="3"/>
       <c r="U177" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -26360,7 +26462,7 @@
       <c r="S178" s="3"/>
       <c r="T178" s="3"/>
       <c r="U178" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -26386,7 +26488,7 @@
       <c r="S179" s="3"/>
       <c r="T179" s="3"/>
       <c r="U179" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -26412,7 +26514,7 @@
       <c r="S180" s="3"/>
       <c r="T180" s="3"/>
       <c r="U180" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -26438,7 +26540,7 @@
       <c r="S181" s="3"/>
       <c r="T181" s="3"/>
       <c r="U181" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -26464,7 +26566,7 @@
       <c r="S182" s="3"/>
       <c r="T182" s="3"/>
       <c r="U182" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -26490,7 +26592,7 @@
       <c r="S183" s="3"/>
       <c r="T183" s="3"/>
       <c r="U183" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -26516,7 +26618,7 @@
       <c r="S184" s="3"/>
       <c r="T184" s="3"/>
       <c r="U184" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -26542,7 +26644,7 @@
       <c r="S185" s="3"/>
       <c r="T185" s="3"/>
       <c r="U185" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -26568,7 +26670,7 @@
       <c r="S186" s="3"/>
       <c r="T186" s="3"/>
       <c r="U186" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -26594,7 +26696,7 @@
       <c r="S187" s="3"/>
       <c r="T187" s="3"/>
       <c r="U187" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -26620,7 +26722,7 @@
       <c r="S188" s="3"/>
       <c r="T188" s="3"/>
       <c r="U188" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -26646,7 +26748,7 @@
       <c r="S189" s="3"/>
       <c r="T189" s="3"/>
       <c r="U189" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -26672,7 +26774,7 @@
       <c r="S190" s="3"/>
       <c r="T190" s="3"/>
       <c r="U190" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -26698,7 +26800,7 @@
       <c r="S191" s="3"/>
       <c r="T191" s="3"/>
       <c r="U191" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -26724,7 +26826,7 @@
       <c r="S192" s="3"/>
       <c r="T192" s="3"/>
       <c r="U192" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -26750,7 +26852,7 @@
       <c r="S193" s="3"/>
       <c r="T193" s="3"/>
       <c r="U193" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -26776,7 +26878,7 @@
       <c r="S194" s="3"/>
       <c r="T194" s="3"/>
       <c r="U194" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -26802,7 +26904,7 @@
       <c r="S195" s="3"/>
       <c r="T195" s="3"/>
       <c r="U195" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -26828,7 +26930,7 @@
       <c r="S196" s="3"/>
       <c r="T196" s="3"/>
       <c r="U196" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -26854,7 +26956,7 @@
       <c r="S197" s="3"/>
       <c r="T197" s="3"/>
       <c r="U197" s="4" t="str">
-        <f t="shared" ref="U197:U260" si="10">IF(COUNTA(B197:T197)=0,"",AVERAGE(B197:T197))</f>
+        <f t="shared" ref="U197:U260" si="11">IF(COUNTA(B197:T197)=0,"",AVERAGE(B197:T197))</f>
         <v/>
       </c>
     </row>
@@ -26880,7 +26982,7 @@
       <c r="S198" s="3"/>
       <c r="T198" s="3"/>
       <c r="U198" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -26906,7 +27008,7 @@
       <c r="S199" s="3"/>
       <c r="T199" s="3"/>
       <c r="U199" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -26932,7 +27034,7 @@
       <c r="S200" s="3"/>
       <c r="T200" s="3"/>
       <c r="U200" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -26958,7 +27060,7 @@
       <c r="S201" s="3"/>
       <c r="T201" s="3"/>
       <c r="U201" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -26984,7 +27086,7 @@
       <c r="S202" s="3"/>
       <c r="T202" s="3"/>
       <c r="U202" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -27010,7 +27112,7 @@
       <c r="S203" s="3"/>
       <c r="T203" s="3"/>
       <c r="U203" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -27036,7 +27138,7 @@
       <c r="S204" s="3"/>
       <c r="T204" s="3"/>
       <c r="U204" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -27062,7 +27164,7 @@
       <c r="S205" s="3"/>
       <c r="T205" s="3"/>
       <c r="U205" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -27088,7 +27190,7 @@
       <c r="S206" s="3"/>
       <c r="T206" s="3"/>
       <c r="U206" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -27114,7 +27216,7 @@
       <c r="S207" s="3"/>
       <c r="T207" s="3"/>
       <c r="U207" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -27140,7 +27242,7 @@
       <c r="S208" s="3"/>
       <c r="T208" s="3"/>
       <c r="U208" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -27166,7 +27268,7 @@
       <c r="S209" s="3"/>
       <c r="T209" s="3"/>
       <c r="U209" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -27192,7 +27294,7 @@
       <c r="S210" s="3"/>
       <c r="T210" s="3"/>
       <c r="U210" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -27218,7 +27320,7 @@
       <c r="S211" s="3"/>
       <c r="T211" s="3"/>
       <c r="U211" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -27244,7 +27346,7 @@
       <c r="S212" s="3"/>
       <c r="T212" s="3"/>
       <c r="U212" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -27270,7 +27372,7 @@
       <c r="S213" s="3"/>
       <c r="T213" s="3"/>
       <c r="U213" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -27296,7 +27398,7 @@
       <c r="S214" s="3"/>
       <c r="T214" s="3"/>
       <c r="U214" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -27322,7 +27424,7 @@
       <c r="S215" s="3"/>
       <c r="T215" s="3"/>
       <c r="U215" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -27348,7 +27450,7 @@
       <c r="S216" s="3"/>
       <c r="T216" s="3"/>
       <c r="U216" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -27374,7 +27476,7 @@
       <c r="S217" s="3"/>
       <c r="T217" s="3"/>
       <c r="U217" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -27400,7 +27502,7 @@
       <c r="S218" s="3"/>
       <c r="T218" s="3"/>
       <c r="U218" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -27426,7 +27528,7 @@
       <c r="S219" s="3"/>
       <c r="T219" s="3"/>
       <c r="U219" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -27452,7 +27554,7 @@
       <c r="S220" s="3"/>
       <c r="T220" s="3"/>
       <c r="U220" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -27478,7 +27580,7 @@
       <c r="S221" s="3"/>
       <c r="T221" s="3"/>
       <c r="U221" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -27504,7 +27606,7 @@
       <c r="S222" s="3"/>
       <c r="T222" s="3"/>
       <c r="U222" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -27530,7 +27632,7 @@
       <c r="S223" s="3"/>
       <c r="T223" s="3"/>
       <c r="U223" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -27556,7 +27658,7 @@
       <c r="S224" s="3"/>
       <c r="T224" s="3"/>
       <c r="U224" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -27582,7 +27684,7 @@
       <c r="S225" s="3"/>
       <c r="T225" s="3"/>
       <c r="U225" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -27608,7 +27710,7 @@
       <c r="S226" s="3"/>
       <c r="T226" s="3"/>
       <c r="U226" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -27634,7 +27736,7 @@
       <c r="S227" s="3"/>
       <c r="T227" s="3"/>
       <c r="U227" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -27660,7 +27762,7 @@
       <c r="S228" s="3"/>
       <c r="T228" s="3"/>
       <c r="U228" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -27686,7 +27788,7 @@
       <c r="S229" s="3"/>
       <c r="T229" s="3"/>
       <c r="U229" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -27712,7 +27814,7 @@
       <c r="S230" s="3"/>
       <c r="T230" s="3"/>
       <c r="U230" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -27738,7 +27840,7 @@
       <c r="S231" s="3"/>
       <c r="T231" s="3"/>
       <c r="U231" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -27764,7 +27866,7 @@
       <c r="S232" s="3"/>
       <c r="T232" s="3"/>
       <c r="U232" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -27790,7 +27892,7 @@
       <c r="S233" s="3"/>
       <c r="T233" s="3"/>
       <c r="U233" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -27816,7 +27918,7 @@
       <c r="S234" s="3"/>
       <c r="T234" s="3"/>
       <c r="U234" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -27842,7 +27944,7 @@
       <c r="S235" s="3"/>
       <c r="T235" s="3"/>
       <c r="U235" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -27868,7 +27970,7 @@
       <c r="S236" s="3"/>
       <c r="T236" s="3"/>
       <c r="U236" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -27894,7 +27996,7 @@
       <c r="S237" s="3"/>
       <c r="T237" s="3"/>
       <c r="U237" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -27920,7 +28022,7 @@
       <c r="S238" s="3"/>
       <c r="T238" s="3"/>
       <c r="U238" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -27946,7 +28048,7 @@
       <c r="S239" s="3"/>
       <c r="T239" s="3"/>
       <c r="U239" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -27972,7 +28074,7 @@
       <c r="S240" s="3"/>
       <c r="T240" s="3"/>
       <c r="U240" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -27998,7 +28100,7 @@
       <c r="S241" s="3"/>
       <c r="T241" s="3"/>
       <c r="U241" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -28024,7 +28126,7 @@
       <c r="S242" s="3"/>
       <c r="T242" s="3"/>
       <c r="U242" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -28050,7 +28152,7 @@
       <c r="S243" s="3"/>
       <c r="T243" s="3"/>
       <c r="U243" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -28076,7 +28178,7 @@
       <c r="S244" s="3"/>
       <c r="T244" s="3"/>
       <c r="U244" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -28102,7 +28204,7 @@
       <c r="S245" s="3"/>
       <c r="T245" s="3"/>
       <c r="U245" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -28128,7 +28230,7 @@
       <c r="S246" s="3"/>
       <c r="T246" s="3"/>
       <c r="U246" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -28154,7 +28256,7 @@
       <c r="S247" s="3"/>
       <c r="T247" s="3"/>
       <c r="U247" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -28180,7 +28282,7 @@
       <c r="S248" s="3"/>
       <c r="T248" s="3"/>
       <c r="U248" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -28206,7 +28308,7 @@
       <c r="S249" s="3"/>
       <c r="T249" s="3"/>
       <c r="U249" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -28232,7 +28334,7 @@
       <c r="S250" s="3"/>
       <c r="T250" s="3"/>
       <c r="U250" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -28258,7 +28360,7 @@
       <c r="S251" s="3"/>
       <c r="T251" s="3"/>
       <c r="U251" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -28284,7 +28386,7 @@
       <c r="S252" s="3"/>
       <c r="T252" s="3"/>
       <c r="U252" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -28310,7 +28412,7 @@
       <c r="S253" s="3"/>
       <c r="T253" s="3"/>
       <c r="U253" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -28336,7 +28438,7 @@
       <c r="S254" s="3"/>
       <c r="T254" s="3"/>
       <c r="U254" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -28362,7 +28464,7 @@
       <c r="S255" s="3"/>
       <c r="T255" s="3"/>
       <c r="U255" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -28388,7 +28490,7 @@
       <c r="S256" s="3"/>
       <c r="T256" s="3"/>
       <c r="U256" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -28414,7 +28516,7 @@
       <c r="S257" s="3"/>
       <c r="T257" s="3"/>
       <c r="U257" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -28440,7 +28542,7 @@
       <c r="S258" s="3"/>
       <c r="T258" s="3"/>
       <c r="U258" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -28466,7 +28568,7 @@
       <c r="S259" s="3"/>
       <c r="T259" s="3"/>
       <c r="U259" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -28492,7 +28594,7 @@
       <c r="S260" s="3"/>
       <c r="T260" s="3"/>
       <c r="U260" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -28518,7 +28620,7 @@
       <c r="S261" s="3"/>
       <c r="T261" s="3"/>
       <c r="U261" s="4" t="str">
-        <f t="shared" ref="U261:U324" si="11">IF(COUNTA(B261:T261)=0,"",AVERAGE(B261:T261))</f>
+        <f t="shared" ref="U261:U324" si="12">IF(COUNTA(B261:T261)=0,"",AVERAGE(B261:T261))</f>
         <v/>
       </c>
     </row>
@@ -28544,7 +28646,7 @@
       <c r="S262" s="3"/>
       <c r="T262" s="3"/>
       <c r="U262" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -28570,7 +28672,7 @@
       <c r="S263" s="3"/>
       <c r="T263" s="3"/>
       <c r="U263" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -28596,7 +28698,7 @@
       <c r="S264" s="3"/>
       <c r="T264" s="3"/>
       <c r="U264" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -28622,7 +28724,7 @@
       <c r="S265" s="3"/>
       <c r="T265" s="3"/>
       <c r="U265" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -28648,7 +28750,7 @@
       <c r="S266" s="3"/>
       <c r="T266" s="3"/>
       <c r="U266" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -28674,7 +28776,7 @@
       <c r="S267" s="3"/>
       <c r="T267" s="3"/>
       <c r="U267" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -28700,7 +28802,7 @@
       <c r="S268" s="3"/>
       <c r="T268" s="3"/>
       <c r="U268" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -28726,7 +28828,7 @@
       <c r="S269" s="3"/>
       <c r="T269" s="3"/>
       <c r="U269" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -28752,7 +28854,7 @@
       <c r="S270" s="3"/>
       <c r="T270" s="3"/>
       <c r="U270" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -28778,7 +28880,7 @@
       <c r="S271" s="3"/>
       <c r="T271" s="3"/>
       <c r="U271" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -28804,7 +28906,7 @@
       <c r="S272" s="3"/>
       <c r="T272" s="3"/>
       <c r="U272" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -28830,7 +28932,7 @@
       <c r="S273" s="3"/>
       <c r="T273" s="3"/>
       <c r="U273" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -28856,7 +28958,7 @@
       <c r="S274" s="3"/>
       <c r="T274" s="3"/>
       <c r="U274" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -28882,7 +28984,7 @@
       <c r="S275" s="3"/>
       <c r="T275" s="3"/>
       <c r="U275" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -28908,7 +29010,7 @@
       <c r="S276" s="3"/>
       <c r="T276" s="3"/>
       <c r="U276" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -28934,7 +29036,7 @@
       <c r="S277" s="3"/>
       <c r="T277" s="3"/>
       <c r="U277" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -28960,7 +29062,7 @@
       <c r="S278" s="3"/>
       <c r="T278" s="3"/>
       <c r="U278" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -28986,7 +29088,7 @@
       <c r="S279" s="3"/>
       <c r="T279" s="3"/>
       <c r="U279" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -29012,7 +29114,7 @@
       <c r="S280" s="3"/>
       <c r="T280" s="3"/>
       <c r="U280" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -29038,7 +29140,7 @@
       <c r="S281" s="3"/>
       <c r="T281" s="3"/>
       <c r="U281" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -29064,7 +29166,7 @@
       <c r="S282" s="3"/>
       <c r="T282" s="3"/>
       <c r="U282" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -29090,7 +29192,7 @@
       <c r="S283" s="3"/>
       <c r="T283" s="3"/>
       <c r="U283" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -29116,7 +29218,7 @@
       <c r="S284" s="3"/>
       <c r="T284" s="3"/>
       <c r="U284" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -29142,7 +29244,7 @@
       <c r="S285" s="3"/>
       <c r="T285" s="3"/>
       <c r="U285" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -29168,7 +29270,7 @@
       <c r="S286" s="3"/>
       <c r="T286" s="3"/>
       <c r="U286" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -29194,7 +29296,7 @@
       <c r="S287" s="3"/>
       <c r="T287" s="3"/>
       <c r="U287" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -29220,7 +29322,7 @@
       <c r="S288" s="3"/>
       <c r="T288" s="3"/>
       <c r="U288" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -29246,7 +29348,7 @@
       <c r="S289" s="3"/>
       <c r="T289" s="3"/>
       <c r="U289" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -29272,7 +29374,7 @@
       <c r="S290" s="3"/>
       <c r="T290" s="3"/>
       <c r="U290" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -29298,7 +29400,7 @@
       <c r="S291" s="3"/>
       <c r="T291" s="3"/>
       <c r="U291" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -29324,7 +29426,7 @@
       <c r="S292" s="3"/>
       <c r="T292" s="3"/>
       <c r="U292" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -29350,7 +29452,7 @@
       <c r="S293" s="3"/>
       <c r="T293" s="3"/>
       <c r="U293" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -29376,7 +29478,7 @@
       <c r="S294" s="3"/>
       <c r="T294" s="3"/>
       <c r="U294" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -29402,7 +29504,7 @@
       <c r="S295" s="3"/>
       <c r="T295" s="3"/>
       <c r="U295" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -29428,7 +29530,7 @@
       <c r="S296" s="3"/>
       <c r="T296" s="3"/>
       <c r="U296" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -29454,7 +29556,7 @@
       <c r="S297" s="3"/>
       <c r="T297" s="3"/>
       <c r="U297" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -29480,7 +29582,7 @@
       <c r="S298" s="3"/>
       <c r="T298" s="3"/>
       <c r="U298" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -29506,7 +29608,7 @@
       <c r="S299" s="3"/>
       <c r="T299" s="3"/>
       <c r="U299" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -29532,7 +29634,7 @@
       <c r="S300" s="3"/>
       <c r="T300" s="3"/>
       <c r="U300" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -29558,7 +29660,7 @@
       <c r="S301" s="3"/>
       <c r="T301" s="3"/>
       <c r="U301" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -29584,7 +29686,7 @@
       <c r="S302" s="3"/>
       <c r="T302" s="3"/>
       <c r="U302" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -29610,7 +29712,7 @@
       <c r="S303" s="3"/>
       <c r="T303" s="3"/>
       <c r="U303" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -29636,7 +29738,7 @@
       <c r="S304" s="3"/>
       <c r="T304" s="3"/>
       <c r="U304" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -29662,7 +29764,7 @@
       <c r="S305" s="3"/>
       <c r="T305" s="3"/>
       <c r="U305" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -29688,7 +29790,7 @@
       <c r="S306" s="3"/>
       <c r="T306" s="3"/>
       <c r="U306" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -29714,7 +29816,7 @@
       <c r="S307" s="3"/>
       <c r="T307" s="3"/>
       <c r="U307" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -29740,7 +29842,7 @@
       <c r="S308" s="3"/>
       <c r="T308" s="3"/>
       <c r="U308" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -29766,7 +29868,7 @@
       <c r="S309" s="3"/>
       <c r="T309" s="3"/>
       <c r="U309" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -29792,7 +29894,7 @@
       <c r="S310" s="3"/>
       <c r="T310" s="3"/>
       <c r="U310" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -29818,7 +29920,7 @@
       <c r="S311" s="3"/>
       <c r="T311" s="3"/>
       <c r="U311" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -29844,7 +29946,7 @@
       <c r="S312" s="3"/>
       <c r="T312" s="3"/>
       <c r="U312" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -29870,7 +29972,7 @@
       <c r="S313" s="3"/>
       <c r="T313" s="3"/>
       <c r="U313" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -29896,7 +29998,7 @@
       <c r="S314" s="3"/>
       <c r="T314" s="3"/>
       <c r="U314" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -29922,7 +30024,7 @@
       <c r="S315" s="3"/>
       <c r="T315" s="3"/>
       <c r="U315" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -29948,7 +30050,7 @@
       <c r="S316" s="3"/>
       <c r="T316" s="3"/>
       <c r="U316" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -29974,7 +30076,7 @@
       <c r="S317" s="3"/>
       <c r="T317" s="3"/>
       <c r="U317" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -30000,7 +30102,7 @@
       <c r="S318" s="3"/>
       <c r="T318" s="3"/>
       <c r="U318" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -30026,7 +30128,7 @@
       <c r="S319" s="3"/>
       <c r="T319" s="3"/>
       <c r="U319" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -30052,7 +30154,7 @@
       <c r="S320" s="3"/>
       <c r="T320" s="3"/>
       <c r="U320" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -30078,7 +30180,7 @@
       <c r="S321" s="3"/>
       <c r="T321" s="3"/>
       <c r="U321" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -30104,7 +30206,7 @@
       <c r="S322" s="3"/>
       <c r="T322" s="3"/>
       <c r="U322" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -30130,7 +30232,7 @@
       <c r="S323" s="3"/>
       <c r="T323" s="3"/>
       <c r="U323" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -30156,7 +30258,7 @@
       <c r="S324" s="3"/>
       <c r="T324" s="3"/>
       <c r="U324" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -30182,7 +30284,7 @@
       <c r="S325" s="3"/>
       <c r="T325" s="3"/>
       <c r="U325" s="4" t="str">
-        <f t="shared" ref="U325:U388" si="12">IF(COUNTA(B325:T325)=0,"",AVERAGE(B325:T325))</f>
+        <f t="shared" ref="U325:U388" si="13">IF(COUNTA(B325:T325)=0,"",AVERAGE(B325:T325))</f>
         <v/>
       </c>
     </row>
@@ -30208,7 +30310,7 @@
       <c r="S326" s="3"/>
       <c r="T326" s="3"/>
       <c r="U326" s="4" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -30234,7 +30336,7 @@
       <c r="S327" s="3"/>
       <c r="T327" s="3"/>
       <c r="U327" s="4" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -30260,7 +30362,7 @@
       <c r="S328" s="3"/>
       <c r="T328" s="3"/>
       <c r="U328" s="4" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -30286,7 +30388,7 @@
       <c r="S329" s="3"/>
       <c r="T329" s="3"/>
       <c r="U329" s="4" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -30312,7 +30414,7 @@
       <c r="S330" s="3"/>
       <c r="T330" s="3"/>
       <c r="U330" s="4" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -30338,7 +30440,7 @@
       <c r="S331" s="3"/>
       <c r="T331" s="3"/>
       <c r="U331" s="4" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -30364,7 +30466,7 @@
       <c r="S332" s="3"/>
       <c r="T332" s="3"/>
       <c r="U332" s="4" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -30390,7 +30492,7 @@
       <c r="S333" s="3"/>
       <c r="T333" s="3"/>
       <c r="U333" s="4" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -30416,7 +30518,7 @@
       <c r="S334" s="3"/>
       <c r="T334" s="3"/>
       <c r="U334" s="4" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -30442,7 +30544,7 @@
       <c r="S335" s="3"/>
       <c r="T335" s="3"/>
       <c r="U335" s="4" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -30468,7 +30570,7 @@
       <c r="S336" s="3"/>
       <c r="T336" s="3"/>
       <c r="U336" s="4" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -30494,7 +30596,7 @@
       <c r="S337" s="3"/>
       <c r="T337" s="3"/>
       <c r="U337" s="4" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -30520,7 +30622,7 @@
       <c r="S338" s="3"/>
       <c r="T338" s="3"/>
       <c r="U338" s="4" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -30546,7 +30648,7 @@
       <c r="S339" s="3"/>
       <c r="T339" s="3"/>
       <c r="U339" s="4" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -30572,7 +30674,7 @@
       <c r="S340" s="3"/>
       <c r="T340" s="3"/>
       <c r="U340" s="4" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -30598,7 +30700,7 @@
       <c r="S341" s="3"/>
       <c r="T341" s="3"/>
       <c r="U341" s="4" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -30624,7 +30726,7 @@
       <c r="S342" s="3"/>
       <c r="T342" s="3"/>
       <c r="U342" s="4" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -30650,7 +30752,7 @@
       <c r="S343" s="3"/>
       <c r="T343" s="3"/>
       <c r="U343" s="4" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -30676,7 +30778,7 @@
       <c r="S344" s="3"/>
       <c r="T344" s="3"/>
       <c r="U344" s="4" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -30702,7 +30804,7 @@
       <c r="S345" s="3"/>
       <c r="T345" s="3"/>
       <c r="U345" s="4" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -30728,7 +30830,7 @@
       <c r="S346" s="3"/>
       <c r="T346" s="3"/>
       <c r="U346" s="4" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -30754,7 +30856,7 @@
       <c r="S347" s="3"/>
       <c r="T347" s="3"/>
       <c r="U347" s="4" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -30780,7 +30882,7 @@
       <c r="S348" s="3"/>
       <c r="T348" s="3"/>
       <c r="U348" s="4" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -30806,7 +30908,7 @@
       <c r="S349" s="3"/>
       <c r="T349" s="3"/>
       <c r="U349" s="4" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -30832,7 +30934,7 @@
       <c r="S350" s="3"/>
       <c r="T350" s="3"/>
       <c r="U350" s="4" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -30858,7 +30960,7 @@
       <c r="S351" s="3"/>
       <c r="T351" s="3"/>
       <c r="U351" s="4" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -30884,7 +30986,7 @@
       <c r="S352" s="3"/>
       <c r="T352" s="3"/>
       <c r="U352" s="4" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -30910,7 +31012,7 @@
       <c r="S353" s="3"/>
       <c r="T353" s="3"/>
       <c r="U353" s="4" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -30936,7 +31038,7 @@
       <c r="S354" s="3"/>
       <c r="T354" s="3"/>
       <c r="U354" s="4" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -30962,7 +31064,7 @@
       <c r="S355" s="3"/>
       <c r="T355" s="3"/>
       <c r="U355" s="4" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -30988,7 +31090,7 @@
       <c r="S356" s="3"/>
       <c r="T356" s="3"/>
       <c r="U356" s="4" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -31014,7 +31116,7 @@
       <c r="S357" s="3"/>
       <c r="T357" s="3"/>
       <c r="U357" s="4" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -31040,7 +31142,7 @@
       <c r="S358" s="3"/>
       <c r="T358" s="3"/>
       <c r="U358" s="4" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -31066,7 +31168,7 @@
       <c r="S359" s="3"/>
       <c r="T359" s="3"/>
       <c r="U359" s="4" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -31092,7 +31194,7 @@
       <c r="S360" s="3"/>
       <c r="T360" s="3"/>
       <c r="U360" s="4" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -31118,7 +31220,7 @@
       <c r="S361" s="3"/>
       <c r="T361" s="3"/>
       <c r="U361" s="4" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -31144,7 +31246,7 @@
       <c r="S362" s="3"/>
       <c r="T362" s="3"/>
       <c r="U362" s="4" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -31170,7 +31272,7 @@
       <c r="S363" s="3"/>
       <c r="T363" s="3"/>
       <c r="U363" s="4" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -31196,7 +31298,7 @@
       <c r="S364" s="3"/>
       <c r="T364" s="3"/>
       <c r="U364" s="4" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -31222,7 +31324,7 @@
       <c r="S365" s="3"/>
       <c r="T365" s="3"/>
       <c r="U365" s="4" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -31248,7 +31350,7 @@
       <c r="S366" s="3"/>
       <c r="T366" s="3"/>
       <c r="U366" s="4" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -31274,7 +31376,7 @@
       <c r="S367" s="3"/>
       <c r="T367" s="3"/>
       <c r="U367" s="4" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -31300,7 +31402,7 @@
       <c r="S368" s="3"/>
       <c r="T368" s="3"/>
       <c r="U368" s="4" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -31326,7 +31428,7 @@
       <c r="S369" s="3"/>
       <c r="T369" s="3"/>
       <c r="U369" s="4" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -31352,7 +31454,7 @@
       <c r="S370" s="3"/>
       <c r="T370" s="3"/>
       <c r="U370" s="4" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -31378,7 +31480,7 @@
       <c r="S371" s="3"/>
       <c r="T371" s="3"/>
       <c r="U371" s="4" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -31404,7 +31506,7 @@
       <c r="S372" s="3"/>
       <c r="T372" s="3"/>
       <c r="U372" s="4" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -31430,7 +31532,7 @@
       <c r="S373" s="3"/>
       <c r="T373" s="3"/>
       <c r="U373" s="4" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -31456,7 +31558,7 @@
       <c r="S374" s="3"/>
       <c r="T374" s="3"/>
       <c r="U374" s="4" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -31482,7 +31584,7 @@
       <c r="S375" s="3"/>
       <c r="T375" s="3"/>
       <c r="U375" s="4" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -31508,7 +31610,7 @@
       <c r="S376" s="3"/>
       <c r="T376" s="3"/>
       <c r="U376" s="4" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -31534,7 +31636,7 @@
       <c r="S377" s="3"/>
       <c r="T377" s="3"/>
       <c r="U377" s="4" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -31560,7 +31662,7 @@
       <c r="S378" s="3"/>
       <c r="T378" s="3"/>
       <c r="U378" s="4" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -31586,7 +31688,7 @@
       <c r="S379" s="3"/>
       <c r="T379" s="3"/>
       <c r="U379" s="4" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -31612,7 +31714,7 @@
       <c r="S380" s="3"/>
       <c r="T380" s="3"/>
       <c r="U380" s="4" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -31638,7 +31740,7 @@
       <c r="S381" s="3"/>
       <c r="T381" s="3"/>
       <c r="U381" s="4" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -31664,7 +31766,7 @@
       <c r="S382" s="3"/>
       <c r="T382" s="3"/>
       <c r="U382" s="4" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -31690,7 +31792,7 @@
       <c r="S383" s="3"/>
       <c r="T383" s="3"/>
       <c r="U383" s="4" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -31716,7 +31818,7 @@
       <c r="S384" s="3"/>
       <c r="T384" s="3"/>
       <c r="U384" s="4" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -31742,7 +31844,7 @@
       <c r="S385" s="3"/>
       <c r="T385" s="3"/>
       <c r="U385" s="4" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -31768,7 +31870,7 @@
       <c r="S386" s="3"/>
       <c r="T386" s="3"/>
       <c r="U386" s="4" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -31794,7 +31896,7 @@
       <c r="S387" s="3"/>
       <c r="T387" s="3"/>
       <c r="U387" s="4" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -31820,7 +31922,7 @@
       <c r="S388" s="3"/>
       <c r="T388" s="3"/>
       <c r="U388" s="4" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -31846,7 +31948,7 @@
       <c r="S389" s="3"/>
       <c r="T389" s="3"/>
       <c r="U389" s="4" t="str">
-        <f t="shared" ref="U389:U390" si="13">IF(COUNTA(B389:T389)=0,"",AVERAGE(B389:T389))</f>
+        <f t="shared" ref="U389:U390" si="14">IF(COUNTA(B389:T389)=0,"",AVERAGE(B389:T389))</f>
         <v/>
       </c>
     </row>
@@ -31872,7 +31974,7 @@
       <c r="S390" s="3"/>
       <c r="T390" s="3"/>
       <c r="U390" s="4" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
@@ -31902,7 +32004,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="8" t="s">
         <v>37</v>
       </c>
       <c r="B1" s="7"/>
@@ -31917,7 +32019,7 @@
       <c r="K1" s="7"/>
     </row>
     <row r="2" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="6" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="7"/>
@@ -33227,19 +33329,39 @@
       </c>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A40" s="2"/>
-      <c r="B40" s="3"/>
-      <c r="C40" s="3"/>
-      <c r="D40" s="3"/>
-      <c r="E40" s="3"/>
-      <c r="F40" s="3"/>
-      <c r="G40" s="3"/>
-      <c r="H40" s="3"/>
-      <c r="I40" s="3"/>
-      <c r="J40" s="3"/>
-      <c r="K40" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
+      <c r="A40" s="2">
+        <v>46181</v>
+      </c>
+      <c r="B40" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="C40" s="3">
+        <v>3.14</v>
+      </c>
+      <c r="D40" s="3">
+        <v>2.83</v>
+      </c>
+      <c r="E40" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="F40" s="3">
+        <v>2.8</v>
+      </c>
+      <c r="G40" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="H40" s="3">
+        <v>2.63</v>
+      </c>
+      <c r="I40" s="3">
+        <v>2.74</v>
+      </c>
+      <c r="J40" s="3">
+        <v>2.59</v>
+      </c>
+      <c r="K40" s="4">
+        <f t="shared" ref="K40" si="8">IF(COUNTA(B40:J40)=0,"",AVERAGE(B40:J40))</f>
+        <v>2.8555555555555556</v>
       </c>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.25">
@@ -33702,7 +33824,7 @@
       <c r="I69" s="3"/>
       <c r="J69" s="3"/>
       <c r="K69" s="4" t="str">
-        <f t="shared" ref="K69:K132" si="8">IF(COUNTA(B69:J69)=0,"",AVERAGE(B69:J69))</f>
+        <f t="shared" ref="K69:K132" si="9">IF(COUNTA(B69:J69)=0,"",AVERAGE(B69:J69))</f>
         <v/>
       </c>
     </row>
@@ -33718,7 +33840,7 @@
       <c r="I70" s="3"/>
       <c r="J70" s="3"/>
       <c r="K70" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -33734,7 +33856,7 @@
       <c r="I71" s="3"/>
       <c r="J71" s="3"/>
       <c r="K71" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -33750,7 +33872,7 @@
       <c r="I72" s="3"/>
       <c r="J72" s="3"/>
       <c r="K72" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -33766,7 +33888,7 @@
       <c r="I73" s="3"/>
       <c r="J73" s="3"/>
       <c r="K73" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -33782,7 +33904,7 @@
       <c r="I74" s="3"/>
       <c r="J74" s="3"/>
       <c r="K74" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -33798,7 +33920,7 @@
       <c r="I75" s="3"/>
       <c r="J75" s="3"/>
       <c r="K75" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -33814,7 +33936,7 @@
       <c r="I76" s="3"/>
       <c r="J76" s="3"/>
       <c r="K76" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -33830,7 +33952,7 @@
       <c r="I77" s="3"/>
       <c r="J77" s="3"/>
       <c r="K77" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -33846,7 +33968,7 @@
       <c r="I78" s="3"/>
       <c r="J78" s="3"/>
       <c r="K78" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -33862,7 +33984,7 @@
       <c r="I79" s="3"/>
       <c r="J79" s="3"/>
       <c r="K79" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -33878,7 +34000,7 @@
       <c r="I80" s="3"/>
       <c r="J80" s="3"/>
       <c r="K80" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -33894,7 +34016,7 @@
       <c r="I81" s="3"/>
       <c r="J81" s="3"/>
       <c r="K81" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -33910,7 +34032,7 @@
       <c r="I82" s="3"/>
       <c r="J82" s="3"/>
       <c r="K82" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -33926,7 +34048,7 @@
       <c r="I83" s="3"/>
       <c r="J83" s="3"/>
       <c r="K83" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -33942,7 +34064,7 @@
       <c r="I84" s="3"/>
       <c r="J84" s="3"/>
       <c r="K84" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -33958,7 +34080,7 @@
       <c r="I85" s="3"/>
       <c r="J85" s="3"/>
       <c r="K85" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -33974,7 +34096,7 @@
       <c r="I86" s="3"/>
       <c r="J86" s="3"/>
       <c r="K86" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -33990,7 +34112,7 @@
       <c r="I87" s="3"/>
       <c r="J87" s="3"/>
       <c r="K87" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -34006,7 +34128,7 @@
       <c r="I88" s="3"/>
       <c r="J88" s="3"/>
       <c r="K88" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -34022,7 +34144,7 @@
       <c r="I89" s="3"/>
       <c r="J89" s="3"/>
       <c r="K89" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -34038,7 +34160,7 @@
       <c r="I90" s="3"/>
       <c r="J90" s="3"/>
       <c r="K90" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -34054,7 +34176,7 @@
       <c r="I91" s="3"/>
       <c r="J91" s="3"/>
       <c r="K91" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -34070,7 +34192,7 @@
       <c r="I92" s="3"/>
       <c r="J92" s="3"/>
       <c r="K92" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -34086,7 +34208,7 @@
       <c r="I93" s="3"/>
       <c r="J93" s="3"/>
       <c r="K93" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -34102,7 +34224,7 @@
       <c r="I94" s="3"/>
       <c r="J94" s="3"/>
       <c r="K94" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -34118,7 +34240,7 @@
       <c r="I95" s="3"/>
       <c r="J95" s="3"/>
       <c r="K95" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -34134,7 +34256,7 @@
       <c r="I96" s="3"/>
       <c r="J96" s="3"/>
       <c r="K96" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -34150,7 +34272,7 @@
       <c r="I97" s="3"/>
       <c r="J97" s="3"/>
       <c r="K97" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -34166,7 +34288,7 @@
       <c r="I98" s="3"/>
       <c r="J98" s="3"/>
       <c r="K98" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -34182,7 +34304,7 @@
       <c r="I99" s="3"/>
       <c r="J99" s="3"/>
       <c r="K99" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -34198,7 +34320,7 @@
       <c r="I100" s="3"/>
       <c r="J100" s="3"/>
       <c r="K100" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -34214,7 +34336,7 @@
       <c r="I101" s="3"/>
       <c r="J101" s="3"/>
       <c r="K101" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -34230,7 +34352,7 @@
       <c r="I102" s="3"/>
       <c r="J102" s="3"/>
       <c r="K102" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -34246,7 +34368,7 @@
       <c r="I103" s="3"/>
       <c r="J103" s="3"/>
       <c r="K103" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -34262,7 +34384,7 @@
       <c r="I104" s="3"/>
       <c r="J104" s="3"/>
       <c r="K104" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -34278,7 +34400,7 @@
       <c r="I105" s="3"/>
       <c r="J105" s="3"/>
       <c r="K105" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -34294,7 +34416,7 @@
       <c r="I106" s="3"/>
       <c r="J106" s="3"/>
       <c r="K106" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -34310,7 +34432,7 @@
       <c r="I107" s="3"/>
       <c r="J107" s="3"/>
       <c r="K107" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -34326,7 +34448,7 @@
       <c r="I108" s="3"/>
       <c r="J108" s="3"/>
       <c r="K108" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -34342,7 +34464,7 @@
       <c r="I109" s="3"/>
       <c r="J109" s="3"/>
       <c r="K109" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -34358,7 +34480,7 @@
       <c r="I110" s="3"/>
       <c r="J110" s="3"/>
       <c r="K110" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -34374,7 +34496,7 @@
       <c r="I111" s="3"/>
       <c r="J111" s="3"/>
       <c r="K111" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -34390,7 +34512,7 @@
       <c r="I112" s="3"/>
       <c r="J112" s="3"/>
       <c r="K112" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -34406,7 +34528,7 @@
       <c r="I113" s="3"/>
       <c r="J113" s="3"/>
       <c r="K113" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -34422,7 +34544,7 @@
       <c r="I114" s="3"/>
       <c r="J114" s="3"/>
       <c r="K114" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -34438,7 +34560,7 @@
       <c r="I115" s="3"/>
       <c r="J115" s="3"/>
       <c r="K115" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -34454,7 +34576,7 @@
       <c r="I116" s="3"/>
       <c r="J116" s="3"/>
       <c r="K116" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -34470,7 +34592,7 @@
       <c r="I117" s="3"/>
       <c r="J117" s="3"/>
       <c r="K117" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -34486,7 +34608,7 @@
       <c r="I118" s="3"/>
       <c r="J118" s="3"/>
       <c r="K118" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -34502,7 +34624,7 @@
       <c r="I119" s="3"/>
       <c r="J119" s="3"/>
       <c r="K119" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -34518,7 +34640,7 @@
       <c r="I120" s="3"/>
       <c r="J120" s="3"/>
       <c r="K120" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -34534,7 +34656,7 @@
       <c r="I121" s="3"/>
       <c r="J121" s="3"/>
       <c r="K121" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -34550,7 +34672,7 @@
       <c r="I122" s="3"/>
       <c r="J122" s="3"/>
       <c r="K122" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -34566,7 +34688,7 @@
       <c r="I123" s="3"/>
       <c r="J123" s="3"/>
       <c r="K123" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -34582,7 +34704,7 @@
       <c r="I124" s="3"/>
       <c r="J124" s="3"/>
       <c r="K124" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -34598,7 +34720,7 @@
       <c r="I125" s="3"/>
       <c r="J125" s="3"/>
       <c r="K125" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -34614,7 +34736,7 @@
       <c r="I126" s="3"/>
       <c r="J126" s="3"/>
       <c r="K126" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -34630,7 +34752,7 @@
       <c r="I127" s="3"/>
       <c r="J127" s="3"/>
       <c r="K127" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -34646,7 +34768,7 @@
       <c r="I128" s="3"/>
       <c r="J128" s="3"/>
       <c r="K128" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -34662,7 +34784,7 @@
       <c r="I129" s="3"/>
       <c r="J129" s="3"/>
       <c r="K129" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -34678,7 +34800,7 @@
       <c r="I130" s="3"/>
       <c r="J130" s="3"/>
       <c r="K130" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -34694,7 +34816,7 @@
       <c r="I131" s="3"/>
       <c r="J131" s="3"/>
       <c r="K131" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -34710,7 +34832,7 @@
       <c r="I132" s="3"/>
       <c r="J132" s="3"/>
       <c r="K132" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -34726,7 +34848,7 @@
       <c r="I133" s="3"/>
       <c r="J133" s="3"/>
       <c r="K133" s="4" t="str">
-        <f t="shared" ref="K133:K196" si="9">IF(COUNTA(B133:J133)=0,"",AVERAGE(B133:J133))</f>
+        <f t="shared" ref="K133:K196" si="10">IF(COUNTA(B133:J133)=0,"",AVERAGE(B133:J133))</f>
         <v/>
       </c>
     </row>
@@ -34742,7 +34864,7 @@
       <c r="I134" s="3"/>
       <c r="J134" s="3"/>
       <c r="K134" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -34758,7 +34880,7 @@
       <c r="I135" s="3"/>
       <c r="J135" s="3"/>
       <c r="K135" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -34774,7 +34896,7 @@
       <c r="I136" s="3"/>
       <c r="J136" s="3"/>
       <c r="K136" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -34790,7 +34912,7 @@
       <c r="I137" s="3"/>
       <c r="J137" s="3"/>
       <c r="K137" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -34806,7 +34928,7 @@
       <c r="I138" s="3"/>
       <c r="J138" s="3"/>
       <c r="K138" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -34822,7 +34944,7 @@
       <c r="I139" s="3"/>
       <c r="J139" s="3"/>
       <c r="K139" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -34838,7 +34960,7 @@
       <c r="I140" s="3"/>
       <c r="J140" s="3"/>
       <c r="K140" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -34854,7 +34976,7 @@
       <c r="I141" s="3"/>
       <c r="J141" s="3"/>
       <c r="K141" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -34870,7 +34992,7 @@
       <c r="I142" s="3"/>
       <c r="J142" s="3"/>
       <c r="K142" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -34886,7 +35008,7 @@
       <c r="I143" s="3"/>
       <c r="J143" s="3"/>
       <c r="K143" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -34902,7 +35024,7 @@
       <c r="I144" s="3"/>
       <c r="J144" s="3"/>
       <c r="K144" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -34918,7 +35040,7 @@
       <c r="I145" s="3"/>
       <c r="J145" s="3"/>
       <c r="K145" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -34934,7 +35056,7 @@
       <c r="I146" s="3"/>
       <c r="J146" s="3"/>
       <c r="K146" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -34950,7 +35072,7 @@
       <c r="I147" s="3"/>
       <c r="J147" s="3"/>
       <c r="K147" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -34966,7 +35088,7 @@
       <c r="I148" s="3"/>
       <c r="J148" s="3"/>
       <c r="K148" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -34982,7 +35104,7 @@
       <c r="I149" s="3"/>
       <c r="J149" s="3"/>
       <c r="K149" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -34998,7 +35120,7 @@
       <c r="I150" s="3"/>
       <c r="J150" s="3"/>
       <c r="K150" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -35014,7 +35136,7 @@
       <c r="I151" s="3"/>
       <c r="J151" s="3"/>
       <c r="K151" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -35030,7 +35152,7 @@
       <c r="I152" s="3"/>
       <c r="J152" s="3"/>
       <c r="K152" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -35046,7 +35168,7 @@
       <c r="I153" s="3"/>
       <c r="J153" s="3"/>
       <c r="K153" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -35062,7 +35184,7 @@
       <c r="I154" s="3"/>
       <c r="J154" s="3"/>
       <c r="K154" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -35078,7 +35200,7 @@
       <c r="I155" s="3"/>
       <c r="J155" s="3"/>
       <c r="K155" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -35094,7 +35216,7 @@
       <c r="I156" s="3"/>
       <c r="J156" s="3"/>
       <c r="K156" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -35110,7 +35232,7 @@
       <c r="I157" s="3"/>
       <c r="J157" s="3"/>
       <c r="K157" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -35126,7 +35248,7 @@
       <c r="I158" s="3"/>
       <c r="J158" s="3"/>
       <c r="K158" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -35142,7 +35264,7 @@
       <c r="I159" s="3"/>
       <c r="J159" s="3"/>
       <c r="K159" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -35158,7 +35280,7 @@
       <c r="I160" s="3"/>
       <c r="J160" s="3"/>
       <c r="K160" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -35174,7 +35296,7 @@
       <c r="I161" s="3"/>
       <c r="J161" s="3"/>
       <c r="K161" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -35190,7 +35312,7 @@
       <c r="I162" s="3"/>
       <c r="J162" s="3"/>
       <c r="K162" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -35206,7 +35328,7 @@
       <c r="I163" s="3"/>
       <c r="J163" s="3"/>
       <c r="K163" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -35222,7 +35344,7 @@
       <c r="I164" s="3"/>
       <c r="J164" s="3"/>
       <c r="K164" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -35238,7 +35360,7 @@
       <c r="I165" s="3"/>
       <c r="J165" s="3"/>
       <c r="K165" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -35254,7 +35376,7 @@
       <c r="I166" s="3"/>
       <c r="J166" s="3"/>
       <c r="K166" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -35270,7 +35392,7 @@
       <c r="I167" s="3"/>
       <c r="J167" s="3"/>
       <c r="K167" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -35286,7 +35408,7 @@
       <c r="I168" s="3"/>
       <c r="J168" s="3"/>
       <c r="K168" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -35302,7 +35424,7 @@
       <c r="I169" s="3"/>
       <c r="J169" s="3"/>
       <c r="K169" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -35318,7 +35440,7 @@
       <c r="I170" s="3"/>
       <c r="J170" s="3"/>
       <c r="K170" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -35334,7 +35456,7 @@
       <c r="I171" s="3"/>
       <c r="J171" s="3"/>
       <c r="K171" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -35350,7 +35472,7 @@
       <c r="I172" s="3"/>
       <c r="J172" s="3"/>
       <c r="K172" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -35366,7 +35488,7 @@
       <c r="I173" s="3"/>
       <c r="J173" s="3"/>
       <c r="K173" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -35382,7 +35504,7 @@
       <c r="I174" s="3"/>
       <c r="J174" s="3"/>
       <c r="K174" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -35398,7 +35520,7 @@
       <c r="I175" s="3"/>
       <c r="J175" s="3"/>
       <c r="K175" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -35414,7 +35536,7 @@
       <c r="I176" s="3"/>
       <c r="J176" s="3"/>
       <c r="K176" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -35430,7 +35552,7 @@
       <c r="I177" s="3"/>
       <c r="J177" s="3"/>
       <c r="K177" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -35446,7 +35568,7 @@
       <c r="I178" s="3"/>
       <c r="J178" s="3"/>
       <c r="K178" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -35462,7 +35584,7 @@
       <c r="I179" s="3"/>
       <c r="J179" s="3"/>
       <c r="K179" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -35478,7 +35600,7 @@
       <c r="I180" s="3"/>
       <c r="J180" s="3"/>
       <c r="K180" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -35494,7 +35616,7 @@
       <c r="I181" s="3"/>
       <c r="J181" s="3"/>
       <c r="K181" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -35510,7 +35632,7 @@
       <c r="I182" s="3"/>
       <c r="J182" s="3"/>
       <c r="K182" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -35526,7 +35648,7 @@
       <c r="I183" s="3"/>
       <c r="J183" s="3"/>
       <c r="K183" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -35542,7 +35664,7 @@
       <c r="I184" s="3"/>
       <c r="J184" s="3"/>
       <c r="K184" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -35558,7 +35680,7 @@
       <c r="I185" s="3"/>
       <c r="J185" s="3"/>
       <c r="K185" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -35574,7 +35696,7 @@
       <c r="I186" s="3"/>
       <c r="J186" s="3"/>
       <c r="K186" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -35590,7 +35712,7 @@
       <c r="I187" s="3"/>
       <c r="J187" s="3"/>
       <c r="K187" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -35606,7 +35728,7 @@
       <c r="I188" s="3"/>
       <c r="J188" s="3"/>
       <c r="K188" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -35622,7 +35744,7 @@
       <c r="I189" s="3"/>
       <c r="J189" s="3"/>
       <c r="K189" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -35638,7 +35760,7 @@
       <c r="I190" s="3"/>
       <c r="J190" s="3"/>
       <c r="K190" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -35654,7 +35776,7 @@
       <c r="I191" s="3"/>
       <c r="J191" s="3"/>
       <c r="K191" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -35670,7 +35792,7 @@
       <c r="I192" s="3"/>
       <c r="J192" s="3"/>
       <c r="K192" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -35686,7 +35808,7 @@
       <c r="I193" s="3"/>
       <c r="J193" s="3"/>
       <c r="K193" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -35702,7 +35824,7 @@
       <c r="I194" s="3"/>
       <c r="J194" s="3"/>
       <c r="K194" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -35718,7 +35840,7 @@
       <c r="I195" s="3"/>
       <c r="J195" s="3"/>
       <c r="K195" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -35734,7 +35856,7 @@
       <c r="I196" s="3"/>
       <c r="J196" s="3"/>
       <c r="K196" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -35750,7 +35872,7 @@
       <c r="I197" s="3"/>
       <c r="J197" s="3"/>
       <c r="K197" s="4" t="str">
-        <f t="shared" ref="K197:K260" si="10">IF(COUNTA(B197:J197)=0,"",AVERAGE(B197:J197))</f>
+        <f t="shared" ref="K197:K260" si="11">IF(COUNTA(B197:J197)=0,"",AVERAGE(B197:J197))</f>
         <v/>
       </c>
     </row>
@@ -35766,7 +35888,7 @@
       <c r="I198" s="3"/>
       <c r="J198" s="3"/>
       <c r="K198" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -35782,7 +35904,7 @@
       <c r="I199" s="3"/>
       <c r="J199" s="3"/>
       <c r="K199" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -35798,7 +35920,7 @@
       <c r="I200" s="3"/>
       <c r="J200" s="3"/>
       <c r="K200" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -35814,7 +35936,7 @@
       <c r="I201" s="3"/>
       <c r="J201" s="3"/>
       <c r="K201" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -35830,7 +35952,7 @@
       <c r="I202" s="3"/>
       <c r="J202" s="3"/>
       <c r="K202" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -35846,7 +35968,7 @@
       <c r="I203" s="3"/>
       <c r="J203" s="3"/>
       <c r="K203" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -35862,7 +35984,7 @@
       <c r="I204" s="3"/>
       <c r="J204" s="3"/>
       <c r="K204" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -35878,7 +36000,7 @@
       <c r="I205" s="3"/>
       <c r="J205" s="3"/>
       <c r="K205" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -35894,7 +36016,7 @@
       <c r="I206" s="3"/>
       <c r="J206" s="3"/>
       <c r="K206" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -35910,7 +36032,7 @@
       <c r="I207" s="3"/>
       <c r="J207" s="3"/>
       <c r="K207" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -35926,7 +36048,7 @@
       <c r="I208" s="3"/>
       <c r="J208" s="3"/>
       <c r="K208" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -35942,7 +36064,7 @@
       <c r="I209" s="3"/>
       <c r="J209" s="3"/>
       <c r="K209" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -35958,7 +36080,7 @@
       <c r="I210" s="3"/>
       <c r="J210" s="3"/>
       <c r="K210" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -35974,7 +36096,7 @@
       <c r="I211" s="3"/>
       <c r="J211" s="3"/>
       <c r="K211" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -35990,7 +36112,7 @@
       <c r="I212" s="3"/>
       <c r="J212" s="3"/>
       <c r="K212" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -36006,7 +36128,7 @@
       <c r="I213" s="3"/>
       <c r="J213" s="3"/>
       <c r="K213" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -36022,7 +36144,7 @@
       <c r="I214" s="3"/>
       <c r="J214" s="3"/>
       <c r="K214" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -36038,7 +36160,7 @@
       <c r="I215" s="3"/>
       <c r="J215" s="3"/>
       <c r="K215" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -36054,7 +36176,7 @@
       <c r="I216" s="3"/>
       <c r="J216" s="3"/>
       <c r="K216" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -36070,7 +36192,7 @@
       <c r="I217" s="3"/>
       <c r="J217" s="3"/>
       <c r="K217" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -36086,7 +36208,7 @@
       <c r="I218" s="3"/>
       <c r="J218" s="3"/>
       <c r="K218" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -36102,7 +36224,7 @@
       <c r="I219" s="3"/>
       <c r="J219" s="3"/>
       <c r="K219" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -36118,7 +36240,7 @@
       <c r="I220" s="3"/>
       <c r="J220" s="3"/>
       <c r="K220" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -36134,7 +36256,7 @@
       <c r="I221" s="3"/>
       <c r="J221" s="3"/>
       <c r="K221" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -36150,7 +36272,7 @@
       <c r="I222" s="3"/>
       <c r="J222" s="3"/>
       <c r="K222" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -36166,7 +36288,7 @@
       <c r="I223" s="3"/>
       <c r="J223" s="3"/>
       <c r="K223" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -36182,7 +36304,7 @@
       <c r="I224" s="3"/>
       <c r="J224" s="3"/>
       <c r="K224" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -36198,7 +36320,7 @@
       <c r="I225" s="3"/>
       <c r="J225" s="3"/>
       <c r="K225" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -36214,7 +36336,7 @@
       <c r="I226" s="3"/>
       <c r="J226" s="3"/>
       <c r="K226" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -36230,7 +36352,7 @@
       <c r="I227" s="3"/>
       <c r="J227" s="3"/>
       <c r="K227" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -36246,7 +36368,7 @@
       <c r="I228" s="3"/>
       <c r="J228" s="3"/>
       <c r="K228" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -36262,7 +36384,7 @@
       <c r="I229" s="3"/>
       <c r="J229" s="3"/>
       <c r="K229" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -36278,7 +36400,7 @@
       <c r="I230" s="3"/>
       <c r="J230" s="3"/>
       <c r="K230" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -36294,7 +36416,7 @@
       <c r="I231" s="3"/>
       <c r="J231" s="3"/>
       <c r="K231" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -36310,7 +36432,7 @@
       <c r="I232" s="3"/>
       <c r="J232" s="3"/>
       <c r="K232" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -36326,7 +36448,7 @@
       <c r="I233" s="3"/>
       <c r="J233" s="3"/>
       <c r="K233" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -36342,7 +36464,7 @@
       <c r="I234" s="3"/>
       <c r="J234" s="3"/>
       <c r="K234" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -36358,7 +36480,7 @@
       <c r="I235" s="3"/>
       <c r="J235" s="3"/>
       <c r="K235" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -36374,7 +36496,7 @@
       <c r="I236" s="3"/>
       <c r="J236" s="3"/>
       <c r="K236" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -36390,7 +36512,7 @@
       <c r="I237" s="3"/>
       <c r="J237" s="3"/>
       <c r="K237" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -36406,7 +36528,7 @@
       <c r="I238" s="3"/>
       <c r="J238" s="3"/>
       <c r="K238" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -36422,7 +36544,7 @@
       <c r="I239" s="3"/>
       <c r="J239" s="3"/>
       <c r="K239" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -36438,7 +36560,7 @@
       <c r="I240" s="3"/>
       <c r="J240" s="3"/>
       <c r="K240" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -36454,7 +36576,7 @@
       <c r="I241" s="3"/>
       <c r="J241" s="3"/>
       <c r="K241" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -36470,7 +36592,7 @@
       <c r="I242" s="3"/>
       <c r="J242" s="3"/>
       <c r="K242" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -36486,7 +36608,7 @@
       <c r="I243" s="3"/>
       <c r="J243" s="3"/>
       <c r="K243" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -36502,7 +36624,7 @@
       <c r="I244" s="3"/>
       <c r="J244" s="3"/>
       <c r="K244" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -36518,7 +36640,7 @@
       <c r="I245" s="3"/>
       <c r="J245" s="3"/>
       <c r="K245" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -36534,7 +36656,7 @@
       <c r="I246" s="3"/>
       <c r="J246" s="3"/>
       <c r="K246" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -36550,7 +36672,7 @@
       <c r="I247" s="3"/>
       <c r="J247" s="3"/>
       <c r="K247" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -36566,7 +36688,7 @@
       <c r="I248" s="3"/>
       <c r="J248" s="3"/>
       <c r="K248" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -36582,7 +36704,7 @@
       <c r="I249" s="3"/>
       <c r="J249" s="3"/>
       <c r="K249" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -36598,7 +36720,7 @@
       <c r="I250" s="3"/>
       <c r="J250" s="3"/>
       <c r="K250" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -36614,7 +36736,7 @@
       <c r="I251" s="3"/>
       <c r="J251" s="3"/>
       <c r="K251" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -36630,7 +36752,7 @@
       <c r="I252" s="3"/>
       <c r="J252" s="3"/>
       <c r="K252" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -36646,7 +36768,7 @@
       <c r="I253" s="3"/>
       <c r="J253" s="3"/>
       <c r="K253" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -36662,7 +36784,7 @@
       <c r="I254" s="3"/>
       <c r="J254" s="3"/>
       <c r="K254" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -36678,7 +36800,7 @@
       <c r="I255" s="3"/>
       <c r="J255" s="3"/>
       <c r="K255" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -36694,7 +36816,7 @@
       <c r="I256" s="3"/>
       <c r="J256" s="3"/>
       <c r="K256" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -36710,7 +36832,7 @@
       <c r="I257" s="3"/>
       <c r="J257" s="3"/>
       <c r="K257" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -36726,7 +36848,7 @@
       <c r="I258" s="3"/>
       <c r="J258" s="3"/>
       <c r="K258" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -36742,7 +36864,7 @@
       <c r="I259" s="3"/>
       <c r="J259" s="3"/>
       <c r="K259" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -36758,7 +36880,7 @@
       <c r="I260" s="3"/>
       <c r="J260" s="3"/>
       <c r="K260" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -36774,7 +36896,7 @@
       <c r="I261" s="3"/>
       <c r="J261" s="3"/>
       <c r="K261" s="4" t="str">
-        <f t="shared" ref="K261:K324" si="11">IF(COUNTA(B261:J261)=0,"",AVERAGE(B261:J261))</f>
+        <f t="shared" ref="K261:K324" si="12">IF(COUNTA(B261:J261)=0,"",AVERAGE(B261:J261))</f>
         <v/>
       </c>
     </row>
@@ -36790,7 +36912,7 @@
       <c r="I262" s="3"/>
       <c r="J262" s="3"/>
       <c r="K262" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -36806,7 +36928,7 @@
       <c r="I263" s="3"/>
       <c r="J263" s="3"/>
       <c r="K263" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -36822,7 +36944,7 @@
       <c r="I264" s="3"/>
       <c r="J264" s="3"/>
       <c r="K264" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -36838,7 +36960,7 @@
       <c r="I265" s="3"/>
       <c r="J265" s="3"/>
       <c r="K265" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -36854,7 +36976,7 @@
       <c r="I266" s="3"/>
       <c r="J266" s="3"/>
       <c r="K266" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -36870,7 +36992,7 @@
       <c r="I267" s="3"/>
       <c r="J267" s="3"/>
       <c r="K267" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -36886,7 +37008,7 @@
       <c r="I268" s="3"/>
       <c r="J268" s="3"/>
       <c r="K268" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -36902,7 +37024,7 @@
       <c r="I269" s="3"/>
       <c r="J269" s="3"/>
       <c r="K269" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -36918,7 +37040,7 @@
       <c r="I270" s="3"/>
       <c r="J270" s="3"/>
       <c r="K270" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -36934,7 +37056,7 @@
       <c r="I271" s="3"/>
       <c r="J271" s="3"/>
       <c r="K271" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -36950,7 +37072,7 @@
       <c r="I272" s="3"/>
       <c r="J272" s="3"/>
       <c r="K272" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -36966,7 +37088,7 @@
       <c r="I273" s="3"/>
       <c r="J273" s="3"/>
       <c r="K273" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -36982,7 +37104,7 @@
       <c r="I274" s="3"/>
       <c r="J274" s="3"/>
       <c r="K274" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -36998,7 +37120,7 @@
       <c r="I275" s="3"/>
       <c r="J275" s="3"/>
       <c r="K275" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -37014,7 +37136,7 @@
       <c r="I276" s="3"/>
       <c r="J276" s="3"/>
       <c r="K276" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -37030,7 +37152,7 @@
       <c r="I277" s="3"/>
       <c r="J277" s="3"/>
       <c r="K277" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -37046,7 +37168,7 @@
       <c r="I278" s="3"/>
       <c r="J278" s="3"/>
       <c r="K278" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -37062,7 +37184,7 @@
       <c r="I279" s="3"/>
       <c r="J279" s="3"/>
       <c r="K279" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -37078,7 +37200,7 @@
       <c r="I280" s="3"/>
       <c r="J280" s="3"/>
       <c r="K280" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -37094,7 +37216,7 @@
       <c r="I281" s="3"/>
       <c r="J281" s="3"/>
       <c r="K281" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -37110,7 +37232,7 @@
       <c r="I282" s="3"/>
       <c r="J282" s="3"/>
       <c r="K282" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -37126,7 +37248,7 @@
       <c r="I283" s="3"/>
       <c r="J283" s="3"/>
       <c r="K283" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -37142,7 +37264,7 @@
       <c r="I284" s="3"/>
       <c r="J284" s="3"/>
       <c r="K284" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -37158,7 +37280,7 @@
       <c r="I285" s="3"/>
       <c r="J285" s="3"/>
       <c r="K285" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -37174,7 +37296,7 @@
       <c r="I286" s="3"/>
       <c r="J286" s="3"/>
       <c r="K286" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -37190,7 +37312,7 @@
       <c r="I287" s="3"/>
       <c r="J287" s="3"/>
       <c r="K287" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -37206,7 +37328,7 @@
       <c r="I288" s="3"/>
       <c r="J288" s="3"/>
       <c r="K288" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -37222,7 +37344,7 @@
       <c r="I289" s="3"/>
       <c r="J289" s="3"/>
       <c r="K289" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -37238,7 +37360,7 @@
       <c r="I290" s="3"/>
       <c r="J290" s="3"/>
       <c r="K290" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -37254,7 +37376,7 @@
       <c r="I291" s="3"/>
       <c r="J291" s="3"/>
       <c r="K291" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -37270,7 +37392,7 @@
       <c r="I292" s="3"/>
       <c r="J292" s="3"/>
       <c r="K292" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -37286,7 +37408,7 @@
       <c r="I293" s="3"/>
       <c r="J293" s="3"/>
       <c r="K293" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -37302,7 +37424,7 @@
       <c r="I294" s="3"/>
       <c r="J294" s="3"/>
       <c r="K294" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -37318,7 +37440,7 @@
       <c r="I295" s="3"/>
       <c r="J295" s="3"/>
       <c r="K295" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -37334,7 +37456,7 @@
       <c r="I296" s="3"/>
       <c r="J296" s="3"/>
       <c r="K296" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -37350,7 +37472,7 @@
       <c r="I297" s="3"/>
       <c r="J297" s="3"/>
       <c r="K297" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -37366,7 +37488,7 @@
       <c r="I298" s="3"/>
       <c r="J298" s="3"/>
       <c r="K298" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -37382,7 +37504,7 @@
       <c r="I299" s="3"/>
       <c r="J299" s="3"/>
       <c r="K299" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -37398,7 +37520,7 @@
       <c r="I300" s="3"/>
       <c r="J300" s="3"/>
       <c r="K300" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -37414,7 +37536,7 @@
       <c r="I301" s="3"/>
       <c r="J301" s="3"/>
       <c r="K301" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -37430,7 +37552,7 @@
       <c r="I302" s="3"/>
       <c r="J302" s="3"/>
       <c r="K302" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -37446,7 +37568,7 @@
       <c r="I303" s="3"/>
       <c r="J303" s="3"/>
       <c r="K303" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -37462,7 +37584,7 @@
       <c r="I304" s="3"/>
       <c r="J304" s="3"/>
       <c r="K304" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -37478,7 +37600,7 @@
       <c r="I305" s="3"/>
       <c r="J305" s="3"/>
       <c r="K305" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -37494,7 +37616,7 @@
       <c r="I306" s="3"/>
       <c r="J306" s="3"/>
       <c r="K306" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -37510,7 +37632,7 @@
       <c r="I307" s="3"/>
       <c r="J307" s="3"/>
       <c r="K307" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -37526,7 +37648,7 @@
       <c r="I308" s="3"/>
       <c r="J308" s="3"/>
       <c r="K308" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -37542,7 +37664,7 @@
       <c r="I309" s="3"/>
       <c r="J309" s="3"/>
       <c r="K309" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -37558,7 +37680,7 @@
       <c r="I310" s="3"/>
       <c r="J310" s="3"/>
       <c r="K310" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -37574,7 +37696,7 @@
       <c r="I311" s="3"/>
       <c r="J311" s="3"/>
       <c r="K311" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -37590,7 +37712,7 @@
       <c r="I312" s="3"/>
       <c r="J312" s="3"/>
       <c r="K312" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -37606,7 +37728,7 @@
       <c r="I313" s="3"/>
       <c r="J313" s="3"/>
       <c r="K313" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -37622,7 +37744,7 @@
       <c r="I314" s="3"/>
       <c r="J314" s="3"/>
       <c r="K314" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -37638,7 +37760,7 @@
       <c r="I315" s="3"/>
       <c r="J315" s="3"/>
       <c r="K315" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -37654,7 +37776,7 @@
       <c r="I316" s="3"/>
       <c r="J316" s="3"/>
       <c r="K316" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -37670,7 +37792,7 @@
       <c r="I317" s="3"/>
       <c r="J317" s="3"/>
       <c r="K317" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -37686,7 +37808,7 @@
       <c r="I318" s="3"/>
       <c r="J318" s="3"/>
       <c r="K318" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -37702,7 +37824,7 @@
       <c r="I319" s="3"/>
       <c r="J319" s="3"/>
       <c r="K319" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -37718,7 +37840,7 @@
       <c r="I320" s="3"/>
       <c r="J320" s="3"/>
       <c r="K320" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -37734,7 +37856,7 @@
       <c r="I321" s="3"/>
       <c r="J321" s="3"/>
       <c r="K321" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -37750,7 +37872,7 @@
       <c r="I322" s="3"/>
       <c r="J322" s="3"/>
       <c r="K322" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -37766,7 +37888,7 @@
       <c r="I323" s="3"/>
       <c r="J323" s="3"/>
       <c r="K323" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -37782,7 +37904,7 @@
       <c r="I324" s="3"/>
       <c r="J324" s="3"/>
       <c r="K324" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -37798,7 +37920,7 @@
       <c r="I325" s="3"/>
       <c r="J325" s="3"/>
       <c r="K325" s="4" t="str">
-        <f t="shared" ref="K325:K388" si="12">IF(COUNTA(B325:J325)=0,"",AVERAGE(B325:J325))</f>
+        <f t="shared" ref="K325:K388" si="13">IF(COUNTA(B325:J325)=0,"",AVERAGE(B325:J325))</f>
         <v/>
       </c>
     </row>
@@ -37814,7 +37936,7 @@
       <c r="I326" s="3"/>
       <c r="J326" s="3"/>
       <c r="K326" s="4" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -37830,7 +37952,7 @@
       <c r="I327" s="3"/>
       <c r="J327" s="3"/>
       <c r="K327" s="4" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -37846,7 +37968,7 @@
       <c r="I328" s="3"/>
       <c r="J328" s="3"/>
       <c r="K328" s="4" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -37862,7 +37984,7 @@
       <c r="I329" s="3"/>
       <c r="J329" s="3"/>
       <c r="K329" s="4" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -37878,7 +38000,7 @@
       <c r="I330" s="3"/>
       <c r="J330" s="3"/>
       <c r="K330" s="4" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -37894,7 +38016,7 @@
       <c r="I331" s="3"/>
       <c r="J331" s="3"/>
       <c r="K331" s="4" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -37910,7 +38032,7 @@
       <c r="I332" s="3"/>
       <c r="J332" s="3"/>
       <c r="K332" s="4" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -37926,7 +38048,7 @@
       <c r="I333" s="3"/>
       <c r="J333" s="3"/>
       <c r="K333" s="4" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -37942,7 +38064,7 @@
       <c r="I334" s="3"/>
       <c r="J334" s="3"/>
       <c r="K334" s="4" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -37958,7 +38080,7 @@
       <c r="I335" s="3"/>
       <c r="J335" s="3"/>
       <c r="K335" s="4" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -37974,7 +38096,7 @@
       <c r="I336" s="3"/>
       <c r="J336" s="3"/>
       <c r="K336" s="4" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -37990,7 +38112,7 @@
       <c r="I337" s="3"/>
       <c r="J337" s="3"/>
       <c r="K337" s="4" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -38006,7 +38128,7 @@
       <c r="I338" s="3"/>
       <c r="J338" s="3"/>
       <c r="K338" s="4" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -38022,7 +38144,7 @@
       <c r="I339" s="3"/>
       <c r="J339" s="3"/>
       <c r="K339" s="4" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -38038,7 +38160,7 @@
       <c r="I340" s="3"/>
       <c r="J340" s="3"/>
       <c r="K340" s="4" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -38054,7 +38176,7 @@
       <c r="I341" s="3"/>
       <c r="J341" s="3"/>
       <c r="K341" s="4" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -38070,7 +38192,7 @@
       <c r="I342" s="3"/>
       <c r="J342" s="3"/>
       <c r="K342" s="4" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -38086,7 +38208,7 @@
       <c r="I343" s="3"/>
       <c r="J343" s="3"/>
       <c r="K343" s="4" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -38102,7 +38224,7 @@
       <c r="I344" s="3"/>
       <c r="J344" s="3"/>
       <c r="K344" s="4" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -38118,7 +38240,7 @@
       <c r="I345" s="3"/>
       <c r="J345" s="3"/>
       <c r="K345" s="4" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -38134,7 +38256,7 @@
       <c r="I346" s="3"/>
       <c r="J346" s="3"/>
       <c r="K346" s="4" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -38150,7 +38272,7 @@
       <c r="I347" s="3"/>
       <c r="J347" s="3"/>
       <c r="K347" s="4" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -38166,7 +38288,7 @@
       <c r="I348" s="3"/>
       <c r="J348" s="3"/>
       <c r="K348" s="4" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -38182,7 +38304,7 @@
       <c r="I349" s="3"/>
       <c r="J349" s="3"/>
       <c r="K349" s="4" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -38198,7 +38320,7 @@
       <c r="I350" s="3"/>
       <c r="J350" s="3"/>
       <c r="K350" s="4" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -38214,7 +38336,7 @@
       <c r="I351" s="3"/>
       <c r="J351" s="3"/>
       <c r="K351" s="4" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -38230,7 +38352,7 @@
       <c r="I352" s="3"/>
       <c r="J352" s="3"/>
       <c r="K352" s="4" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -38246,7 +38368,7 @@
       <c r="I353" s="3"/>
       <c r="J353" s="3"/>
       <c r="K353" s="4" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -38262,7 +38384,7 @@
       <c r="I354" s="3"/>
       <c r="J354" s="3"/>
       <c r="K354" s="4" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -38278,7 +38400,7 @@
       <c r="I355" s="3"/>
       <c r="J355" s="3"/>
       <c r="K355" s="4" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -38294,7 +38416,7 @@
       <c r="I356" s="3"/>
       <c r="J356" s="3"/>
       <c r="K356" s="4" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -38310,7 +38432,7 @@
       <c r="I357" s="3"/>
       <c r="J357" s="3"/>
       <c r="K357" s="4" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -38326,7 +38448,7 @@
       <c r="I358" s="3"/>
       <c r="J358" s="3"/>
       <c r="K358" s="4" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -38342,7 +38464,7 @@
       <c r="I359" s="3"/>
       <c r="J359" s="3"/>
       <c r="K359" s="4" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -38358,7 +38480,7 @@
       <c r="I360" s="3"/>
       <c r="J360" s="3"/>
       <c r="K360" s="4" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -38374,7 +38496,7 @@
       <c r="I361" s="3"/>
       <c r="J361" s="3"/>
       <c r="K361" s="4" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -38390,7 +38512,7 @@
       <c r="I362" s="3"/>
       <c r="J362" s="3"/>
       <c r="K362" s="4" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -38406,7 +38528,7 @@
       <c r="I363" s="3"/>
       <c r="J363" s="3"/>
       <c r="K363" s="4" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -38422,7 +38544,7 @@
       <c r="I364" s="3"/>
       <c r="J364" s="3"/>
       <c r="K364" s="4" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -38438,7 +38560,7 @@
       <c r="I365" s="3"/>
       <c r="J365" s="3"/>
       <c r="K365" s="4" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -38454,7 +38576,7 @@
       <c r="I366" s="3"/>
       <c r="J366" s="3"/>
       <c r="K366" s="4" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -38470,7 +38592,7 @@
       <c r="I367" s="3"/>
       <c r="J367" s="3"/>
       <c r="K367" s="4" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -38486,7 +38608,7 @@
       <c r="I368" s="3"/>
       <c r="J368" s="3"/>
       <c r="K368" s="4" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -38502,7 +38624,7 @@
       <c r="I369" s="3"/>
       <c r="J369" s="3"/>
       <c r="K369" s="4" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -38518,7 +38640,7 @@
       <c r="I370" s="3"/>
       <c r="J370" s="3"/>
       <c r="K370" s="4" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -38534,7 +38656,7 @@
       <c r="I371" s="3"/>
       <c r="J371" s="3"/>
       <c r="K371" s="4" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -38550,7 +38672,7 @@
       <c r="I372" s="3"/>
       <c r="J372" s="3"/>
       <c r="K372" s="4" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -38566,7 +38688,7 @@
       <c r="I373" s="3"/>
       <c r="J373" s="3"/>
       <c r="K373" s="4" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -38582,7 +38704,7 @@
       <c r="I374" s="3"/>
       <c r="J374" s="3"/>
       <c r="K374" s="4" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -38598,7 +38720,7 @@
       <c r="I375" s="3"/>
       <c r="J375" s="3"/>
       <c r="K375" s="4" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -38614,7 +38736,7 @@
       <c r="I376" s="3"/>
       <c r="J376" s="3"/>
       <c r="K376" s="4" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -38630,7 +38752,7 @@
       <c r="I377" s="3"/>
       <c r="J377" s="3"/>
       <c r="K377" s="4" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -38646,7 +38768,7 @@
       <c r="I378" s="3"/>
       <c r="J378" s="3"/>
       <c r="K378" s="4" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -38662,7 +38784,7 @@
       <c r="I379" s="3"/>
       <c r="J379" s="3"/>
       <c r="K379" s="4" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -38678,7 +38800,7 @@
       <c r="I380" s="3"/>
       <c r="J380" s="3"/>
       <c r="K380" s="4" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -38694,7 +38816,7 @@
       <c r="I381" s="3"/>
       <c r="J381" s="3"/>
       <c r="K381" s="4" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -38710,7 +38832,7 @@
       <c r="I382" s="3"/>
       <c r="J382" s="3"/>
       <c r="K382" s="4" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -38726,7 +38848,7 @@
       <c r="I383" s="3"/>
       <c r="J383" s="3"/>
       <c r="K383" s="4" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -38742,7 +38864,7 @@
       <c r="I384" s="3"/>
       <c r="J384" s="3"/>
       <c r="K384" s="4" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -38758,7 +38880,7 @@
       <c r="I385" s="3"/>
       <c r="J385" s="3"/>
       <c r="K385" s="4" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -38774,7 +38896,7 @@
       <c r="I386" s="3"/>
       <c r="J386" s="3"/>
       <c r="K386" s="4" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -38790,7 +38912,7 @@
       <c r="I387" s="3"/>
       <c r="J387" s="3"/>
       <c r="K387" s="4" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -38806,7 +38928,7 @@
       <c r="I388" s="3"/>
       <c r="J388" s="3"/>
       <c r="K388" s="4" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -38822,7 +38944,7 @@
       <c r="I389" s="3"/>
       <c r="J389" s="3"/>
       <c r="K389" s="4" t="str">
-        <f t="shared" ref="K389:K390" si="13">IF(COUNTA(B389:J389)=0,"",AVERAGE(B389:J389))</f>
+        <f t="shared" ref="K389:K390" si="14">IF(COUNTA(B389:J389)=0,"",AVERAGE(B389:J389))</f>
         <v/>
       </c>
     </row>
@@ -38838,7 +38960,7 @@
       <c r="I390" s="3"/>
       <c r="J390" s="3"/>
       <c r="K390" s="4" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
@@ -38868,7 +38990,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="8" t="s">
         <v>39</v>
       </c>
       <c r="B1" s="7"/>
@@ -38884,7 +39006,7 @@
       <c r="L1" s="7"/>
     </row>
     <row r="2" spans="1:12" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="6" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="7"/>
@@ -40303,20 +40425,42 @@
       </c>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A40" s="2"/>
-      <c r="B40" s="3"/>
-      <c r="C40" s="3"/>
-      <c r="D40" s="3"/>
-      <c r="E40" s="3"/>
-      <c r="F40" s="3"/>
-      <c r="G40" s="3"/>
-      <c r="H40" s="3"/>
-      <c r="I40" s="3"/>
-      <c r="J40" s="3"/>
-      <c r="K40" s="3"/>
-      <c r="L40" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
+      <c r="A40" s="2">
+        <v>46181</v>
+      </c>
+      <c r="B40" s="3">
+        <v>3.59</v>
+      </c>
+      <c r="C40" s="3">
+        <v>3.19</v>
+      </c>
+      <c r="D40" s="3">
+        <v>3.59</v>
+      </c>
+      <c r="E40" s="3">
+        <v>3.35</v>
+      </c>
+      <c r="F40" s="3">
+        <v>3.43</v>
+      </c>
+      <c r="G40" s="3">
+        <v>3.69</v>
+      </c>
+      <c r="H40" s="3">
+        <v>3.11</v>
+      </c>
+      <c r="I40" s="3">
+        <v>3.29</v>
+      </c>
+      <c r="J40" s="3">
+        <v>3.46</v>
+      </c>
+      <c r="K40" s="3">
+        <v>3.29</v>
+      </c>
+      <c r="L40" s="4">
+        <f t="shared" ref="L40" si="8">IF(COUNTA(B40:K40)=0,"",AVERAGE(B40:K40))</f>
+        <v>3.399</v>
       </c>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.25">
@@ -40808,7 +40952,7 @@
       <c r="J69" s="3"/>
       <c r="K69" s="3"/>
       <c r="L69" s="4" t="str">
-        <f t="shared" ref="L69:L132" si="8">IF(COUNTA(B69:K69)=0,"",AVERAGE(B69:K69))</f>
+        <f t="shared" ref="L69:L132" si="9">IF(COUNTA(B69:K69)=0,"",AVERAGE(B69:K69))</f>
         <v/>
       </c>
     </row>
@@ -40825,7 +40969,7 @@
       <c r="J70" s="3"/>
       <c r="K70" s="3"/>
       <c r="L70" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -40842,7 +40986,7 @@
       <c r="J71" s="3"/>
       <c r="K71" s="3"/>
       <c r="L71" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -40859,7 +41003,7 @@
       <c r="J72" s="3"/>
       <c r="K72" s="3"/>
       <c r="L72" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -40876,7 +41020,7 @@
       <c r="J73" s="3"/>
       <c r="K73" s="3"/>
       <c r="L73" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -40893,7 +41037,7 @@
       <c r="J74" s="3"/>
       <c r="K74" s="3"/>
       <c r="L74" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -40910,7 +41054,7 @@
       <c r="J75" s="3"/>
       <c r="K75" s="3"/>
       <c r="L75" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -40927,7 +41071,7 @@
       <c r="J76" s="3"/>
       <c r="K76" s="3"/>
       <c r="L76" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -40944,7 +41088,7 @@
       <c r="J77" s="3"/>
       <c r="K77" s="3"/>
       <c r="L77" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -40961,7 +41105,7 @@
       <c r="J78" s="3"/>
       <c r="K78" s="3"/>
       <c r="L78" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -40978,7 +41122,7 @@
       <c r="J79" s="3"/>
       <c r="K79" s="3"/>
       <c r="L79" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -40995,7 +41139,7 @@
       <c r="J80" s="3"/>
       <c r="K80" s="3"/>
       <c r="L80" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -41012,7 +41156,7 @@
       <c r="J81" s="3"/>
       <c r="K81" s="3"/>
       <c r="L81" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -41029,7 +41173,7 @@
       <c r="J82" s="3"/>
       <c r="K82" s="3"/>
       <c r="L82" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -41046,7 +41190,7 @@
       <c r="J83" s="3"/>
       <c r="K83" s="3"/>
       <c r="L83" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -41063,7 +41207,7 @@
       <c r="J84" s="3"/>
       <c r="K84" s="3"/>
       <c r="L84" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -41080,7 +41224,7 @@
       <c r="J85" s="3"/>
       <c r="K85" s="3"/>
       <c r="L85" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -41097,7 +41241,7 @@
       <c r="J86" s="3"/>
       <c r="K86" s="3"/>
       <c r="L86" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -41114,7 +41258,7 @@
       <c r="J87" s="3"/>
       <c r="K87" s="3"/>
       <c r="L87" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -41131,7 +41275,7 @@
       <c r="J88" s="3"/>
       <c r="K88" s="3"/>
       <c r="L88" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -41148,7 +41292,7 @@
       <c r="J89" s="3"/>
       <c r="K89" s="3"/>
       <c r="L89" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -41165,7 +41309,7 @@
       <c r="J90" s="3"/>
       <c r="K90" s="3"/>
       <c r="L90" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -41182,7 +41326,7 @@
       <c r="J91" s="3"/>
       <c r="K91" s="3"/>
       <c r="L91" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -41199,7 +41343,7 @@
       <c r="J92" s="3"/>
       <c r="K92" s="3"/>
       <c r="L92" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -41216,7 +41360,7 @@
       <c r="J93" s="3"/>
       <c r="K93" s="3"/>
       <c r="L93" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -41233,7 +41377,7 @@
       <c r="J94" s="3"/>
       <c r="K94" s="3"/>
       <c r="L94" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -41250,7 +41394,7 @@
       <c r="J95" s="3"/>
       <c r="K95" s="3"/>
       <c r="L95" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -41267,7 +41411,7 @@
       <c r="J96" s="3"/>
       <c r="K96" s="3"/>
       <c r="L96" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -41284,7 +41428,7 @@
       <c r="J97" s="3"/>
       <c r="K97" s="3"/>
       <c r="L97" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -41301,7 +41445,7 @@
       <c r="J98" s="3"/>
       <c r="K98" s="3"/>
       <c r="L98" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -41318,7 +41462,7 @@
       <c r="J99" s="3"/>
       <c r="K99" s="3"/>
       <c r="L99" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -41335,7 +41479,7 @@
       <c r="J100" s="3"/>
       <c r="K100" s="3"/>
       <c r="L100" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -41352,7 +41496,7 @@
       <c r="J101" s="3"/>
       <c r="K101" s="3"/>
       <c r="L101" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -41369,7 +41513,7 @@
       <c r="J102" s="3"/>
       <c r="K102" s="3"/>
       <c r="L102" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -41386,7 +41530,7 @@
       <c r="J103" s="3"/>
       <c r="K103" s="3"/>
       <c r="L103" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -41403,7 +41547,7 @@
       <c r="J104" s="3"/>
       <c r="K104" s="3"/>
       <c r="L104" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -41420,7 +41564,7 @@
       <c r="J105" s="3"/>
       <c r="K105" s="3"/>
       <c r="L105" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -41437,7 +41581,7 @@
       <c r="J106" s="3"/>
       <c r="K106" s="3"/>
       <c r="L106" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -41454,7 +41598,7 @@
       <c r="J107" s="3"/>
       <c r="K107" s="3"/>
       <c r="L107" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -41471,7 +41615,7 @@
       <c r="J108" s="3"/>
       <c r="K108" s="3"/>
       <c r="L108" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -41488,7 +41632,7 @@
       <c r="J109" s="3"/>
       <c r="K109" s="3"/>
       <c r="L109" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -41505,7 +41649,7 @@
       <c r="J110" s="3"/>
       <c r="K110" s="3"/>
       <c r="L110" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -41522,7 +41666,7 @@
       <c r="J111" s="3"/>
       <c r="K111" s="3"/>
       <c r="L111" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -41539,7 +41683,7 @@
       <c r="J112" s="3"/>
       <c r="K112" s="3"/>
       <c r="L112" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -41556,7 +41700,7 @@
       <c r="J113" s="3"/>
       <c r="K113" s="3"/>
       <c r="L113" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -41573,7 +41717,7 @@
       <c r="J114" s="3"/>
       <c r="K114" s="3"/>
       <c r="L114" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -41590,7 +41734,7 @@
       <c r="J115" s="3"/>
       <c r="K115" s="3"/>
       <c r="L115" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -41607,7 +41751,7 @@
       <c r="J116" s="3"/>
       <c r="K116" s="3"/>
       <c r="L116" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -41624,7 +41768,7 @@
       <c r="J117" s="3"/>
       <c r="K117" s="3"/>
       <c r="L117" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -41641,7 +41785,7 @@
       <c r="J118" s="3"/>
       <c r="K118" s="3"/>
       <c r="L118" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -41658,7 +41802,7 @@
       <c r="J119" s="3"/>
       <c r="K119" s="3"/>
       <c r="L119" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -41675,7 +41819,7 @@
       <c r="J120" s="3"/>
       <c r="K120" s="3"/>
       <c r="L120" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -41692,7 +41836,7 @@
       <c r="J121" s="3"/>
       <c r="K121" s="3"/>
       <c r="L121" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -41709,7 +41853,7 @@
       <c r="J122" s="3"/>
       <c r="K122" s="3"/>
       <c r="L122" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -41726,7 +41870,7 @@
       <c r="J123" s="3"/>
       <c r="K123" s="3"/>
       <c r="L123" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -41743,7 +41887,7 @@
       <c r="J124" s="3"/>
       <c r="K124" s="3"/>
       <c r="L124" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -41760,7 +41904,7 @@
       <c r="J125" s="3"/>
       <c r="K125" s="3"/>
       <c r="L125" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -41777,7 +41921,7 @@
       <c r="J126" s="3"/>
       <c r="K126" s="3"/>
       <c r="L126" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -41794,7 +41938,7 @@
       <c r="J127" s="3"/>
       <c r="K127" s="3"/>
       <c r="L127" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -41811,7 +41955,7 @@
       <c r="J128" s="3"/>
       <c r="K128" s="3"/>
       <c r="L128" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -41828,7 +41972,7 @@
       <c r="J129" s="3"/>
       <c r="K129" s="3"/>
       <c r="L129" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -41845,7 +41989,7 @@
       <c r="J130" s="3"/>
       <c r="K130" s="3"/>
       <c r="L130" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -41862,7 +42006,7 @@
       <c r="J131" s="3"/>
       <c r="K131" s="3"/>
       <c r="L131" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -41879,7 +42023,7 @@
       <c r="J132" s="3"/>
       <c r="K132" s="3"/>
       <c r="L132" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -41896,7 +42040,7 @@
       <c r="J133" s="3"/>
       <c r="K133" s="3"/>
       <c r="L133" s="4" t="str">
-        <f t="shared" ref="L133:L196" si="9">IF(COUNTA(B133:K133)=0,"",AVERAGE(B133:K133))</f>
+        <f t="shared" ref="L133:L196" si="10">IF(COUNTA(B133:K133)=0,"",AVERAGE(B133:K133))</f>
         <v/>
       </c>
     </row>
@@ -41913,7 +42057,7 @@
       <c r="J134" s="3"/>
       <c r="K134" s="3"/>
       <c r="L134" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -41930,7 +42074,7 @@
       <c r="J135" s="3"/>
       <c r="K135" s="3"/>
       <c r="L135" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -41947,7 +42091,7 @@
       <c r="J136" s="3"/>
       <c r="K136" s="3"/>
       <c r="L136" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -41964,7 +42108,7 @@
       <c r="J137" s="3"/>
       <c r="K137" s="3"/>
       <c r="L137" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -41981,7 +42125,7 @@
       <c r="J138" s="3"/>
       <c r="K138" s="3"/>
       <c r="L138" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -41998,7 +42142,7 @@
       <c r="J139" s="3"/>
       <c r="K139" s="3"/>
       <c r="L139" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -42015,7 +42159,7 @@
       <c r="J140" s="3"/>
       <c r="K140" s="3"/>
       <c r="L140" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -42032,7 +42176,7 @@
       <c r="J141" s="3"/>
       <c r="K141" s="3"/>
       <c r="L141" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -42049,7 +42193,7 @@
       <c r="J142" s="3"/>
       <c r="K142" s="3"/>
       <c r="L142" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -42066,7 +42210,7 @@
       <c r="J143" s="3"/>
       <c r="K143" s="3"/>
       <c r="L143" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -42083,7 +42227,7 @@
       <c r="J144" s="3"/>
       <c r="K144" s="3"/>
       <c r="L144" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -42100,7 +42244,7 @@
       <c r="J145" s="3"/>
       <c r="K145" s="3"/>
       <c r="L145" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -42117,7 +42261,7 @@
       <c r="J146" s="3"/>
       <c r="K146" s="3"/>
       <c r="L146" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -42134,7 +42278,7 @@
       <c r="J147" s="3"/>
       <c r="K147" s="3"/>
       <c r="L147" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -42151,7 +42295,7 @@
       <c r="J148" s="3"/>
       <c r="K148" s="3"/>
       <c r="L148" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -42168,7 +42312,7 @@
       <c r="J149" s="3"/>
       <c r="K149" s="3"/>
       <c r="L149" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -42185,7 +42329,7 @@
       <c r="J150" s="3"/>
       <c r="K150" s="3"/>
       <c r="L150" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -42202,7 +42346,7 @@
       <c r="J151" s="3"/>
       <c r="K151" s="3"/>
       <c r="L151" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -42219,7 +42363,7 @@
       <c r="J152" s="3"/>
       <c r="K152" s="3"/>
       <c r="L152" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -42236,7 +42380,7 @@
       <c r="J153" s="3"/>
       <c r="K153" s="3"/>
       <c r="L153" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -42253,7 +42397,7 @@
       <c r="J154" s="3"/>
       <c r="K154" s="3"/>
       <c r="L154" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -42270,7 +42414,7 @@
       <c r="J155" s="3"/>
       <c r="K155" s="3"/>
       <c r="L155" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -42287,7 +42431,7 @@
       <c r="J156" s="3"/>
       <c r="K156" s="3"/>
       <c r="L156" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -42304,7 +42448,7 @@
       <c r="J157" s="3"/>
       <c r="K157" s="3"/>
       <c r="L157" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -42321,7 +42465,7 @@
       <c r="J158" s="3"/>
       <c r="K158" s="3"/>
       <c r="L158" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -42338,7 +42482,7 @@
       <c r="J159" s="3"/>
       <c r="K159" s="3"/>
       <c r="L159" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -42355,7 +42499,7 @@
       <c r="J160" s="3"/>
       <c r="K160" s="3"/>
       <c r="L160" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -42372,7 +42516,7 @@
       <c r="J161" s="3"/>
       <c r="K161" s="3"/>
       <c r="L161" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -42389,7 +42533,7 @@
       <c r="J162" s="3"/>
       <c r="K162" s="3"/>
       <c r="L162" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -42406,7 +42550,7 @@
       <c r="J163" s="3"/>
       <c r="K163" s="3"/>
       <c r="L163" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -42423,7 +42567,7 @@
       <c r="J164" s="3"/>
       <c r="K164" s="3"/>
       <c r="L164" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -42440,7 +42584,7 @@
       <c r="J165" s="3"/>
       <c r="K165" s="3"/>
       <c r="L165" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -42457,7 +42601,7 @@
       <c r="J166" s="3"/>
       <c r="K166" s="3"/>
       <c r="L166" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -42474,7 +42618,7 @@
       <c r="J167" s="3"/>
       <c r="K167" s="3"/>
       <c r="L167" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -42491,7 +42635,7 @@
       <c r="J168" s="3"/>
       <c r="K168" s="3"/>
       <c r="L168" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -42508,7 +42652,7 @@
       <c r="J169" s="3"/>
       <c r="K169" s="3"/>
       <c r="L169" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -42525,7 +42669,7 @@
       <c r="J170" s="3"/>
       <c r="K170" s="3"/>
       <c r="L170" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -42542,7 +42686,7 @@
       <c r="J171" s="3"/>
       <c r="K171" s="3"/>
       <c r="L171" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -42559,7 +42703,7 @@
       <c r="J172" s="3"/>
       <c r="K172" s="3"/>
       <c r="L172" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -42576,7 +42720,7 @@
       <c r="J173" s="3"/>
       <c r="K173" s="3"/>
       <c r="L173" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -42593,7 +42737,7 @@
       <c r="J174" s="3"/>
       <c r="K174" s="3"/>
       <c r="L174" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -42610,7 +42754,7 @@
       <c r="J175" s="3"/>
       <c r="K175" s="3"/>
       <c r="L175" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -42627,7 +42771,7 @@
       <c r="J176" s="3"/>
       <c r="K176" s="3"/>
       <c r="L176" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -42644,7 +42788,7 @@
       <c r="J177" s="3"/>
       <c r="K177" s="3"/>
       <c r="L177" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -42661,7 +42805,7 @@
       <c r="J178" s="3"/>
       <c r="K178" s="3"/>
       <c r="L178" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -42678,7 +42822,7 @@
       <c r="J179" s="3"/>
       <c r="K179" s="3"/>
       <c r="L179" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -42695,7 +42839,7 @@
       <c r="J180" s="3"/>
       <c r="K180" s="3"/>
       <c r="L180" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -42712,7 +42856,7 @@
       <c r="J181" s="3"/>
       <c r="K181" s="3"/>
       <c r="L181" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -42729,7 +42873,7 @@
       <c r="J182" s="3"/>
       <c r="K182" s="3"/>
       <c r="L182" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -42746,7 +42890,7 @@
       <c r="J183" s="3"/>
       <c r="K183" s="3"/>
       <c r="L183" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -42763,7 +42907,7 @@
       <c r="J184" s="3"/>
       <c r="K184" s="3"/>
       <c r="L184" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -42780,7 +42924,7 @@
       <c r="J185" s="3"/>
       <c r="K185" s="3"/>
       <c r="L185" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -42797,7 +42941,7 @@
       <c r="J186" s="3"/>
       <c r="K186" s="3"/>
       <c r="L186" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -42814,7 +42958,7 @@
       <c r="J187" s="3"/>
       <c r="K187" s="3"/>
       <c r="L187" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -42831,7 +42975,7 @@
       <c r="J188" s="3"/>
       <c r="K188" s="3"/>
       <c r="L188" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -42848,7 +42992,7 @@
       <c r="J189" s="3"/>
       <c r="K189" s="3"/>
       <c r="L189" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -42865,7 +43009,7 @@
       <c r="J190" s="3"/>
       <c r="K190" s="3"/>
       <c r="L190" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -42882,7 +43026,7 @@
       <c r="J191" s="3"/>
       <c r="K191" s="3"/>
       <c r="L191" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -42899,7 +43043,7 @@
       <c r="J192" s="3"/>
       <c r="K192" s="3"/>
       <c r="L192" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -42916,7 +43060,7 @@
       <c r="J193" s="3"/>
       <c r="K193" s="3"/>
       <c r="L193" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -42933,7 +43077,7 @@
       <c r="J194" s="3"/>
       <c r="K194" s="3"/>
       <c r="L194" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -42950,7 +43094,7 @@
       <c r="J195" s="3"/>
       <c r="K195" s="3"/>
       <c r="L195" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -42967,7 +43111,7 @@
       <c r="J196" s="3"/>
       <c r="K196" s="3"/>
       <c r="L196" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -42984,7 +43128,7 @@
       <c r="J197" s="3"/>
       <c r="K197" s="3"/>
       <c r="L197" s="4" t="str">
-        <f t="shared" ref="L197:L260" si="10">IF(COUNTA(B197:K197)=0,"",AVERAGE(B197:K197))</f>
+        <f t="shared" ref="L197:L260" si="11">IF(COUNTA(B197:K197)=0,"",AVERAGE(B197:K197))</f>
         <v/>
       </c>
     </row>
@@ -43001,7 +43145,7 @@
       <c r="J198" s="3"/>
       <c r="K198" s="3"/>
       <c r="L198" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -43018,7 +43162,7 @@
       <c r="J199" s="3"/>
       <c r="K199" s="3"/>
       <c r="L199" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -43035,7 +43179,7 @@
       <c r="J200" s="3"/>
       <c r="K200" s="3"/>
       <c r="L200" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -43052,7 +43196,7 @@
       <c r="J201" s="3"/>
       <c r="K201" s="3"/>
       <c r="L201" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -43069,7 +43213,7 @@
       <c r="J202" s="3"/>
       <c r="K202" s="3"/>
       <c r="L202" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -43086,7 +43230,7 @@
       <c r="J203" s="3"/>
       <c r="K203" s="3"/>
       <c r="L203" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -43103,7 +43247,7 @@
       <c r="J204" s="3"/>
       <c r="K204" s="3"/>
       <c r="L204" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -43120,7 +43264,7 @@
       <c r="J205" s="3"/>
       <c r="K205" s="3"/>
       <c r="L205" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -43137,7 +43281,7 @@
       <c r="J206" s="3"/>
       <c r="K206" s="3"/>
       <c r="L206" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -43154,7 +43298,7 @@
       <c r="J207" s="3"/>
       <c r="K207" s="3"/>
       <c r="L207" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -43171,7 +43315,7 @@
       <c r="J208" s="3"/>
       <c r="K208" s="3"/>
       <c r="L208" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -43188,7 +43332,7 @@
       <c r="J209" s="3"/>
       <c r="K209" s="3"/>
       <c r="L209" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -43205,7 +43349,7 @@
       <c r="J210" s="3"/>
       <c r="K210" s="3"/>
       <c r="L210" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -43222,7 +43366,7 @@
       <c r="J211" s="3"/>
       <c r="K211" s="3"/>
       <c r="L211" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -43239,7 +43383,7 @@
       <c r="J212" s="3"/>
       <c r="K212" s="3"/>
       <c r="L212" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -43256,7 +43400,7 @@
       <c r="J213" s="3"/>
       <c r="K213" s="3"/>
       <c r="L213" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -43273,7 +43417,7 @@
       <c r="J214" s="3"/>
       <c r="K214" s="3"/>
       <c r="L214" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -43290,7 +43434,7 @@
       <c r="J215" s="3"/>
       <c r="K215" s="3"/>
       <c r="L215" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -43307,7 +43451,7 @@
       <c r="J216" s="3"/>
       <c r="K216" s="3"/>
       <c r="L216" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -43324,7 +43468,7 @@
       <c r="J217" s="3"/>
       <c r="K217" s="3"/>
       <c r="L217" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -43341,7 +43485,7 @@
       <c r="J218" s="3"/>
       <c r="K218" s="3"/>
       <c r="L218" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -43358,7 +43502,7 @@
       <c r="J219" s="3"/>
       <c r="K219" s="3"/>
       <c r="L219" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -43375,7 +43519,7 @@
       <c r="J220" s="3"/>
       <c r="K220" s="3"/>
       <c r="L220" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -43392,7 +43536,7 @@
       <c r="J221" s="3"/>
       <c r="K221" s="3"/>
       <c r="L221" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -43409,7 +43553,7 @@
       <c r="J222" s="3"/>
       <c r="K222" s="3"/>
       <c r="L222" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -43426,7 +43570,7 @@
       <c r="J223" s="3"/>
       <c r="K223" s="3"/>
       <c r="L223" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -43443,7 +43587,7 @@
       <c r="J224" s="3"/>
       <c r="K224" s="3"/>
       <c r="L224" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -43460,7 +43604,7 @@
       <c r="J225" s="3"/>
       <c r="K225" s="3"/>
       <c r="L225" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -43477,7 +43621,7 @@
       <c r="J226" s="3"/>
       <c r="K226" s="3"/>
       <c r="L226" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -43494,7 +43638,7 @@
       <c r="J227" s="3"/>
       <c r="K227" s="3"/>
       <c r="L227" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -43511,7 +43655,7 @@
       <c r="J228" s="3"/>
       <c r="K228" s="3"/>
       <c r="L228" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -43528,7 +43672,7 @@
       <c r="J229" s="3"/>
       <c r="K229" s="3"/>
       <c r="L229" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -43545,7 +43689,7 @@
       <c r="J230" s="3"/>
       <c r="K230" s="3"/>
       <c r="L230" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -43562,7 +43706,7 @@
       <c r="J231" s="3"/>
       <c r="K231" s="3"/>
       <c r="L231" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -43579,7 +43723,7 @@
       <c r="J232" s="3"/>
       <c r="K232" s="3"/>
       <c r="L232" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -43596,7 +43740,7 @@
       <c r="J233" s="3"/>
       <c r="K233" s="3"/>
       <c r="L233" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -43613,7 +43757,7 @@
       <c r="J234" s="3"/>
       <c r="K234" s="3"/>
       <c r="L234" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -43630,7 +43774,7 @@
       <c r="J235" s="3"/>
       <c r="K235" s="3"/>
       <c r="L235" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -43647,7 +43791,7 @@
       <c r="J236" s="3"/>
       <c r="K236" s="3"/>
       <c r="L236" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -43664,7 +43808,7 @@
       <c r="J237" s="3"/>
       <c r="K237" s="3"/>
       <c r="L237" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -43681,7 +43825,7 @@
       <c r="J238" s="3"/>
       <c r="K238" s="3"/>
       <c r="L238" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -43698,7 +43842,7 @@
       <c r="J239" s="3"/>
       <c r="K239" s="3"/>
       <c r="L239" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -43715,7 +43859,7 @@
       <c r="J240" s="3"/>
       <c r="K240" s="3"/>
       <c r="L240" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -43732,7 +43876,7 @@
       <c r="J241" s="3"/>
       <c r="K241" s="3"/>
       <c r="L241" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -43749,7 +43893,7 @@
       <c r="J242" s="3"/>
       <c r="K242" s="3"/>
       <c r="L242" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -43766,7 +43910,7 @@
       <c r="J243" s="3"/>
       <c r="K243" s="3"/>
       <c r="L243" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -43783,7 +43927,7 @@
       <c r="J244" s="3"/>
       <c r="K244" s="3"/>
       <c r="L244" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -43800,7 +43944,7 @@
       <c r="J245" s="3"/>
       <c r="K245" s="3"/>
       <c r="L245" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -43817,7 +43961,7 @@
       <c r="J246" s="3"/>
       <c r="K246" s="3"/>
       <c r="L246" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -43834,7 +43978,7 @@
       <c r="J247" s="3"/>
       <c r="K247" s="3"/>
       <c r="L247" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -43851,7 +43995,7 @@
       <c r="J248" s="3"/>
       <c r="K248" s="3"/>
       <c r="L248" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -43868,7 +44012,7 @@
       <c r="J249" s="3"/>
       <c r="K249" s="3"/>
       <c r="L249" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -43885,7 +44029,7 @@
       <c r="J250" s="3"/>
       <c r="K250" s="3"/>
       <c r="L250" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -43902,7 +44046,7 @@
       <c r="J251" s="3"/>
       <c r="K251" s="3"/>
       <c r="L251" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -43919,7 +44063,7 @@
       <c r="J252" s="3"/>
       <c r="K252" s="3"/>
       <c r="L252" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -43936,7 +44080,7 @@
       <c r="J253" s="3"/>
       <c r="K253" s="3"/>
       <c r="L253" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -43953,7 +44097,7 @@
       <c r="J254" s="3"/>
       <c r="K254" s="3"/>
       <c r="L254" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -43970,7 +44114,7 @@
       <c r="J255" s="3"/>
       <c r="K255" s="3"/>
       <c r="L255" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -43987,7 +44131,7 @@
       <c r="J256" s="3"/>
       <c r="K256" s="3"/>
       <c r="L256" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -44004,7 +44148,7 @@
       <c r="J257" s="3"/>
       <c r="K257" s="3"/>
       <c r="L257" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -44021,7 +44165,7 @@
       <c r="J258" s="3"/>
       <c r="K258" s="3"/>
       <c r="L258" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -44038,7 +44182,7 @@
       <c r="J259" s="3"/>
       <c r="K259" s="3"/>
       <c r="L259" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -44055,7 +44199,7 @@
       <c r="J260" s="3"/>
       <c r="K260" s="3"/>
       <c r="L260" s="4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -44072,7 +44216,7 @@
       <c r="J261" s="3"/>
       <c r="K261" s="3"/>
       <c r="L261" s="4" t="str">
-        <f t="shared" ref="L261:L324" si="11">IF(COUNTA(B261:K261)=0,"",AVERAGE(B261:K261))</f>
+        <f t="shared" ref="L261:L324" si="12">IF(COUNTA(B261:K261)=0,"",AVERAGE(B261:K261))</f>
         <v/>
       </c>
     </row>
@@ -44089,7 +44233,7 @@
       <c r="J262" s="3"/>
       <c r="K262" s="3"/>
       <c r="L262" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -44106,7 +44250,7 @@
       <c r="J263" s="3"/>
       <c r="K263" s="3"/>
       <c r="L263" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -44123,7 +44267,7 @@
       <c r="J264" s="3"/>
       <c r="K264" s="3"/>
       <c r="L264" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -44140,7 +44284,7 @@
       <c r="J265" s="3"/>
       <c r="K265" s="3"/>
       <c r="L265" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -44157,7 +44301,7 @@
       <c r="J266" s="3"/>
       <c r="K266" s="3"/>
       <c r="L266" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -44174,7 +44318,7 @@
       <c r="J267" s="3"/>
       <c r="K267" s="3"/>
       <c r="L267" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -44191,7 +44335,7 @@
       <c r="J268" s="3"/>
       <c r="K268" s="3"/>
       <c r="L268" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -44208,7 +44352,7 @@
       <c r="J269" s="3"/>
       <c r="K269" s="3"/>
       <c r="L269" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -44225,7 +44369,7 @@
       <c r="J270" s="3"/>
       <c r="K270" s="3"/>
       <c r="L270" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -44242,7 +44386,7 @@
       <c r="J271" s="3"/>
       <c r="K271" s="3"/>
       <c r="L271" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -44259,7 +44403,7 @@
       <c r="J272" s="3"/>
       <c r="K272" s="3"/>
       <c r="L272" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -44276,7 +44420,7 @@
       <c r="J273" s="3"/>
       <c r="K273" s="3"/>
       <c r="L273" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -44293,7 +44437,7 @@
       <c r="J274" s="3"/>
       <c r="K274" s="3"/>
       <c r="L274" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -44310,7 +44454,7 @@
       <c r="J275" s="3"/>
       <c r="K275" s="3"/>
       <c r="L275" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -44327,7 +44471,7 @@
       <c r="J276" s="3"/>
       <c r="K276" s="3"/>
       <c r="L276" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -44344,7 +44488,7 @@
       <c r="J277" s="3"/>
       <c r="K277" s="3"/>
       <c r="L277" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -44361,7 +44505,7 @@
       <c r="J278" s="3"/>
       <c r="K278" s="3"/>
       <c r="L278" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -44378,7 +44522,7 @@
       <c r="J279" s="3"/>
       <c r="K279" s="3"/>
       <c r="L279" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -44395,7 +44539,7 @@
       <c r="J280" s="3"/>
       <c r="K280" s="3"/>
       <c r="L280" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -44412,7 +44556,7 @@
       <c r="J281" s="3"/>
       <c r="K281" s="3"/>
       <c r="L281" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -44429,7 +44573,7 @@
       <c r="J282" s="3"/>
       <c r="K282" s="3"/>
       <c r="L282" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -44446,7 +44590,7 @@
       <c r="J283" s="3"/>
       <c r="K283" s="3"/>
       <c r="L283" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -44463,7 +44607,7 @@
       <c r="J284" s="3"/>
       <c r="K284" s="3"/>
       <c r="L284" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -44480,7 +44624,7 @@
       <c r="J285" s="3"/>
       <c r="K285" s="3"/>
       <c r="L285" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -44497,7 +44641,7 @@
       <c r="J286" s="3"/>
       <c r="K286" s="3"/>
       <c r="L286" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -44514,7 +44658,7 @@
       <c r="J287" s="3"/>
       <c r="K287" s="3"/>
       <c r="L287" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -44531,7 +44675,7 @@
       <c r="J288" s="3"/>
       <c r="K288" s="3"/>
       <c r="L288" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -44548,7 +44692,7 @@
       <c r="J289" s="3"/>
       <c r="K289" s="3"/>
       <c r="L289" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -44565,7 +44709,7 @@
       <c r="J290" s="3"/>
       <c r="K290" s="3"/>
       <c r="L290" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -44582,7 +44726,7 @@
       <c r="J291" s="3"/>
       <c r="K291" s="3"/>
       <c r="L291" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -44599,7 +44743,7 @@
       <c r="J292" s="3"/>
       <c r="K292" s="3"/>
       <c r="L292" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -44616,7 +44760,7 @@
       <c r="J293" s="3"/>
       <c r="K293" s="3"/>
       <c r="L293" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -44633,7 +44777,7 @@
       <c r="J294" s="3"/>
       <c r="K294" s="3"/>
       <c r="L294" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -44650,7 +44794,7 @@
       <c r="J295" s="3"/>
       <c r="K295" s="3"/>
       <c r="L295" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -44667,7 +44811,7 @@
       <c r="J296" s="3"/>
       <c r="K296" s="3"/>
       <c r="L296" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -44684,7 +44828,7 @@
       <c r="J297" s="3"/>
       <c r="K297" s="3"/>
       <c r="L297" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -44701,7 +44845,7 @@
       <c r="J298" s="3"/>
       <c r="K298" s="3"/>
       <c r="L298" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -44718,7 +44862,7 @@
       <c r="J299" s="3"/>
       <c r="K299" s="3"/>
       <c r="L299" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -44735,7 +44879,7 @@
       <c r="J300" s="3"/>
       <c r="K300" s="3"/>
       <c r="L300" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -44752,7 +44896,7 @@
       <c r="J301" s="3"/>
       <c r="K301" s="3"/>
       <c r="L301" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -44769,7 +44913,7 @@
       <c r="J302" s="3"/>
       <c r="K302" s="3"/>
       <c r="L302" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -44786,7 +44930,7 @@
       <c r="J303" s="3"/>
       <c r="K303" s="3"/>
       <c r="L303" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -44803,7 +44947,7 @@
       <c r="J304" s="3"/>
       <c r="K304" s="3"/>
       <c r="L304" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -44820,7 +44964,7 @@
       <c r="J305" s="3"/>
       <c r="K305" s="3"/>
       <c r="L305" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -44837,7 +44981,7 @@
       <c r="J306" s="3"/>
       <c r="K306" s="3"/>
       <c r="L306" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -44854,7 +44998,7 @@
       <c r="J307" s="3"/>
       <c r="K307" s="3"/>
       <c r="L307" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -44871,7 +45015,7 @@
       <c r="J308" s="3"/>
       <c r="K308" s="3"/>
       <c r="L308" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -44888,7 +45032,7 @@
       <c r="J309" s="3"/>
       <c r="K309" s="3"/>
       <c r="L309" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -44905,7 +45049,7 @@
       <c r="J310" s="3"/>
       <c r="K310" s="3"/>
       <c r="L310" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -44922,7 +45066,7 @@
       <c r="J311" s="3"/>
       <c r="K311" s="3"/>
       <c r="L311" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -44939,7 +45083,7 @@
       <c r="J312" s="3"/>
       <c r="K312" s="3"/>
       <c r="L312" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -44956,7 +45100,7 @@
       <c r="J313" s="3"/>
       <c r="K313" s="3"/>
       <c r="L313" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -44973,7 +45117,7 @@
       <c r="J314" s="3"/>
       <c r="K314" s="3"/>
       <c r="L314" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -44990,7 +45134,7 @@
       <c r="J315" s="3"/>
       <c r="K315" s="3"/>
       <c r="L315" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -45007,7 +45151,7 @@
       <c r="J316" s="3"/>
       <c r="K316" s="3"/>
       <c r="L316" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -45024,7 +45168,7 @@
       <c r="J317" s="3"/>
       <c r="K317" s="3"/>
       <c r="L317" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -45041,7 +45185,7 @@
       <c r="J318" s="3"/>
       <c r="K318" s="3"/>
       <c r="L318" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -45058,7 +45202,7 @@
       <c r="J319" s="3"/>
       <c r="K319" s="3"/>
       <c r="L319" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -45075,7 +45219,7 @@
       <c r="J320" s="3"/>
       <c r="K320" s="3"/>
       <c r="L320" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -45092,7 +45236,7 @@
       <c r="J321" s="3"/>
       <c r="K321" s="3"/>
       <c r="L321" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -45109,7 +45253,7 @@
       <c r="J322" s="3"/>
       <c r="K322" s="3"/>
       <c r="L322" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -45126,7 +45270,7 @@
       <c r="J323" s="3"/>
       <c r="K323" s="3"/>
       <c r="L323" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -45143,7 +45287,7 @@
       <c r="J324" s="3"/>
       <c r="K324" s="3"/>
       <c r="L324" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -45160,7 +45304,7 @@
       <c r="J325" s="3"/>
       <c r="K325" s="3"/>
       <c r="L325" s="4" t="str">
-        <f t="shared" ref="L325:L388" si="12">IF(COUNTA(B325:K325)=0,"",AVERAGE(B325:K325))</f>
+        <f t="shared" ref="L325:L388" si="13">IF(COUNTA(B325:K325)=0,"",AVERAGE(B325:K325))</f>
         <v/>
       </c>
     </row>
@@ -45177,7 +45321,7 @@
       <c r="J326" s="3"/>
       <c r="K326" s="3"/>
       <c r="L326" s="4" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -45194,7 +45338,7 @@
       <c r="J327" s="3"/>
       <c r="K327" s="3"/>
       <c r="L327" s="4" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -45211,7 +45355,7 @@
       <c r="J328" s="3"/>
       <c r="K328" s="3"/>
       <c r="L328" s="4" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -45228,7 +45372,7 @@
       <c r="J329" s="3"/>
       <c r="K329" s="3"/>
       <c r="L329" s="4" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -45245,7 +45389,7 @@
       <c r="J330" s="3"/>
       <c r="K330" s="3"/>
       <c r="L330" s="4" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -45262,7 +45406,7 @@
       <c r="J331" s="3"/>
       <c r="K331" s="3"/>
       <c r="L331" s="4" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -45279,7 +45423,7 @@
       <c r="J332" s="3"/>
       <c r="K332" s="3"/>
       <c r="L332" s="4" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -45296,7 +45440,7 @@
       <c r="J333" s="3"/>
       <c r="K333" s="3"/>
       <c r="L333" s="4" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -45313,7 +45457,7 @@
       <c r="J334" s="3"/>
       <c r="K334" s="3"/>
       <c r="L334" s="4" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -45330,7 +45474,7 @@
       <c r="J335" s="3"/>
       <c r="K335" s="3"/>
       <c r="L335" s="4" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -45347,7 +45491,7 @@
       <c r="J336" s="3"/>
       <c r="K336" s="3"/>
       <c r="L336" s="4" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -45364,7 +45508,7 @@
       <c r="J337" s="3"/>
       <c r="K337" s="3"/>
       <c r="L337" s="4" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -45381,7 +45525,7 @@
       <c r="J338" s="3"/>
       <c r="K338" s="3"/>
       <c r="L338" s="4" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -45398,7 +45542,7 @@
       <c r="J339" s="3"/>
       <c r="K339" s="3"/>
       <c r="L339" s="4" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -45415,7 +45559,7 @@
       <c r="J340" s="3"/>
       <c r="K340" s="3"/>
       <c r="L340" s="4" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -45432,7 +45576,7 @@
       <c r="J341" s="3"/>
       <c r="K341" s="3"/>
       <c r="L341" s="4" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -45449,7 +45593,7 @@
       <c r="J342" s="3"/>
       <c r="K342" s="3"/>
       <c r="L342" s="4" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -45466,7 +45610,7 @@
       <c r="J343" s="3"/>
       <c r="K343" s="3"/>
       <c r="L343" s="4" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -45483,7 +45627,7 @@
       <c r="J344" s="3"/>
       <c r="K344" s="3"/>
       <c r="L344" s="4" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -45500,7 +45644,7 @@
       <c r="J345" s="3"/>
       <c r="K345" s="3"/>
       <c r="L345" s="4" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -45517,7 +45661,7 @@
       <c r="J346" s="3"/>
       <c r="K346" s="3"/>
       <c r="L346" s="4" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -45534,7 +45678,7 @@
       <c r="J347" s="3"/>
       <c r="K347" s="3"/>
       <c r="L347" s="4" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -45551,7 +45695,7 @@
       <c r="J348" s="3"/>
       <c r="K348" s="3"/>
       <c r="L348" s="4" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -45568,7 +45712,7 @@
       <c r="J349" s="3"/>
       <c r="K349" s="3"/>
       <c r="L349" s="4" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -45585,7 +45729,7 @@
       <c r="J350" s="3"/>
       <c r="K350" s="3"/>
       <c r="L350" s="4" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -45602,7 +45746,7 @@
       <c r="J351" s="3"/>
       <c r="K351" s="3"/>
       <c r="L351" s="4" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -45619,7 +45763,7 @@
       <c r="J352" s="3"/>
       <c r="K352" s="3"/>
       <c r="L352" s="4" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -45636,7 +45780,7 @@
       <c r="J353" s="3"/>
       <c r="K353" s="3"/>
       <c r="L353" s="4" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -45653,7 +45797,7 @@
       <c r="J354" s="3"/>
       <c r="K354" s="3"/>
       <c r="L354" s="4" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -45670,7 +45814,7 @@
       <c r="J355" s="3"/>
       <c r="K355" s="3"/>
       <c r="L355" s="4" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -45687,7 +45831,7 @@
       <c r="J356" s="3"/>
       <c r="K356" s="3"/>
       <c r="L356" s="4" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -45704,7 +45848,7 @@
       <c r="J357" s="3"/>
       <c r="K357" s="3"/>
       <c r="L357" s="4" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -45721,7 +45865,7 @@
       <c r="J358" s="3"/>
       <c r="K358" s="3"/>
       <c r="L358" s="4" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -45738,7 +45882,7 @@
       <c r="J359" s="3"/>
       <c r="K359" s="3"/>
       <c r="L359" s="4" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -45755,7 +45899,7 @@
       <c r="J360" s="3"/>
       <c r="K360" s="3"/>
       <c r="L360" s="4" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -45772,7 +45916,7 @@
       <c r="J361" s="3"/>
       <c r="K361" s="3"/>
       <c r="L361" s="4" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -45789,7 +45933,7 @@
       <c r="J362" s="3"/>
       <c r="K362" s="3"/>
       <c r="L362" s="4" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -45806,7 +45950,7 @@
       <c r="J363" s="3"/>
       <c r="K363" s="3"/>
       <c r="L363" s="4" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -45823,7 +45967,7 @@
       <c r="J364" s="3"/>
       <c r="K364" s="3"/>
       <c r="L364" s="4" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -45840,7 +45984,7 @@
       <c r="J365" s="3"/>
       <c r="K365" s="3"/>
       <c r="L365" s="4" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -45857,7 +46001,7 @@
       <c r="J366" s="3"/>
       <c r="K366" s="3"/>
       <c r="L366" s="4" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -45874,7 +46018,7 @@
       <c r="J367" s="3"/>
       <c r="K367" s="3"/>
       <c r="L367" s="4" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -45891,7 +46035,7 @@
       <c r="J368" s="3"/>
       <c r="K368" s="3"/>
       <c r="L368" s="4" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -45908,7 +46052,7 @@
       <c r="J369" s="3"/>
       <c r="K369" s="3"/>
       <c r="L369" s="4" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -45925,7 +46069,7 @@
       <c r="J370" s="3"/>
       <c r="K370" s="3"/>
       <c r="L370" s="4" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -45942,7 +46086,7 @@
       <c r="J371" s="3"/>
       <c r="K371" s="3"/>
       <c r="L371" s="4" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -45959,7 +46103,7 @@
       <c r="J372" s="3"/>
       <c r="K372" s="3"/>
       <c r="L372" s="4" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -45976,7 +46120,7 @@
       <c r="J373" s="3"/>
       <c r="K373" s="3"/>
       <c r="L373" s="4" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -45993,7 +46137,7 @@
       <c r="J374" s="3"/>
       <c r="K374" s="3"/>
       <c r="L374" s="4" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -46010,7 +46154,7 @@
       <c r="J375" s="3"/>
       <c r="K375" s="3"/>
       <c r="L375" s="4" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -46027,7 +46171,7 @@
       <c r="J376" s="3"/>
       <c r="K376" s="3"/>
       <c r="L376" s="4" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -46044,7 +46188,7 @@
       <c r="J377" s="3"/>
       <c r="K377" s="3"/>
       <c r="L377" s="4" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -46061,7 +46205,7 @@
       <c r="J378" s="3"/>
       <c r="K378" s="3"/>
       <c r="L378" s="4" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -46078,7 +46222,7 @@
       <c r="J379" s="3"/>
       <c r="K379" s="3"/>
       <c r="L379" s="4" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -46095,7 +46239,7 @@
       <c r="J380" s="3"/>
       <c r="K380" s="3"/>
       <c r="L380" s="4" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -46112,7 +46256,7 @@
       <c r="J381" s="3"/>
       <c r="K381" s="3"/>
       <c r="L381" s="4" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -46129,7 +46273,7 @@
       <c r="J382" s="3"/>
       <c r="K382" s="3"/>
       <c r="L382" s="4" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -46146,7 +46290,7 @@
       <c r="J383" s="3"/>
       <c r="K383" s="3"/>
       <c r="L383" s="4" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -46163,7 +46307,7 @@
       <c r="J384" s="3"/>
       <c r="K384" s="3"/>
       <c r="L384" s="4" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -46180,7 +46324,7 @@
       <c r="J385" s="3"/>
       <c r="K385" s="3"/>
       <c r="L385" s="4" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -46197,7 +46341,7 @@
       <c r="J386" s="3"/>
       <c r="K386" s="3"/>
       <c r="L386" s="4" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -46214,7 +46358,7 @@
       <c r="J387" s="3"/>
       <c r="K387" s="3"/>
       <c r="L387" s="4" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -46231,7 +46375,7 @@
       <c r="J388" s="3"/>
       <c r="K388" s="3"/>
       <c r="L388" s="4" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -46248,7 +46392,7 @@
       <c r="J389" s="3"/>
       <c r="K389" s="3"/>
       <c r="L389" s="4" t="str">
-        <f t="shared" ref="L389:L390" si="13">IF(COUNTA(B389:K389)=0,"",AVERAGE(B389:K389))</f>
+        <f t="shared" ref="L389:L390" si="14">IF(COUNTA(B389:K389)=0,"",AVERAGE(B389:K389))</f>
         <v/>
       </c>
     </row>
@@ -46265,7 +46409,7 @@
       <c r="J390" s="3"/>
       <c r="K390" s="3"/>
       <c r="L390" s="4" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>

--- a/app/mevduat-kredi-faizleri/data/hoca-ile-borsa-faiz-takip-sablonu-guncel.xlsx
+++ b/app/mevduat-kredi-faizleri/data/hoca-ile-borsa-faiz-takip-sablonu-guncel.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projeler\hoca-ile-borsa\app\mevduat-kredi-faizleri\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8731FC9E-F9E1-41C4-A7FD-044A4A8BE587}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25DFFEA0-DC28-4FFE-A6EC-C747DAEA2EB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="39">
   <si>
     <t>Mevduat Günlük Oran Takip Şablonu</t>
   </si>
@@ -97,9 +97,6 @@
   </si>
   <si>
     <t>TEB - Türk Ekonomi Bankası</t>
-  </si>
-  <si>
-    <t>Şekerbank</t>
   </si>
   <si>
     <t>Yapı Kredi</t>
@@ -318,7 +315,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Mevduat!$Z$4</c:f>
+              <c:f>Mevduat!$Y$4</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -449,125 +446,128 @@
                 <c:pt idx="35">
                   <c:v>46181</c:v>
                 </c:pt>
+                <c:pt idx="36">
+                  <c:v>46182</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Mevduat!$Z$5:$Z$390</c:f>
+              <c:f>Mevduat!$Y$5:$Y$390</c:f>
               <c:numCache>
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="386"/>
                 <c:pt idx="0">
-                  <c:v>42.825416666666662</c:v>
+                  <c:v>43.078695652173913</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>42.825416666666662</c:v>
+                  <c:v>43.078695652173913</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>42.825416666666662</c:v>
+                  <c:v>43.078695652173913</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>43.248333333333335</c:v>
+                  <c:v>43.52</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>43.085416666666667</c:v>
+                  <c:v>43.35</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>43.127083333333331</c:v>
+                  <c:v>43.393478260869564</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>43.085416666666667</c:v>
+                  <c:v>43.35</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>43.078749999999992</c:v>
+                  <c:v>43.343043478260867</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>43.109999999999992</c:v>
+                  <c:v>43.375652173913046</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>43.109999999999992</c:v>
+                  <c:v>43.375652173913046</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>43.099583333333328</c:v>
+                  <c:v>43.364782608695648</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>43.148750000000007</c:v>
+                  <c:v>43.416086956521738</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>43.117500000000007</c:v>
+                  <c:v>43.383478260869566</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>43.117500000000007</c:v>
+                  <c:v>43.383478260869566</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>43.534166666666671</c:v>
+                  <c:v>43.470434782608699</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>43.502083333333331</c:v>
+                  <c:v>43.436956521739127</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>43.491666666666667</c:v>
+                  <c:v>43.426086956521736</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>43.460416666666667</c:v>
+                  <c:v>43.393478260869564</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>43.449999999999996</c:v>
+                  <c:v>43.382608695652173</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>43.449999999999996</c:v>
+                  <c:v>43.382608695652173</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>43.439583333333331</c:v>
+                  <c:v>43.371739130434783</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>43.455000000000005</c:v>
+                  <c:v>43.387826086956522</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>43.413333333333334</c:v>
+                  <c:v>43.344347826086953</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>43.413333333333334</c:v>
+                  <c:v>43.344347826086953</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>43.413333333333334</c:v>
+                  <c:v>43.344347826086953</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>43.455000000000005</c:v>
+                  <c:v>43.387826086956522</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>43.434583333333329</c:v>
+                  <c:v>43.366521739130434</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>43.434583333333329</c:v>
+                  <c:v>43.366521739130434</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>43.476249999999993</c:v>
+                  <c:v>43.41</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>43.476249999999993</c:v>
+                  <c:v>43.41</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>43.476249999999993</c:v>
+                  <c:v>43.41</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>43.472500000000004</c:v>
+                  <c:v>43.40608695652174</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>43.472500000000004</c:v>
+                  <c:v>43.40608695652174</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>43.472500000000004</c:v>
+                  <c:v>43.40608695652174</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>43.472500000000004</c:v>
+                  <c:v>43.40608695652174</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>43.472500000000004</c:v>
+                  <c:v>43.40608695652174</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>0</c:v>
+                  <c:v>43.44086956521739</c:v>
                 </c:pt>
                 <c:pt idx="37">
                   <c:v>0</c:v>
@@ -1883,6 +1883,9 @@
                 <c:pt idx="35">
                   <c:v>46181</c:v>
                 </c:pt>
+                <c:pt idx="36">
+                  <c:v>46182</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2001,7 +2004,7 @@
                   <c:v>3.7305263157894726</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>0</c:v>
+                  <c:v>3.6863157894736838</c:v>
                 </c:pt>
                 <c:pt idx="37">
                   <c:v>0</c:v>
@@ -3317,6 +3320,9 @@
                 <c:pt idx="35">
                   <c:v>46181</c:v>
                 </c:pt>
+                <c:pt idx="36">
+                  <c:v>46182</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3435,7 +3441,7 @@
                   <c:v>2.8555555555555556</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>0</c:v>
+                  <c:v>2.8611111111111112</c:v>
                 </c:pt>
                 <c:pt idx="37">
                   <c:v>0</c:v>
@@ -4751,6 +4757,9 @@
                 <c:pt idx="35">
                   <c:v>46181</c:v>
                 </c:pt>
+                <c:pt idx="36">
+                  <c:v>46182</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -4869,7 +4878,7 @@
                   <c:v>3.399</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>0</c:v>
+                  <c:v>3.4189999999999996</c:v>
                 </c:pt>
                 <c:pt idx="37">
                   <c:v>0</c:v>
@@ -6448,15 +6457,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Z392"/>
+  <dimension ref="A1:Y392"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
-    <col min="2" max="25" width="18" customWidth="1"/>
-    <col min="26" max="26" width="16" customWidth="1"/>
+    <col min="2" max="24" width="18" customWidth="1"/>
+    <col min="25" max="25" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:25" ht="24" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
@@ -6484,9 +6493,8 @@
       <c r="W1" s="7"/>
       <c r="X1" s="7"/>
       <c r="Y1" s="7"/>
-      <c r="Z1" s="7"/>
-    </row>
-    <row r="2" spans="1:26" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:25" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
         <v>1</v>
       </c>
@@ -6514,9 +6522,8 @@
       <c r="W2" s="7"/>
       <c r="X2" s="7"/>
       <c r="Y2" s="7"/>
-      <c r="Z2" s="7"/>
-    </row>
-    <row r="4" spans="1:26" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4" spans="1:25" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
@@ -6592,11 +6599,8 @@
       <c r="Y4" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="Z4" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.25">
+    </row>
+    <row r="5" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>46123</v>
       </c>
@@ -6655,29 +6659,26 @@
         <v>37</v>
       </c>
       <c r="T5" s="3">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="U5" s="3">
-        <v>43</v>
+        <v>44.5</v>
       </c>
       <c r="V5" s="3">
-        <v>44.5</v>
+        <v>42</v>
       </c>
       <c r="W5" s="3">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="X5" s="3">
-        <v>46</v>
-      </c>
-      <c r="Y5" s="3">
         <v>45.25</v>
       </c>
-      <c r="Z5" s="4">
-        <f t="shared" ref="Z5:Z68" si="0">IF(COUNTA(B5:Y5)=0,"",AVERAGE(B5:Y5))</f>
-        <v>42.825416666666662</v>
-      </c>
-    </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y5" s="4">
+        <f>IF(COUNTA(B5:X5)=0,"",AVERAGE(B5:X5))</f>
+        <v>43.078695652173913</v>
+      </c>
+    </row>
+    <row r="6" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>46125</v>
       </c>
@@ -6736,29 +6737,26 @@
         <v>37</v>
       </c>
       <c r="T6" s="3">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="U6" s="3">
-        <v>43</v>
+        <v>44.5</v>
       </c>
       <c r="V6" s="3">
-        <v>44.5</v>
+        <v>42</v>
       </c>
       <c r="W6" s="3">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="X6" s="3">
-        <v>46</v>
-      </c>
-      <c r="Y6" s="3">
         <v>45.25</v>
       </c>
-      <c r="Z6" s="4">
-        <f t="shared" ref="Z6" si="1">IF(COUNTA(B6:Y6)=0,"",AVERAGE(B6:Y6))</f>
-        <v>42.825416666666662</v>
-      </c>
-    </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y6" s="4">
+        <f>IF(COUNTA(B6:X6)=0,"",AVERAGE(B6:X6))</f>
+        <v>43.078695652173913</v>
+      </c>
+    </row>
+    <row r="7" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>46126</v>
       </c>
@@ -6817,29 +6815,26 @@
         <v>37</v>
       </c>
       <c r="T7" s="3">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="U7" s="3">
-        <v>43</v>
+        <v>44.5</v>
       </c>
       <c r="V7" s="3">
-        <v>44.5</v>
+        <v>42</v>
       </c>
       <c r="W7" s="3">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="X7" s="3">
-        <v>46</v>
-      </c>
-      <c r="Y7" s="3">
         <v>45.25</v>
       </c>
-      <c r="Z7" s="4">
-        <f t="shared" si="0"/>
-        <v>42.825416666666662</v>
-      </c>
-    </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y7" s="4">
+        <f>IF(COUNTA(B7:X7)=0,"",AVERAGE(B7:X7))</f>
+        <v>43.078695652173913</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>46127</v>
       </c>
@@ -6898,29 +6893,26 @@
         <v>45</v>
       </c>
       <c r="T8" s="3">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="U8" s="3">
-        <v>43</v>
+        <v>44.5</v>
       </c>
       <c r="V8" s="3">
-        <v>44.5</v>
+        <v>42</v>
       </c>
       <c r="W8" s="3">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="X8" s="3">
-        <v>46</v>
-      </c>
-      <c r="Y8" s="3">
         <v>45.25</v>
       </c>
-      <c r="Z8" s="4">
-        <f t="shared" si="0"/>
-        <v>43.248333333333335</v>
-      </c>
-    </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y8" s="4">
+        <f>IF(COUNTA(B8:X8)=0,"",AVERAGE(B8:X8))</f>
+        <v>43.52</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>46128</v>
       </c>
@@ -6979,29 +6971,26 @@
         <v>45</v>
       </c>
       <c r="T9" s="3">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="U9" s="3">
-        <v>43</v>
+        <v>44.5</v>
       </c>
       <c r="V9" s="3">
-        <v>44.5</v>
+        <v>42</v>
       </c>
       <c r="W9" s="3">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="X9" s="3">
-        <v>46</v>
-      </c>
-      <c r="Y9" s="3">
         <v>45.25</v>
       </c>
-      <c r="Z9" s="4">
-        <f t="shared" si="0"/>
-        <v>43.085416666666667</v>
-      </c>
-    </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y9" s="4">
+        <f>IF(COUNTA(B9:X9)=0,"",AVERAGE(B9:X9))</f>
+        <v>43.35</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>46129</v>
       </c>
@@ -7060,29 +7049,26 @@
         <v>45</v>
       </c>
       <c r="T10" s="3">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="U10" s="3">
-        <v>43</v>
+        <v>44.5</v>
       </c>
       <c r="V10" s="3">
-        <v>44.5</v>
+        <v>42</v>
       </c>
       <c r="W10" s="3">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="X10" s="3">
-        <v>46</v>
-      </c>
-      <c r="Y10" s="3">
         <v>45.25</v>
       </c>
-      <c r="Z10" s="4">
-        <f t="shared" si="0"/>
-        <v>43.127083333333331</v>
-      </c>
-    </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y10" s="4">
+        <f>IF(COUNTA(B10:X10)=0,"",AVERAGE(B10:X10))</f>
+        <v>43.393478260869564</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <v>46132</v>
       </c>
@@ -7141,29 +7127,26 @@
         <v>45</v>
       </c>
       <c r="T11" s="3">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="U11" s="3">
-        <v>43</v>
+        <v>44.5</v>
       </c>
       <c r="V11" s="3">
-        <v>44.5</v>
+        <v>42</v>
       </c>
       <c r="W11" s="3">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="X11" s="3">
-        <v>46</v>
-      </c>
-      <c r="Y11" s="3">
         <v>45.25</v>
       </c>
-      <c r="Z11" s="4">
-        <f t="shared" si="0"/>
-        <v>43.085416666666667</v>
-      </c>
-    </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y11" s="4">
+        <f>IF(COUNTA(B11:X11)=0,"",AVERAGE(B11:X11))</f>
+        <v>43.35</v>
+      </c>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <v>46133</v>
       </c>
@@ -7222,29 +7205,26 @@
         <v>45</v>
       </c>
       <c r="T12" s="3">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="U12" s="3">
-        <v>43</v>
+        <v>44.25</v>
       </c>
       <c r="V12" s="3">
-        <v>44.25</v>
+        <v>42</v>
       </c>
       <c r="W12" s="3">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="X12" s="3">
-        <v>46</v>
-      </c>
-      <c r="Y12" s="3">
         <v>45.25</v>
       </c>
-      <c r="Z12" s="4">
-        <f t="shared" si="0"/>
-        <v>43.078749999999992</v>
-      </c>
-    </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y12" s="4">
+        <f>IF(COUNTA(B12:X12)=0,"",AVERAGE(B12:X12))</f>
+        <v>43.343043478260867</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
         <v>46134</v>
       </c>
@@ -7303,29 +7283,26 @@
         <v>45</v>
       </c>
       <c r="T13" s="3">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="U13" s="3">
-        <v>43</v>
+        <v>43.75</v>
       </c>
       <c r="V13" s="3">
-        <v>43.75</v>
+        <v>42</v>
       </c>
       <c r="W13" s="3">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="X13" s="3">
-        <v>46</v>
-      </c>
-      <c r="Y13" s="3">
         <v>45.25</v>
       </c>
-      <c r="Z13" s="4">
-        <f t="shared" si="0"/>
-        <v>43.109999999999992</v>
-      </c>
-    </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y13" s="4">
+        <f>IF(COUNTA(B13:X13)=0,"",AVERAGE(B13:X13))</f>
+        <v>43.375652173913046</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
         <v>46136</v>
       </c>
@@ -7384,29 +7361,26 @@
         <v>45</v>
       </c>
       <c r="T14" s="3">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="U14" s="3">
-        <v>43</v>
+        <v>43.75</v>
       </c>
       <c r="V14" s="3">
-        <v>43.75</v>
+        <v>42</v>
       </c>
       <c r="W14" s="3">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="X14" s="3">
-        <v>46</v>
-      </c>
-      <c r="Y14" s="3">
         <v>45.25</v>
       </c>
-      <c r="Z14" s="4">
-        <f t="shared" si="0"/>
-        <v>43.109999999999992</v>
-      </c>
-    </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y14" s="4">
+        <f>IF(COUNTA(B14:X14)=0,"",AVERAGE(B14:X14))</f>
+        <v>43.375652173913046</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
         <v>46139</v>
       </c>
@@ -7465,29 +7439,26 @@
         <v>45</v>
       </c>
       <c r="T15" s="3">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="U15" s="3">
-        <v>43</v>
+        <v>43.5</v>
       </c>
       <c r="V15" s="3">
-        <v>43.5</v>
+        <v>42</v>
       </c>
       <c r="W15" s="3">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="X15" s="3">
-        <v>46</v>
-      </c>
-      <c r="Y15" s="3">
         <v>45.25</v>
       </c>
-      <c r="Z15" s="4">
-        <f t="shared" si="0"/>
-        <v>43.099583333333328</v>
-      </c>
-    </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y15" s="4">
+        <f>IF(COUNTA(B15:X15)=0,"",AVERAGE(B15:X15))</f>
+        <v>43.364782608695648</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
         <v>46140</v>
       </c>
@@ -7546,29 +7517,26 @@
         <v>45</v>
       </c>
       <c r="T16" s="3">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="U16" s="3">
-        <v>43</v>
+        <v>43.5</v>
       </c>
       <c r="V16" s="3">
-        <v>43.5</v>
+        <v>42</v>
       </c>
       <c r="W16" s="3">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="X16" s="3">
-        <v>47</v>
-      </c>
-      <c r="Y16" s="3">
         <v>45.25</v>
       </c>
-      <c r="Z16" s="4">
-        <f t="shared" si="0"/>
-        <v>43.148750000000007</v>
-      </c>
-    </row>
-    <row r="17" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y16" s="4">
+        <f>IF(COUNTA(B16:X16)=0,"",AVERAGE(B16:X16))</f>
+        <v>43.416086956521738</v>
+      </c>
+    </row>
+    <row r="17" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
         <v>46141</v>
       </c>
@@ -7627,29 +7595,26 @@
         <v>45</v>
       </c>
       <c r="T17" s="3">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="U17" s="3">
-        <v>43</v>
+        <v>43.5</v>
       </c>
       <c r="V17" s="3">
-        <v>43.5</v>
+        <v>42</v>
       </c>
       <c r="W17" s="3">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="X17" s="3">
-        <v>47</v>
-      </c>
-      <c r="Y17" s="3">
         <v>45.25</v>
       </c>
-      <c r="Z17" s="4">
-        <f t="shared" si="0"/>
-        <v>43.117500000000007</v>
-      </c>
-    </row>
-    <row r="18" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y17" s="4">
+        <f>IF(COUNTA(B17:X17)=0,"",AVERAGE(B17:X17))</f>
+        <v>43.383478260869566</v>
+      </c>
+    </row>
+    <row r="18" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
         <v>46142</v>
       </c>
@@ -7708,29 +7673,26 @@
         <v>45</v>
       </c>
       <c r="T18" s="3">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="U18" s="3">
-        <v>43</v>
+        <v>43.5</v>
       </c>
       <c r="V18" s="3">
-        <v>43.5</v>
+        <v>42</v>
       </c>
       <c r="W18" s="3">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="X18" s="3">
-        <v>47</v>
-      </c>
-      <c r="Y18" s="3">
         <v>45.25</v>
       </c>
-      <c r="Z18" s="4">
-        <f t="shared" si="0"/>
-        <v>43.117500000000007</v>
-      </c>
-    </row>
-    <row r="19" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y18" s="4">
+        <f>IF(COUNTA(B18:X18)=0,"",AVERAGE(B18:X18))</f>
+        <v>43.383478260869566</v>
+      </c>
+    </row>
+    <row r="19" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
         <v>46146</v>
       </c>
@@ -7789,29 +7751,26 @@
         <v>45</v>
       </c>
       <c r="T19" s="3">
+        <v>43.5</v>
+      </c>
+      <c r="U19" s="3">
         <v>45</v>
       </c>
-      <c r="U19" s="3">
-        <v>43.5</v>
-      </c>
       <c r="V19" s="3">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="W19" s="3">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="X19" s="3">
-        <v>47</v>
-      </c>
-      <c r="Y19" s="3">
         <v>45.25</v>
       </c>
-      <c r="Z19" s="4">
-        <f t="shared" si="0"/>
-        <v>43.534166666666671</v>
-      </c>
-    </row>
-    <row r="20" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y19" s="4">
+        <f>IF(COUNTA(B19:X19)=0,"",AVERAGE(B19:X19))</f>
+        <v>43.470434782608699</v>
+      </c>
+    </row>
+    <row r="20" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
         <v>46147</v>
       </c>
@@ -7870,29 +7829,26 @@
         <v>45</v>
       </c>
       <c r="T20" s="3">
-        <v>45</v>
+        <v>43.5</v>
       </c>
       <c r="U20" s="3">
-        <v>43.5</v>
+        <v>44</v>
       </c>
       <c r="V20" s="3">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="W20" s="3">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="X20" s="3">
-        <v>47</v>
-      </c>
-      <c r="Y20" s="3">
         <v>45.25</v>
       </c>
-      <c r="Z20" s="4">
-        <f t="shared" si="0"/>
-        <v>43.502083333333331</v>
-      </c>
-    </row>
-    <row r="21" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y20" s="4">
+        <f>IF(COUNTA(B20:X20)=0,"",AVERAGE(B20:X20))</f>
+        <v>43.436956521739127</v>
+      </c>
+    </row>
+    <row r="21" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
         <v>46148</v>
       </c>
@@ -7951,29 +7907,26 @@
         <v>45</v>
       </c>
       <c r="T21" s="3">
-        <v>45</v>
+        <v>43.5</v>
       </c>
       <c r="U21" s="3">
-        <v>43.5</v>
+        <v>43.75</v>
       </c>
       <c r="V21" s="3">
-        <v>43.75</v>
+        <v>42</v>
       </c>
       <c r="W21" s="3">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="X21" s="3">
-        <v>47</v>
-      </c>
-      <c r="Y21" s="3">
         <v>45.25</v>
       </c>
-      <c r="Z21" s="4">
-        <f t="shared" si="0"/>
-        <v>43.491666666666667</v>
-      </c>
-    </row>
-    <row r="22" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y21" s="4">
+        <f>IF(COUNTA(B21:X21)=0,"",AVERAGE(B21:X21))</f>
+        <v>43.426086956521736</v>
+      </c>
+    </row>
+    <row r="22" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
         <v>46149</v>
       </c>
@@ -8032,29 +7985,26 @@
         <v>45</v>
       </c>
       <c r="T22" s="3">
-        <v>45</v>
+        <v>43.5</v>
       </c>
       <c r="U22" s="3">
-        <v>43.5</v>
+        <v>43.25</v>
       </c>
       <c r="V22" s="3">
-        <v>43.25</v>
+        <v>42</v>
       </c>
       <c r="W22" s="3">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="X22" s="3">
-        <v>47</v>
-      </c>
-      <c r="Y22" s="3">
         <v>45.25</v>
       </c>
-      <c r="Z22" s="4">
-        <f t="shared" si="0"/>
-        <v>43.460416666666667</v>
-      </c>
-    </row>
-    <row r="23" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y22" s="4">
+        <f>IF(COUNTA(B22:X22)=0,"",AVERAGE(B22:X22))</f>
+        <v>43.393478260869564</v>
+      </c>
+    </row>
+    <row r="23" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
         <v>46150</v>
       </c>
@@ -8113,29 +8063,26 @@
         <v>45</v>
       </c>
       <c r="T23" s="3">
-        <v>45</v>
+        <v>43.5</v>
       </c>
       <c r="U23" s="3">
-        <v>43.5</v>
+        <v>43</v>
       </c>
       <c r="V23" s="3">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="W23" s="3">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="X23" s="3">
-        <v>47</v>
-      </c>
-      <c r="Y23" s="3">
         <v>45.25</v>
       </c>
-      <c r="Z23" s="4">
-        <f t="shared" si="0"/>
-        <v>43.449999999999996</v>
-      </c>
-    </row>
-    <row r="24" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y23" s="4">
+        <f>IF(COUNTA(B23:X23)=0,"",AVERAGE(B23:X23))</f>
+        <v>43.382608695652173</v>
+      </c>
+    </row>
+    <row r="24" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
         <v>46153</v>
       </c>
@@ -8194,29 +8141,26 @@
         <v>45</v>
       </c>
       <c r="T24" s="3">
-        <v>45</v>
+        <v>43.5</v>
       </c>
       <c r="U24" s="3">
-        <v>43.5</v>
+        <v>43</v>
       </c>
       <c r="V24" s="3">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="W24" s="3">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="X24" s="3">
-        <v>47</v>
-      </c>
-      <c r="Y24" s="3">
         <v>45.25</v>
       </c>
-      <c r="Z24" s="4">
-        <f t="shared" si="0"/>
-        <v>43.449999999999996</v>
-      </c>
-    </row>
-    <row r="25" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y24" s="4">
+        <f>IF(COUNTA(B24:X24)=0,"",AVERAGE(B24:X24))</f>
+        <v>43.382608695652173</v>
+      </c>
+    </row>
+    <row r="25" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
         <v>46154</v>
       </c>
@@ -8275,29 +8219,26 @@
         <v>45</v>
       </c>
       <c r="T25" s="3">
-        <v>45</v>
+        <v>43.5</v>
       </c>
       <c r="U25" s="3">
-        <v>43.5</v>
+        <v>43</v>
       </c>
       <c r="V25" s="3">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="W25" s="3">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="X25" s="3">
-        <v>47</v>
-      </c>
-      <c r="Y25" s="3">
         <v>45.25</v>
       </c>
-      <c r="Z25" s="4">
-        <f t="shared" si="0"/>
-        <v>43.439583333333331</v>
-      </c>
-    </row>
-    <row r="26" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y25" s="4">
+        <f>IF(COUNTA(B25:X25)=0,"",AVERAGE(B25:X25))</f>
+        <v>43.371739130434783</v>
+      </c>
+    </row>
+    <row r="26" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
         <v>46155</v>
       </c>
@@ -8356,29 +8297,26 @@
         <v>45</v>
       </c>
       <c r="T26" s="3">
-        <v>45</v>
+        <v>43.5</v>
       </c>
       <c r="U26" s="3">
         <v>43.5</v>
       </c>
       <c r="V26" s="3">
-        <v>43.5</v>
+        <v>42</v>
       </c>
       <c r="W26" s="3">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="X26" s="3">
-        <v>47</v>
-      </c>
-      <c r="Y26" s="3">
         <v>45.25</v>
       </c>
-      <c r="Z26" s="4">
-        <f t="shared" si="0"/>
-        <v>43.455000000000005</v>
-      </c>
-    </row>
-    <row r="27" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y26" s="4">
+        <f>IF(COUNTA(B26:X26)=0,"",AVERAGE(B26:X26))</f>
+        <v>43.387826086956522</v>
+      </c>
+    </row>
+    <row r="27" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
         <v>46156</v>
       </c>
@@ -8437,29 +8375,26 @@
         <v>45</v>
       </c>
       <c r="T27" s="3">
-        <v>45</v>
+        <v>43.5</v>
       </c>
       <c r="U27" s="3">
         <v>43.5</v>
       </c>
       <c r="V27" s="3">
-        <v>43.5</v>
+        <v>42</v>
       </c>
       <c r="W27" s="3">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="X27" s="3">
-        <v>47</v>
-      </c>
-      <c r="Y27" s="3">
         <v>45.25</v>
       </c>
-      <c r="Z27" s="4">
-        <f t="shared" si="0"/>
-        <v>43.413333333333334</v>
-      </c>
-    </row>
-    <row r="28" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y27" s="4">
+        <f>IF(COUNTA(B27:X27)=0,"",AVERAGE(B27:X27))</f>
+        <v>43.344347826086953</v>
+      </c>
+    </row>
+    <row r="28" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A28" s="2">
         <v>46157</v>
       </c>
@@ -8518,29 +8453,26 @@
         <v>45</v>
       </c>
       <c r="T28" s="3">
-        <v>45</v>
+        <v>43.5</v>
       </c>
       <c r="U28" s="3">
         <v>43.5</v>
       </c>
       <c r="V28" s="3">
-        <v>43.5</v>
+        <v>42</v>
       </c>
       <c r="W28" s="3">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="X28" s="3">
-        <v>47</v>
-      </c>
-      <c r="Y28" s="3">
         <v>45.25</v>
       </c>
-      <c r="Z28" s="4">
-        <f t="shared" si="0"/>
-        <v>43.413333333333334</v>
-      </c>
-    </row>
-    <row r="29" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y28" s="4">
+        <f>IF(COUNTA(B28:X28)=0,"",AVERAGE(B28:X28))</f>
+        <v>43.344347826086953</v>
+      </c>
+    </row>
+    <row r="29" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A29" s="2">
         <v>46160</v>
       </c>
@@ -8599,29 +8531,26 @@
         <v>45</v>
       </c>
       <c r="T29" s="3">
-        <v>45</v>
+        <v>43.5</v>
       </c>
       <c r="U29" s="3">
         <v>43.5</v>
       </c>
       <c r="V29" s="3">
-        <v>43.5</v>
+        <v>42</v>
       </c>
       <c r="W29" s="3">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="X29" s="3">
-        <v>47</v>
-      </c>
-      <c r="Y29" s="3">
         <v>45.25</v>
       </c>
-      <c r="Z29" s="4">
-        <f t="shared" si="0"/>
-        <v>43.413333333333334</v>
-      </c>
-    </row>
-    <row r="30" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y29" s="4">
+        <f>IF(COUNTA(B29:X29)=0,"",AVERAGE(B29:X29))</f>
+        <v>43.344347826086953</v>
+      </c>
+    </row>
+    <row r="30" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A30" s="2">
         <v>46162</v>
       </c>
@@ -8680,29 +8609,26 @@
         <v>45</v>
       </c>
       <c r="T30" s="3">
-        <v>45</v>
+        <v>43.5</v>
       </c>
       <c r="U30" s="3">
-        <v>43.5</v>
+        <v>44.5</v>
       </c>
       <c r="V30" s="3">
-        <v>44.5</v>
+        <v>42</v>
       </c>
       <c r="W30" s="3">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="X30" s="3">
-        <v>47</v>
-      </c>
-      <c r="Y30" s="3">
         <v>45.25</v>
       </c>
-      <c r="Z30" s="4">
-        <f t="shared" si="0"/>
-        <v>43.455000000000005</v>
-      </c>
-    </row>
-    <row r="31" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y30" s="4">
+        <f>IF(COUNTA(B30:X30)=0,"",AVERAGE(B30:X30))</f>
+        <v>43.387826086956522</v>
+      </c>
+    </row>
+    <row r="31" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A31" s="2">
         <v>46163</v>
       </c>
@@ -8761,29 +8687,26 @@
         <v>45</v>
       </c>
       <c r="T31" s="3">
-        <v>45</v>
+        <v>43.5</v>
       </c>
       <c r="U31" s="3">
-        <v>43.5</v>
+        <v>44.5</v>
       </c>
       <c r="V31" s="3">
-        <v>44.5</v>
+        <v>42</v>
       </c>
       <c r="W31" s="3">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="X31" s="3">
-        <v>47</v>
-      </c>
-      <c r="Y31" s="3">
         <v>45.25</v>
       </c>
-      <c r="Z31" s="4">
-        <f t="shared" si="0"/>
-        <v>43.434583333333329</v>
-      </c>
-    </row>
-    <row r="32" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y31" s="4">
+        <f>IF(COUNTA(B31:X31)=0,"",AVERAGE(B31:X31))</f>
+        <v>43.366521739130434</v>
+      </c>
+    </row>
+    <row r="32" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A32" s="2">
         <v>46164</v>
       </c>
@@ -8842,29 +8765,26 @@
         <v>45</v>
       </c>
       <c r="T32" s="3">
-        <v>45</v>
+        <v>43.5</v>
       </c>
       <c r="U32" s="3">
-        <v>43.5</v>
+        <v>44.5</v>
       </c>
       <c r="V32" s="3">
-        <v>44.5</v>
+        <v>42</v>
       </c>
       <c r="W32" s="3">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="X32" s="3">
-        <v>47</v>
-      </c>
-      <c r="Y32" s="3">
         <v>45.25</v>
       </c>
-      <c r="Z32" s="4">
-        <f t="shared" ref="Z32" si="2">IF(COUNTA(B32:Y32)=0,"",AVERAGE(B32:Y32))</f>
-        <v>43.434583333333329</v>
-      </c>
-    </row>
-    <row r="33" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y32" s="4">
+        <f>IF(COUNTA(B32:X32)=0,"",AVERAGE(B32:X32))</f>
+        <v>43.366521739130434</v>
+      </c>
+    </row>
+    <row r="33" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A33" s="2">
         <v>46167</v>
       </c>
@@ -8923,29 +8843,26 @@
         <v>45</v>
       </c>
       <c r="T33" s="3">
+        <v>43.5</v>
+      </c>
+      <c r="U33" s="3">
         <v>45</v>
       </c>
-      <c r="U33" s="3">
-        <v>43.5</v>
-      </c>
       <c r="V33" s="3">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="W33" s="3">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="X33" s="3">
-        <v>47</v>
-      </c>
-      <c r="Y33" s="3">
         <v>45.25</v>
       </c>
-      <c r="Z33" s="4">
-        <f t="shared" si="0"/>
-        <v>43.476249999999993</v>
-      </c>
-    </row>
-    <row r="34" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y33" s="4">
+        <f>IF(COUNTA(B33:X33)=0,"",AVERAGE(B33:X33))</f>
+        <v>43.41</v>
+      </c>
+    </row>
+    <row r="34" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A34" s="2">
         <v>46168</v>
       </c>
@@ -9004,29 +8921,26 @@
         <v>45</v>
       </c>
       <c r="T34" s="3">
+        <v>43.5</v>
+      </c>
+      <c r="U34" s="3">
         <v>45</v>
       </c>
-      <c r="U34" s="3">
-        <v>43.5</v>
-      </c>
       <c r="V34" s="3">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="W34" s="3">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="X34" s="3">
-        <v>47</v>
-      </c>
-      <c r="Y34" s="3">
         <v>45.25</v>
       </c>
-      <c r="Z34" s="4">
-        <f t="shared" ref="Z34" si="3">IF(COUNTA(B34:Y34)=0,"",AVERAGE(B34:Y34))</f>
-        <v>43.476249999999993</v>
-      </c>
-    </row>
-    <row r="35" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y34" s="4">
+        <f>IF(COUNTA(B34:X34)=0,"",AVERAGE(B34:X34))</f>
+        <v>43.41</v>
+      </c>
+    </row>
+    <row r="35" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A35" s="2">
         <v>46174</v>
       </c>
@@ -9085,29 +8999,26 @@
         <v>45</v>
       </c>
       <c r="T35" s="3">
+        <v>43.5</v>
+      </c>
+      <c r="U35" s="3">
         <v>45</v>
       </c>
-      <c r="U35" s="3">
-        <v>43.5</v>
-      </c>
       <c r="V35" s="3">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="W35" s="3">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="X35" s="3">
-        <v>47</v>
-      </c>
-      <c r="Y35" s="3">
         <v>45.25</v>
       </c>
-      <c r="Z35" s="4">
-        <f t="shared" ref="Z35" si="4">IF(COUNTA(B35:Y35)=0,"",AVERAGE(B35:Y35))</f>
-        <v>43.476249999999993</v>
-      </c>
-    </row>
-    <row r="36" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y35" s="4">
+        <f>IF(COUNTA(B35:X35)=0,"",AVERAGE(B35:X35))</f>
+        <v>43.41</v>
+      </c>
+    </row>
+    <row r="36" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A36" s="2">
         <v>46175</v>
       </c>
@@ -9166,29 +9077,26 @@
         <v>45</v>
       </c>
       <c r="T36" s="3">
-        <v>45</v>
+        <v>43.5</v>
       </c>
       <c r="U36" s="3">
-        <v>43.5</v>
+        <v>44.5</v>
       </c>
       <c r="V36" s="3">
-        <v>44.5</v>
+        <v>42</v>
       </c>
       <c r="W36" s="3">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="X36" s="3">
-        <v>47</v>
-      </c>
-      <c r="Y36" s="3">
         <v>45.25</v>
       </c>
-      <c r="Z36" s="4">
-        <f t="shared" si="0"/>
-        <v>43.472500000000004</v>
-      </c>
-    </row>
-    <row r="37" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y36" s="4">
+        <f>IF(COUNTA(B36:X36)=0,"",AVERAGE(B36:X36))</f>
+        <v>43.40608695652174</v>
+      </c>
+    </row>
+    <row r="37" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A37" s="2">
         <v>46176</v>
       </c>
@@ -9247,29 +9155,26 @@
         <v>45</v>
       </c>
       <c r="T37" s="3">
-        <v>45</v>
+        <v>43.5</v>
       </c>
       <c r="U37" s="3">
-        <v>43.5</v>
+        <v>44.5</v>
       </c>
       <c r="V37" s="3">
-        <v>44.5</v>
+        <v>42</v>
       </c>
       <c r="W37" s="3">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="X37" s="3">
-        <v>47</v>
-      </c>
-      <c r="Y37" s="3">
         <v>45.25</v>
       </c>
-      <c r="Z37" s="4">
-        <f t="shared" ref="Z37" si="5">IF(COUNTA(B37:Y37)=0,"",AVERAGE(B37:Y37))</f>
-        <v>43.472500000000004</v>
-      </c>
-    </row>
-    <row r="38" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y37" s="4">
+        <f>IF(COUNTA(B37:X37)=0,"",AVERAGE(B37:X37))</f>
+        <v>43.40608695652174</v>
+      </c>
+    </row>
+    <row r="38" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A38" s="2">
         <v>46177</v>
       </c>
@@ -9328,29 +9233,26 @@
         <v>45</v>
       </c>
       <c r="T38" s="3">
-        <v>45</v>
+        <v>43.5</v>
       </c>
       <c r="U38" s="3">
-        <v>43.5</v>
+        <v>44.5</v>
       </c>
       <c r="V38" s="3">
-        <v>44.5</v>
+        <v>42</v>
       </c>
       <c r="W38" s="3">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="X38" s="3">
-        <v>47</v>
-      </c>
-      <c r="Y38" s="3">
         <v>45.25</v>
       </c>
-      <c r="Z38" s="4">
-        <f t="shared" ref="Z38" si="6">IF(COUNTA(B38:Y38)=0,"",AVERAGE(B38:Y38))</f>
-        <v>43.472500000000004</v>
-      </c>
-    </row>
-    <row r="39" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y38" s="4">
+        <f>IF(COUNTA(B38:X38)=0,"",AVERAGE(B38:X38))</f>
+        <v>43.40608695652174</v>
+      </c>
+    </row>
+    <row r="39" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A39" s="2">
         <v>46178</v>
       </c>
@@ -9409,29 +9311,26 @@
         <v>45</v>
       </c>
       <c r="T39" s="3">
-        <v>45</v>
+        <v>43.5</v>
       </c>
       <c r="U39" s="3">
-        <v>43.5</v>
+        <v>44.5</v>
       </c>
       <c r="V39" s="3">
-        <v>44.5</v>
+        <v>42</v>
       </c>
       <c r="W39" s="3">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="X39" s="3">
-        <v>47</v>
-      </c>
-      <c r="Y39" s="3">
         <v>45.25</v>
       </c>
-      <c r="Z39" s="4">
-        <f t="shared" si="0"/>
-        <v>43.472500000000004</v>
-      </c>
-    </row>
-    <row r="40" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y39" s="4">
+        <f>IF(COUNTA(B39:X39)=0,"",AVERAGE(B39:X39))</f>
+        <v>43.40608695652174</v>
+      </c>
+    </row>
+    <row r="40" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A40" s="2">
         <v>46181</v>
       </c>
@@ -9490,60 +9389,104 @@
         <v>45</v>
       </c>
       <c r="T40" s="3">
+        <v>43.5</v>
+      </c>
+      <c r="U40" s="3">
+        <v>44.5</v>
+      </c>
+      <c r="V40" s="3">
+        <v>42</v>
+      </c>
+      <c r="W40" s="3">
+        <v>47</v>
+      </c>
+      <c r="X40" s="3">
+        <v>45.25</v>
+      </c>
+      <c r="Y40" s="4">
+        <f>IF(COUNTA(B40:X40)=0,"",AVERAGE(B40:X40))</f>
+        <v>43.40608695652174</v>
+      </c>
+    </row>
+    <row r="41" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A41" s="2">
+        <v>46182</v>
+      </c>
+      <c r="B41" s="3">
+        <v>42.5</v>
+      </c>
+      <c r="C41" s="3">
+        <v>46</v>
+      </c>
+      <c r="D41" s="3">
+        <v>46</v>
+      </c>
+      <c r="E41" s="3">
         <v>45</v>
       </c>
-      <c r="U40" s="3">
+      <c r="F41" s="3">
         <v>43.5</v>
       </c>
-      <c r="V40" s="3">
+      <c r="G41" s="3">
+        <v>41</v>
+      </c>
+      <c r="H41" s="3">
+        <v>46</v>
+      </c>
+      <c r="I41" s="3">
+        <v>41.5</v>
+      </c>
+      <c r="J41" s="3">
+        <v>43</v>
+      </c>
+      <c r="K41" s="3">
+        <v>41</v>
+      </c>
+      <c r="L41" s="3">
+        <v>36</v>
+      </c>
+      <c r="M41" s="3">
+        <v>44</v>
+      </c>
+      <c r="N41" s="3">
+        <v>45</v>
+      </c>
+      <c r="O41" s="3">
+        <v>42.39</v>
+      </c>
+      <c r="P41" s="3">
+        <v>39</v>
+      </c>
+      <c r="Q41" s="3">
+        <v>45</v>
+      </c>
+      <c r="R41" s="3">
+        <v>45</v>
+      </c>
+      <c r="S41" s="3">
+        <v>45</v>
+      </c>
+      <c r="T41" s="3">
+        <v>43.5</v>
+      </c>
+      <c r="U41" s="3">
         <v>44.5</v>
       </c>
-      <c r="W40" s="3">
+      <c r="V41" s="3">
         <v>42</v>
       </c>
-      <c r="X40" s="3">
+      <c r="W41" s="3">
         <v>47</v>
       </c>
-      <c r="Y40" s="3">
+      <c r="X41" s="3">
         <v>45.25</v>
       </c>
-      <c r="Z40" s="4">
-        <f t="shared" si="0"/>
-        <v>43.472500000000004</v>
-      </c>
-    </row>
-    <row r="41" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A41" s="2"/>
-      <c r="B41" s="3"/>
-      <c r="C41" s="3"/>
-      <c r="D41" s="3"/>
-      <c r="E41" s="3"/>
-      <c r="F41" s="3"/>
-      <c r="G41" s="3"/>
-      <c r="H41" s="3"/>
-      <c r="I41" s="3"/>
-      <c r="J41" s="3"/>
-      <c r="K41" s="3"/>
-      <c r="L41" s="3"/>
-      <c r="M41" s="3"/>
-      <c r="N41" s="3"/>
-      <c r="O41" s="3"/>
-      <c r="P41" s="3"/>
-      <c r="Q41" s="3"/>
-      <c r="R41" s="3"/>
-      <c r="S41" s="3"/>
-      <c r="T41" s="3"/>
-      <c r="U41" s="3"/>
-      <c r="V41" s="3"/>
-      <c r="W41" s="3"/>
-      <c r="X41" s="3"/>
-      <c r="Y41" s="3"/>
-      <c r="Z41" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="42" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y41" s="4">
+        <f>IF(COUNTA(B41:X41)=0,"",AVERAGE(B41:X41))</f>
+        <v>43.44086956521739</v>
+      </c>
+    </row>
+    <row r="42" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A42" s="2"/>
       <c r="B42" s="3"/>
       <c r="C42" s="3"/>
@@ -9568,13 +9511,12 @@
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
-      <c r="Y42" s="3"/>
-      <c r="Z42" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="43" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y42" s="4" t="str">
+        <f>IF(COUNTA(B42:X42)=0,"",AVERAGE(B42:X42))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A43" s="2"/>
       <c r="B43" s="3"/>
       <c r="C43" s="3"/>
@@ -9599,13 +9541,12 @@
       <c r="V43" s="3"/>
       <c r="W43" s="3"/>
       <c r="X43" s="3"/>
-      <c r="Y43" s="3"/>
-      <c r="Z43" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="44" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y43" s="4" t="str">
+        <f>IF(COUNTA(B43:X43)=0,"",AVERAGE(B43:X43))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A44" s="2"/>
       <c r="B44" s="3"/>
       <c r="C44" s="3"/>
@@ -9630,13 +9571,12 @@
       <c r="V44" s="3"/>
       <c r="W44" s="3"/>
       <c r="X44" s="3"/>
-      <c r="Y44" s="3"/>
-      <c r="Z44" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="45" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y44" s="4" t="str">
+        <f>IF(COUNTA(B44:X44)=0,"",AVERAGE(B44:X44))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A45" s="2"/>
       <c r="B45" s="3"/>
       <c r="C45" s="3"/>
@@ -9661,13 +9601,12 @@
       <c r="V45" s="3"/>
       <c r="W45" s="3"/>
       <c r="X45" s="3"/>
-      <c r="Y45" s="3"/>
-      <c r="Z45" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="46" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y45" s="4" t="str">
+        <f>IF(COUNTA(B45:X45)=0,"",AVERAGE(B45:X45))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A46" s="2"/>
       <c r="B46" s="3"/>
       <c r="C46" s="3"/>
@@ -9692,13 +9631,12 @@
       <c r="V46" s="3"/>
       <c r="W46" s="3"/>
       <c r="X46" s="3"/>
-      <c r="Y46" s="3"/>
-      <c r="Z46" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="47" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y46" s="4" t="str">
+        <f>IF(COUNTA(B46:X46)=0,"",AVERAGE(B46:X46))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A47" s="2"/>
       <c r="B47" s="3"/>
       <c r="C47" s="3"/>
@@ -9723,13 +9661,12 @@
       <c r="V47" s="3"/>
       <c r="W47" s="3"/>
       <c r="X47" s="3"/>
-      <c r="Y47" s="3"/>
-      <c r="Z47" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="48" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y47" s="4" t="str">
+        <f>IF(COUNTA(B47:X47)=0,"",AVERAGE(B47:X47))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A48" s="2"/>
       <c r="B48" s="3"/>
       <c r="C48" s="3"/>
@@ -9754,13 +9691,12 @@
       <c r="V48" s="3"/>
       <c r="W48" s="3"/>
       <c r="X48" s="3"/>
-      <c r="Y48" s="3"/>
-      <c r="Z48" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="49" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y48" s="4" t="str">
+        <f>IF(COUNTA(B48:X48)=0,"",AVERAGE(B48:X48))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A49" s="2"/>
       <c r="B49" s="3"/>
       <c r="C49" s="3"/>
@@ -9785,13 +9721,12 @@
       <c r="V49" s="3"/>
       <c r="W49" s="3"/>
       <c r="X49" s="3"/>
-      <c r="Y49" s="3"/>
-      <c r="Z49" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="50" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y49" s="4" t="str">
+        <f>IF(COUNTA(B49:X49)=0,"",AVERAGE(B49:X49))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A50" s="2"/>
       <c r="B50" s="3"/>
       <c r="C50" s="3"/>
@@ -9816,13 +9751,12 @@
       <c r="V50" s="3"/>
       <c r="W50" s="3"/>
       <c r="X50" s="3"/>
-      <c r="Y50" s="3"/>
-      <c r="Z50" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="51" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y50" s="4" t="str">
+        <f>IF(COUNTA(B50:X50)=0,"",AVERAGE(B50:X50))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A51" s="2"/>
       <c r="B51" s="3"/>
       <c r="C51" s="3"/>
@@ -9847,13 +9781,12 @@
       <c r="V51" s="3"/>
       <c r="W51" s="3"/>
       <c r="X51" s="3"/>
-      <c r="Y51" s="3"/>
-      <c r="Z51" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="52" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y51" s="4" t="str">
+        <f>IF(COUNTA(B51:X51)=0,"",AVERAGE(B51:X51))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A52" s="2"/>
       <c r="B52" s="3"/>
       <c r="C52" s="3"/>
@@ -9878,13 +9811,12 @@
       <c r="V52" s="3"/>
       <c r="W52" s="3"/>
       <c r="X52" s="3"/>
-      <c r="Y52" s="3"/>
-      <c r="Z52" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="53" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y52" s="4" t="str">
+        <f>IF(COUNTA(B52:X52)=0,"",AVERAGE(B52:X52))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A53" s="2"/>
       <c r="B53" s="3"/>
       <c r="C53" s="3"/>
@@ -9909,13 +9841,12 @@
       <c r="V53" s="3"/>
       <c r="W53" s="3"/>
       <c r="X53" s="3"/>
-      <c r="Y53" s="3"/>
-      <c r="Z53" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="54" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y53" s="4" t="str">
+        <f>IF(COUNTA(B53:X53)=0,"",AVERAGE(B53:X53))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A54" s="2"/>
       <c r="B54" s="3"/>
       <c r="C54" s="3"/>
@@ -9940,13 +9871,12 @@
       <c r="V54" s="3"/>
       <c r="W54" s="3"/>
       <c r="X54" s="3"/>
-      <c r="Y54" s="3"/>
-      <c r="Z54" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="55" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y54" s="4" t="str">
+        <f>IF(COUNTA(B54:X54)=0,"",AVERAGE(B54:X54))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A55" s="2"/>
       <c r="B55" s="3"/>
       <c r="C55" s="3"/>
@@ -9971,13 +9901,12 @@
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
-      <c r="Y55" s="3"/>
-      <c r="Z55" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="56" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y55" s="4" t="str">
+        <f>IF(COUNTA(B55:X55)=0,"",AVERAGE(B55:X55))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A56" s="2"/>
       <c r="B56" s="3"/>
       <c r="C56" s="3"/>
@@ -10002,13 +9931,12 @@
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
-      <c r="Y56" s="3"/>
-      <c r="Z56" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="57" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y56" s="4" t="str">
+        <f>IF(COUNTA(B56:X56)=0,"",AVERAGE(B56:X56))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A57" s="2"/>
       <c r="B57" s="3"/>
       <c r="C57" s="3"/>
@@ -10033,13 +9961,12 @@
       <c r="V57" s="3"/>
       <c r="W57" s="3"/>
       <c r="X57" s="3"/>
-      <c r="Y57" s="3"/>
-      <c r="Z57" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="58" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y57" s="4" t="str">
+        <f>IF(COUNTA(B57:X57)=0,"",AVERAGE(B57:X57))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A58" s="2"/>
       <c r="B58" s="3"/>
       <c r="C58" s="3"/>
@@ -10064,13 +9991,12 @@
       <c r="V58" s="3"/>
       <c r="W58" s="3"/>
       <c r="X58" s="3"/>
-      <c r="Y58" s="3"/>
-      <c r="Z58" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="59" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y58" s="4" t="str">
+        <f>IF(COUNTA(B58:X58)=0,"",AVERAGE(B58:X58))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A59" s="2"/>
       <c r="B59" s="3"/>
       <c r="C59" s="3"/>
@@ -10095,13 +10021,12 @@
       <c r="V59" s="3"/>
       <c r="W59" s="3"/>
       <c r="X59" s="3"/>
-      <c r="Y59" s="3"/>
-      <c r="Z59" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="60" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y59" s="4" t="str">
+        <f>IF(COUNTA(B59:X59)=0,"",AVERAGE(B59:X59))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A60" s="2"/>
       <c r="B60" s="3"/>
       <c r="C60" s="3"/>
@@ -10126,13 +10051,12 @@
       <c r="V60" s="3"/>
       <c r="W60" s="3"/>
       <c r="X60" s="3"/>
-      <c r="Y60" s="3"/>
-      <c r="Z60" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="61" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y60" s="4" t="str">
+        <f>IF(COUNTA(B60:X60)=0,"",AVERAGE(B60:X60))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="61" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A61" s="2"/>
       <c r="B61" s="3"/>
       <c r="C61" s="3"/>
@@ -10157,13 +10081,12 @@
       <c r="V61" s="3"/>
       <c r="W61" s="3"/>
       <c r="X61" s="3"/>
-      <c r="Y61" s="3"/>
-      <c r="Z61" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="62" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y61" s="4" t="str">
+        <f>IF(COUNTA(B61:X61)=0,"",AVERAGE(B61:X61))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="62" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A62" s="2"/>
       <c r="B62" s="3"/>
       <c r="C62" s="3"/>
@@ -10188,13 +10111,12 @@
       <c r="V62" s="3"/>
       <c r="W62" s="3"/>
       <c r="X62" s="3"/>
-      <c r="Y62" s="3"/>
-      <c r="Z62" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="63" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y62" s="4" t="str">
+        <f>IF(COUNTA(B62:X62)=0,"",AVERAGE(B62:X62))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="63" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A63" s="2"/>
       <c r="B63" s="3"/>
       <c r="C63" s="3"/>
@@ -10219,13 +10141,12 @@
       <c r="V63" s="3"/>
       <c r="W63" s="3"/>
       <c r="X63" s="3"/>
-      <c r="Y63" s="3"/>
-      <c r="Z63" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="64" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y63" s="4" t="str">
+        <f>IF(COUNTA(B63:X63)=0,"",AVERAGE(B63:X63))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="64" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A64" s="2"/>
       <c r="B64" s="3"/>
       <c r="C64" s="3"/>
@@ -10250,13 +10171,12 @@
       <c r="V64" s="3"/>
       <c r="W64" s="3"/>
       <c r="X64" s="3"/>
-      <c r="Y64" s="3"/>
-      <c r="Z64" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="65" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y64" s="4" t="str">
+        <f>IF(COUNTA(B64:X64)=0,"",AVERAGE(B64:X64))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="65" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A65" s="2"/>
       <c r="B65" s="3"/>
       <c r="C65" s="3"/>
@@ -10281,13 +10201,12 @@
       <c r="V65" s="3"/>
       <c r="W65" s="3"/>
       <c r="X65" s="3"/>
-      <c r="Y65" s="3"/>
-      <c r="Z65" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="66" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y65" s="4" t="str">
+        <f>IF(COUNTA(B65:X65)=0,"",AVERAGE(B65:X65))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="66" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A66" s="2"/>
       <c r="B66" s="3"/>
       <c r="C66" s="3"/>
@@ -10312,13 +10231,12 @@
       <c r="V66" s="3"/>
       <c r="W66" s="3"/>
       <c r="X66" s="3"/>
-      <c r="Y66" s="3"/>
-      <c r="Z66" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="67" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y66" s="4" t="str">
+        <f>IF(COUNTA(B66:X66)=0,"",AVERAGE(B66:X66))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="67" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A67" s="2"/>
       <c r="B67" s="3"/>
       <c r="C67" s="3"/>
@@ -10343,13 +10261,12 @@
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
-      <c r="Y67" s="3"/>
-      <c r="Z67" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="68" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y67" s="4" t="str">
+        <f>IF(COUNTA(B67:X67)=0,"",AVERAGE(B67:X67))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="68" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A68" s="2"/>
       <c r="B68" s="3"/>
       <c r="C68" s="3"/>
@@ -10374,13 +10291,12 @@
       <c r="V68" s="3"/>
       <c r="W68" s="3"/>
       <c r="X68" s="3"/>
-      <c r="Y68" s="3"/>
-      <c r="Z68" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="69" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y68" s="4" t="str">
+        <f>IF(COUNTA(B68:X68)=0,"",AVERAGE(B68:X68))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="69" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A69" s="2"/>
       <c r="B69" s="3"/>
       <c r="C69" s="3"/>
@@ -10405,13 +10321,12 @@
       <c r="V69" s="3"/>
       <c r="W69" s="3"/>
       <c r="X69" s="3"/>
-      <c r="Y69" s="3"/>
-      <c r="Z69" s="4" t="str">
-        <f t="shared" ref="Z69:Z132" si="7">IF(COUNTA(B69:Y69)=0,"",AVERAGE(B69:Y69))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="70" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y69" s="4" t="str">
+        <f>IF(COUNTA(B69:X69)=0,"",AVERAGE(B69:X69))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="70" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A70" s="2"/>
       <c r="B70" s="3"/>
       <c r="C70" s="3"/>
@@ -10436,13 +10351,12 @@
       <c r="V70" s="3"/>
       <c r="W70" s="3"/>
       <c r="X70" s="3"/>
-      <c r="Y70" s="3"/>
-      <c r="Z70" s="4" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="71" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y70" s="4" t="str">
+        <f>IF(COUNTA(B70:X70)=0,"",AVERAGE(B70:X70))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="71" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A71" s="2"/>
       <c r="B71" s="3"/>
       <c r="C71" s="3"/>
@@ -10467,13 +10381,12 @@
       <c r="V71" s="3"/>
       <c r="W71" s="3"/>
       <c r="X71" s="3"/>
-      <c r="Y71" s="3"/>
-      <c r="Z71" s="4" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="72" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y71" s="4" t="str">
+        <f>IF(COUNTA(B71:X71)=0,"",AVERAGE(B71:X71))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="72" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A72" s="2"/>
       <c r="B72" s="3"/>
       <c r="C72" s="3"/>
@@ -10498,13 +10411,12 @@
       <c r="V72" s="3"/>
       <c r="W72" s="3"/>
       <c r="X72" s="3"/>
-      <c r="Y72" s="3"/>
-      <c r="Z72" s="4" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="73" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y72" s="4" t="str">
+        <f>IF(COUNTA(B72:X72)=0,"",AVERAGE(B72:X72))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="73" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A73" s="2"/>
       <c r="B73" s="3"/>
       <c r="C73" s="3"/>
@@ -10529,13 +10441,12 @@
       <c r="V73" s="3"/>
       <c r="W73" s="3"/>
       <c r="X73" s="3"/>
-      <c r="Y73" s="3"/>
-      <c r="Z73" s="4" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="74" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y73" s="4" t="str">
+        <f>IF(COUNTA(B73:X73)=0,"",AVERAGE(B73:X73))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="74" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A74" s="2"/>
       <c r="B74" s="3"/>
       <c r="C74" s="3"/>
@@ -10560,13 +10471,12 @@
       <c r="V74" s="3"/>
       <c r="W74" s="3"/>
       <c r="X74" s="3"/>
-      <c r="Y74" s="3"/>
-      <c r="Z74" s="4" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="75" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y74" s="4" t="str">
+        <f>IF(COUNTA(B74:X74)=0,"",AVERAGE(B74:X74))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="75" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A75" s="2"/>
       <c r="B75" s="3"/>
       <c r="C75" s="3"/>
@@ -10591,13 +10501,12 @@
       <c r="V75" s="3"/>
       <c r="W75" s="3"/>
       <c r="X75" s="3"/>
-      <c r="Y75" s="3"/>
-      <c r="Z75" s="4" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="76" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y75" s="4" t="str">
+        <f>IF(COUNTA(B75:X75)=0,"",AVERAGE(B75:X75))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="76" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A76" s="2"/>
       <c r="B76" s="3"/>
       <c r="C76" s="3"/>
@@ -10622,13 +10531,12 @@
       <c r="V76" s="3"/>
       <c r="W76" s="3"/>
       <c r="X76" s="3"/>
-      <c r="Y76" s="3"/>
-      <c r="Z76" s="4" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="77" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y76" s="4" t="str">
+        <f>IF(COUNTA(B76:X76)=0,"",AVERAGE(B76:X76))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="77" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A77" s="2"/>
       <c r="B77" s="3"/>
       <c r="C77" s="3"/>
@@ -10653,13 +10561,12 @@
       <c r="V77" s="3"/>
       <c r="W77" s="3"/>
       <c r="X77" s="3"/>
-      <c r="Y77" s="3"/>
-      <c r="Z77" s="4" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="78" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y77" s="4" t="str">
+        <f>IF(COUNTA(B77:X77)=0,"",AVERAGE(B77:X77))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="78" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A78" s="2"/>
       <c r="B78" s="3"/>
       <c r="C78" s="3"/>
@@ -10684,13 +10591,12 @@
       <c r="V78" s="3"/>
       <c r="W78" s="3"/>
       <c r="X78" s="3"/>
-      <c r="Y78" s="3"/>
-      <c r="Z78" s="4" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="79" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y78" s="4" t="str">
+        <f>IF(COUNTA(B78:X78)=0,"",AVERAGE(B78:X78))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="79" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A79" s="2"/>
       <c r="B79" s="3"/>
       <c r="C79" s="3"/>
@@ -10715,13 +10621,12 @@
       <c r="V79" s="3"/>
       <c r="W79" s="3"/>
       <c r="X79" s="3"/>
-      <c r="Y79" s="3"/>
-      <c r="Z79" s="4" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="80" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y79" s="4" t="str">
+        <f>IF(COUNTA(B79:X79)=0,"",AVERAGE(B79:X79))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="80" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A80" s="2"/>
       <c r="B80" s="3"/>
       <c r="C80" s="3"/>
@@ -10746,13 +10651,12 @@
       <c r="V80" s="3"/>
       <c r="W80" s="3"/>
       <c r="X80" s="3"/>
-      <c r="Y80" s="3"/>
-      <c r="Z80" s="4" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="81" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y80" s="4" t="str">
+        <f>IF(COUNTA(B80:X80)=0,"",AVERAGE(B80:X80))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="81" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A81" s="2"/>
       <c r="B81" s="3"/>
       <c r="C81" s="3"/>
@@ -10777,13 +10681,12 @@
       <c r="V81" s="3"/>
       <c r="W81" s="3"/>
       <c r="X81" s="3"/>
-      <c r="Y81" s="3"/>
-      <c r="Z81" s="4" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="82" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y81" s="4" t="str">
+        <f>IF(COUNTA(B81:X81)=0,"",AVERAGE(B81:X81))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="82" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A82" s="2"/>
       <c r="B82" s="3"/>
       <c r="C82" s="3"/>
@@ -10808,13 +10711,12 @@
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
-      <c r="Y82" s="3"/>
-      <c r="Z82" s="4" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="83" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y82" s="4" t="str">
+        <f>IF(COUNTA(B82:X82)=0,"",AVERAGE(B82:X82))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="83" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A83" s="2"/>
       <c r="B83" s="3"/>
       <c r="C83" s="3"/>
@@ -10839,13 +10741,12 @@
       <c r="V83" s="3"/>
       <c r="W83" s="3"/>
       <c r="X83" s="3"/>
-      <c r="Y83" s="3"/>
-      <c r="Z83" s="4" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="84" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y83" s="4" t="str">
+        <f>IF(COUNTA(B83:X83)=0,"",AVERAGE(B83:X83))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="84" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A84" s="2"/>
       <c r="B84" s="3"/>
       <c r="C84" s="3"/>
@@ -10870,13 +10771,12 @@
       <c r="V84" s="3"/>
       <c r="W84" s="3"/>
       <c r="X84" s="3"/>
-      <c r="Y84" s="3"/>
-      <c r="Z84" s="4" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="85" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y84" s="4" t="str">
+        <f>IF(COUNTA(B84:X84)=0,"",AVERAGE(B84:X84))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="85" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A85" s="2"/>
       <c r="B85" s="3"/>
       <c r="C85" s="3"/>
@@ -10901,13 +10801,12 @@
       <c r="V85" s="3"/>
       <c r="W85" s="3"/>
       <c r="X85" s="3"/>
-      <c r="Y85" s="3"/>
-      <c r="Z85" s="4" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="86" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y85" s="4" t="str">
+        <f>IF(COUNTA(B85:X85)=0,"",AVERAGE(B85:X85))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="86" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A86" s="2"/>
       <c r="B86" s="3"/>
       <c r="C86" s="3"/>
@@ -10932,13 +10831,12 @@
       <c r="V86" s="3"/>
       <c r="W86" s="3"/>
       <c r="X86" s="3"/>
-      <c r="Y86" s="3"/>
-      <c r="Z86" s="4" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="87" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y86" s="4" t="str">
+        <f>IF(COUNTA(B86:X86)=0,"",AVERAGE(B86:X86))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="87" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A87" s="2"/>
       <c r="B87" s="3"/>
       <c r="C87" s="3"/>
@@ -10963,13 +10861,12 @@
       <c r="V87" s="3"/>
       <c r="W87" s="3"/>
       <c r="X87" s="3"/>
-      <c r="Y87" s="3"/>
-      <c r="Z87" s="4" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="88" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y87" s="4" t="str">
+        <f>IF(COUNTA(B87:X87)=0,"",AVERAGE(B87:X87))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="88" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A88" s="2"/>
       <c r="B88" s="3"/>
       <c r="C88" s="3"/>
@@ -10994,13 +10891,12 @@
       <c r="V88" s="3"/>
       <c r="W88" s="3"/>
       <c r="X88" s="3"/>
-      <c r="Y88" s="3"/>
-      <c r="Z88" s="4" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="89" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y88" s="4" t="str">
+        <f>IF(COUNTA(B88:X88)=0,"",AVERAGE(B88:X88))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="89" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A89" s="2"/>
       <c r="B89" s="3"/>
       <c r="C89" s="3"/>
@@ -11025,13 +10921,12 @@
       <c r="V89" s="3"/>
       <c r="W89" s="3"/>
       <c r="X89" s="3"/>
-      <c r="Y89" s="3"/>
-      <c r="Z89" s="4" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="90" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y89" s="4" t="str">
+        <f>IF(COUNTA(B89:X89)=0,"",AVERAGE(B89:X89))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="90" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A90" s="2"/>
       <c r="B90" s="3"/>
       <c r="C90" s="3"/>
@@ -11056,13 +10951,12 @@
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
-      <c r="Y90" s="3"/>
-      <c r="Z90" s="4" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="91" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y90" s="4" t="str">
+        <f>IF(COUNTA(B90:X90)=0,"",AVERAGE(B90:X90))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="91" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A91" s="2"/>
       <c r="B91" s="3"/>
       <c r="C91" s="3"/>
@@ -11087,13 +10981,12 @@
       <c r="V91" s="3"/>
       <c r="W91" s="3"/>
       <c r="X91" s="3"/>
-      <c r="Y91" s="3"/>
-      <c r="Z91" s="4" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="92" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y91" s="4" t="str">
+        <f>IF(COUNTA(B91:X91)=0,"",AVERAGE(B91:X91))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="92" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A92" s="2"/>
       <c r="B92" s="3"/>
       <c r="C92" s="3"/>
@@ -11118,13 +11011,12 @@
       <c r="V92" s="3"/>
       <c r="W92" s="3"/>
       <c r="X92" s="3"/>
-      <c r="Y92" s="3"/>
-      <c r="Z92" s="4" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="93" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y92" s="4" t="str">
+        <f>IF(COUNTA(B92:X92)=0,"",AVERAGE(B92:X92))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="93" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A93" s="2"/>
       <c r="B93" s="3"/>
       <c r="C93" s="3"/>
@@ -11149,13 +11041,12 @@
       <c r="V93" s="3"/>
       <c r="W93" s="3"/>
       <c r="X93" s="3"/>
-      <c r="Y93" s="3"/>
-      <c r="Z93" s="4" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="94" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y93" s="4" t="str">
+        <f>IF(COUNTA(B93:X93)=0,"",AVERAGE(B93:X93))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="94" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A94" s="2"/>
       <c r="B94" s="3"/>
       <c r="C94" s="3"/>
@@ -11180,13 +11071,12 @@
       <c r="V94" s="3"/>
       <c r="W94" s="3"/>
       <c r="X94" s="3"/>
-      <c r="Y94" s="3"/>
-      <c r="Z94" s="4" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="95" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y94" s="4" t="str">
+        <f>IF(COUNTA(B94:X94)=0,"",AVERAGE(B94:X94))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="95" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A95" s="2"/>
       <c r="B95" s="3"/>
       <c r="C95" s="3"/>
@@ -11211,13 +11101,12 @@
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
-      <c r="Y95" s="3"/>
-      <c r="Z95" s="4" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="96" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y95" s="4" t="str">
+        <f>IF(COUNTA(B95:X95)=0,"",AVERAGE(B95:X95))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="96" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A96" s="2"/>
       <c r="B96" s="3"/>
       <c r="C96" s="3"/>
@@ -11242,13 +11131,12 @@
       <c r="V96" s="3"/>
       <c r="W96" s="3"/>
       <c r="X96" s="3"/>
-      <c r="Y96" s="3"/>
-      <c r="Z96" s="4" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="97" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y96" s="4" t="str">
+        <f>IF(COUNTA(B96:X96)=0,"",AVERAGE(B96:X96))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="97" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A97" s="2"/>
       <c r="B97" s="3"/>
       <c r="C97" s="3"/>
@@ -11273,13 +11161,12 @@
       <c r="V97" s="3"/>
       <c r="W97" s="3"/>
       <c r="X97" s="3"/>
-      <c r="Y97" s="3"/>
-      <c r="Z97" s="4" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="98" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y97" s="4" t="str">
+        <f>IF(COUNTA(B97:X97)=0,"",AVERAGE(B97:X97))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="98" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A98" s="2"/>
       <c r="B98" s="3"/>
       <c r="C98" s="3"/>
@@ -11304,13 +11191,12 @@
       <c r="V98" s="3"/>
       <c r="W98" s="3"/>
       <c r="X98" s="3"/>
-      <c r="Y98" s="3"/>
-      <c r="Z98" s="4" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="99" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y98" s="4" t="str">
+        <f>IF(COUNTA(B98:X98)=0,"",AVERAGE(B98:X98))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="99" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A99" s="2"/>
       <c r="B99" s="3"/>
       <c r="C99" s="3"/>
@@ -11335,13 +11221,12 @@
       <c r="V99" s="3"/>
       <c r="W99" s="3"/>
       <c r="X99" s="3"/>
-      <c r="Y99" s="3"/>
-      <c r="Z99" s="4" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="100" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y99" s="4" t="str">
+        <f>IF(COUNTA(B99:X99)=0,"",AVERAGE(B99:X99))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="100" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A100" s="2"/>
       <c r="B100" s="3"/>
       <c r="C100" s="3"/>
@@ -11366,13 +11251,12 @@
       <c r="V100" s="3"/>
       <c r="W100" s="3"/>
       <c r="X100" s="3"/>
-      <c r="Y100" s="3"/>
-      <c r="Z100" s="4" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="101" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y100" s="4" t="str">
+        <f>IF(COUNTA(B100:X100)=0,"",AVERAGE(B100:X100))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="101" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A101" s="2"/>
       <c r="B101" s="3"/>
       <c r="C101" s="3"/>
@@ -11397,13 +11281,12 @@
       <c r="V101" s="3"/>
       <c r="W101" s="3"/>
       <c r="X101" s="3"/>
-      <c r="Y101" s="3"/>
-      <c r="Z101" s="4" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="102" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y101" s="4" t="str">
+        <f>IF(COUNTA(B101:X101)=0,"",AVERAGE(B101:X101))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="102" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A102" s="2"/>
       <c r="B102" s="3"/>
       <c r="C102" s="3"/>
@@ -11428,13 +11311,12 @@
       <c r="V102" s="3"/>
       <c r="W102" s="3"/>
       <c r="X102" s="3"/>
-      <c r="Y102" s="3"/>
-      <c r="Z102" s="4" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="103" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y102" s="4" t="str">
+        <f>IF(COUNTA(B102:X102)=0,"",AVERAGE(B102:X102))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="103" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A103" s="2"/>
       <c r="B103" s="3"/>
       <c r="C103" s="3"/>
@@ -11459,13 +11341,12 @@
       <c r="V103" s="3"/>
       <c r="W103" s="3"/>
       <c r="X103" s="3"/>
-      <c r="Y103" s="3"/>
-      <c r="Z103" s="4" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="104" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y103" s="4" t="str">
+        <f>IF(COUNTA(B103:X103)=0,"",AVERAGE(B103:X103))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="104" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A104" s="2"/>
       <c r="B104" s="3"/>
       <c r="C104" s="3"/>
@@ -11490,13 +11371,12 @@
       <c r="V104" s="3"/>
       <c r="W104" s="3"/>
       <c r="X104" s="3"/>
-      <c r="Y104" s="3"/>
-      <c r="Z104" s="4" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="105" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y104" s="4" t="str">
+        <f>IF(COUNTA(B104:X104)=0,"",AVERAGE(B104:X104))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="105" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A105" s="2"/>
       <c r="B105" s="3"/>
       <c r="C105" s="3"/>
@@ -11521,13 +11401,12 @@
       <c r="V105" s="3"/>
       <c r="W105" s="3"/>
       <c r="X105" s="3"/>
-      <c r="Y105" s="3"/>
-      <c r="Z105" s="4" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="106" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y105" s="4" t="str">
+        <f>IF(COUNTA(B105:X105)=0,"",AVERAGE(B105:X105))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="106" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A106" s="2"/>
       <c r="B106" s="3"/>
       <c r="C106" s="3"/>
@@ -11552,13 +11431,12 @@
       <c r="V106" s="3"/>
       <c r="W106" s="3"/>
       <c r="X106" s="3"/>
-      <c r="Y106" s="3"/>
-      <c r="Z106" s="4" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="107" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y106" s="4" t="str">
+        <f>IF(COUNTA(B106:X106)=0,"",AVERAGE(B106:X106))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="107" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A107" s="2"/>
       <c r="B107" s="3"/>
       <c r="C107" s="3"/>
@@ -11583,13 +11461,12 @@
       <c r="V107" s="3"/>
       <c r="W107" s="3"/>
       <c r="X107" s="3"/>
-      <c r="Y107" s="3"/>
-      <c r="Z107" s="4" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="108" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y107" s="4" t="str">
+        <f>IF(COUNTA(B107:X107)=0,"",AVERAGE(B107:X107))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="108" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A108" s="2"/>
       <c r="B108" s="3"/>
       <c r="C108" s="3"/>
@@ -11614,13 +11491,12 @@
       <c r="V108" s="3"/>
       <c r="W108" s="3"/>
       <c r="X108" s="3"/>
-      <c r="Y108" s="3"/>
-      <c r="Z108" s="4" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="109" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y108" s="4" t="str">
+        <f>IF(COUNTA(B108:X108)=0,"",AVERAGE(B108:X108))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="109" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A109" s="2"/>
       <c r="B109" s="3"/>
       <c r="C109" s="3"/>
@@ -11645,13 +11521,12 @@
       <c r="V109" s="3"/>
       <c r="W109" s="3"/>
       <c r="X109" s="3"/>
-      <c r="Y109" s="3"/>
-      <c r="Z109" s="4" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="110" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y109" s="4" t="str">
+        <f>IF(COUNTA(B109:X109)=0,"",AVERAGE(B109:X109))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="110" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A110" s="2"/>
       <c r="B110" s="3"/>
       <c r="C110" s="3"/>
@@ -11676,13 +11551,12 @@
       <c r="V110" s="3"/>
       <c r="W110" s="3"/>
       <c r="X110" s="3"/>
-      <c r="Y110" s="3"/>
-      <c r="Z110" s="4" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="111" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y110" s="4" t="str">
+        <f>IF(COUNTA(B110:X110)=0,"",AVERAGE(B110:X110))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="111" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A111" s="2"/>
       <c r="B111" s="3"/>
       <c r="C111" s="3"/>
@@ -11707,13 +11581,12 @@
       <c r="V111" s="3"/>
       <c r="W111" s="3"/>
       <c r="X111" s="3"/>
-      <c r="Y111" s="3"/>
-      <c r="Z111" s="4" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="112" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y111" s="4" t="str">
+        <f>IF(COUNTA(B111:X111)=0,"",AVERAGE(B111:X111))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="112" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A112" s="2"/>
       <c r="B112" s="3"/>
       <c r="C112" s="3"/>
@@ -11738,13 +11611,12 @@
       <c r="V112" s="3"/>
       <c r="W112" s="3"/>
       <c r="X112" s="3"/>
-      <c r="Y112" s="3"/>
-      <c r="Z112" s="4" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="113" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y112" s="4" t="str">
+        <f>IF(COUNTA(B112:X112)=0,"",AVERAGE(B112:X112))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="113" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A113" s="2"/>
       <c r="B113" s="3"/>
       <c r="C113" s="3"/>
@@ -11769,13 +11641,12 @@
       <c r="V113" s="3"/>
       <c r="W113" s="3"/>
       <c r="X113" s="3"/>
-      <c r="Y113" s="3"/>
-      <c r="Z113" s="4" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="114" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y113" s="4" t="str">
+        <f>IF(COUNTA(B113:X113)=0,"",AVERAGE(B113:X113))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="114" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A114" s="2"/>
       <c r="B114" s="3"/>
       <c r="C114" s="3"/>
@@ -11800,13 +11671,12 @@
       <c r="V114" s="3"/>
       <c r="W114" s="3"/>
       <c r="X114" s="3"/>
-      <c r="Y114" s="3"/>
-      <c r="Z114" s="4" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="115" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y114" s="4" t="str">
+        <f>IF(COUNTA(B114:X114)=0,"",AVERAGE(B114:X114))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="115" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A115" s="2"/>
       <c r="B115" s="3"/>
       <c r="C115" s="3"/>
@@ -11831,13 +11701,12 @@
       <c r="V115" s="3"/>
       <c r="W115" s="3"/>
       <c r="X115" s="3"/>
-      <c r="Y115" s="3"/>
-      <c r="Z115" s="4" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="116" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y115" s="4" t="str">
+        <f>IF(COUNTA(B115:X115)=0,"",AVERAGE(B115:X115))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="116" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A116" s="2"/>
       <c r="B116" s="3"/>
       <c r="C116" s="3"/>
@@ -11862,13 +11731,12 @@
       <c r="V116" s="3"/>
       <c r="W116" s="3"/>
       <c r="X116" s="3"/>
-      <c r="Y116" s="3"/>
-      <c r="Z116" s="4" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="117" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y116" s="4" t="str">
+        <f>IF(COUNTA(B116:X116)=0,"",AVERAGE(B116:X116))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="117" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A117" s="2"/>
       <c r="B117" s="3"/>
       <c r="C117" s="3"/>
@@ -11893,13 +11761,12 @@
       <c r="V117" s="3"/>
       <c r="W117" s="3"/>
       <c r="X117" s="3"/>
-      <c r="Y117" s="3"/>
-      <c r="Z117" s="4" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="118" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y117" s="4" t="str">
+        <f>IF(COUNTA(B117:X117)=0,"",AVERAGE(B117:X117))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="118" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A118" s="2"/>
       <c r="B118" s="3"/>
       <c r="C118" s="3"/>
@@ -11924,13 +11791,12 @@
       <c r="V118" s="3"/>
       <c r="W118" s="3"/>
       <c r="X118" s="3"/>
-      <c r="Y118" s="3"/>
-      <c r="Z118" s="4" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="119" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y118" s="4" t="str">
+        <f>IF(COUNTA(B118:X118)=0,"",AVERAGE(B118:X118))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="119" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A119" s="2"/>
       <c r="B119" s="3"/>
       <c r="C119" s="3"/>
@@ -11955,13 +11821,12 @@
       <c r="V119" s="3"/>
       <c r="W119" s="3"/>
       <c r="X119" s="3"/>
-      <c r="Y119" s="3"/>
-      <c r="Z119" s="4" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="120" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y119" s="4" t="str">
+        <f>IF(COUNTA(B119:X119)=0,"",AVERAGE(B119:X119))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="120" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A120" s="2"/>
       <c r="B120" s="3"/>
       <c r="C120" s="3"/>
@@ -11986,13 +11851,12 @@
       <c r="V120" s="3"/>
       <c r="W120" s="3"/>
       <c r="X120" s="3"/>
-      <c r="Y120" s="3"/>
-      <c r="Z120" s="4" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="121" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y120" s="4" t="str">
+        <f>IF(COUNTA(B120:X120)=0,"",AVERAGE(B120:X120))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="121" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A121" s="2"/>
       <c r="B121" s="3"/>
       <c r="C121" s="3"/>
@@ -12017,13 +11881,12 @@
       <c r="V121" s="3"/>
       <c r="W121" s="3"/>
       <c r="X121" s="3"/>
-      <c r="Y121" s="3"/>
-      <c r="Z121" s="4" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="122" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y121" s="4" t="str">
+        <f>IF(COUNTA(B121:X121)=0,"",AVERAGE(B121:X121))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="122" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A122" s="2"/>
       <c r="B122" s="3"/>
       <c r="C122" s="3"/>
@@ -12048,13 +11911,12 @@
       <c r="V122" s="3"/>
       <c r="W122" s="3"/>
       <c r="X122" s="3"/>
-      <c r="Y122" s="3"/>
-      <c r="Z122" s="4" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="123" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y122" s="4" t="str">
+        <f>IF(COUNTA(B122:X122)=0,"",AVERAGE(B122:X122))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="123" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A123" s="2"/>
       <c r="B123" s="3"/>
       <c r="C123" s="3"/>
@@ -12079,13 +11941,12 @@
       <c r="V123" s="3"/>
       <c r="W123" s="3"/>
       <c r="X123" s="3"/>
-      <c r="Y123" s="3"/>
-      <c r="Z123" s="4" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="124" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y123" s="4" t="str">
+        <f>IF(COUNTA(B123:X123)=0,"",AVERAGE(B123:X123))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="124" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A124" s="2"/>
       <c r="B124" s="3"/>
       <c r="C124" s="3"/>
@@ -12110,13 +11971,12 @@
       <c r="V124" s="3"/>
       <c r="W124" s="3"/>
       <c r="X124" s="3"/>
-      <c r="Y124" s="3"/>
-      <c r="Z124" s="4" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="125" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y124" s="4" t="str">
+        <f>IF(COUNTA(B124:X124)=0,"",AVERAGE(B124:X124))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="125" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A125" s="2"/>
       <c r="B125" s="3"/>
       <c r="C125" s="3"/>
@@ -12141,13 +12001,12 @@
       <c r="V125" s="3"/>
       <c r="W125" s="3"/>
       <c r="X125" s="3"/>
-      <c r="Y125" s="3"/>
-      <c r="Z125" s="4" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="126" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y125" s="4" t="str">
+        <f>IF(COUNTA(B125:X125)=0,"",AVERAGE(B125:X125))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="126" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A126" s="2"/>
       <c r="B126" s="3"/>
       <c r="C126" s="3"/>
@@ -12172,13 +12031,12 @@
       <c r="V126" s="3"/>
       <c r="W126" s="3"/>
       <c r="X126" s="3"/>
-      <c r="Y126" s="3"/>
-      <c r="Z126" s="4" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="127" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y126" s="4" t="str">
+        <f>IF(COUNTA(B126:X126)=0,"",AVERAGE(B126:X126))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="127" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A127" s="2"/>
       <c r="B127" s="3"/>
       <c r="C127" s="3"/>
@@ -12203,13 +12061,12 @@
       <c r="V127" s="3"/>
       <c r="W127" s="3"/>
       <c r="X127" s="3"/>
-      <c r="Y127" s="3"/>
-      <c r="Z127" s="4" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="128" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y127" s="4" t="str">
+        <f>IF(COUNTA(B127:X127)=0,"",AVERAGE(B127:X127))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="128" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A128" s="2"/>
       <c r="B128" s="3"/>
       <c r="C128" s="3"/>
@@ -12234,13 +12091,12 @@
       <c r="V128" s="3"/>
       <c r="W128" s="3"/>
       <c r="X128" s="3"/>
-      <c r="Y128" s="3"/>
-      <c r="Z128" s="4" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="129" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y128" s="4" t="str">
+        <f>IF(COUNTA(B128:X128)=0,"",AVERAGE(B128:X128))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="129" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A129" s="2"/>
       <c r="B129" s="3"/>
       <c r="C129" s="3"/>
@@ -12265,13 +12121,12 @@
       <c r="V129" s="3"/>
       <c r="W129" s="3"/>
       <c r="X129" s="3"/>
-      <c r="Y129" s="3"/>
-      <c r="Z129" s="4" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="130" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y129" s="4" t="str">
+        <f>IF(COUNTA(B129:X129)=0,"",AVERAGE(B129:X129))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="130" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A130" s="2"/>
       <c r="B130" s="3"/>
       <c r="C130" s="3"/>
@@ -12296,13 +12151,12 @@
       <c r="V130" s="3"/>
       <c r="W130" s="3"/>
       <c r="X130" s="3"/>
-      <c r="Y130" s="3"/>
-      <c r="Z130" s="4" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="131" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y130" s="4" t="str">
+        <f>IF(COUNTA(B130:X130)=0,"",AVERAGE(B130:X130))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="131" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A131" s="2"/>
       <c r="B131" s="3"/>
       <c r="C131" s="3"/>
@@ -12327,13 +12181,12 @@
       <c r="V131" s="3"/>
       <c r="W131" s="3"/>
       <c r="X131" s="3"/>
-      <c r="Y131" s="3"/>
-      <c r="Z131" s="4" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="132" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y131" s="4" t="str">
+        <f>IF(COUNTA(B131:X131)=0,"",AVERAGE(B131:X131))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="132" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A132" s="2"/>
       <c r="B132" s="3"/>
       <c r="C132" s="3"/>
@@ -12358,13 +12211,12 @@
       <c r="V132" s="3"/>
       <c r="W132" s="3"/>
       <c r="X132" s="3"/>
-      <c r="Y132" s="3"/>
-      <c r="Z132" s="4" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="133" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y132" s="4" t="str">
+        <f>IF(COUNTA(B132:X132)=0,"",AVERAGE(B132:X132))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="133" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A133" s="2"/>
       <c r="B133" s="3"/>
       <c r="C133" s="3"/>
@@ -12389,13 +12241,12 @@
       <c r="V133" s="3"/>
       <c r="W133" s="3"/>
       <c r="X133" s="3"/>
-      <c r="Y133" s="3"/>
-      <c r="Z133" s="4" t="str">
-        <f t="shared" ref="Z133:Z196" si="8">IF(COUNTA(B133:Y133)=0,"",AVERAGE(B133:Y133))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="134" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y133" s="4" t="str">
+        <f>IF(COUNTA(B133:X133)=0,"",AVERAGE(B133:X133))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="134" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A134" s="2"/>
       <c r="B134" s="3"/>
       <c r="C134" s="3"/>
@@ -12420,13 +12271,12 @@
       <c r="V134" s="3"/>
       <c r="W134" s="3"/>
       <c r="X134" s="3"/>
-      <c r="Y134" s="3"/>
-      <c r="Z134" s="4" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-    </row>
-    <row r="135" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y134" s="4" t="str">
+        <f>IF(COUNTA(B134:X134)=0,"",AVERAGE(B134:X134))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="135" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A135" s="2"/>
       <c r="B135" s="3"/>
       <c r="C135" s="3"/>
@@ -12451,13 +12301,12 @@
       <c r="V135" s="3"/>
       <c r="W135" s="3"/>
       <c r="X135" s="3"/>
-      <c r="Y135" s="3"/>
-      <c r="Z135" s="4" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-    </row>
-    <row r="136" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y135" s="4" t="str">
+        <f>IF(COUNTA(B135:X135)=0,"",AVERAGE(B135:X135))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="136" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A136" s="2"/>
       <c r="B136" s="3"/>
       <c r="C136" s="3"/>
@@ -12482,13 +12331,12 @@
       <c r="V136" s="3"/>
       <c r="W136" s="3"/>
       <c r="X136" s="3"/>
-      <c r="Y136" s="3"/>
-      <c r="Z136" s="4" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-    </row>
-    <row r="137" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y136" s="4" t="str">
+        <f>IF(COUNTA(B136:X136)=0,"",AVERAGE(B136:X136))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="137" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A137" s="2"/>
       <c r="B137" s="3"/>
       <c r="C137" s="3"/>
@@ -12513,13 +12361,12 @@
       <c r="V137" s="3"/>
       <c r="W137" s="3"/>
       <c r="X137" s="3"/>
-      <c r="Y137" s="3"/>
-      <c r="Z137" s="4" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-    </row>
-    <row r="138" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y137" s="4" t="str">
+        <f>IF(COUNTA(B137:X137)=0,"",AVERAGE(B137:X137))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="138" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A138" s="2"/>
       <c r="B138" s="3"/>
       <c r="C138" s="3"/>
@@ -12544,13 +12391,12 @@
       <c r="V138" s="3"/>
       <c r="W138" s="3"/>
       <c r="X138" s="3"/>
-      <c r="Y138" s="3"/>
-      <c r="Z138" s="4" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-    </row>
-    <row r="139" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y138" s="4" t="str">
+        <f>IF(COUNTA(B138:X138)=0,"",AVERAGE(B138:X138))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="139" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A139" s="2"/>
       <c r="B139" s="3"/>
       <c r="C139" s="3"/>
@@ -12575,13 +12421,12 @@
       <c r="V139" s="3"/>
       <c r="W139" s="3"/>
       <c r="X139" s="3"/>
-      <c r="Y139" s="3"/>
-      <c r="Z139" s="4" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-    </row>
-    <row r="140" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y139" s="4" t="str">
+        <f>IF(COUNTA(B139:X139)=0,"",AVERAGE(B139:X139))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="140" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A140" s="2"/>
       <c r="B140" s="3"/>
       <c r="C140" s="3"/>
@@ -12606,13 +12451,12 @@
       <c r="V140" s="3"/>
       <c r="W140" s="3"/>
       <c r="X140" s="3"/>
-      <c r="Y140" s="3"/>
-      <c r="Z140" s="4" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-    </row>
-    <row r="141" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y140" s="4" t="str">
+        <f>IF(COUNTA(B140:X140)=0,"",AVERAGE(B140:X140))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="141" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A141" s="2"/>
       <c r="B141" s="3"/>
       <c r="C141" s="3"/>
@@ -12637,13 +12481,12 @@
       <c r="V141" s="3"/>
       <c r="W141" s="3"/>
       <c r="X141" s="3"/>
-      <c r="Y141" s="3"/>
-      <c r="Z141" s="4" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-    </row>
-    <row r="142" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y141" s="4" t="str">
+        <f>IF(COUNTA(B141:X141)=0,"",AVERAGE(B141:X141))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="142" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A142" s="2"/>
       <c r="B142" s="3"/>
       <c r="C142" s="3"/>
@@ -12668,13 +12511,12 @@
       <c r="V142" s="3"/>
       <c r="W142" s="3"/>
       <c r="X142" s="3"/>
-      <c r="Y142" s="3"/>
-      <c r="Z142" s="4" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-    </row>
-    <row r="143" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y142" s="4" t="str">
+        <f>IF(COUNTA(B142:X142)=0,"",AVERAGE(B142:X142))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="143" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A143" s="2"/>
       <c r="B143" s="3"/>
       <c r="C143" s="3"/>
@@ -12699,13 +12541,12 @@
       <c r="V143" s="3"/>
       <c r="W143" s="3"/>
       <c r="X143" s="3"/>
-      <c r="Y143" s="3"/>
-      <c r="Z143" s="4" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-    </row>
-    <row r="144" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y143" s="4" t="str">
+        <f>IF(COUNTA(B143:X143)=0,"",AVERAGE(B143:X143))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="144" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A144" s="2"/>
       <c r="B144" s="3"/>
       <c r="C144" s="3"/>
@@ -12730,13 +12571,12 @@
       <c r="V144" s="3"/>
       <c r="W144" s="3"/>
       <c r="X144" s="3"/>
-      <c r="Y144" s="3"/>
-      <c r="Z144" s="4" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-    </row>
-    <row r="145" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y144" s="4" t="str">
+        <f>IF(COUNTA(B144:X144)=0,"",AVERAGE(B144:X144))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="145" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A145" s="2"/>
       <c r="B145" s="3"/>
       <c r="C145" s="3"/>
@@ -12761,13 +12601,12 @@
       <c r="V145" s="3"/>
       <c r="W145" s="3"/>
       <c r="X145" s="3"/>
-      <c r="Y145" s="3"/>
-      <c r="Z145" s="4" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-    </row>
-    <row r="146" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y145" s="4" t="str">
+        <f>IF(COUNTA(B145:X145)=0,"",AVERAGE(B145:X145))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="146" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A146" s="2"/>
       <c r="B146" s="3"/>
       <c r="C146" s="3"/>
@@ -12792,13 +12631,12 @@
       <c r="V146" s="3"/>
       <c r="W146" s="3"/>
       <c r="X146" s="3"/>
-      <c r="Y146" s="3"/>
-      <c r="Z146" s="4" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-    </row>
-    <row r="147" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y146" s="4" t="str">
+        <f>IF(COUNTA(B146:X146)=0,"",AVERAGE(B146:X146))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="147" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A147" s="2"/>
       <c r="B147" s="3"/>
       <c r="C147" s="3"/>
@@ -12823,13 +12661,12 @@
       <c r="V147" s="3"/>
       <c r="W147" s="3"/>
       <c r="X147" s="3"/>
-      <c r="Y147" s="3"/>
-      <c r="Z147" s="4" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-    </row>
-    <row r="148" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y147" s="4" t="str">
+        <f>IF(COUNTA(B147:X147)=0,"",AVERAGE(B147:X147))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="148" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A148" s="2"/>
       <c r="B148" s="3"/>
       <c r="C148" s="3"/>
@@ -12854,13 +12691,12 @@
       <c r="V148" s="3"/>
       <c r="W148" s="3"/>
       <c r="X148" s="3"/>
-      <c r="Y148" s="3"/>
-      <c r="Z148" s="4" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-    </row>
-    <row r="149" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y148" s="4" t="str">
+        <f>IF(COUNTA(B148:X148)=0,"",AVERAGE(B148:X148))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="149" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A149" s="2"/>
       <c r="B149" s="3"/>
       <c r="C149" s="3"/>
@@ -12885,13 +12721,12 @@
       <c r="V149" s="3"/>
       <c r="W149" s="3"/>
       <c r="X149" s="3"/>
-      <c r="Y149" s="3"/>
-      <c r="Z149" s="4" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-    </row>
-    <row r="150" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y149" s="4" t="str">
+        <f>IF(COUNTA(B149:X149)=0,"",AVERAGE(B149:X149))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="150" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A150" s="2"/>
       <c r="B150" s="3"/>
       <c r="C150" s="3"/>
@@ -12916,13 +12751,12 @@
       <c r="V150" s="3"/>
       <c r="W150" s="3"/>
       <c r="X150" s="3"/>
-      <c r="Y150" s="3"/>
-      <c r="Z150" s="4" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-    </row>
-    <row r="151" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y150" s="4" t="str">
+        <f>IF(COUNTA(B150:X150)=0,"",AVERAGE(B150:X150))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="151" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A151" s="2"/>
       <c r="B151" s="3"/>
       <c r="C151" s="3"/>
@@ -12947,13 +12781,12 @@
       <c r="V151" s="3"/>
       <c r="W151" s="3"/>
       <c r="X151" s="3"/>
-      <c r="Y151" s="3"/>
-      <c r="Z151" s="4" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-    </row>
-    <row r="152" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y151" s="4" t="str">
+        <f>IF(COUNTA(B151:X151)=0,"",AVERAGE(B151:X151))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="152" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A152" s="2"/>
       <c r="B152" s="3"/>
       <c r="C152" s="3"/>
@@ -12978,13 +12811,12 @@
       <c r="V152" s="3"/>
       <c r="W152" s="3"/>
       <c r="X152" s="3"/>
-      <c r="Y152" s="3"/>
-      <c r="Z152" s="4" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-    </row>
-    <row r="153" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y152" s="4" t="str">
+        <f>IF(COUNTA(B152:X152)=0,"",AVERAGE(B152:X152))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="153" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A153" s="2"/>
       <c r="B153" s="3"/>
       <c r="C153" s="3"/>
@@ -13009,13 +12841,12 @@
       <c r="V153" s="3"/>
       <c r="W153" s="3"/>
       <c r="X153" s="3"/>
-      <c r="Y153" s="3"/>
-      <c r="Z153" s="4" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-    </row>
-    <row r="154" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y153" s="4" t="str">
+        <f>IF(COUNTA(B153:X153)=0,"",AVERAGE(B153:X153))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="154" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A154" s="2"/>
       <c r="B154" s="3"/>
       <c r="C154" s="3"/>
@@ -13040,13 +12871,12 @@
       <c r="V154" s="3"/>
       <c r="W154" s="3"/>
       <c r="X154" s="3"/>
-      <c r="Y154" s="3"/>
-      <c r="Z154" s="4" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-    </row>
-    <row r="155" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y154" s="4" t="str">
+        <f>IF(COUNTA(B154:X154)=0,"",AVERAGE(B154:X154))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="155" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A155" s="2"/>
       <c r="B155" s="3"/>
       <c r="C155" s="3"/>
@@ -13071,13 +12901,12 @@
       <c r="V155" s="3"/>
       <c r="W155" s="3"/>
       <c r="X155" s="3"/>
-      <c r="Y155" s="3"/>
-      <c r="Z155" s="4" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-    </row>
-    <row r="156" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y155" s="4" t="str">
+        <f>IF(COUNTA(B155:X155)=0,"",AVERAGE(B155:X155))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="156" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A156" s="2"/>
       <c r="B156" s="3"/>
       <c r="C156" s="3"/>
@@ -13102,13 +12931,12 @@
       <c r="V156" s="3"/>
       <c r="W156" s="3"/>
       <c r="X156" s="3"/>
-      <c r="Y156" s="3"/>
-      <c r="Z156" s="4" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-    </row>
-    <row r="157" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y156" s="4" t="str">
+        <f>IF(COUNTA(B156:X156)=0,"",AVERAGE(B156:X156))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="157" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A157" s="2"/>
       <c r="B157" s="3"/>
       <c r="C157" s="3"/>
@@ -13133,13 +12961,12 @@
       <c r="V157" s="3"/>
       <c r="W157" s="3"/>
       <c r="X157" s="3"/>
-      <c r="Y157" s="3"/>
-      <c r="Z157" s="4" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-    </row>
-    <row r="158" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y157" s="4" t="str">
+        <f>IF(COUNTA(B157:X157)=0,"",AVERAGE(B157:X157))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="158" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A158" s="2"/>
       <c r="B158" s="3"/>
       <c r="C158" s="3"/>
@@ -13164,13 +12991,12 @@
       <c r="V158" s="3"/>
       <c r="W158" s="3"/>
       <c r="X158" s="3"/>
-      <c r="Y158" s="3"/>
-      <c r="Z158" s="4" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-    </row>
-    <row r="159" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y158" s="4" t="str">
+        <f>IF(COUNTA(B158:X158)=0,"",AVERAGE(B158:X158))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="159" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A159" s="2"/>
       <c r="B159" s="3"/>
       <c r="C159" s="3"/>
@@ -13195,13 +13021,12 @@
       <c r="V159" s="3"/>
       <c r="W159" s="3"/>
       <c r="X159" s="3"/>
-      <c r="Y159" s="3"/>
-      <c r="Z159" s="4" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-    </row>
-    <row r="160" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y159" s="4" t="str">
+        <f>IF(COUNTA(B159:X159)=0,"",AVERAGE(B159:X159))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="160" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A160" s="2"/>
       <c r="B160" s="3"/>
       <c r="C160" s="3"/>
@@ -13226,13 +13051,12 @@
       <c r="V160" s="3"/>
       <c r="W160" s="3"/>
       <c r="X160" s="3"/>
-      <c r="Y160" s="3"/>
-      <c r="Z160" s="4" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-    </row>
-    <row r="161" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y160" s="4" t="str">
+        <f>IF(COUNTA(B160:X160)=0,"",AVERAGE(B160:X160))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="161" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A161" s="2"/>
       <c r="B161" s="3"/>
       <c r="C161" s="3"/>
@@ -13257,13 +13081,12 @@
       <c r="V161" s="3"/>
       <c r="W161" s="3"/>
       <c r="X161" s="3"/>
-      <c r="Y161" s="3"/>
-      <c r="Z161" s="4" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-    </row>
-    <row r="162" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y161" s="4" t="str">
+        <f>IF(COUNTA(B161:X161)=0,"",AVERAGE(B161:X161))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="162" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A162" s="2"/>
       <c r="B162" s="3"/>
       <c r="C162" s="3"/>
@@ -13288,13 +13111,12 @@
       <c r="V162" s="3"/>
       <c r="W162" s="3"/>
       <c r="X162" s="3"/>
-      <c r="Y162" s="3"/>
-      <c r="Z162" s="4" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-    </row>
-    <row r="163" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y162" s="4" t="str">
+        <f>IF(COUNTA(B162:X162)=0,"",AVERAGE(B162:X162))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="163" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A163" s="2"/>
       <c r="B163" s="3"/>
       <c r="C163" s="3"/>
@@ -13319,13 +13141,12 @@
       <c r="V163" s="3"/>
       <c r="W163" s="3"/>
       <c r="X163" s="3"/>
-      <c r="Y163" s="3"/>
-      <c r="Z163" s="4" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-    </row>
-    <row r="164" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y163" s="4" t="str">
+        <f>IF(COUNTA(B163:X163)=0,"",AVERAGE(B163:X163))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="164" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A164" s="2"/>
       <c r="B164" s="3"/>
       <c r="C164" s="3"/>
@@ -13350,13 +13171,12 @@
       <c r="V164" s="3"/>
       <c r="W164" s="3"/>
       <c r="X164" s="3"/>
-      <c r="Y164" s="3"/>
-      <c r="Z164" s="4" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-    </row>
-    <row r="165" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y164" s="4" t="str">
+        <f>IF(COUNTA(B164:X164)=0,"",AVERAGE(B164:X164))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="165" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A165" s="2"/>
       <c r="B165" s="3"/>
       <c r="C165" s="3"/>
@@ -13381,13 +13201,12 @@
       <c r="V165" s="3"/>
       <c r="W165" s="3"/>
       <c r="X165" s="3"/>
-      <c r="Y165" s="3"/>
-      <c r="Z165" s="4" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-    </row>
-    <row r="166" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y165" s="4" t="str">
+        <f>IF(COUNTA(B165:X165)=0,"",AVERAGE(B165:X165))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="166" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A166" s="2"/>
       <c r="B166" s="3"/>
       <c r="C166" s="3"/>
@@ -13412,13 +13231,12 @@
       <c r="V166" s="3"/>
       <c r="W166" s="3"/>
       <c r="X166" s="3"/>
-      <c r="Y166" s="3"/>
-      <c r="Z166" s="4" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-    </row>
-    <row r="167" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y166" s="4" t="str">
+        <f>IF(COUNTA(B166:X166)=0,"",AVERAGE(B166:X166))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="167" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A167" s="2"/>
       <c r="B167" s="3"/>
       <c r="C167" s="3"/>
@@ -13443,13 +13261,12 @@
       <c r="V167" s="3"/>
       <c r="W167" s="3"/>
       <c r="X167" s="3"/>
-      <c r="Y167" s="3"/>
-      <c r="Z167" s="4" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-    </row>
-    <row r="168" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y167" s="4" t="str">
+        <f>IF(COUNTA(B167:X167)=0,"",AVERAGE(B167:X167))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="168" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A168" s="2"/>
       <c r="B168" s="3"/>
       <c r="C168" s="3"/>
@@ -13474,13 +13291,12 @@
       <c r="V168" s="3"/>
       <c r="W168" s="3"/>
       <c r="X168" s="3"/>
-      <c r="Y168" s="3"/>
-      <c r="Z168" s="4" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-    </row>
-    <row r="169" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y168" s="4" t="str">
+        <f>IF(COUNTA(B168:X168)=0,"",AVERAGE(B168:X168))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="169" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A169" s="2"/>
       <c r="B169" s="3"/>
       <c r="C169" s="3"/>
@@ -13505,13 +13321,12 @@
       <c r="V169" s="3"/>
       <c r="W169" s="3"/>
       <c r="X169" s="3"/>
-      <c r="Y169" s="3"/>
-      <c r="Z169" s="4" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-    </row>
-    <row r="170" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y169" s="4" t="str">
+        <f>IF(COUNTA(B169:X169)=0,"",AVERAGE(B169:X169))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="170" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A170" s="2"/>
       <c r="B170" s="3"/>
       <c r="C170" s="3"/>
@@ -13536,13 +13351,12 @@
       <c r="V170" s="3"/>
       <c r="W170" s="3"/>
       <c r="X170" s="3"/>
-      <c r="Y170" s="3"/>
-      <c r="Z170" s="4" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-    </row>
-    <row r="171" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y170" s="4" t="str">
+        <f>IF(COUNTA(B170:X170)=0,"",AVERAGE(B170:X170))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="171" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A171" s="2"/>
       <c r="B171" s="3"/>
       <c r="C171" s="3"/>
@@ -13567,13 +13381,12 @@
       <c r="V171" s="3"/>
       <c r="W171" s="3"/>
       <c r="X171" s="3"/>
-      <c r="Y171" s="3"/>
-      <c r="Z171" s="4" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-    </row>
-    <row r="172" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y171" s="4" t="str">
+        <f>IF(COUNTA(B171:X171)=0,"",AVERAGE(B171:X171))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="172" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A172" s="2"/>
       <c r="B172" s="3"/>
       <c r="C172" s="3"/>
@@ -13598,13 +13411,12 @@
       <c r="V172" s="3"/>
       <c r="W172" s="3"/>
       <c r="X172" s="3"/>
-      <c r="Y172" s="3"/>
-      <c r="Z172" s="4" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-    </row>
-    <row r="173" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y172" s="4" t="str">
+        <f>IF(COUNTA(B172:X172)=0,"",AVERAGE(B172:X172))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="173" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A173" s="2"/>
       <c r="B173" s="3"/>
       <c r="C173" s="3"/>
@@ -13629,13 +13441,12 @@
       <c r="V173" s="3"/>
       <c r="W173" s="3"/>
       <c r="X173" s="3"/>
-      <c r="Y173" s="3"/>
-      <c r="Z173" s="4" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-    </row>
-    <row r="174" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y173" s="4" t="str">
+        <f>IF(COUNTA(B173:X173)=0,"",AVERAGE(B173:X173))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="174" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A174" s="2"/>
       <c r="B174" s="3"/>
       <c r="C174" s="3"/>
@@ -13660,13 +13471,12 @@
       <c r="V174" s="3"/>
       <c r="W174" s="3"/>
       <c r="X174" s="3"/>
-      <c r="Y174" s="3"/>
-      <c r="Z174" s="4" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-    </row>
-    <row r="175" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y174" s="4" t="str">
+        <f>IF(COUNTA(B174:X174)=0,"",AVERAGE(B174:X174))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="175" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A175" s="2"/>
       <c r="B175" s="3"/>
       <c r="C175" s="3"/>
@@ -13691,13 +13501,12 @@
       <c r="V175" s="3"/>
       <c r="W175" s="3"/>
       <c r="X175" s="3"/>
-      <c r="Y175" s="3"/>
-      <c r="Z175" s="4" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-    </row>
-    <row r="176" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y175" s="4" t="str">
+        <f>IF(COUNTA(B175:X175)=0,"",AVERAGE(B175:X175))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="176" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A176" s="2"/>
       <c r="B176" s="3"/>
       <c r="C176" s="3"/>
@@ -13722,13 +13531,12 @@
       <c r="V176" s="3"/>
       <c r="W176" s="3"/>
       <c r="X176" s="3"/>
-      <c r="Y176" s="3"/>
-      <c r="Z176" s="4" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-    </row>
-    <row r="177" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y176" s="4" t="str">
+        <f>IF(COUNTA(B176:X176)=0,"",AVERAGE(B176:X176))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="177" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A177" s="2"/>
       <c r="B177" s="3"/>
       <c r="C177" s="3"/>
@@ -13753,13 +13561,12 @@
       <c r="V177" s="3"/>
       <c r="W177" s="3"/>
       <c r="X177" s="3"/>
-      <c r="Y177" s="3"/>
-      <c r="Z177" s="4" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-    </row>
-    <row r="178" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y177" s="4" t="str">
+        <f>IF(COUNTA(B177:X177)=0,"",AVERAGE(B177:X177))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="178" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A178" s="2"/>
       <c r="B178" s="3"/>
       <c r="C178" s="3"/>
@@ -13784,13 +13591,12 @@
       <c r="V178" s="3"/>
       <c r="W178" s="3"/>
       <c r="X178" s="3"/>
-      <c r="Y178" s="3"/>
-      <c r="Z178" s="4" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-    </row>
-    <row r="179" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y178" s="4" t="str">
+        <f>IF(COUNTA(B178:X178)=0,"",AVERAGE(B178:X178))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="179" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A179" s="2"/>
       <c r="B179" s="3"/>
       <c r="C179" s="3"/>
@@ -13815,13 +13621,12 @@
       <c r="V179" s="3"/>
       <c r="W179" s="3"/>
       <c r="X179" s="3"/>
-      <c r="Y179" s="3"/>
-      <c r="Z179" s="4" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-    </row>
-    <row r="180" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y179" s="4" t="str">
+        <f>IF(COUNTA(B179:X179)=0,"",AVERAGE(B179:X179))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="180" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A180" s="2"/>
       <c r="B180" s="3"/>
       <c r="C180" s="3"/>
@@ -13846,13 +13651,12 @@
       <c r="V180" s="3"/>
       <c r="W180" s="3"/>
       <c r="X180" s="3"/>
-      <c r="Y180" s="3"/>
-      <c r="Z180" s="4" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-    </row>
-    <row r="181" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y180" s="4" t="str">
+        <f>IF(COUNTA(B180:X180)=0,"",AVERAGE(B180:X180))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="181" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A181" s="2"/>
       <c r="B181" s="3"/>
       <c r="C181" s="3"/>
@@ -13877,13 +13681,12 @@
       <c r="V181" s="3"/>
       <c r="W181" s="3"/>
       <c r="X181" s="3"/>
-      <c r="Y181" s="3"/>
-      <c r="Z181" s="4" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-    </row>
-    <row r="182" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y181" s="4" t="str">
+        <f>IF(COUNTA(B181:X181)=0,"",AVERAGE(B181:X181))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="182" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A182" s="2"/>
       <c r="B182" s="3"/>
       <c r="C182" s="3"/>
@@ -13908,13 +13711,12 @@
       <c r="V182" s="3"/>
       <c r="W182" s="3"/>
       <c r="X182" s="3"/>
-      <c r="Y182" s="3"/>
-      <c r="Z182" s="4" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-    </row>
-    <row r="183" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y182" s="4" t="str">
+        <f>IF(COUNTA(B182:X182)=0,"",AVERAGE(B182:X182))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="183" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A183" s="2"/>
       <c r="B183" s="3"/>
       <c r="C183" s="3"/>
@@ -13939,13 +13741,12 @@
       <c r="V183" s="3"/>
       <c r="W183" s="3"/>
       <c r="X183" s="3"/>
-      <c r="Y183" s="3"/>
-      <c r="Z183" s="4" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-    </row>
-    <row r="184" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y183" s="4" t="str">
+        <f>IF(COUNTA(B183:X183)=0,"",AVERAGE(B183:X183))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="184" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A184" s="2"/>
       <c r="B184" s="3"/>
       <c r="C184" s="3"/>
@@ -13970,13 +13771,12 @@
       <c r="V184" s="3"/>
       <c r="W184" s="3"/>
       <c r="X184" s="3"/>
-      <c r="Y184" s="3"/>
-      <c r="Z184" s="4" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-    </row>
-    <row r="185" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y184" s="4" t="str">
+        <f>IF(COUNTA(B184:X184)=0,"",AVERAGE(B184:X184))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="185" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A185" s="2"/>
       <c r="B185" s="3"/>
       <c r="C185" s="3"/>
@@ -14001,13 +13801,12 @@
       <c r="V185" s="3"/>
       <c r="W185" s="3"/>
       <c r="X185" s="3"/>
-      <c r="Y185" s="3"/>
-      <c r="Z185" s="4" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-    </row>
-    <row r="186" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y185" s="4" t="str">
+        <f>IF(COUNTA(B185:X185)=0,"",AVERAGE(B185:X185))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="186" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A186" s="2"/>
       <c r="B186" s="3"/>
       <c r="C186" s="3"/>
@@ -14032,13 +13831,12 @@
       <c r="V186" s="3"/>
       <c r="W186" s="3"/>
       <c r="X186" s="3"/>
-      <c r="Y186" s="3"/>
-      <c r="Z186" s="4" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-    </row>
-    <row r="187" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y186" s="4" t="str">
+        <f>IF(COUNTA(B186:X186)=0,"",AVERAGE(B186:X186))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="187" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A187" s="2"/>
       <c r="B187" s="3"/>
       <c r="C187" s="3"/>
@@ -14063,13 +13861,12 @@
       <c r="V187" s="3"/>
       <c r="W187" s="3"/>
       <c r="X187" s="3"/>
-      <c r="Y187" s="3"/>
-      <c r="Z187" s="4" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-    </row>
-    <row r="188" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y187" s="4" t="str">
+        <f>IF(COUNTA(B187:X187)=0,"",AVERAGE(B187:X187))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="188" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A188" s="2"/>
       <c r="B188" s="3"/>
       <c r="C188" s="3"/>
@@ -14094,13 +13891,12 @@
       <c r="V188" s="3"/>
       <c r="W188" s="3"/>
       <c r="X188" s="3"/>
-      <c r="Y188" s="3"/>
-      <c r="Z188" s="4" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-    </row>
-    <row r="189" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y188" s="4" t="str">
+        <f>IF(COUNTA(B188:X188)=0,"",AVERAGE(B188:X188))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="189" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A189" s="2"/>
       <c r="B189" s="3"/>
       <c r="C189" s="3"/>
@@ -14125,13 +13921,12 @@
       <c r="V189" s="3"/>
       <c r="W189" s="3"/>
       <c r="X189" s="3"/>
-      <c r="Y189" s="3"/>
-      <c r="Z189" s="4" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-    </row>
-    <row r="190" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y189" s="4" t="str">
+        <f>IF(COUNTA(B189:X189)=0,"",AVERAGE(B189:X189))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="190" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A190" s="2"/>
       <c r="B190" s="3"/>
       <c r="C190" s="3"/>
@@ -14156,13 +13951,12 @@
       <c r="V190" s="3"/>
       <c r="W190" s="3"/>
       <c r="X190" s="3"/>
-      <c r="Y190" s="3"/>
-      <c r="Z190" s="4" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-    </row>
-    <row r="191" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y190" s="4" t="str">
+        <f>IF(COUNTA(B190:X190)=0,"",AVERAGE(B190:X190))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="191" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A191" s="2"/>
       <c r="B191" s="3"/>
       <c r="C191" s="3"/>
@@ -14187,13 +13981,12 @@
       <c r="V191" s="3"/>
       <c r="W191" s="3"/>
       <c r="X191" s="3"/>
-      <c r="Y191" s="3"/>
-      <c r="Z191" s="4" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-    </row>
-    <row r="192" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y191" s="4" t="str">
+        <f>IF(COUNTA(B191:X191)=0,"",AVERAGE(B191:X191))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="192" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A192" s="2"/>
       <c r="B192" s="3"/>
       <c r="C192" s="3"/>
@@ -14218,13 +14011,12 @@
       <c r="V192" s="3"/>
       <c r="W192" s="3"/>
       <c r="X192" s="3"/>
-      <c r="Y192" s="3"/>
-      <c r="Z192" s="4" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-    </row>
-    <row r="193" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y192" s="4" t="str">
+        <f>IF(COUNTA(B192:X192)=0,"",AVERAGE(B192:X192))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="193" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A193" s="2"/>
       <c r="B193" s="3"/>
       <c r="C193" s="3"/>
@@ -14249,13 +14041,12 @@
       <c r="V193" s="3"/>
       <c r="W193" s="3"/>
       <c r="X193" s="3"/>
-      <c r="Y193" s="3"/>
-      <c r="Z193" s="4" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-    </row>
-    <row r="194" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y193" s="4" t="str">
+        <f>IF(COUNTA(B193:X193)=0,"",AVERAGE(B193:X193))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="194" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A194" s="2"/>
       <c r="B194" s="3"/>
       <c r="C194" s="3"/>
@@ -14280,13 +14071,12 @@
       <c r="V194" s="3"/>
       <c r="W194" s="3"/>
       <c r="X194" s="3"/>
-      <c r="Y194" s="3"/>
-      <c r="Z194" s="4" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-    </row>
-    <row r="195" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y194" s="4" t="str">
+        <f>IF(COUNTA(B194:X194)=0,"",AVERAGE(B194:X194))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="195" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A195" s="2"/>
       <c r="B195" s="3"/>
       <c r="C195" s="3"/>
@@ -14311,13 +14101,12 @@
       <c r="V195" s="3"/>
       <c r="W195" s="3"/>
       <c r="X195" s="3"/>
-      <c r="Y195" s="3"/>
-      <c r="Z195" s="4" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-    </row>
-    <row r="196" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y195" s="4" t="str">
+        <f>IF(COUNTA(B195:X195)=0,"",AVERAGE(B195:X195))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="196" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A196" s="2"/>
       <c r="B196" s="3"/>
       <c r="C196" s="3"/>
@@ -14342,13 +14131,12 @@
       <c r="V196" s="3"/>
       <c r="W196" s="3"/>
       <c r="X196" s="3"/>
-      <c r="Y196" s="3"/>
-      <c r="Z196" s="4" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-    </row>
-    <row r="197" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y196" s="4" t="str">
+        <f>IF(COUNTA(B196:X196)=0,"",AVERAGE(B196:X196))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="197" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A197" s="2"/>
       <c r="B197" s="3"/>
       <c r="C197" s="3"/>
@@ -14373,13 +14161,12 @@
       <c r="V197" s="3"/>
       <c r="W197" s="3"/>
       <c r="X197" s="3"/>
-      <c r="Y197" s="3"/>
-      <c r="Z197" s="4" t="str">
-        <f t="shared" ref="Z197:Z260" si="9">IF(COUNTA(B197:Y197)=0,"",AVERAGE(B197:Y197))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="198" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y197" s="4" t="str">
+        <f>IF(COUNTA(B197:X197)=0,"",AVERAGE(B197:X197))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="198" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A198" s="2"/>
       <c r="B198" s="3"/>
       <c r="C198" s="3"/>
@@ -14404,13 +14191,12 @@
       <c r="V198" s="3"/>
       <c r="W198" s="3"/>
       <c r="X198" s="3"/>
-      <c r="Y198" s="3"/>
-      <c r="Z198" s="4" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="199" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y198" s="4" t="str">
+        <f>IF(COUNTA(B198:X198)=0,"",AVERAGE(B198:X198))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="199" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A199" s="2"/>
       <c r="B199" s="3"/>
       <c r="C199" s="3"/>
@@ -14435,13 +14221,12 @@
       <c r="V199" s="3"/>
       <c r="W199" s="3"/>
       <c r="X199" s="3"/>
-      <c r="Y199" s="3"/>
-      <c r="Z199" s="4" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="200" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y199" s="4" t="str">
+        <f>IF(COUNTA(B199:X199)=0,"",AVERAGE(B199:X199))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="200" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A200" s="2"/>
       <c r="B200" s="3"/>
       <c r="C200" s="3"/>
@@ -14466,13 +14251,12 @@
       <c r="V200" s="3"/>
       <c r="W200" s="3"/>
       <c r="X200" s="3"/>
-      <c r="Y200" s="3"/>
-      <c r="Z200" s="4" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="201" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y200" s="4" t="str">
+        <f>IF(COUNTA(B200:X200)=0,"",AVERAGE(B200:X200))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="201" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A201" s="2"/>
       <c r="B201" s="3"/>
       <c r="C201" s="3"/>
@@ -14497,13 +14281,12 @@
       <c r="V201" s="3"/>
       <c r="W201" s="3"/>
       <c r="X201" s="3"/>
-      <c r="Y201" s="3"/>
-      <c r="Z201" s="4" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="202" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y201" s="4" t="str">
+        <f>IF(COUNTA(B201:X201)=0,"",AVERAGE(B201:X201))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="202" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A202" s="2"/>
       <c r="B202" s="3"/>
       <c r="C202" s="3"/>
@@ -14528,13 +14311,12 @@
       <c r="V202" s="3"/>
       <c r="W202" s="3"/>
       <c r="X202" s="3"/>
-      <c r="Y202" s="3"/>
-      <c r="Z202" s="4" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="203" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y202" s="4" t="str">
+        <f>IF(COUNTA(B202:X202)=0,"",AVERAGE(B202:X202))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="203" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A203" s="2"/>
       <c r="B203" s="3"/>
       <c r="C203" s="3"/>
@@ -14559,13 +14341,12 @@
       <c r="V203" s="3"/>
       <c r="W203" s="3"/>
       <c r="X203" s="3"/>
-      <c r="Y203" s="3"/>
-      <c r="Z203" s="4" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="204" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y203" s="4" t="str">
+        <f>IF(COUNTA(B203:X203)=0,"",AVERAGE(B203:X203))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="204" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A204" s="2"/>
       <c r="B204" s="3"/>
       <c r="C204" s="3"/>
@@ -14590,13 +14371,12 @@
       <c r="V204" s="3"/>
       <c r="W204" s="3"/>
       <c r="X204" s="3"/>
-      <c r="Y204" s="3"/>
-      <c r="Z204" s="4" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="205" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y204" s="4" t="str">
+        <f>IF(COUNTA(B204:X204)=0,"",AVERAGE(B204:X204))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="205" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A205" s="2"/>
       <c r="B205" s="3"/>
       <c r="C205" s="3"/>
@@ -14621,13 +14401,12 @@
       <c r="V205" s="3"/>
       <c r="W205" s="3"/>
       <c r="X205" s="3"/>
-      <c r="Y205" s="3"/>
-      <c r="Z205" s="4" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="206" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y205" s="4" t="str">
+        <f>IF(COUNTA(B205:X205)=0,"",AVERAGE(B205:X205))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="206" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A206" s="2"/>
       <c r="B206" s="3"/>
       <c r="C206" s="3"/>
@@ -14652,13 +14431,12 @@
       <c r="V206" s="3"/>
       <c r="W206" s="3"/>
       <c r="X206" s="3"/>
-      <c r="Y206" s="3"/>
-      <c r="Z206" s="4" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="207" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y206" s="4" t="str">
+        <f>IF(COUNTA(B206:X206)=0,"",AVERAGE(B206:X206))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="207" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A207" s="2"/>
       <c r="B207" s="3"/>
       <c r="C207" s="3"/>
@@ -14683,13 +14461,12 @@
       <c r="V207" s="3"/>
       <c r="W207" s="3"/>
       <c r="X207" s="3"/>
-      <c r="Y207" s="3"/>
-      <c r="Z207" s="4" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="208" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y207" s="4" t="str">
+        <f>IF(COUNTA(B207:X207)=0,"",AVERAGE(B207:X207))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="208" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A208" s="2"/>
       <c r="B208" s="3"/>
       <c r="C208" s="3"/>
@@ -14714,13 +14491,12 @@
       <c r="V208" s="3"/>
       <c r="W208" s="3"/>
       <c r="X208" s="3"/>
-      <c r="Y208" s="3"/>
-      <c r="Z208" s="4" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="209" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y208" s="4" t="str">
+        <f>IF(COUNTA(B208:X208)=0,"",AVERAGE(B208:X208))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="209" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A209" s="2"/>
       <c r="B209" s="3"/>
       <c r="C209" s="3"/>
@@ -14745,13 +14521,12 @@
       <c r="V209" s="3"/>
       <c r="W209" s="3"/>
       <c r="X209" s="3"/>
-      <c r="Y209" s="3"/>
-      <c r="Z209" s="4" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="210" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y209" s="4" t="str">
+        <f>IF(COUNTA(B209:X209)=0,"",AVERAGE(B209:X209))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="210" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A210" s="2"/>
       <c r="B210" s="3"/>
       <c r="C210" s="3"/>
@@ -14776,13 +14551,12 @@
       <c r="V210" s="3"/>
       <c r="W210" s="3"/>
       <c r="X210" s="3"/>
-      <c r="Y210" s="3"/>
-      <c r="Z210" s="4" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="211" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y210" s="4" t="str">
+        <f>IF(COUNTA(B210:X210)=0,"",AVERAGE(B210:X210))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="211" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A211" s="2"/>
       <c r="B211" s="3"/>
       <c r="C211" s="3"/>
@@ -14807,13 +14581,12 @@
       <c r="V211" s="3"/>
       <c r="W211" s="3"/>
       <c r="X211" s="3"/>
-      <c r="Y211" s="3"/>
-      <c r="Z211" s="4" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="212" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y211" s="4" t="str">
+        <f>IF(COUNTA(B211:X211)=0,"",AVERAGE(B211:X211))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="212" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A212" s="2"/>
       <c r="B212" s="3"/>
       <c r="C212" s="3"/>
@@ -14838,13 +14611,12 @@
       <c r="V212" s="3"/>
       <c r="W212" s="3"/>
       <c r="X212" s="3"/>
-      <c r="Y212" s="3"/>
-      <c r="Z212" s="4" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="213" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y212" s="4" t="str">
+        <f>IF(COUNTA(B212:X212)=0,"",AVERAGE(B212:X212))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="213" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A213" s="2"/>
       <c r="B213" s="3"/>
       <c r="C213" s="3"/>
@@ -14869,13 +14641,12 @@
       <c r="V213" s="3"/>
       <c r="W213" s="3"/>
       <c r="X213" s="3"/>
-      <c r="Y213" s="3"/>
-      <c r="Z213" s="4" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="214" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y213" s="4" t="str">
+        <f>IF(COUNTA(B213:X213)=0,"",AVERAGE(B213:X213))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="214" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A214" s="2"/>
       <c r="B214" s="3"/>
       <c r="C214" s="3"/>
@@ -14900,13 +14671,12 @@
       <c r="V214" s="3"/>
       <c r="W214" s="3"/>
       <c r="X214" s="3"/>
-      <c r="Y214" s="3"/>
-      <c r="Z214" s="4" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="215" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y214" s="4" t="str">
+        <f>IF(COUNTA(B214:X214)=0,"",AVERAGE(B214:X214))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="215" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A215" s="2"/>
       <c r="B215" s="3"/>
       <c r="C215" s="3"/>
@@ -14931,13 +14701,12 @@
       <c r="V215" s="3"/>
       <c r="W215" s="3"/>
       <c r="X215" s="3"/>
-      <c r="Y215" s="3"/>
-      <c r="Z215" s="4" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="216" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y215" s="4" t="str">
+        <f>IF(COUNTA(B215:X215)=0,"",AVERAGE(B215:X215))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="216" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A216" s="2"/>
       <c r="B216" s="3"/>
       <c r="C216" s="3"/>
@@ -14962,13 +14731,12 @@
       <c r="V216" s="3"/>
       <c r="W216" s="3"/>
       <c r="X216" s="3"/>
-      <c r="Y216" s="3"/>
-      <c r="Z216" s="4" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="217" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y216" s="4" t="str">
+        <f>IF(COUNTA(B216:X216)=0,"",AVERAGE(B216:X216))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="217" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A217" s="2"/>
       <c r="B217" s="3"/>
       <c r="C217" s="3"/>
@@ -14993,13 +14761,12 @@
       <c r="V217" s="3"/>
       <c r="W217" s="3"/>
       <c r="X217" s="3"/>
-      <c r="Y217" s="3"/>
-      <c r="Z217" s="4" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="218" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y217" s="4" t="str">
+        <f>IF(COUNTA(B217:X217)=0,"",AVERAGE(B217:X217))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="218" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A218" s="2"/>
       <c r="B218" s="3"/>
       <c r="C218" s="3"/>
@@ -15024,13 +14791,12 @@
       <c r="V218" s="3"/>
       <c r="W218" s="3"/>
       <c r="X218" s="3"/>
-      <c r="Y218" s="3"/>
-      <c r="Z218" s="4" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="219" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y218" s="4" t="str">
+        <f>IF(COUNTA(B218:X218)=0,"",AVERAGE(B218:X218))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="219" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A219" s="2"/>
       <c r="B219" s="3"/>
       <c r="C219" s="3"/>
@@ -15055,13 +14821,12 @@
       <c r="V219" s="3"/>
       <c r="W219" s="3"/>
       <c r="X219" s="3"/>
-      <c r="Y219" s="3"/>
-      <c r="Z219" s="4" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="220" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y219" s="4" t="str">
+        <f>IF(COUNTA(B219:X219)=0,"",AVERAGE(B219:X219))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="220" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A220" s="2"/>
       <c r="B220" s="3"/>
       <c r="C220" s="3"/>
@@ -15086,13 +14851,12 @@
       <c r="V220" s="3"/>
       <c r="W220" s="3"/>
       <c r="X220" s="3"/>
-      <c r="Y220" s="3"/>
-      <c r="Z220" s="4" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="221" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y220" s="4" t="str">
+        <f>IF(COUNTA(B220:X220)=0,"",AVERAGE(B220:X220))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="221" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A221" s="2"/>
       <c r="B221" s="3"/>
       <c r="C221" s="3"/>
@@ -15117,13 +14881,12 @@
       <c r="V221" s="3"/>
       <c r="W221" s="3"/>
       <c r="X221" s="3"/>
-      <c r="Y221" s="3"/>
-      <c r="Z221" s="4" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="222" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y221" s="4" t="str">
+        <f>IF(COUNTA(B221:X221)=0,"",AVERAGE(B221:X221))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="222" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A222" s="2"/>
       <c r="B222" s="3"/>
       <c r="C222" s="3"/>
@@ -15148,13 +14911,12 @@
       <c r="V222" s="3"/>
       <c r="W222" s="3"/>
       <c r="X222" s="3"/>
-      <c r="Y222" s="3"/>
-      <c r="Z222" s="4" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="223" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y222" s="4" t="str">
+        <f>IF(COUNTA(B222:X222)=0,"",AVERAGE(B222:X222))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="223" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A223" s="2"/>
       <c r="B223" s="3"/>
       <c r="C223" s="3"/>
@@ -15179,13 +14941,12 @@
       <c r="V223" s="3"/>
       <c r="W223" s="3"/>
       <c r="X223" s="3"/>
-      <c r="Y223" s="3"/>
-      <c r="Z223" s="4" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="224" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y223" s="4" t="str">
+        <f>IF(COUNTA(B223:X223)=0,"",AVERAGE(B223:X223))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="224" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A224" s="2"/>
       <c r="B224" s="3"/>
       <c r="C224" s="3"/>
@@ -15210,13 +14971,12 @@
       <c r="V224" s="3"/>
       <c r="W224" s="3"/>
       <c r="X224" s="3"/>
-      <c r="Y224" s="3"/>
-      <c r="Z224" s="4" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="225" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y224" s="4" t="str">
+        <f>IF(COUNTA(B224:X224)=0,"",AVERAGE(B224:X224))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="225" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A225" s="2"/>
       <c r="B225" s="3"/>
       <c r="C225" s="3"/>
@@ -15241,13 +15001,12 @@
       <c r="V225" s="3"/>
       <c r="W225" s="3"/>
       <c r="X225" s="3"/>
-      <c r="Y225" s="3"/>
-      <c r="Z225" s="4" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="226" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y225" s="4" t="str">
+        <f>IF(COUNTA(B225:X225)=0,"",AVERAGE(B225:X225))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="226" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A226" s="2"/>
       <c r="B226" s="3"/>
       <c r="C226" s="3"/>
@@ -15272,13 +15031,12 @@
       <c r="V226" s="3"/>
       <c r="W226" s="3"/>
       <c r="X226" s="3"/>
-      <c r="Y226" s="3"/>
-      <c r="Z226" s="4" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="227" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y226" s="4" t="str">
+        <f>IF(COUNTA(B226:X226)=0,"",AVERAGE(B226:X226))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="227" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A227" s="2"/>
       <c r="B227" s="3"/>
       <c r="C227" s="3"/>
@@ -15303,13 +15061,12 @@
       <c r="V227" s="3"/>
       <c r="W227" s="3"/>
       <c r="X227" s="3"/>
-      <c r="Y227" s="3"/>
-      <c r="Z227" s="4" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="228" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y227" s="4" t="str">
+        <f>IF(COUNTA(B227:X227)=0,"",AVERAGE(B227:X227))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="228" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A228" s="2"/>
       <c r="B228" s="3"/>
       <c r="C228" s="3"/>
@@ -15334,13 +15091,12 @@
       <c r="V228" s="3"/>
       <c r="W228" s="3"/>
       <c r="X228" s="3"/>
-      <c r="Y228" s="3"/>
-      <c r="Z228" s="4" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="229" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y228" s="4" t="str">
+        <f>IF(COUNTA(B228:X228)=0,"",AVERAGE(B228:X228))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="229" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A229" s="2"/>
       <c r="B229" s="3"/>
       <c r="C229" s="3"/>
@@ -15365,13 +15121,12 @@
       <c r="V229" s="3"/>
       <c r="W229" s="3"/>
       <c r="X229" s="3"/>
-      <c r="Y229" s="3"/>
-      <c r="Z229" s="4" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="230" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y229" s="4" t="str">
+        <f>IF(COUNTA(B229:X229)=0,"",AVERAGE(B229:X229))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="230" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A230" s="2"/>
       <c r="B230" s="3"/>
       <c r="C230" s="3"/>
@@ -15396,13 +15151,12 @@
       <c r="V230" s="3"/>
       <c r="W230" s="3"/>
       <c r="X230" s="3"/>
-      <c r="Y230" s="3"/>
-      <c r="Z230" s="4" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="231" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y230" s="4" t="str">
+        <f>IF(COUNTA(B230:X230)=0,"",AVERAGE(B230:X230))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="231" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A231" s="2"/>
       <c r="B231" s="3"/>
       <c r="C231" s="3"/>
@@ -15427,13 +15181,12 @@
       <c r="V231" s="3"/>
       <c r="W231" s="3"/>
       <c r="X231" s="3"/>
-      <c r="Y231" s="3"/>
-      <c r="Z231" s="4" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="232" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y231" s="4" t="str">
+        <f>IF(COUNTA(B231:X231)=0,"",AVERAGE(B231:X231))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="232" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A232" s="2"/>
       <c r="B232" s="3"/>
       <c r="C232" s="3"/>
@@ -15458,13 +15211,12 @@
       <c r="V232" s="3"/>
       <c r="W232" s="3"/>
       <c r="X232" s="3"/>
-      <c r="Y232" s="3"/>
-      <c r="Z232" s="4" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="233" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y232" s="4" t="str">
+        <f>IF(COUNTA(B232:X232)=0,"",AVERAGE(B232:X232))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="233" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A233" s="2"/>
       <c r="B233" s="3"/>
       <c r="C233" s="3"/>
@@ -15489,13 +15241,12 @@
       <c r="V233" s="3"/>
       <c r="W233" s="3"/>
       <c r="X233" s="3"/>
-      <c r="Y233" s="3"/>
-      <c r="Z233" s="4" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="234" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y233" s="4" t="str">
+        <f>IF(COUNTA(B233:X233)=0,"",AVERAGE(B233:X233))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="234" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A234" s="2"/>
       <c r="B234" s="3"/>
       <c r="C234" s="3"/>
@@ -15520,13 +15271,12 @@
       <c r="V234" s="3"/>
       <c r="W234" s="3"/>
       <c r="X234" s="3"/>
-      <c r="Y234" s="3"/>
-      <c r="Z234" s="4" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="235" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y234" s="4" t="str">
+        <f>IF(COUNTA(B234:X234)=0,"",AVERAGE(B234:X234))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="235" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A235" s="2"/>
       <c r="B235" s="3"/>
       <c r="C235" s="3"/>
@@ -15551,13 +15301,12 @@
       <c r="V235" s="3"/>
       <c r="W235" s="3"/>
       <c r="X235" s="3"/>
-      <c r="Y235" s="3"/>
-      <c r="Z235" s="4" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="236" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y235" s="4" t="str">
+        <f>IF(COUNTA(B235:X235)=0,"",AVERAGE(B235:X235))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="236" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A236" s="2"/>
       <c r="B236" s="3"/>
       <c r="C236" s="3"/>
@@ -15582,13 +15331,12 @@
       <c r="V236" s="3"/>
       <c r="W236" s="3"/>
       <c r="X236" s="3"/>
-      <c r="Y236" s="3"/>
-      <c r="Z236" s="4" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="237" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y236" s="4" t="str">
+        <f>IF(COUNTA(B236:X236)=0,"",AVERAGE(B236:X236))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="237" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A237" s="2"/>
       <c r="B237" s="3"/>
       <c r="C237" s="3"/>
@@ -15613,13 +15361,12 @@
       <c r="V237" s="3"/>
       <c r="W237" s="3"/>
       <c r="X237" s="3"/>
-      <c r="Y237" s="3"/>
-      <c r="Z237" s="4" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="238" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y237" s="4" t="str">
+        <f>IF(COUNTA(B237:X237)=0,"",AVERAGE(B237:X237))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="238" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A238" s="2"/>
       <c r="B238" s="3"/>
       <c r="C238" s="3"/>
@@ -15644,13 +15391,12 @@
       <c r="V238" s="3"/>
       <c r="W238" s="3"/>
       <c r="X238" s="3"/>
-      <c r="Y238" s="3"/>
-      <c r="Z238" s="4" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="239" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y238" s="4" t="str">
+        <f>IF(COUNTA(B238:X238)=0,"",AVERAGE(B238:X238))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="239" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A239" s="2"/>
       <c r="B239" s="3"/>
       <c r="C239" s="3"/>
@@ -15675,13 +15421,12 @@
       <c r="V239" s="3"/>
       <c r="W239" s="3"/>
       <c r="X239" s="3"/>
-      <c r="Y239" s="3"/>
-      <c r="Z239" s="4" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="240" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y239" s="4" t="str">
+        <f>IF(COUNTA(B239:X239)=0,"",AVERAGE(B239:X239))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="240" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A240" s="2"/>
       <c r="B240" s="3"/>
       <c r="C240" s="3"/>
@@ -15706,13 +15451,12 @@
       <c r="V240" s="3"/>
       <c r="W240" s="3"/>
       <c r="X240" s="3"/>
-      <c r="Y240" s="3"/>
-      <c r="Z240" s="4" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="241" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y240" s="4" t="str">
+        <f>IF(COUNTA(B240:X240)=0,"",AVERAGE(B240:X240))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="241" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A241" s="2"/>
       <c r="B241" s="3"/>
       <c r="C241" s="3"/>
@@ -15737,13 +15481,12 @@
       <c r="V241" s="3"/>
       <c r="W241" s="3"/>
       <c r="X241" s="3"/>
-      <c r="Y241" s="3"/>
-      <c r="Z241" s="4" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="242" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y241" s="4" t="str">
+        <f>IF(COUNTA(B241:X241)=0,"",AVERAGE(B241:X241))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="242" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A242" s="2"/>
       <c r="B242" s="3"/>
       <c r="C242" s="3"/>
@@ -15768,13 +15511,12 @@
       <c r="V242" s="3"/>
       <c r="W242" s="3"/>
       <c r="X242" s="3"/>
-      <c r="Y242" s="3"/>
-      <c r="Z242" s="4" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="243" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y242" s="4" t="str">
+        <f>IF(COUNTA(B242:X242)=0,"",AVERAGE(B242:X242))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="243" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A243" s="2"/>
       <c r="B243" s="3"/>
       <c r="C243" s="3"/>
@@ -15799,13 +15541,12 @@
       <c r="V243" s="3"/>
       <c r="W243" s="3"/>
       <c r="X243" s="3"/>
-      <c r="Y243" s="3"/>
-      <c r="Z243" s="4" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="244" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y243" s="4" t="str">
+        <f>IF(COUNTA(B243:X243)=0,"",AVERAGE(B243:X243))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="244" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A244" s="2"/>
       <c r="B244" s="3"/>
       <c r="C244" s="3"/>
@@ -15830,13 +15571,12 @@
       <c r="V244" s="3"/>
       <c r="W244" s="3"/>
       <c r="X244" s="3"/>
-      <c r="Y244" s="3"/>
-      <c r="Z244" s="4" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="245" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y244" s="4" t="str">
+        <f>IF(COUNTA(B244:X244)=0,"",AVERAGE(B244:X244))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="245" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A245" s="2"/>
       <c r="B245" s="3"/>
       <c r="C245" s="3"/>
@@ -15861,13 +15601,12 @@
       <c r="V245" s="3"/>
       <c r="W245" s="3"/>
       <c r="X245" s="3"/>
-      <c r="Y245" s="3"/>
-      <c r="Z245" s="4" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="246" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y245" s="4" t="str">
+        <f>IF(COUNTA(B245:X245)=0,"",AVERAGE(B245:X245))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="246" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A246" s="2"/>
       <c r="B246" s="3"/>
       <c r="C246" s="3"/>
@@ -15892,13 +15631,12 @@
       <c r="V246" s="3"/>
       <c r="W246" s="3"/>
       <c r="X246" s="3"/>
-      <c r="Y246" s="3"/>
-      <c r="Z246" s="4" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="247" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y246" s="4" t="str">
+        <f>IF(COUNTA(B246:X246)=0,"",AVERAGE(B246:X246))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="247" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A247" s="2"/>
       <c r="B247" s="3"/>
       <c r="C247" s="3"/>
@@ -15923,13 +15661,12 @@
       <c r="V247" s="3"/>
       <c r="W247" s="3"/>
       <c r="X247" s="3"/>
-      <c r="Y247" s="3"/>
-      <c r="Z247" s="4" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="248" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y247" s="4" t="str">
+        <f>IF(COUNTA(B247:X247)=0,"",AVERAGE(B247:X247))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="248" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A248" s="2"/>
       <c r="B248" s="3"/>
       <c r="C248" s="3"/>
@@ -15954,13 +15691,12 @@
       <c r="V248" s="3"/>
       <c r="W248" s="3"/>
       <c r="X248" s="3"/>
-      <c r="Y248" s="3"/>
-      <c r="Z248" s="4" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="249" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y248" s="4" t="str">
+        <f>IF(COUNTA(B248:X248)=0,"",AVERAGE(B248:X248))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="249" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A249" s="2"/>
       <c r="B249" s="3"/>
       <c r="C249" s="3"/>
@@ -15985,13 +15721,12 @@
       <c r="V249" s="3"/>
       <c r="W249" s="3"/>
       <c r="X249" s="3"/>
-      <c r="Y249" s="3"/>
-      <c r="Z249" s="4" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="250" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y249" s="4" t="str">
+        <f>IF(COUNTA(B249:X249)=0,"",AVERAGE(B249:X249))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="250" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A250" s="2"/>
       <c r="B250" s="3"/>
       <c r="C250" s="3"/>
@@ -16016,13 +15751,12 @@
       <c r="V250" s="3"/>
       <c r="W250" s="3"/>
       <c r="X250" s="3"/>
-      <c r="Y250" s="3"/>
-      <c r="Z250" s="4" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="251" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y250" s="4" t="str">
+        <f>IF(COUNTA(B250:X250)=0,"",AVERAGE(B250:X250))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="251" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A251" s="2"/>
       <c r="B251" s="3"/>
       <c r="C251" s="3"/>
@@ -16047,13 +15781,12 @@
       <c r="V251" s="3"/>
       <c r="W251" s="3"/>
       <c r="X251" s="3"/>
-      <c r="Y251" s="3"/>
-      <c r="Z251" s="4" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="252" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y251" s="4" t="str">
+        <f>IF(COUNTA(B251:X251)=0,"",AVERAGE(B251:X251))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="252" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A252" s="2"/>
       <c r="B252" s="3"/>
       <c r="C252" s="3"/>
@@ -16078,13 +15811,12 @@
       <c r="V252" s="3"/>
       <c r="W252" s="3"/>
       <c r="X252" s="3"/>
-      <c r="Y252" s="3"/>
-      <c r="Z252" s="4" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="253" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y252" s="4" t="str">
+        <f>IF(COUNTA(B252:X252)=0,"",AVERAGE(B252:X252))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="253" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A253" s="2"/>
       <c r="B253" s="3"/>
       <c r="C253" s="3"/>
@@ -16109,13 +15841,12 @@
       <c r="V253" s="3"/>
       <c r="W253" s="3"/>
       <c r="X253" s="3"/>
-      <c r="Y253" s="3"/>
-      <c r="Z253" s="4" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="254" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y253" s="4" t="str">
+        <f>IF(COUNTA(B253:X253)=0,"",AVERAGE(B253:X253))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="254" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A254" s="2"/>
       <c r="B254" s="3"/>
       <c r="C254" s="3"/>
@@ -16140,13 +15871,12 @@
       <c r="V254" s="3"/>
       <c r="W254" s="3"/>
       <c r="X254" s="3"/>
-      <c r="Y254" s="3"/>
-      <c r="Z254" s="4" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="255" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y254" s="4" t="str">
+        <f>IF(COUNTA(B254:X254)=0,"",AVERAGE(B254:X254))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="255" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A255" s="2"/>
       <c r="B255" s="3"/>
       <c r="C255" s="3"/>
@@ -16171,13 +15901,12 @@
       <c r="V255" s="3"/>
       <c r="W255" s="3"/>
       <c r="X255" s="3"/>
-      <c r="Y255" s="3"/>
-      <c r="Z255" s="4" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="256" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y255" s="4" t="str">
+        <f>IF(COUNTA(B255:X255)=0,"",AVERAGE(B255:X255))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="256" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A256" s="2"/>
       <c r="B256" s="3"/>
       <c r="C256" s="3"/>
@@ -16202,13 +15931,12 @@
       <c r="V256" s="3"/>
       <c r="W256" s="3"/>
       <c r="X256" s="3"/>
-      <c r="Y256" s="3"/>
-      <c r="Z256" s="4" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="257" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y256" s="4" t="str">
+        <f>IF(COUNTA(B256:X256)=0,"",AVERAGE(B256:X256))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="257" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A257" s="2"/>
       <c r="B257" s="3"/>
       <c r="C257" s="3"/>
@@ -16233,13 +15961,12 @@
       <c r="V257" s="3"/>
       <c r="W257" s="3"/>
       <c r="X257" s="3"/>
-      <c r="Y257" s="3"/>
-      <c r="Z257" s="4" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="258" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y257" s="4" t="str">
+        <f>IF(COUNTA(B257:X257)=0,"",AVERAGE(B257:X257))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="258" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A258" s="2"/>
       <c r="B258" s="3"/>
       <c r="C258" s="3"/>
@@ -16264,13 +15991,12 @@
       <c r="V258" s="3"/>
       <c r="W258" s="3"/>
       <c r="X258" s="3"/>
-      <c r="Y258" s="3"/>
-      <c r="Z258" s="4" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="259" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y258" s="4" t="str">
+        <f>IF(COUNTA(B258:X258)=0,"",AVERAGE(B258:X258))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="259" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A259" s="2"/>
       <c r="B259" s="3"/>
       <c r="C259" s="3"/>
@@ -16295,13 +16021,12 @@
       <c r="V259" s="3"/>
       <c r="W259" s="3"/>
       <c r="X259" s="3"/>
-      <c r="Y259" s="3"/>
-      <c r="Z259" s="4" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="260" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y259" s="4" t="str">
+        <f>IF(COUNTA(B259:X259)=0,"",AVERAGE(B259:X259))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="260" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A260" s="2"/>
       <c r="B260" s="3"/>
       <c r="C260" s="3"/>
@@ -16326,13 +16051,12 @@
       <c r="V260" s="3"/>
       <c r="W260" s="3"/>
       <c r="X260" s="3"/>
-      <c r="Y260" s="3"/>
-      <c r="Z260" s="4" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="261" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y260" s="4" t="str">
+        <f>IF(COUNTA(B260:X260)=0,"",AVERAGE(B260:X260))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="261" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A261" s="2"/>
       <c r="B261" s="3"/>
       <c r="C261" s="3"/>
@@ -16357,13 +16081,12 @@
       <c r="V261" s="3"/>
       <c r="W261" s="3"/>
       <c r="X261" s="3"/>
-      <c r="Y261" s="3"/>
-      <c r="Z261" s="4" t="str">
-        <f t="shared" ref="Z261:Z324" si="10">IF(COUNTA(B261:Y261)=0,"",AVERAGE(B261:Y261))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="262" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y261" s="4" t="str">
+        <f>IF(COUNTA(B261:X261)=0,"",AVERAGE(B261:X261))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="262" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A262" s="2"/>
       <c r="B262" s="3"/>
       <c r="C262" s="3"/>
@@ -16388,13 +16111,12 @@
       <c r="V262" s="3"/>
       <c r="W262" s="3"/>
       <c r="X262" s="3"/>
-      <c r="Y262" s="3"/>
-      <c r="Z262" s="4" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="263" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y262" s="4" t="str">
+        <f>IF(COUNTA(B262:X262)=0,"",AVERAGE(B262:X262))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="263" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A263" s="2"/>
       <c r="B263" s="3"/>
       <c r="C263" s="3"/>
@@ -16419,13 +16141,12 @@
       <c r="V263" s="3"/>
       <c r="W263" s="3"/>
       <c r="X263" s="3"/>
-      <c r="Y263" s="3"/>
-      <c r="Z263" s="4" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="264" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y263" s="4" t="str">
+        <f>IF(COUNTA(B263:X263)=0,"",AVERAGE(B263:X263))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="264" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A264" s="2"/>
       <c r="B264" s="3"/>
       <c r="C264" s="3"/>
@@ -16450,13 +16171,12 @@
       <c r="V264" s="3"/>
       <c r="W264" s="3"/>
       <c r="X264" s="3"/>
-      <c r="Y264" s="3"/>
-      <c r="Z264" s="4" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="265" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y264" s="4" t="str">
+        <f>IF(COUNTA(B264:X264)=0,"",AVERAGE(B264:X264))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="265" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A265" s="2"/>
       <c r="B265" s="3"/>
       <c r="C265" s="3"/>
@@ -16481,13 +16201,12 @@
       <c r="V265" s="3"/>
       <c r="W265" s="3"/>
       <c r="X265" s="3"/>
-      <c r="Y265" s="3"/>
-      <c r="Z265" s="4" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="266" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y265" s="4" t="str">
+        <f>IF(COUNTA(B265:X265)=0,"",AVERAGE(B265:X265))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="266" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A266" s="2"/>
       <c r="B266" s="3"/>
       <c r="C266" s="3"/>
@@ -16512,13 +16231,12 @@
       <c r="V266" s="3"/>
       <c r="W266" s="3"/>
       <c r="X266" s="3"/>
-      <c r="Y266" s="3"/>
-      <c r="Z266" s="4" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="267" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y266" s="4" t="str">
+        <f>IF(COUNTA(B266:X266)=0,"",AVERAGE(B266:X266))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="267" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A267" s="2"/>
       <c r="B267" s="3"/>
       <c r="C267" s="3"/>
@@ -16543,13 +16261,12 @@
       <c r="V267" s="3"/>
       <c r="W267" s="3"/>
       <c r="X267" s="3"/>
-      <c r="Y267" s="3"/>
-      <c r="Z267" s="4" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="268" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y267" s="4" t="str">
+        <f>IF(COUNTA(B267:X267)=0,"",AVERAGE(B267:X267))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="268" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A268" s="2"/>
       <c r="B268" s="3"/>
       <c r="C268" s="3"/>
@@ -16574,13 +16291,12 @@
       <c r="V268" s="3"/>
       <c r="W268" s="3"/>
       <c r="X268" s="3"/>
-      <c r="Y268" s="3"/>
-      <c r="Z268" s="4" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="269" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y268" s="4" t="str">
+        <f>IF(COUNTA(B268:X268)=0,"",AVERAGE(B268:X268))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="269" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A269" s="2"/>
       <c r="B269" s="3"/>
       <c r="C269" s="3"/>
@@ -16605,13 +16321,12 @@
       <c r="V269" s="3"/>
       <c r="W269" s="3"/>
       <c r="X269" s="3"/>
-      <c r="Y269" s="3"/>
-      <c r="Z269" s="4" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="270" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y269" s="4" t="str">
+        <f>IF(COUNTA(B269:X269)=0,"",AVERAGE(B269:X269))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="270" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A270" s="2"/>
       <c r="B270" s="3"/>
       <c r="C270" s="3"/>
@@ -16636,13 +16351,12 @@
       <c r="V270" s="3"/>
       <c r="W270" s="3"/>
       <c r="X270" s="3"/>
-      <c r="Y270" s="3"/>
-      <c r="Z270" s="4" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="271" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y270" s="4" t="str">
+        <f>IF(COUNTA(B270:X270)=0,"",AVERAGE(B270:X270))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="271" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A271" s="2"/>
       <c r="B271" s="3"/>
       <c r="C271" s="3"/>
@@ -16667,13 +16381,12 @@
       <c r="V271" s="3"/>
       <c r="W271" s="3"/>
       <c r="X271" s="3"/>
-      <c r="Y271" s="3"/>
-      <c r="Z271" s="4" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="272" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y271" s="4" t="str">
+        <f>IF(COUNTA(B271:X271)=0,"",AVERAGE(B271:X271))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="272" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A272" s="2"/>
       <c r="B272" s="3"/>
       <c r="C272" s="3"/>
@@ -16698,13 +16411,12 @@
       <c r="V272" s="3"/>
       <c r="W272" s="3"/>
       <c r="X272" s="3"/>
-      <c r="Y272" s="3"/>
-      <c r="Z272" s="4" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="273" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y272" s="4" t="str">
+        <f>IF(COUNTA(B272:X272)=0,"",AVERAGE(B272:X272))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="273" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A273" s="2"/>
       <c r="B273" s="3"/>
       <c r="C273" s="3"/>
@@ -16729,13 +16441,12 @@
       <c r="V273" s="3"/>
       <c r="W273" s="3"/>
       <c r="X273" s="3"/>
-      <c r="Y273" s="3"/>
-      <c r="Z273" s="4" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="274" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y273" s="4" t="str">
+        <f>IF(COUNTA(B273:X273)=0,"",AVERAGE(B273:X273))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="274" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A274" s="2"/>
       <c r="B274" s="3"/>
       <c r="C274" s="3"/>
@@ -16760,13 +16471,12 @@
       <c r="V274" s="3"/>
       <c r="W274" s="3"/>
       <c r="X274" s="3"/>
-      <c r="Y274" s="3"/>
-      <c r="Z274" s="4" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="275" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y274" s="4" t="str">
+        <f>IF(COUNTA(B274:X274)=0,"",AVERAGE(B274:X274))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="275" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A275" s="2"/>
       <c r="B275" s="3"/>
       <c r="C275" s="3"/>
@@ -16791,13 +16501,12 @@
       <c r="V275" s="3"/>
       <c r="W275" s="3"/>
       <c r="X275" s="3"/>
-      <c r="Y275" s="3"/>
-      <c r="Z275" s="4" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="276" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y275" s="4" t="str">
+        <f>IF(COUNTA(B275:X275)=0,"",AVERAGE(B275:X275))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="276" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A276" s="2"/>
       <c r="B276" s="3"/>
       <c r="C276" s="3"/>
@@ -16822,13 +16531,12 @@
       <c r="V276" s="3"/>
       <c r="W276" s="3"/>
       <c r="X276" s="3"/>
-      <c r="Y276" s="3"/>
-      <c r="Z276" s="4" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="277" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y276" s="4" t="str">
+        <f>IF(COUNTA(B276:X276)=0,"",AVERAGE(B276:X276))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="277" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A277" s="2"/>
       <c r="B277" s="3"/>
       <c r="C277" s="3"/>
@@ -16853,13 +16561,12 @@
       <c r="V277" s="3"/>
       <c r="W277" s="3"/>
       <c r="X277" s="3"/>
-      <c r="Y277" s="3"/>
-      <c r="Z277" s="4" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="278" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y277" s="4" t="str">
+        <f>IF(COUNTA(B277:X277)=0,"",AVERAGE(B277:X277))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="278" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A278" s="2"/>
       <c r="B278" s="3"/>
       <c r="C278" s="3"/>
@@ -16884,13 +16591,12 @@
       <c r="V278" s="3"/>
       <c r="W278" s="3"/>
       <c r="X278" s="3"/>
-      <c r="Y278" s="3"/>
-      <c r="Z278" s="4" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="279" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y278" s="4" t="str">
+        <f>IF(COUNTA(B278:X278)=0,"",AVERAGE(B278:X278))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="279" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A279" s="2"/>
       <c r="B279" s="3"/>
       <c r="C279" s="3"/>
@@ -16915,13 +16621,12 @@
       <c r="V279" s="3"/>
       <c r="W279" s="3"/>
       <c r="X279" s="3"/>
-      <c r="Y279" s="3"/>
-      <c r="Z279" s="4" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="280" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y279" s="4" t="str">
+        <f>IF(COUNTA(B279:X279)=0,"",AVERAGE(B279:X279))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="280" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A280" s="2"/>
       <c r="B280" s="3"/>
       <c r="C280" s="3"/>
@@ -16946,13 +16651,12 @@
       <c r="V280" s="3"/>
       <c r="W280" s="3"/>
       <c r="X280" s="3"/>
-      <c r="Y280" s="3"/>
-      <c r="Z280" s="4" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="281" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y280" s="4" t="str">
+        <f>IF(COUNTA(B280:X280)=0,"",AVERAGE(B280:X280))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="281" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A281" s="2"/>
       <c r="B281" s="3"/>
       <c r="C281" s="3"/>
@@ -16977,13 +16681,12 @@
       <c r="V281" s="3"/>
       <c r="W281" s="3"/>
       <c r="X281" s="3"/>
-      <c r="Y281" s="3"/>
-      <c r="Z281" s="4" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="282" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y281" s="4" t="str">
+        <f>IF(COUNTA(B281:X281)=0,"",AVERAGE(B281:X281))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="282" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A282" s="2"/>
       <c r="B282" s="3"/>
       <c r="C282" s="3"/>
@@ -17008,13 +16711,12 @@
       <c r="V282" s="3"/>
       <c r="W282" s="3"/>
       <c r="X282" s="3"/>
-      <c r="Y282" s="3"/>
-      <c r="Z282" s="4" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="283" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y282" s="4" t="str">
+        <f>IF(COUNTA(B282:X282)=0,"",AVERAGE(B282:X282))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="283" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A283" s="2"/>
       <c r="B283" s="3"/>
       <c r="C283" s="3"/>
@@ -17039,13 +16741,12 @@
       <c r="V283" s="3"/>
       <c r="W283" s="3"/>
       <c r="X283" s="3"/>
-      <c r="Y283" s="3"/>
-      <c r="Z283" s="4" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="284" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y283" s="4" t="str">
+        <f>IF(COUNTA(B283:X283)=0,"",AVERAGE(B283:X283))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="284" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A284" s="2"/>
       <c r="B284" s="3"/>
       <c r="C284" s="3"/>
@@ -17070,13 +16771,12 @@
       <c r="V284" s="3"/>
       <c r="W284" s="3"/>
       <c r="X284" s="3"/>
-      <c r="Y284" s="3"/>
-      <c r="Z284" s="4" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="285" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y284" s="4" t="str">
+        <f>IF(COUNTA(B284:X284)=0,"",AVERAGE(B284:X284))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="285" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A285" s="2"/>
       <c r="B285" s="3"/>
       <c r="C285" s="3"/>
@@ -17101,13 +16801,12 @@
       <c r="V285" s="3"/>
       <c r="W285" s="3"/>
       <c r="X285" s="3"/>
-      <c r="Y285" s="3"/>
-      <c r="Z285" s="4" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="286" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y285" s="4" t="str">
+        <f>IF(COUNTA(B285:X285)=0,"",AVERAGE(B285:X285))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="286" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A286" s="2"/>
       <c r="B286" s="3"/>
       <c r="C286" s="3"/>
@@ -17132,13 +16831,12 @@
       <c r="V286" s="3"/>
       <c r="W286" s="3"/>
       <c r="X286" s="3"/>
-      <c r="Y286" s="3"/>
-      <c r="Z286" s="4" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="287" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y286" s="4" t="str">
+        <f>IF(COUNTA(B286:X286)=0,"",AVERAGE(B286:X286))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="287" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A287" s="2"/>
       <c r="B287" s="3"/>
       <c r="C287" s="3"/>
@@ -17163,13 +16861,12 @@
       <c r="V287" s="3"/>
       <c r="W287" s="3"/>
       <c r="X287" s="3"/>
-      <c r="Y287" s="3"/>
-      <c r="Z287" s="4" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="288" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y287" s="4" t="str">
+        <f>IF(COUNTA(B287:X287)=0,"",AVERAGE(B287:X287))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="288" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A288" s="2"/>
       <c r="B288" s="3"/>
       <c r="C288" s="3"/>
@@ -17194,13 +16891,12 @@
       <c r="V288" s="3"/>
       <c r="W288" s="3"/>
       <c r="X288" s="3"/>
-      <c r="Y288" s="3"/>
-      <c r="Z288" s="4" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="289" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y288" s="4" t="str">
+        <f>IF(COUNTA(B288:X288)=0,"",AVERAGE(B288:X288))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="289" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A289" s="2"/>
       <c r="B289" s="3"/>
       <c r="C289" s="3"/>
@@ -17225,13 +16921,12 @@
       <c r="V289" s="3"/>
       <c r="W289" s="3"/>
       <c r="X289" s="3"/>
-      <c r="Y289" s="3"/>
-      <c r="Z289" s="4" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="290" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y289" s="4" t="str">
+        <f>IF(COUNTA(B289:X289)=0,"",AVERAGE(B289:X289))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="290" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A290" s="2"/>
       <c r="B290" s="3"/>
       <c r="C290" s="3"/>
@@ -17256,13 +16951,12 @@
       <c r="V290" s="3"/>
       <c r="W290" s="3"/>
       <c r="X290" s="3"/>
-      <c r="Y290" s="3"/>
-      <c r="Z290" s="4" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="291" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y290" s="4" t="str">
+        <f>IF(COUNTA(B290:X290)=0,"",AVERAGE(B290:X290))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="291" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A291" s="2"/>
       <c r="B291" s="3"/>
       <c r="C291" s="3"/>
@@ -17287,13 +16981,12 @@
       <c r="V291" s="3"/>
       <c r="W291" s="3"/>
       <c r="X291" s="3"/>
-      <c r="Y291" s="3"/>
-      <c r="Z291" s="4" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="292" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y291" s="4" t="str">
+        <f>IF(COUNTA(B291:X291)=0,"",AVERAGE(B291:X291))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="292" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A292" s="2"/>
       <c r="B292" s="3"/>
       <c r="C292" s="3"/>
@@ -17318,13 +17011,12 @@
       <c r="V292" s="3"/>
       <c r="W292" s="3"/>
       <c r="X292" s="3"/>
-      <c r="Y292" s="3"/>
-      <c r="Z292" s="4" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="293" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y292" s="4" t="str">
+        <f>IF(COUNTA(B292:X292)=0,"",AVERAGE(B292:X292))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="293" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A293" s="2"/>
       <c r="B293" s="3"/>
       <c r="C293" s="3"/>
@@ -17349,13 +17041,12 @@
       <c r="V293" s="3"/>
       <c r="W293" s="3"/>
       <c r="X293" s="3"/>
-      <c r="Y293" s="3"/>
-      <c r="Z293" s="4" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="294" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y293" s="4" t="str">
+        <f>IF(COUNTA(B293:X293)=0,"",AVERAGE(B293:X293))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="294" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A294" s="2"/>
       <c r="B294" s="3"/>
       <c r="C294" s="3"/>
@@ -17380,13 +17071,12 @@
       <c r="V294" s="3"/>
       <c r="W294" s="3"/>
       <c r="X294" s="3"/>
-      <c r="Y294" s="3"/>
-      <c r="Z294" s="4" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="295" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y294" s="4" t="str">
+        <f>IF(COUNTA(B294:X294)=0,"",AVERAGE(B294:X294))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="295" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A295" s="2"/>
       <c r="B295" s="3"/>
       <c r="C295" s="3"/>
@@ -17411,13 +17101,12 @@
       <c r="V295" s="3"/>
       <c r="W295" s="3"/>
       <c r="X295" s="3"/>
-      <c r="Y295" s="3"/>
-      <c r="Z295" s="4" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="296" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y295" s="4" t="str">
+        <f>IF(COUNTA(B295:X295)=0,"",AVERAGE(B295:X295))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="296" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A296" s="2"/>
       <c r="B296" s="3"/>
       <c r="C296" s="3"/>
@@ -17442,13 +17131,12 @@
       <c r="V296" s="3"/>
       <c r="W296" s="3"/>
       <c r="X296" s="3"/>
-      <c r="Y296" s="3"/>
-      <c r="Z296" s="4" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="297" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y296" s="4" t="str">
+        <f>IF(COUNTA(B296:X296)=0,"",AVERAGE(B296:X296))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="297" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A297" s="2"/>
       <c r="B297" s="3"/>
       <c r="C297" s="3"/>
@@ -17473,13 +17161,12 @@
       <c r="V297" s="3"/>
       <c r="W297" s="3"/>
       <c r="X297" s="3"/>
-      <c r="Y297" s="3"/>
-      <c r="Z297" s="4" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="298" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y297" s="4" t="str">
+        <f>IF(COUNTA(B297:X297)=0,"",AVERAGE(B297:X297))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="298" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A298" s="2"/>
       <c r="B298" s="3"/>
       <c r="C298" s="3"/>
@@ -17504,13 +17191,12 @@
       <c r="V298" s="3"/>
       <c r="W298" s="3"/>
       <c r="X298" s="3"/>
-      <c r="Y298" s="3"/>
-      <c r="Z298" s="4" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="299" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y298" s="4" t="str">
+        <f>IF(COUNTA(B298:X298)=0,"",AVERAGE(B298:X298))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="299" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A299" s="2"/>
       <c r="B299" s="3"/>
       <c r="C299" s="3"/>
@@ -17535,13 +17221,12 @@
       <c r="V299" s="3"/>
       <c r="W299" s="3"/>
       <c r="X299" s="3"/>
-      <c r="Y299" s="3"/>
-      <c r="Z299" s="4" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="300" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y299" s="4" t="str">
+        <f>IF(COUNTA(B299:X299)=0,"",AVERAGE(B299:X299))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="300" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A300" s="2"/>
       <c r="B300" s="3"/>
       <c r="C300" s="3"/>
@@ -17566,13 +17251,12 @@
       <c r="V300" s="3"/>
       <c r="W300" s="3"/>
       <c r="X300" s="3"/>
-      <c r="Y300" s="3"/>
-      <c r="Z300" s="4" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="301" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y300" s="4" t="str">
+        <f>IF(COUNTA(B300:X300)=0,"",AVERAGE(B300:X300))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="301" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A301" s="2"/>
       <c r="B301" s="3"/>
       <c r="C301" s="3"/>
@@ -17597,13 +17281,12 @@
       <c r="V301" s="3"/>
       <c r="W301" s="3"/>
       <c r="X301" s="3"/>
-      <c r="Y301" s="3"/>
-      <c r="Z301" s="4" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="302" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y301" s="4" t="str">
+        <f>IF(COUNTA(B301:X301)=0,"",AVERAGE(B301:X301))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="302" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A302" s="2"/>
       <c r="B302" s="3"/>
       <c r="C302" s="3"/>
@@ -17628,13 +17311,12 @@
       <c r="V302" s="3"/>
       <c r="W302" s="3"/>
       <c r="X302" s="3"/>
-      <c r="Y302" s="3"/>
-      <c r="Z302" s="4" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="303" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y302" s="4" t="str">
+        <f>IF(COUNTA(B302:X302)=0,"",AVERAGE(B302:X302))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="303" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A303" s="2"/>
       <c r="B303" s="3"/>
       <c r="C303" s="3"/>
@@ -17659,13 +17341,12 @@
       <c r="V303" s="3"/>
       <c r="W303" s="3"/>
       <c r="X303" s="3"/>
-      <c r="Y303" s="3"/>
-      <c r="Z303" s="4" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="304" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y303" s="4" t="str">
+        <f>IF(COUNTA(B303:X303)=0,"",AVERAGE(B303:X303))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="304" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A304" s="2"/>
       <c r="B304" s="3"/>
       <c r="C304" s="3"/>
@@ -17690,13 +17371,12 @@
       <c r="V304" s="3"/>
       <c r="W304" s="3"/>
       <c r="X304" s="3"/>
-      <c r="Y304" s="3"/>
-      <c r="Z304" s="4" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="305" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y304" s="4" t="str">
+        <f>IF(COUNTA(B304:X304)=0,"",AVERAGE(B304:X304))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="305" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A305" s="2"/>
       <c r="B305" s="3"/>
       <c r="C305" s="3"/>
@@ -17721,13 +17401,12 @@
       <c r="V305" s="3"/>
       <c r="W305" s="3"/>
       <c r="X305" s="3"/>
-      <c r="Y305" s="3"/>
-      <c r="Z305" s="4" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="306" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y305" s="4" t="str">
+        <f>IF(COUNTA(B305:X305)=0,"",AVERAGE(B305:X305))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="306" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A306" s="2"/>
       <c r="B306" s="3"/>
       <c r="C306" s="3"/>
@@ -17752,13 +17431,12 @@
       <c r="V306" s="3"/>
       <c r="W306" s="3"/>
       <c r="X306" s="3"/>
-      <c r="Y306" s="3"/>
-      <c r="Z306" s="4" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="307" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y306" s="4" t="str">
+        <f>IF(COUNTA(B306:X306)=0,"",AVERAGE(B306:X306))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="307" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A307" s="2"/>
       <c r="B307" s="3"/>
       <c r="C307" s="3"/>
@@ -17783,13 +17461,12 @@
       <c r="V307" s="3"/>
       <c r="W307" s="3"/>
       <c r="X307" s="3"/>
-      <c r="Y307" s="3"/>
-      <c r="Z307" s="4" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="308" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y307" s="4" t="str">
+        <f>IF(COUNTA(B307:X307)=0,"",AVERAGE(B307:X307))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="308" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A308" s="2"/>
       <c r="B308" s="3"/>
       <c r="C308" s="3"/>
@@ -17814,13 +17491,12 @@
       <c r="V308" s="3"/>
       <c r="W308" s="3"/>
       <c r="X308" s="3"/>
-      <c r="Y308" s="3"/>
-      <c r="Z308" s="4" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="309" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y308" s="4" t="str">
+        <f>IF(COUNTA(B308:X308)=0,"",AVERAGE(B308:X308))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="309" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A309" s="2"/>
       <c r="B309" s="3"/>
       <c r="C309" s="3"/>
@@ -17845,13 +17521,12 @@
       <c r="V309" s="3"/>
       <c r="W309" s="3"/>
       <c r="X309" s="3"/>
-      <c r="Y309" s="3"/>
-      <c r="Z309" s="4" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="310" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y309" s="4" t="str">
+        <f>IF(COUNTA(B309:X309)=0,"",AVERAGE(B309:X309))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="310" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A310" s="2"/>
       <c r="B310" s="3"/>
       <c r="C310" s="3"/>
@@ -17876,13 +17551,12 @@
       <c r="V310" s="3"/>
       <c r="W310" s="3"/>
       <c r="X310" s="3"/>
-      <c r="Y310" s="3"/>
-      <c r="Z310" s="4" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="311" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y310" s="4" t="str">
+        <f>IF(COUNTA(B310:X310)=0,"",AVERAGE(B310:X310))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="311" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A311" s="2"/>
       <c r="B311" s="3"/>
       <c r="C311" s="3"/>
@@ -17907,13 +17581,12 @@
       <c r="V311" s="3"/>
       <c r="W311" s="3"/>
       <c r="X311" s="3"/>
-      <c r="Y311" s="3"/>
-      <c r="Z311" s="4" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="312" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y311" s="4" t="str">
+        <f>IF(COUNTA(B311:X311)=0,"",AVERAGE(B311:X311))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="312" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A312" s="2"/>
       <c r="B312" s="3"/>
       <c r="C312" s="3"/>
@@ -17938,13 +17611,12 @@
       <c r="V312" s="3"/>
       <c r="W312" s="3"/>
       <c r="X312" s="3"/>
-      <c r="Y312" s="3"/>
-      <c r="Z312" s="4" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="313" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y312" s="4" t="str">
+        <f>IF(COUNTA(B312:X312)=0,"",AVERAGE(B312:X312))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="313" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A313" s="2"/>
       <c r="B313" s="3"/>
       <c r="C313" s="3"/>
@@ -17969,13 +17641,12 @@
       <c r="V313" s="3"/>
       <c r="W313" s="3"/>
       <c r="X313" s="3"/>
-      <c r="Y313" s="3"/>
-      <c r="Z313" s="4" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="314" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y313" s="4" t="str">
+        <f>IF(COUNTA(B313:X313)=0,"",AVERAGE(B313:X313))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="314" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A314" s="2"/>
       <c r="B314" s="3"/>
       <c r="C314" s="3"/>
@@ -18000,13 +17671,12 @@
       <c r="V314" s="3"/>
       <c r="W314" s="3"/>
       <c r="X314" s="3"/>
-      <c r="Y314" s="3"/>
-      <c r="Z314" s="4" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="315" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y314" s="4" t="str">
+        <f>IF(COUNTA(B314:X314)=0,"",AVERAGE(B314:X314))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="315" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A315" s="2"/>
       <c r="B315" s="3"/>
       <c r="C315" s="3"/>
@@ -18031,13 +17701,12 @@
       <c r="V315" s="3"/>
       <c r="W315" s="3"/>
       <c r="X315" s="3"/>
-      <c r="Y315" s="3"/>
-      <c r="Z315" s="4" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="316" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y315" s="4" t="str">
+        <f>IF(COUNTA(B315:X315)=0,"",AVERAGE(B315:X315))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="316" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A316" s="2"/>
       <c r="B316" s="3"/>
       <c r="C316" s="3"/>
@@ -18062,13 +17731,12 @@
       <c r="V316" s="3"/>
       <c r="W316" s="3"/>
       <c r="X316" s="3"/>
-      <c r="Y316" s="3"/>
-      <c r="Z316" s="4" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="317" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y316" s="4" t="str">
+        <f>IF(COUNTA(B316:X316)=0,"",AVERAGE(B316:X316))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="317" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A317" s="2"/>
       <c r="B317" s="3"/>
       <c r="C317" s="3"/>
@@ -18093,13 +17761,12 @@
       <c r="V317" s="3"/>
       <c r="W317" s="3"/>
       <c r="X317" s="3"/>
-      <c r="Y317" s="3"/>
-      <c r="Z317" s="4" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="318" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y317" s="4" t="str">
+        <f>IF(COUNTA(B317:X317)=0,"",AVERAGE(B317:X317))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="318" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A318" s="2"/>
       <c r="B318" s="3"/>
       <c r="C318" s="3"/>
@@ -18124,13 +17791,12 @@
       <c r="V318" s="3"/>
       <c r="W318" s="3"/>
       <c r="X318" s="3"/>
-      <c r="Y318" s="3"/>
-      <c r="Z318" s="4" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="319" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y318" s="4" t="str">
+        <f>IF(COUNTA(B318:X318)=0,"",AVERAGE(B318:X318))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="319" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A319" s="2"/>
       <c r="B319" s="3"/>
       <c r="C319" s="3"/>
@@ -18155,13 +17821,12 @@
       <c r="V319" s="3"/>
       <c r="W319" s="3"/>
       <c r="X319" s="3"/>
-      <c r="Y319" s="3"/>
-      <c r="Z319" s="4" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="320" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y319" s="4" t="str">
+        <f>IF(COUNTA(B319:X319)=0,"",AVERAGE(B319:X319))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="320" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A320" s="2"/>
       <c r="B320" s="3"/>
       <c r="C320" s="3"/>
@@ -18186,13 +17851,12 @@
       <c r="V320" s="3"/>
       <c r="W320" s="3"/>
       <c r="X320" s="3"/>
-      <c r="Y320" s="3"/>
-      <c r="Z320" s="4" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="321" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y320" s="4" t="str">
+        <f>IF(COUNTA(B320:X320)=0,"",AVERAGE(B320:X320))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="321" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A321" s="2"/>
       <c r="B321" s="3"/>
       <c r="C321" s="3"/>
@@ -18217,13 +17881,12 @@
       <c r="V321" s="3"/>
       <c r="W321" s="3"/>
       <c r="X321" s="3"/>
-      <c r="Y321" s="3"/>
-      <c r="Z321" s="4" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="322" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y321" s="4" t="str">
+        <f>IF(COUNTA(B321:X321)=0,"",AVERAGE(B321:X321))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="322" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A322" s="2"/>
       <c r="B322" s="3"/>
       <c r="C322" s="3"/>
@@ -18248,13 +17911,12 @@
       <c r="V322" s="3"/>
       <c r="W322" s="3"/>
       <c r="X322" s="3"/>
-      <c r="Y322" s="3"/>
-      <c r="Z322" s="4" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="323" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y322" s="4" t="str">
+        <f>IF(COUNTA(B322:X322)=0,"",AVERAGE(B322:X322))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="323" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A323" s="2"/>
       <c r="B323" s="3"/>
       <c r="C323" s="3"/>
@@ -18279,13 +17941,12 @@
       <c r="V323" s="3"/>
       <c r="W323" s="3"/>
       <c r="X323" s="3"/>
-      <c r="Y323" s="3"/>
-      <c r="Z323" s="4" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="324" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y323" s="4" t="str">
+        <f>IF(COUNTA(B323:X323)=0,"",AVERAGE(B323:X323))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="324" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A324" s="2"/>
       <c r="B324" s="3"/>
       <c r="C324" s="3"/>
@@ -18310,13 +17971,12 @@
       <c r="V324" s="3"/>
       <c r="W324" s="3"/>
       <c r="X324" s="3"/>
-      <c r="Y324" s="3"/>
-      <c r="Z324" s="4" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="325" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y324" s="4" t="str">
+        <f>IF(COUNTA(B324:X324)=0,"",AVERAGE(B324:X324))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="325" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A325" s="2"/>
       <c r="B325" s="3"/>
       <c r="C325" s="3"/>
@@ -18341,13 +18001,12 @@
       <c r="V325" s="3"/>
       <c r="W325" s="3"/>
       <c r="X325" s="3"/>
-      <c r="Y325" s="3"/>
-      <c r="Z325" s="4" t="str">
-        <f t="shared" ref="Z325:Z388" si="11">IF(COUNTA(B325:Y325)=0,"",AVERAGE(B325:Y325))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="326" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y325" s="4" t="str">
+        <f>IF(COUNTA(B325:X325)=0,"",AVERAGE(B325:X325))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="326" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A326" s="2"/>
       <c r="B326" s="3"/>
       <c r="C326" s="3"/>
@@ -18372,13 +18031,12 @@
       <c r="V326" s="3"/>
       <c r="W326" s="3"/>
       <c r="X326" s="3"/>
-      <c r="Y326" s="3"/>
-      <c r="Z326" s="4" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-    </row>
-    <row r="327" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y326" s="4" t="str">
+        <f>IF(COUNTA(B326:X326)=0,"",AVERAGE(B326:X326))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="327" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A327" s="2"/>
       <c r="B327" s="3"/>
       <c r="C327" s="3"/>
@@ -18403,13 +18061,12 @@
       <c r="V327" s="3"/>
       <c r="W327" s="3"/>
       <c r="X327" s="3"/>
-      <c r="Y327" s="3"/>
-      <c r="Z327" s="4" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-    </row>
-    <row r="328" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y327" s="4" t="str">
+        <f>IF(COUNTA(B327:X327)=0,"",AVERAGE(B327:X327))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="328" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A328" s="2"/>
       <c r="B328" s="3"/>
       <c r="C328" s="3"/>
@@ -18434,13 +18091,12 @@
       <c r="V328" s="3"/>
       <c r="W328" s="3"/>
       <c r="X328" s="3"/>
-      <c r="Y328" s="3"/>
-      <c r="Z328" s="4" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-    </row>
-    <row r="329" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y328" s="4" t="str">
+        <f>IF(COUNTA(B328:X328)=0,"",AVERAGE(B328:X328))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="329" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A329" s="2"/>
       <c r="B329" s="3"/>
       <c r="C329" s="3"/>
@@ -18465,13 +18121,12 @@
       <c r="V329" s="3"/>
       <c r="W329" s="3"/>
       <c r="X329" s="3"/>
-      <c r="Y329" s="3"/>
-      <c r="Z329" s="4" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-    </row>
-    <row r="330" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y329" s="4" t="str">
+        <f>IF(COUNTA(B329:X329)=0,"",AVERAGE(B329:X329))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="330" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A330" s="2"/>
       <c r="B330" s="3"/>
       <c r="C330" s="3"/>
@@ -18496,13 +18151,12 @@
       <c r="V330" s="3"/>
       <c r="W330" s="3"/>
       <c r="X330" s="3"/>
-      <c r="Y330" s="3"/>
-      <c r="Z330" s="4" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-    </row>
-    <row r="331" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y330" s="4" t="str">
+        <f>IF(COUNTA(B330:X330)=0,"",AVERAGE(B330:X330))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="331" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A331" s="2"/>
       <c r="B331" s="3"/>
       <c r="C331" s="3"/>
@@ -18527,13 +18181,12 @@
       <c r="V331" s="3"/>
       <c r="W331" s="3"/>
       <c r="X331" s="3"/>
-      <c r="Y331" s="3"/>
-      <c r="Z331" s="4" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-    </row>
-    <row r="332" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y331" s="4" t="str">
+        <f>IF(COUNTA(B331:X331)=0,"",AVERAGE(B331:X331))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="332" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A332" s="2"/>
       <c r="B332" s="3"/>
       <c r="C332" s="3"/>
@@ -18558,13 +18211,12 @@
       <c r="V332" s="3"/>
       <c r="W332" s="3"/>
       <c r="X332" s="3"/>
-      <c r="Y332" s="3"/>
-      <c r="Z332" s="4" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-    </row>
-    <row r="333" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y332" s="4" t="str">
+        <f>IF(COUNTA(B332:X332)=0,"",AVERAGE(B332:X332))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="333" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A333" s="2"/>
       <c r="B333" s="3"/>
       <c r="C333" s="3"/>
@@ -18589,13 +18241,12 @@
       <c r="V333" s="3"/>
       <c r="W333" s="3"/>
       <c r="X333" s="3"/>
-      <c r="Y333" s="3"/>
-      <c r="Z333" s="4" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-    </row>
-    <row r="334" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y333" s="4" t="str">
+        <f>IF(COUNTA(B333:X333)=0,"",AVERAGE(B333:X333))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="334" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A334" s="2"/>
       <c r="B334" s="3"/>
       <c r="C334" s="3"/>
@@ -18620,13 +18271,12 @@
       <c r="V334" s="3"/>
       <c r="W334" s="3"/>
       <c r="X334" s="3"/>
-      <c r="Y334" s="3"/>
-      <c r="Z334" s="4" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-    </row>
-    <row r="335" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y334" s="4" t="str">
+        <f>IF(COUNTA(B334:X334)=0,"",AVERAGE(B334:X334))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="335" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A335" s="2"/>
       <c r="B335" s="3"/>
       <c r="C335" s="3"/>
@@ -18651,13 +18301,12 @@
       <c r="V335" s="3"/>
       <c r="W335" s="3"/>
       <c r="X335" s="3"/>
-      <c r="Y335" s="3"/>
-      <c r="Z335" s="4" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-    </row>
-    <row r="336" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y335" s="4" t="str">
+        <f>IF(COUNTA(B335:X335)=0,"",AVERAGE(B335:X335))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="336" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A336" s="2"/>
       <c r="B336" s="3"/>
       <c r="C336" s="3"/>
@@ -18682,13 +18331,12 @@
       <c r="V336" s="3"/>
       <c r="W336" s="3"/>
       <c r="X336" s="3"/>
-      <c r="Y336" s="3"/>
-      <c r="Z336" s="4" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-    </row>
-    <row r="337" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y336" s="4" t="str">
+        <f>IF(COUNTA(B336:X336)=0,"",AVERAGE(B336:X336))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="337" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A337" s="2"/>
       <c r="B337" s="3"/>
       <c r="C337" s="3"/>
@@ -18713,13 +18361,12 @@
       <c r="V337" s="3"/>
       <c r="W337" s="3"/>
       <c r="X337" s="3"/>
-      <c r="Y337" s="3"/>
-      <c r="Z337" s="4" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-    </row>
-    <row r="338" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y337" s="4" t="str">
+        <f>IF(COUNTA(B337:X337)=0,"",AVERAGE(B337:X337))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="338" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A338" s="2"/>
       <c r="B338" s="3"/>
       <c r="C338" s="3"/>
@@ -18744,13 +18391,12 @@
       <c r="V338" s="3"/>
       <c r="W338" s="3"/>
       <c r="X338" s="3"/>
-      <c r="Y338" s="3"/>
-      <c r="Z338" s="4" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-    </row>
-    <row r="339" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y338" s="4" t="str">
+        <f>IF(COUNTA(B338:X338)=0,"",AVERAGE(B338:X338))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="339" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A339" s="2"/>
       <c r="B339" s="3"/>
       <c r="C339" s="3"/>
@@ -18775,13 +18421,12 @@
       <c r="V339" s="3"/>
       <c r="W339" s="3"/>
       <c r="X339" s="3"/>
-      <c r="Y339" s="3"/>
-      <c r="Z339" s="4" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-    </row>
-    <row r="340" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y339" s="4" t="str">
+        <f>IF(COUNTA(B339:X339)=0,"",AVERAGE(B339:X339))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="340" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A340" s="2"/>
       <c r="B340" s="3"/>
       <c r="C340" s="3"/>
@@ -18806,13 +18451,12 @@
       <c r="V340" s="3"/>
       <c r="W340" s="3"/>
       <c r="X340" s="3"/>
-      <c r="Y340" s="3"/>
-      <c r="Z340" s="4" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-    </row>
-    <row r="341" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y340" s="4" t="str">
+        <f>IF(COUNTA(B340:X340)=0,"",AVERAGE(B340:X340))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="341" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A341" s="2"/>
       <c r="B341" s="3"/>
       <c r="C341" s="3"/>
@@ -18837,13 +18481,12 @@
       <c r="V341" s="3"/>
       <c r="W341" s="3"/>
       <c r="X341" s="3"/>
-      <c r="Y341" s="3"/>
-      <c r="Z341" s="4" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-    </row>
-    <row r="342" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y341" s="4" t="str">
+        <f>IF(COUNTA(B341:X341)=0,"",AVERAGE(B341:X341))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="342" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A342" s="2"/>
       <c r="B342" s="3"/>
       <c r="C342" s="3"/>
@@ -18868,13 +18511,12 @@
       <c r="V342" s="3"/>
       <c r="W342" s="3"/>
       <c r="X342" s="3"/>
-      <c r="Y342" s="3"/>
-      <c r="Z342" s="4" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-    </row>
-    <row r="343" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y342" s="4" t="str">
+        <f>IF(COUNTA(B342:X342)=0,"",AVERAGE(B342:X342))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="343" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A343" s="2"/>
       <c r="B343" s="3"/>
       <c r="C343" s="3"/>
@@ -18899,13 +18541,12 @@
       <c r="V343" s="3"/>
       <c r="W343" s="3"/>
       <c r="X343" s="3"/>
-      <c r="Y343" s="3"/>
-      <c r="Z343" s="4" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-    </row>
-    <row r="344" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y343" s="4" t="str">
+        <f>IF(COUNTA(B343:X343)=0,"",AVERAGE(B343:X343))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="344" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A344" s="2"/>
       <c r="B344" s="3"/>
       <c r="C344" s="3"/>
@@ -18930,13 +18571,12 @@
       <c r="V344" s="3"/>
       <c r="W344" s="3"/>
       <c r="X344" s="3"/>
-      <c r="Y344" s="3"/>
-      <c r="Z344" s="4" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-    </row>
-    <row r="345" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y344" s="4" t="str">
+        <f>IF(COUNTA(B344:X344)=0,"",AVERAGE(B344:X344))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="345" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A345" s="2"/>
       <c r="B345" s="3"/>
       <c r="C345" s="3"/>
@@ -18961,13 +18601,12 @@
       <c r="V345" s="3"/>
       <c r="W345" s="3"/>
       <c r="X345" s="3"/>
-      <c r="Y345" s="3"/>
-      <c r="Z345" s="4" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-    </row>
-    <row r="346" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y345" s="4" t="str">
+        <f>IF(COUNTA(B345:X345)=0,"",AVERAGE(B345:X345))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="346" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A346" s="2"/>
       <c r="B346" s="3"/>
       <c r="C346" s="3"/>
@@ -18992,13 +18631,12 @@
       <c r="V346" s="3"/>
       <c r="W346" s="3"/>
       <c r="X346" s="3"/>
-      <c r="Y346" s="3"/>
-      <c r="Z346" s="4" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-    </row>
-    <row r="347" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y346" s="4" t="str">
+        <f>IF(COUNTA(B346:X346)=0,"",AVERAGE(B346:X346))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="347" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A347" s="2"/>
       <c r="B347" s="3"/>
       <c r="C347" s="3"/>
@@ -19023,13 +18661,12 @@
       <c r="V347" s="3"/>
       <c r="W347" s="3"/>
       <c r="X347" s="3"/>
-      <c r="Y347" s="3"/>
-      <c r="Z347" s="4" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-    </row>
-    <row r="348" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y347" s="4" t="str">
+        <f>IF(COUNTA(B347:X347)=0,"",AVERAGE(B347:X347))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="348" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A348" s="2"/>
       <c r="B348" s="3"/>
       <c r="C348" s="3"/>
@@ -19054,13 +18691,12 @@
       <c r="V348" s="3"/>
       <c r="W348" s="3"/>
       <c r="X348" s="3"/>
-      <c r="Y348" s="3"/>
-      <c r="Z348" s="4" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-    </row>
-    <row r="349" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y348" s="4" t="str">
+        <f>IF(COUNTA(B348:X348)=0,"",AVERAGE(B348:X348))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="349" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A349" s="2"/>
       <c r="B349" s="3"/>
       <c r="C349" s="3"/>
@@ -19085,13 +18721,12 @@
       <c r="V349" s="3"/>
       <c r="W349" s="3"/>
       <c r="X349" s="3"/>
-      <c r="Y349" s="3"/>
-      <c r="Z349" s="4" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-    </row>
-    <row r="350" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y349" s="4" t="str">
+        <f>IF(COUNTA(B349:X349)=0,"",AVERAGE(B349:X349))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="350" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A350" s="2"/>
       <c r="B350" s="3"/>
       <c r="C350" s="3"/>
@@ -19116,13 +18751,12 @@
       <c r="V350" s="3"/>
       <c r="W350" s="3"/>
       <c r="X350" s="3"/>
-      <c r="Y350" s="3"/>
-      <c r="Z350" s="4" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-    </row>
-    <row r="351" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y350" s="4" t="str">
+        <f>IF(COUNTA(B350:X350)=0,"",AVERAGE(B350:X350))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="351" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A351" s="2"/>
       <c r="B351" s="3"/>
       <c r="C351" s="3"/>
@@ -19147,13 +18781,12 @@
       <c r="V351" s="3"/>
       <c r="W351" s="3"/>
       <c r="X351" s="3"/>
-      <c r="Y351" s="3"/>
-      <c r="Z351" s="4" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-    </row>
-    <row r="352" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y351" s="4" t="str">
+        <f>IF(COUNTA(B351:X351)=0,"",AVERAGE(B351:X351))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="352" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A352" s="2"/>
       <c r="B352" s="3"/>
       <c r="C352" s="3"/>
@@ -19178,13 +18811,12 @@
       <c r="V352" s="3"/>
       <c r="W352" s="3"/>
       <c r="X352" s="3"/>
-      <c r="Y352" s="3"/>
-      <c r="Z352" s="4" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-    </row>
-    <row r="353" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y352" s="4" t="str">
+        <f>IF(COUNTA(B352:X352)=0,"",AVERAGE(B352:X352))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="353" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A353" s="2"/>
       <c r="B353" s="3"/>
       <c r="C353" s="3"/>
@@ -19209,13 +18841,12 @@
       <c r="V353" s="3"/>
       <c r="W353" s="3"/>
       <c r="X353" s="3"/>
-      <c r="Y353" s="3"/>
-      <c r="Z353" s="4" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-    </row>
-    <row r="354" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y353" s="4" t="str">
+        <f>IF(COUNTA(B353:X353)=0,"",AVERAGE(B353:X353))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="354" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A354" s="2"/>
       <c r="B354" s="3"/>
       <c r="C354" s="3"/>
@@ -19240,13 +18871,12 @@
       <c r="V354" s="3"/>
       <c r="W354" s="3"/>
       <c r="X354" s="3"/>
-      <c r="Y354" s="3"/>
-      <c r="Z354" s="4" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-    </row>
-    <row r="355" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y354" s="4" t="str">
+        <f>IF(COUNTA(B354:X354)=0,"",AVERAGE(B354:X354))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="355" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A355" s="2"/>
       <c r="B355" s="3"/>
       <c r="C355" s="3"/>
@@ -19271,13 +18901,12 @@
       <c r="V355" s="3"/>
       <c r="W355" s="3"/>
       <c r="X355" s="3"/>
-      <c r="Y355" s="3"/>
-      <c r="Z355" s="4" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-    </row>
-    <row r="356" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y355" s="4" t="str">
+        <f>IF(COUNTA(B355:X355)=0,"",AVERAGE(B355:X355))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="356" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A356" s="2"/>
       <c r="B356" s="3"/>
       <c r="C356" s="3"/>
@@ -19302,13 +18931,12 @@
       <c r="V356" s="3"/>
       <c r="W356" s="3"/>
       <c r="X356" s="3"/>
-      <c r="Y356" s="3"/>
-      <c r="Z356" s="4" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-    </row>
-    <row r="357" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y356" s="4" t="str">
+        <f>IF(COUNTA(B356:X356)=0,"",AVERAGE(B356:X356))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="357" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A357" s="2"/>
       <c r="B357" s="3"/>
       <c r="C357" s="3"/>
@@ -19333,13 +18961,12 @@
       <c r="V357" s="3"/>
       <c r="W357" s="3"/>
       <c r="X357" s="3"/>
-      <c r="Y357" s="3"/>
-      <c r="Z357" s="4" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-    </row>
-    <row r="358" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y357" s="4" t="str">
+        <f>IF(COUNTA(B357:X357)=0,"",AVERAGE(B357:X357))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="358" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A358" s="2"/>
       <c r="B358" s="3"/>
       <c r="C358" s="3"/>
@@ -19364,13 +18991,12 @@
       <c r="V358" s="3"/>
       <c r="W358" s="3"/>
       <c r="X358" s="3"/>
-      <c r="Y358" s="3"/>
-      <c r="Z358" s="4" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-    </row>
-    <row r="359" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y358" s="4" t="str">
+        <f>IF(COUNTA(B358:X358)=0,"",AVERAGE(B358:X358))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="359" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A359" s="2"/>
       <c r="B359" s="3"/>
       <c r="C359" s="3"/>
@@ -19395,13 +19021,12 @@
       <c r="V359" s="3"/>
       <c r="W359" s="3"/>
       <c r="X359" s="3"/>
-      <c r="Y359" s="3"/>
-      <c r="Z359" s="4" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-    </row>
-    <row r="360" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y359" s="4" t="str">
+        <f>IF(COUNTA(B359:X359)=0,"",AVERAGE(B359:X359))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="360" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A360" s="2"/>
       <c r="B360" s="3"/>
       <c r="C360" s="3"/>
@@ -19426,13 +19051,12 @@
       <c r="V360" s="3"/>
       <c r="W360" s="3"/>
       <c r="X360" s="3"/>
-      <c r="Y360" s="3"/>
-      <c r="Z360" s="4" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-    </row>
-    <row r="361" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y360" s="4" t="str">
+        <f>IF(COUNTA(B360:X360)=0,"",AVERAGE(B360:X360))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="361" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A361" s="2"/>
       <c r="B361" s="3"/>
       <c r="C361" s="3"/>
@@ -19457,13 +19081,12 @@
       <c r="V361" s="3"/>
       <c r="W361" s="3"/>
       <c r="X361" s="3"/>
-      <c r="Y361" s="3"/>
-      <c r="Z361" s="4" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-    </row>
-    <row r="362" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y361" s="4" t="str">
+        <f>IF(COUNTA(B361:X361)=0,"",AVERAGE(B361:X361))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="362" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A362" s="2"/>
       <c r="B362" s="3"/>
       <c r="C362" s="3"/>
@@ -19488,13 +19111,12 @@
       <c r="V362" s="3"/>
       <c r="W362" s="3"/>
       <c r="X362" s="3"/>
-      <c r="Y362" s="3"/>
-      <c r="Z362" s="4" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-    </row>
-    <row r="363" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y362" s="4" t="str">
+        <f>IF(COUNTA(B362:X362)=0,"",AVERAGE(B362:X362))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="363" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A363" s="2"/>
       <c r="B363" s="3"/>
       <c r="C363" s="3"/>
@@ -19519,13 +19141,12 @@
       <c r="V363" s="3"/>
       <c r="W363" s="3"/>
       <c r="X363" s="3"/>
-      <c r="Y363" s="3"/>
-      <c r="Z363" s="4" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-    </row>
-    <row r="364" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y363" s="4" t="str">
+        <f>IF(COUNTA(B363:X363)=0,"",AVERAGE(B363:X363))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="364" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A364" s="2"/>
       <c r="B364" s="3"/>
       <c r="C364" s="3"/>
@@ -19550,13 +19171,12 @@
       <c r="V364" s="3"/>
       <c r="W364" s="3"/>
       <c r="X364" s="3"/>
-      <c r="Y364" s="3"/>
-      <c r="Z364" s="4" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-    </row>
-    <row r="365" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y364" s="4" t="str">
+        <f>IF(COUNTA(B364:X364)=0,"",AVERAGE(B364:X364))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="365" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A365" s="2"/>
       <c r="B365" s="3"/>
       <c r="C365" s="3"/>
@@ -19581,13 +19201,12 @@
       <c r="V365" s="3"/>
       <c r="W365" s="3"/>
       <c r="X365" s="3"/>
-      <c r="Y365" s="3"/>
-      <c r="Z365" s="4" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-    </row>
-    <row r="366" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y365" s="4" t="str">
+        <f>IF(COUNTA(B365:X365)=0,"",AVERAGE(B365:X365))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="366" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A366" s="2"/>
       <c r="B366" s="3"/>
       <c r="C366" s="3"/>
@@ -19612,13 +19231,12 @@
       <c r="V366" s="3"/>
       <c r="W366" s="3"/>
       <c r="X366" s="3"/>
-      <c r="Y366" s="3"/>
-      <c r="Z366" s="4" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-    </row>
-    <row r="367" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y366" s="4" t="str">
+        <f>IF(COUNTA(B366:X366)=0,"",AVERAGE(B366:X366))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="367" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A367" s="2"/>
       <c r="B367" s="3"/>
       <c r="C367" s="3"/>
@@ -19643,13 +19261,12 @@
       <c r="V367" s="3"/>
       <c r="W367" s="3"/>
       <c r="X367" s="3"/>
-      <c r="Y367" s="3"/>
-      <c r="Z367" s="4" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-    </row>
-    <row r="368" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y367" s="4" t="str">
+        <f>IF(COUNTA(B367:X367)=0,"",AVERAGE(B367:X367))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="368" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A368" s="2"/>
       <c r="B368" s="3"/>
       <c r="C368" s="3"/>
@@ -19674,13 +19291,12 @@
       <c r="V368" s="3"/>
       <c r="W368" s="3"/>
       <c r="X368" s="3"/>
-      <c r="Y368" s="3"/>
-      <c r="Z368" s="4" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-    </row>
-    <row r="369" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y368" s="4" t="str">
+        <f>IF(COUNTA(B368:X368)=0,"",AVERAGE(B368:X368))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="369" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A369" s="2"/>
       <c r="B369" s="3"/>
       <c r="C369" s="3"/>
@@ -19705,13 +19321,12 @@
       <c r="V369" s="3"/>
       <c r="W369" s="3"/>
       <c r="X369" s="3"/>
-      <c r="Y369" s="3"/>
-      <c r="Z369" s="4" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-    </row>
-    <row r="370" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y369" s="4" t="str">
+        <f>IF(COUNTA(B369:X369)=0,"",AVERAGE(B369:X369))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="370" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A370" s="2"/>
       <c r="B370" s="3"/>
       <c r="C370" s="3"/>
@@ -19736,13 +19351,12 @@
       <c r="V370" s="3"/>
       <c r="W370" s="3"/>
       <c r="X370" s="3"/>
-      <c r="Y370" s="3"/>
-      <c r="Z370" s="4" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-    </row>
-    <row r="371" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y370" s="4" t="str">
+        <f>IF(COUNTA(B370:X370)=0,"",AVERAGE(B370:X370))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="371" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A371" s="2"/>
       <c r="B371" s="3"/>
       <c r="C371" s="3"/>
@@ -19767,13 +19381,12 @@
       <c r="V371" s="3"/>
       <c r="W371" s="3"/>
       <c r="X371" s="3"/>
-      <c r="Y371" s="3"/>
-      <c r="Z371" s="4" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-    </row>
-    <row r="372" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y371" s="4" t="str">
+        <f>IF(COUNTA(B371:X371)=0,"",AVERAGE(B371:X371))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="372" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A372" s="2"/>
       <c r="B372" s="3"/>
       <c r="C372" s="3"/>
@@ -19798,13 +19411,12 @@
       <c r="V372" s="3"/>
       <c r="W372" s="3"/>
       <c r="X372" s="3"/>
-      <c r="Y372" s="3"/>
-      <c r="Z372" s="4" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-    </row>
-    <row r="373" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y372" s="4" t="str">
+        <f>IF(COUNTA(B372:X372)=0,"",AVERAGE(B372:X372))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="373" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A373" s="2"/>
       <c r="B373" s="3"/>
       <c r="C373" s="3"/>
@@ -19829,13 +19441,12 @@
       <c r="V373" s="3"/>
       <c r="W373" s="3"/>
       <c r="X373" s="3"/>
-      <c r="Y373" s="3"/>
-      <c r="Z373" s="4" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-    </row>
-    <row r="374" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y373" s="4" t="str">
+        <f>IF(COUNTA(B373:X373)=0,"",AVERAGE(B373:X373))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="374" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A374" s="2"/>
       <c r="B374" s="3"/>
       <c r="C374" s="3"/>
@@ -19860,13 +19471,12 @@
       <c r="V374" s="3"/>
       <c r="W374" s="3"/>
       <c r="X374" s="3"/>
-      <c r="Y374" s="3"/>
-      <c r="Z374" s="4" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-    </row>
-    <row r="375" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y374" s="4" t="str">
+        <f>IF(COUNTA(B374:X374)=0,"",AVERAGE(B374:X374))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="375" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A375" s="2"/>
       <c r="B375" s="3"/>
       <c r="C375" s="3"/>
@@ -19891,13 +19501,12 @@
       <c r="V375" s="3"/>
       <c r="W375" s="3"/>
       <c r="X375" s="3"/>
-      <c r="Y375" s="3"/>
-      <c r="Z375" s="4" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-    </row>
-    <row r="376" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y375" s="4" t="str">
+        <f>IF(COUNTA(B375:X375)=0,"",AVERAGE(B375:X375))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="376" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A376" s="2"/>
       <c r="B376" s="3"/>
       <c r="C376" s="3"/>
@@ -19922,13 +19531,12 @@
       <c r="V376" s="3"/>
       <c r="W376" s="3"/>
       <c r="X376" s="3"/>
-      <c r="Y376" s="3"/>
-      <c r="Z376" s="4" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-    </row>
-    <row r="377" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y376" s="4" t="str">
+        <f>IF(COUNTA(B376:X376)=0,"",AVERAGE(B376:X376))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="377" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A377" s="2"/>
       <c r="B377" s="3"/>
       <c r="C377" s="3"/>
@@ -19953,13 +19561,12 @@
       <c r="V377" s="3"/>
       <c r="W377" s="3"/>
       <c r="X377" s="3"/>
-      <c r="Y377" s="3"/>
-      <c r="Z377" s="4" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-    </row>
-    <row r="378" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y377" s="4" t="str">
+        <f>IF(COUNTA(B377:X377)=0,"",AVERAGE(B377:X377))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="378" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A378" s="2"/>
       <c r="B378" s="3"/>
       <c r="C378" s="3"/>
@@ -19984,13 +19591,12 @@
       <c r="V378" s="3"/>
       <c r="W378" s="3"/>
       <c r="X378" s="3"/>
-      <c r="Y378" s="3"/>
-      <c r="Z378" s="4" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-    </row>
-    <row r="379" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y378" s="4" t="str">
+        <f>IF(COUNTA(B378:X378)=0,"",AVERAGE(B378:X378))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="379" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A379" s="2"/>
       <c r="B379" s="3"/>
       <c r="C379" s="3"/>
@@ -20015,13 +19621,12 @@
       <c r="V379" s="3"/>
       <c r="W379" s="3"/>
       <c r="X379" s="3"/>
-      <c r="Y379" s="3"/>
-      <c r="Z379" s="4" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-    </row>
-    <row r="380" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y379" s="4" t="str">
+        <f>IF(COUNTA(B379:X379)=0,"",AVERAGE(B379:X379))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="380" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A380" s="2"/>
       <c r="B380" s="3"/>
       <c r="C380" s="3"/>
@@ -20046,13 +19651,12 @@
       <c r="V380" s="3"/>
       <c r="W380" s="3"/>
       <c r="X380" s="3"/>
-      <c r="Y380" s="3"/>
-      <c r="Z380" s="4" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-    </row>
-    <row r="381" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y380" s="4" t="str">
+        <f>IF(COUNTA(B380:X380)=0,"",AVERAGE(B380:X380))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="381" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A381" s="2"/>
       <c r="B381" s="3"/>
       <c r="C381" s="3"/>
@@ -20077,13 +19681,12 @@
       <c r="V381" s="3"/>
       <c r="W381" s="3"/>
       <c r="X381" s="3"/>
-      <c r="Y381" s="3"/>
-      <c r="Z381" s="4" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-    </row>
-    <row r="382" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y381" s="4" t="str">
+        <f>IF(COUNTA(B381:X381)=0,"",AVERAGE(B381:X381))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="382" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A382" s="2"/>
       <c r="B382" s="3"/>
       <c r="C382" s="3"/>
@@ -20108,13 +19711,12 @@
       <c r="V382" s="3"/>
       <c r="W382" s="3"/>
       <c r="X382" s="3"/>
-      <c r="Y382" s="3"/>
-      <c r="Z382" s="4" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-    </row>
-    <row r="383" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y382" s="4" t="str">
+        <f>IF(COUNTA(B382:X382)=0,"",AVERAGE(B382:X382))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="383" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A383" s="2"/>
       <c r="B383" s="3"/>
       <c r="C383" s="3"/>
@@ -20139,13 +19741,12 @@
       <c r="V383" s="3"/>
       <c r="W383" s="3"/>
       <c r="X383" s="3"/>
-      <c r="Y383" s="3"/>
-      <c r="Z383" s="4" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-    </row>
-    <row r="384" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y383" s="4" t="str">
+        <f>IF(COUNTA(B383:X383)=0,"",AVERAGE(B383:X383))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="384" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A384" s="2"/>
       <c r="B384" s="3"/>
       <c r="C384" s="3"/>
@@ -20170,13 +19771,12 @@
       <c r="V384" s="3"/>
       <c r="W384" s="3"/>
       <c r="X384" s="3"/>
-      <c r="Y384" s="3"/>
-      <c r="Z384" s="4" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-    </row>
-    <row r="385" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y384" s="4" t="str">
+        <f>IF(COUNTA(B384:X384)=0,"",AVERAGE(B384:X384))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="385" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A385" s="2"/>
       <c r="B385" s="3"/>
       <c r="C385" s="3"/>
@@ -20201,13 +19801,12 @@
       <c r="V385" s="3"/>
       <c r="W385" s="3"/>
       <c r="X385" s="3"/>
-      <c r="Y385" s="3"/>
-      <c r="Z385" s="4" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-    </row>
-    <row r="386" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y385" s="4" t="str">
+        <f>IF(COUNTA(B385:X385)=0,"",AVERAGE(B385:X385))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="386" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A386" s="2"/>
       <c r="B386" s="3"/>
       <c r="C386" s="3"/>
@@ -20232,13 +19831,12 @@
       <c r="V386" s="3"/>
       <c r="W386" s="3"/>
       <c r="X386" s="3"/>
-      <c r="Y386" s="3"/>
-      <c r="Z386" s="4" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-    </row>
-    <row r="387" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y386" s="4" t="str">
+        <f>IF(COUNTA(B386:X386)=0,"",AVERAGE(B386:X386))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="387" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A387" s="2"/>
       <c r="B387" s="3"/>
       <c r="C387" s="3"/>
@@ -20263,13 +19861,12 @@
       <c r="V387" s="3"/>
       <c r="W387" s="3"/>
       <c r="X387" s="3"/>
-      <c r="Y387" s="3"/>
-      <c r="Z387" s="4" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-    </row>
-    <row r="388" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y387" s="4" t="str">
+        <f>IF(COUNTA(B387:X387)=0,"",AVERAGE(B387:X387))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="388" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A388" s="2"/>
       <c r="B388" s="3"/>
       <c r="C388" s="3"/>
@@ -20294,13 +19891,12 @@
       <c r="V388" s="3"/>
       <c r="W388" s="3"/>
       <c r="X388" s="3"/>
-      <c r="Y388" s="3"/>
-      <c r="Z388" s="4" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-    </row>
-    <row r="389" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y388" s="4" t="str">
+        <f>IF(COUNTA(B388:X388)=0,"",AVERAGE(B388:X388))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="389" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A389" s="2"/>
       <c r="B389" s="3"/>
       <c r="C389" s="3"/>
@@ -20325,13 +19921,12 @@
       <c r="V389" s="3"/>
       <c r="W389" s="3"/>
       <c r="X389" s="3"/>
-      <c r="Y389" s="3"/>
-      <c r="Z389" s="4" t="str">
-        <f t="shared" ref="Z389:Z390" si="12">IF(COUNTA(B389:Y389)=0,"",AVERAGE(B389:Y389))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="390" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y389" s="4" t="str">
+        <f>IF(COUNTA(B389:X389)=0,"",AVERAGE(B389:X389))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="390" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A390" s="2"/>
       <c r="B390" s="3"/>
       <c r="C390" s="3"/>
@@ -20356,21 +19951,20 @@
       <c r="V390" s="3"/>
       <c r="W390" s="3"/>
       <c r="X390" s="3"/>
-      <c r="Y390" s="3"/>
-      <c r="Z390" s="4" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-    </row>
-    <row r="392" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y390" s="4" t="str">
+        <f>IF(COUNTA(B390:X390)=0,"",AVERAGE(B390:X390))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="392" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A392" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A1:Z1"/>
-    <mergeCell ref="A2:Z2"/>
+    <mergeCell ref="A1:Y1"/>
+    <mergeCell ref="A2:Y2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing r:id="rId1"/>
@@ -20389,7 +19983,7 @@
   <sheetData>
     <row r="1" spans="1:21" ht="24" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="8" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B1" s="7"/>
       <c r="C1" s="7"/>
@@ -20445,7 +20039,7 @@
         <v>3</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>4</v>
@@ -20457,7 +20051,7 @@
         <v>7</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H4" s="1" t="s">
         <v>15</v>
@@ -20469,7 +20063,7 @@
         <v>11</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="L4" s="1" t="s">
         <v>19</v>
@@ -20478,28 +20072,28 @@
         <v>12</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O4" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="P4" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="P4" s="1" t="s">
+      <c r="Q4" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="Q4" s="1" t="s">
+      <c r="R4" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="S4" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="R4" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="S4" s="1" t="s">
-        <v>36</v>
-      </c>
       <c r="T4" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="U4" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5" spans="1:21" x14ac:dyDescent="0.25">
@@ -22879,29 +22473,69 @@
       </c>
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A41" s="2"/>
-      <c r="B41" s="3"/>
-      <c r="C41" s="3"/>
-      <c r="D41" s="3"/>
-      <c r="E41" s="3"/>
-      <c r="F41" s="3"/>
-      <c r="G41" s="3"/>
-      <c r="H41" s="3"/>
-      <c r="I41" s="3"/>
-      <c r="J41" s="3"/>
-      <c r="K41" s="3"/>
-      <c r="L41" s="3"/>
-      <c r="M41" s="3"/>
-      <c r="N41" s="3"/>
-      <c r="O41" s="3"/>
-      <c r="P41" s="3"/>
-      <c r="Q41" s="3"/>
-      <c r="R41" s="3"/>
-      <c r="S41" s="3"/>
-      <c r="T41" s="3"/>
-      <c r="U41" s="4" t="str">
+      <c r="A41" s="2">
+        <v>46182</v>
+      </c>
+      <c r="B41" s="3">
+        <v>4.29</v>
+      </c>
+      <c r="C41" s="3">
+        <v>3.95</v>
+      </c>
+      <c r="D41" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="E41" s="3">
+        <v>4.1900000000000004</v>
+      </c>
+      <c r="F41" s="3">
+        <v>4.3099999999999996</v>
+      </c>
+      <c r="G41" s="3">
+        <v>3.99</v>
+      </c>
+      <c r="H41" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="I41" s="3">
+        <v>3.39</v>
+      </c>
+      <c r="J41" s="3">
+        <v>3.09</v>
+      </c>
+      <c r="K41" s="3">
+        <v>3.95</v>
+      </c>
+      <c r="L41" s="3">
+        <v>3.49</v>
+      </c>
+      <c r="M41" s="3">
+        <v>3.59</v>
+      </c>
+      <c r="N41" s="3">
+        <v>3.84</v>
+      </c>
+      <c r="O41" s="3">
+        <v>4.1900000000000004</v>
+      </c>
+      <c r="P41" s="3">
+        <v>3.89</v>
+      </c>
+      <c r="Q41" s="3">
+        <v>4.03</v>
+      </c>
+      <c r="R41" s="3">
+        <v>3.89</v>
+      </c>
+      <c r="S41" s="3">
+        <v>3.99</v>
+      </c>
+      <c r="T41" s="3">
+        <v>1.99</v>
+      </c>
+      <c r="U41" s="4">
         <f t="shared" si="0"/>
-        <v/>
+        <v>3.6863157894736838</v>
       </c>
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
@@ -31980,7 +31614,7 @@
     </row>
     <row r="392" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A392" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -32005,7 +31639,7 @@
   <sheetData>
     <row r="1" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="8" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B1" s="7"/>
       <c r="C1" s="7"/>
@@ -32044,28 +31678,28 @@
         <v>10</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>15</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G4" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H4" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="I4" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="J4" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="I4" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>36</v>
-      </c>
       <c r="K4" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
@@ -33365,19 +32999,39 @@
       </c>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A41" s="2"/>
-      <c r="B41" s="3"/>
-      <c r="C41" s="3"/>
-      <c r="D41" s="3"/>
-      <c r="E41" s="3"/>
-      <c r="F41" s="3"/>
-      <c r="G41" s="3"/>
-      <c r="H41" s="3"/>
-      <c r="I41" s="3"/>
-      <c r="J41" s="3"/>
-      <c r="K41" s="4" t="str">
+      <c r="A41" s="2">
+        <v>46182</v>
+      </c>
+      <c r="B41" s="3">
+        <v>2.89</v>
+      </c>
+      <c r="C41" s="3">
+        <v>3.14</v>
+      </c>
+      <c r="D41" s="3">
+        <v>2.83</v>
+      </c>
+      <c r="E41" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="F41" s="3">
+        <v>2.8</v>
+      </c>
+      <c r="G41" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="H41" s="3">
+        <v>2.63</v>
+      </c>
+      <c r="I41" s="3">
+        <v>2.89</v>
+      </c>
+      <c r="J41" s="3">
+        <v>2.59</v>
+      </c>
+      <c r="K41" s="4">
         <f t="shared" si="0"/>
-        <v/>
+        <v>2.8611111111111112</v>
       </c>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.25">
@@ -38966,7 +38620,7 @@
     </row>
     <row r="392" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A392" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -38991,7 +38645,7 @@
   <sheetData>
     <row r="1" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B1" s="7"/>
       <c r="C1" s="7"/>
@@ -39029,34 +38683,34 @@
         <v>3</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E4" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="G4" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="F4" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="G4" s="1" t="s">
+      <c r="H4" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="J4" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="K4" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="I4" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>36</v>
-      </c>
       <c r="L4" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
@@ -40464,20 +40118,42 @@
       </c>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A41" s="2"/>
-      <c r="B41" s="3"/>
-      <c r="C41" s="3"/>
-      <c r="D41" s="3"/>
-      <c r="E41" s="3"/>
-      <c r="F41" s="3"/>
-      <c r="G41" s="3"/>
-      <c r="H41" s="3"/>
-      <c r="I41" s="3"/>
-      <c r="J41" s="3"/>
-      <c r="K41" s="3"/>
-      <c r="L41" s="4" t="str">
+      <c r="A41" s="2">
+        <v>46182</v>
+      </c>
+      <c r="B41" s="3">
+        <v>3.59</v>
+      </c>
+      <c r="C41" s="3">
+        <v>3.19</v>
+      </c>
+      <c r="D41" s="3">
+        <v>3.59</v>
+      </c>
+      <c r="E41" s="3">
+        <v>3.35</v>
+      </c>
+      <c r="F41" s="3">
+        <v>3.43</v>
+      </c>
+      <c r="G41" s="3">
+        <v>3.89</v>
+      </c>
+      <c r="H41" s="3">
+        <v>3.11</v>
+      </c>
+      <c r="I41" s="3">
+        <v>3.29</v>
+      </c>
+      <c r="J41" s="3">
+        <v>3.46</v>
+      </c>
+      <c r="K41" s="3">
+        <v>3.29</v>
+      </c>
+      <c r="L41" s="4">
         <f t="shared" si="0"/>
-        <v/>
+        <v>3.4189999999999996</v>
       </c>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.25">
@@ -46415,7 +46091,7 @@
     </row>
     <row r="392" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A392" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>

--- a/app/mevduat-kredi-faizleri/data/hoca-ile-borsa-faiz-takip-sablonu-guncel.xlsx
+++ b/app/mevduat-kredi-faizleri/data/hoca-ile-borsa-faiz-takip-sablonu-guncel.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projeler\hoca-ile-borsa\app\mevduat-kredi-faizleri\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25DFFEA0-DC28-4FFE-A6EC-C747DAEA2EB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B00A3F1-F32E-41FB-B1EA-ABD5CB58DE66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -449,6 +449,9 @@
                 <c:pt idx="36">
                   <c:v>46182</c:v>
                 </c:pt>
+                <c:pt idx="37">
+                  <c:v>46183</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -570,7 +573,7 @@
                   <c:v>43.44086956521739</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>0</c:v>
+                  <c:v>43.44086956521739</c:v>
                 </c:pt>
                 <c:pt idx="38">
                   <c:v>0</c:v>
@@ -1886,6 +1889,9 @@
                 <c:pt idx="36">
                   <c:v>46182</c:v>
                 </c:pt>
+                <c:pt idx="37">
+                  <c:v>46183</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2007,7 +2013,7 @@
                   <c:v>3.6863157894736838</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>0</c:v>
+                  <c:v>3.6168421052631579</c:v>
                 </c:pt>
                 <c:pt idx="38">
                   <c:v>0</c:v>
@@ -3323,6 +3329,9 @@
                 <c:pt idx="36">
                   <c:v>46182</c:v>
                 </c:pt>
+                <c:pt idx="37">
+                  <c:v>46183</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3444,7 +3453,7 @@
                   <c:v>2.8611111111111112</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>0</c:v>
+                  <c:v>2.8611111111111112</c:v>
                 </c:pt>
                 <c:pt idx="38">
                   <c:v>0</c:v>
@@ -4760,6 +4769,9 @@
                 <c:pt idx="36">
                   <c:v>46182</c:v>
                 </c:pt>
+                <c:pt idx="37">
+                  <c:v>46183</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -4881,7 +4893,7 @@
                   <c:v>3.4189999999999996</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>0</c:v>
+                  <c:v>3.4189999999999996</c:v>
                 </c:pt>
                 <c:pt idx="38">
                   <c:v>0</c:v>
@@ -6674,7 +6686,7 @@
         <v>45.25</v>
       </c>
       <c r="Y5" s="4">
-        <f>IF(COUNTA(B5:X5)=0,"",AVERAGE(B5:X5))</f>
+        <f t="shared" ref="Y5:Y68" si="0">IF(COUNTA(B5:X5)=0,"",AVERAGE(B5:X5))</f>
         <v>43.078695652173913</v>
       </c>
     </row>
@@ -6752,7 +6764,7 @@
         <v>45.25</v>
       </c>
       <c r="Y6" s="4">
-        <f>IF(COUNTA(B6:X6)=0,"",AVERAGE(B6:X6))</f>
+        <f t="shared" si="0"/>
         <v>43.078695652173913</v>
       </c>
     </row>
@@ -6830,7 +6842,7 @@
         <v>45.25</v>
       </c>
       <c r="Y7" s="4">
-        <f>IF(COUNTA(B7:X7)=0,"",AVERAGE(B7:X7))</f>
+        <f t="shared" si="0"/>
         <v>43.078695652173913</v>
       </c>
     </row>
@@ -6908,7 +6920,7 @@
         <v>45.25</v>
       </c>
       <c r="Y8" s="4">
-        <f>IF(COUNTA(B8:X8)=0,"",AVERAGE(B8:X8))</f>
+        <f t="shared" si="0"/>
         <v>43.52</v>
       </c>
     </row>
@@ -6986,7 +6998,7 @@
         <v>45.25</v>
       </c>
       <c r="Y9" s="4">
-        <f>IF(COUNTA(B9:X9)=0,"",AVERAGE(B9:X9))</f>
+        <f t="shared" si="0"/>
         <v>43.35</v>
       </c>
     </row>
@@ -7064,7 +7076,7 @@
         <v>45.25</v>
       </c>
       <c r="Y10" s="4">
-        <f>IF(COUNTA(B10:X10)=0,"",AVERAGE(B10:X10))</f>
+        <f t="shared" si="0"/>
         <v>43.393478260869564</v>
       </c>
     </row>
@@ -7142,7 +7154,7 @@
         <v>45.25</v>
       </c>
       <c r="Y11" s="4">
-        <f>IF(COUNTA(B11:X11)=0,"",AVERAGE(B11:X11))</f>
+        <f t="shared" si="0"/>
         <v>43.35</v>
       </c>
     </row>
@@ -7220,7 +7232,7 @@
         <v>45.25</v>
       </c>
       <c r="Y12" s="4">
-        <f>IF(COUNTA(B12:X12)=0,"",AVERAGE(B12:X12))</f>
+        <f t="shared" si="0"/>
         <v>43.343043478260867</v>
       </c>
     </row>
@@ -7298,7 +7310,7 @@
         <v>45.25</v>
       </c>
       <c r="Y13" s="4">
-        <f>IF(COUNTA(B13:X13)=0,"",AVERAGE(B13:X13))</f>
+        <f t="shared" si="0"/>
         <v>43.375652173913046</v>
       </c>
     </row>
@@ -7376,7 +7388,7 @@
         <v>45.25</v>
       </c>
       <c r="Y14" s="4">
-        <f>IF(COUNTA(B14:X14)=0,"",AVERAGE(B14:X14))</f>
+        <f t="shared" si="0"/>
         <v>43.375652173913046</v>
       </c>
     </row>
@@ -7454,7 +7466,7 @@
         <v>45.25</v>
       </c>
       <c r="Y15" s="4">
-        <f>IF(COUNTA(B15:X15)=0,"",AVERAGE(B15:X15))</f>
+        <f t="shared" si="0"/>
         <v>43.364782608695648</v>
       </c>
     </row>
@@ -7532,7 +7544,7 @@
         <v>45.25</v>
       </c>
       <c r="Y16" s="4">
-        <f>IF(COUNTA(B16:X16)=0,"",AVERAGE(B16:X16))</f>
+        <f t="shared" si="0"/>
         <v>43.416086956521738</v>
       </c>
     </row>
@@ -7610,7 +7622,7 @@
         <v>45.25</v>
       </c>
       <c r="Y17" s="4">
-        <f>IF(COUNTA(B17:X17)=0,"",AVERAGE(B17:X17))</f>
+        <f t="shared" si="0"/>
         <v>43.383478260869566</v>
       </c>
     </row>
@@ -7688,7 +7700,7 @@
         <v>45.25</v>
       </c>
       <c r="Y18" s="4">
-        <f>IF(COUNTA(B18:X18)=0,"",AVERAGE(B18:X18))</f>
+        <f t="shared" si="0"/>
         <v>43.383478260869566</v>
       </c>
     </row>
@@ -7766,7 +7778,7 @@
         <v>45.25</v>
       </c>
       <c r="Y19" s="4">
-        <f>IF(COUNTA(B19:X19)=0,"",AVERAGE(B19:X19))</f>
+        <f t="shared" si="0"/>
         <v>43.470434782608699</v>
       </c>
     </row>
@@ -7844,7 +7856,7 @@
         <v>45.25</v>
       </c>
       <c r="Y20" s="4">
-        <f>IF(COUNTA(B20:X20)=0,"",AVERAGE(B20:X20))</f>
+        <f t="shared" si="0"/>
         <v>43.436956521739127</v>
       </c>
     </row>
@@ -7922,7 +7934,7 @@
         <v>45.25</v>
       </c>
       <c r="Y21" s="4">
-        <f>IF(COUNTA(B21:X21)=0,"",AVERAGE(B21:X21))</f>
+        <f t="shared" si="0"/>
         <v>43.426086956521736</v>
       </c>
     </row>
@@ -8000,7 +8012,7 @@
         <v>45.25</v>
       </c>
       <c r="Y22" s="4">
-        <f>IF(COUNTA(B22:X22)=0,"",AVERAGE(B22:X22))</f>
+        <f t="shared" si="0"/>
         <v>43.393478260869564</v>
       </c>
     </row>
@@ -8078,7 +8090,7 @@
         <v>45.25</v>
       </c>
       <c r="Y23" s="4">
-        <f>IF(COUNTA(B23:X23)=0,"",AVERAGE(B23:X23))</f>
+        <f t="shared" si="0"/>
         <v>43.382608695652173</v>
       </c>
     </row>
@@ -8156,7 +8168,7 @@
         <v>45.25</v>
       </c>
       <c r="Y24" s="4">
-        <f>IF(COUNTA(B24:X24)=0,"",AVERAGE(B24:X24))</f>
+        <f t="shared" si="0"/>
         <v>43.382608695652173</v>
       </c>
     </row>
@@ -8234,7 +8246,7 @@
         <v>45.25</v>
       </c>
       <c r="Y25" s="4">
-        <f>IF(COUNTA(B25:X25)=0,"",AVERAGE(B25:X25))</f>
+        <f t="shared" si="0"/>
         <v>43.371739130434783</v>
       </c>
     </row>
@@ -8312,7 +8324,7 @@
         <v>45.25</v>
       </c>
       <c r="Y26" s="4">
-        <f>IF(COUNTA(B26:X26)=0,"",AVERAGE(B26:X26))</f>
+        <f t="shared" si="0"/>
         <v>43.387826086956522</v>
       </c>
     </row>
@@ -8390,7 +8402,7 @@
         <v>45.25</v>
       </c>
       <c r="Y27" s="4">
-        <f>IF(COUNTA(B27:X27)=0,"",AVERAGE(B27:X27))</f>
+        <f t="shared" si="0"/>
         <v>43.344347826086953</v>
       </c>
     </row>
@@ -8468,7 +8480,7 @@
         <v>45.25</v>
       </c>
       <c r="Y28" s="4">
-        <f>IF(COUNTA(B28:X28)=0,"",AVERAGE(B28:X28))</f>
+        <f t="shared" si="0"/>
         <v>43.344347826086953</v>
       </c>
     </row>
@@ -8546,7 +8558,7 @@
         <v>45.25</v>
       </c>
       <c r="Y29" s="4">
-        <f>IF(COUNTA(B29:X29)=0,"",AVERAGE(B29:X29))</f>
+        <f t="shared" si="0"/>
         <v>43.344347826086953</v>
       </c>
     </row>
@@ -8624,7 +8636,7 @@
         <v>45.25</v>
       </c>
       <c r="Y30" s="4">
-        <f>IF(COUNTA(B30:X30)=0,"",AVERAGE(B30:X30))</f>
+        <f t="shared" si="0"/>
         <v>43.387826086956522</v>
       </c>
     </row>
@@ -8702,7 +8714,7 @@
         <v>45.25</v>
       </c>
       <c r="Y31" s="4">
-        <f>IF(COUNTA(B31:X31)=0,"",AVERAGE(B31:X31))</f>
+        <f t="shared" si="0"/>
         <v>43.366521739130434</v>
       </c>
     </row>
@@ -8780,7 +8792,7 @@
         <v>45.25</v>
       </c>
       <c r="Y32" s="4">
-        <f>IF(COUNTA(B32:X32)=0,"",AVERAGE(B32:X32))</f>
+        <f t="shared" si="0"/>
         <v>43.366521739130434</v>
       </c>
     </row>
@@ -8858,7 +8870,7 @@
         <v>45.25</v>
       </c>
       <c r="Y33" s="4">
-        <f>IF(COUNTA(B33:X33)=0,"",AVERAGE(B33:X33))</f>
+        <f t="shared" si="0"/>
         <v>43.41</v>
       </c>
     </row>
@@ -8936,7 +8948,7 @@
         <v>45.25</v>
       </c>
       <c r="Y34" s="4">
-        <f>IF(COUNTA(B34:X34)=0,"",AVERAGE(B34:X34))</f>
+        <f t="shared" si="0"/>
         <v>43.41</v>
       </c>
     </row>
@@ -9014,7 +9026,7 @@
         <v>45.25</v>
       </c>
       <c r="Y35" s="4">
-        <f>IF(COUNTA(B35:X35)=0,"",AVERAGE(B35:X35))</f>
+        <f t="shared" si="0"/>
         <v>43.41</v>
       </c>
     </row>
@@ -9092,7 +9104,7 @@
         <v>45.25</v>
       </c>
       <c r="Y36" s="4">
-        <f>IF(COUNTA(B36:X36)=0,"",AVERAGE(B36:X36))</f>
+        <f t="shared" si="0"/>
         <v>43.40608695652174</v>
       </c>
     </row>
@@ -9170,7 +9182,7 @@
         <v>45.25</v>
       </c>
       <c r="Y37" s="4">
-        <f>IF(COUNTA(B37:X37)=0,"",AVERAGE(B37:X37))</f>
+        <f t="shared" si="0"/>
         <v>43.40608695652174</v>
       </c>
     </row>
@@ -9248,7 +9260,7 @@
         <v>45.25</v>
       </c>
       <c r="Y38" s="4">
-        <f>IF(COUNTA(B38:X38)=0,"",AVERAGE(B38:X38))</f>
+        <f t="shared" si="0"/>
         <v>43.40608695652174</v>
       </c>
     </row>
@@ -9326,7 +9338,7 @@
         <v>45.25</v>
       </c>
       <c r="Y39" s="4">
-        <f>IF(COUNTA(B39:X39)=0,"",AVERAGE(B39:X39))</f>
+        <f t="shared" si="0"/>
         <v>43.40608695652174</v>
       </c>
     </row>
@@ -9404,7 +9416,7 @@
         <v>45.25</v>
       </c>
       <c r="Y40" s="4">
-        <f>IF(COUNTA(B40:X40)=0,"",AVERAGE(B40:X40))</f>
+        <f t="shared" si="0"/>
         <v>43.40608695652174</v>
       </c>
     </row>
@@ -9482,38 +9494,86 @@
         <v>45.25</v>
       </c>
       <c r="Y41" s="4">
-        <f>IF(COUNTA(B41:X41)=0,"",AVERAGE(B41:X41))</f>
+        <f t="shared" si="0"/>
         <v>43.44086956521739</v>
       </c>
     </row>
     <row r="42" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A42" s="2"/>
-      <c r="B42" s="3"/>
-      <c r="C42" s="3"/>
-      <c r="D42" s="3"/>
-      <c r="E42" s="3"/>
-      <c r="F42" s="3"/>
-      <c r="G42" s="3"/>
-      <c r="H42" s="3"/>
-      <c r="I42" s="3"/>
-      <c r="J42" s="3"/>
-      <c r="K42" s="3"/>
-      <c r="L42" s="3"/>
-      <c r="M42" s="3"/>
-      <c r="N42" s="3"/>
-      <c r="O42" s="3"/>
-      <c r="P42" s="3"/>
-      <c r="Q42" s="3"/>
-      <c r="R42" s="3"/>
-      <c r="S42" s="3"/>
-      <c r="T42" s="3"/>
-      <c r="U42" s="3"/>
-      <c r="V42" s="3"/>
-      <c r="W42" s="3"/>
-      <c r="X42" s="3"/>
-      <c r="Y42" s="4" t="str">
-        <f>IF(COUNTA(B42:X42)=0,"",AVERAGE(B42:X42))</f>
-        <v/>
+      <c r="A42" s="2">
+        <v>46183</v>
+      </c>
+      <c r="B42" s="3">
+        <v>42.5</v>
+      </c>
+      <c r="C42" s="3">
+        <v>46</v>
+      </c>
+      <c r="D42" s="3">
+        <v>46</v>
+      </c>
+      <c r="E42" s="3">
+        <v>45</v>
+      </c>
+      <c r="F42" s="3">
+        <v>43.5</v>
+      </c>
+      <c r="G42" s="3">
+        <v>41</v>
+      </c>
+      <c r="H42" s="3">
+        <v>46</v>
+      </c>
+      <c r="I42" s="3">
+        <v>41.5</v>
+      </c>
+      <c r="J42" s="3">
+        <v>43</v>
+      </c>
+      <c r="K42" s="3">
+        <v>41</v>
+      </c>
+      <c r="L42" s="3">
+        <v>36</v>
+      </c>
+      <c r="M42" s="3">
+        <v>44</v>
+      </c>
+      <c r="N42" s="3">
+        <v>45</v>
+      </c>
+      <c r="O42" s="3">
+        <v>42.39</v>
+      </c>
+      <c r="P42" s="3">
+        <v>39</v>
+      </c>
+      <c r="Q42" s="3">
+        <v>45</v>
+      </c>
+      <c r="R42" s="3">
+        <v>45</v>
+      </c>
+      <c r="S42" s="3">
+        <v>45</v>
+      </c>
+      <c r="T42" s="3">
+        <v>43.5</v>
+      </c>
+      <c r="U42" s="3">
+        <v>44.5</v>
+      </c>
+      <c r="V42" s="3">
+        <v>42</v>
+      </c>
+      <c r="W42" s="3">
+        <v>47</v>
+      </c>
+      <c r="X42" s="3">
+        <v>45.25</v>
+      </c>
+      <c r="Y42" s="4">
+        <f t="shared" si="0"/>
+        <v>43.44086956521739</v>
       </c>
     </row>
     <row r="43" spans="1:25" x14ac:dyDescent="0.25">
@@ -9542,7 +9602,7 @@
       <c r="W43" s="3"/>
       <c r="X43" s="3"/>
       <c r="Y43" s="4" t="str">
-        <f>IF(COUNTA(B43:X43)=0,"",AVERAGE(B43:X43))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -9572,7 +9632,7 @@
       <c r="W44" s="3"/>
       <c r="X44" s="3"/>
       <c r="Y44" s="4" t="str">
-        <f>IF(COUNTA(B44:X44)=0,"",AVERAGE(B44:X44))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -9602,7 +9662,7 @@
       <c r="W45" s="3"/>
       <c r="X45" s="3"/>
       <c r="Y45" s="4" t="str">
-        <f>IF(COUNTA(B45:X45)=0,"",AVERAGE(B45:X45))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -9632,7 +9692,7 @@
       <c r="W46" s="3"/>
       <c r="X46" s="3"/>
       <c r="Y46" s="4" t="str">
-        <f>IF(COUNTA(B46:X46)=0,"",AVERAGE(B46:X46))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -9662,7 +9722,7 @@
       <c r="W47" s="3"/>
       <c r="X47" s="3"/>
       <c r="Y47" s="4" t="str">
-        <f>IF(COUNTA(B47:X47)=0,"",AVERAGE(B47:X47))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -9692,7 +9752,7 @@
       <c r="W48" s="3"/>
       <c r="X48" s="3"/>
       <c r="Y48" s="4" t="str">
-        <f>IF(COUNTA(B48:X48)=0,"",AVERAGE(B48:X48))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -9722,7 +9782,7 @@
       <c r="W49" s="3"/>
       <c r="X49" s="3"/>
       <c r="Y49" s="4" t="str">
-        <f>IF(COUNTA(B49:X49)=0,"",AVERAGE(B49:X49))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -9752,7 +9812,7 @@
       <c r="W50" s="3"/>
       <c r="X50" s="3"/>
       <c r="Y50" s="4" t="str">
-        <f>IF(COUNTA(B50:X50)=0,"",AVERAGE(B50:X50))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -9782,7 +9842,7 @@
       <c r="W51" s="3"/>
       <c r="X51" s="3"/>
       <c r="Y51" s="4" t="str">
-        <f>IF(COUNTA(B51:X51)=0,"",AVERAGE(B51:X51))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -9812,7 +9872,7 @@
       <c r="W52" s="3"/>
       <c r="X52" s="3"/>
       <c r="Y52" s="4" t="str">
-        <f>IF(COUNTA(B52:X52)=0,"",AVERAGE(B52:X52))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -9842,7 +9902,7 @@
       <c r="W53" s="3"/>
       <c r="X53" s="3"/>
       <c r="Y53" s="4" t="str">
-        <f>IF(COUNTA(B53:X53)=0,"",AVERAGE(B53:X53))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -9872,7 +9932,7 @@
       <c r="W54" s="3"/>
       <c r="X54" s="3"/>
       <c r="Y54" s="4" t="str">
-        <f>IF(COUNTA(B54:X54)=0,"",AVERAGE(B54:X54))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -9902,7 +9962,7 @@
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
       <c r="Y55" s="4" t="str">
-        <f>IF(COUNTA(B55:X55)=0,"",AVERAGE(B55:X55))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -9932,7 +9992,7 @@
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
       <c r="Y56" s="4" t="str">
-        <f>IF(COUNTA(B56:X56)=0,"",AVERAGE(B56:X56))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -9962,7 +10022,7 @@
       <c r="W57" s="3"/>
       <c r="X57" s="3"/>
       <c r="Y57" s="4" t="str">
-        <f>IF(COUNTA(B57:X57)=0,"",AVERAGE(B57:X57))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -9992,7 +10052,7 @@
       <c r="W58" s="3"/>
       <c r="X58" s="3"/>
       <c r="Y58" s="4" t="str">
-        <f>IF(COUNTA(B58:X58)=0,"",AVERAGE(B58:X58))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -10022,7 +10082,7 @@
       <c r="W59" s="3"/>
       <c r="X59" s="3"/>
       <c r="Y59" s="4" t="str">
-        <f>IF(COUNTA(B59:X59)=0,"",AVERAGE(B59:X59))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -10052,7 +10112,7 @@
       <c r="W60" s="3"/>
       <c r="X60" s="3"/>
       <c r="Y60" s="4" t="str">
-        <f>IF(COUNTA(B60:X60)=0,"",AVERAGE(B60:X60))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -10082,7 +10142,7 @@
       <c r="W61" s="3"/>
       <c r="X61" s="3"/>
       <c r="Y61" s="4" t="str">
-        <f>IF(COUNTA(B61:X61)=0,"",AVERAGE(B61:X61))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -10112,7 +10172,7 @@
       <c r="W62" s="3"/>
       <c r="X62" s="3"/>
       <c r="Y62" s="4" t="str">
-        <f>IF(COUNTA(B62:X62)=0,"",AVERAGE(B62:X62))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -10142,7 +10202,7 @@
       <c r="W63" s="3"/>
       <c r="X63" s="3"/>
       <c r="Y63" s="4" t="str">
-        <f>IF(COUNTA(B63:X63)=0,"",AVERAGE(B63:X63))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -10172,7 +10232,7 @@
       <c r="W64" s="3"/>
       <c r="X64" s="3"/>
       <c r="Y64" s="4" t="str">
-        <f>IF(COUNTA(B64:X64)=0,"",AVERAGE(B64:X64))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -10202,7 +10262,7 @@
       <c r="W65" s="3"/>
       <c r="X65" s="3"/>
       <c r="Y65" s="4" t="str">
-        <f>IF(COUNTA(B65:X65)=0,"",AVERAGE(B65:X65))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -10232,7 +10292,7 @@
       <c r="W66" s="3"/>
       <c r="X66" s="3"/>
       <c r="Y66" s="4" t="str">
-        <f>IF(COUNTA(B66:X66)=0,"",AVERAGE(B66:X66))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -10262,7 +10322,7 @@
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
       <c r="Y67" s="4" t="str">
-        <f>IF(COUNTA(B67:X67)=0,"",AVERAGE(B67:X67))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -10292,7 +10352,7 @@
       <c r="W68" s="3"/>
       <c r="X68" s="3"/>
       <c r="Y68" s="4" t="str">
-        <f>IF(COUNTA(B68:X68)=0,"",AVERAGE(B68:X68))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -10322,7 +10382,7 @@
       <c r="W69" s="3"/>
       <c r="X69" s="3"/>
       <c r="Y69" s="4" t="str">
-        <f>IF(COUNTA(B69:X69)=0,"",AVERAGE(B69:X69))</f>
+        <f t="shared" ref="Y69:Y132" si="1">IF(COUNTA(B69:X69)=0,"",AVERAGE(B69:X69))</f>
         <v/>
       </c>
     </row>
@@ -10352,7 +10412,7 @@
       <c r="W70" s="3"/>
       <c r="X70" s="3"/>
       <c r="Y70" s="4" t="str">
-        <f>IF(COUNTA(B70:X70)=0,"",AVERAGE(B70:X70))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -10382,7 +10442,7 @@
       <c r="W71" s="3"/>
       <c r="X71" s="3"/>
       <c r="Y71" s="4" t="str">
-        <f>IF(COUNTA(B71:X71)=0,"",AVERAGE(B71:X71))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -10412,7 +10472,7 @@
       <c r="W72" s="3"/>
       <c r="X72" s="3"/>
       <c r="Y72" s="4" t="str">
-        <f>IF(COUNTA(B72:X72)=0,"",AVERAGE(B72:X72))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -10442,7 +10502,7 @@
       <c r="W73" s="3"/>
       <c r="X73" s="3"/>
       <c r="Y73" s="4" t="str">
-        <f>IF(COUNTA(B73:X73)=0,"",AVERAGE(B73:X73))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -10472,7 +10532,7 @@
       <c r="W74" s="3"/>
       <c r="X74" s="3"/>
       <c r="Y74" s="4" t="str">
-        <f>IF(COUNTA(B74:X74)=0,"",AVERAGE(B74:X74))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -10502,7 +10562,7 @@
       <c r="W75" s="3"/>
       <c r="X75" s="3"/>
       <c r="Y75" s="4" t="str">
-        <f>IF(COUNTA(B75:X75)=0,"",AVERAGE(B75:X75))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -10532,7 +10592,7 @@
       <c r="W76" s="3"/>
       <c r="X76" s="3"/>
       <c r="Y76" s="4" t="str">
-        <f>IF(COUNTA(B76:X76)=0,"",AVERAGE(B76:X76))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -10562,7 +10622,7 @@
       <c r="W77" s="3"/>
       <c r="X77" s="3"/>
       <c r="Y77" s="4" t="str">
-        <f>IF(COUNTA(B77:X77)=0,"",AVERAGE(B77:X77))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -10592,7 +10652,7 @@
       <c r="W78" s="3"/>
       <c r="X78" s="3"/>
       <c r="Y78" s="4" t="str">
-        <f>IF(COUNTA(B78:X78)=0,"",AVERAGE(B78:X78))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -10622,7 +10682,7 @@
       <c r="W79" s="3"/>
       <c r="X79" s="3"/>
       <c r="Y79" s="4" t="str">
-        <f>IF(COUNTA(B79:X79)=0,"",AVERAGE(B79:X79))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -10652,7 +10712,7 @@
       <c r="W80" s="3"/>
       <c r="X80" s="3"/>
       <c r="Y80" s="4" t="str">
-        <f>IF(COUNTA(B80:X80)=0,"",AVERAGE(B80:X80))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -10682,7 +10742,7 @@
       <c r="W81" s="3"/>
       <c r="X81" s="3"/>
       <c r="Y81" s="4" t="str">
-        <f>IF(COUNTA(B81:X81)=0,"",AVERAGE(B81:X81))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -10712,7 +10772,7 @@
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
       <c r="Y82" s="4" t="str">
-        <f>IF(COUNTA(B82:X82)=0,"",AVERAGE(B82:X82))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -10742,7 +10802,7 @@
       <c r="W83" s="3"/>
       <c r="X83" s="3"/>
       <c r="Y83" s="4" t="str">
-        <f>IF(COUNTA(B83:X83)=0,"",AVERAGE(B83:X83))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -10772,7 +10832,7 @@
       <c r="W84" s="3"/>
       <c r="X84" s="3"/>
       <c r="Y84" s="4" t="str">
-        <f>IF(COUNTA(B84:X84)=0,"",AVERAGE(B84:X84))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -10802,7 +10862,7 @@
       <c r="W85" s="3"/>
       <c r="X85" s="3"/>
       <c r="Y85" s="4" t="str">
-        <f>IF(COUNTA(B85:X85)=0,"",AVERAGE(B85:X85))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -10832,7 +10892,7 @@
       <c r="W86" s="3"/>
       <c r="X86" s="3"/>
       <c r="Y86" s="4" t="str">
-        <f>IF(COUNTA(B86:X86)=0,"",AVERAGE(B86:X86))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -10862,7 +10922,7 @@
       <c r="W87" s="3"/>
       <c r="X87" s="3"/>
       <c r="Y87" s="4" t="str">
-        <f>IF(COUNTA(B87:X87)=0,"",AVERAGE(B87:X87))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -10892,7 +10952,7 @@
       <c r="W88" s="3"/>
       <c r="X88" s="3"/>
       <c r="Y88" s="4" t="str">
-        <f>IF(COUNTA(B88:X88)=0,"",AVERAGE(B88:X88))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -10922,7 +10982,7 @@
       <c r="W89" s="3"/>
       <c r="X89" s="3"/>
       <c r="Y89" s="4" t="str">
-        <f>IF(COUNTA(B89:X89)=0,"",AVERAGE(B89:X89))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -10952,7 +11012,7 @@
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
       <c r="Y90" s="4" t="str">
-        <f>IF(COUNTA(B90:X90)=0,"",AVERAGE(B90:X90))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -10982,7 +11042,7 @@
       <c r="W91" s="3"/>
       <c r="X91" s="3"/>
       <c r="Y91" s="4" t="str">
-        <f>IF(COUNTA(B91:X91)=0,"",AVERAGE(B91:X91))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -11012,7 +11072,7 @@
       <c r="W92" s="3"/>
       <c r="X92" s="3"/>
       <c r="Y92" s="4" t="str">
-        <f>IF(COUNTA(B92:X92)=0,"",AVERAGE(B92:X92))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -11042,7 +11102,7 @@
       <c r="W93" s="3"/>
       <c r="X93" s="3"/>
       <c r="Y93" s="4" t="str">
-        <f>IF(COUNTA(B93:X93)=0,"",AVERAGE(B93:X93))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -11072,7 +11132,7 @@
       <c r="W94" s="3"/>
       <c r="X94" s="3"/>
       <c r="Y94" s="4" t="str">
-        <f>IF(COUNTA(B94:X94)=0,"",AVERAGE(B94:X94))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -11102,7 +11162,7 @@
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
       <c r="Y95" s="4" t="str">
-        <f>IF(COUNTA(B95:X95)=0,"",AVERAGE(B95:X95))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -11132,7 +11192,7 @@
       <c r="W96" s="3"/>
       <c r="X96" s="3"/>
       <c r="Y96" s="4" t="str">
-        <f>IF(COUNTA(B96:X96)=0,"",AVERAGE(B96:X96))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -11162,7 +11222,7 @@
       <c r="W97" s="3"/>
       <c r="X97" s="3"/>
       <c r="Y97" s="4" t="str">
-        <f>IF(COUNTA(B97:X97)=0,"",AVERAGE(B97:X97))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -11192,7 +11252,7 @@
       <c r="W98" s="3"/>
       <c r="X98" s="3"/>
       <c r="Y98" s="4" t="str">
-        <f>IF(COUNTA(B98:X98)=0,"",AVERAGE(B98:X98))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -11222,7 +11282,7 @@
       <c r="W99" s="3"/>
       <c r="X99" s="3"/>
       <c r="Y99" s="4" t="str">
-        <f>IF(COUNTA(B99:X99)=0,"",AVERAGE(B99:X99))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -11252,7 +11312,7 @@
       <c r="W100" s="3"/>
       <c r="X100" s="3"/>
       <c r="Y100" s="4" t="str">
-        <f>IF(COUNTA(B100:X100)=0,"",AVERAGE(B100:X100))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -11282,7 +11342,7 @@
       <c r="W101" s="3"/>
       <c r="X101" s="3"/>
       <c r="Y101" s="4" t="str">
-        <f>IF(COUNTA(B101:X101)=0,"",AVERAGE(B101:X101))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -11312,7 +11372,7 @@
       <c r="W102" s="3"/>
       <c r="X102" s="3"/>
       <c r="Y102" s="4" t="str">
-        <f>IF(COUNTA(B102:X102)=0,"",AVERAGE(B102:X102))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -11342,7 +11402,7 @@
       <c r="W103" s="3"/>
       <c r="X103" s="3"/>
       <c r="Y103" s="4" t="str">
-        <f>IF(COUNTA(B103:X103)=0,"",AVERAGE(B103:X103))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -11372,7 +11432,7 @@
       <c r="W104" s="3"/>
       <c r="X104" s="3"/>
       <c r="Y104" s="4" t="str">
-        <f>IF(COUNTA(B104:X104)=0,"",AVERAGE(B104:X104))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -11402,7 +11462,7 @@
       <c r="W105" s="3"/>
       <c r="X105" s="3"/>
       <c r="Y105" s="4" t="str">
-        <f>IF(COUNTA(B105:X105)=0,"",AVERAGE(B105:X105))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -11432,7 +11492,7 @@
       <c r="W106" s="3"/>
       <c r="X106" s="3"/>
       <c r="Y106" s="4" t="str">
-        <f>IF(COUNTA(B106:X106)=0,"",AVERAGE(B106:X106))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -11462,7 +11522,7 @@
       <c r="W107" s="3"/>
       <c r="X107" s="3"/>
       <c r="Y107" s="4" t="str">
-        <f>IF(COUNTA(B107:X107)=0,"",AVERAGE(B107:X107))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -11492,7 +11552,7 @@
       <c r="W108" s="3"/>
       <c r="X108" s="3"/>
       <c r="Y108" s="4" t="str">
-        <f>IF(COUNTA(B108:X108)=0,"",AVERAGE(B108:X108))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -11522,7 +11582,7 @@
       <c r="W109" s="3"/>
       <c r="X109" s="3"/>
       <c r="Y109" s="4" t="str">
-        <f>IF(COUNTA(B109:X109)=0,"",AVERAGE(B109:X109))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -11552,7 +11612,7 @@
       <c r="W110" s="3"/>
       <c r="X110" s="3"/>
       <c r="Y110" s="4" t="str">
-        <f>IF(COUNTA(B110:X110)=0,"",AVERAGE(B110:X110))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -11582,7 +11642,7 @@
       <c r="W111" s="3"/>
       <c r="X111" s="3"/>
       <c r="Y111" s="4" t="str">
-        <f>IF(COUNTA(B111:X111)=0,"",AVERAGE(B111:X111))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -11612,7 +11672,7 @@
       <c r="W112" s="3"/>
       <c r="X112" s="3"/>
       <c r="Y112" s="4" t="str">
-        <f>IF(COUNTA(B112:X112)=0,"",AVERAGE(B112:X112))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -11642,7 +11702,7 @@
       <c r="W113" s="3"/>
       <c r="X113" s="3"/>
       <c r="Y113" s="4" t="str">
-        <f>IF(COUNTA(B113:X113)=0,"",AVERAGE(B113:X113))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -11672,7 +11732,7 @@
       <c r="W114" s="3"/>
       <c r="X114" s="3"/>
       <c r="Y114" s="4" t="str">
-        <f>IF(COUNTA(B114:X114)=0,"",AVERAGE(B114:X114))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -11702,7 +11762,7 @@
       <c r="W115" s="3"/>
       <c r="X115" s="3"/>
       <c r="Y115" s="4" t="str">
-        <f>IF(COUNTA(B115:X115)=0,"",AVERAGE(B115:X115))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -11732,7 +11792,7 @@
       <c r="W116" s="3"/>
       <c r="X116" s="3"/>
       <c r="Y116" s="4" t="str">
-        <f>IF(COUNTA(B116:X116)=0,"",AVERAGE(B116:X116))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -11762,7 +11822,7 @@
       <c r="W117" s="3"/>
       <c r="X117" s="3"/>
       <c r="Y117" s="4" t="str">
-        <f>IF(COUNTA(B117:X117)=0,"",AVERAGE(B117:X117))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -11792,7 +11852,7 @@
       <c r="W118" s="3"/>
       <c r="X118" s="3"/>
       <c r="Y118" s="4" t="str">
-        <f>IF(COUNTA(B118:X118)=0,"",AVERAGE(B118:X118))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -11822,7 +11882,7 @@
       <c r="W119" s="3"/>
       <c r="X119" s="3"/>
       <c r="Y119" s="4" t="str">
-        <f>IF(COUNTA(B119:X119)=0,"",AVERAGE(B119:X119))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -11852,7 +11912,7 @@
       <c r="W120" s="3"/>
       <c r="X120" s="3"/>
       <c r="Y120" s="4" t="str">
-        <f>IF(COUNTA(B120:X120)=0,"",AVERAGE(B120:X120))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -11882,7 +11942,7 @@
       <c r="W121" s="3"/>
       <c r="X121" s="3"/>
       <c r="Y121" s="4" t="str">
-        <f>IF(COUNTA(B121:X121)=0,"",AVERAGE(B121:X121))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -11912,7 +11972,7 @@
       <c r="W122" s="3"/>
       <c r="X122" s="3"/>
       <c r="Y122" s="4" t="str">
-        <f>IF(COUNTA(B122:X122)=0,"",AVERAGE(B122:X122))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -11942,7 +12002,7 @@
       <c r="W123" s="3"/>
       <c r="X123" s="3"/>
       <c r="Y123" s="4" t="str">
-        <f>IF(COUNTA(B123:X123)=0,"",AVERAGE(B123:X123))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -11972,7 +12032,7 @@
       <c r="W124" s="3"/>
       <c r="X124" s="3"/>
       <c r="Y124" s="4" t="str">
-        <f>IF(COUNTA(B124:X124)=0,"",AVERAGE(B124:X124))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -12002,7 +12062,7 @@
       <c r="W125" s="3"/>
       <c r="X125" s="3"/>
       <c r="Y125" s="4" t="str">
-        <f>IF(COUNTA(B125:X125)=0,"",AVERAGE(B125:X125))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -12032,7 +12092,7 @@
       <c r="W126" s="3"/>
       <c r="X126" s="3"/>
       <c r="Y126" s="4" t="str">
-        <f>IF(COUNTA(B126:X126)=0,"",AVERAGE(B126:X126))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -12062,7 +12122,7 @@
       <c r="W127" s="3"/>
       <c r="X127" s="3"/>
       <c r="Y127" s="4" t="str">
-        <f>IF(COUNTA(B127:X127)=0,"",AVERAGE(B127:X127))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -12092,7 +12152,7 @@
       <c r="W128" s="3"/>
       <c r="X128" s="3"/>
       <c r="Y128" s="4" t="str">
-        <f>IF(COUNTA(B128:X128)=0,"",AVERAGE(B128:X128))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -12122,7 +12182,7 @@
       <c r="W129" s="3"/>
       <c r="X129" s="3"/>
       <c r="Y129" s="4" t="str">
-        <f>IF(COUNTA(B129:X129)=0,"",AVERAGE(B129:X129))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -12152,7 +12212,7 @@
       <c r="W130" s="3"/>
       <c r="X130" s="3"/>
       <c r="Y130" s="4" t="str">
-        <f>IF(COUNTA(B130:X130)=0,"",AVERAGE(B130:X130))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -12182,7 +12242,7 @@
       <c r="W131" s="3"/>
       <c r="X131" s="3"/>
       <c r="Y131" s="4" t="str">
-        <f>IF(COUNTA(B131:X131)=0,"",AVERAGE(B131:X131))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -12212,7 +12272,7 @@
       <c r="W132" s="3"/>
       <c r="X132" s="3"/>
       <c r="Y132" s="4" t="str">
-        <f>IF(COUNTA(B132:X132)=0,"",AVERAGE(B132:X132))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -12242,7 +12302,7 @@
       <c r="W133" s="3"/>
       <c r="X133" s="3"/>
       <c r="Y133" s="4" t="str">
-        <f>IF(COUNTA(B133:X133)=0,"",AVERAGE(B133:X133))</f>
+        <f t="shared" ref="Y133:Y196" si="2">IF(COUNTA(B133:X133)=0,"",AVERAGE(B133:X133))</f>
         <v/>
       </c>
     </row>
@@ -12272,7 +12332,7 @@
       <c r="W134" s="3"/>
       <c r="X134" s="3"/>
       <c r="Y134" s="4" t="str">
-        <f>IF(COUNTA(B134:X134)=0,"",AVERAGE(B134:X134))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -12302,7 +12362,7 @@
       <c r="W135" s="3"/>
       <c r="X135" s="3"/>
       <c r="Y135" s="4" t="str">
-        <f>IF(COUNTA(B135:X135)=0,"",AVERAGE(B135:X135))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -12332,7 +12392,7 @@
       <c r="W136" s="3"/>
       <c r="X136" s="3"/>
       <c r="Y136" s="4" t="str">
-        <f>IF(COUNTA(B136:X136)=0,"",AVERAGE(B136:X136))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -12362,7 +12422,7 @@
       <c r="W137" s="3"/>
       <c r="X137" s="3"/>
       <c r="Y137" s="4" t="str">
-        <f>IF(COUNTA(B137:X137)=0,"",AVERAGE(B137:X137))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -12392,7 +12452,7 @@
       <c r="W138" s="3"/>
       <c r="X138" s="3"/>
       <c r="Y138" s="4" t="str">
-        <f>IF(COUNTA(B138:X138)=0,"",AVERAGE(B138:X138))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -12422,7 +12482,7 @@
       <c r="W139" s="3"/>
       <c r="X139" s="3"/>
       <c r="Y139" s="4" t="str">
-        <f>IF(COUNTA(B139:X139)=0,"",AVERAGE(B139:X139))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -12452,7 +12512,7 @@
       <c r="W140" s="3"/>
       <c r="X140" s="3"/>
       <c r="Y140" s="4" t="str">
-        <f>IF(COUNTA(B140:X140)=0,"",AVERAGE(B140:X140))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -12482,7 +12542,7 @@
       <c r="W141" s="3"/>
       <c r="X141" s="3"/>
       <c r="Y141" s="4" t="str">
-        <f>IF(COUNTA(B141:X141)=0,"",AVERAGE(B141:X141))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -12512,7 +12572,7 @@
       <c r="W142" s="3"/>
       <c r="X142" s="3"/>
       <c r="Y142" s="4" t="str">
-        <f>IF(COUNTA(B142:X142)=0,"",AVERAGE(B142:X142))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -12542,7 +12602,7 @@
       <c r="W143" s="3"/>
       <c r="X143" s="3"/>
       <c r="Y143" s="4" t="str">
-        <f>IF(COUNTA(B143:X143)=0,"",AVERAGE(B143:X143))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -12572,7 +12632,7 @@
       <c r="W144" s="3"/>
       <c r="X144" s="3"/>
       <c r="Y144" s="4" t="str">
-        <f>IF(COUNTA(B144:X144)=0,"",AVERAGE(B144:X144))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -12602,7 +12662,7 @@
       <c r="W145" s="3"/>
       <c r="X145" s="3"/>
       <c r="Y145" s="4" t="str">
-        <f>IF(COUNTA(B145:X145)=0,"",AVERAGE(B145:X145))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -12632,7 +12692,7 @@
       <c r="W146" s="3"/>
       <c r="X146" s="3"/>
       <c r="Y146" s="4" t="str">
-        <f>IF(COUNTA(B146:X146)=0,"",AVERAGE(B146:X146))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -12662,7 +12722,7 @@
       <c r="W147" s="3"/>
       <c r="X147" s="3"/>
       <c r="Y147" s="4" t="str">
-        <f>IF(COUNTA(B147:X147)=0,"",AVERAGE(B147:X147))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -12692,7 +12752,7 @@
       <c r="W148" s="3"/>
       <c r="X148" s="3"/>
       <c r="Y148" s="4" t="str">
-        <f>IF(COUNTA(B148:X148)=0,"",AVERAGE(B148:X148))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -12722,7 +12782,7 @@
       <c r="W149" s="3"/>
       <c r="X149" s="3"/>
       <c r="Y149" s="4" t="str">
-        <f>IF(COUNTA(B149:X149)=0,"",AVERAGE(B149:X149))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -12752,7 +12812,7 @@
       <c r="W150" s="3"/>
       <c r="X150" s="3"/>
       <c r="Y150" s="4" t="str">
-        <f>IF(COUNTA(B150:X150)=0,"",AVERAGE(B150:X150))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -12782,7 +12842,7 @@
       <c r="W151" s="3"/>
       <c r="X151" s="3"/>
       <c r="Y151" s="4" t="str">
-        <f>IF(COUNTA(B151:X151)=0,"",AVERAGE(B151:X151))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -12812,7 +12872,7 @@
       <c r="W152" s="3"/>
       <c r="X152" s="3"/>
       <c r="Y152" s="4" t="str">
-        <f>IF(COUNTA(B152:X152)=0,"",AVERAGE(B152:X152))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -12842,7 +12902,7 @@
       <c r="W153" s="3"/>
       <c r="X153" s="3"/>
       <c r="Y153" s="4" t="str">
-        <f>IF(COUNTA(B153:X153)=0,"",AVERAGE(B153:X153))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -12872,7 +12932,7 @@
       <c r="W154" s="3"/>
       <c r="X154" s="3"/>
       <c r="Y154" s="4" t="str">
-        <f>IF(COUNTA(B154:X154)=0,"",AVERAGE(B154:X154))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -12902,7 +12962,7 @@
       <c r="W155" s="3"/>
       <c r="X155" s="3"/>
       <c r="Y155" s="4" t="str">
-        <f>IF(COUNTA(B155:X155)=0,"",AVERAGE(B155:X155))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -12932,7 +12992,7 @@
       <c r="W156" s="3"/>
       <c r="X156" s="3"/>
       <c r="Y156" s="4" t="str">
-        <f>IF(COUNTA(B156:X156)=0,"",AVERAGE(B156:X156))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -12962,7 +13022,7 @@
       <c r="W157" s="3"/>
       <c r="X157" s="3"/>
       <c r="Y157" s="4" t="str">
-        <f>IF(COUNTA(B157:X157)=0,"",AVERAGE(B157:X157))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -12992,7 +13052,7 @@
       <c r="W158" s="3"/>
       <c r="X158" s="3"/>
       <c r="Y158" s="4" t="str">
-        <f>IF(COUNTA(B158:X158)=0,"",AVERAGE(B158:X158))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -13022,7 +13082,7 @@
       <c r="W159" s="3"/>
       <c r="X159" s="3"/>
       <c r="Y159" s="4" t="str">
-        <f>IF(COUNTA(B159:X159)=0,"",AVERAGE(B159:X159))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -13052,7 +13112,7 @@
       <c r="W160" s="3"/>
       <c r="X160" s="3"/>
       <c r="Y160" s="4" t="str">
-        <f>IF(COUNTA(B160:X160)=0,"",AVERAGE(B160:X160))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -13082,7 +13142,7 @@
       <c r="W161" s="3"/>
       <c r="X161" s="3"/>
       <c r="Y161" s="4" t="str">
-        <f>IF(COUNTA(B161:X161)=0,"",AVERAGE(B161:X161))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -13112,7 +13172,7 @@
       <c r="W162" s="3"/>
       <c r="X162" s="3"/>
       <c r="Y162" s="4" t="str">
-        <f>IF(COUNTA(B162:X162)=0,"",AVERAGE(B162:X162))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -13142,7 +13202,7 @@
       <c r="W163" s="3"/>
       <c r="X163" s="3"/>
       <c r="Y163" s="4" t="str">
-        <f>IF(COUNTA(B163:X163)=0,"",AVERAGE(B163:X163))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -13172,7 +13232,7 @@
       <c r="W164" s="3"/>
       <c r="X164" s="3"/>
       <c r="Y164" s="4" t="str">
-        <f>IF(COUNTA(B164:X164)=0,"",AVERAGE(B164:X164))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -13202,7 +13262,7 @@
       <c r="W165" s="3"/>
       <c r="X165" s="3"/>
       <c r="Y165" s="4" t="str">
-        <f>IF(COUNTA(B165:X165)=0,"",AVERAGE(B165:X165))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -13232,7 +13292,7 @@
       <c r="W166" s="3"/>
       <c r="X166" s="3"/>
       <c r="Y166" s="4" t="str">
-        <f>IF(COUNTA(B166:X166)=0,"",AVERAGE(B166:X166))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -13262,7 +13322,7 @@
       <c r="W167" s="3"/>
       <c r="X167" s="3"/>
       <c r="Y167" s="4" t="str">
-        <f>IF(COUNTA(B167:X167)=0,"",AVERAGE(B167:X167))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -13292,7 +13352,7 @@
       <c r="W168" s="3"/>
       <c r="X168" s="3"/>
       <c r="Y168" s="4" t="str">
-        <f>IF(COUNTA(B168:X168)=0,"",AVERAGE(B168:X168))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -13322,7 +13382,7 @@
       <c r="W169" s="3"/>
       <c r="X169" s="3"/>
       <c r="Y169" s="4" t="str">
-        <f>IF(COUNTA(B169:X169)=0,"",AVERAGE(B169:X169))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -13352,7 +13412,7 @@
       <c r="W170" s="3"/>
       <c r="X170" s="3"/>
       <c r="Y170" s="4" t="str">
-        <f>IF(COUNTA(B170:X170)=0,"",AVERAGE(B170:X170))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -13382,7 +13442,7 @@
       <c r="W171" s="3"/>
       <c r="X171" s="3"/>
       <c r="Y171" s="4" t="str">
-        <f>IF(COUNTA(B171:X171)=0,"",AVERAGE(B171:X171))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -13412,7 +13472,7 @@
       <c r="W172" s="3"/>
       <c r="X172" s="3"/>
       <c r="Y172" s="4" t="str">
-        <f>IF(COUNTA(B172:X172)=0,"",AVERAGE(B172:X172))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -13442,7 +13502,7 @@
       <c r="W173" s="3"/>
       <c r="X173" s="3"/>
       <c r="Y173" s="4" t="str">
-        <f>IF(COUNTA(B173:X173)=0,"",AVERAGE(B173:X173))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -13472,7 +13532,7 @@
       <c r="W174" s="3"/>
       <c r="X174" s="3"/>
       <c r="Y174" s="4" t="str">
-        <f>IF(COUNTA(B174:X174)=0,"",AVERAGE(B174:X174))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -13502,7 +13562,7 @@
       <c r="W175" s="3"/>
       <c r="X175" s="3"/>
       <c r="Y175" s="4" t="str">
-        <f>IF(COUNTA(B175:X175)=0,"",AVERAGE(B175:X175))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -13532,7 +13592,7 @@
       <c r="W176" s="3"/>
       <c r="X176" s="3"/>
       <c r="Y176" s="4" t="str">
-        <f>IF(COUNTA(B176:X176)=0,"",AVERAGE(B176:X176))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -13562,7 +13622,7 @@
       <c r="W177" s="3"/>
       <c r="X177" s="3"/>
       <c r="Y177" s="4" t="str">
-        <f>IF(COUNTA(B177:X177)=0,"",AVERAGE(B177:X177))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -13592,7 +13652,7 @@
       <c r="W178" s="3"/>
       <c r="X178" s="3"/>
       <c r="Y178" s="4" t="str">
-        <f>IF(COUNTA(B178:X178)=0,"",AVERAGE(B178:X178))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -13622,7 +13682,7 @@
       <c r="W179" s="3"/>
       <c r="X179" s="3"/>
       <c r="Y179" s="4" t="str">
-        <f>IF(COUNTA(B179:X179)=0,"",AVERAGE(B179:X179))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -13652,7 +13712,7 @@
       <c r="W180" s="3"/>
       <c r="X180" s="3"/>
       <c r="Y180" s="4" t="str">
-        <f>IF(COUNTA(B180:X180)=0,"",AVERAGE(B180:X180))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -13682,7 +13742,7 @@
       <c r="W181" s="3"/>
       <c r="X181" s="3"/>
       <c r="Y181" s="4" t="str">
-        <f>IF(COUNTA(B181:X181)=0,"",AVERAGE(B181:X181))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -13712,7 +13772,7 @@
       <c r="W182" s="3"/>
       <c r="X182" s="3"/>
       <c r="Y182" s="4" t="str">
-        <f>IF(COUNTA(B182:X182)=0,"",AVERAGE(B182:X182))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -13742,7 +13802,7 @@
       <c r="W183" s="3"/>
       <c r="X183" s="3"/>
       <c r="Y183" s="4" t="str">
-        <f>IF(COUNTA(B183:X183)=0,"",AVERAGE(B183:X183))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -13772,7 +13832,7 @@
       <c r="W184" s="3"/>
       <c r="X184" s="3"/>
       <c r="Y184" s="4" t="str">
-        <f>IF(COUNTA(B184:X184)=0,"",AVERAGE(B184:X184))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -13802,7 +13862,7 @@
       <c r="W185" s="3"/>
       <c r="X185" s="3"/>
       <c r="Y185" s="4" t="str">
-        <f>IF(COUNTA(B185:X185)=0,"",AVERAGE(B185:X185))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -13832,7 +13892,7 @@
       <c r="W186" s="3"/>
       <c r="X186" s="3"/>
       <c r="Y186" s="4" t="str">
-        <f>IF(COUNTA(B186:X186)=0,"",AVERAGE(B186:X186))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -13862,7 +13922,7 @@
       <c r="W187" s="3"/>
       <c r="X187" s="3"/>
       <c r="Y187" s="4" t="str">
-        <f>IF(COUNTA(B187:X187)=0,"",AVERAGE(B187:X187))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -13892,7 +13952,7 @@
       <c r="W188" s="3"/>
       <c r="X188" s="3"/>
       <c r="Y188" s="4" t="str">
-        <f>IF(COUNTA(B188:X188)=0,"",AVERAGE(B188:X188))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -13922,7 +13982,7 @@
       <c r="W189" s="3"/>
       <c r="X189" s="3"/>
       <c r="Y189" s="4" t="str">
-        <f>IF(COUNTA(B189:X189)=0,"",AVERAGE(B189:X189))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -13952,7 +14012,7 @@
       <c r="W190" s="3"/>
       <c r="X190" s="3"/>
       <c r="Y190" s="4" t="str">
-        <f>IF(COUNTA(B190:X190)=0,"",AVERAGE(B190:X190))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -13982,7 +14042,7 @@
       <c r="W191" s="3"/>
       <c r="X191" s="3"/>
       <c r="Y191" s="4" t="str">
-        <f>IF(COUNTA(B191:X191)=0,"",AVERAGE(B191:X191))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -14012,7 +14072,7 @@
       <c r="W192" s="3"/>
       <c r="X192" s="3"/>
       <c r="Y192" s="4" t="str">
-        <f>IF(COUNTA(B192:X192)=0,"",AVERAGE(B192:X192))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -14042,7 +14102,7 @@
       <c r="W193" s="3"/>
       <c r="X193" s="3"/>
       <c r="Y193" s="4" t="str">
-        <f>IF(COUNTA(B193:X193)=0,"",AVERAGE(B193:X193))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -14072,7 +14132,7 @@
       <c r="W194" s="3"/>
       <c r="X194" s="3"/>
       <c r="Y194" s="4" t="str">
-        <f>IF(COUNTA(B194:X194)=0,"",AVERAGE(B194:X194))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -14102,7 +14162,7 @@
       <c r="W195" s="3"/>
       <c r="X195" s="3"/>
       <c r="Y195" s="4" t="str">
-        <f>IF(COUNTA(B195:X195)=0,"",AVERAGE(B195:X195))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -14132,7 +14192,7 @@
       <c r="W196" s="3"/>
       <c r="X196" s="3"/>
       <c r="Y196" s="4" t="str">
-        <f>IF(COUNTA(B196:X196)=0,"",AVERAGE(B196:X196))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -14162,7 +14222,7 @@
       <c r="W197" s="3"/>
       <c r="X197" s="3"/>
       <c r="Y197" s="4" t="str">
-        <f>IF(COUNTA(B197:X197)=0,"",AVERAGE(B197:X197))</f>
+        <f t="shared" ref="Y197:Y260" si="3">IF(COUNTA(B197:X197)=0,"",AVERAGE(B197:X197))</f>
         <v/>
       </c>
     </row>
@@ -14192,7 +14252,7 @@
       <c r="W198" s="3"/>
       <c r="X198" s="3"/>
       <c r="Y198" s="4" t="str">
-        <f>IF(COUNTA(B198:X198)=0,"",AVERAGE(B198:X198))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -14222,7 +14282,7 @@
       <c r="W199" s="3"/>
       <c r="X199" s="3"/>
       <c r="Y199" s="4" t="str">
-        <f>IF(COUNTA(B199:X199)=0,"",AVERAGE(B199:X199))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -14252,7 +14312,7 @@
       <c r="W200" s="3"/>
       <c r="X200" s="3"/>
       <c r="Y200" s="4" t="str">
-        <f>IF(COUNTA(B200:X200)=0,"",AVERAGE(B200:X200))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -14282,7 +14342,7 @@
       <c r="W201" s="3"/>
       <c r="X201" s="3"/>
       <c r="Y201" s="4" t="str">
-        <f>IF(COUNTA(B201:X201)=0,"",AVERAGE(B201:X201))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -14312,7 +14372,7 @@
       <c r="W202" s="3"/>
       <c r="X202" s="3"/>
       <c r="Y202" s="4" t="str">
-        <f>IF(COUNTA(B202:X202)=0,"",AVERAGE(B202:X202))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -14342,7 +14402,7 @@
       <c r="W203" s="3"/>
       <c r="X203" s="3"/>
       <c r="Y203" s="4" t="str">
-        <f>IF(COUNTA(B203:X203)=0,"",AVERAGE(B203:X203))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -14372,7 +14432,7 @@
       <c r="W204" s="3"/>
       <c r="X204" s="3"/>
       <c r="Y204" s="4" t="str">
-        <f>IF(COUNTA(B204:X204)=0,"",AVERAGE(B204:X204))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -14402,7 +14462,7 @@
       <c r="W205" s="3"/>
       <c r="X205" s="3"/>
       <c r="Y205" s="4" t="str">
-        <f>IF(COUNTA(B205:X205)=0,"",AVERAGE(B205:X205))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -14432,7 +14492,7 @@
       <c r="W206" s="3"/>
       <c r="X206" s="3"/>
       <c r="Y206" s="4" t="str">
-        <f>IF(COUNTA(B206:X206)=0,"",AVERAGE(B206:X206))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -14462,7 +14522,7 @@
       <c r="W207" s="3"/>
       <c r="X207" s="3"/>
       <c r="Y207" s="4" t="str">
-        <f>IF(COUNTA(B207:X207)=0,"",AVERAGE(B207:X207))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -14492,7 +14552,7 @@
       <c r="W208" s="3"/>
       <c r="X208" s="3"/>
       <c r="Y208" s="4" t="str">
-        <f>IF(COUNTA(B208:X208)=0,"",AVERAGE(B208:X208))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -14522,7 +14582,7 @@
       <c r="W209" s="3"/>
       <c r="X209" s="3"/>
       <c r="Y209" s="4" t="str">
-        <f>IF(COUNTA(B209:X209)=0,"",AVERAGE(B209:X209))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -14552,7 +14612,7 @@
       <c r="W210" s="3"/>
       <c r="X210" s="3"/>
       <c r="Y210" s="4" t="str">
-        <f>IF(COUNTA(B210:X210)=0,"",AVERAGE(B210:X210))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -14582,7 +14642,7 @@
       <c r="W211" s="3"/>
       <c r="X211" s="3"/>
       <c r="Y211" s="4" t="str">
-        <f>IF(COUNTA(B211:X211)=0,"",AVERAGE(B211:X211))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -14612,7 +14672,7 @@
       <c r="W212" s="3"/>
       <c r="X212" s="3"/>
       <c r="Y212" s="4" t="str">
-        <f>IF(COUNTA(B212:X212)=0,"",AVERAGE(B212:X212))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -14642,7 +14702,7 @@
       <c r="W213" s="3"/>
       <c r="X213" s="3"/>
       <c r="Y213" s="4" t="str">
-        <f>IF(COUNTA(B213:X213)=0,"",AVERAGE(B213:X213))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -14672,7 +14732,7 @@
       <c r="W214" s="3"/>
       <c r="X214" s="3"/>
       <c r="Y214" s="4" t="str">
-        <f>IF(COUNTA(B214:X214)=0,"",AVERAGE(B214:X214))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -14702,7 +14762,7 @@
       <c r="W215" s="3"/>
       <c r="X215" s="3"/>
       <c r="Y215" s="4" t="str">
-        <f>IF(COUNTA(B215:X215)=0,"",AVERAGE(B215:X215))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -14732,7 +14792,7 @@
       <c r="W216" s="3"/>
       <c r="X216" s="3"/>
       <c r="Y216" s="4" t="str">
-        <f>IF(COUNTA(B216:X216)=0,"",AVERAGE(B216:X216))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -14762,7 +14822,7 @@
       <c r="W217" s="3"/>
       <c r="X217" s="3"/>
       <c r="Y217" s="4" t="str">
-        <f>IF(COUNTA(B217:X217)=0,"",AVERAGE(B217:X217))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -14792,7 +14852,7 @@
       <c r="W218" s="3"/>
       <c r="X218" s="3"/>
       <c r="Y218" s="4" t="str">
-        <f>IF(COUNTA(B218:X218)=0,"",AVERAGE(B218:X218))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -14822,7 +14882,7 @@
       <c r="W219" s="3"/>
       <c r="X219" s="3"/>
       <c r="Y219" s="4" t="str">
-        <f>IF(COUNTA(B219:X219)=0,"",AVERAGE(B219:X219))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -14852,7 +14912,7 @@
       <c r="W220" s="3"/>
       <c r="X220" s="3"/>
       <c r="Y220" s="4" t="str">
-        <f>IF(COUNTA(B220:X220)=0,"",AVERAGE(B220:X220))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -14882,7 +14942,7 @@
       <c r="W221" s="3"/>
       <c r="X221" s="3"/>
       <c r="Y221" s="4" t="str">
-        <f>IF(COUNTA(B221:X221)=0,"",AVERAGE(B221:X221))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -14912,7 +14972,7 @@
       <c r="W222" s="3"/>
       <c r="X222" s="3"/>
       <c r="Y222" s="4" t="str">
-        <f>IF(COUNTA(B222:X222)=0,"",AVERAGE(B222:X222))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -14942,7 +15002,7 @@
       <c r="W223" s="3"/>
       <c r="X223" s="3"/>
       <c r="Y223" s="4" t="str">
-        <f>IF(COUNTA(B223:X223)=0,"",AVERAGE(B223:X223))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -14972,7 +15032,7 @@
       <c r="W224" s="3"/>
       <c r="X224" s="3"/>
       <c r="Y224" s="4" t="str">
-        <f>IF(COUNTA(B224:X224)=0,"",AVERAGE(B224:X224))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -15002,7 +15062,7 @@
       <c r="W225" s="3"/>
       <c r="X225" s="3"/>
       <c r="Y225" s="4" t="str">
-        <f>IF(COUNTA(B225:X225)=0,"",AVERAGE(B225:X225))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -15032,7 +15092,7 @@
       <c r="W226" s="3"/>
       <c r="X226" s="3"/>
       <c r="Y226" s="4" t="str">
-        <f>IF(COUNTA(B226:X226)=0,"",AVERAGE(B226:X226))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -15062,7 +15122,7 @@
       <c r="W227" s="3"/>
       <c r="X227" s="3"/>
       <c r="Y227" s="4" t="str">
-        <f>IF(COUNTA(B227:X227)=0,"",AVERAGE(B227:X227))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -15092,7 +15152,7 @@
       <c r="W228" s="3"/>
       <c r="X228" s="3"/>
       <c r="Y228" s="4" t="str">
-        <f>IF(COUNTA(B228:X228)=0,"",AVERAGE(B228:X228))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -15122,7 +15182,7 @@
       <c r="W229" s="3"/>
       <c r="X229" s="3"/>
       <c r="Y229" s="4" t="str">
-        <f>IF(COUNTA(B229:X229)=0,"",AVERAGE(B229:X229))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -15152,7 +15212,7 @@
       <c r="W230" s="3"/>
       <c r="X230" s="3"/>
       <c r="Y230" s="4" t="str">
-        <f>IF(COUNTA(B230:X230)=0,"",AVERAGE(B230:X230))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -15182,7 +15242,7 @@
       <c r="W231" s="3"/>
       <c r="X231" s="3"/>
       <c r="Y231" s="4" t="str">
-        <f>IF(COUNTA(B231:X231)=0,"",AVERAGE(B231:X231))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -15212,7 +15272,7 @@
       <c r="W232" s="3"/>
       <c r="X232" s="3"/>
       <c r="Y232" s="4" t="str">
-        <f>IF(COUNTA(B232:X232)=0,"",AVERAGE(B232:X232))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -15242,7 +15302,7 @@
       <c r="W233" s="3"/>
       <c r="X233" s="3"/>
       <c r="Y233" s="4" t="str">
-        <f>IF(COUNTA(B233:X233)=0,"",AVERAGE(B233:X233))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -15272,7 +15332,7 @@
       <c r="W234" s="3"/>
       <c r="X234" s="3"/>
       <c r="Y234" s="4" t="str">
-        <f>IF(COUNTA(B234:X234)=0,"",AVERAGE(B234:X234))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -15302,7 +15362,7 @@
       <c r="W235" s="3"/>
       <c r="X235" s="3"/>
       <c r="Y235" s="4" t="str">
-        <f>IF(COUNTA(B235:X235)=0,"",AVERAGE(B235:X235))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -15332,7 +15392,7 @@
       <c r="W236" s="3"/>
       <c r="X236" s="3"/>
       <c r="Y236" s="4" t="str">
-        <f>IF(COUNTA(B236:X236)=0,"",AVERAGE(B236:X236))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -15362,7 +15422,7 @@
       <c r="W237" s="3"/>
       <c r="X237" s="3"/>
       <c r="Y237" s="4" t="str">
-        <f>IF(COUNTA(B237:X237)=0,"",AVERAGE(B237:X237))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -15392,7 +15452,7 @@
       <c r="W238" s="3"/>
       <c r="X238" s="3"/>
       <c r="Y238" s="4" t="str">
-        <f>IF(COUNTA(B238:X238)=0,"",AVERAGE(B238:X238))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -15422,7 +15482,7 @@
       <c r="W239" s="3"/>
       <c r="X239" s="3"/>
       <c r="Y239" s="4" t="str">
-        <f>IF(COUNTA(B239:X239)=0,"",AVERAGE(B239:X239))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -15452,7 +15512,7 @@
       <c r="W240" s="3"/>
       <c r="X240" s="3"/>
       <c r="Y240" s="4" t="str">
-        <f>IF(COUNTA(B240:X240)=0,"",AVERAGE(B240:X240))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -15482,7 +15542,7 @@
       <c r="W241" s="3"/>
       <c r="X241" s="3"/>
       <c r="Y241" s="4" t="str">
-        <f>IF(COUNTA(B241:X241)=0,"",AVERAGE(B241:X241))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -15512,7 +15572,7 @@
       <c r="W242" s="3"/>
       <c r="X242" s="3"/>
       <c r="Y242" s="4" t="str">
-        <f>IF(COUNTA(B242:X242)=0,"",AVERAGE(B242:X242))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -15542,7 +15602,7 @@
       <c r="W243" s="3"/>
       <c r="X243" s="3"/>
       <c r="Y243" s="4" t="str">
-        <f>IF(COUNTA(B243:X243)=0,"",AVERAGE(B243:X243))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -15572,7 +15632,7 @@
       <c r="W244" s="3"/>
       <c r="X244" s="3"/>
       <c r="Y244" s="4" t="str">
-        <f>IF(COUNTA(B244:X244)=0,"",AVERAGE(B244:X244))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -15602,7 +15662,7 @@
       <c r="W245" s="3"/>
       <c r="X245" s="3"/>
       <c r="Y245" s="4" t="str">
-        <f>IF(COUNTA(B245:X245)=0,"",AVERAGE(B245:X245))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -15632,7 +15692,7 @@
       <c r="W246" s="3"/>
       <c r="X246" s="3"/>
       <c r="Y246" s="4" t="str">
-        <f>IF(COUNTA(B246:X246)=0,"",AVERAGE(B246:X246))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -15662,7 +15722,7 @@
       <c r="W247" s="3"/>
       <c r="X247" s="3"/>
       <c r="Y247" s="4" t="str">
-        <f>IF(COUNTA(B247:X247)=0,"",AVERAGE(B247:X247))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -15692,7 +15752,7 @@
       <c r="W248" s="3"/>
       <c r="X248" s="3"/>
       <c r="Y248" s="4" t="str">
-        <f>IF(COUNTA(B248:X248)=0,"",AVERAGE(B248:X248))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -15722,7 +15782,7 @@
       <c r="W249" s="3"/>
       <c r="X249" s="3"/>
       <c r="Y249" s="4" t="str">
-        <f>IF(COUNTA(B249:X249)=0,"",AVERAGE(B249:X249))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -15752,7 +15812,7 @@
       <c r="W250" s="3"/>
       <c r="X250" s="3"/>
       <c r="Y250" s="4" t="str">
-        <f>IF(COUNTA(B250:X250)=0,"",AVERAGE(B250:X250))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -15782,7 +15842,7 @@
       <c r="W251" s="3"/>
       <c r="X251" s="3"/>
       <c r="Y251" s="4" t="str">
-        <f>IF(COUNTA(B251:X251)=0,"",AVERAGE(B251:X251))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -15812,7 +15872,7 @@
       <c r="W252" s="3"/>
       <c r="X252" s="3"/>
       <c r="Y252" s="4" t="str">
-        <f>IF(COUNTA(B252:X252)=0,"",AVERAGE(B252:X252))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -15842,7 +15902,7 @@
       <c r="W253" s="3"/>
       <c r="X253" s="3"/>
       <c r="Y253" s="4" t="str">
-        <f>IF(COUNTA(B253:X253)=0,"",AVERAGE(B253:X253))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -15872,7 +15932,7 @@
       <c r="W254" s="3"/>
       <c r="X254" s="3"/>
       <c r="Y254" s="4" t="str">
-        <f>IF(COUNTA(B254:X254)=0,"",AVERAGE(B254:X254))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -15902,7 +15962,7 @@
       <c r="W255" s="3"/>
       <c r="X255" s="3"/>
       <c r="Y255" s="4" t="str">
-        <f>IF(COUNTA(B255:X255)=0,"",AVERAGE(B255:X255))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -15932,7 +15992,7 @@
       <c r="W256" s="3"/>
       <c r="X256" s="3"/>
       <c r="Y256" s="4" t="str">
-        <f>IF(COUNTA(B256:X256)=0,"",AVERAGE(B256:X256))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -15962,7 +16022,7 @@
       <c r="W257" s="3"/>
       <c r="X257" s="3"/>
       <c r="Y257" s="4" t="str">
-        <f>IF(COUNTA(B257:X257)=0,"",AVERAGE(B257:X257))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -15992,7 +16052,7 @@
       <c r="W258" s="3"/>
       <c r="X258" s="3"/>
       <c r="Y258" s="4" t="str">
-        <f>IF(COUNTA(B258:X258)=0,"",AVERAGE(B258:X258))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -16022,7 +16082,7 @@
       <c r="W259" s="3"/>
       <c r="X259" s="3"/>
       <c r="Y259" s="4" t="str">
-        <f>IF(COUNTA(B259:X259)=0,"",AVERAGE(B259:X259))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -16052,7 +16112,7 @@
       <c r="W260" s="3"/>
       <c r="X260" s="3"/>
       <c r="Y260" s="4" t="str">
-        <f>IF(COUNTA(B260:X260)=0,"",AVERAGE(B260:X260))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -16082,7 +16142,7 @@
       <c r="W261" s="3"/>
       <c r="X261" s="3"/>
       <c r="Y261" s="4" t="str">
-        <f>IF(COUNTA(B261:X261)=0,"",AVERAGE(B261:X261))</f>
+        <f t="shared" ref="Y261:Y324" si="4">IF(COUNTA(B261:X261)=0,"",AVERAGE(B261:X261))</f>
         <v/>
       </c>
     </row>
@@ -16112,7 +16172,7 @@
       <c r="W262" s="3"/>
       <c r="X262" s="3"/>
       <c r="Y262" s="4" t="str">
-        <f>IF(COUNTA(B262:X262)=0,"",AVERAGE(B262:X262))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
@@ -16142,7 +16202,7 @@
       <c r="W263" s="3"/>
       <c r="X263" s="3"/>
       <c r="Y263" s="4" t="str">
-        <f>IF(COUNTA(B263:X263)=0,"",AVERAGE(B263:X263))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
@@ -16172,7 +16232,7 @@
       <c r="W264" s="3"/>
       <c r="X264" s="3"/>
       <c r="Y264" s="4" t="str">
-        <f>IF(COUNTA(B264:X264)=0,"",AVERAGE(B264:X264))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
@@ -16202,7 +16262,7 @@
       <c r="W265" s="3"/>
       <c r="X265" s="3"/>
       <c r="Y265" s="4" t="str">
-        <f>IF(COUNTA(B265:X265)=0,"",AVERAGE(B265:X265))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
@@ -16232,7 +16292,7 @@
       <c r="W266" s="3"/>
       <c r="X266" s="3"/>
       <c r="Y266" s="4" t="str">
-        <f>IF(COUNTA(B266:X266)=0,"",AVERAGE(B266:X266))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
@@ -16262,7 +16322,7 @@
       <c r="W267" s="3"/>
       <c r="X267" s="3"/>
       <c r="Y267" s="4" t="str">
-        <f>IF(COUNTA(B267:X267)=0,"",AVERAGE(B267:X267))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
@@ -16292,7 +16352,7 @@
       <c r="W268" s="3"/>
       <c r="X268" s="3"/>
       <c r="Y268" s="4" t="str">
-        <f>IF(COUNTA(B268:X268)=0,"",AVERAGE(B268:X268))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
@@ -16322,7 +16382,7 @@
       <c r="W269" s="3"/>
       <c r="X269" s="3"/>
       <c r="Y269" s="4" t="str">
-        <f>IF(COUNTA(B269:X269)=0,"",AVERAGE(B269:X269))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
@@ -16352,7 +16412,7 @@
       <c r="W270" s="3"/>
       <c r="X270" s="3"/>
       <c r="Y270" s="4" t="str">
-        <f>IF(COUNTA(B270:X270)=0,"",AVERAGE(B270:X270))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
@@ -16382,7 +16442,7 @@
       <c r="W271" s="3"/>
       <c r="X271" s="3"/>
       <c r="Y271" s="4" t="str">
-        <f>IF(COUNTA(B271:X271)=0,"",AVERAGE(B271:X271))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
@@ -16412,7 +16472,7 @@
       <c r="W272" s="3"/>
       <c r="X272" s="3"/>
       <c r="Y272" s="4" t="str">
-        <f>IF(COUNTA(B272:X272)=0,"",AVERAGE(B272:X272))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
@@ -16442,7 +16502,7 @@
       <c r="W273" s="3"/>
       <c r="X273" s="3"/>
       <c r="Y273" s="4" t="str">
-        <f>IF(COUNTA(B273:X273)=0,"",AVERAGE(B273:X273))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
@@ -16472,7 +16532,7 @@
       <c r="W274" s="3"/>
       <c r="X274" s="3"/>
       <c r="Y274" s="4" t="str">
-        <f>IF(COUNTA(B274:X274)=0,"",AVERAGE(B274:X274))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
@@ -16502,7 +16562,7 @@
       <c r="W275" s="3"/>
       <c r="X275" s="3"/>
       <c r="Y275" s="4" t="str">
-        <f>IF(COUNTA(B275:X275)=0,"",AVERAGE(B275:X275))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
@@ -16532,7 +16592,7 @@
       <c r="W276" s="3"/>
       <c r="X276" s="3"/>
       <c r="Y276" s="4" t="str">
-        <f>IF(COUNTA(B276:X276)=0,"",AVERAGE(B276:X276))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
@@ -16562,7 +16622,7 @@
       <c r="W277" s="3"/>
       <c r="X277" s="3"/>
       <c r="Y277" s="4" t="str">
-        <f>IF(COUNTA(B277:X277)=0,"",AVERAGE(B277:X277))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
@@ -16592,7 +16652,7 @@
       <c r="W278" s="3"/>
       <c r="X278" s="3"/>
       <c r="Y278" s="4" t="str">
-        <f>IF(COUNTA(B278:X278)=0,"",AVERAGE(B278:X278))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
@@ -16622,7 +16682,7 @@
       <c r="W279" s="3"/>
       <c r="X279" s="3"/>
       <c r="Y279" s="4" t="str">
-        <f>IF(COUNTA(B279:X279)=0,"",AVERAGE(B279:X279))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
@@ -16652,7 +16712,7 @@
       <c r="W280" s="3"/>
       <c r="X280" s="3"/>
       <c r="Y280" s="4" t="str">
-        <f>IF(COUNTA(B280:X280)=0,"",AVERAGE(B280:X280))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
@@ -16682,7 +16742,7 @@
       <c r="W281" s="3"/>
       <c r="X281" s="3"/>
       <c r="Y281" s="4" t="str">
-        <f>IF(COUNTA(B281:X281)=0,"",AVERAGE(B281:X281))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
@@ -16712,7 +16772,7 @@
       <c r="W282" s="3"/>
       <c r="X282" s="3"/>
       <c r="Y282" s="4" t="str">
-        <f>IF(COUNTA(B282:X282)=0,"",AVERAGE(B282:X282))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
@@ -16742,7 +16802,7 @@
       <c r="W283" s="3"/>
       <c r="X283" s="3"/>
       <c r="Y283" s="4" t="str">
-        <f>IF(COUNTA(B283:X283)=0,"",AVERAGE(B283:X283))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
@@ -16772,7 +16832,7 @@
       <c r="W284" s="3"/>
       <c r="X284" s="3"/>
       <c r="Y284" s="4" t="str">
-        <f>IF(COUNTA(B284:X284)=0,"",AVERAGE(B284:X284))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
@@ -16802,7 +16862,7 @@
       <c r="W285" s="3"/>
       <c r="X285" s="3"/>
       <c r="Y285" s="4" t="str">
-        <f>IF(COUNTA(B285:X285)=0,"",AVERAGE(B285:X285))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
@@ -16832,7 +16892,7 @@
       <c r="W286" s="3"/>
       <c r="X286" s="3"/>
       <c r="Y286" s="4" t="str">
-        <f>IF(COUNTA(B286:X286)=0,"",AVERAGE(B286:X286))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
@@ -16862,7 +16922,7 @@
       <c r="W287" s="3"/>
       <c r="X287" s="3"/>
       <c r="Y287" s="4" t="str">
-        <f>IF(COUNTA(B287:X287)=0,"",AVERAGE(B287:X287))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
@@ -16892,7 +16952,7 @@
       <c r="W288" s="3"/>
       <c r="X288" s="3"/>
       <c r="Y288" s="4" t="str">
-        <f>IF(COUNTA(B288:X288)=0,"",AVERAGE(B288:X288))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
@@ -16922,7 +16982,7 @@
       <c r="W289" s="3"/>
       <c r="X289" s="3"/>
       <c r="Y289" s="4" t="str">
-        <f>IF(COUNTA(B289:X289)=0,"",AVERAGE(B289:X289))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
@@ -16952,7 +17012,7 @@
       <c r="W290" s="3"/>
       <c r="X290" s="3"/>
       <c r="Y290" s="4" t="str">
-        <f>IF(COUNTA(B290:X290)=0,"",AVERAGE(B290:X290))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
@@ -16982,7 +17042,7 @@
       <c r="W291" s="3"/>
       <c r="X291" s="3"/>
       <c r="Y291" s="4" t="str">
-        <f>IF(COUNTA(B291:X291)=0,"",AVERAGE(B291:X291))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
@@ -17012,7 +17072,7 @@
       <c r="W292" s="3"/>
       <c r="X292" s="3"/>
       <c r="Y292" s="4" t="str">
-        <f>IF(COUNTA(B292:X292)=0,"",AVERAGE(B292:X292))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
@@ -17042,7 +17102,7 @@
       <c r="W293" s="3"/>
       <c r="X293" s="3"/>
       <c r="Y293" s="4" t="str">
-        <f>IF(COUNTA(B293:X293)=0,"",AVERAGE(B293:X293))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
@@ -17072,7 +17132,7 @@
       <c r="W294" s="3"/>
       <c r="X294" s="3"/>
       <c r="Y294" s="4" t="str">
-        <f>IF(COUNTA(B294:X294)=0,"",AVERAGE(B294:X294))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
@@ -17102,7 +17162,7 @@
       <c r="W295" s="3"/>
       <c r="X295" s="3"/>
       <c r="Y295" s="4" t="str">
-        <f>IF(COUNTA(B295:X295)=0,"",AVERAGE(B295:X295))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
@@ -17132,7 +17192,7 @@
       <c r="W296" s="3"/>
       <c r="X296" s="3"/>
       <c r="Y296" s="4" t="str">
-        <f>IF(COUNTA(B296:X296)=0,"",AVERAGE(B296:X296))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
@@ -17162,7 +17222,7 @@
       <c r="W297" s="3"/>
       <c r="X297" s="3"/>
       <c r="Y297" s="4" t="str">
-        <f>IF(COUNTA(B297:X297)=0,"",AVERAGE(B297:X297))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
@@ -17192,7 +17252,7 @@
       <c r="W298" s="3"/>
       <c r="X298" s="3"/>
       <c r="Y298" s="4" t="str">
-        <f>IF(COUNTA(B298:X298)=0,"",AVERAGE(B298:X298))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
@@ -17222,7 +17282,7 @@
       <c r="W299" s="3"/>
       <c r="X299" s="3"/>
       <c r="Y299" s="4" t="str">
-        <f>IF(COUNTA(B299:X299)=0,"",AVERAGE(B299:X299))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
@@ -17252,7 +17312,7 @@
       <c r="W300" s="3"/>
       <c r="X300" s="3"/>
       <c r="Y300" s="4" t="str">
-        <f>IF(COUNTA(B300:X300)=0,"",AVERAGE(B300:X300))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
@@ -17282,7 +17342,7 @@
       <c r="W301" s="3"/>
       <c r="X301" s="3"/>
       <c r="Y301" s="4" t="str">
-        <f>IF(COUNTA(B301:X301)=0,"",AVERAGE(B301:X301))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
@@ -17312,7 +17372,7 @@
       <c r="W302" s="3"/>
       <c r="X302" s="3"/>
       <c r="Y302" s="4" t="str">
-        <f>IF(COUNTA(B302:X302)=0,"",AVERAGE(B302:X302))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
@@ -17342,7 +17402,7 @@
       <c r="W303" s="3"/>
       <c r="X303" s="3"/>
       <c r="Y303" s="4" t="str">
-        <f>IF(COUNTA(B303:X303)=0,"",AVERAGE(B303:X303))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
@@ -17372,7 +17432,7 @@
       <c r="W304" s="3"/>
       <c r="X304" s="3"/>
       <c r="Y304" s="4" t="str">
-        <f>IF(COUNTA(B304:X304)=0,"",AVERAGE(B304:X304))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
@@ -17402,7 +17462,7 @@
       <c r="W305" s="3"/>
       <c r="X305" s="3"/>
       <c r="Y305" s="4" t="str">
-        <f>IF(COUNTA(B305:X305)=0,"",AVERAGE(B305:X305))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
@@ -17432,7 +17492,7 @@
       <c r="W306" s="3"/>
       <c r="X306" s="3"/>
       <c r="Y306" s="4" t="str">
-        <f>IF(COUNTA(B306:X306)=0,"",AVERAGE(B306:X306))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
@@ -17462,7 +17522,7 @@
       <c r="W307" s="3"/>
       <c r="X307" s="3"/>
       <c r="Y307" s="4" t="str">
-        <f>IF(COUNTA(B307:X307)=0,"",AVERAGE(B307:X307))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
@@ -17492,7 +17552,7 @@
       <c r="W308" s="3"/>
       <c r="X308" s="3"/>
       <c r="Y308" s="4" t="str">
-        <f>IF(COUNTA(B308:X308)=0,"",AVERAGE(B308:X308))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
@@ -17522,7 +17582,7 @@
       <c r="W309" s="3"/>
       <c r="X309" s="3"/>
       <c r="Y309" s="4" t="str">
-        <f>IF(COUNTA(B309:X309)=0,"",AVERAGE(B309:X309))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
@@ -17552,7 +17612,7 @@
       <c r="W310" s="3"/>
       <c r="X310" s="3"/>
       <c r="Y310" s="4" t="str">
-        <f>IF(COUNTA(B310:X310)=0,"",AVERAGE(B310:X310))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
@@ -17582,7 +17642,7 @@
       <c r="W311" s="3"/>
       <c r="X311" s="3"/>
       <c r="Y311" s="4" t="str">
-        <f>IF(COUNTA(B311:X311)=0,"",AVERAGE(B311:X311))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
@@ -17612,7 +17672,7 @@
       <c r="W312" s="3"/>
       <c r="X312" s="3"/>
       <c r="Y312" s="4" t="str">
-        <f>IF(COUNTA(B312:X312)=0,"",AVERAGE(B312:X312))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
@@ -17642,7 +17702,7 @@
       <c r="W313" s="3"/>
       <c r="X313" s="3"/>
       <c r="Y313" s="4" t="str">
-        <f>IF(COUNTA(B313:X313)=0,"",AVERAGE(B313:X313))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
@@ -17672,7 +17732,7 @@
       <c r="W314" s="3"/>
       <c r="X314" s="3"/>
       <c r="Y314" s="4" t="str">
-        <f>IF(COUNTA(B314:X314)=0,"",AVERAGE(B314:X314))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
@@ -17702,7 +17762,7 @@
       <c r="W315" s="3"/>
       <c r="X315" s="3"/>
       <c r="Y315" s="4" t="str">
-        <f>IF(COUNTA(B315:X315)=0,"",AVERAGE(B315:X315))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
@@ -17732,7 +17792,7 @@
       <c r="W316" s="3"/>
       <c r="X316" s="3"/>
       <c r="Y316" s="4" t="str">
-        <f>IF(COUNTA(B316:X316)=0,"",AVERAGE(B316:X316))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
@@ -17762,7 +17822,7 @@
       <c r="W317" s="3"/>
       <c r="X317" s="3"/>
       <c r="Y317" s="4" t="str">
-        <f>IF(COUNTA(B317:X317)=0,"",AVERAGE(B317:X317))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
@@ -17792,7 +17852,7 @@
       <c r="W318" s="3"/>
       <c r="X318" s="3"/>
       <c r="Y318" s="4" t="str">
-        <f>IF(COUNTA(B318:X318)=0,"",AVERAGE(B318:X318))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
@@ -17822,7 +17882,7 @@
       <c r="W319" s="3"/>
       <c r="X319" s="3"/>
       <c r="Y319" s="4" t="str">
-        <f>IF(COUNTA(B319:X319)=0,"",AVERAGE(B319:X319))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
@@ -17852,7 +17912,7 @@
       <c r="W320" s="3"/>
       <c r="X320" s="3"/>
       <c r="Y320" s="4" t="str">
-        <f>IF(COUNTA(B320:X320)=0,"",AVERAGE(B320:X320))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
@@ -17882,7 +17942,7 @@
       <c r="W321" s="3"/>
       <c r="X321" s="3"/>
       <c r="Y321" s="4" t="str">
-        <f>IF(COUNTA(B321:X321)=0,"",AVERAGE(B321:X321))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
@@ -17912,7 +17972,7 @@
       <c r="W322" s="3"/>
       <c r="X322" s="3"/>
       <c r="Y322" s="4" t="str">
-        <f>IF(COUNTA(B322:X322)=0,"",AVERAGE(B322:X322))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
@@ -17942,7 +18002,7 @@
       <c r="W323" s="3"/>
       <c r="X323" s="3"/>
       <c r="Y323" s="4" t="str">
-        <f>IF(COUNTA(B323:X323)=0,"",AVERAGE(B323:X323))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
@@ -17972,7 +18032,7 @@
       <c r="W324" s="3"/>
       <c r="X324" s="3"/>
       <c r="Y324" s="4" t="str">
-        <f>IF(COUNTA(B324:X324)=0,"",AVERAGE(B324:X324))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
@@ -18002,7 +18062,7 @@
       <c r="W325" s="3"/>
       <c r="X325" s="3"/>
       <c r="Y325" s="4" t="str">
-        <f>IF(COUNTA(B325:X325)=0,"",AVERAGE(B325:X325))</f>
+        <f t="shared" ref="Y325:Y388" si="5">IF(COUNTA(B325:X325)=0,"",AVERAGE(B325:X325))</f>
         <v/>
       </c>
     </row>
@@ -18032,7 +18092,7 @@
       <c r="W326" s="3"/>
       <c r="X326" s="3"/>
       <c r="Y326" s="4" t="str">
-        <f>IF(COUNTA(B326:X326)=0,"",AVERAGE(B326:X326))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -18062,7 +18122,7 @@
       <c r="W327" s="3"/>
       <c r="X327" s="3"/>
       <c r="Y327" s="4" t="str">
-        <f>IF(COUNTA(B327:X327)=0,"",AVERAGE(B327:X327))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -18092,7 +18152,7 @@
       <c r="W328" s="3"/>
       <c r="X328" s="3"/>
       <c r="Y328" s="4" t="str">
-        <f>IF(COUNTA(B328:X328)=0,"",AVERAGE(B328:X328))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -18122,7 +18182,7 @@
       <c r="W329" s="3"/>
       <c r="X329" s="3"/>
       <c r="Y329" s="4" t="str">
-        <f>IF(COUNTA(B329:X329)=0,"",AVERAGE(B329:X329))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -18152,7 +18212,7 @@
       <c r="W330" s="3"/>
       <c r="X330" s="3"/>
       <c r="Y330" s="4" t="str">
-        <f>IF(COUNTA(B330:X330)=0,"",AVERAGE(B330:X330))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -18182,7 +18242,7 @@
       <c r="W331" s="3"/>
       <c r="X331" s="3"/>
       <c r="Y331" s="4" t="str">
-        <f>IF(COUNTA(B331:X331)=0,"",AVERAGE(B331:X331))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -18212,7 +18272,7 @@
       <c r="W332" s="3"/>
       <c r="X332" s="3"/>
       <c r="Y332" s="4" t="str">
-        <f>IF(COUNTA(B332:X332)=0,"",AVERAGE(B332:X332))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -18242,7 +18302,7 @@
       <c r="W333" s="3"/>
       <c r="X333" s="3"/>
       <c r="Y333" s="4" t="str">
-        <f>IF(COUNTA(B333:X333)=0,"",AVERAGE(B333:X333))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -18272,7 +18332,7 @@
       <c r="W334" s="3"/>
       <c r="X334" s="3"/>
       <c r="Y334" s="4" t="str">
-        <f>IF(COUNTA(B334:X334)=0,"",AVERAGE(B334:X334))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -18302,7 +18362,7 @@
       <c r="W335" s="3"/>
       <c r="X335" s="3"/>
       <c r="Y335" s="4" t="str">
-        <f>IF(COUNTA(B335:X335)=0,"",AVERAGE(B335:X335))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -18332,7 +18392,7 @@
       <c r="W336" s="3"/>
       <c r="X336" s="3"/>
       <c r="Y336" s="4" t="str">
-        <f>IF(COUNTA(B336:X336)=0,"",AVERAGE(B336:X336))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -18362,7 +18422,7 @@
       <c r="W337" s="3"/>
       <c r="X337" s="3"/>
       <c r="Y337" s="4" t="str">
-        <f>IF(COUNTA(B337:X337)=0,"",AVERAGE(B337:X337))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -18392,7 +18452,7 @@
       <c r="W338" s="3"/>
       <c r="X338" s="3"/>
       <c r="Y338" s="4" t="str">
-        <f>IF(COUNTA(B338:X338)=0,"",AVERAGE(B338:X338))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -18422,7 +18482,7 @@
       <c r="W339" s="3"/>
       <c r="X339" s="3"/>
       <c r="Y339" s="4" t="str">
-        <f>IF(COUNTA(B339:X339)=0,"",AVERAGE(B339:X339))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -18452,7 +18512,7 @@
       <c r="W340" s="3"/>
       <c r="X340" s="3"/>
       <c r="Y340" s="4" t="str">
-        <f>IF(COUNTA(B340:X340)=0,"",AVERAGE(B340:X340))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -18482,7 +18542,7 @@
       <c r="W341" s="3"/>
       <c r="X341" s="3"/>
       <c r="Y341" s="4" t="str">
-        <f>IF(COUNTA(B341:X341)=0,"",AVERAGE(B341:X341))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -18512,7 +18572,7 @@
       <c r="W342" s="3"/>
       <c r="X342" s="3"/>
       <c r="Y342" s="4" t="str">
-        <f>IF(COUNTA(B342:X342)=0,"",AVERAGE(B342:X342))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -18542,7 +18602,7 @@
       <c r="W343" s="3"/>
       <c r="X343" s="3"/>
       <c r="Y343" s="4" t="str">
-        <f>IF(COUNTA(B343:X343)=0,"",AVERAGE(B343:X343))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -18572,7 +18632,7 @@
       <c r="W344" s="3"/>
       <c r="X344" s="3"/>
       <c r="Y344" s="4" t="str">
-        <f>IF(COUNTA(B344:X344)=0,"",AVERAGE(B344:X344))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -18602,7 +18662,7 @@
       <c r="W345" s="3"/>
       <c r="X345" s="3"/>
       <c r="Y345" s="4" t="str">
-        <f>IF(COUNTA(B345:X345)=0,"",AVERAGE(B345:X345))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -18632,7 +18692,7 @@
       <c r="W346" s="3"/>
       <c r="X346" s="3"/>
       <c r="Y346" s="4" t="str">
-        <f>IF(COUNTA(B346:X346)=0,"",AVERAGE(B346:X346))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -18662,7 +18722,7 @@
       <c r="W347" s="3"/>
       <c r="X347" s="3"/>
       <c r="Y347" s="4" t="str">
-        <f>IF(COUNTA(B347:X347)=0,"",AVERAGE(B347:X347))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -18692,7 +18752,7 @@
       <c r="W348" s="3"/>
       <c r="X348" s="3"/>
       <c r="Y348" s="4" t="str">
-        <f>IF(COUNTA(B348:X348)=0,"",AVERAGE(B348:X348))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -18722,7 +18782,7 @@
       <c r="W349" s="3"/>
       <c r="X349" s="3"/>
       <c r="Y349" s="4" t="str">
-        <f>IF(COUNTA(B349:X349)=0,"",AVERAGE(B349:X349))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -18752,7 +18812,7 @@
       <c r="W350" s="3"/>
       <c r="X350" s="3"/>
       <c r="Y350" s="4" t="str">
-        <f>IF(COUNTA(B350:X350)=0,"",AVERAGE(B350:X350))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -18782,7 +18842,7 @@
       <c r="W351" s="3"/>
       <c r="X351" s="3"/>
       <c r="Y351" s="4" t="str">
-        <f>IF(COUNTA(B351:X351)=0,"",AVERAGE(B351:X351))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -18812,7 +18872,7 @@
       <c r="W352" s="3"/>
       <c r="X352" s="3"/>
       <c r="Y352" s="4" t="str">
-        <f>IF(COUNTA(B352:X352)=0,"",AVERAGE(B352:X352))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -18842,7 +18902,7 @@
       <c r="W353" s="3"/>
       <c r="X353" s="3"/>
       <c r="Y353" s="4" t="str">
-        <f>IF(COUNTA(B353:X353)=0,"",AVERAGE(B353:X353))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -18872,7 +18932,7 @@
       <c r="W354" s="3"/>
       <c r="X354" s="3"/>
       <c r="Y354" s="4" t="str">
-        <f>IF(COUNTA(B354:X354)=0,"",AVERAGE(B354:X354))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -18902,7 +18962,7 @@
       <c r="W355" s="3"/>
       <c r="X355" s="3"/>
       <c r="Y355" s="4" t="str">
-        <f>IF(COUNTA(B355:X355)=0,"",AVERAGE(B355:X355))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -18932,7 +18992,7 @@
       <c r="W356" s="3"/>
       <c r="X356" s="3"/>
       <c r="Y356" s="4" t="str">
-        <f>IF(COUNTA(B356:X356)=0,"",AVERAGE(B356:X356))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -18962,7 +19022,7 @@
       <c r="W357" s="3"/>
       <c r="X357" s="3"/>
       <c r="Y357" s="4" t="str">
-        <f>IF(COUNTA(B357:X357)=0,"",AVERAGE(B357:X357))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -18992,7 +19052,7 @@
       <c r="W358" s="3"/>
       <c r="X358" s="3"/>
       <c r="Y358" s="4" t="str">
-        <f>IF(COUNTA(B358:X358)=0,"",AVERAGE(B358:X358))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -19022,7 +19082,7 @@
       <c r="W359" s="3"/>
       <c r="X359" s="3"/>
       <c r="Y359" s="4" t="str">
-        <f>IF(COUNTA(B359:X359)=0,"",AVERAGE(B359:X359))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -19052,7 +19112,7 @@
       <c r="W360" s="3"/>
       <c r="X360" s="3"/>
       <c r="Y360" s="4" t="str">
-        <f>IF(COUNTA(B360:X360)=0,"",AVERAGE(B360:X360))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -19082,7 +19142,7 @@
       <c r="W361" s="3"/>
       <c r="X361" s="3"/>
       <c r="Y361" s="4" t="str">
-        <f>IF(COUNTA(B361:X361)=0,"",AVERAGE(B361:X361))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -19112,7 +19172,7 @@
       <c r="W362" s="3"/>
       <c r="X362" s="3"/>
       <c r="Y362" s="4" t="str">
-        <f>IF(COUNTA(B362:X362)=0,"",AVERAGE(B362:X362))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -19142,7 +19202,7 @@
       <c r="W363" s="3"/>
       <c r="X363" s="3"/>
       <c r="Y363" s="4" t="str">
-        <f>IF(COUNTA(B363:X363)=0,"",AVERAGE(B363:X363))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -19172,7 +19232,7 @@
       <c r="W364" s="3"/>
       <c r="X364" s="3"/>
       <c r="Y364" s="4" t="str">
-        <f>IF(COUNTA(B364:X364)=0,"",AVERAGE(B364:X364))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -19202,7 +19262,7 @@
       <c r="W365" s="3"/>
       <c r="X365" s="3"/>
       <c r="Y365" s="4" t="str">
-        <f>IF(COUNTA(B365:X365)=0,"",AVERAGE(B365:X365))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -19232,7 +19292,7 @@
       <c r="W366" s="3"/>
       <c r="X366" s="3"/>
       <c r="Y366" s="4" t="str">
-        <f>IF(COUNTA(B366:X366)=0,"",AVERAGE(B366:X366))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -19262,7 +19322,7 @@
       <c r="W367" s="3"/>
       <c r="X367" s="3"/>
       <c r="Y367" s="4" t="str">
-        <f>IF(COUNTA(B367:X367)=0,"",AVERAGE(B367:X367))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -19292,7 +19352,7 @@
       <c r="W368" s="3"/>
       <c r="X368" s="3"/>
       <c r="Y368" s="4" t="str">
-        <f>IF(COUNTA(B368:X368)=0,"",AVERAGE(B368:X368))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -19322,7 +19382,7 @@
       <c r="W369" s="3"/>
       <c r="X369" s="3"/>
       <c r="Y369" s="4" t="str">
-        <f>IF(COUNTA(B369:X369)=0,"",AVERAGE(B369:X369))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -19352,7 +19412,7 @@
       <c r="W370" s="3"/>
       <c r="X370" s="3"/>
       <c r="Y370" s="4" t="str">
-        <f>IF(COUNTA(B370:X370)=0,"",AVERAGE(B370:X370))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -19382,7 +19442,7 @@
       <c r="W371" s="3"/>
       <c r="X371" s="3"/>
       <c r="Y371" s="4" t="str">
-        <f>IF(COUNTA(B371:X371)=0,"",AVERAGE(B371:X371))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -19412,7 +19472,7 @@
       <c r="W372" s="3"/>
       <c r="X372" s="3"/>
       <c r="Y372" s="4" t="str">
-        <f>IF(COUNTA(B372:X372)=0,"",AVERAGE(B372:X372))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -19442,7 +19502,7 @@
       <c r="W373" s="3"/>
       <c r="X373" s="3"/>
       <c r="Y373" s="4" t="str">
-        <f>IF(COUNTA(B373:X373)=0,"",AVERAGE(B373:X373))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -19472,7 +19532,7 @@
       <c r="W374" s="3"/>
       <c r="X374" s="3"/>
       <c r="Y374" s="4" t="str">
-        <f>IF(COUNTA(B374:X374)=0,"",AVERAGE(B374:X374))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -19502,7 +19562,7 @@
       <c r="W375" s="3"/>
       <c r="X375" s="3"/>
       <c r="Y375" s="4" t="str">
-        <f>IF(COUNTA(B375:X375)=0,"",AVERAGE(B375:X375))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -19532,7 +19592,7 @@
       <c r="W376" s="3"/>
       <c r="X376" s="3"/>
       <c r="Y376" s="4" t="str">
-        <f>IF(COUNTA(B376:X376)=0,"",AVERAGE(B376:X376))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -19562,7 +19622,7 @@
       <c r="W377" s="3"/>
       <c r="X377" s="3"/>
       <c r="Y377" s="4" t="str">
-        <f>IF(COUNTA(B377:X377)=0,"",AVERAGE(B377:X377))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -19592,7 +19652,7 @@
       <c r="W378" s="3"/>
       <c r="X378" s="3"/>
       <c r="Y378" s="4" t="str">
-        <f>IF(COUNTA(B378:X378)=0,"",AVERAGE(B378:X378))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -19622,7 +19682,7 @@
       <c r="W379" s="3"/>
       <c r="X379" s="3"/>
       <c r="Y379" s="4" t="str">
-        <f>IF(COUNTA(B379:X379)=0,"",AVERAGE(B379:X379))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -19652,7 +19712,7 @@
       <c r="W380" s="3"/>
       <c r="X380" s="3"/>
       <c r="Y380" s="4" t="str">
-        <f>IF(COUNTA(B380:X380)=0,"",AVERAGE(B380:X380))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -19682,7 +19742,7 @@
       <c r="W381" s="3"/>
       <c r="X381" s="3"/>
       <c r="Y381" s="4" t="str">
-        <f>IF(COUNTA(B381:X381)=0,"",AVERAGE(B381:X381))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -19712,7 +19772,7 @@
       <c r="W382" s="3"/>
       <c r="X382" s="3"/>
       <c r="Y382" s="4" t="str">
-        <f>IF(COUNTA(B382:X382)=0,"",AVERAGE(B382:X382))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -19742,7 +19802,7 @@
       <c r="W383" s="3"/>
       <c r="X383" s="3"/>
       <c r="Y383" s="4" t="str">
-        <f>IF(COUNTA(B383:X383)=0,"",AVERAGE(B383:X383))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -19772,7 +19832,7 @@
       <c r="W384" s="3"/>
       <c r="X384" s="3"/>
       <c r="Y384" s="4" t="str">
-        <f>IF(COUNTA(B384:X384)=0,"",AVERAGE(B384:X384))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -19802,7 +19862,7 @@
       <c r="W385" s="3"/>
       <c r="X385" s="3"/>
       <c r="Y385" s="4" t="str">
-        <f>IF(COUNTA(B385:X385)=0,"",AVERAGE(B385:X385))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -19832,7 +19892,7 @@
       <c r="W386" s="3"/>
       <c r="X386" s="3"/>
       <c r="Y386" s="4" t="str">
-        <f>IF(COUNTA(B386:X386)=0,"",AVERAGE(B386:X386))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -19862,7 +19922,7 @@
       <c r="W387" s="3"/>
       <c r="X387" s="3"/>
       <c r="Y387" s="4" t="str">
-        <f>IF(COUNTA(B387:X387)=0,"",AVERAGE(B387:X387))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -19892,7 +19952,7 @@
       <c r="W388" s="3"/>
       <c r="X388" s="3"/>
       <c r="Y388" s="4" t="str">
-        <f>IF(COUNTA(B388:X388)=0,"",AVERAGE(B388:X388))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -19922,7 +19982,7 @@
       <c r="W389" s="3"/>
       <c r="X389" s="3"/>
       <c r="Y389" s="4" t="str">
-        <f>IF(COUNTA(B389:X389)=0,"",AVERAGE(B389:X389))</f>
+        <f t="shared" ref="Y389:Y452" si="6">IF(COUNTA(B389:X389)=0,"",AVERAGE(B389:X389))</f>
         <v/>
       </c>
     </row>
@@ -19952,7 +20012,7 @@
       <c r="W390" s="3"/>
       <c r="X390" s="3"/>
       <c r="Y390" s="4" t="str">
-        <f>IF(COUNTA(B390:X390)=0,"",AVERAGE(B390:X390))</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
@@ -22539,29 +22599,69 @@
       </c>
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A42" s="2"/>
-      <c r="B42" s="3"/>
-      <c r="C42" s="3"/>
-      <c r="D42" s="3"/>
-      <c r="E42" s="3"/>
-      <c r="F42" s="3"/>
-      <c r="G42" s="3"/>
-      <c r="H42" s="3"/>
-      <c r="I42" s="3"/>
-      <c r="J42" s="3"/>
-      <c r="K42" s="3"/>
-      <c r="L42" s="3"/>
-      <c r="M42" s="3"/>
-      <c r="N42" s="3"/>
-      <c r="O42" s="3"/>
-      <c r="P42" s="3"/>
-      <c r="Q42" s="3"/>
-      <c r="R42" s="3"/>
-      <c r="S42" s="3"/>
-      <c r="T42" s="3"/>
-      <c r="U42" s="4" t="str">
+      <c r="A42" s="2">
+        <v>46183</v>
+      </c>
+      <c r="B42" s="3">
+        <v>4.29</v>
+      </c>
+      <c r="C42" s="3">
+        <v>3.95</v>
+      </c>
+      <c r="D42" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="E42" s="3">
+        <v>4.1900000000000004</v>
+      </c>
+      <c r="F42" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="G42" s="3">
+        <v>3.99</v>
+      </c>
+      <c r="H42" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="I42" s="3">
+        <v>3.39</v>
+      </c>
+      <c r="J42" s="3">
+        <v>3.09</v>
+      </c>
+      <c r="K42" s="3">
+        <v>3.95</v>
+      </c>
+      <c r="L42" s="3">
+        <v>3.49</v>
+      </c>
+      <c r="M42" s="3">
+        <v>3.59</v>
+      </c>
+      <c r="N42" s="3">
+        <v>3.84</v>
+      </c>
+      <c r="O42" s="3">
+        <v>4.1900000000000004</v>
+      </c>
+      <c r="P42" s="3">
+        <v>3.89</v>
+      </c>
+      <c r="Q42" s="3">
+        <v>4.03</v>
+      </c>
+      <c r="R42" s="3">
+        <v>3.89</v>
+      </c>
+      <c r="S42" s="3">
+        <v>3.99</v>
+      </c>
+      <c r="T42" s="3">
+        <v>1.99</v>
+      </c>
+      <c r="U42" s="4">
         <f t="shared" si="0"/>
-        <v/>
+        <v>3.6168421052631579</v>
       </c>
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
@@ -33035,19 +33135,39 @@
       </c>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A42" s="2"/>
-      <c r="B42" s="3"/>
-      <c r="C42" s="3"/>
-      <c r="D42" s="3"/>
-      <c r="E42" s="3"/>
-      <c r="F42" s="3"/>
-      <c r="G42" s="3"/>
-      <c r="H42" s="3"/>
-      <c r="I42" s="3"/>
-      <c r="J42" s="3"/>
-      <c r="K42" s="4" t="str">
+      <c r="A42" s="2">
+        <v>46183</v>
+      </c>
+      <c r="B42" s="3">
+        <v>2.89</v>
+      </c>
+      <c r="C42" s="3">
+        <v>3.14</v>
+      </c>
+      <c r="D42" s="3">
+        <v>2.83</v>
+      </c>
+      <c r="E42" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="F42" s="3">
+        <v>2.8</v>
+      </c>
+      <c r="G42" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="H42" s="3">
+        <v>2.63</v>
+      </c>
+      <c r="I42" s="3">
+        <v>2.89</v>
+      </c>
+      <c r="J42" s="3">
+        <v>2.59</v>
+      </c>
+      <c r="K42" s="4">
         <f t="shared" si="0"/>
-        <v/>
+        <v>2.8611111111111112</v>
       </c>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.25">
@@ -40157,20 +40277,42 @@
       </c>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A42" s="2"/>
-      <c r="B42" s="3"/>
-      <c r="C42" s="3"/>
-      <c r="D42" s="3"/>
-      <c r="E42" s="3"/>
-      <c r="F42" s="3"/>
-      <c r="G42" s="3"/>
-      <c r="H42" s="3"/>
-      <c r="I42" s="3"/>
-      <c r="J42" s="3"/>
-      <c r="K42" s="3"/>
-      <c r="L42" s="4" t="str">
+      <c r="A42" s="2">
+        <v>46183</v>
+      </c>
+      <c r="B42" s="3">
+        <v>3.59</v>
+      </c>
+      <c r="C42" s="3">
+        <v>3.19</v>
+      </c>
+      <c r="D42" s="3">
+        <v>3.59</v>
+      </c>
+      <c r="E42" s="3">
+        <v>3.35</v>
+      </c>
+      <c r="F42" s="3">
+        <v>3.43</v>
+      </c>
+      <c r="G42" s="3">
+        <v>3.89</v>
+      </c>
+      <c r="H42" s="3">
+        <v>3.11</v>
+      </c>
+      <c r="I42" s="3">
+        <v>3.29</v>
+      </c>
+      <c r="J42" s="3">
+        <v>3.46</v>
+      </c>
+      <c r="K42" s="3">
+        <v>3.29</v>
+      </c>
+      <c r="L42" s="4">
         <f t="shared" si="0"/>
-        <v/>
+        <v>3.4189999999999996</v>
       </c>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.25">

--- a/app/mevduat-kredi-faizleri/data/hoca-ile-borsa-faiz-takip-sablonu-guncel.xlsx
+++ b/app/mevduat-kredi-faizleri/data/hoca-ile-borsa-faiz-takip-sablonu-guncel.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projeler\hoca-ile-borsa\app\mevduat-kredi-faizleri\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5C759E1-7B92-49C0-B923-CDF73C207272}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61791D6B-96F8-48C6-B847-F92816AA42DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="840" yWindow="225" windowWidth="37860" windowHeight="19380" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Mevduat" sheetId="1" r:id="rId1"/>
@@ -458,6 +458,9 @@
                 <c:pt idx="39">
                   <c:v>46185</c:v>
                 </c:pt>
+                <c:pt idx="40">
+                  <c:v>46188</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -588,7 +591,7 @@
                   <c:v>43.44086956521739</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>0</c:v>
+                  <c:v>43.44086956521739</c:v>
                 </c:pt>
                 <c:pt idx="41">
                   <c:v>0</c:v>
@@ -1904,6 +1907,9 @@
                 <c:pt idx="39">
                   <c:v>46185</c:v>
                 </c:pt>
+                <c:pt idx="40">
+                  <c:v>46188</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2034,7 +2040,7 @@
                   <c:v>3.6168421052631579</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>0</c:v>
+                  <c:v>3.6905263157894739</c:v>
                 </c:pt>
                 <c:pt idx="41">
                   <c:v>0</c:v>
@@ -3350,6 +3356,9 @@
                 <c:pt idx="39">
                   <c:v>46185</c:v>
                 </c:pt>
+                <c:pt idx="40">
+                  <c:v>46188</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3480,7 +3489,7 @@
                   <c:v>2.8611111111111112</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>0</c:v>
+                  <c:v>2.8944444444444444</c:v>
                 </c:pt>
                 <c:pt idx="41">
                   <c:v>0</c:v>
@@ -4796,6 +4805,9 @@
                 <c:pt idx="39">
                   <c:v>46185</c:v>
                 </c:pt>
+                <c:pt idx="40">
+                  <c:v>46188</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -4926,7 +4938,7 @@
                   <c:v>3.4189999999999996</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>0</c:v>
+                  <c:v>3.4189999999999996</c:v>
                 </c:pt>
                 <c:pt idx="41">
                   <c:v>0</c:v>
@@ -9757,33 +9769,81 @@
       </c>
     </row>
     <row r="45" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A45" s="2"/>
-      <c r="B45" s="3"/>
-      <c r="C45" s="3"/>
-      <c r="D45" s="3"/>
-      <c r="E45" s="3"/>
-      <c r="F45" s="3"/>
-      <c r="G45" s="3"/>
-      <c r="H45" s="3"/>
-      <c r="I45" s="3"/>
-      <c r="J45" s="3"/>
-      <c r="K45" s="3"/>
-      <c r="L45" s="3"/>
-      <c r="M45" s="3"/>
-      <c r="N45" s="3"/>
-      <c r="O45" s="3"/>
-      <c r="P45" s="3"/>
-      <c r="Q45" s="3"/>
-      <c r="R45" s="3"/>
-      <c r="S45" s="3"/>
-      <c r="T45" s="3"/>
-      <c r="U45" s="3"/>
-      <c r="V45" s="3"/>
-      <c r="W45" s="3"/>
-      <c r="X45" s="3"/>
-      <c r="Y45" s="4" t="str">
+      <c r="A45" s="2">
+        <v>46188</v>
+      </c>
+      <c r="B45" s="3">
+        <v>42.5</v>
+      </c>
+      <c r="C45" s="3">
+        <v>46</v>
+      </c>
+      <c r="D45" s="3">
+        <v>46</v>
+      </c>
+      <c r="E45" s="3">
+        <v>45</v>
+      </c>
+      <c r="F45" s="3">
+        <v>43.5</v>
+      </c>
+      <c r="G45" s="3">
+        <v>41</v>
+      </c>
+      <c r="H45" s="3">
+        <v>46</v>
+      </c>
+      <c r="I45" s="3">
+        <v>41.5</v>
+      </c>
+      <c r="J45" s="3">
+        <v>43</v>
+      </c>
+      <c r="K45" s="3">
+        <v>41</v>
+      </c>
+      <c r="L45" s="3">
+        <v>36</v>
+      </c>
+      <c r="M45" s="3">
+        <v>44</v>
+      </c>
+      <c r="N45" s="3">
+        <v>45</v>
+      </c>
+      <c r="O45" s="3">
+        <v>42.39</v>
+      </c>
+      <c r="P45" s="3">
+        <v>39</v>
+      </c>
+      <c r="Q45" s="3">
+        <v>45</v>
+      </c>
+      <c r="R45" s="3">
+        <v>45</v>
+      </c>
+      <c r="S45" s="3">
+        <v>45</v>
+      </c>
+      <c r="T45" s="3">
+        <v>43.5</v>
+      </c>
+      <c r="U45" s="3">
+        <v>44.5</v>
+      </c>
+      <c r="V45" s="3">
+        <v>42</v>
+      </c>
+      <c r="W45" s="3">
+        <v>47</v>
+      </c>
+      <c r="X45" s="3">
+        <v>45.25</v>
+      </c>
+      <c r="Y45" s="4">
         <f t="shared" si="0"/>
-        <v/>
+        <v>43.44086956521739</v>
       </c>
     </row>
     <row r="46" spans="1:25" x14ac:dyDescent="0.25">
@@ -22917,29 +22977,69 @@
       </c>
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A45" s="2"/>
-      <c r="B45" s="3"/>
-      <c r="C45" s="3"/>
-      <c r="D45" s="3"/>
-      <c r="E45" s="3"/>
-      <c r="F45" s="3"/>
-      <c r="G45" s="3"/>
-      <c r="H45" s="3"/>
-      <c r="I45" s="3"/>
-      <c r="J45" s="3"/>
-      <c r="K45" s="3"/>
-      <c r="L45" s="3"/>
-      <c r="M45" s="3"/>
-      <c r="N45" s="3"/>
-      <c r="O45" s="3"/>
-      <c r="P45" s="3"/>
-      <c r="Q45" s="3"/>
-      <c r="R45" s="3"/>
-      <c r="S45" s="3"/>
-      <c r="T45" s="3"/>
-      <c r="U45" s="4" t="str">
+      <c r="A45" s="2">
+        <v>46188</v>
+      </c>
+      <c r="B45" s="3">
+        <v>3.79</v>
+      </c>
+      <c r="C45" s="3">
+        <v>3.95</v>
+      </c>
+      <c r="D45" s="3">
+        <v>3.49</v>
+      </c>
+      <c r="E45" s="3">
+        <v>4.1900000000000004</v>
+      </c>
+      <c r="F45" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="G45" s="3">
+        <v>3.99</v>
+      </c>
+      <c r="H45" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="I45" s="3">
+        <v>3.39</v>
+      </c>
+      <c r="J45" s="3">
+        <v>3.49</v>
+      </c>
+      <c r="K45" s="3">
+        <v>3.95</v>
+      </c>
+      <c r="L45" s="3">
+        <v>3.49</v>
+      </c>
+      <c r="M45" s="3">
+        <v>3.59</v>
+      </c>
+      <c r="N45" s="3">
+        <v>3.84</v>
+      </c>
+      <c r="O45" s="3">
+        <v>4.1900000000000004</v>
+      </c>
+      <c r="P45" s="3">
+        <v>3.89</v>
+      </c>
+      <c r="Q45" s="3">
+        <v>4.03</v>
+      </c>
+      <c r="R45" s="3">
+        <v>3.89</v>
+      </c>
+      <c r="S45" s="3">
+        <v>4.99</v>
+      </c>
+      <c r="T45" s="3">
+        <v>1.99</v>
+      </c>
+      <c r="U45" s="4">
         <f t="shared" si="0"/>
-        <v/>
+        <v>3.6905263157894739</v>
       </c>
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
@@ -33443,19 +33543,39 @@
       </c>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A45" s="2"/>
-      <c r="B45" s="3"/>
-      <c r="C45" s="3"/>
-      <c r="D45" s="3"/>
-      <c r="E45" s="3"/>
-      <c r="F45" s="3"/>
-      <c r="G45" s="3"/>
-      <c r="H45" s="3"/>
-      <c r="I45" s="3"/>
-      <c r="J45" s="3"/>
-      <c r="K45" s="4" t="str">
+      <c r="A45" s="2">
+        <v>46188</v>
+      </c>
+      <c r="B45" s="3">
+        <v>2.89</v>
+      </c>
+      <c r="C45" s="3">
+        <v>3.14</v>
+      </c>
+      <c r="D45" s="3">
+        <v>2.83</v>
+      </c>
+      <c r="E45" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="F45" s="3">
+        <v>2.8</v>
+      </c>
+      <c r="G45" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="H45" s="3">
+        <v>2.63</v>
+      </c>
+      <c r="I45" s="3">
+        <v>2.89</v>
+      </c>
+      <c r="J45" s="3">
+        <v>2.89</v>
+      </c>
+      <c r="K45" s="4">
         <f t="shared" si="0"/>
-        <v/>
+        <v>2.8944444444444444</v>
       </c>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.25">
@@ -40634,20 +40754,42 @@
       </c>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A45" s="2"/>
-      <c r="B45" s="3"/>
-      <c r="C45" s="3"/>
-      <c r="D45" s="3"/>
-      <c r="E45" s="3"/>
-      <c r="F45" s="3"/>
-      <c r="G45" s="3"/>
-      <c r="H45" s="3"/>
-      <c r="I45" s="3"/>
-      <c r="J45" s="3"/>
-      <c r="K45" s="3"/>
-      <c r="L45" s="4" t="str">
+      <c r="A45" s="2">
+        <v>46188</v>
+      </c>
+      <c r="B45" s="3">
+        <v>3.59</v>
+      </c>
+      <c r="C45" s="3">
+        <v>3.19</v>
+      </c>
+      <c r="D45" s="3">
+        <v>3.59</v>
+      </c>
+      <c r="E45" s="3">
+        <v>3.35</v>
+      </c>
+      <c r="F45" s="3">
+        <v>3.43</v>
+      </c>
+      <c r="G45" s="3">
+        <v>3.89</v>
+      </c>
+      <c r="H45" s="3">
+        <v>3.11</v>
+      </c>
+      <c r="I45" s="3">
+        <v>3.29</v>
+      </c>
+      <c r="J45" s="3">
+        <v>3.46</v>
+      </c>
+      <c r="K45" s="3">
+        <v>3.29</v>
+      </c>
+      <c r="L45" s="4">
         <f t="shared" si="0"/>
-        <v/>
+        <v>3.4189999999999996</v>
       </c>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.25">

--- a/app/mevduat-kredi-faizleri/data/hoca-ile-borsa-faiz-takip-sablonu-guncel.xlsx
+++ b/app/mevduat-kredi-faizleri/data/hoca-ile-borsa-faiz-takip-sablonu-guncel.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projeler\hoca-ile-borsa\app\mevduat-kredi-faizleri\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{009F8CA3-5929-4320-899D-7108364B399E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5F08784-C0E9-441E-9805-60ED9054D2CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="840" yWindow="225" windowWidth="37860" windowHeight="19380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Mevduat" sheetId="1" r:id="rId1"/>
@@ -470,6 +470,9 @@
                 <c:pt idx="43">
                   <c:v>46191</c:v>
                 </c:pt>
+                <c:pt idx="44">
+                  <c:v>46192</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -612,7 +615,7 @@
                   <c:v>43.44086956521739</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>0</c:v>
+                  <c:v>43.651739130434784</c:v>
                 </c:pt>
                 <c:pt idx="45">
                   <c:v>0</c:v>
@@ -1928,6 +1931,9 @@
                 <c:pt idx="43">
                   <c:v>46191</c:v>
                 </c:pt>
+                <c:pt idx="44">
+                  <c:v>46192</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2070,7 +2076,7 @@
                   <c:v>3.6905263157894739</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>0</c:v>
+                  <c:v>3.7042105263157894</c:v>
                 </c:pt>
                 <c:pt idx="45">
                   <c:v>0</c:v>
@@ -3386,6 +3392,9 @@
                 <c:pt idx="43">
                   <c:v>46191</c:v>
                 </c:pt>
+                <c:pt idx="44">
+                  <c:v>46192</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3528,7 +3537,7 @@
                   <c:v>2.8944444444444444</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>0</c:v>
+                  <c:v>2.9022222222222225</c:v>
                 </c:pt>
                 <c:pt idx="45">
                   <c:v>0</c:v>
@@ -4844,6 +4853,9 @@
                 <c:pt idx="43">
                   <c:v>46191</c:v>
                 </c:pt>
+                <c:pt idx="44">
+                  <c:v>46192</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -4986,7 +4998,7 @@
                   <c:v>3.4189999999999996</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>0</c:v>
+                  <c:v>3.4219999999999997</c:v>
                 </c:pt>
                 <c:pt idx="45">
                   <c:v>0</c:v>
@@ -10117,33 +10129,81 @@
       </c>
     </row>
     <row r="49" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A49" s="2"/>
-      <c r="B49" s="3"/>
-      <c r="C49" s="3"/>
-      <c r="D49" s="3"/>
-      <c r="E49" s="3"/>
-      <c r="F49" s="3"/>
-      <c r="G49" s="3"/>
-      <c r="H49" s="3"/>
-      <c r="I49" s="3"/>
-      <c r="J49" s="3"/>
-      <c r="K49" s="3"/>
-      <c r="L49" s="3"/>
-      <c r="M49" s="3"/>
-      <c r="N49" s="3"/>
-      <c r="O49" s="3"/>
-      <c r="P49" s="3"/>
-      <c r="Q49" s="3"/>
-      <c r="R49" s="3"/>
-      <c r="S49" s="3"/>
-      <c r="T49" s="3"/>
-      <c r="U49" s="3"/>
-      <c r="V49" s="3"/>
-      <c r="W49" s="3"/>
-      <c r="X49" s="3"/>
-      <c r="Y49" s="4" t="str">
+      <c r="A49" s="2">
+        <v>46192</v>
+      </c>
+      <c r="B49" s="3">
+        <v>42.5</v>
+      </c>
+      <c r="C49" s="3">
+        <v>46</v>
+      </c>
+      <c r="D49" s="3">
+        <v>46</v>
+      </c>
+      <c r="E49" s="3">
+        <v>46</v>
+      </c>
+      <c r="F49" s="3">
+        <v>44</v>
+      </c>
+      <c r="G49" s="3">
+        <v>41</v>
+      </c>
+      <c r="H49" s="3">
+        <v>46</v>
+      </c>
+      <c r="I49" s="3">
+        <v>41.5</v>
+      </c>
+      <c r="J49" s="3">
+        <v>44</v>
+      </c>
+      <c r="K49" s="3">
+        <v>41</v>
+      </c>
+      <c r="L49" s="3">
+        <v>36</v>
+      </c>
+      <c r="M49" s="3">
+        <v>44</v>
+      </c>
+      <c r="N49" s="3">
+        <v>45</v>
+      </c>
+      <c r="O49" s="3">
+        <v>41.99</v>
+      </c>
+      <c r="P49" s="3">
+        <v>41</v>
+      </c>
+      <c r="Q49" s="3">
+        <v>45</v>
+      </c>
+      <c r="R49" s="3">
+        <v>45</v>
+      </c>
+      <c r="S49" s="3">
+        <v>46</v>
+      </c>
+      <c r="T49" s="3">
+        <v>43.5</v>
+      </c>
+      <c r="U49" s="3">
+        <v>44.25</v>
+      </c>
+      <c r="V49" s="3">
+        <v>42</v>
+      </c>
+      <c r="W49" s="3">
+        <v>47</v>
+      </c>
+      <c r="X49" s="3">
+        <v>45.25</v>
+      </c>
+      <c r="Y49" s="4">
         <f t="shared" si="0"/>
-        <v/>
+        <v>43.651739130434784</v>
       </c>
     </row>
     <row r="50" spans="1:25" x14ac:dyDescent="0.25">
@@ -23416,34 +23476,74 @@
         <v>1.99</v>
       </c>
       <c r="U48" s="4">
-        <f t="shared" ref="U48" si="13">IF(COUNTA(B48:T48)=0,"",AVERAGE(B48:T48))</f>
+        <f t="shared" ref="U48:U49" si="13">IF(COUNTA(B48:T48)=0,"",AVERAGE(B48:T48))</f>
         <v>3.6905263157894739</v>
       </c>
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A49" s="2"/>
-      <c r="B49" s="3"/>
-      <c r="C49" s="3"/>
-      <c r="D49" s="3"/>
-      <c r="E49" s="3"/>
-      <c r="F49" s="3"/>
-      <c r="G49" s="3"/>
-      <c r="H49" s="3"/>
-      <c r="I49" s="3"/>
-      <c r="J49" s="3"/>
-      <c r="K49" s="3"/>
-      <c r="L49" s="3"/>
-      <c r="M49" s="3"/>
-      <c r="N49" s="3"/>
-      <c r="O49" s="3"/>
-      <c r="P49" s="3"/>
-      <c r="Q49" s="3"/>
-      <c r="R49" s="3"/>
-      <c r="S49" s="3"/>
-      <c r="T49" s="3"/>
-      <c r="U49" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
+      <c r="A49" s="2">
+        <v>46192</v>
+      </c>
+      <c r="B49" s="3">
+        <v>3.79</v>
+      </c>
+      <c r="C49" s="3">
+        <v>3.95</v>
+      </c>
+      <c r="D49" s="3">
+        <v>3.79</v>
+      </c>
+      <c r="E49" s="3">
+        <v>4.1900000000000004</v>
+      </c>
+      <c r="F49" s="3">
+        <v>3.99</v>
+      </c>
+      <c r="G49" s="3">
+        <v>3.99</v>
+      </c>
+      <c r="H49" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="I49" s="3">
+        <v>3.39</v>
+      </c>
+      <c r="J49" s="3">
+        <v>3.49</v>
+      </c>
+      <c r="K49" s="3">
+        <v>3.95</v>
+      </c>
+      <c r="L49" s="3">
+        <v>3.49</v>
+      </c>
+      <c r="M49" s="3">
+        <v>3.39</v>
+      </c>
+      <c r="N49" s="3">
+        <v>3.84</v>
+      </c>
+      <c r="O49" s="3">
+        <v>3.73</v>
+      </c>
+      <c r="P49" s="3">
+        <v>3.89</v>
+      </c>
+      <c r="Q49" s="3">
+        <v>3.65</v>
+      </c>
+      <c r="R49" s="3">
+        <v>3.89</v>
+      </c>
+      <c r="S49" s="3">
+        <v>4.99</v>
+      </c>
+      <c r="T49" s="3">
+        <v>1.99</v>
+      </c>
+      <c r="U49" s="4">
+        <f t="shared" si="13"/>
+        <v>3.7042105263157894</v>
       </c>
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
@@ -33987,19 +34087,39 @@
       </c>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A49" s="2"/>
-      <c r="B49" s="3"/>
-      <c r="C49" s="3"/>
-      <c r="D49" s="3"/>
-      <c r="E49" s="3"/>
-      <c r="F49" s="3"/>
-      <c r="G49" s="3"/>
-      <c r="H49" s="3"/>
-      <c r="I49" s="3"/>
-      <c r="J49" s="3"/>
-      <c r="K49" s="4" t="str">
+      <c r="A49" s="2">
+        <v>46192</v>
+      </c>
+      <c r="B49" s="3">
+        <v>2.89</v>
+      </c>
+      <c r="C49" s="3">
+        <v>3.14</v>
+      </c>
+      <c r="D49" s="3">
+        <v>2.8</v>
+      </c>
+      <c r="E49" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="F49" s="3">
+        <v>2.8</v>
+      </c>
+      <c r="G49" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="H49" s="3">
+        <v>2.73</v>
+      </c>
+      <c r="I49" s="3">
+        <v>2.89</v>
+      </c>
+      <c r="J49" s="3">
+        <v>2.89</v>
+      </c>
+      <c r="K49" s="4">
         <f t="shared" si="0"/>
-        <v/>
+        <v>2.9022222222222225</v>
       </c>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.25">
@@ -41270,20 +41390,42 @@
       </c>
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A49" s="2"/>
-      <c r="B49" s="3"/>
-      <c r="C49" s="3"/>
-      <c r="D49" s="3"/>
-      <c r="E49" s="3"/>
-      <c r="F49" s="3"/>
-      <c r="G49" s="3"/>
-      <c r="H49" s="3"/>
-      <c r="I49" s="3"/>
-      <c r="J49" s="3"/>
-      <c r="K49" s="3"/>
-      <c r="L49" s="4" t="str">
+      <c r="A49" s="2">
+        <v>46192</v>
+      </c>
+      <c r="B49" s="3">
+        <v>3.59</v>
+      </c>
+      <c r="C49" s="3">
+        <v>3.19</v>
+      </c>
+      <c r="D49" s="3">
+        <v>3.59</v>
+      </c>
+      <c r="E49" s="3">
+        <v>3.35</v>
+      </c>
+      <c r="F49" s="3">
+        <v>3.43</v>
+      </c>
+      <c r="G49" s="3">
+        <v>3.89</v>
+      </c>
+      <c r="H49" s="3">
+        <v>3.14</v>
+      </c>
+      <c r="I49" s="3">
+        <v>3.29</v>
+      </c>
+      <c r="J49" s="3">
+        <v>3.46</v>
+      </c>
+      <c r="K49" s="3">
+        <v>3.29</v>
+      </c>
+      <c r="L49" s="4">
         <f t="shared" si="0"/>
-        <v/>
+        <v>3.4219999999999997</v>
       </c>
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.25">

--- a/app/mevduat-kredi-faizleri/data/hoca-ile-borsa-faiz-takip-sablonu-guncel.xlsx
+++ b/app/mevduat-kredi-faizleri/data/hoca-ile-borsa-faiz-takip-sablonu-guncel.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projeler\hoca-ile-borsa\app\mevduat-kredi-faizleri\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19360A04-3E84-420A-9D4D-921B6D3C4EA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB80B9F2-BF54-4D44-8916-567B8476C6D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Mevduat" sheetId="1" r:id="rId1"/>
@@ -488,6 +488,9 @@
                 <c:pt idx="49">
                   <c:v>46199</c:v>
                 </c:pt>
+                <c:pt idx="50">
+                  <c:v>46202</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -648,7 +651,7 @@
                   <c:v>43.651739130434784</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>0</c:v>
+                  <c:v>43.759130434782612</c:v>
                 </c:pt>
                 <c:pt idx="51">
                   <c:v>0</c:v>
@@ -1964,6 +1967,9 @@
                 <c:pt idx="49">
                   <c:v>46199</c:v>
                 </c:pt>
+                <c:pt idx="50">
+                  <c:v>46202</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2124,7 +2130,7 @@
                   <c:v>3.7042105263157894</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>0</c:v>
+                  <c:v>3.5336842105263164</c:v>
                 </c:pt>
                 <c:pt idx="51">
                   <c:v>0</c:v>
@@ -3440,6 +3446,9 @@
                 <c:pt idx="49">
                   <c:v>46199</c:v>
                 </c:pt>
+                <c:pt idx="50">
+                  <c:v>46202</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3594,13 +3603,13 @@
                   <c:v>2.9022222222222225</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>2.9037500000000001</c:v>
+                  <c:v>2.9022222222222225</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>2.9037500000000001</c:v>
+                  <c:v>2.9022222222222225</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>0</c:v>
+                  <c:v>2.8977777777777778</c:v>
                 </c:pt>
                 <c:pt idx="51">
                   <c:v>0</c:v>
@@ -4916,6 +4925,9 @@
                 <c:pt idx="49">
                   <c:v>46199</c:v>
                 </c:pt>
+                <c:pt idx="50">
+                  <c:v>46202</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -5076,7 +5088,7 @@
                   <c:v>3.4219999999999997</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>0</c:v>
+                  <c:v>3.4185000000000003</c:v>
                 </c:pt>
                 <c:pt idx="51">
                   <c:v>0</c:v>
@@ -10657,33 +10669,81 @@
       </c>
     </row>
     <row r="55" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A55" s="2"/>
-      <c r="B55" s="3"/>
-      <c r="C55" s="3"/>
-      <c r="D55" s="3"/>
-      <c r="E55" s="3"/>
-      <c r="F55" s="3"/>
-      <c r="G55" s="3"/>
-      <c r="H55" s="3"/>
-      <c r="I55" s="3"/>
-      <c r="J55" s="3"/>
-      <c r="K55" s="3"/>
-      <c r="L55" s="3"/>
-      <c r="M55" s="3"/>
-      <c r="N55" s="3"/>
-      <c r="O55" s="3"/>
-      <c r="P55" s="3"/>
-      <c r="Q55" s="3"/>
-      <c r="R55" s="3"/>
-      <c r="S55" s="3"/>
-      <c r="T55" s="3"/>
-      <c r="U55" s="3"/>
-      <c r="V55" s="3"/>
-      <c r="W55" s="3"/>
-      <c r="X55" s="3"/>
-      <c r="Y55" s="4" t="str">
+      <c r="A55" s="2">
+        <v>46202</v>
+      </c>
+      <c r="B55" s="3">
+        <v>42.5</v>
+      </c>
+      <c r="C55" s="3">
+        <v>46</v>
+      </c>
+      <c r="D55" s="3">
+        <v>46</v>
+      </c>
+      <c r="E55" s="3">
+        <v>46</v>
+      </c>
+      <c r="F55" s="3">
+        <v>45</v>
+      </c>
+      <c r="G55" s="3">
+        <v>41.5</v>
+      </c>
+      <c r="H55" s="3">
+        <v>46</v>
+      </c>
+      <c r="I55" s="3">
+        <v>41.5</v>
+      </c>
+      <c r="J55" s="3">
+        <v>44</v>
+      </c>
+      <c r="K55" s="3">
+        <v>41</v>
+      </c>
+      <c r="L55" s="3">
+        <v>36</v>
+      </c>
+      <c r="M55" s="3">
+        <v>44</v>
+      </c>
+      <c r="N55" s="3">
+        <v>45</v>
+      </c>
+      <c r="O55" s="3">
+        <v>41.96</v>
+      </c>
+      <c r="P55" s="3">
+        <v>41</v>
+      </c>
+      <c r="Q55" s="3">
+        <v>45</v>
+      </c>
+      <c r="R55" s="3">
+        <v>46</v>
+      </c>
+      <c r="S55" s="3">
+        <v>46</v>
+      </c>
+      <c r="T55" s="3">
+        <v>43.5</v>
+      </c>
+      <c r="U55" s="3">
+        <v>44.25</v>
+      </c>
+      <c r="V55" s="3">
+        <v>42</v>
+      </c>
+      <c r="W55" s="3">
+        <v>47</v>
+      </c>
+      <c r="X55" s="3">
+        <v>45.25</v>
+      </c>
+      <c r="Y55" s="4">
         <f t="shared" si="0"/>
-        <v/>
+        <v>43.759130434782612</v>
       </c>
     </row>
     <row r="56" spans="1:25" x14ac:dyDescent="0.25">
@@ -24177,29 +24237,69 @@
       </c>
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A55" s="2"/>
-      <c r="B55" s="3"/>
-      <c r="C55" s="3"/>
-      <c r="D55" s="3"/>
-      <c r="E55" s="3"/>
-      <c r="F55" s="3"/>
-      <c r="G55" s="3"/>
-      <c r="H55" s="3"/>
-      <c r="I55" s="3"/>
-      <c r="J55" s="3"/>
-      <c r="K55" s="3"/>
-      <c r="L55" s="3"/>
-      <c r="M55" s="3"/>
-      <c r="N55" s="3"/>
-      <c r="O55" s="3"/>
-      <c r="P55" s="3"/>
-      <c r="Q55" s="3"/>
-      <c r="R55" s="3"/>
-      <c r="S55" s="3"/>
-      <c r="T55" s="3"/>
-      <c r="U55" s="4" t="str">
+      <c r="A55" s="2">
+        <v>46202</v>
+      </c>
+      <c r="B55" s="3">
+        <v>3.79</v>
+      </c>
+      <c r="C55" s="3">
+        <v>3.95</v>
+      </c>
+      <c r="D55" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="E55" s="3">
+        <v>3.59</v>
+      </c>
+      <c r="F55" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="G55" s="3">
+        <v>3.99</v>
+      </c>
+      <c r="H55" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="I55" s="3">
+        <v>3.39</v>
+      </c>
+      <c r="J55" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="K55" s="3">
+        <v>3.95</v>
+      </c>
+      <c r="L55" s="3">
+        <v>3.29</v>
+      </c>
+      <c r="M55" s="3">
+        <v>3.39</v>
+      </c>
+      <c r="N55" s="3">
+        <v>3.84</v>
+      </c>
+      <c r="O55" s="3">
+        <v>3.59</v>
+      </c>
+      <c r="P55" s="3">
+        <v>3.89</v>
+      </c>
+      <c r="Q55" s="3">
+        <v>3.65</v>
+      </c>
+      <c r="R55" s="3">
+        <v>3.89</v>
+      </c>
+      <c r="S55" s="3">
+        <v>4.99</v>
+      </c>
+      <c r="T55" s="3">
+        <v>1.99</v>
+      </c>
+      <c r="U55" s="4">
         <f t="shared" si="0"/>
-        <v/>
+        <v>3.5336842105263164</v>
       </c>
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
@@ -34734,7 +34834,9 @@
       <c r="A53" s="2">
         <v>46198</v>
       </c>
-      <c r="B53" s="3"/>
+      <c r="B53" s="3">
+        <v>2.89</v>
+      </c>
       <c r="C53" s="3">
         <v>3.14</v>
       </c>
@@ -34761,14 +34863,16 @@
       </c>
       <c r="K53" s="4">
         <f t="shared" ref="K53" si="17">IF(COUNTA(B53:J53)=0,"",AVERAGE(B53:J53))</f>
-        <v>2.9037500000000001</v>
+        <v>2.9022222222222225</v>
       </c>
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A54" s="2">
         <v>46199</v>
       </c>
-      <c r="B54" s="3"/>
+      <c r="B54" s="3">
+        <v>2.89</v>
+      </c>
       <c r="C54" s="3">
         <v>3.14</v>
       </c>
@@ -34795,23 +34899,43 @@
       </c>
       <c r="K54" s="4">
         <f t="shared" ref="K54" si="18">IF(COUNTA(B54:J54)=0,"",AVERAGE(B54:J54))</f>
-        <v>2.9037500000000001</v>
+        <v>2.9022222222222225</v>
       </c>
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A55" s="2"/>
-      <c r="B55" s="3"/>
-      <c r="C55" s="3"/>
-      <c r="D55" s="3"/>
-      <c r="E55" s="3"/>
-      <c r="F55" s="3"/>
-      <c r="G55" s="3"/>
-      <c r="H55" s="3"/>
-      <c r="I55" s="3"/>
-      <c r="J55" s="3"/>
-      <c r="K55" s="4" t="str">
+      <c r="A55" s="2">
+        <v>46202</v>
+      </c>
+      <c r="B55" s="3">
+        <v>2.89</v>
+      </c>
+      <c r="C55" s="3">
+        <v>3.14</v>
+      </c>
+      <c r="D55" s="3">
+        <v>2.8</v>
+      </c>
+      <c r="E55" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="F55" s="3">
+        <v>2.8</v>
+      </c>
+      <c r="G55" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="H55" s="3">
+        <v>2.69</v>
+      </c>
+      <c r="I55" s="3">
+        <v>2.89</v>
+      </c>
+      <c r="J55" s="3">
+        <v>2.89</v>
+      </c>
+      <c r="K55" s="4">
         <f t="shared" si="0"/>
-        <v/>
+        <v>2.8977777777777778</v>
       </c>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.25">
@@ -42220,20 +42344,42 @@
       </c>
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A55" s="2"/>
-      <c r="B55" s="3"/>
-      <c r="C55" s="3"/>
-      <c r="D55" s="3"/>
-      <c r="E55" s="3"/>
-      <c r="F55" s="3"/>
-      <c r="G55" s="3"/>
-      <c r="H55" s="3"/>
-      <c r="I55" s="3"/>
-      <c r="J55" s="3"/>
-      <c r="K55" s="3"/>
-      <c r="L55" s="4" t="str">
+      <c r="A55" s="2">
+        <v>46202</v>
+      </c>
+      <c r="B55" s="3">
+        <v>3.59</v>
+      </c>
+      <c r="C55" s="3">
+        <v>3.19</v>
+      </c>
+      <c r="D55" s="3">
+        <v>3.59</v>
+      </c>
+      <c r="E55" s="3">
+        <v>3.3650000000000002</v>
+      </c>
+      <c r="F55" s="3">
+        <v>3.43</v>
+      </c>
+      <c r="G55" s="3">
+        <v>3.89</v>
+      </c>
+      <c r="H55" s="3">
+        <v>3.09</v>
+      </c>
+      <c r="I55" s="3">
+        <v>3.29</v>
+      </c>
+      <c r="J55" s="3">
+        <v>3.46</v>
+      </c>
+      <c r="K55" s="3">
+        <v>3.29</v>
+      </c>
+      <c r="L55" s="4">
         <f t="shared" si="0"/>
-        <v/>
+        <v>3.4185000000000003</v>
       </c>
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.25">

--- a/app/mevduat-kredi-faizleri/data/hoca-ile-borsa-faiz-takip-sablonu-guncel.xlsx
+++ b/app/mevduat-kredi-faizleri/data/hoca-ile-borsa-faiz-takip-sablonu-guncel.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projeler\hoca-ile-borsa\app\mevduat-kredi-faizleri\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08AD2EF6-D4F2-4174-8C18-DABEE2D60CBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CD3DB31-D709-4868-91B5-56C7543E4FFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Mevduat" sheetId="1" r:id="rId1"/>
@@ -508,6 +508,9 @@
                 <c:pt idx="54">
                   <c:v>46206</c:v>
                 </c:pt>
+                <c:pt idx="55">
+                  <c:v>46209</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -683,7 +686,7 @@
                   <c:v>43.759130434782612</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>0</c:v>
+                  <c:v>43.7</c:v>
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>0</c:v>
@@ -1999,6 +2002,9 @@
                 <c:pt idx="54">
                   <c:v>46206</c:v>
                 </c:pt>
+                <c:pt idx="55">
+                  <c:v>46209</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2174,7 +2180,7 @@
                   <c:v>3.5336842105263164</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>0</c:v>
+                  <c:v>3.5257894736842101</c:v>
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>0</c:v>
@@ -3490,6 +3496,9 @@
                 <c:pt idx="54">
                   <c:v>46206</c:v>
                 </c:pt>
+                <c:pt idx="55">
+                  <c:v>46209</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3665,7 +3674,7 @@
                   <c:v>2.8977777777777778</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>0</c:v>
+                  <c:v>2.911111111111111</c:v>
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>0</c:v>
@@ -4981,6 +4990,9 @@
                 <c:pt idx="54">
                   <c:v>46206</c:v>
                 </c:pt>
+                <c:pt idx="55">
+                  <c:v>46209</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -5156,7 +5168,7 @@
                   <c:v>3.4185000000000003</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>0</c:v>
+                  <c:v>3.3600000000000003</c:v>
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>0</c:v>
@@ -11112,33 +11124,81 @@
       </c>
     </row>
     <row r="60" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A60" s="2"/>
-      <c r="B60" s="3"/>
-      <c r="C60" s="3"/>
-      <c r="D60" s="3"/>
-      <c r="E60" s="3"/>
-      <c r="F60" s="3"/>
-      <c r="G60" s="3"/>
-      <c r="H60" s="3"/>
-      <c r="I60" s="3"/>
-      <c r="J60" s="3"/>
-      <c r="K60" s="3"/>
-      <c r="L60" s="3"/>
-      <c r="M60" s="3"/>
-      <c r="N60" s="3"/>
-      <c r="O60" s="3"/>
-      <c r="P60" s="3"/>
-      <c r="Q60" s="3"/>
-      <c r="R60" s="3"/>
-      <c r="S60" s="3"/>
-      <c r="T60" s="3"/>
-      <c r="U60" s="3"/>
-      <c r="V60" s="3"/>
-      <c r="W60" s="3"/>
-      <c r="X60" s="3"/>
-      <c r="Y60" s="4" t="str">
+      <c r="A60" s="2">
+        <v>46209</v>
+      </c>
+      <c r="B60" s="3">
+        <v>42.5</v>
+      </c>
+      <c r="C60" s="3">
+        <v>46</v>
+      </c>
+      <c r="D60" s="3">
+        <v>46</v>
+      </c>
+      <c r="E60" s="3">
+        <v>46</v>
+      </c>
+      <c r="F60" s="3">
+        <v>45</v>
+      </c>
+      <c r="G60" s="3">
+        <v>41.5</v>
+      </c>
+      <c r="H60" s="3">
+        <v>46</v>
+      </c>
+      <c r="I60" s="3">
+        <v>41.5</v>
+      </c>
+      <c r="J60" s="3">
+        <v>44</v>
+      </c>
+      <c r="K60" s="3">
+        <v>41</v>
+      </c>
+      <c r="L60" s="3">
+        <v>36</v>
+      </c>
+      <c r="M60" s="3">
+        <v>44</v>
+      </c>
+      <c r="N60" s="3">
+        <v>45</v>
+      </c>
+      <c r="O60" s="3">
+        <v>42.35</v>
+      </c>
+      <c r="P60" s="3">
+        <v>41</v>
+      </c>
+      <c r="Q60" s="3">
+        <v>46</v>
+      </c>
+      <c r="R60" s="3">
+        <v>46</v>
+      </c>
+      <c r="S60" s="3">
+        <v>46</v>
+      </c>
+      <c r="T60" s="3">
+        <v>43.5</v>
+      </c>
+      <c r="U60" s="3">
+        <v>43.5</v>
+      </c>
+      <c r="V60" s="3">
+        <v>40</v>
+      </c>
+      <c r="W60" s="3">
+        <v>47</v>
+      </c>
+      <c r="X60" s="3">
+        <v>45.25</v>
+      </c>
+      <c r="Y60" s="4">
         <f t="shared" si="0"/>
-        <v/>
+        <v>43.7</v>
       </c>
     </row>
     <row r="61" spans="1:25" x14ac:dyDescent="0.25">
@@ -24812,29 +24872,69 @@
       </c>
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A60" s="2"/>
-      <c r="B60" s="3"/>
-      <c r="C60" s="3"/>
-      <c r="D60" s="3"/>
-      <c r="E60" s="3"/>
-      <c r="F60" s="3"/>
-      <c r="G60" s="3"/>
-      <c r="H60" s="3"/>
-      <c r="I60" s="3"/>
-      <c r="J60" s="3"/>
-      <c r="K60" s="3"/>
-      <c r="L60" s="3"/>
-      <c r="M60" s="3"/>
-      <c r="N60" s="3"/>
-      <c r="O60" s="3"/>
-      <c r="P60" s="3"/>
-      <c r="Q60" s="3"/>
-      <c r="R60" s="3"/>
-      <c r="S60" s="3"/>
-      <c r="T60" s="3"/>
-      <c r="U60" s="4" t="str">
+      <c r="A60" s="2">
+        <v>46209</v>
+      </c>
+      <c r="B60" s="3">
+        <v>3.79</v>
+      </c>
+      <c r="C60" s="3">
+        <v>3.95</v>
+      </c>
+      <c r="D60" s="3">
+        <v>3.39</v>
+      </c>
+      <c r="E60" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="F60" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="G60" s="3">
+        <v>3.99</v>
+      </c>
+      <c r="H60" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="I60" s="3">
+        <v>3.39</v>
+      </c>
+      <c r="J60" s="3">
+        <v>3.49</v>
+      </c>
+      <c r="K60" s="3">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="L60" s="3">
+        <v>3.29</v>
+      </c>
+      <c r="M60" s="3">
+        <v>3.39</v>
+      </c>
+      <c r="N60" s="3">
+        <v>3.84</v>
+      </c>
+      <c r="O60" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="P60" s="3">
+        <v>3.89</v>
+      </c>
+      <c r="Q60" s="3">
+        <v>3.65</v>
+      </c>
+      <c r="R60" s="3">
+        <v>3.89</v>
+      </c>
+      <c r="S60" s="3">
+        <v>4.99</v>
+      </c>
+      <c r="T60" s="3">
+        <v>1.99</v>
+      </c>
+      <c r="U60" s="4">
         <f t="shared" si="0"/>
-        <v/>
+        <v>3.5257894736842101</v>
       </c>
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
@@ -35488,19 +35588,39 @@
       </c>
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A60" s="2"/>
-      <c r="B60" s="3"/>
-      <c r="C60" s="3"/>
-      <c r="D60" s="3"/>
-      <c r="E60" s="3"/>
-      <c r="F60" s="3"/>
-      <c r="G60" s="3"/>
-      <c r="H60" s="3"/>
-      <c r="I60" s="3"/>
-      <c r="J60" s="3"/>
-      <c r="K60" s="4" t="str">
+      <c r="A60" s="2">
+        <v>46209</v>
+      </c>
+      <c r="B60" s="3">
+        <v>3.01</v>
+      </c>
+      <c r="C60" s="3">
+        <v>3.14</v>
+      </c>
+      <c r="D60" s="3">
+        <v>2.8</v>
+      </c>
+      <c r="E60" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="F60" s="3">
+        <v>2.8</v>
+      </c>
+      <c r="G60" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="H60" s="3">
+        <v>2.69</v>
+      </c>
+      <c r="I60" s="3">
+        <v>2.89</v>
+      </c>
+      <c r="J60" s="3">
+        <v>2.89</v>
+      </c>
+      <c r="K60" s="4">
         <f t="shared" si="0"/>
-        <v/>
+        <v>2.911111111111111</v>
       </c>
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.25">
@@ -43024,20 +43144,42 @@
       </c>
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A60" s="2"/>
-      <c r="B60" s="3"/>
-      <c r="C60" s="3"/>
-      <c r="D60" s="3"/>
-      <c r="E60" s="3"/>
-      <c r="F60" s="3"/>
-      <c r="G60" s="3"/>
-      <c r="H60" s="3"/>
-      <c r="I60" s="3"/>
-      <c r="J60" s="3"/>
-      <c r="K60" s="3"/>
-      <c r="L60" s="4" t="str">
+      <c r="A60" s="2">
+        <v>46209</v>
+      </c>
+      <c r="B60" s="3">
+        <v>3.18</v>
+      </c>
+      <c r="C60" s="3">
+        <v>3.19</v>
+      </c>
+      <c r="D60" s="3">
+        <v>3.59</v>
+      </c>
+      <c r="E60" s="3">
+        <v>3.59</v>
+      </c>
+      <c r="F60" s="3">
+        <v>3.43</v>
+      </c>
+      <c r="G60" s="3">
+        <v>3.49</v>
+      </c>
+      <c r="H60" s="3">
+        <v>3.09</v>
+      </c>
+      <c r="I60" s="3">
+        <v>3.29</v>
+      </c>
+      <c r="J60" s="3">
+        <v>3.46</v>
+      </c>
+      <c r="K60" s="3">
+        <v>3.29</v>
+      </c>
+      <c r="L60" s="4">
         <f t="shared" si="0"/>
-        <v/>
+        <v>3.3600000000000003</v>
       </c>
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.25">

--- a/app/mevduat-kredi-faizleri/data/hoca-ile-borsa-faiz-takip-sablonu-guncel.xlsx
+++ b/app/mevduat-kredi-faizleri/data/hoca-ile-borsa-faiz-takip-sablonu-guncel.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projeler\hoca-ile-borsa\app\mevduat-kredi-faizleri\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D622FF3-12A5-4679-9571-5297BAB0DFDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED42CB93-F9FB-44DF-84A8-5EFE1B1C98DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Mevduat" sheetId="1" r:id="rId1"/>
@@ -261,12 +261,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -523,6 +523,9 @@
                 <c:pt idx="59">
                   <c:v>46213</c:v>
                 </c:pt>
+                <c:pt idx="60">
+                  <c:v>46216</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -713,7 +716,7 @@
                   <c:v>43.7</c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>0</c:v>
+                  <c:v>43.670869565217387</c:v>
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>0</c:v>
@@ -2029,6 +2032,9 @@
                 <c:pt idx="59">
                   <c:v>46213</c:v>
                 </c:pt>
+                <c:pt idx="60">
+                  <c:v>46216</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2219,7 +2225,7 @@
                   <c:v>3.5257894736842101</c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>0</c:v>
+                  <c:v>3.5363157894736843</c:v>
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>0</c:v>
@@ -3535,6 +3541,9 @@
                 <c:pt idx="59">
                   <c:v>46213</c:v>
                 </c:pt>
+                <c:pt idx="60">
+                  <c:v>46216</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3725,7 +3734,7 @@
                   <c:v>2.911111111111111</c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>0</c:v>
+                  <c:v>2.911111111111111</c:v>
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>0</c:v>
@@ -5041,6 +5050,9 @@
                 <c:pt idx="59">
                   <c:v>46213</c:v>
                 </c:pt>
+                <c:pt idx="60">
+                  <c:v>46216</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -5231,7 +5243,7 @@
                   <c:v>3.3600000000000003</c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>0</c:v>
+                  <c:v>3.3600000000000003</c:v>
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>0</c:v>
@@ -6747,7 +6759,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="7"/>
@@ -6776,7 +6788,7 @@
       <c r="Y1" s="7"/>
     </row>
     <row r="2" spans="1:25" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="8" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="7"/>
@@ -11562,33 +11574,81 @@
       </c>
     </row>
     <row r="65" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A65" s="2"/>
-      <c r="B65" s="3"/>
-      <c r="C65" s="3"/>
-      <c r="D65" s="3"/>
-      <c r="E65" s="3"/>
-      <c r="F65" s="3"/>
-      <c r="G65" s="3"/>
-      <c r="H65" s="3"/>
-      <c r="I65" s="3"/>
-      <c r="J65" s="3"/>
-      <c r="K65" s="3"/>
-      <c r="L65" s="3"/>
-      <c r="M65" s="3"/>
-      <c r="N65" s="3"/>
-      <c r="O65" s="3"/>
-      <c r="P65" s="3"/>
-      <c r="Q65" s="3"/>
-      <c r="R65" s="3"/>
-      <c r="S65" s="3"/>
-      <c r="T65" s="3"/>
-      <c r="U65" s="3"/>
-      <c r="V65" s="3"/>
-      <c r="W65" s="3"/>
-      <c r="X65" s="3"/>
-      <c r="Y65" s="4" t="str">
+      <c r="A65" s="2">
+        <v>46216</v>
+      </c>
+      <c r="B65" s="3">
+        <v>42</v>
+      </c>
+      <c r="C65" s="3">
+        <v>46</v>
+      </c>
+      <c r="D65" s="3">
+        <v>46</v>
+      </c>
+      <c r="E65" s="3">
+        <v>46</v>
+      </c>
+      <c r="F65" s="3">
+        <v>45</v>
+      </c>
+      <c r="G65" s="3">
+        <v>40.5</v>
+      </c>
+      <c r="H65" s="3">
+        <v>47</v>
+      </c>
+      <c r="I65" s="3">
+        <v>41.5</v>
+      </c>
+      <c r="J65" s="3">
+        <v>44</v>
+      </c>
+      <c r="K65" s="3">
+        <v>41</v>
+      </c>
+      <c r="L65" s="3">
+        <v>36</v>
+      </c>
+      <c r="M65" s="3">
+        <v>44</v>
+      </c>
+      <c r="N65" s="3">
+        <v>45</v>
+      </c>
+      <c r="O65" s="3">
+        <v>42.18</v>
+      </c>
+      <c r="P65" s="3">
+        <v>40</v>
+      </c>
+      <c r="Q65" s="3">
+        <v>46</v>
+      </c>
+      <c r="R65" s="3">
+        <v>46</v>
+      </c>
+      <c r="S65" s="3">
+        <v>46</v>
+      </c>
+      <c r="T65" s="3">
+        <v>43.5</v>
+      </c>
+      <c r="U65" s="3">
+        <v>43.5</v>
+      </c>
+      <c r="V65" s="3">
+        <v>41</v>
+      </c>
+      <c r="W65" s="3">
+        <v>47</v>
+      </c>
+      <c r="X65" s="3">
+        <v>45.25</v>
+      </c>
+      <c r="Y65" s="4">
         <f t="shared" si="0"/>
-        <v/>
+        <v>43.670869565217387</v>
       </c>
     </row>
     <row r="66" spans="1:25" x14ac:dyDescent="0.25">
@@ -21367,7 +21427,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="6" t="s">
         <v>28</v>
       </c>
       <c r="B1" s="7"/>
@@ -21392,7 +21452,7 @@
       <c r="U1" s="7"/>
     </row>
     <row r="2" spans="1:21" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="8" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="7"/>
@@ -25442,29 +25502,69 @@
       </c>
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A65" s="2"/>
-      <c r="B65" s="3"/>
-      <c r="C65" s="3"/>
-      <c r="D65" s="3"/>
-      <c r="E65" s="3"/>
-      <c r="F65" s="3"/>
-      <c r="G65" s="3"/>
-      <c r="H65" s="3"/>
-      <c r="I65" s="3"/>
-      <c r="J65" s="3"/>
-      <c r="K65" s="3"/>
-      <c r="L65" s="3"/>
-      <c r="M65" s="3"/>
-      <c r="N65" s="3"/>
-      <c r="O65" s="3"/>
-      <c r="P65" s="3"/>
-      <c r="Q65" s="3"/>
-      <c r="R65" s="3"/>
-      <c r="S65" s="3"/>
-      <c r="T65" s="3"/>
-      <c r="U65" s="4" t="str">
+      <c r="A65" s="2">
+        <v>46216</v>
+      </c>
+      <c r="B65" s="3">
+        <v>3.79</v>
+      </c>
+      <c r="C65" s="3">
+        <v>3.95</v>
+      </c>
+      <c r="D65" s="3">
+        <v>3.69</v>
+      </c>
+      <c r="E65" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="F65" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="G65" s="3">
+        <v>3.99</v>
+      </c>
+      <c r="H65" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="I65" s="3">
+        <v>3.39</v>
+      </c>
+      <c r="J65" s="3">
+        <v>3.49</v>
+      </c>
+      <c r="K65" s="3">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="L65" s="3">
+        <v>3.19</v>
+      </c>
+      <c r="M65" s="3">
+        <v>3.39</v>
+      </c>
+      <c r="N65" s="3">
+        <v>3.84</v>
+      </c>
+      <c r="O65" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="P65" s="3">
+        <v>3.89</v>
+      </c>
+      <c r="Q65" s="3">
+        <v>3.65</v>
+      </c>
+      <c r="R65" s="3">
+        <v>3.89</v>
+      </c>
+      <c r="S65" s="3">
+        <v>4.99</v>
+      </c>
+      <c r="T65" s="3">
+        <v>1.99</v>
+      </c>
+      <c r="U65" s="4">
         <f t="shared" si="0"/>
-        <v/>
+        <v>3.5363157894736843</v>
       </c>
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
@@ -33943,7 +34043,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="6" t="s">
         <v>36</v>
       </c>
       <c r="B1" s="7"/>
@@ -33958,7 +34058,7 @@
       <c r="K1" s="7"/>
     </row>
     <row r="2" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="8" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="7"/>
@@ -36168,19 +36268,39 @@
       </c>
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A65" s="2"/>
-      <c r="B65" s="3"/>
-      <c r="C65" s="3"/>
-      <c r="D65" s="3"/>
-      <c r="E65" s="3"/>
-      <c r="F65" s="3"/>
-      <c r="G65" s="3"/>
-      <c r="H65" s="3"/>
-      <c r="I65" s="3"/>
-      <c r="J65" s="3"/>
-      <c r="K65" s="4" t="str">
+      <c r="A65" s="2">
+        <v>46216</v>
+      </c>
+      <c r="B65" s="3">
+        <v>3.01</v>
+      </c>
+      <c r="C65" s="3">
+        <v>3.14</v>
+      </c>
+      <c r="D65" s="3">
+        <v>2.8</v>
+      </c>
+      <c r="E65" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="F65" s="3">
+        <v>2.8</v>
+      </c>
+      <c r="G65" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="H65" s="3">
+        <v>2.69</v>
+      </c>
+      <c r="I65" s="3">
+        <v>2.89</v>
+      </c>
+      <c r="J65" s="3">
+        <v>2.89</v>
+      </c>
+      <c r="K65" s="4">
         <f t="shared" si="0"/>
-        <v/>
+        <v>2.911111111111111</v>
       </c>
     </row>
     <row r="66" spans="1:11" x14ac:dyDescent="0.25">
@@ -41409,7 +41529,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="6" t="s">
         <v>38</v>
       </c>
       <c r="B1" s="7"/>
@@ -41425,7 +41545,7 @@
       <c r="L1" s="7"/>
     </row>
     <row r="2" spans="1:12" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="8" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="7"/>
@@ -43819,20 +43939,42 @@
       </c>
     </row>
     <row r="65" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A65" s="2"/>
-      <c r="B65" s="3"/>
-      <c r="C65" s="3"/>
-      <c r="D65" s="3"/>
-      <c r="E65" s="3"/>
-      <c r="F65" s="3"/>
-      <c r="G65" s="3"/>
-      <c r="H65" s="3"/>
-      <c r="I65" s="3"/>
-      <c r="J65" s="3"/>
-      <c r="K65" s="3"/>
-      <c r="L65" s="4" t="str">
+      <c r="A65" s="2">
+        <v>46216</v>
+      </c>
+      <c r="B65" s="3">
+        <v>3.18</v>
+      </c>
+      <c r="C65" s="3">
+        <v>3.19</v>
+      </c>
+      <c r="D65" s="3">
+        <v>3.59</v>
+      </c>
+      <c r="E65" s="3">
+        <v>3.59</v>
+      </c>
+      <c r="F65" s="3">
+        <v>3.43</v>
+      </c>
+      <c r="G65" s="3">
+        <v>3.49</v>
+      </c>
+      <c r="H65" s="3">
+        <v>3.09</v>
+      </c>
+      <c r="I65" s="3">
+        <v>3.29</v>
+      </c>
+      <c r="J65" s="3">
+        <v>3.46</v>
+      </c>
+      <c r="K65" s="3">
+        <v>3.29</v>
+      </c>
+      <c r="L65" s="4">
         <f t="shared" si="0"/>
-        <v/>
+        <v>3.3600000000000003</v>
       </c>
     </row>
     <row r="66" spans="1:12" x14ac:dyDescent="0.25">

--- a/app/mevduat-kredi-faizleri/data/hoca-ile-borsa-faiz-takip-sablonu-guncel.xlsx
+++ b/app/mevduat-kredi-faizleri/data/hoca-ile-borsa-faiz-takip-sablonu-guncel.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projeler\hoca-ile-borsa\app\mevduat-kredi-faizleri\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10AD5EC8-4570-42B8-BFA4-2F48B59B8D00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA38FFEF-3CD5-45F3-89DF-CDCAE3770286}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Mevduat" sheetId="1" r:id="rId1"/>
@@ -547,6 +547,9 @@
                 <c:pt idx="67">
                   <c:v>46226</c:v>
                 </c:pt>
+                <c:pt idx="68">
+                  <c:v>46227</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -761,7 +764,7 @@
                   <c:v>43.670869565217387</c:v>
                 </c:pt>
                 <c:pt idx="68">
-                  <c:v>0</c:v>
+                  <c:v>43.508695652173913</c:v>
                 </c:pt>
                 <c:pt idx="69">
                   <c:v>0</c:v>
@@ -2077,6 +2080,9 @@
                 <c:pt idx="67">
                   <c:v>46226</c:v>
                 </c:pt>
+                <c:pt idx="68">
+                  <c:v>46227</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2291,7 +2297,7 @@
                   <c:v>3.5363157894736843</c:v>
                 </c:pt>
                 <c:pt idx="68">
-                  <c:v>0</c:v>
+                  <c:v>3.5600000000000009</c:v>
                 </c:pt>
                 <c:pt idx="69">
                   <c:v>0</c:v>
@@ -3607,6 +3613,9 @@
                 <c:pt idx="67">
                   <c:v>46226</c:v>
                 </c:pt>
+                <c:pt idx="68">
+                  <c:v>46227</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3821,7 +3830,7 @@
                   <c:v>2.911111111111111</c:v>
                 </c:pt>
                 <c:pt idx="68">
-                  <c:v>0</c:v>
+                  <c:v>2.9155555555555557</c:v>
                 </c:pt>
                 <c:pt idx="69">
                   <c:v>0</c:v>
@@ -5137,6 +5146,9 @@
                 <c:pt idx="67">
                   <c:v>46226</c:v>
                 </c:pt>
+                <c:pt idx="68">
+                  <c:v>46227</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -5351,7 +5363,7 @@
                   <c:v>3.3600000000000003</c:v>
                 </c:pt>
                 <c:pt idx="68">
-                  <c:v>0</c:v>
+                  <c:v>3.3579999999999997</c:v>
                 </c:pt>
                 <c:pt idx="69">
                   <c:v>0</c:v>
@@ -12282,33 +12294,81 @@
       </c>
     </row>
     <row r="73" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A73" s="2"/>
-      <c r="B73" s="3"/>
-      <c r="C73" s="3"/>
-      <c r="D73" s="3"/>
-      <c r="E73" s="3"/>
-      <c r="F73" s="3"/>
-      <c r="G73" s="3"/>
-      <c r="H73" s="3"/>
-      <c r="I73" s="3"/>
-      <c r="J73" s="3"/>
-      <c r="K73" s="3"/>
-      <c r="L73" s="3"/>
-      <c r="M73" s="3"/>
-      <c r="N73" s="3"/>
-      <c r="O73" s="3"/>
-      <c r="P73" s="3"/>
-      <c r="Q73" s="3"/>
-      <c r="R73" s="3"/>
-      <c r="S73" s="3"/>
-      <c r="T73" s="3"/>
-      <c r="U73" s="3"/>
-      <c r="V73" s="3"/>
-      <c r="W73" s="3"/>
-      <c r="X73" s="3"/>
-      <c r="Y73" s="4" t="str">
-        <f t="shared" ref="Y72:Y132" si="26">IF(COUNTA(B73:X73)=0,"",AVERAGE(B73:X73))</f>
-        <v/>
+      <c r="A73" s="2">
+        <v>46227</v>
+      </c>
+      <c r="B73" s="3">
+        <v>41.5</v>
+      </c>
+      <c r="C73" s="3">
+        <v>46</v>
+      </c>
+      <c r="D73" s="3">
+        <v>46</v>
+      </c>
+      <c r="E73" s="3">
+        <v>45</v>
+      </c>
+      <c r="F73" s="3">
+        <v>45</v>
+      </c>
+      <c r="G73" s="3">
+        <v>40</v>
+      </c>
+      <c r="H73" s="3">
+        <v>47</v>
+      </c>
+      <c r="I73" s="3">
+        <v>41</v>
+      </c>
+      <c r="J73" s="3">
+        <v>44</v>
+      </c>
+      <c r="K73" s="3">
+        <v>41</v>
+      </c>
+      <c r="L73" s="3">
+        <v>36</v>
+      </c>
+      <c r="M73" s="3">
+        <v>45</v>
+      </c>
+      <c r="N73" s="3">
+        <v>45</v>
+      </c>
+      <c r="O73" s="3">
+        <v>41.95</v>
+      </c>
+      <c r="P73" s="3">
+        <v>40</v>
+      </c>
+      <c r="Q73" s="3">
+        <v>46</v>
+      </c>
+      <c r="R73" s="3">
+        <v>46</v>
+      </c>
+      <c r="S73" s="3">
+        <v>45</v>
+      </c>
+      <c r="T73" s="3">
+        <v>43.5</v>
+      </c>
+      <c r="U73" s="3">
+        <v>43.5</v>
+      </c>
+      <c r="V73" s="3">
+        <v>40</v>
+      </c>
+      <c r="W73" s="3">
+        <v>47</v>
+      </c>
+      <c r="X73" s="3">
+        <v>45.25</v>
+      </c>
+      <c r="Y73" s="4">
+        <f t="shared" ref="Y73:Y132" si="26">IF(COUNTA(B73:X73)=0,"",AVERAGE(B73:X73))</f>
+        <v>43.508695652173913</v>
       </c>
     </row>
     <row r="74" spans="1:25" x14ac:dyDescent="0.25">
@@ -26450,29 +26510,69 @@
       </c>
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A73" s="2"/>
-      <c r="B73" s="3"/>
-      <c r="C73" s="3"/>
-      <c r="D73" s="3"/>
-      <c r="E73" s="3"/>
-      <c r="F73" s="3"/>
-      <c r="G73" s="3"/>
-      <c r="H73" s="3"/>
-      <c r="I73" s="3"/>
-      <c r="J73" s="3"/>
-      <c r="K73" s="3"/>
-      <c r="L73" s="3"/>
-      <c r="M73" s="3"/>
-      <c r="N73" s="3"/>
-      <c r="O73" s="3"/>
-      <c r="P73" s="3"/>
-      <c r="Q73" s="3"/>
-      <c r="R73" s="3"/>
-      <c r="S73" s="3"/>
-      <c r="T73" s="3"/>
-      <c r="U73" s="4" t="str">
-        <f t="shared" ref="U72:U132" si="34">IF(COUNTA(B73:T73)=0,"",AVERAGE(B73:T73))</f>
-        <v/>
+      <c r="A73" s="2">
+        <v>46227</v>
+      </c>
+      <c r="B73" s="3">
+        <v>3.79</v>
+      </c>
+      <c r="C73" s="3">
+        <v>3.95</v>
+      </c>
+      <c r="D73" s="3">
+        <v>3.69</v>
+      </c>
+      <c r="E73" s="3">
+        <v>2.89</v>
+      </c>
+      <c r="F73" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="G73" s="3">
+        <v>3.99</v>
+      </c>
+      <c r="H73" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="I73" s="3">
+        <v>3.39</v>
+      </c>
+      <c r="J73" s="3">
+        <v>3.49</v>
+      </c>
+      <c r="K73" s="3">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="L73" s="3">
+        <v>3.29</v>
+      </c>
+      <c r="M73" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="N73" s="3">
+        <v>3.84</v>
+      </c>
+      <c r="O73" s="3">
+        <v>3.84</v>
+      </c>
+      <c r="P73" s="3">
+        <v>3.89</v>
+      </c>
+      <c r="Q73" s="3">
+        <v>3.65</v>
+      </c>
+      <c r="R73" s="3">
+        <v>3.89</v>
+      </c>
+      <c r="S73" s="3">
+        <v>4.99</v>
+      </c>
+      <c r="T73" s="3">
+        <v>1.99</v>
+      </c>
+      <c r="U73" s="4">
+        <f t="shared" ref="U73:U132" si="34">IF(COUNTA(B73:T73)=0,"",AVERAGE(B73:T73))</f>
+        <v>3.5600000000000009</v>
       </c>
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
@@ -37256,19 +37356,39 @@
       </c>
     </row>
     <row r="73" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A73" s="2"/>
-      <c r="B73" s="3"/>
-      <c r="C73" s="3"/>
-      <c r="D73" s="3"/>
-      <c r="E73" s="3"/>
-      <c r="F73" s="3"/>
-      <c r="G73" s="3"/>
-      <c r="H73" s="3"/>
-      <c r="I73" s="3"/>
-      <c r="J73" s="3"/>
-      <c r="K73" s="4" t="str">
-        <f t="shared" ref="K72:K132" si="34">IF(COUNTA(B73:J73)=0,"",AVERAGE(B73:J73))</f>
-        <v/>
+      <c r="A73" s="2">
+        <v>46227</v>
+      </c>
+      <c r="B73" s="3">
+        <v>3.1</v>
+      </c>
+      <c r="C73" s="3">
+        <v>3.14</v>
+      </c>
+      <c r="D73" s="3">
+        <v>2.8</v>
+      </c>
+      <c r="E73" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="F73" s="3">
+        <v>2.79</v>
+      </c>
+      <c r="G73" s="3">
+        <v>2.95</v>
+      </c>
+      <c r="H73" s="3">
+        <v>2.69</v>
+      </c>
+      <c r="I73" s="3">
+        <v>2.89</v>
+      </c>
+      <c r="J73" s="3">
+        <v>2.89</v>
+      </c>
+      <c r="K73" s="4">
+        <f t="shared" ref="K73:K132" si="34">IF(COUNTA(B73:J73)=0,"",AVERAGE(B73:J73))</f>
+        <v>2.9155555555555557</v>
       </c>
     </row>
     <row r="74" spans="1:11" x14ac:dyDescent="0.25">
@@ -45091,20 +45211,42 @@
       </c>
     </row>
     <row r="73" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A73" s="2"/>
-      <c r="B73" s="3"/>
-      <c r="C73" s="3"/>
-      <c r="D73" s="3"/>
-      <c r="E73" s="3"/>
-      <c r="F73" s="3"/>
-      <c r="G73" s="3"/>
-      <c r="H73" s="3"/>
-      <c r="I73" s="3"/>
-      <c r="J73" s="3"/>
-      <c r="K73" s="3"/>
-      <c r="L73" s="4" t="str">
-        <f t="shared" ref="L72:L132" si="34">IF(COUNTA(B73:K73)=0,"",AVERAGE(B73:K73))</f>
-        <v/>
+      <c r="A73" s="2">
+        <v>46227</v>
+      </c>
+      <c r="B73" s="3">
+        <v>3.18</v>
+      </c>
+      <c r="C73" s="3">
+        <v>3.19</v>
+      </c>
+      <c r="D73" s="3">
+        <v>3.59</v>
+      </c>
+      <c r="E73" s="3">
+        <v>3.59</v>
+      </c>
+      <c r="F73" s="3">
+        <v>3.45</v>
+      </c>
+      <c r="G73" s="3">
+        <v>3.49</v>
+      </c>
+      <c r="H73" s="3">
+        <v>3.09</v>
+      </c>
+      <c r="I73" s="3">
+        <v>3.29</v>
+      </c>
+      <c r="J73" s="3">
+        <v>3.42</v>
+      </c>
+      <c r="K73" s="3">
+        <v>3.29</v>
+      </c>
+      <c r="L73" s="4">
+        <f t="shared" ref="L73:L132" si="34">IF(COUNTA(B73:K73)=0,"",AVERAGE(B73:K73))</f>
+        <v>3.3579999999999997</v>
       </c>
     </row>
     <row r="74" spans="1:12" x14ac:dyDescent="0.25">

--- a/app/mevduat-kredi-faizleri/data/hoca-ile-borsa-faiz-takip-sablonu-guncel.xlsx
+++ b/app/mevduat-kredi-faizleri/data/hoca-ile-borsa-faiz-takip-sablonu-guncel.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projeler\hoca-ile-borsa\app\mevduat-kredi-faizleri\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA38FFEF-3CD5-45F3-89DF-CDCAE3770286}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCBE0F7C-DF6A-4280-8995-8AF5CF4E27D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -261,12 +261,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -550,6 +550,9 @@
                 <c:pt idx="68">
                   <c:v>46227</c:v>
                 </c:pt>
+                <c:pt idx="69">
+                  <c:v>46230</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -767,7 +770,7 @@
                   <c:v>43.508695652173913</c:v>
                 </c:pt>
                 <c:pt idx="69">
-                  <c:v>0</c:v>
+                  <c:v>43.508695652173913</c:v>
                 </c:pt>
                 <c:pt idx="70">
                   <c:v>0</c:v>
@@ -2083,6 +2086,9 @@
                 <c:pt idx="68">
                   <c:v>46227</c:v>
                 </c:pt>
+                <c:pt idx="69">
+                  <c:v>46230</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2300,7 +2306,7 @@
                   <c:v>3.5600000000000009</c:v>
                 </c:pt>
                 <c:pt idx="69">
-                  <c:v>0</c:v>
+                  <c:v>3.5600000000000009</c:v>
                 </c:pt>
                 <c:pt idx="70">
                   <c:v>0</c:v>
@@ -3616,6 +3622,9 @@
                 <c:pt idx="68">
                   <c:v>46227</c:v>
                 </c:pt>
+                <c:pt idx="69">
+                  <c:v>46230</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3833,7 +3842,7 @@
                   <c:v>2.9155555555555557</c:v>
                 </c:pt>
                 <c:pt idx="69">
-                  <c:v>0</c:v>
+                  <c:v>2.9155555555555557</c:v>
                 </c:pt>
                 <c:pt idx="70">
                   <c:v>0</c:v>
@@ -5149,6 +5158,9 @@
                 <c:pt idx="68">
                   <c:v>46227</c:v>
                 </c:pt>
+                <c:pt idx="69">
+                  <c:v>46230</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -5366,7 +5378,7 @@
                   <c:v>3.3579999999999997</c:v>
                 </c:pt>
                 <c:pt idx="69">
-                  <c:v>0</c:v>
+                  <c:v>3.3579999999999997</c:v>
                 </c:pt>
                 <c:pt idx="70">
                   <c:v>0</c:v>
@@ -6855,7 +6867,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="7"/>
@@ -6884,7 +6896,7 @@
       <c r="Y1" s="7"/>
     </row>
     <row r="2" spans="1:25" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="6" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="7"/>
@@ -12372,33 +12384,81 @@
       </c>
     </row>
     <row r="74" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A74" s="2"/>
-      <c r="B74" s="3"/>
-      <c r="C74" s="3"/>
-      <c r="D74" s="3"/>
-      <c r="E74" s="3"/>
-      <c r="F74" s="3"/>
-      <c r="G74" s="3"/>
-      <c r="H74" s="3"/>
-      <c r="I74" s="3"/>
-      <c r="J74" s="3"/>
-      <c r="K74" s="3"/>
-      <c r="L74" s="3"/>
-      <c r="M74" s="3"/>
-      <c r="N74" s="3"/>
-      <c r="O74" s="3"/>
-      <c r="P74" s="3"/>
-      <c r="Q74" s="3"/>
-      <c r="R74" s="3"/>
-      <c r="S74" s="3"/>
-      <c r="T74" s="3"/>
-      <c r="U74" s="3"/>
-      <c r="V74" s="3"/>
-      <c r="W74" s="3"/>
-      <c r="X74" s="3"/>
-      <c r="Y74" s="4" t="str">
-        <f t="shared" si="26"/>
-        <v/>
+      <c r="A74" s="2">
+        <v>46230</v>
+      </c>
+      <c r="B74" s="3">
+        <v>41.5</v>
+      </c>
+      <c r="C74" s="3">
+        <v>46</v>
+      </c>
+      <c r="D74" s="3">
+        <v>46</v>
+      </c>
+      <c r="E74" s="3">
+        <v>45</v>
+      </c>
+      <c r="F74" s="3">
+        <v>45</v>
+      </c>
+      <c r="G74" s="3">
+        <v>40</v>
+      </c>
+      <c r="H74" s="3">
+        <v>47</v>
+      </c>
+      <c r="I74" s="3">
+        <v>41</v>
+      </c>
+      <c r="J74" s="3">
+        <v>44</v>
+      </c>
+      <c r="K74" s="3">
+        <v>41</v>
+      </c>
+      <c r="L74" s="3">
+        <v>36</v>
+      </c>
+      <c r="M74" s="3">
+        <v>45</v>
+      </c>
+      <c r="N74" s="3">
+        <v>45</v>
+      </c>
+      <c r="O74" s="3">
+        <v>41.95</v>
+      </c>
+      <c r="P74" s="3">
+        <v>40</v>
+      </c>
+      <c r="Q74" s="3">
+        <v>46</v>
+      </c>
+      <c r="R74" s="3">
+        <v>46</v>
+      </c>
+      <c r="S74" s="3">
+        <v>45</v>
+      </c>
+      <c r="T74" s="3">
+        <v>43.5</v>
+      </c>
+      <c r="U74" s="3">
+        <v>43.5</v>
+      </c>
+      <c r="V74" s="3">
+        <v>40</v>
+      </c>
+      <c r="W74" s="3">
+        <v>47</v>
+      </c>
+      <c r="X74" s="3">
+        <v>45.25</v>
+      </c>
+      <c r="Y74" s="4">
+        <f t="shared" ref="Y74" si="27">IF(COUNTA(B74:X74)=0,"",AVERAGE(B74:X74))</f>
+        <v>43.508695652173913</v>
       </c>
     </row>
     <row r="75" spans="1:25" x14ac:dyDescent="0.25">
@@ -14167,7 +14227,7 @@
       <c r="W133" s="3"/>
       <c r="X133" s="3"/>
       <c r="Y133" s="4" t="str">
-        <f t="shared" ref="Y133:Y196" si="27">IF(COUNTA(B133:X133)=0,"",AVERAGE(B133:X133))</f>
+        <f t="shared" ref="Y133:Y196" si="28">IF(COUNTA(B133:X133)=0,"",AVERAGE(B133:X133))</f>
         <v/>
       </c>
     </row>
@@ -14197,7 +14257,7 @@
       <c r="W134" s="3"/>
       <c r="X134" s="3"/>
       <c r="Y134" s="4" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
     </row>
@@ -14227,7 +14287,7 @@
       <c r="W135" s="3"/>
       <c r="X135" s="3"/>
       <c r="Y135" s="4" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
     </row>
@@ -14257,7 +14317,7 @@
       <c r="W136" s="3"/>
       <c r="X136" s="3"/>
       <c r="Y136" s="4" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
     </row>
@@ -14287,7 +14347,7 @@
       <c r="W137" s="3"/>
       <c r="X137" s="3"/>
       <c r="Y137" s="4" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
     </row>
@@ -14317,7 +14377,7 @@
       <c r="W138" s="3"/>
       <c r="X138" s="3"/>
       <c r="Y138" s="4" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
     </row>
@@ -14347,7 +14407,7 @@
       <c r="W139" s="3"/>
       <c r="X139" s="3"/>
       <c r="Y139" s="4" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
     </row>
@@ -14377,7 +14437,7 @@
       <c r="W140" s="3"/>
       <c r="X140" s="3"/>
       <c r="Y140" s="4" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
     </row>
@@ -14407,7 +14467,7 @@
       <c r="W141" s="3"/>
       <c r="X141" s="3"/>
       <c r="Y141" s="4" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
     </row>
@@ -14437,7 +14497,7 @@
       <c r="W142" s="3"/>
       <c r="X142" s="3"/>
       <c r="Y142" s="4" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
     </row>
@@ -14467,7 +14527,7 @@
       <c r="W143" s="3"/>
       <c r="X143" s="3"/>
       <c r="Y143" s="4" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
     </row>
@@ -14497,7 +14557,7 @@
       <c r="W144" s="3"/>
       <c r="X144" s="3"/>
       <c r="Y144" s="4" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
     </row>
@@ -14527,7 +14587,7 @@
       <c r="W145" s="3"/>
       <c r="X145" s="3"/>
       <c r="Y145" s="4" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
     </row>
@@ -14557,7 +14617,7 @@
       <c r="W146" s="3"/>
       <c r="X146" s="3"/>
       <c r="Y146" s="4" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
     </row>
@@ -14587,7 +14647,7 @@
       <c r="W147" s="3"/>
       <c r="X147" s="3"/>
       <c r="Y147" s="4" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
     </row>
@@ -14617,7 +14677,7 @@
       <c r="W148" s="3"/>
       <c r="X148" s="3"/>
       <c r="Y148" s="4" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
     </row>
@@ -14647,7 +14707,7 @@
       <c r="W149" s="3"/>
       <c r="X149" s="3"/>
       <c r="Y149" s="4" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
     </row>
@@ -14677,7 +14737,7 @@
       <c r="W150" s="3"/>
       <c r="X150" s="3"/>
       <c r="Y150" s="4" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
     </row>
@@ -14707,7 +14767,7 @@
       <c r="W151" s="3"/>
       <c r="X151" s="3"/>
       <c r="Y151" s="4" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
     </row>
@@ -14737,7 +14797,7 @@
       <c r="W152" s="3"/>
       <c r="X152" s="3"/>
       <c r="Y152" s="4" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
     </row>
@@ -14767,7 +14827,7 @@
       <c r="W153" s="3"/>
       <c r="X153" s="3"/>
       <c r="Y153" s="4" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
     </row>
@@ -14797,7 +14857,7 @@
       <c r="W154" s="3"/>
       <c r="X154" s="3"/>
       <c r="Y154" s="4" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
     </row>
@@ -14827,7 +14887,7 @@
       <c r="W155" s="3"/>
       <c r="X155" s="3"/>
       <c r="Y155" s="4" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
     </row>
@@ -14857,7 +14917,7 @@
       <c r="W156" s="3"/>
       <c r="X156" s="3"/>
       <c r="Y156" s="4" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
     </row>
@@ -14887,7 +14947,7 @@
       <c r="W157" s="3"/>
       <c r="X157" s="3"/>
       <c r="Y157" s="4" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
     </row>
@@ -14917,7 +14977,7 @@
       <c r="W158" s="3"/>
       <c r="X158" s="3"/>
       <c r="Y158" s="4" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
     </row>
@@ -14947,7 +15007,7 @@
       <c r="W159" s="3"/>
       <c r="X159" s="3"/>
       <c r="Y159" s="4" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
     </row>
@@ -14977,7 +15037,7 @@
       <c r="W160" s="3"/>
       <c r="X160" s="3"/>
       <c r="Y160" s="4" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
     </row>
@@ -15007,7 +15067,7 @@
       <c r="W161" s="3"/>
       <c r="X161" s="3"/>
       <c r="Y161" s="4" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
     </row>
@@ -15037,7 +15097,7 @@
       <c r="W162" s="3"/>
       <c r="X162" s="3"/>
       <c r="Y162" s="4" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
     </row>
@@ -15067,7 +15127,7 @@
       <c r="W163" s="3"/>
       <c r="X163" s="3"/>
       <c r="Y163" s="4" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
     </row>
@@ -15097,7 +15157,7 @@
       <c r="W164" s="3"/>
       <c r="X164" s="3"/>
       <c r="Y164" s="4" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
     </row>
@@ -15127,7 +15187,7 @@
       <c r="W165" s="3"/>
       <c r="X165" s="3"/>
       <c r="Y165" s="4" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
     </row>
@@ -15157,7 +15217,7 @@
       <c r="W166" s="3"/>
       <c r="X166" s="3"/>
       <c r="Y166" s="4" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
     </row>
@@ -15187,7 +15247,7 @@
       <c r="W167" s="3"/>
       <c r="X167" s="3"/>
       <c r="Y167" s="4" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
     </row>
@@ -15217,7 +15277,7 @@
       <c r="W168" s="3"/>
       <c r="X168" s="3"/>
       <c r="Y168" s="4" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
     </row>
@@ -15247,7 +15307,7 @@
       <c r="W169" s="3"/>
       <c r="X169" s="3"/>
       <c r="Y169" s="4" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
     </row>
@@ -15277,7 +15337,7 @@
       <c r="W170" s="3"/>
       <c r="X170" s="3"/>
       <c r="Y170" s="4" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
     </row>
@@ -15307,7 +15367,7 @@
       <c r="W171" s="3"/>
       <c r="X171" s="3"/>
       <c r="Y171" s="4" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
     </row>
@@ -15337,7 +15397,7 @@
       <c r="W172" s="3"/>
       <c r="X172" s="3"/>
       <c r="Y172" s="4" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
     </row>
@@ -15367,7 +15427,7 @@
       <c r="W173" s="3"/>
       <c r="X173" s="3"/>
       <c r="Y173" s="4" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
     </row>
@@ -15397,7 +15457,7 @@
       <c r="W174" s="3"/>
       <c r="X174" s="3"/>
       <c r="Y174" s="4" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
     </row>
@@ -15427,7 +15487,7 @@
       <c r="W175" s="3"/>
       <c r="X175" s="3"/>
       <c r="Y175" s="4" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
     </row>
@@ -15457,7 +15517,7 @@
       <c r="W176" s="3"/>
       <c r="X176" s="3"/>
       <c r="Y176" s="4" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
     </row>
@@ -15487,7 +15547,7 @@
       <c r="W177" s="3"/>
       <c r="X177" s="3"/>
       <c r="Y177" s="4" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
     </row>
@@ -15517,7 +15577,7 @@
       <c r="W178" s="3"/>
       <c r="X178" s="3"/>
       <c r="Y178" s="4" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
     </row>
@@ -15547,7 +15607,7 @@
       <c r="W179" s="3"/>
       <c r="X179" s="3"/>
       <c r="Y179" s="4" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
     </row>
@@ -15577,7 +15637,7 @@
       <c r="W180" s="3"/>
       <c r="X180" s="3"/>
       <c r="Y180" s="4" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
     </row>
@@ -15607,7 +15667,7 @@
       <c r="W181" s="3"/>
       <c r="X181" s="3"/>
       <c r="Y181" s="4" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
     </row>
@@ -15637,7 +15697,7 @@
       <c r="W182" s="3"/>
       <c r="X182" s="3"/>
       <c r="Y182" s="4" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
     </row>
@@ -15667,7 +15727,7 @@
       <c r="W183" s="3"/>
       <c r="X183" s="3"/>
       <c r="Y183" s="4" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
     </row>
@@ -15697,7 +15757,7 @@
       <c r="W184" s="3"/>
       <c r="X184" s="3"/>
       <c r="Y184" s="4" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
     </row>
@@ -15727,7 +15787,7 @@
       <c r="W185" s="3"/>
       <c r="X185" s="3"/>
       <c r="Y185" s="4" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
     </row>
@@ -15757,7 +15817,7 @@
       <c r="W186" s="3"/>
       <c r="X186" s="3"/>
       <c r="Y186" s="4" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
     </row>
@@ -15787,7 +15847,7 @@
       <c r="W187" s="3"/>
       <c r="X187" s="3"/>
       <c r="Y187" s="4" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
     </row>
@@ -15817,7 +15877,7 @@
       <c r="W188" s="3"/>
       <c r="X188" s="3"/>
       <c r="Y188" s="4" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
     </row>
@@ -15847,7 +15907,7 @@
       <c r="W189" s="3"/>
       <c r="X189" s="3"/>
       <c r="Y189" s="4" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
     </row>
@@ -15877,7 +15937,7 @@
       <c r="W190" s="3"/>
       <c r="X190" s="3"/>
       <c r="Y190" s="4" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
     </row>
@@ -15907,7 +15967,7 @@
       <c r="W191" s="3"/>
       <c r="X191" s="3"/>
       <c r="Y191" s="4" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
     </row>
@@ -15937,7 +15997,7 @@
       <c r="W192" s="3"/>
       <c r="X192" s="3"/>
       <c r="Y192" s="4" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
     </row>
@@ -15967,7 +16027,7 @@
       <c r="W193" s="3"/>
       <c r="X193" s="3"/>
       <c r="Y193" s="4" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
     </row>
@@ -15997,7 +16057,7 @@
       <c r="W194" s="3"/>
       <c r="X194" s="3"/>
       <c r="Y194" s="4" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
     </row>
@@ -16027,7 +16087,7 @@
       <c r="W195" s="3"/>
       <c r="X195" s="3"/>
       <c r="Y195" s="4" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
     </row>
@@ -16057,7 +16117,7 @@
       <c r="W196" s="3"/>
       <c r="X196" s="3"/>
       <c r="Y196" s="4" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
     </row>
@@ -16087,7 +16147,7 @@
       <c r="W197" s="3"/>
       <c r="X197" s="3"/>
       <c r="Y197" s="4" t="str">
-        <f t="shared" ref="Y197:Y260" si="28">IF(COUNTA(B197:X197)=0,"",AVERAGE(B197:X197))</f>
+        <f t="shared" ref="Y197:Y260" si="29">IF(COUNTA(B197:X197)=0,"",AVERAGE(B197:X197))</f>
         <v/>
       </c>
     </row>
@@ -16117,7 +16177,7 @@
       <c r="W198" s="3"/>
       <c r="X198" s="3"/>
       <c r="Y198" s="4" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
     </row>
@@ -16147,7 +16207,7 @@
       <c r="W199" s="3"/>
       <c r="X199" s="3"/>
       <c r="Y199" s="4" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
     </row>
@@ -16177,7 +16237,7 @@
       <c r="W200" s="3"/>
       <c r="X200" s="3"/>
       <c r="Y200" s="4" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
     </row>
@@ -16207,7 +16267,7 @@
       <c r="W201" s="3"/>
       <c r="X201" s="3"/>
       <c r="Y201" s="4" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
     </row>
@@ -16237,7 +16297,7 @@
       <c r="W202" s="3"/>
       <c r="X202" s="3"/>
       <c r="Y202" s="4" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
     </row>
@@ -16267,7 +16327,7 @@
       <c r="W203" s="3"/>
       <c r="X203" s="3"/>
       <c r="Y203" s="4" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
     </row>
@@ -16297,7 +16357,7 @@
       <c r="W204" s="3"/>
       <c r="X204" s="3"/>
       <c r="Y204" s="4" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
     </row>
@@ -16327,7 +16387,7 @@
       <c r="W205" s="3"/>
       <c r="X205" s="3"/>
       <c r="Y205" s="4" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
     </row>
@@ -16357,7 +16417,7 @@
       <c r="W206" s="3"/>
       <c r="X206" s="3"/>
       <c r="Y206" s="4" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
     </row>
@@ -16387,7 +16447,7 @@
       <c r="W207" s="3"/>
       <c r="X207" s="3"/>
       <c r="Y207" s="4" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
     </row>
@@ -16417,7 +16477,7 @@
       <c r="W208" s="3"/>
       <c r="X208" s="3"/>
       <c r="Y208" s="4" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
     </row>
@@ -16447,7 +16507,7 @@
       <c r="W209" s="3"/>
       <c r="X209" s="3"/>
       <c r="Y209" s="4" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
     </row>
@@ -16477,7 +16537,7 @@
       <c r="W210" s="3"/>
       <c r="X210" s="3"/>
       <c r="Y210" s="4" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
     </row>
@@ -16507,7 +16567,7 @@
       <c r="W211" s="3"/>
       <c r="X211" s="3"/>
       <c r="Y211" s="4" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
     </row>
@@ -16537,7 +16597,7 @@
       <c r="W212" s="3"/>
       <c r="X212" s="3"/>
       <c r="Y212" s="4" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
     </row>
@@ -16567,7 +16627,7 @@
       <c r="W213" s="3"/>
       <c r="X213" s="3"/>
       <c r="Y213" s="4" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
     </row>
@@ -16597,7 +16657,7 @@
       <c r="W214" s="3"/>
       <c r="X214" s="3"/>
       <c r="Y214" s="4" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
     </row>
@@ -16627,7 +16687,7 @@
       <c r="W215" s="3"/>
       <c r="X215" s="3"/>
       <c r="Y215" s="4" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
     </row>
@@ -16657,7 +16717,7 @@
       <c r="W216" s="3"/>
       <c r="X216" s="3"/>
       <c r="Y216" s="4" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
     </row>
@@ -16687,7 +16747,7 @@
       <c r="W217" s="3"/>
       <c r="X217" s="3"/>
       <c r="Y217" s="4" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
     </row>
@@ -16717,7 +16777,7 @@
       <c r="W218" s="3"/>
       <c r="X218" s="3"/>
       <c r="Y218" s="4" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
     </row>
@@ -16747,7 +16807,7 @@
       <c r="W219" s="3"/>
       <c r="X219" s="3"/>
       <c r="Y219" s="4" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
     </row>
@@ -16777,7 +16837,7 @@
       <c r="W220" s="3"/>
       <c r="X220" s="3"/>
       <c r="Y220" s="4" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
     </row>
@@ -16807,7 +16867,7 @@
       <c r="W221" s="3"/>
       <c r="X221" s="3"/>
       <c r="Y221" s="4" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
     </row>
@@ -16837,7 +16897,7 @@
       <c r="W222" s="3"/>
       <c r="X222" s="3"/>
       <c r="Y222" s="4" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
     </row>
@@ -16867,7 +16927,7 @@
       <c r="W223" s="3"/>
       <c r="X223" s="3"/>
       <c r="Y223" s="4" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
     </row>
@@ -16897,7 +16957,7 @@
       <c r="W224" s="3"/>
       <c r="X224" s="3"/>
       <c r="Y224" s="4" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
     </row>
@@ -16927,7 +16987,7 @@
       <c r="W225" s="3"/>
       <c r="X225" s="3"/>
       <c r="Y225" s="4" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
     </row>
@@ -16957,7 +17017,7 @@
       <c r="W226" s="3"/>
       <c r="X226" s="3"/>
       <c r="Y226" s="4" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
     </row>
@@ -16987,7 +17047,7 @@
       <c r="W227" s="3"/>
       <c r="X227" s="3"/>
       <c r="Y227" s="4" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
     </row>
@@ -17017,7 +17077,7 @@
       <c r="W228" s="3"/>
       <c r="X228" s="3"/>
       <c r="Y228" s="4" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
     </row>
@@ -17047,7 +17107,7 @@
       <c r="W229" s="3"/>
       <c r="X229" s="3"/>
       <c r="Y229" s="4" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
     </row>
@@ -17077,7 +17137,7 @@
       <c r="W230" s="3"/>
       <c r="X230" s="3"/>
       <c r="Y230" s="4" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
     </row>
@@ -17107,7 +17167,7 @@
       <c r="W231" s="3"/>
       <c r="X231" s="3"/>
       <c r="Y231" s="4" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
     </row>
@@ -17137,7 +17197,7 @@
       <c r="W232" s="3"/>
       <c r="X232" s="3"/>
       <c r="Y232" s="4" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
     </row>
@@ -17167,7 +17227,7 @@
       <c r="W233" s="3"/>
       <c r="X233" s="3"/>
       <c r="Y233" s="4" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
     </row>
@@ -17197,7 +17257,7 @@
       <c r="W234" s="3"/>
       <c r="X234" s="3"/>
       <c r="Y234" s="4" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
     </row>
@@ -17227,7 +17287,7 @@
       <c r="W235" s="3"/>
       <c r="X235" s="3"/>
       <c r="Y235" s="4" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
     </row>
@@ -17257,7 +17317,7 @@
       <c r="W236" s="3"/>
       <c r="X236" s="3"/>
       <c r="Y236" s="4" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
     </row>
@@ -17287,7 +17347,7 @@
       <c r="W237" s="3"/>
       <c r="X237" s="3"/>
       <c r="Y237" s="4" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
     </row>
@@ -17317,7 +17377,7 @@
       <c r="W238" s="3"/>
       <c r="X238" s="3"/>
       <c r="Y238" s="4" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
     </row>
@@ -17347,7 +17407,7 @@
       <c r="W239" s="3"/>
       <c r="X239" s="3"/>
       <c r="Y239" s="4" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
     </row>
@@ -17377,7 +17437,7 @@
       <c r="W240" s="3"/>
       <c r="X240" s="3"/>
       <c r="Y240" s="4" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
     </row>
@@ -17407,7 +17467,7 @@
       <c r="W241" s="3"/>
       <c r="X241" s="3"/>
       <c r="Y241" s="4" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
     </row>
@@ -17437,7 +17497,7 @@
       <c r="W242" s="3"/>
       <c r="X242" s="3"/>
       <c r="Y242" s="4" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
     </row>
@@ -17467,7 +17527,7 @@
       <c r="W243" s="3"/>
       <c r="X243" s="3"/>
       <c r="Y243" s="4" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
     </row>
@@ -17497,7 +17557,7 @@
       <c r="W244" s="3"/>
       <c r="X244" s="3"/>
       <c r="Y244" s="4" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
     </row>
@@ -17527,7 +17587,7 @@
       <c r="W245" s="3"/>
       <c r="X245" s="3"/>
       <c r="Y245" s="4" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
     </row>
@@ -17557,7 +17617,7 @@
       <c r="W246" s="3"/>
       <c r="X246" s="3"/>
       <c r="Y246" s="4" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
     </row>
@@ -17587,7 +17647,7 @@
       <c r="W247" s="3"/>
       <c r="X247" s="3"/>
       <c r="Y247" s="4" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
     </row>
@@ -17617,7 +17677,7 @@
       <c r="W248" s="3"/>
       <c r="X248" s="3"/>
       <c r="Y248" s="4" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
     </row>
@@ -17647,7 +17707,7 @@
       <c r="W249" s="3"/>
       <c r="X249" s="3"/>
       <c r="Y249" s="4" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
     </row>
@@ -17677,7 +17737,7 @@
       <c r="W250" s="3"/>
       <c r="X250" s="3"/>
       <c r="Y250" s="4" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
     </row>
@@ -17707,7 +17767,7 @@
       <c r="W251" s="3"/>
       <c r="X251" s="3"/>
       <c r="Y251" s="4" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
     </row>
@@ -17737,7 +17797,7 @@
       <c r="W252" s="3"/>
       <c r="X252" s="3"/>
       <c r="Y252" s="4" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
     </row>
@@ -17767,7 +17827,7 @@
       <c r="W253" s="3"/>
       <c r="X253" s="3"/>
       <c r="Y253" s="4" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
     </row>
@@ -17797,7 +17857,7 @@
       <c r="W254" s="3"/>
       <c r="X254" s="3"/>
       <c r="Y254" s="4" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
     </row>
@@ -17827,7 +17887,7 @@
       <c r="W255" s="3"/>
       <c r="X255" s="3"/>
       <c r="Y255" s="4" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
     </row>
@@ -17857,7 +17917,7 @@
       <c r="W256" s="3"/>
       <c r="X256" s="3"/>
       <c r="Y256" s="4" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
     </row>
@@ -17887,7 +17947,7 @@
       <c r="W257" s="3"/>
       <c r="X257" s="3"/>
       <c r="Y257" s="4" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
     </row>
@@ -17917,7 +17977,7 @@
       <c r="W258" s="3"/>
       <c r="X258" s="3"/>
       <c r="Y258" s="4" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
     </row>
@@ -17947,7 +18007,7 @@
       <c r="W259" s="3"/>
       <c r="X259" s="3"/>
       <c r="Y259" s="4" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
     </row>
@@ -17977,7 +18037,7 @@
       <c r="W260" s="3"/>
       <c r="X260" s="3"/>
       <c r="Y260" s="4" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
     </row>
@@ -18007,7 +18067,7 @@
       <c r="W261" s="3"/>
       <c r="X261" s="3"/>
       <c r="Y261" s="4" t="str">
-        <f t="shared" ref="Y261:Y324" si="29">IF(COUNTA(B261:X261)=0,"",AVERAGE(B261:X261))</f>
+        <f t="shared" ref="Y261:Y324" si="30">IF(COUNTA(B261:X261)=0,"",AVERAGE(B261:X261))</f>
         <v/>
       </c>
     </row>
@@ -18037,7 +18097,7 @@
       <c r="W262" s="3"/>
       <c r="X262" s="3"/>
       <c r="Y262" s="4" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
     </row>
@@ -18067,7 +18127,7 @@
       <c r="W263" s="3"/>
       <c r="X263" s="3"/>
       <c r="Y263" s="4" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
     </row>
@@ -18097,7 +18157,7 @@
       <c r="W264" s="3"/>
       <c r="X264" s="3"/>
       <c r="Y264" s="4" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
     </row>
@@ -18127,7 +18187,7 @@
       <c r="W265" s="3"/>
       <c r="X265" s="3"/>
       <c r="Y265" s="4" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
     </row>
@@ -18157,7 +18217,7 @@
       <c r="W266" s="3"/>
       <c r="X266" s="3"/>
       <c r="Y266" s="4" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
     </row>
@@ -18187,7 +18247,7 @@
       <c r="W267" s="3"/>
       <c r="X267" s="3"/>
       <c r="Y267" s="4" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
     </row>
@@ -18217,7 +18277,7 @@
       <c r="W268" s="3"/>
       <c r="X268" s="3"/>
       <c r="Y268" s="4" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
     </row>
@@ -18247,7 +18307,7 @@
       <c r="W269" s="3"/>
       <c r="X269" s="3"/>
       <c r="Y269" s="4" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
     </row>
@@ -18277,7 +18337,7 @@
       <c r="W270" s="3"/>
       <c r="X270" s="3"/>
       <c r="Y270" s="4" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
     </row>
@@ -18307,7 +18367,7 @@
       <c r="W271" s="3"/>
       <c r="X271" s="3"/>
       <c r="Y271" s="4" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
     </row>
@@ -18337,7 +18397,7 @@
       <c r="W272" s="3"/>
       <c r="X272" s="3"/>
       <c r="Y272" s="4" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
     </row>
@@ -18367,7 +18427,7 @@
       <c r="W273" s="3"/>
       <c r="X273" s="3"/>
       <c r="Y273" s="4" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
     </row>
@@ -18397,7 +18457,7 @@
       <c r="W274" s="3"/>
       <c r="X274" s="3"/>
       <c r="Y274" s="4" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
     </row>
@@ -18427,7 +18487,7 @@
       <c r="W275" s="3"/>
       <c r="X275" s="3"/>
       <c r="Y275" s="4" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
     </row>
@@ -18457,7 +18517,7 @@
       <c r="W276" s="3"/>
       <c r="X276" s="3"/>
       <c r="Y276" s="4" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
     </row>
@@ -18487,7 +18547,7 @@
       <c r="W277" s="3"/>
       <c r="X277" s="3"/>
       <c r="Y277" s="4" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
     </row>
@@ -18517,7 +18577,7 @@
       <c r="W278" s="3"/>
       <c r="X278" s="3"/>
       <c r="Y278" s="4" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
     </row>
@@ -18547,7 +18607,7 @@
       <c r="W279" s="3"/>
       <c r="X279" s="3"/>
       <c r="Y279" s="4" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
     </row>
@@ -18577,7 +18637,7 @@
       <c r="W280" s="3"/>
       <c r="X280" s="3"/>
       <c r="Y280" s="4" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
     </row>
@@ -18607,7 +18667,7 @@
       <c r="W281" s="3"/>
       <c r="X281" s="3"/>
       <c r="Y281" s="4" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
     </row>
@@ -18637,7 +18697,7 @@
       <c r="W282" s="3"/>
       <c r="X282" s="3"/>
       <c r="Y282" s="4" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
     </row>
@@ -18667,7 +18727,7 @@
       <c r="W283" s="3"/>
       <c r="X283" s="3"/>
       <c r="Y283" s="4" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
     </row>
@@ -18697,7 +18757,7 @@
       <c r="W284" s="3"/>
       <c r="X284" s="3"/>
       <c r="Y284" s="4" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
     </row>
@@ -18727,7 +18787,7 @@
       <c r="W285" s="3"/>
       <c r="X285" s="3"/>
       <c r="Y285" s="4" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
     </row>
@@ -18757,7 +18817,7 @@
       <c r="W286" s="3"/>
       <c r="X286" s="3"/>
       <c r="Y286" s="4" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
     </row>
@@ -18787,7 +18847,7 @@
       <c r="W287" s="3"/>
       <c r="X287" s="3"/>
       <c r="Y287" s="4" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
     </row>
@@ -18817,7 +18877,7 @@
       <c r="W288" s="3"/>
       <c r="X288" s="3"/>
       <c r="Y288" s="4" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
     </row>
@@ -18847,7 +18907,7 @@
       <c r="W289" s="3"/>
       <c r="X289" s="3"/>
       <c r="Y289" s="4" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
     </row>
@@ -18877,7 +18937,7 @@
       <c r="W290" s="3"/>
       <c r="X290" s="3"/>
       <c r="Y290" s="4" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
     </row>
@@ -18907,7 +18967,7 @@
       <c r="W291" s="3"/>
       <c r="X291" s="3"/>
       <c r="Y291" s="4" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
     </row>
@@ -18937,7 +18997,7 @@
       <c r="W292" s="3"/>
       <c r="X292" s="3"/>
       <c r="Y292" s="4" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
     </row>
@@ -18967,7 +19027,7 @@
       <c r="W293" s="3"/>
       <c r="X293" s="3"/>
       <c r="Y293" s="4" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
     </row>
@@ -18997,7 +19057,7 @@
       <c r="W294" s="3"/>
       <c r="X294" s="3"/>
       <c r="Y294" s="4" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
     </row>
@@ -19027,7 +19087,7 @@
       <c r="W295" s="3"/>
       <c r="X295" s="3"/>
       <c r="Y295" s="4" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
     </row>
@@ -19057,7 +19117,7 @@
       <c r="W296" s="3"/>
       <c r="X296" s="3"/>
       <c r="Y296" s="4" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
     </row>
@@ -19087,7 +19147,7 @@
       <c r="W297" s="3"/>
       <c r="X297" s="3"/>
       <c r="Y297" s="4" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
     </row>
@@ -19117,7 +19177,7 @@
       <c r="W298" s="3"/>
       <c r="X298" s="3"/>
       <c r="Y298" s="4" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
     </row>
@@ -19147,7 +19207,7 @@
       <c r="W299" s="3"/>
       <c r="X299" s="3"/>
       <c r="Y299" s="4" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
     </row>
@@ -19177,7 +19237,7 @@
       <c r="W300" s="3"/>
       <c r="X300" s="3"/>
       <c r="Y300" s="4" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
     </row>
@@ -19207,7 +19267,7 @@
       <c r="W301" s="3"/>
       <c r="X301" s="3"/>
       <c r="Y301" s="4" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
     </row>
@@ -19237,7 +19297,7 @@
       <c r="W302" s="3"/>
       <c r="X302" s="3"/>
       <c r="Y302" s="4" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
     </row>
@@ -19267,7 +19327,7 @@
       <c r="W303" s="3"/>
       <c r="X303" s="3"/>
       <c r="Y303" s="4" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
     </row>
@@ -19297,7 +19357,7 @@
       <c r="W304" s="3"/>
       <c r="X304" s="3"/>
       <c r="Y304" s="4" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
     </row>
@@ -19327,7 +19387,7 @@
       <c r="W305" s="3"/>
       <c r="X305" s="3"/>
       <c r="Y305" s="4" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
     </row>
@@ -19357,7 +19417,7 @@
       <c r="W306" s="3"/>
       <c r="X306" s="3"/>
       <c r="Y306" s="4" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
     </row>
@@ -19387,7 +19447,7 @@
       <c r="W307" s="3"/>
       <c r="X307" s="3"/>
       <c r="Y307" s="4" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
     </row>
@@ -19417,7 +19477,7 @@
       <c r="W308" s="3"/>
       <c r="X308" s="3"/>
       <c r="Y308" s="4" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
     </row>
@@ -19447,7 +19507,7 @@
       <c r="W309" s="3"/>
       <c r="X309" s="3"/>
       <c r="Y309" s="4" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
     </row>
@@ -19477,7 +19537,7 @@
       <c r="W310" s="3"/>
       <c r="X310" s="3"/>
       <c r="Y310" s="4" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
     </row>
@@ -19507,7 +19567,7 @@
       <c r="W311" s="3"/>
       <c r="X311" s="3"/>
       <c r="Y311" s="4" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
     </row>
@@ -19537,7 +19597,7 @@
       <c r="W312" s="3"/>
       <c r="X312" s="3"/>
       <c r="Y312" s="4" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
     </row>
@@ -19567,7 +19627,7 @@
       <c r="W313" s="3"/>
       <c r="X313" s="3"/>
       <c r="Y313" s="4" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
     </row>
@@ -19597,7 +19657,7 @@
       <c r="W314" s="3"/>
       <c r="X314" s="3"/>
       <c r="Y314" s="4" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
     </row>
@@ -19627,7 +19687,7 @@
       <c r="W315" s="3"/>
       <c r="X315" s="3"/>
       <c r="Y315" s="4" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
     </row>
@@ -19657,7 +19717,7 @@
       <c r="W316" s="3"/>
       <c r="X316" s="3"/>
       <c r="Y316" s="4" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
     </row>
@@ -19687,7 +19747,7 @@
       <c r="W317" s="3"/>
       <c r="X317" s="3"/>
       <c r="Y317" s="4" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
     </row>
@@ -19717,7 +19777,7 @@
       <c r="W318" s="3"/>
       <c r="X318" s="3"/>
       <c r="Y318" s="4" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
     </row>
@@ -19747,7 +19807,7 @@
       <c r="W319" s="3"/>
       <c r="X319" s="3"/>
       <c r="Y319" s="4" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
     </row>
@@ -19777,7 +19837,7 @@
       <c r="W320" s="3"/>
       <c r="X320" s="3"/>
       <c r="Y320" s="4" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
     </row>
@@ -19807,7 +19867,7 @@
       <c r="W321" s="3"/>
       <c r="X321" s="3"/>
       <c r="Y321" s="4" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
     </row>
@@ -19837,7 +19897,7 @@
       <c r="W322" s="3"/>
       <c r="X322" s="3"/>
       <c r="Y322" s="4" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
     </row>
@@ -19867,7 +19927,7 @@
       <c r="W323" s="3"/>
       <c r="X323" s="3"/>
       <c r="Y323" s="4" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
     </row>
@@ -19897,7 +19957,7 @@
       <c r="W324" s="3"/>
       <c r="X324" s="3"/>
       <c r="Y324" s="4" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
     </row>
@@ -19927,7 +19987,7 @@
       <c r="W325" s="3"/>
       <c r="X325" s="3"/>
       <c r="Y325" s="4" t="str">
-        <f t="shared" ref="Y325:Y388" si="30">IF(COUNTA(B325:X325)=0,"",AVERAGE(B325:X325))</f>
+        <f t="shared" ref="Y325:Y388" si="31">IF(COUNTA(B325:X325)=0,"",AVERAGE(B325:X325))</f>
         <v/>
       </c>
     </row>
@@ -19957,7 +20017,7 @@
       <c r="W326" s="3"/>
       <c r="X326" s="3"/>
       <c r="Y326" s="4" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
     </row>
@@ -19987,7 +20047,7 @@
       <c r="W327" s="3"/>
       <c r="X327" s="3"/>
       <c r="Y327" s="4" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
     </row>
@@ -20017,7 +20077,7 @@
       <c r="W328" s="3"/>
       <c r="X328" s="3"/>
       <c r="Y328" s="4" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
     </row>
@@ -20047,7 +20107,7 @@
       <c r="W329" s="3"/>
       <c r="X329" s="3"/>
       <c r="Y329" s="4" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
     </row>
@@ -20077,7 +20137,7 @@
       <c r="W330" s="3"/>
       <c r="X330" s="3"/>
       <c r="Y330" s="4" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
     </row>
@@ -20107,7 +20167,7 @@
       <c r="W331" s="3"/>
       <c r="X331" s="3"/>
       <c r="Y331" s="4" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
     </row>
@@ -20137,7 +20197,7 @@
       <c r="W332" s="3"/>
       <c r="X332" s="3"/>
       <c r="Y332" s="4" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
     </row>
@@ -20167,7 +20227,7 @@
       <c r="W333" s="3"/>
       <c r="X333" s="3"/>
       <c r="Y333" s="4" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
     </row>
@@ -20197,7 +20257,7 @@
       <c r="W334" s="3"/>
       <c r="X334" s="3"/>
       <c r="Y334" s="4" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
     </row>
@@ -20227,7 +20287,7 @@
       <c r="W335" s="3"/>
       <c r="X335" s="3"/>
       <c r="Y335" s="4" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
     </row>
@@ -20257,7 +20317,7 @@
       <c r="W336" s="3"/>
       <c r="X336" s="3"/>
       <c r="Y336" s="4" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
     </row>
@@ -20287,7 +20347,7 @@
       <c r="W337" s="3"/>
       <c r="X337" s="3"/>
       <c r="Y337" s="4" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
     </row>
@@ -20317,7 +20377,7 @@
       <c r="W338" s="3"/>
       <c r="X338" s="3"/>
       <c r="Y338" s="4" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
     </row>
@@ -20347,7 +20407,7 @@
       <c r="W339" s="3"/>
       <c r="X339" s="3"/>
       <c r="Y339" s="4" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
     </row>
@@ -20377,7 +20437,7 @@
       <c r="W340" s="3"/>
       <c r="X340" s="3"/>
       <c r="Y340" s="4" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
     </row>
@@ -20407,7 +20467,7 @@
       <c r="W341" s="3"/>
       <c r="X341" s="3"/>
       <c r="Y341" s="4" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
     </row>
@@ -20437,7 +20497,7 @@
       <c r="W342" s="3"/>
       <c r="X342" s="3"/>
       <c r="Y342" s="4" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
     </row>
@@ -20467,7 +20527,7 @@
       <c r="W343" s="3"/>
       <c r="X343" s="3"/>
       <c r="Y343" s="4" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
     </row>
@@ -20497,7 +20557,7 @@
       <c r="W344" s="3"/>
       <c r="X344" s="3"/>
       <c r="Y344" s="4" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
     </row>
@@ -20527,7 +20587,7 @@
       <c r="W345" s="3"/>
       <c r="X345" s="3"/>
       <c r="Y345" s="4" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
     </row>
@@ -20557,7 +20617,7 @@
       <c r="W346" s="3"/>
       <c r="X346" s="3"/>
       <c r="Y346" s="4" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
     </row>
@@ -20587,7 +20647,7 @@
       <c r="W347" s="3"/>
       <c r="X347" s="3"/>
       <c r="Y347" s="4" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
     </row>
@@ -20617,7 +20677,7 @@
       <c r="W348" s="3"/>
       <c r="X348" s="3"/>
       <c r="Y348" s="4" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
     </row>
@@ -20647,7 +20707,7 @@
       <c r="W349" s="3"/>
       <c r="X349" s="3"/>
       <c r="Y349" s="4" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
     </row>
@@ -20677,7 +20737,7 @@
       <c r="W350" s="3"/>
       <c r="X350" s="3"/>
       <c r="Y350" s="4" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
     </row>
@@ -20707,7 +20767,7 @@
       <c r="W351" s="3"/>
       <c r="X351" s="3"/>
       <c r="Y351" s="4" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
     </row>
@@ -20737,7 +20797,7 @@
       <c r="W352" s="3"/>
       <c r="X352" s="3"/>
       <c r="Y352" s="4" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
     </row>
@@ -20767,7 +20827,7 @@
       <c r="W353" s="3"/>
       <c r="X353" s="3"/>
       <c r="Y353" s="4" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
     </row>
@@ -20797,7 +20857,7 @@
       <c r="W354" s="3"/>
       <c r="X354" s="3"/>
       <c r="Y354" s="4" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
     </row>
@@ -20827,7 +20887,7 @@
       <c r="W355" s="3"/>
       <c r="X355" s="3"/>
       <c r="Y355" s="4" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
     </row>
@@ -20857,7 +20917,7 @@
       <c r="W356" s="3"/>
       <c r="X356" s="3"/>
       <c r="Y356" s="4" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
     </row>
@@ -20887,7 +20947,7 @@
       <c r="W357" s="3"/>
       <c r="X357" s="3"/>
       <c r="Y357" s="4" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
     </row>
@@ -20917,7 +20977,7 @@
       <c r="W358" s="3"/>
       <c r="X358" s="3"/>
       <c r="Y358" s="4" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
     </row>
@@ -20947,7 +21007,7 @@
       <c r="W359" s="3"/>
       <c r="X359" s="3"/>
       <c r="Y359" s="4" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
     </row>
@@ -20977,7 +21037,7 @@
       <c r="W360" s="3"/>
       <c r="X360" s="3"/>
       <c r="Y360" s="4" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
     </row>
@@ -21007,7 +21067,7 @@
       <c r="W361" s="3"/>
       <c r="X361" s="3"/>
       <c r="Y361" s="4" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
     </row>
@@ -21037,7 +21097,7 @@
       <c r="W362" s="3"/>
       <c r="X362" s="3"/>
       <c r="Y362" s="4" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
     </row>
@@ -21067,7 +21127,7 @@
       <c r="W363" s="3"/>
       <c r="X363" s="3"/>
       <c r="Y363" s="4" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
     </row>
@@ -21097,7 +21157,7 @@
       <c r="W364" s="3"/>
       <c r="X364" s="3"/>
       <c r="Y364" s="4" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
     </row>
@@ -21127,7 +21187,7 @@
       <c r="W365" s="3"/>
       <c r="X365" s="3"/>
       <c r="Y365" s="4" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
     </row>
@@ -21157,7 +21217,7 @@
       <c r="W366" s="3"/>
       <c r="X366" s="3"/>
       <c r="Y366" s="4" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
     </row>
@@ -21187,7 +21247,7 @@
       <c r="W367" s="3"/>
       <c r="X367" s="3"/>
       <c r="Y367" s="4" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
     </row>
@@ -21217,7 +21277,7 @@
       <c r="W368" s="3"/>
       <c r="X368" s="3"/>
       <c r="Y368" s="4" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
     </row>
@@ -21247,7 +21307,7 @@
       <c r="W369" s="3"/>
       <c r="X369" s="3"/>
       <c r="Y369" s="4" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
     </row>
@@ -21277,7 +21337,7 @@
       <c r="W370" s="3"/>
       <c r="X370" s="3"/>
       <c r="Y370" s="4" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
     </row>
@@ -21307,7 +21367,7 @@
       <c r="W371" s="3"/>
       <c r="X371" s="3"/>
       <c r="Y371" s="4" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
     </row>
@@ -21337,7 +21397,7 @@
       <c r="W372" s="3"/>
       <c r="X372" s="3"/>
       <c r="Y372" s="4" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
     </row>
@@ -21367,7 +21427,7 @@
       <c r="W373" s="3"/>
       <c r="X373" s="3"/>
       <c r="Y373" s="4" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
     </row>
@@ -21397,7 +21457,7 @@
       <c r="W374" s="3"/>
       <c r="X374" s="3"/>
       <c r="Y374" s="4" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
     </row>
@@ -21427,7 +21487,7 @@
       <c r="W375" s="3"/>
       <c r="X375" s="3"/>
       <c r="Y375" s="4" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
     </row>
@@ -21457,7 +21517,7 @@
       <c r="W376" s="3"/>
       <c r="X376" s="3"/>
       <c r="Y376" s="4" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
     </row>
@@ -21487,7 +21547,7 @@
       <c r="W377" s="3"/>
       <c r="X377" s="3"/>
       <c r="Y377" s="4" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
     </row>
@@ -21517,7 +21577,7 @@
       <c r="W378" s="3"/>
       <c r="X378" s="3"/>
       <c r="Y378" s="4" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
     </row>
@@ -21547,7 +21607,7 @@
       <c r="W379" s="3"/>
       <c r="X379" s="3"/>
       <c r="Y379" s="4" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
     </row>
@@ -21577,7 +21637,7 @@
       <c r="W380" s="3"/>
       <c r="X380" s="3"/>
       <c r="Y380" s="4" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
     </row>
@@ -21607,7 +21667,7 @@
       <c r="W381" s="3"/>
       <c r="X381" s="3"/>
       <c r="Y381" s="4" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
     </row>
@@ -21637,7 +21697,7 @@
       <c r="W382" s="3"/>
       <c r="X382" s="3"/>
       <c r="Y382" s="4" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
     </row>
@@ -21667,7 +21727,7 @@
       <c r="W383" s="3"/>
       <c r="X383" s="3"/>
       <c r="Y383" s="4" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
     </row>
@@ -21697,7 +21757,7 @@
       <c r="W384" s="3"/>
       <c r="X384" s="3"/>
       <c r="Y384" s="4" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
     </row>
@@ -21727,7 +21787,7 @@
       <c r="W385" s="3"/>
       <c r="X385" s="3"/>
       <c r="Y385" s="4" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
     </row>
@@ -21757,7 +21817,7 @@
       <c r="W386" s="3"/>
       <c r="X386" s="3"/>
       <c r="Y386" s="4" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
     </row>
@@ -21787,7 +21847,7 @@
       <c r="W387" s="3"/>
       <c r="X387" s="3"/>
       <c r="Y387" s="4" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
     </row>
@@ -21817,7 +21877,7 @@
       <c r="W388" s="3"/>
       <c r="X388" s="3"/>
       <c r="Y388" s="4" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
     </row>
@@ -21847,7 +21907,7 @@
       <c r="W389" s="3"/>
       <c r="X389" s="3"/>
       <c r="Y389" s="4" t="str">
-        <f t="shared" ref="Y389:Y390" si="31">IF(COUNTA(B389:X389)=0,"",AVERAGE(B389:X389))</f>
+        <f t="shared" ref="Y389:Y390" si="32">IF(COUNTA(B389:X389)=0,"",AVERAGE(B389:X389))</f>
         <v/>
       </c>
     </row>
@@ -21877,7 +21937,7 @@
       <c r="W390" s="3"/>
       <c r="X390" s="3"/>
       <c r="Y390" s="4" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
     </row>
@@ -21907,7 +21967,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="8" t="s">
         <v>28</v>
       </c>
       <c r="B1" s="7"/>
@@ -21932,7 +21992,7 @@
       <c r="U1" s="7"/>
     </row>
     <row r="2" spans="1:21" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="6" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="7"/>
@@ -26576,29 +26636,69 @@
       </c>
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A74" s="2"/>
-      <c r="B74" s="3"/>
-      <c r="C74" s="3"/>
-      <c r="D74" s="3"/>
-      <c r="E74" s="3"/>
-      <c r="F74" s="3"/>
-      <c r="G74" s="3"/>
-      <c r="H74" s="3"/>
-      <c r="I74" s="3"/>
-      <c r="J74" s="3"/>
-      <c r="K74" s="3"/>
-      <c r="L74" s="3"/>
-      <c r="M74" s="3"/>
-      <c r="N74" s="3"/>
-      <c r="O74" s="3"/>
-      <c r="P74" s="3"/>
-      <c r="Q74" s="3"/>
-      <c r="R74" s="3"/>
-      <c r="S74" s="3"/>
-      <c r="T74" s="3"/>
-      <c r="U74" s="4" t="str">
-        <f t="shared" si="34"/>
-        <v/>
+      <c r="A74" s="2">
+        <v>46230</v>
+      </c>
+      <c r="B74" s="3">
+        <v>3.79</v>
+      </c>
+      <c r="C74" s="3">
+        <v>3.95</v>
+      </c>
+      <c r="D74" s="3">
+        <v>3.69</v>
+      </c>
+      <c r="E74" s="3">
+        <v>2.89</v>
+      </c>
+      <c r="F74" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="G74" s="3">
+        <v>3.99</v>
+      </c>
+      <c r="H74" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="I74" s="3">
+        <v>3.39</v>
+      </c>
+      <c r="J74" s="3">
+        <v>3.49</v>
+      </c>
+      <c r="K74" s="3">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="L74" s="3">
+        <v>3.29</v>
+      </c>
+      <c r="M74" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="N74" s="3">
+        <v>3.84</v>
+      </c>
+      <c r="O74" s="3">
+        <v>3.84</v>
+      </c>
+      <c r="P74" s="3">
+        <v>3.89</v>
+      </c>
+      <c r="Q74" s="3">
+        <v>3.65</v>
+      </c>
+      <c r="R74" s="3">
+        <v>3.89</v>
+      </c>
+      <c r="S74" s="3">
+        <v>4.99</v>
+      </c>
+      <c r="T74" s="3">
+        <v>1.99</v>
+      </c>
+      <c r="U74" s="4">
+        <f t="shared" ref="U74" si="35">IF(COUNTA(B74:T74)=0,"",AVERAGE(B74:T74))</f>
+        <v>3.5600000000000009</v>
       </c>
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
@@ -28131,7 +28231,7 @@
       <c r="S133" s="3"/>
       <c r="T133" s="3"/>
       <c r="U133" s="4" t="str">
-        <f t="shared" ref="U133:U196" si="35">IF(COUNTA(B133:T133)=0,"",AVERAGE(B133:T133))</f>
+        <f t="shared" ref="U133:U196" si="36">IF(COUNTA(B133:T133)=0,"",AVERAGE(B133:T133))</f>
         <v/>
       </c>
     </row>
@@ -28157,7 +28257,7 @@
       <c r="S134" s="3"/>
       <c r="T134" s="3"/>
       <c r="U134" s="4" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
@@ -28183,7 +28283,7 @@
       <c r="S135" s="3"/>
       <c r="T135" s="3"/>
       <c r="U135" s="4" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
@@ -28209,7 +28309,7 @@
       <c r="S136" s="3"/>
       <c r="T136" s="3"/>
       <c r="U136" s="4" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
@@ -28235,7 +28335,7 @@
       <c r="S137" s="3"/>
       <c r="T137" s="3"/>
       <c r="U137" s="4" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
@@ -28261,7 +28361,7 @@
       <c r="S138" s="3"/>
       <c r="T138" s="3"/>
       <c r="U138" s="4" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
@@ -28287,7 +28387,7 @@
       <c r="S139" s="3"/>
       <c r="T139" s="3"/>
       <c r="U139" s="4" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
@@ -28313,7 +28413,7 @@
       <c r="S140" s="3"/>
       <c r="T140" s="3"/>
       <c r="U140" s="4" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
@@ -28339,7 +28439,7 @@
       <c r="S141" s="3"/>
       <c r="T141" s="3"/>
       <c r="U141" s="4" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
@@ -28365,7 +28465,7 @@
       <c r="S142" s="3"/>
       <c r="T142" s="3"/>
       <c r="U142" s="4" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
@@ -28391,7 +28491,7 @@
       <c r="S143" s="3"/>
       <c r="T143" s="3"/>
       <c r="U143" s="4" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
@@ -28417,7 +28517,7 @@
       <c r="S144" s="3"/>
       <c r="T144" s="3"/>
       <c r="U144" s="4" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
@@ -28443,7 +28543,7 @@
       <c r="S145" s="3"/>
       <c r="T145" s="3"/>
       <c r="U145" s="4" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
@@ -28469,7 +28569,7 @@
       <c r="S146" s="3"/>
       <c r="T146" s="3"/>
       <c r="U146" s="4" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
@@ -28495,7 +28595,7 @@
       <c r="S147" s="3"/>
       <c r="T147" s="3"/>
       <c r="U147" s="4" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
@@ -28521,7 +28621,7 @@
       <c r="S148" s="3"/>
       <c r="T148" s="3"/>
       <c r="U148" s="4" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
@@ -28547,7 +28647,7 @@
       <c r="S149" s="3"/>
       <c r="T149" s="3"/>
       <c r="U149" s="4" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
@@ -28573,7 +28673,7 @@
       <c r="S150" s="3"/>
       <c r="T150" s="3"/>
       <c r="U150" s="4" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
@@ -28599,7 +28699,7 @@
       <c r="S151" s="3"/>
       <c r="T151" s="3"/>
       <c r="U151" s="4" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
@@ -28625,7 +28725,7 @@
       <c r="S152" s="3"/>
       <c r="T152" s="3"/>
       <c r="U152" s="4" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
@@ -28651,7 +28751,7 @@
       <c r="S153" s="3"/>
       <c r="T153" s="3"/>
       <c r="U153" s="4" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
@@ -28677,7 +28777,7 @@
       <c r="S154" s="3"/>
       <c r="T154" s="3"/>
       <c r="U154" s="4" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
@@ -28703,7 +28803,7 @@
       <c r="S155" s="3"/>
       <c r="T155" s="3"/>
       <c r="U155" s="4" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
@@ -28729,7 +28829,7 @@
       <c r="S156" s="3"/>
       <c r="T156" s="3"/>
       <c r="U156" s="4" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
@@ -28755,7 +28855,7 @@
       <c r="S157" s="3"/>
       <c r="T157" s="3"/>
       <c r="U157" s="4" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
@@ -28781,7 +28881,7 @@
       <c r="S158" s="3"/>
       <c r="T158" s="3"/>
       <c r="U158" s="4" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
@@ -28807,7 +28907,7 @@
       <c r="S159" s="3"/>
       <c r="T159" s="3"/>
       <c r="U159" s="4" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
@@ -28833,7 +28933,7 @@
       <c r="S160" s="3"/>
       <c r="T160" s="3"/>
       <c r="U160" s="4" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
@@ -28859,7 +28959,7 @@
       <c r="S161" s="3"/>
       <c r="T161" s="3"/>
       <c r="U161" s="4" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
@@ -28885,7 +28985,7 @@
       <c r="S162" s="3"/>
       <c r="T162" s="3"/>
       <c r="U162" s="4" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
@@ -28911,7 +29011,7 @@
       <c r="S163" s="3"/>
       <c r="T163" s="3"/>
       <c r="U163" s="4" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
@@ -28937,7 +29037,7 @@
       <c r="S164" s="3"/>
       <c r="T164" s="3"/>
       <c r="U164" s="4" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
@@ -28963,7 +29063,7 @@
       <c r="S165" s="3"/>
       <c r="T165" s="3"/>
       <c r="U165" s="4" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
@@ -28989,7 +29089,7 @@
       <c r="S166" s="3"/>
       <c r="T166" s="3"/>
       <c r="U166" s="4" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
@@ -29015,7 +29115,7 @@
       <c r="S167" s="3"/>
       <c r="T167" s="3"/>
       <c r="U167" s="4" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
@@ -29041,7 +29141,7 @@
       <c r="S168" s="3"/>
       <c r="T168" s="3"/>
       <c r="U168" s="4" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
@@ -29067,7 +29167,7 @@
       <c r="S169" s="3"/>
       <c r="T169" s="3"/>
       <c r="U169" s="4" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
@@ -29093,7 +29193,7 @@
       <c r="S170" s="3"/>
       <c r="T170" s="3"/>
       <c r="U170" s="4" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
@@ -29119,7 +29219,7 @@
       <c r="S171" s="3"/>
       <c r="T171" s="3"/>
       <c r="U171" s="4" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
@@ -29145,7 +29245,7 @@
       <c r="S172" s="3"/>
       <c r="T172" s="3"/>
       <c r="U172" s="4" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
@@ -29171,7 +29271,7 @@
       <c r="S173" s="3"/>
       <c r="T173" s="3"/>
       <c r="U173" s="4" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
@@ -29197,7 +29297,7 @@
       <c r="S174" s="3"/>
       <c r="T174" s="3"/>
       <c r="U174" s="4" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
@@ -29223,7 +29323,7 @@
       <c r="S175" s="3"/>
       <c r="T175" s="3"/>
       <c r="U175" s="4" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
@@ -29249,7 +29349,7 @@
       <c r="S176" s="3"/>
       <c r="T176" s="3"/>
       <c r="U176" s="4" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
@@ -29275,7 +29375,7 @@
       <c r="S177" s="3"/>
       <c r="T177" s="3"/>
       <c r="U177" s="4" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
@@ -29301,7 +29401,7 @@
       <c r="S178" s="3"/>
       <c r="T178" s="3"/>
       <c r="U178" s="4" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
@@ -29327,7 +29427,7 @@
       <c r="S179" s="3"/>
       <c r="T179" s="3"/>
       <c r="U179" s="4" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
@@ -29353,7 +29453,7 @@
       <c r="S180" s="3"/>
       <c r="T180" s="3"/>
       <c r="U180" s="4" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
@@ -29379,7 +29479,7 @@
       <c r="S181" s="3"/>
       <c r="T181" s="3"/>
       <c r="U181" s="4" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
@@ -29405,7 +29505,7 @@
       <c r="S182" s="3"/>
       <c r="T182" s="3"/>
       <c r="U182" s="4" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
@@ -29431,7 +29531,7 @@
       <c r="S183" s="3"/>
       <c r="T183" s="3"/>
       <c r="U183" s="4" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
@@ -29457,7 +29557,7 @@
       <c r="S184" s="3"/>
       <c r="T184" s="3"/>
       <c r="U184" s="4" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
@@ -29483,7 +29583,7 @@
       <c r="S185" s="3"/>
       <c r="T185" s="3"/>
       <c r="U185" s="4" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
@@ -29509,7 +29609,7 @@
       <c r="S186" s="3"/>
       <c r="T186" s="3"/>
       <c r="U186" s="4" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
@@ -29535,7 +29635,7 @@
       <c r="S187" s="3"/>
       <c r="T187" s="3"/>
       <c r="U187" s="4" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
@@ -29561,7 +29661,7 @@
       <c r="S188" s="3"/>
       <c r="T188" s="3"/>
       <c r="U188" s="4" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
@@ -29587,7 +29687,7 @@
       <c r="S189" s="3"/>
       <c r="T189" s="3"/>
       <c r="U189" s="4" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
@@ -29613,7 +29713,7 @@
       <c r="S190" s="3"/>
       <c r="T190" s="3"/>
       <c r="U190" s="4" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
@@ -29639,7 +29739,7 @@
       <c r="S191" s="3"/>
       <c r="T191" s="3"/>
       <c r="U191" s="4" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
@@ -29665,7 +29765,7 @@
       <c r="S192" s="3"/>
       <c r="T192" s="3"/>
       <c r="U192" s="4" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
@@ -29691,7 +29791,7 @@
       <c r="S193" s="3"/>
       <c r="T193" s="3"/>
       <c r="U193" s="4" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
@@ -29717,7 +29817,7 @@
       <c r="S194" s="3"/>
       <c r="T194" s="3"/>
       <c r="U194" s="4" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
@@ -29743,7 +29843,7 @@
       <c r="S195" s="3"/>
       <c r="T195" s="3"/>
       <c r="U195" s="4" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
@@ -29769,7 +29869,7 @@
       <c r="S196" s="3"/>
       <c r="T196" s="3"/>
       <c r="U196" s="4" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
@@ -29795,7 +29895,7 @@
       <c r="S197" s="3"/>
       <c r="T197" s="3"/>
       <c r="U197" s="4" t="str">
-        <f t="shared" ref="U197:U260" si="36">IF(COUNTA(B197:T197)=0,"",AVERAGE(B197:T197))</f>
+        <f t="shared" ref="U197:U260" si="37">IF(COUNTA(B197:T197)=0,"",AVERAGE(B197:T197))</f>
         <v/>
       </c>
     </row>
@@ -29821,7 +29921,7 @@
       <c r="S198" s="3"/>
       <c r="T198" s="3"/>
       <c r="U198" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -29847,7 +29947,7 @@
       <c r="S199" s="3"/>
       <c r="T199" s="3"/>
       <c r="U199" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -29873,7 +29973,7 @@
       <c r="S200" s="3"/>
       <c r="T200" s="3"/>
       <c r="U200" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -29899,7 +29999,7 @@
       <c r="S201" s="3"/>
       <c r="T201" s="3"/>
       <c r="U201" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -29925,7 +30025,7 @@
       <c r="S202" s="3"/>
       <c r="T202" s="3"/>
       <c r="U202" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -29951,7 +30051,7 @@
       <c r="S203" s="3"/>
       <c r="T203" s="3"/>
       <c r="U203" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -29977,7 +30077,7 @@
       <c r="S204" s="3"/>
       <c r="T204" s="3"/>
       <c r="U204" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -30003,7 +30103,7 @@
       <c r="S205" s="3"/>
       <c r="T205" s="3"/>
       <c r="U205" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -30029,7 +30129,7 @@
       <c r="S206" s="3"/>
       <c r="T206" s="3"/>
       <c r="U206" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -30055,7 +30155,7 @@
       <c r="S207" s="3"/>
       <c r="T207" s="3"/>
       <c r="U207" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -30081,7 +30181,7 @@
       <c r="S208" s="3"/>
       <c r="T208" s="3"/>
       <c r="U208" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -30107,7 +30207,7 @@
       <c r="S209" s="3"/>
       <c r="T209" s="3"/>
       <c r="U209" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -30133,7 +30233,7 @@
       <c r="S210" s="3"/>
       <c r="T210" s="3"/>
       <c r="U210" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -30159,7 +30259,7 @@
       <c r="S211" s="3"/>
       <c r="T211" s="3"/>
       <c r="U211" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -30185,7 +30285,7 @@
       <c r="S212" s="3"/>
       <c r="T212" s="3"/>
       <c r="U212" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -30211,7 +30311,7 @@
       <c r="S213" s="3"/>
       <c r="T213" s="3"/>
       <c r="U213" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -30237,7 +30337,7 @@
       <c r="S214" s="3"/>
       <c r="T214" s="3"/>
       <c r="U214" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -30263,7 +30363,7 @@
       <c r="S215" s="3"/>
       <c r="T215" s="3"/>
       <c r="U215" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -30289,7 +30389,7 @@
       <c r="S216" s="3"/>
       <c r="T216" s="3"/>
       <c r="U216" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -30315,7 +30415,7 @@
       <c r="S217" s="3"/>
       <c r="T217" s="3"/>
       <c r="U217" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -30341,7 +30441,7 @@
       <c r="S218" s="3"/>
       <c r="T218" s="3"/>
       <c r="U218" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -30367,7 +30467,7 @@
       <c r="S219" s="3"/>
       <c r="T219" s="3"/>
       <c r="U219" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -30393,7 +30493,7 @@
       <c r="S220" s="3"/>
       <c r="T220" s="3"/>
       <c r="U220" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -30419,7 +30519,7 @@
       <c r="S221" s="3"/>
       <c r="T221" s="3"/>
       <c r="U221" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -30445,7 +30545,7 @@
       <c r="S222" s="3"/>
       <c r="T222" s="3"/>
       <c r="U222" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -30471,7 +30571,7 @@
       <c r="S223" s="3"/>
       <c r="T223" s="3"/>
       <c r="U223" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -30497,7 +30597,7 @@
       <c r="S224" s="3"/>
       <c r="T224" s="3"/>
       <c r="U224" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -30523,7 +30623,7 @@
       <c r="S225" s="3"/>
       <c r="T225" s="3"/>
       <c r="U225" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -30549,7 +30649,7 @@
       <c r="S226" s="3"/>
       <c r="T226" s="3"/>
       <c r="U226" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -30575,7 +30675,7 @@
       <c r="S227" s="3"/>
       <c r="T227" s="3"/>
       <c r="U227" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -30601,7 +30701,7 @@
       <c r="S228" s="3"/>
       <c r="T228" s="3"/>
       <c r="U228" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -30627,7 +30727,7 @@
       <c r="S229" s="3"/>
       <c r="T229" s="3"/>
       <c r="U229" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -30653,7 +30753,7 @@
       <c r="S230" s="3"/>
       <c r="T230" s="3"/>
       <c r="U230" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -30679,7 +30779,7 @@
       <c r="S231" s="3"/>
       <c r="T231" s="3"/>
       <c r="U231" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -30705,7 +30805,7 @@
       <c r="S232" s="3"/>
       <c r="T232" s="3"/>
       <c r="U232" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -30731,7 +30831,7 @@
       <c r="S233" s="3"/>
       <c r="T233" s="3"/>
       <c r="U233" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -30757,7 +30857,7 @@
       <c r="S234" s="3"/>
       <c r="T234" s="3"/>
       <c r="U234" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -30783,7 +30883,7 @@
       <c r="S235" s="3"/>
       <c r="T235" s="3"/>
       <c r="U235" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -30809,7 +30909,7 @@
       <c r="S236" s="3"/>
       <c r="T236" s="3"/>
       <c r="U236" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -30835,7 +30935,7 @@
       <c r="S237" s="3"/>
       <c r="T237" s="3"/>
       <c r="U237" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -30861,7 +30961,7 @@
       <c r="S238" s="3"/>
       <c r="T238" s="3"/>
       <c r="U238" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -30887,7 +30987,7 @@
       <c r="S239" s="3"/>
       <c r="T239" s="3"/>
       <c r="U239" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -30913,7 +31013,7 @@
       <c r="S240" s="3"/>
       <c r="T240" s="3"/>
       <c r="U240" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -30939,7 +31039,7 @@
       <c r="S241" s="3"/>
       <c r="T241" s="3"/>
       <c r="U241" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -30965,7 +31065,7 @@
       <c r="S242" s="3"/>
       <c r="T242" s="3"/>
       <c r="U242" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -30991,7 +31091,7 @@
       <c r="S243" s="3"/>
       <c r="T243" s="3"/>
       <c r="U243" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -31017,7 +31117,7 @@
       <c r="S244" s="3"/>
       <c r="T244" s="3"/>
       <c r="U244" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -31043,7 +31143,7 @@
       <c r="S245" s="3"/>
       <c r="T245" s="3"/>
       <c r="U245" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -31069,7 +31169,7 @@
       <c r="S246" s="3"/>
       <c r="T246" s="3"/>
       <c r="U246" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -31095,7 +31195,7 @@
       <c r="S247" s="3"/>
       <c r="T247" s="3"/>
       <c r="U247" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -31121,7 +31221,7 @@
       <c r="S248" s="3"/>
       <c r="T248" s="3"/>
       <c r="U248" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -31147,7 +31247,7 @@
       <c r="S249" s="3"/>
       <c r="T249" s="3"/>
       <c r="U249" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -31173,7 +31273,7 @@
       <c r="S250" s="3"/>
       <c r="T250" s="3"/>
       <c r="U250" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -31199,7 +31299,7 @@
       <c r="S251" s="3"/>
       <c r="T251" s="3"/>
       <c r="U251" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -31225,7 +31325,7 @@
       <c r="S252" s="3"/>
       <c r="T252" s="3"/>
       <c r="U252" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -31251,7 +31351,7 @@
       <c r="S253" s="3"/>
       <c r="T253" s="3"/>
       <c r="U253" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -31277,7 +31377,7 @@
       <c r="S254" s="3"/>
       <c r="T254" s="3"/>
       <c r="U254" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -31303,7 +31403,7 @@
       <c r="S255" s="3"/>
       <c r="T255" s="3"/>
       <c r="U255" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -31329,7 +31429,7 @@
       <c r="S256" s="3"/>
       <c r="T256" s="3"/>
       <c r="U256" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -31355,7 +31455,7 @@
       <c r="S257" s="3"/>
       <c r="T257" s="3"/>
       <c r="U257" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -31381,7 +31481,7 @@
       <c r="S258" s="3"/>
       <c r="T258" s="3"/>
       <c r="U258" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -31407,7 +31507,7 @@
       <c r="S259" s="3"/>
       <c r="T259" s="3"/>
       <c r="U259" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -31433,7 +31533,7 @@
       <c r="S260" s="3"/>
       <c r="T260" s="3"/>
       <c r="U260" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -31459,7 +31559,7 @@
       <c r="S261" s="3"/>
       <c r="T261" s="3"/>
       <c r="U261" s="4" t="str">
-        <f t="shared" ref="U261:U324" si="37">IF(COUNTA(B261:T261)=0,"",AVERAGE(B261:T261))</f>
+        <f t="shared" ref="U261:U324" si="38">IF(COUNTA(B261:T261)=0,"",AVERAGE(B261:T261))</f>
         <v/>
       </c>
     </row>
@@ -31485,7 +31585,7 @@
       <c r="S262" s="3"/>
       <c r="T262" s="3"/>
       <c r="U262" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -31511,7 +31611,7 @@
       <c r="S263" s="3"/>
       <c r="T263" s="3"/>
       <c r="U263" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -31537,7 +31637,7 @@
       <c r="S264" s="3"/>
       <c r="T264" s="3"/>
       <c r="U264" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -31563,7 +31663,7 @@
       <c r="S265" s="3"/>
       <c r="T265" s="3"/>
       <c r="U265" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -31589,7 +31689,7 @@
       <c r="S266" s="3"/>
       <c r="T266" s="3"/>
       <c r="U266" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -31615,7 +31715,7 @@
       <c r="S267" s="3"/>
       <c r="T267" s="3"/>
       <c r="U267" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -31641,7 +31741,7 @@
       <c r="S268" s="3"/>
       <c r="T268" s="3"/>
       <c r="U268" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -31667,7 +31767,7 @@
       <c r="S269" s="3"/>
       <c r="T269" s="3"/>
       <c r="U269" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -31693,7 +31793,7 @@
       <c r="S270" s="3"/>
       <c r="T270" s="3"/>
       <c r="U270" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -31719,7 +31819,7 @@
       <c r="S271" s="3"/>
       <c r="T271" s="3"/>
       <c r="U271" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -31745,7 +31845,7 @@
       <c r="S272" s="3"/>
       <c r="T272" s="3"/>
       <c r="U272" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -31771,7 +31871,7 @@
       <c r="S273" s="3"/>
       <c r="T273" s="3"/>
       <c r="U273" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -31797,7 +31897,7 @@
       <c r="S274" s="3"/>
       <c r="T274" s="3"/>
       <c r="U274" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -31823,7 +31923,7 @@
       <c r="S275" s="3"/>
       <c r="T275" s="3"/>
       <c r="U275" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -31849,7 +31949,7 @@
       <c r="S276" s="3"/>
       <c r="T276" s="3"/>
       <c r="U276" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -31875,7 +31975,7 @@
       <c r="S277" s="3"/>
       <c r="T277" s="3"/>
       <c r="U277" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -31901,7 +32001,7 @@
       <c r="S278" s="3"/>
       <c r="T278" s="3"/>
       <c r="U278" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -31927,7 +32027,7 @@
       <c r="S279" s="3"/>
       <c r="T279" s="3"/>
       <c r="U279" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -31953,7 +32053,7 @@
       <c r="S280" s="3"/>
       <c r="T280" s="3"/>
       <c r="U280" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -31979,7 +32079,7 @@
       <c r="S281" s="3"/>
       <c r="T281" s="3"/>
       <c r="U281" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -32005,7 +32105,7 @@
       <c r="S282" s="3"/>
       <c r="T282" s="3"/>
       <c r="U282" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -32031,7 +32131,7 @@
       <c r="S283" s="3"/>
       <c r="T283" s="3"/>
       <c r="U283" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -32057,7 +32157,7 @@
       <c r="S284" s="3"/>
       <c r="T284" s="3"/>
       <c r="U284" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -32083,7 +32183,7 @@
       <c r="S285" s="3"/>
       <c r="T285" s="3"/>
       <c r="U285" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -32109,7 +32209,7 @@
       <c r="S286" s="3"/>
       <c r="T286" s="3"/>
       <c r="U286" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -32135,7 +32235,7 @@
       <c r="S287" s="3"/>
       <c r="T287" s="3"/>
       <c r="U287" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -32161,7 +32261,7 @@
       <c r="S288" s="3"/>
       <c r="T288" s="3"/>
       <c r="U288" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -32187,7 +32287,7 @@
       <c r="S289" s="3"/>
       <c r="T289" s="3"/>
       <c r="U289" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -32213,7 +32313,7 @@
       <c r="S290" s="3"/>
       <c r="T290" s="3"/>
       <c r="U290" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -32239,7 +32339,7 @@
       <c r="S291" s="3"/>
       <c r="T291" s="3"/>
       <c r="U291" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -32265,7 +32365,7 @@
       <c r="S292" s="3"/>
       <c r="T292" s="3"/>
       <c r="U292" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -32291,7 +32391,7 @@
       <c r="S293" s="3"/>
       <c r="T293" s="3"/>
       <c r="U293" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -32317,7 +32417,7 @@
       <c r="S294" s="3"/>
       <c r="T294" s="3"/>
       <c r="U294" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -32343,7 +32443,7 @@
       <c r="S295" s="3"/>
       <c r="T295" s="3"/>
       <c r="U295" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -32369,7 +32469,7 @@
       <c r="S296" s="3"/>
       <c r="T296" s="3"/>
       <c r="U296" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -32395,7 +32495,7 @@
       <c r="S297" s="3"/>
       <c r="T297" s="3"/>
       <c r="U297" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -32421,7 +32521,7 @@
       <c r="S298" s="3"/>
       <c r="T298" s="3"/>
       <c r="U298" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -32447,7 +32547,7 @@
       <c r="S299" s="3"/>
       <c r="T299" s="3"/>
       <c r="U299" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -32473,7 +32573,7 @@
       <c r="S300" s="3"/>
       <c r="T300" s="3"/>
       <c r="U300" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -32499,7 +32599,7 @@
       <c r="S301" s="3"/>
       <c r="T301" s="3"/>
       <c r="U301" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -32525,7 +32625,7 @@
       <c r="S302" s="3"/>
       <c r="T302" s="3"/>
       <c r="U302" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -32551,7 +32651,7 @@
       <c r="S303" s="3"/>
       <c r="T303" s="3"/>
       <c r="U303" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -32577,7 +32677,7 @@
       <c r="S304" s="3"/>
       <c r="T304" s="3"/>
       <c r="U304" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -32603,7 +32703,7 @@
       <c r="S305" s="3"/>
       <c r="T305" s="3"/>
       <c r="U305" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -32629,7 +32729,7 @@
       <c r="S306" s="3"/>
       <c r="T306" s="3"/>
       <c r="U306" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -32655,7 +32755,7 @@
       <c r="S307" s="3"/>
       <c r="T307" s="3"/>
       <c r="U307" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -32681,7 +32781,7 @@
       <c r="S308" s="3"/>
       <c r="T308" s="3"/>
       <c r="U308" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -32707,7 +32807,7 @@
       <c r="S309" s="3"/>
       <c r="T309" s="3"/>
       <c r="U309" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -32733,7 +32833,7 @@
       <c r="S310" s="3"/>
       <c r="T310" s="3"/>
       <c r="U310" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -32759,7 +32859,7 @@
       <c r="S311" s="3"/>
       <c r="T311" s="3"/>
       <c r="U311" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -32785,7 +32885,7 @@
       <c r="S312" s="3"/>
       <c r="T312" s="3"/>
       <c r="U312" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -32811,7 +32911,7 @@
       <c r="S313" s="3"/>
       <c r="T313" s="3"/>
       <c r="U313" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -32837,7 +32937,7 @@
       <c r="S314" s="3"/>
       <c r="T314" s="3"/>
       <c r="U314" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -32863,7 +32963,7 @@
       <c r="S315" s="3"/>
       <c r="T315" s="3"/>
       <c r="U315" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -32889,7 +32989,7 @@
       <c r="S316" s="3"/>
       <c r="T316" s="3"/>
       <c r="U316" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -32915,7 +33015,7 @@
       <c r="S317" s="3"/>
       <c r="T317" s="3"/>
       <c r="U317" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -32941,7 +33041,7 @@
       <c r="S318" s="3"/>
       <c r="T318" s="3"/>
       <c r="U318" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -32967,7 +33067,7 @@
       <c r="S319" s="3"/>
       <c r="T319" s="3"/>
       <c r="U319" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -32993,7 +33093,7 @@
       <c r="S320" s="3"/>
       <c r="T320" s="3"/>
       <c r="U320" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -33019,7 +33119,7 @@
       <c r="S321" s="3"/>
       <c r="T321" s="3"/>
       <c r="U321" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -33045,7 +33145,7 @@
       <c r="S322" s="3"/>
       <c r="T322" s="3"/>
       <c r="U322" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -33071,7 +33171,7 @@
       <c r="S323" s="3"/>
       <c r="T323" s="3"/>
       <c r="U323" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -33097,7 +33197,7 @@
       <c r="S324" s="3"/>
       <c r="T324" s="3"/>
       <c r="U324" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -33123,7 +33223,7 @@
       <c r="S325" s="3"/>
       <c r="T325" s="3"/>
       <c r="U325" s="4" t="str">
-        <f t="shared" ref="U325:U388" si="38">IF(COUNTA(B325:T325)=0,"",AVERAGE(B325:T325))</f>
+        <f t="shared" ref="U325:U388" si="39">IF(COUNTA(B325:T325)=0,"",AVERAGE(B325:T325))</f>
         <v/>
       </c>
     </row>
@@ -33149,7 +33249,7 @@
       <c r="S326" s="3"/>
       <c r="T326" s="3"/>
       <c r="U326" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -33175,7 +33275,7 @@
       <c r="S327" s="3"/>
       <c r="T327" s="3"/>
       <c r="U327" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -33201,7 +33301,7 @@
       <c r="S328" s="3"/>
       <c r="T328" s="3"/>
       <c r="U328" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -33227,7 +33327,7 @@
       <c r="S329" s="3"/>
       <c r="T329" s="3"/>
       <c r="U329" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -33253,7 +33353,7 @@
       <c r="S330" s="3"/>
       <c r="T330" s="3"/>
       <c r="U330" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -33279,7 +33379,7 @@
       <c r="S331" s="3"/>
       <c r="T331" s="3"/>
       <c r="U331" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -33305,7 +33405,7 @@
       <c r="S332" s="3"/>
       <c r="T332" s="3"/>
       <c r="U332" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -33331,7 +33431,7 @@
       <c r="S333" s="3"/>
       <c r="T333" s="3"/>
       <c r="U333" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -33357,7 +33457,7 @@
       <c r="S334" s="3"/>
       <c r="T334" s="3"/>
       <c r="U334" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -33383,7 +33483,7 @@
       <c r="S335" s="3"/>
       <c r="T335" s="3"/>
       <c r="U335" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -33409,7 +33509,7 @@
       <c r="S336" s="3"/>
       <c r="T336" s="3"/>
       <c r="U336" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -33435,7 +33535,7 @@
       <c r="S337" s="3"/>
       <c r="T337" s="3"/>
       <c r="U337" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -33461,7 +33561,7 @@
       <c r="S338" s="3"/>
       <c r="T338" s="3"/>
       <c r="U338" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -33487,7 +33587,7 @@
       <c r="S339" s="3"/>
       <c r="T339" s="3"/>
       <c r="U339" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -33513,7 +33613,7 @@
       <c r="S340" s="3"/>
       <c r="T340" s="3"/>
       <c r="U340" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -33539,7 +33639,7 @@
       <c r="S341" s="3"/>
       <c r="T341" s="3"/>
       <c r="U341" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -33565,7 +33665,7 @@
       <c r="S342" s="3"/>
       <c r="T342" s="3"/>
       <c r="U342" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -33591,7 +33691,7 @@
       <c r="S343" s="3"/>
       <c r="T343" s="3"/>
       <c r="U343" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -33617,7 +33717,7 @@
       <c r="S344" s="3"/>
       <c r="T344" s="3"/>
       <c r="U344" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -33643,7 +33743,7 @@
       <c r="S345" s="3"/>
       <c r="T345" s="3"/>
       <c r="U345" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -33669,7 +33769,7 @@
       <c r="S346" s="3"/>
       <c r="T346" s="3"/>
       <c r="U346" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -33695,7 +33795,7 @@
       <c r="S347" s="3"/>
       <c r="T347" s="3"/>
       <c r="U347" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -33721,7 +33821,7 @@
       <c r="S348" s="3"/>
       <c r="T348" s="3"/>
       <c r="U348" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -33747,7 +33847,7 @@
       <c r="S349" s="3"/>
       <c r="T349" s="3"/>
       <c r="U349" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -33773,7 +33873,7 @@
       <c r="S350" s="3"/>
       <c r="T350" s="3"/>
       <c r="U350" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -33799,7 +33899,7 @@
       <c r="S351" s="3"/>
       <c r="T351" s="3"/>
       <c r="U351" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -33825,7 +33925,7 @@
       <c r="S352" s="3"/>
       <c r="T352" s="3"/>
       <c r="U352" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -33851,7 +33951,7 @@
       <c r="S353" s="3"/>
       <c r="T353" s="3"/>
       <c r="U353" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -33877,7 +33977,7 @@
       <c r="S354" s="3"/>
       <c r="T354" s="3"/>
       <c r="U354" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -33903,7 +34003,7 @@
       <c r="S355" s="3"/>
       <c r="T355" s="3"/>
       <c r="U355" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -33929,7 +34029,7 @@
       <c r="S356" s="3"/>
       <c r="T356" s="3"/>
       <c r="U356" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -33955,7 +34055,7 @@
       <c r="S357" s="3"/>
       <c r="T357" s="3"/>
       <c r="U357" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -33981,7 +34081,7 @@
       <c r="S358" s="3"/>
       <c r="T358" s="3"/>
       <c r="U358" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -34007,7 +34107,7 @@
       <c r="S359" s="3"/>
       <c r="T359" s="3"/>
       <c r="U359" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -34033,7 +34133,7 @@
       <c r="S360" s="3"/>
       <c r="T360" s="3"/>
       <c r="U360" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -34059,7 +34159,7 @@
       <c r="S361" s="3"/>
       <c r="T361" s="3"/>
       <c r="U361" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -34085,7 +34185,7 @@
       <c r="S362" s="3"/>
       <c r="T362" s="3"/>
       <c r="U362" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -34111,7 +34211,7 @@
       <c r="S363" s="3"/>
       <c r="T363" s="3"/>
       <c r="U363" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -34137,7 +34237,7 @@
       <c r="S364" s="3"/>
       <c r="T364" s="3"/>
       <c r="U364" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -34163,7 +34263,7 @@
       <c r="S365" s="3"/>
       <c r="T365" s="3"/>
       <c r="U365" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -34189,7 +34289,7 @@
       <c r="S366" s="3"/>
       <c r="T366" s="3"/>
       <c r="U366" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -34215,7 +34315,7 @@
       <c r="S367" s="3"/>
       <c r="T367" s="3"/>
       <c r="U367" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -34241,7 +34341,7 @@
       <c r="S368" s="3"/>
       <c r="T368" s="3"/>
       <c r="U368" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -34267,7 +34367,7 @@
       <c r="S369" s="3"/>
       <c r="T369" s="3"/>
       <c r="U369" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -34293,7 +34393,7 @@
       <c r="S370" s="3"/>
       <c r="T370" s="3"/>
       <c r="U370" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -34319,7 +34419,7 @@
       <c r="S371" s="3"/>
       <c r="T371" s="3"/>
       <c r="U371" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -34345,7 +34445,7 @@
       <c r="S372" s="3"/>
       <c r="T372" s="3"/>
       <c r="U372" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -34371,7 +34471,7 @@
       <c r="S373" s="3"/>
       <c r="T373" s="3"/>
       <c r="U373" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -34397,7 +34497,7 @@
       <c r="S374" s="3"/>
       <c r="T374" s="3"/>
       <c r="U374" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -34423,7 +34523,7 @@
       <c r="S375" s="3"/>
       <c r="T375" s="3"/>
       <c r="U375" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -34449,7 +34549,7 @@
       <c r="S376" s="3"/>
       <c r="T376" s="3"/>
       <c r="U376" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -34475,7 +34575,7 @@
       <c r="S377" s="3"/>
       <c r="T377" s="3"/>
       <c r="U377" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -34501,7 +34601,7 @@
       <c r="S378" s="3"/>
       <c r="T378" s="3"/>
       <c r="U378" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -34527,7 +34627,7 @@
       <c r="S379" s="3"/>
       <c r="T379" s="3"/>
       <c r="U379" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -34553,7 +34653,7 @@
       <c r="S380" s="3"/>
       <c r="T380" s="3"/>
       <c r="U380" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -34579,7 +34679,7 @@
       <c r="S381" s="3"/>
       <c r="T381" s="3"/>
       <c r="U381" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -34605,7 +34705,7 @@
       <c r="S382" s="3"/>
       <c r="T382" s="3"/>
       <c r="U382" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -34631,7 +34731,7 @@
       <c r="S383" s="3"/>
       <c r="T383" s="3"/>
       <c r="U383" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -34657,7 +34757,7 @@
       <c r="S384" s="3"/>
       <c r="T384" s="3"/>
       <c r="U384" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -34683,7 +34783,7 @@
       <c r="S385" s="3"/>
       <c r="T385" s="3"/>
       <c r="U385" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -34709,7 +34809,7 @@
       <c r="S386" s="3"/>
       <c r="T386" s="3"/>
       <c r="U386" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -34735,7 +34835,7 @@
       <c r="S387" s="3"/>
       <c r="T387" s="3"/>
       <c r="U387" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -34761,7 +34861,7 @@
       <c r="S388" s="3"/>
       <c r="T388" s="3"/>
       <c r="U388" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -34787,7 +34887,7 @@
       <c r="S389" s="3"/>
       <c r="T389" s="3"/>
       <c r="U389" s="4" t="str">
-        <f t="shared" ref="U389:U390" si="39">IF(COUNTA(B389:T389)=0,"",AVERAGE(B389:T389))</f>
+        <f t="shared" ref="U389:U390" si="40">IF(COUNTA(B389:T389)=0,"",AVERAGE(B389:T389))</f>
         <v/>
       </c>
     </row>
@@ -34813,7 +34913,7 @@
       <c r="S390" s="3"/>
       <c r="T390" s="3"/>
       <c r="U390" s="4" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
     </row>
@@ -34843,7 +34943,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="8" t="s">
         <v>36</v>
       </c>
       <c r="B1" s="7"/>
@@ -34858,7 +34958,7 @@
       <c r="K1" s="7"/>
     </row>
     <row r="2" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="6" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="7"/>
@@ -37392,19 +37492,39 @@
       </c>
     </row>
     <row r="74" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A74" s="2"/>
-      <c r="B74" s="3"/>
-      <c r="C74" s="3"/>
-      <c r="D74" s="3"/>
-      <c r="E74" s="3"/>
-      <c r="F74" s="3"/>
-      <c r="G74" s="3"/>
-      <c r="H74" s="3"/>
-      <c r="I74" s="3"/>
-      <c r="J74" s="3"/>
-      <c r="K74" s="4" t="str">
-        <f t="shared" si="34"/>
-        <v/>
+      <c r="A74" s="2">
+        <v>46230</v>
+      </c>
+      <c r="B74" s="3">
+        <v>3.1</v>
+      </c>
+      <c r="C74" s="3">
+        <v>3.14</v>
+      </c>
+      <c r="D74" s="3">
+        <v>2.8</v>
+      </c>
+      <c r="E74" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="F74" s="3">
+        <v>2.79</v>
+      </c>
+      <c r="G74" s="3">
+        <v>2.95</v>
+      </c>
+      <c r="H74" s="3">
+        <v>2.69</v>
+      </c>
+      <c r="I74" s="3">
+        <v>2.89</v>
+      </c>
+      <c r="J74" s="3">
+        <v>2.89</v>
+      </c>
+      <c r="K74" s="4">
+        <f t="shared" ref="K74" si="35">IF(COUNTA(B74:J74)=0,"",AVERAGE(B74:J74))</f>
+        <v>2.9155555555555557</v>
       </c>
     </row>
     <row r="75" spans="1:11" x14ac:dyDescent="0.25">
@@ -38347,7 +38467,7 @@
       <c r="I133" s="3"/>
       <c r="J133" s="3"/>
       <c r="K133" s="4" t="str">
-        <f t="shared" ref="K133:K196" si="35">IF(COUNTA(B133:J133)=0,"",AVERAGE(B133:J133))</f>
+        <f t="shared" ref="K133:K196" si="36">IF(COUNTA(B133:J133)=0,"",AVERAGE(B133:J133))</f>
         <v/>
       </c>
     </row>
@@ -38363,7 +38483,7 @@
       <c r="I134" s="3"/>
       <c r="J134" s="3"/>
       <c r="K134" s="4" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
@@ -38379,7 +38499,7 @@
       <c r="I135" s="3"/>
       <c r="J135" s="3"/>
       <c r="K135" s="4" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
@@ -38395,7 +38515,7 @@
       <c r="I136" s="3"/>
       <c r="J136" s="3"/>
       <c r="K136" s="4" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
@@ -38411,7 +38531,7 @@
       <c r="I137" s="3"/>
       <c r="J137" s="3"/>
       <c r="K137" s="4" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
@@ -38427,7 +38547,7 @@
       <c r="I138" s="3"/>
       <c r="J138" s="3"/>
       <c r="K138" s="4" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
@@ -38443,7 +38563,7 @@
       <c r="I139" s="3"/>
       <c r="J139" s="3"/>
       <c r="K139" s="4" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
@@ -38459,7 +38579,7 @@
       <c r="I140" s="3"/>
       <c r="J140" s="3"/>
       <c r="K140" s="4" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
@@ -38475,7 +38595,7 @@
       <c r="I141" s="3"/>
       <c r="J141" s="3"/>
       <c r="K141" s="4" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
@@ -38491,7 +38611,7 @@
       <c r="I142" s="3"/>
       <c r="J142" s="3"/>
       <c r="K142" s="4" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
@@ -38507,7 +38627,7 @@
       <c r="I143" s="3"/>
       <c r="J143" s="3"/>
       <c r="K143" s="4" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
@@ -38523,7 +38643,7 @@
       <c r="I144" s="3"/>
       <c r="J144" s="3"/>
       <c r="K144" s="4" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
@@ -38539,7 +38659,7 @@
       <c r="I145" s="3"/>
       <c r="J145" s="3"/>
       <c r="K145" s="4" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
@@ -38555,7 +38675,7 @@
       <c r="I146" s="3"/>
       <c r="J146" s="3"/>
       <c r="K146" s="4" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
@@ -38571,7 +38691,7 @@
       <c r="I147" s="3"/>
       <c r="J147" s="3"/>
       <c r="K147" s="4" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
@@ -38587,7 +38707,7 @@
       <c r="I148" s="3"/>
       <c r="J148" s="3"/>
       <c r="K148" s="4" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
@@ -38603,7 +38723,7 @@
       <c r="I149" s="3"/>
       <c r="J149" s="3"/>
       <c r="K149" s="4" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
@@ -38619,7 +38739,7 @@
       <c r="I150" s="3"/>
       <c r="J150" s="3"/>
       <c r="K150" s="4" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
@@ -38635,7 +38755,7 @@
       <c r="I151" s="3"/>
       <c r="J151" s="3"/>
       <c r="K151" s="4" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
@@ -38651,7 +38771,7 @@
       <c r="I152" s="3"/>
       <c r="J152" s="3"/>
       <c r="K152" s="4" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
@@ -38667,7 +38787,7 @@
       <c r="I153" s="3"/>
       <c r="J153" s="3"/>
       <c r="K153" s="4" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
@@ -38683,7 +38803,7 @@
       <c r="I154" s="3"/>
       <c r="J154" s="3"/>
       <c r="K154" s="4" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
@@ -38699,7 +38819,7 @@
       <c r="I155" s="3"/>
       <c r="J155" s="3"/>
       <c r="K155" s="4" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
@@ -38715,7 +38835,7 @@
       <c r="I156" s="3"/>
       <c r="J156" s="3"/>
       <c r="K156" s="4" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
@@ -38731,7 +38851,7 @@
       <c r="I157" s="3"/>
       <c r="J157" s="3"/>
       <c r="K157" s="4" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
@@ -38747,7 +38867,7 @@
       <c r="I158" s="3"/>
       <c r="J158" s="3"/>
       <c r="K158" s="4" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
@@ -38763,7 +38883,7 @@
       <c r="I159" s="3"/>
       <c r="J159" s="3"/>
       <c r="K159" s="4" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
@@ -38779,7 +38899,7 @@
       <c r="I160" s="3"/>
       <c r="J160" s="3"/>
       <c r="K160" s="4" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
@@ -38795,7 +38915,7 @@
       <c r="I161" s="3"/>
       <c r="J161" s="3"/>
       <c r="K161" s="4" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
@@ -38811,7 +38931,7 @@
       <c r="I162" s="3"/>
       <c r="J162" s="3"/>
       <c r="K162" s="4" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
@@ -38827,7 +38947,7 @@
       <c r="I163" s="3"/>
       <c r="J163" s="3"/>
       <c r="K163" s="4" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
@@ -38843,7 +38963,7 @@
       <c r="I164" s="3"/>
       <c r="J164" s="3"/>
       <c r="K164" s="4" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
@@ -38859,7 +38979,7 @@
       <c r="I165" s="3"/>
       <c r="J165" s="3"/>
       <c r="K165" s="4" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
@@ -38875,7 +38995,7 @@
       <c r="I166" s="3"/>
       <c r="J166" s="3"/>
       <c r="K166" s="4" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
@@ -38891,7 +39011,7 @@
       <c r="I167" s="3"/>
       <c r="J167" s="3"/>
       <c r="K167" s="4" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
@@ -38907,7 +39027,7 @@
       <c r="I168" s="3"/>
       <c r="J168" s="3"/>
       <c r="K168" s="4" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
@@ -38923,7 +39043,7 @@
       <c r="I169" s="3"/>
       <c r="J169" s="3"/>
       <c r="K169" s="4" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
@@ -38939,7 +39059,7 @@
       <c r="I170" s="3"/>
       <c r="J170" s="3"/>
       <c r="K170" s="4" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
@@ -38955,7 +39075,7 @@
       <c r="I171" s="3"/>
       <c r="J171" s="3"/>
       <c r="K171" s="4" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
@@ -38971,7 +39091,7 @@
       <c r="I172" s="3"/>
       <c r="J172" s="3"/>
       <c r="K172" s="4" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
@@ -38987,7 +39107,7 @@
       <c r="I173" s="3"/>
       <c r="J173" s="3"/>
       <c r="K173" s="4" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
@@ -39003,7 +39123,7 @@
       <c r="I174" s="3"/>
       <c r="J174" s="3"/>
       <c r="K174" s="4" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
@@ -39019,7 +39139,7 @@
       <c r="I175" s="3"/>
       <c r="J175" s="3"/>
       <c r="K175" s="4" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
@@ -39035,7 +39155,7 @@
       <c r="I176" s="3"/>
       <c r="J176" s="3"/>
       <c r="K176" s="4" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
@@ -39051,7 +39171,7 @@
       <c r="I177" s="3"/>
       <c r="J177" s="3"/>
       <c r="K177" s="4" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
@@ -39067,7 +39187,7 @@
       <c r="I178" s="3"/>
       <c r="J178" s="3"/>
       <c r="K178" s="4" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
@@ -39083,7 +39203,7 @@
       <c r="I179" s="3"/>
       <c r="J179" s="3"/>
       <c r="K179" s="4" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
@@ -39099,7 +39219,7 @@
       <c r="I180" s="3"/>
       <c r="J180" s="3"/>
       <c r="K180" s="4" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
@@ -39115,7 +39235,7 @@
       <c r="I181" s="3"/>
       <c r="J181" s="3"/>
       <c r="K181" s="4" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
@@ -39131,7 +39251,7 @@
       <c r="I182" s="3"/>
       <c r="J182" s="3"/>
       <c r="K182" s="4" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
@@ -39147,7 +39267,7 @@
       <c r="I183" s="3"/>
       <c r="J183" s="3"/>
       <c r="K183" s="4" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
@@ -39163,7 +39283,7 @@
       <c r="I184" s="3"/>
       <c r="J184" s="3"/>
       <c r="K184" s="4" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
@@ -39179,7 +39299,7 @@
       <c r="I185" s="3"/>
       <c r="J185" s="3"/>
       <c r="K185" s="4" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
@@ -39195,7 +39315,7 @@
       <c r="I186" s="3"/>
       <c r="J186" s="3"/>
       <c r="K186" s="4" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
@@ -39211,7 +39331,7 @@
       <c r="I187" s="3"/>
       <c r="J187" s="3"/>
       <c r="K187" s="4" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
@@ -39227,7 +39347,7 @@
       <c r="I188" s="3"/>
       <c r="J188" s="3"/>
       <c r="K188" s="4" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
@@ -39243,7 +39363,7 @@
       <c r="I189" s="3"/>
       <c r="J189" s="3"/>
       <c r="K189" s="4" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
@@ -39259,7 +39379,7 @@
       <c r="I190" s="3"/>
       <c r="J190" s="3"/>
       <c r="K190" s="4" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
@@ -39275,7 +39395,7 @@
       <c r="I191" s="3"/>
       <c r="J191" s="3"/>
       <c r="K191" s="4" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
@@ -39291,7 +39411,7 @@
       <c r="I192" s="3"/>
       <c r="J192" s="3"/>
       <c r="K192" s="4" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
@@ -39307,7 +39427,7 @@
       <c r="I193" s="3"/>
       <c r="J193" s="3"/>
       <c r="K193" s="4" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
@@ -39323,7 +39443,7 @@
       <c r="I194" s="3"/>
       <c r="J194" s="3"/>
       <c r="K194" s="4" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
@@ -39339,7 +39459,7 @@
       <c r="I195" s="3"/>
       <c r="J195" s="3"/>
       <c r="K195" s="4" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
@@ -39355,7 +39475,7 @@
       <c r="I196" s="3"/>
       <c r="J196" s="3"/>
       <c r="K196" s="4" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
@@ -39371,7 +39491,7 @@
       <c r="I197" s="3"/>
       <c r="J197" s="3"/>
       <c r="K197" s="4" t="str">
-        <f t="shared" ref="K197:K260" si="36">IF(COUNTA(B197:J197)=0,"",AVERAGE(B197:J197))</f>
+        <f t="shared" ref="K197:K260" si="37">IF(COUNTA(B197:J197)=0,"",AVERAGE(B197:J197))</f>
         <v/>
       </c>
     </row>
@@ -39387,7 +39507,7 @@
       <c r="I198" s="3"/>
       <c r="J198" s="3"/>
       <c r="K198" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -39403,7 +39523,7 @@
       <c r="I199" s="3"/>
       <c r="J199" s="3"/>
       <c r="K199" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -39419,7 +39539,7 @@
       <c r="I200" s="3"/>
       <c r="J200" s="3"/>
       <c r="K200" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -39435,7 +39555,7 @@
       <c r="I201" s="3"/>
       <c r="J201" s="3"/>
       <c r="K201" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -39451,7 +39571,7 @@
       <c r="I202" s="3"/>
       <c r="J202" s="3"/>
       <c r="K202" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -39467,7 +39587,7 @@
       <c r="I203" s="3"/>
       <c r="J203" s="3"/>
       <c r="K203" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -39483,7 +39603,7 @@
       <c r="I204" s="3"/>
       <c r="J204" s="3"/>
       <c r="K204" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -39499,7 +39619,7 @@
       <c r="I205" s="3"/>
       <c r="J205" s="3"/>
       <c r="K205" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -39515,7 +39635,7 @@
       <c r="I206" s="3"/>
       <c r="J206" s="3"/>
       <c r="K206" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -39531,7 +39651,7 @@
       <c r="I207" s="3"/>
       <c r="J207" s="3"/>
       <c r="K207" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -39547,7 +39667,7 @@
       <c r="I208" s="3"/>
       <c r="J208" s="3"/>
       <c r="K208" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -39563,7 +39683,7 @@
       <c r="I209" s="3"/>
       <c r="J209" s="3"/>
       <c r="K209" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -39579,7 +39699,7 @@
       <c r="I210" s="3"/>
       <c r="J210" s="3"/>
       <c r="K210" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -39595,7 +39715,7 @@
       <c r="I211" s="3"/>
       <c r="J211" s="3"/>
       <c r="K211" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -39611,7 +39731,7 @@
       <c r="I212" s="3"/>
       <c r="J212" s="3"/>
       <c r="K212" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -39627,7 +39747,7 @@
       <c r="I213" s="3"/>
       <c r="J213" s="3"/>
       <c r="K213" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -39643,7 +39763,7 @@
       <c r="I214" s="3"/>
       <c r="J214" s="3"/>
       <c r="K214" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -39659,7 +39779,7 @@
       <c r="I215" s="3"/>
       <c r="J215" s="3"/>
       <c r="K215" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -39675,7 +39795,7 @@
       <c r="I216" s="3"/>
       <c r="J216" s="3"/>
       <c r="K216" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -39691,7 +39811,7 @@
       <c r="I217" s="3"/>
       <c r="J217" s="3"/>
       <c r="K217" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -39707,7 +39827,7 @@
       <c r="I218" s="3"/>
       <c r="J218" s="3"/>
       <c r="K218" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -39723,7 +39843,7 @@
       <c r="I219" s="3"/>
       <c r="J219" s="3"/>
       <c r="K219" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -39739,7 +39859,7 @@
       <c r="I220" s="3"/>
       <c r="J220" s="3"/>
       <c r="K220" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -39755,7 +39875,7 @@
       <c r="I221" s="3"/>
       <c r="J221" s="3"/>
       <c r="K221" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -39771,7 +39891,7 @@
       <c r="I222" s="3"/>
       <c r="J222" s="3"/>
       <c r="K222" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -39787,7 +39907,7 @@
       <c r="I223" s="3"/>
       <c r="J223" s="3"/>
       <c r="K223" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -39803,7 +39923,7 @@
       <c r="I224" s="3"/>
       <c r="J224" s="3"/>
       <c r="K224" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -39819,7 +39939,7 @@
       <c r="I225" s="3"/>
       <c r="J225" s="3"/>
       <c r="K225" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -39835,7 +39955,7 @@
       <c r="I226" s="3"/>
       <c r="J226" s="3"/>
       <c r="K226" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -39851,7 +39971,7 @@
       <c r="I227" s="3"/>
       <c r="J227" s="3"/>
       <c r="K227" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -39867,7 +39987,7 @@
       <c r="I228" s="3"/>
       <c r="J228" s="3"/>
       <c r="K228" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -39883,7 +40003,7 @@
       <c r="I229" s="3"/>
       <c r="J229" s="3"/>
       <c r="K229" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -39899,7 +40019,7 @@
       <c r="I230" s="3"/>
       <c r="J230" s="3"/>
       <c r="K230" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -39915,7 +40035,7 @@
       <c r="I231" s="3"/>
       <c r="J231" s="3"/>
       <c r="K231" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -39931,7 +40051,7 @@
       <c r="I232" s="3"/>
       <c r="J232" s="3"/>
       <c r="K232" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -39947,7 +40067,7 @@
       <c r="I233" s="3"/>
       <c r="J233" s="3"/>
       <c r="K233" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -39963,7 +40083,7 @@
       <c r="I234" s="3"/>
       <c r="J234" s="3"/>
       <c r="K234" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -39979,7 +40099,7 @@
       <c r="I235" s="3"/>
       <c r="J235" s="3"/>
       <c r="K235" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -39995,7 +40115,7 @@
       <c r="I236" s="3"/>
       <c r="J236" s="3"/>
       <c r="K236" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -40011,7 +40131,7 @@
       <c r="I237" s="3"/>
       <c r="J237" s="3"/>
       <c r="K237" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -40027,7 +40147,7 @@
       <c r="I238" s="3"/>
       <c r="J238" s="3"/>
       <c r="K238" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -40043,7 +40163,7 @@
       <c r="I239" s="3"/>
       <c r="J239" s="3"/>
       <c r="K239" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -40059,7 +40179,7 @@
       <c r="I240" s="3"/>
       <c r="J240" s="3"/>
       <c r="K240" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -40075,7 +40195,7 @@
       <c r="I241" s="3"/>
       <c r="J241" s="3"/>
       <c r="K241" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -40091,7 +40211,7 @@
       <c r="I242" s="3"/>
       <c r="J242" s="3"/>
       <c r="K242" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -40107,7 +40227,7 @@
       <c r="I243" s="3"/>
       <c r="J243" s="3"/>
       <c r="K243" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -40123,7 +40243,7 @@
       <c r="I244" s="3"/>
       <c r="J244" s="3"/>
       <c r="K244" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -40139,7 +40259,7 @@
       <c r="I245" s="3"/>
       <c r="J245" s="3"/>
       <c r="K245" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -40155,7 +40275,7 @@
       <c r="I246" s="3"/>
       <c r="J246" s="3"/>
       <c r="K246" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -40171,7 +40291,7 @@
       <c r="I247" s="3"/>
       <c r="J247" s="3"/>
       <c r="K247" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -40187,7 +40307,7 @@
       <c r="I248" s="3"/>
       <c r="J248" s="3"/>
       <c r="K248" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -40203,7 +40323,7 @@
       <c r="I249" s="3"/>
       <c r="J249" s="3"/>
       <c r="K249" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -40219,7 +40339,7 @@
       <c r="I250" s="3"/>
       <c r="J250" s="3"/>
       <c r="K250" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -40235,7 +40355,7 @@
       <c r="I251" s="3"/>
       <c r="J251" s="3"/>
       <c r="K251" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -40251,7 +40371,7 @@
       <c r="I252" s="3"/>
       <c r="J252" s="3"/>
       <c r="K252" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -40267,7 +40387,7 @@
       <c r="I253" s="3"/>
       <c r="J253" s="3"/>
       <c r="K253" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -40283,7 +40403,7 @@
       <c r="I254" s="3"/>
       <c r="J254" s="3"/>
       <c r="K254" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -40299,7 +40419,7 @@
       <c r="I255" s="3"/>
       <c r="J255" s="3"/>
       <c r="K255" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -40315,7 +40435,7 @@
       <c r="I256" s="3"/>
       <c r="J256" s="3"/>
       <c r="K256" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -40331,7 +40451,7 @@
       <c r="I257" s="3"/>
       <c r="J257" s="3"/>
       <c r="K257" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -40347,7 +40467,7 @@
       <c r="I258" s="3"/>
       <c r="J258" s="3"/>
       <c r="K258" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -40363,7 +40483,7 @@
       <c r="I259" s="3"/>
       <c r="J259" s="3"/>
       <c r="K259" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -40379,7 +40499,7 @@
       <c r="I260" s="3"/>
       <c r="J260" s="3"/>
       <c r="K260" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -40395,7 +40515,7 @@
       <c r="I261" s="3"/>
       <c r="J261" s="3"/>
       <c r="K261" s="4" t="str">
-        <f t="shared" ref="K261:K324" si="37">IF(COUNTA(B261:J261)=0,"",AVERAGE(B261:J261))</f>
+        <f t="shared" ref="K261:K324" si="38">IF(COUNTA(B261:J261)=0,"",AVERAGE(B261:J261))</f>
         <v/>
       </c>
     </row>
@@ -40411,7 +40531,7 @@
       <c r="I262" s="3"/>
       <c r="J262" s="3"/>
       <c r="K262" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -40427,7 +40547,7 @@
       <c r="I263" s="3"/>
       <c r="J263" s="3"/>
       <c r="K263" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -40443,7 +40563,7 @@
       <c r="I264" s="3"/>
       <c r="J264" s="3"/>
       <c r="K264" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -40459,7 +40579,7 @@
       <c r="I265" s="3"/>
       <c r="J265" s="3"/>
       <c r="K265" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -40475,7 +40595,7 @@
       <c r="I266" s="3"/>
       <c r="J266" s="3"/>
       <c r="K266" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -40491,7 +40611,7 @@
       <c r="I267" s="3"/>
       <c r="J267" s="3"/>
       <c r="K267" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -40507,7 +40627,7 @@
       <c r="I268" s="3"/>
       <c r="J268" s="3"/>
       <c r="K268" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -40523,7 +40643,7 @@
       <c r="I269" s="3"/>
       <c r="J269" s="3"/>
       <c r="K269" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -40539,7 +40659,7 @@
       <c r="I270" s="3"/>
       <c r="J270" s="3"/>
       <c r="K270" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -40555,7 +40675,7 @@
       <c r="I271" s="3"/>
       <c r="J271" s="3"/>
       <c r="K271" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -40571,7 +40691,7 @@
       <c r="I272" s="3"/>
       <c r="J272" s="3"/>
       <c r="K272" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -40587,7 +40707,7 @@
       <c r="I273" s="3"/>
       <c r="J273" s="3"/>
       <c r="K273" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -40603,7 +40723,7 @@
       <c r="I274" s="3"/>
       <c r="J274" s="3"/>
       <c r="K274" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -40619,7 +40739,7 @@
       <c r="I275" s="3"/>
       <c r="J275" s="3"/>
       <c r="K275" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -40635,7 +40755,7 @@
       <c r="I276" s="3"/>
       <c r="J276" s="3"/>
       <c r="K276" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -40651,7 +40771,7 @@
       <c r="I277" s="3"/>
       <c r="J277" s="3"/>
       <c r="K277" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -40667,7 +40787,7 @@
       <c r="I278" s="3"/>
       <c r="J278" s="3"/>
       <c r="K278" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -40683,7 +40803,7 @@
       <c r="I279" s="3"/>
       <c r="J279" s="3"/>
       <c r="K279" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -40699,7 +40819,7 @@
       <c r="I280" s="3"/>
       <c r="J280" s="3"/>
       <c r="K280" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -40715,7 +40835,7 @@
       <c r="I281" s="3"/>
       <c r="J281" s="3"/>
       <c r="K281" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -40731,7 +40851,7 @@
       <c r="I282" s="3"/>
       <c r="J282" s="3"/>
       <c r="K282" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -40747,7 +40867,7 @@
       <c r="I283" s="3"/>
       <c r="J283" s="3"/>
       <c r="K283" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -40763,7 +40883,7 @@
       <c r="I284" s="3"/>
       <c r="J284" s="3"/>
       <c r="K284" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -40779,7 +40899,7 @@
       <c r="I285" s="3"/>
       <c r="J285" s="3"/>
       <c r="K285" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -40795,7 +40915,7 @@
       <c r="I286" s="3"/>
       <c r="J286" s="3"/>
       <c r="K286" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -40811,7 +40931,7 @@
       <c r="I287" s="3"/>
       <c r="J287" s="3"/>
       <c r="K287" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -40827,7 +40947,7 @@
       <c r="I288" s="3"/>
       <c r="J288" s="3"/>
       <c r="K288" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -40843,7 +40963,7 @@
       <c r="I289" s="3"/>
       <c r="J289" s="3"/>
       <c r="K289" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -40859,7 +40979,7 @@
       <c r="I290" s="3"/>
       <c r="J290" s="3"/>
       <c r="K290" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -40875,7 +40995,7 @@
       <c r="I291" s="3"/>
       <c r="J291" s="3"/>
       <c r="K291" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -40891,7 +41011,7 @@
       <c r="I292" s="3"/>
       <c r="J292" s="3"/>
       <c r="K292" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -40907,7 +41027,7 @@
       <c r="I293" s="3"/>
       <c r="J293" s="3"/>
       <c r="K293" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -40923,7 +41043,7 @@
       <c r="I294" s="3"/>
       <c r="J294" s="3"/>
       <c r="K294" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -40939,7 +41059,7 @@
       <c r="I295" s="3"/>
       <c r="J295" s="3"/>
       <c r="K295" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -40955,7 +41075,7 @@
       <c r="I296" s="3"/>
       <c r="J296" s="3"/>
       <c r="K296" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -40971,7 +41091,7 @@
       <c r="I297" s="3"/>
       <c r="J297" s="3"/>
       <c r="K297" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -40987,7 +41107,7 @@
       <c r="I298" s="3"/>
       <c r="J298" s="3"/>
       <c r="K298" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -41003,7 +41123,7 @@
       <c r="I299" s="3"/>
       <c r="J299" s="3"/>
       <c r="K299" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -41019,7 +41139,7 @@
       <c r="I300" s="3"/>
       <c r="J300" s="3"/>
       <c r="K300" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -41035,7 +41155,7 @@
       <c r="I301" s="3"/>
       <c r="J301" s="3"/>
       <c r="K301" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -41051,7 +41171,7 @@
       <c r="I302" s="3"/>
       <c r="J302" s="3"/>
       <c r="K302" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -41067,7 +41187,7 @@
       <c r="I303" s="3"/>
       <c r="J303" s="3"/>
       <c r="K303" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -41083,7 +41203,7 @@
       <c r="I304" s="3"/>
       <c r="J304" s="3"/>
       <c r="K304" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -41099,7 +41219,7 @@
       <c r="I305" s="3"/>
       <c r="J305" s="3"/>
       <c r="K305" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -41115,7 +41235,7 @@
       <c r="I306" s="3"/>
       <c r="J306" s="3"/>
       <c r="K306" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -41131,7 +41251,7 @@
       <c r="I307" s="3"/>
       <c r="J307" s="3"/>
       <c r="K307" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -41147,7 +41267,7 @@
       <c r="I308" s="3"/>
       <c r="J308" s="3"/>
       <c r="K308" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -41163,7 +41283,7 @@
       <c r="I309" s="3"/>
       <c r="J309" s="3"/>
       <c r="K309" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -41179,7 +41299,7 @@
       <c r="I310" s="3"/>
       <c r="J310" s="3"/>
       <c r="K310" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -41195,7 +41315,7 @@
       <c r="I311" s="3"/>
       <c r="J311" s="3"/>
       <c r="K311" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -41211,7 +41331,7 @@
       <c r="I312" s="3"/>
       <c r="J312" s="3"/>
       <c r="K312" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -41227,7 +41347,7 @@
       <c r="I313" s="3"/>
       <c r="J313" s="3"/>
       <c r="K313" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -41243,7 +41363,7 @@
       <c r="I314" s="3"/>
       <c r="J314" s="3"/>
       <c r="K314" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -41259,7 +41379,7 @@
       <c r="I315" s="3"/>
       <c r="J315" s="3"/>
       <c r="K315" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -41275,7 +41395,7 @@
       <c r="I316" s="3"/>
       <c r="J316" s="3"/>
       <c r="K316" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -41291,7 +41411,7 @@
       <c r="I317" s="3"/>
       <c r="J317" s="3"/>
       <c r="K317" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -41307,7 +41427,7 @@
       <c r="I318" s="3"/>
       <c r="J318" s="3"/>
       <c r="K318" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -41323,7 +41443,7 @@
       <c r="I319" s="3"/>
       <c r="J319" s="3"/>
       <c r="K319" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -41339,7 +41459,7 @@
       <c r="I320" s="3"/>
       <c r="J320" s="3"/>
       <c r="K320" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -41355,7 +41475,7 @@
       <c r="I321" s="3"/>
       <c r="J321" s="3"/>
       <c r="K321" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -41371,7 +41491,7 @@
       <c r="I322" s="3"/>
       <c r="J322" s="3"/>
       <c r="K322" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -41387,7 +41507,7 @@
       <c r="I323" s="3"/>
       <c r="J323" s="3"/>
       <c r="K323" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -41403,7 +41523,7 @@
       <c r="I324" s="3"/>
       <c r="J324" s="3"/>
       <c r="K324" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -41419,7 +41539,7 @@
       <c r="I325" s="3"/>
       <c r="J325" s="3"/>
       <c r="K325" s="4" t="str">
-        <f t="shared" ref="K325:K388" si="38">IF(COUNTA(B325:J325)=0,"",AVERAGE(B325:J325))</f>
+        <f t="shared" ref="K325:K388" si="39">IF(COUNTA(B325:J325)=0,"",AVERAGE(B325:J325))</f>
         <v/>
       </c>
     </row>
@@ -41435,7 +41555,7 @@
       <c r="I326" s="3"/>
       <c r="J326" s="3"/>
       <c r="K326" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -41451,7 +41571,7 @@
       <c r="I327" s="3"/>
       <c r="J327" s="3"/>
       <c r="K327" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -41467,7 +41587,7 @@
       <c r="I328" s="3"/>
       <c r="J328" s="3"/>
       <c r="K328" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -41483,7 +41603,7 @@
       <c r="I329" s="3"/>
       <c r="J329" s="3"/>
       <c r="K329" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -41499,7 +41619,7 @@
       <c r="I330" s="3"/>
       <c r="J330" s="3"/>
       <c r="K330" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -41515,7 +41635,7 @@
       <c r="I331" s="3"/>
       <c r="J331" s="3"/>
       <c r="K331" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -41531,7 +41651,7 @@
       <c r="I332" s="3"/>
       <c r="J332" s="3"/>
       <c r="K332" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -41547,7 +41667,7 @@
       <c r="I333" s="3"/>
       <c r="J333" s="3"/>
       <c r="K333" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -41563,7 +41683,7 @@
       <c r="I334" s="3"/>
       <c r="J334" s="3"/>
       <c r="K334" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -41579,7 +41699,7 @@
       <c r="I335" s="3"/>
       <c r="J335" s="3"/>
       <c r="K335" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -41595,7 +41715,7 @@
       <c r="I336" s="3"/>
       <c r="J336" s="3"/>
       <c r="K336" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -41611,7 +41731,7 @@
       <c r="I337" s="3"/>
       <c r="J337" s="3"/>
       <c r="K337" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -41627,7 +41747,7 @@
       <c r="I338" s="3"/>
       <c r="J338" s="3"/>
       <c r="K338" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -41643,7 +41763,7 @@
       <c r="I339" s="3"/>
       <c r="J339" s="3"/>
       <c r="K339" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -41659,7 +41779,7 @@
       <c r="I340" s="3"/>
       <c r="J340" s="3"/>
       <c r="K340" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -41675,7 +41795,7 @@
       <c r="I341" s="3"/>
       <c r="J341" s="3"/>
       <c r="K341" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -41691,7 +41811,7 @@
       <c r="I342" s="3"/>
       <c r="J342" s="3"/>
       <c r="K342" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -41707,7 +41827,7 @@
       <c r="I343" s="3"/>
       <c r="J343" s="3"/>
       <c r="K343" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -41723,7 +41843,7 @@
       <c r="I344" s="3"/>
       <c r="J344" s="3"/>
       <c r="K344" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -41739,7 +41859,7 @@
       <c r="I345" s="3"/>
       <c r="J345" s="3"/>
       <c r="K345" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -41755,7 +41875,7 @@
       <c r="I346" s="3"/>
       <c r="J346" s="3"/>
       <c r="K346" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -41771,7 +41891,7 @@
       <c r="I347" s="3"/>
       <c r="J347" s="3"/>
       <c r="K347" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -41787,7 +41907,7 @@
       <c r="I348" s="3"/>
       <c r="J348" s="3"/>
       <c r="K348" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -41803,7 +41923,7 @@
       <c r="I349" s="3"/>
       <c r="J349" s="3"/>
       <c r="K349" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -41819,7 +41939,7 @@
       <c r="I350" s="3"/>
       <c r="J350" s="3"/>
       <c r="K350" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -41835,7 +41955,7 @@
       <c r="I351" s="3"/>
       <c r="J351" s="3"/>
       <c r="K351" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -41851,7 +41971,7 @@
       <c r="I352" s="3"/>
       <c r="J352" s="3"/>
       <c r="K352" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -41867,7 +41987,7 @@
       <c r="I353" s="3"/>
       <c r="J353" s="3"/>
       <c r="K353" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -41883,7 +42003,7 @@
       <c r="I354" s="3"/>
       <c r="J354" s="3"/>
       <c r="K354" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -41899,7 +42019,7 @@
       <c r="I355" s="3"/>
       <c r="J355" s="3"/>
       <c r="K355" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -41915,7 +42035,7 @@
       <c r="I356" s="3"/>
       <c r="J356" s="3"/>
       <c r="K356" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -41931,7 +42051,7 @@
       <c r="I357" s="3"/>
       <c r="J357" s="3"/>
       <c r="K357" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -41947,7 +42067,7 @@
       <c r="I358" s="3"/>
       <c r="J358" s="3"/>
       <c r="K358" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -41963,7 +42083,7 @@
       <c r="I359" s="3"/>
       <c r="J359" s="3"/>
       <c r="K359" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -41979,7 +42099,7 @@
       <c r="I360" s="3"/>
       <c r="J360" s="3"/>
       <c r="K360" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -41995,7 +42115,7 @@
       <c r="I361" s="3"/>
       <c r="J361" s="3"/>
       <c r="K361" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -42011,7 +42131,7 @@
       <c r="I362" s="3"/>
       <c r="J362" s="3"/>
       <c r="K362" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -42027,7 +42147,7 @@
       <c r="I363" s="3"/>
       <c r="J363" s="3"/>
       <c r="K363" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -42043,7 +42163,7 @@
       <c r="I364" s="3"/>
       <c r="J364" s="3"/>
       <c r="K364" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -42059,7 +42179,7 @@
       <c r="I365" s="3"/>
       <c r="J365" s="3"/>
       <c r="K365" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -42075,7 +42195,7 @@
       <c r="I366" s="3"/>
       <c r="J366" s="3"/>
       <c r="K366" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -42091,7 +42211,7 @@
       <c r="I367" s="3"/>
       <c r="J367" s="3"/>
       <c r="K367" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -42107,7 +42227,7 @@
       <c r="I368" s="3"/>
       <c r="J368" s="3"/>
       <c r="K368" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -42123,7 +42243,7 @@
       <c r="I369" s="3"/>
       <c r="J369" s="3"/>
       <c r="K369" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -42139,7 +42259,7 @@
       <c r="I370" s="3"/>
       <c r="J370" s="3"/>
       <c r="K370" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -42155,7 +42275,7 @@
       <c r="I371" s="3"/>
       <c r="J371" s="3"/>
       <c r="K371" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -42171,7 +42291,7 @@
       <c r="I372" s="3"/>
       <c r="J372" s="3"/>
       <c r="K372" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -42187,7 +42307,7 @@
       <c r="I373" s="3"/>
       <c r="J373" s="3"/>
       <c r="K373" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -42203,7 +42323,7 @@
       <c r="I374" s="3"/>
       <c r="J374" s="3"/>
       <c r="K374" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -42219,7 +42339,7 @@
       <c r="I375" s="3"/>
       <c r="J375" s="3"/>
       <c r="K375" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -42235,7 +42355,7 @@
       <c r="I376" s="3"/>
       <c r="J376" s="3"/>
       <c r="K376" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -42251,7 +42371,7 @@
       <c r="I377" s="3"/>
       <c r="J377" s="3"/>
       <c r="K377" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -42267,7 +42387,7 @@
       <c r="I378" s="3"/>
       <c r="J378" s="3"/>
       <c r="K378" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -42283,7 +42403,7 @@
       <c r="I379" s="3"/>
       <c r="J379" s="3"/>
       <c r="K379" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -42299,7 +42419,7 @@
       <c r="I380" s="3"/>
       <c r="J380" s="3"/>
       <c r="K380" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -42315,7 +42435,7 @@
       <c r="I381" s="3"/>
       <c r="J381" s="3"/>
       <c r="K381" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -42331,7 +42451,7 @@
       <c r="I382" s="3"/>
       <c r="J382" s="3"/>
       <c r="K382" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -42347,7 +42467,7 @@
       <c r="I383" s="3"/>
       <c r="J383" s="3"/>
       <c r="K383" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -42363,7 +42483,7 @@
       <c r="I384" s="3"/>
       <c r="J384" s="3"/>
       <c r="K384" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -42379,7 +42499,7 @@
       <c r="I385" s="3"/>
       <c r="J385" s="3"/>
       <c r="K385" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -42395,7 +42515,7 @@
       <c r="I386" s="3"/>
       <c r="J386" s="3"/>
       <c r="K386" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -42411,7 +42531,7 @@
       <c r="I387" s="3"/>
       <c r="J387" s="3"/>
       <c r="K387" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -42427,7 +42547,7 @@
       <c r="I388" s="3"/>
       <c r="J388" s="3"/>
       <c r="K388" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -42443,7 +42563,7 @@
       <c r="I389" s="3"/>
       <c r="J389" s="3"/>
       <c r="K389" s="4" t="str">
-        <f t="shared" ref="K389:K390" si="39">IF(COUNTA(B389:J389)=0,"",AVERAGE(B389:J389))</f>
+        <f t="shared" ref="K389:K390" si="40">IF(COUNTA(B389:J389)=0,"",AVERAGE(B389:J389))</f>
         <v/>
       </c>
     </row>
@@ -42459,7 +42579,7 @@
       <c r="I390" s="3"/>
       <c r="J390" s="3"/>
       <c r="K390" s="4" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
     </row>
@@ -42489,7 +42609,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="8" t="s">
         <v>38</v>
       </c>
       <c r="B1" s="7"/>
@@ -42505,7 +42625,7 @@
       <c r="L1" s="7"/>
     </row>
     <row r="2" spans="1:12" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="6" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="7"/>
@@ -45250,20 +45370,42 @@
       </c>
     </row>
     <row r="74" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A74" s="2"/>
-      <c r="B74" s="3"/>
-      <c r="C74" s="3"/>
-      <c r="D74" s="3"/>
-      <c r="E74" s="3"/>
-      <c r="F74" s="3"/>
-      <c r="G74" s="3"/>
-      <c r="H74" s="3"/>
-      <c r="I74" s="3"/>
-      <c r="J74" s="3"/>
-      <c r="K74" s="3"/>
-      <c r="L74" s="4" t="str">
-        <f t="shared" si="34"/>
-        <v/>
+      <c r="A74" s="2">
+        <v>46230</v>
+      </c>
+      <c r="B74" s="3">
+        <v>3.18</v>
+      </c>
+      <c r="C74" s="3">
+        <v>3.19</v>
+      </c>
+      <c r="D74" s="3">
+        <v>3.59</v>
+      </c>
+      <c r="E74" s="3">
+        <v>3.59</v>
+      </c>
+      <c r="F74" s="3">
+        <v>3.45</v>
+      </c>
+      <c r="G74" s="3">
+        <v>3.49</v>
+      </c>
+      <c r="H74" s="3">
+        <v>3.09</v>
+      </c>
+      <c r="I74" s="3">
+        <v>3.29</v>
+      </c>
+      <c r="J74" s="3">
+        <v>3.42</v>
+      </c>
+      <c r="K74" s="3">
+        <v>3.29</v>
+      </c>
+      <c r="L74" s="4">
+        <f t="shared" ref="L74" si="35">IF(COUNTA(B74:K74)=0,"",AVERAGE(B74:K74))</f>
+        <v>3.3579999999999997</v>
       </c>
     </row>
     <row r="75" spans="1:12" x14ac:dyDescent="0.25">
@@ -46265,7 +46407,7 @@
       <c r="J133" s="3"/>
       <c r="K133" s="3"/>
       <c r="L133" s="4" t="str">
-        <f t="shared" ref="L133:L196" si="35">IF(COUNTA(B133:K133)=0,"",AVERAGE(B133:K133))</f>
+        <f t="shared" ref="L133:L196" si="36">IF(COUNTA(B133:K133)=0,"",AVERAGE(B133:K133))</f>
         <v/>
       </c>
     </row>
@@ -46282,7 +46424,7 @@
       <c r="J134" s="3"/>
       <c r="K134" s="3"/>
       <c r="L134" s="4" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
@@ -46299,7 +46441,7 @@
       <c r="J135" s="3"/>
       <c r="K135" s="3"/>
       <c r="L135" s="4" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
@@ -46316,7 +46458,7 @@
       <c r="J136" s="3"/>
       <c r="K136" s="3"/>
       <c r="L136" s="4" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
@@ -46333,7 +46475,7 @@
       <c r="J137" s="3"/>
       <c r="K137" s="3"/>
       <c r="L137" s="4" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
@@ -46350,7 +46492,7 @@
       <c r="J138" s="3"/>
       <c r="K138" s="3"/>
       <c r="L138" s="4" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
@@ -46367,7 +46509,7 @@
       <c r="J139" s="3"/>
       <c r="K139" s="3"/>
       <c r="L139" s="4" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
@@ -46384,7 +46526,7 @@
       <c r="J140" s="3"/>
       <c r="K140" s="3"/>
       <c r="L140" s="4" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
@@ -46401,7 +46543,7 @@
       <c r="J141" s="3"/>
       <c r="K141" s="3"/>
       <c r="L141" s="4" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
@@ -46418,7 +46560,7 @@
       <c r="J142" s="3"/>
       <c r="K142" s="3"/>
       <c r="L142" s="4" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
@@ -46435,7 +46577,7 @@
       <c r="J143" s="3"/>
       <c r="K143" s="3"/>
       <c r="L143" s="4" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
@@ -46452,7 +46594,7 @@
       <c r="J144" s="3"/>
       <c r="K144" s="3"/>
       <c r="L144" s="4" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
@@ -46469,7 +46611,7 @@
       <c r="J145" s="3"/>
       <c r="K145" s="3"/>
       <c r="L145" s="4" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
@@ -46486,7 +46628,7 @@
       <c r="J146" s="3"/>
       <c r="K146" s="3"/>
       <c r="L146" s="4" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
@@ -46503,7 +46645,7 @@
       <c r="J147" s="3"/>
       <c r="K147" s="3"/>
       <c r="L147" s="4" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
@@ -46520,7 +46662,7 @@
       <c r="J148" s="3"/>
       <c r="K148" s="3"/>
       <c r="L148" s="4" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
@@ -46537,7 +46679,7 @@
       <c r="J149" s="3"/>
       <c r="K149" s="3"/>
       <c r="L149" s="4" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
@@ -46554,7 +46696,7 @@
       <c r="J150" s="3"/>
       <c r="K150" s="3"/>
       <c r="L150" s="4" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
@@ -46571,7 +46713,7 @@
       <c r="J151" s="3"/>
       <c r="K151" s="3"/>
       <c r="L151" s="4" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
@@ -46588,7 +46730,7 @@
       <c r="J152" s="3"/>
       <c r="K152" s="3"/>
       <c r="L152" s="4" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
@@ -46605,7 +46747,7 @@
       <c r="J153" s="3"/>
       <c r="K153" s="3"/>
       <c r="L153" s="4" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
@@ -46622,7 +46764,7 @@
       <c r="J154" s="3"/>
       <c r="K154" s="3"/>
       <c r="L154" s="4" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
@@ -46639,7 +46781,7 @@
       <c r="J155" s="3"/>
       <c r="K155" s="3"/>
       <c r="L155" s="4" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
@@ -46656,7 +46798,7 @@
       <c r="J156" s="3"/>
       <c r="K156" s="3"/>
       <c r="L156" s="4" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
@@ -46673,7 +46815,7 @@
       <c r="J157" s="3"/>
       <c r="K157" s="3"/>
       <c r="L157" s="4" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
@@ -46690,7 +46832,7 @@
       <c r="J158" s="3"/>
       <c r="K158" s="3"/>
       <c r="L158" s="4" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
@@ -46707,7 +46849,7 @@
       <c r="J159" s="3"/>
       <c r="K159" s="3"/>
       <c r="L159" s="4" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
@@ -46724,7 +46866,7 @@
       <c r="J160" s="3"/>
       <c r="K160" s="3"/>
       <c r="L160" s="4" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
@@ -46741,7 +46883,7 @@
       <c r="J161" s="3"/>
       <c r="K161" s="3"/>
       <c r="L161" s="4" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
@@ -46758,7 +46900,7 @@
       <c r="J162" s="3"/>
       <c r="K162" s="3"/>
       <c r="L162" s="4" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
@@ -46775,7 +46917,7 @@
       <c r="J163" s="3"/>
       <c r="K163" s="3"/>
       <c r="L163" s="4" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
@@ -46792,7 +46934,7 @@
       <c r="J164" s="3"/>
       <c r="K164" s="3"/>
       <c r="L164" s="4" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
@@ -46809,7 +46951,7 @@
       <c r="J165" s="3"/>
       <c r="K165" s="3"/>
       <c r="L165" s="4" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
@@ -46826,7 +46968,7 @@
       <c r="J166" s="3"/>
       <c r="K166" s="3"/>
       <c r="L166" s="4" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
@@ -46843,7 +46985,7 @@
       <c r="J167" s="3"/>
       <c r="K167" s="3"/>
       <c r="L167" s="4" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
@@ -46860,7 +47002,7 @@
       <c r="J168" s="3"/>
       <c r="K168" s="3"/>
       <c r="L168" s="4" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
@@ -46877,7 +47019,7 @@
       <c r="J169" s="3"/>
       <c r="K169" s="3"/>
       <c r="L169" s="4" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
@@ -46894,7 +47036,7 @@
       <c r="J170" s="3"/>
       <c r="K170" s="3"/>
       <c r="L170" s="4" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
@@ -46911,7 +47053,7 @@
       <c r="J171" s="3"/>
       <c r="K171" s="3"/>
       <c r="L171" s="4" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
@@ -46928,7 +47070,7 @@
       <c r="J172" s="3"/>
       <c r="K172" s="3"/>
       <c r="L172" s="4" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
@@ -46945,7 +47087,7 @@
       <c r="J173" s="3"/>
       <c r="K173" s="3"/>
       <c r="L173" s="4" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
@@ -46962,7 +47104,7 @@
       <c r="J174" s="3"/>
       <c r="K174" s="3"/>
       <c r="L174" s="4" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
@@ -46979,7 +47121,7 @@
       <c r="J175" s="3"/>
       <c r="K175" s="3"/>
       <c r="L175" s="4" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
@@ -46996,7 +47138,7 @@
       <c r="J176" s="3"/>
       <c r="K176" s="3"/>
       <c r="L176" s="4" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
@@ -47013,7 +47155,7 @@
       <c r="J177" s="3"/>
       <c r="K177" s="3"/>
       <c r="L177" s="4" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
@@ -47030,7 +47172,7 @@
       <c r="J178" s="3"/>
       <c r="K178" s="3"/>
       <c r="L178" s="4" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
@@ -47047,7 +47189,7 @@
       <c r="J179" s="3"/>
       <c r="K179" s="3"/>
       <c r="L179" s="4" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
@@ -47064,7 +47206,7 @@
       <c r="J180" s="3"/>
       <c r="K180" s="3"/>
       <c r="L180" s="4" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
@@ -47081,7 +47223,7 @@
       <c r="J181" s="3"/>
       <c r="K181" s="3"/>
       <c r="L181" s="4" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
@@ -47098,7 +47240,7 @@
       <c r="J182" s="3"/>
       <c r="K182" s="3"/>
       <c r="L182" s="4" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
@@ -47115,7 +47257,7 @@
       <c r="J183" s="3"/>
       <c r="K183" s="3"/>
       <c r="L183" s="4" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
@@ -47132,7 +47274,7 @@
       <c r="J184" s="3"/>
       <c r="K184" s="3"/>
       <c r="L184" s="4" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
@@ -47149,7 +47291,7 @@
       <c r="J185" s="3"/>
       <c r="K185" s="3"/>
       <c r="L185" s="4" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
@@ -47166,7 +47308,7 @@
       <c r="J186" s="3"/>
       <c r="K186" s="3"/>
       <c r="L186" s="4" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
@@ -47183,7 +47325,7 @@
       <c r="J187" s="3"/>
       <c r="K187" s="3"/>
       <c r="L187" s="4" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
@@ -47200,7 +47342,7 @@
       <c r="J188" s="3"/>
       <c r="K188" s="3"/>
       <c r="L188" s="4" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
@@ -47217,7 +47359,7 @@
       <c r="J189" s="3"/>
       <c r="K189" s="3"/>
       <c r="L189" s="4" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
@@ -47234,7 +47376,7 @@
       <c r="J190" s="3"/>
       <c r="K190" s="3"/>
       <c r="L190" s="4" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
@@ -47251,7 +47393,7 @@
       <c r="J191" s="3"/>
       <c r="K191" s="3"/>
       <c r="L191" s="4" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
@@ -47268,7 +47410,7 @@
       <c r="J192" s="3"/>
       <c r="K192" s="3"/>
       <c r="L192" s="4" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
@@ -47285,7 +47427,7 @@
       <c r="J193" s="3"/>
       <c r="K193" s="3"/>
       <c r="L193" s="4" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
@@ -47302,7 +47444,7 @@
       <c r="J194" s="3"/>
       <c r="K194" s="3"/>
       <c r="L194" s="4" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
@@ -47319,7 +47461,7 @@
       <c r="J195" s="3"/>
       <c r="K195" s="3"/>
       <c r="L195" s="4" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
@@ -47336,7 +47478,7 @@
       <c r="J196" s="3"/>
       <c r="K196" s="3"/>
       <c r="L196" s="4" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
@@ -47353,7 +47495,7 @@
       <c r="J197" s="3"/>
       <c r="K197" s="3"/>
       <c r="L197" s="4" t="str">
-        <f t="shared" ref="L197:L260" si="36">IF(COUNTA(B197:K197)=0,"",AVERAGE(B197:K197))</f>
+        <f t="shared" ref="L197:L260" si="37">IF(COUNTA(B197:K197)=0,"",AVERAGE(B197:K197))</f>
         <v/>
       </c>
     </row>
@@ -47370,7 +47512,7 @@
       <c r="J198" s="3"/>
       <c r="K198" s="3"/>
       <c r="L198" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -47387,7 +47529,7 @@
       <c r="J199" s="3"/>
       <c r="K199" s="3"/>
       <c r="L199" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -47404,7 +47546,7 @@
       <c r="J200" s="3"/>
       <c r="K200" s="3"/>
       <c r="L200" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -47421,7 +47563,7 @@
       <c r="J201" s="3"/>
       <c r="K201" s="3"/>
       <c r="L201" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -47438,7 +47580,7 @@
       <c r="J202" s="3"/>
       <c r="K202" s="3"/>
       <c r="L202" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -47455,7 +47597,7 @@
       <c r="J203" s="3"/>
       <c r="K203" s="3"/>
       <c r="L203" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -47472,7 +47614,7 @@
       <c r="J204" s="3"/>
       <c r="K204" s="3"/>
       <c r="L204" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -47489,7 +47631,7 @@
       <c r="J205" s="3"/>
       <c r="K205" s="3"/>
       <c r="L205" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -47506,7 +47648,7 @@
       <c r="J206" s="3"/>
       <c r="K206" s="3"/>
       <c r="L206" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -47523,7 +47665,7 @@
       <c r="J207" s="3"/>
       <c r="K207" s="3"/>
       <c r="L207" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -47540,7 +47682,7 @@
       <c r="J208" s="3"/>
       <c r="K208" s="3"/>
       <c r="L208" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -47557,7 +47699,7 @@
       <c r="J209" s="3"/>
       <c r="K209" s="3"/>
       <c r="L209" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -47574,7 +47716,7 @@
       <c r="J210" s="3"/>
       <c r="K210" s="3"/>
       <c r="L210" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -47591,7 +47733,7 @@
       <c r="J211" s="3"/>
       <c r="K211" s="3"/>
       <c r="L211" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -47608,7 +47750,7 @@
       <c r="J212" s="3"/>
       <c r="K212" s="3"/>
       <c r="L212" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -47625,7 +47767,7 @@
       <c r="J213" s="3"/>
       <c r="K213" s="3"/>
       <c r="L213" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -47642,7 +47784,7 @@
       <c r="J214" s="3"/>
       <c r="K214" s="3"/>
       <c r="L214" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -47659,7 +47801,7 @@
       <c r="J215" s="3"/>
       <c r="K215" s="3"/>
       <c r="L215" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -47676,7 +47818,7 @@
       <c r="J216" s="3"/>
       <c r="K216" s="3"/>
       <c r="L216" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -47693,7 +47835,7 @@
       <c r="J217" s="3"/>
       <c r="K217" s="3"/>
       <c r="L217" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -47710,7 +47852,7 @@
       <c r="J218" s="3"/>
       <c r="K218" s="3"/>
       <c r="L218" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -47727,7 +47869,7 @@
       <c r="J219" s="3"/>
       <c r="K219" s="3"/>
       <c r="L219" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -47744,7 +47886,7 @@
       <c r="J220" s="3"/>
       <c r="K220" s="3"/>
       <c r="L220" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -47761,7 +47903,7 @@
       <c r="J221" s="3"/>
       <c r="K221" s="3"/>
       <c r="L221" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -47778,7 +47920,7 @@
       <c r="J222" s="3"/>
       <c r="K222" s="3"/>
       <c r="L222" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -47795,7 +47937,7 @@
       <c r="J223" s="3"/>
       <c r="K223" s="3"/>
       <c r="L223" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -47812,7 +47954,7 @@
       <c r="J224" s="3"/>
       <c r="K224" s="3"/>
       <c r="L224" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -47829,7 +47971,7 @@
       <c r="J225" s="3"/>
       <c r="K225" s="3"/>
       <c r="L225" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -47846,7 +47988,7 @@
       <c r="J226" s="3"/>
       <c r="K226" s="3"/>
       <c r="L226" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -47863,7 +48005,7 @@
       <c r="J227" s="3"/>
       <c r="K227" s="3"/>
       <c r="L227" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -47880,7 +48022,7 @@
       <c r="J228" s="3"/>
       <c r="K228" s="3"/>
       <c r="L228" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -47897,7 +48039,7 @@
       <c r="J229" s="3"/>
       <c r="K229" s="3"/>
       <c r="L229" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -47914,7 +48056,7 @@
       <c r="J230" s="3"/>
       <c r="K230" s="3"/>
       <c r="L230" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -47931,7 +48073,7 @@
       <c r="J231" s="3"/>
       <c r="K231" s="3"/>
       <c r="L231" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -47948,7 +48090,7 @@
       <c r="J232" s="3"/>
       <c r="K232" s="3"/>
       <c r="L232" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -47965,7 +48107,7 @@
       <c r="J233" s="3"/>
       <c r="K233" s="3"/>
       <c r="L233" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -47982,7 +48124,7 @@
       <c r="J234" s="3"/>
       <c r="K234" s="3"/>
       <c r="L234" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -47999,7 +48141,7 @@
       <c r="J235" s="3"/>
       <c r="K235" s="3"/>
       <c r="L235" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -48016,7 +48158,7 @@
       <c r="J236" s="3"/>
       <c r="K236" s="3"/>
       <c r="L236" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -48033,7 +48175,7 @@
       <c r="J237" s="3"/>
       <c r="K237" s="3"/>
       <c r="L237" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -48050,7 +48192,7 @@
       <c r="J238" s="3"/>
       <c r="K238" s="3"/>
       <c r="L238" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -48067,7 +48209,7 @@
       <c r="J239" s="3"/>
       <c r="K239" s="3"/>
       <c r="L239" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -48084,7 +48226,7 @@
       <c r="J240" s="3"/>
       <c r="K240" s="3"/>
       <c r="L240" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -48101,7 +48243,7 @@
       <c r="J241" s="3"/>
       <c r="K241" s="3"/>
       <c r="L241" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -48118,7 +48260,7 @@
       <c r="J242" s="3"/>
       <c r="K242" s="3"/>
       <c r="L242" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -48135,7 +48277,7 @@
       <c r="J243" s="3"/>
       <c r="K243" s="3"/>
       <c r="L243" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -48152,7 +48294,7 @@
       <c r="J244" s="3"/>
       <c r="K244" s="3"/>
       <c r="L244" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -48169,7 +48311,7 @@
       <c r="J245" s="3"/>
       <c r="K245" s="3"/>
       <c r="L245" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -48186,7 +48328,7 @@
       <c r="J246" s="3"/>
       <c r="K246" s="3"/>
       <c r="L246" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -48203,7 +48345,7 @@
       <c r="J247" s="3"/>
       <c r="K247" s="3"/>
       <c r="L247" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -48220,7 +48362,7 @@
       <c r="J248" s="3"/>
       <c r="K248" s="3"/>
       <c r="L248" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -48237,7 +48379,7 @@
       <c r="J249" s="3"/>
       <c r="K249" s="3"/>
       <c r="L249" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -48254,7 +48396,7 @@
       <c r="J250" s="3"/>
       <c r="K250" s="3"/>
       <c r="L250" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -48271,7 +48413,7 @@
       <c r="J251" s="3"/>
       <c r="K251" s="3"/>
       <c r="L251" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -48288,7 +48430,7 @@
       <c r="J252" s="3"/>
       <c r="K252" s="3"/>
       <c r="L252" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -48305,7 +48447,7 @@
       <c r="J253" s="3"/>
       <c r="K253" s="3"/>
       <c r="L253" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -48322,7 +48464,7 @@
       <c r="J254" s="3"/>
       <c r="K254" s="3"/>
       <c r="L254" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -48339,7 +48481,7 @@
       <c r="J255" s="3"/>
       <c r="K255" s="3"/>
       <c r="L255" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -48356,7 +48498,7 @@
       <c r="J256" s="3"/>
       <c r="K256" s="3"/>
       <c r="L256" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -48373,7 +48515,7 @@
       <c r="J257" s="3"/>
       <c r="K257" s="3"/>
       <c r="L257" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -48390,7 +48532,7 @@
       <c r="J258" s="3"/>
       <c r="K258" s="3"/>
       <c r="L258" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -48407,7 +48549,7 @@
       <c r="J259" s="3"/>
       <c r="K259" s="3"/>
       <c r="L259" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -48424,7 +48566,7 @@
       <c r="J260" s="3"/>
       <c r="K260" s="3"/>
       <c r="L260" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -48441,7 +48583,7 @@
       <c r="J261" s="3"/>
       <c r="K261" s="3"/>
       <c r="L261" s="4" t="str">
-        <f t="shared" ref="L261:L324" si="37">IF(COUNTA(B261:K261)=0,"",AVERAGE(B261:K261))</f>
+        <f t="shared" ref="L261:L324" si="38">IF(COUNTA(B261:K261)=0,"",AVERAGE(B261:K261))</f>
         <v/>
       </c>
     </row>
@@ -48458,7 +48600,7 @@
       <c r="J262" s="3"/>
       <c r="K262" s="3"/>
       <c r="L262" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -48475,7 +48617,7 @@
       <c r="J263" s="3"/>
       <c r="K263" s="3"/>
       <c r="L263" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -48492,7 +48634,7 @@
       <c r="J264" s="3"/>
       <c r="K264" s="3"/>
       <c r="L264" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -48509,7 +48651,7 @@
       <c r="J265" s="3"/>
       <c r="K265" s="3"/>
       <c r="L265" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -48526,7 +48668,7 @@
       <c r="J266" s="3"/>
       <c r="K266" s="3"/>
       <c r="L266" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -48543,7 +48685,7 @@
       <c r="J267" s="3"/>
       <c r="K267" s="3"/>
       <c r="L267" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -48560,7 +48702,7 @@
       <c r="J268" s="3"/>
       <c r="K268" s="3"/>
       <c r="L268" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -48577,7 +48719,7 @@
       <c r="J269" s="3"/>
       <c r="K269" s="3"/>
       <c r="L269" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -48594,7 +48736,7 @@
       <c r="J270" s="3"/>
       <c r="K270" s="3"/>
       <c r="L270" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -48611,7 +48753,7 @@
       <c r="J271" s="3"/>
       <c r="K271" s="3"/>
       <c r="L271" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -48628,7 +48770,7 @@
       <c r="J272" s="3"/>
       <c r="K272" s="3"/>
       <c r="L272" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -48645,7 +48787,7 @@
       <c r="J273" s="3"/>
       <c r="K273" s="3"/>
       <c r="L273" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -48662,7 +48804,7 @@
       <c r="J274" s="3"/>
       <c r="K274" s="3"/>
       <c r="L274" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -48679,7 +48821,7 @@
       <c r="J275" s="3"/>
       <c r="K275" s="3"/>
       <c r="L275" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -48696,7 +48838,7 @@
       <c r="J276" s="3"/>
       <c r="K276" s="3"/>
       <c r="L276" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -48713,7 +48855,7 @@
       <c r="J277" s="3"/>
       <c r="K277" s="3"/>
       <c r="L277" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -48730,7 +48872,7 @@
       <c r="J278" s="3"/>
       <c r="K278" s="3"/>
       <c r="L278" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -48747,7 +48889,7 @@
       <c r="J279" s="3"/>
       <c r="K279" s="3"/>
       <c r="L279" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -48764,7 +48906,7 @@
       <c r="J280" s="3"/>
       <c r="K280" s="3"/>
       <c r="L280" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -48781,7 +48923,7 @@
       <c r="J281" s="3"/>
       <c r="K281" s="3"/>
       <c r="L281" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -48798,7 +48940,7 @@
       <c r="J282" s="3"/>
       <c r="K282" s="3"/>
       <c r="L282" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -48815,7 +48957,7 @@
       <c r="J283" s="3"/>
       <c r="K283" s="3"/>
       <c r="L283" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -48832,7 +48974,7 @@
       <c r="J284" s="3"/>
       <c r="K284" s="3"/>
       <c r="L284" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -48849,7 +48991,7 @@
       <c r="J285" s="3"/>
       <c r="K285" s="3"/>
       <c r="L285" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -48866,7 +49008,7 @@
       <c r="J286" s="3"/>
       <c r="K286" s="3"/>
       <c r="L286" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -48883,7 +49025,7 @@
       <c r="J287" s="3"/>
       <c r="K287" s="3"/>
       <c r="L287" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -48900,7 +49042,7 @@
       <c r="J288" s="3"/>
       <c r="K288" s="3"/>
       <c r="L288" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -48917,7 +49059,7 @@
       <c r="J289" s="3"/>
       <c r="K289" s="3"/>
       <c r="L289" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -48934,7 +49076,7 @@
       <c r="J290" s="3"/>
       <c r="K290" s="3"/>
       <c r="L290" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -48951,7 +49093,7 @@
       <c r="J291" s="3"/>
       <c r="K291" s="3"/>
       <c r="L291" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -48968,7 +49110,7 @@
       <c r="J292" s="3"/>
       <c r="K292" s="3"/>
       <c r="L292" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -48985,7 +49127,7 @@
       <c r="J293" s="3"/>
       <c r="K293" s="3"/>
       <c r="L293" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -49002,7 +49144,7 @@
       <c r="J294" s="3"/>
       <c r="K294" s="3"/>
       <c r="L294" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -49019,7 +49161,7 @@
       <c r="J295" s="3"/>
       <c r="K295" s="3"/>
       <c r="L295" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -49036,7 +49178,7 @@
       <c r="J296" s="3"/>
       <c r="K296" s="3"/>
       <c r="L296" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -49053,7 +49195,7 @@
       <c r="J297" s="3"/>
       <c r="K297" s="3"/>
       <c r="L297" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -49070,7 +49212,7 @@
       <c r="J298" s="3"/>
       <c r="K298" s="3"/>
       <c r="L298" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -49087,7 +49229,7 @@
       <c r="J299" s="3"/>
       <c r="K299" s="3"/>
       <c r="L299" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -49104,7 +49246,7 @@
       <c r="J300" s="3"/>
       <c r="K300" s="3"/>
       <c r="L300" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -49121,7 +49263,7 @@
       <c r="J301" s="3"/>
       <c r="K301" s="3"/>
       <c r="L301" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -49138,7 +49280,7 @@
       <c r="J302" s="3"/>
       <c r="K302" s="3"/>
       <c r="L302" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -49155,7 +49297,7 @@
       <c r="J303" s="3"/>
       <c r="K303" s="3"/>
       <c r="L303" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -49172,7 +49314,7 @@
       <c r="J304" s="3"/>
       <c r="K304" s="3"/>
       <c r="L304" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -49189,7 +49331,7 @@
       <c r="J305" s="3"/>
       <c r="K305" s="3"/>
       <c r="L305" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -49206,7 +49348,7 @@
       <c r="J306" s="3"/>
       <c r="K306" s="3"/>
       <c r="L306" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -49223,7 +49365,7 @@
       <c r="J307" s="3"/>
       <c r="K307" s="3"/>
       <c r="L307" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -49240,7 +49382,7 @@
       <c r="J308" s="3"/>
       <c r="K308" s="3"/>
       <c r="L308" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -49257,7 +49399,7 @@
       <c r="J309" s="3"/>
       <c r="K309" s="3"/>
       <c r="L309" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -49274,7 +49416,7 @@
       <c r="J310" s="3"/>
       <c r="K310" s="3"/>
       <c r="L310" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -49291,7 +49433,7 @@
       <c r="J311" s="3"/>
       <c r="K311" s="3"/>
       <c r="L311" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -49308,7 +49450,7 @@
       <c r="J312" s="3"/>
       <c r="K312" s="3"/>
       <c r="L312" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -49325,7 +49467,7 @@
       <c r="J313" s="3"/>
       <c r="K313" s="3"/>
       <c r="L313" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -49342,7 +49484,7 @@
       <c r="J314" s="3"/>
       <c r="K314" s="3"/>
       <c r="L314" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -49359,7 +49501,7 @@
       <c r="J315" s="3"/>
       <c r="K315" s="3"/>
       <c r="L315" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -49376,7 +49518,7 @@
       <c r="J316" s="3"/>
       <c r="K316" s="3"/>
       <c r="L316" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -49393,7 +49535,7 @@
       <c r="J317" s="3"/>
       <c r="K317" s="3"/>
       <c r="L317" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -49410,7 +49552,7 @@
       <c r="J318" s="3"/>
       <c r="K318" s="3"/>
       <c r="L318" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -49427,7 +49569,7 @@
       <c r="J319" s="3"/>
       <c r="K319" s="3"/>
       <c r="L319" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -49444,7 +49586,7 @@
       <c r="J320" s="3"/>
       <c r="K320" s="3"/>
       <c r="L320" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -49461,7 +49603,7 @@
       <c r="J321" s="3"/>
       <c r="K321" s="3"/>
       <c r="L321" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -49478,7 +49620,7 @@
       <c r="J322" s="3"/>
       <c r="K322" s="3"/>
       <c r="L322" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -49495,7 +49637,7 @@
       <c r="J323" s="3"/>
       <c r="K323" s="3"/>
       <c r="L323" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -49512,7 +49654,7 @@
       <c r="J324" s="3"/>
       <c r="K324" s="3"/>
       <c r="L324" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -49529,7 +49671,7 @@
       <c r="J325" s="3"/>
       <c r="K325" s="3"/>
       <c r="L325" s="4" t="str">
-        <f t="shared" ref="L325:L388" si="38">IF(COUNTA(B325:K325)=0,"",AVERAGE(B325:K325))</f>
+        <f t="shared" ref="L325:L388" si="39">IF(COUNTA(B325:K325)=0,"",AVERAGE(B325:K325))</f>
         <v/>
       </c>
     </row>
@@ -49546,7 +49688,7 @@
       <c r="J326" s="3"/>
       <c r="K326" s="3"/>
       <c r="L326" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -49563,7 +49705,7 @@
       <c r="J327" s="3"/>
       <c r="K327" s="3"/>
       <c r="L327" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -49580,7 +49722,7 @@
       <c r="J328" s="3"/>
       <c r="K328" s="3"/>
       <c r="L328" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -49597,7 +49739,7 @@
       <c r="J329" s="3"/>
       <c r="K329" s="3"/>
       <c r="L329" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -49614,7 +49756,7 @@
       <c r="J330" s="3"/>
       <c r="K330" s="3"/>
       <c r="L330" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -49631,7 +49773,7 @@
       <c r="J331" s="3"/>
       <c r="K331" s="3"/>
       <c r="L331" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -49648,7 +49790,7 @@
       <c r="J332" s="3"/>
       <c r="K332" s="3"/>
       <c r="L332" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -49665,7 +49807,7 @@
       <c r="J333" s="3"/>
       <c r="K333" s="3"/>
       <c r="L333" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -49682,7 +49824,7 @@
       <c r="J334" s="3"/>
       <c r="K334" s="3"/>
       <c r="L334" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -49699,7 +49841,7 @@
       <c r="J335" s="3"/>
       <c r="K335" s="3"/>
       <c r="L335" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -49716,7 +49858,7 @@
       <c r="J336" s="3"/>
       <c r="K336" s="3"/>
       <c r="L336" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -49733,7 +49875,7 @@
       <c r="J337" s="3"/>
       <c r="K337" s="3"/>
       <c r="L337" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -49750,7 +49892,7 @@
       <c r="J338" s="3"/>
       <c r="K338" s="3"/>
       <c r="L338" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -49767,7 +49909,7 @@
       <c r="J339" s="3"/>
       <c r="K339" s="3"/>
       <c r="L339" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -49784,7 +49926,7 @@
       <c r="J340" s="3"/>
       <c r="K340" s="3"/>
       <c r="L340" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -49801,7 +49943,7 @@
       <c r="J341" s="3"/>
       <c r="K341" s="3"/>
       <c r="L341" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -49818,7 +49960,7 @@
       <c r="J342" s="3"/>
       <c r="K342" s="3"/>
       <c r="L342" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -49835,7 +49977,7 @@
       <c r="J343" s="3"/>
       <c r="K343" s="3"/>
       <c r="L343" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -49852,7 +49994,7 @@
       <c r="J344" s="3"/>
       <c r="K344" s="3"/>
       <c r="L344" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -49869,7 +50011,7 @@
       <c r="J345" s="3"/>
       <c r="K345" s="3"/>
       <c r="L345" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -49886,7 +50028,7 @@
       <c r="J346" s="3"/>
       <c r="K346" s="3"/>
       <c r="L346" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -49903,7 +50045,7 @@
       <c r="J347" s="3"/>
       <c r="K347" s="3"/>
       <c r="L347" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -49920,7 +50062,7 @@
       <c r="J348" s="3"/>
       <c r="K348" s="3"/>
       <c r="L348" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -49937,7 +50079,7 @@
       <c r="J349" s="3"/>
       <c r="K349" s="3"/>
       <c r="L349" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -49954,7 +50096,7 @@
       <c r="J350" s="3"/>
       <c r="K350" s="3"/>
       <c r="L350" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -49971,7 +50113,7 @@
       <c r="J351" s="3"/>
       <c r="K351" s="3"/>
       <c r="L351" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -49988,7 +50130,7 @@
       <c r="J352" s="3"/>
       <c r="K352" s="3"/>
       <c r="L352" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -50005,7 +50147,7 @@
       <c r="J353" s="3"/>
       <c r="K353" s="3"/>
       <c r="L353" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -50022,7 +50164,7 @@
       <c r="J354" s="3"/>
       <c r="K354" s="3"/>
       <c r="L354" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -50039,7 +50181,7 @@
       <c r="J355" s="3"/>
       <c r="K355" s="3"/>
       <c r="L355" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -50056,7 +50198,7 @@
       <c r="J356" s="3"/>
       <c r="K356" s="3"/>
       <c r="L356" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -50073,7 +50215,7 @@
       <c r="J357" s="3"/>
       <c r="K357" s="3"/>
       <c r="L357" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -50090,7 +50232,7 @@
       <c r="J358" s="3"/>
       <c r="K358" s="3"/>
       <c r="L358" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -50107,7 +50249,7 @@
       <c r="J359" s="3"/>
       <c r="K359" s="3"/>
       <c r="L359" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -50124,7 +50266,7 @@
       <c r="J360" s="3"/>
       <c r="K360" s="3"/>
       <c r="L360" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -50141,7 +50283,7 @@
       <c r="J361" s="3"/>
       <c r="K361" s="3"/>
       <c r="L361" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -50158,7 +50300,7 @@
       <c r="J362" s="3"/>
       <c r="K362" s="3"/>
       <c r="L362" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -50175,7 +50317,7 @@
       <c r="J363" s="3"/>
       <c r="K363" s="3"/>
       <c r="L363" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -50192,7 +50334,7 @@
       <c r="J364" s="3"/>
       <c r="K364" s="3"/>
       <c r="L364" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -50209,7 +50351,7 @@
       <c r="J365" s="3"/>
       <c r="K365" s="3"/>
       <c r="L365" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -50226,7 +50368,7 @@
       <c r="J366" s="3"/>
       <c r="K366" s="3"/>
       <c r="L366" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -50243,7 +50385,7 @@
       <c r="J367" s="3"/>
       <c r="K367" s="3"/>
       <c r="L367" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -50260,7 +50402,7 @@
       <c r="J368" s="3"/>
       <c r="K368" s="3"/>
       <c r="L368" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -50277,7 +50419,7 @@
       <c r="J369" s="3"/>
       <c r="K369" s="3"/>
       <c r="L369" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -50294,7 +50436,7 @@
       <c r="J370" s="3"/>
       <c r="K370" s="3"/>
       <c r="L370" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -50311,7 +50453,7 @@
       <c r="J371" s="3"/>
       <c r="K371" s="3"/>
       <c r="L371" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -50328,7 +50470,7 @@
       <c r="J372" s="3"/>
       <c r="K372" s="3"/>
       <c r="L372" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -50345,7 +50487,7 @@
       <c r="J373" s="3"/>
       <c r="K373" s="3"/>
       <c r="L373" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -50362,7 +50504,7 @@
       <c r="J374" s="3"/>
       <c r="K374" s="3"/>
       <c r="L374" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -50379,7 +50521,7 @@
       <c r="J375" s="3"/>
       <c r="K375" s="3"/>
       <c r="L375" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -50396,7 +50538,7 @@
       <c r="J376" s="3"/>
       <c r="K376" s="3"/>
       <c r="L376" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -50413,7 +50555,7 @@
       <c r="J377" s="3"/>
       <c r="K377" s="3"/>
       <c r="L377" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -50430,7 +50572,7 @@
       <c r="J378" s="3"/>
       <c r="K378" s="3"/>
       <c r="L378" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -50447,7 +50589,7 @@
       <c r="J379" s="3"/>
       <c r="K379" s="3"/>
       <c r="L379" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -50464,7 +50606,7 @@
       <c r="J380" s="3"/>
       <c r="K380" s="3"/>
       <c r="L380" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -50481,7 +50623,7 @@
       <c r="J381" s="3"/>
       <c r="K381" s="3"/>
       <c r="L381" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -50498,7 +50640,7 @@
       <c r="J382" s="3"/>
       <c r="K382" s="3"/>
       <c r="L382" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -50515,7 +50657,7 @@
       <c r="J383" s="3"/>
       <c r="K383" s="3"/>
       <c r="L383" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -50532,7 +50674,7 @@
       <c r="J384" s="3"/>
       <c r="K384" s="3"/>
       <c r="L384" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -50549,7 +50691,7 @@
       <c r="J385" s="3"/>
       <c r="K385" s="3"/>
       <c r="L385" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -50566,7 +50708,7 @@
       <c r="J386" s="3"/>
       <c r="K386" s="3"/>
       <c r="L386" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -50583,7 +50725,7 @@
       <c r="J387" s="3"/>
       <c r="K387" s="3"/>
       <c r="L387" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -50600,7 +50742,7 @@
       <c r="J388" s="3"/>
       <c r="K388" s="3"/>
       <c r="L388" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -50617,7 +50759,7 @@
       <c r="J389" s="3"/>
       <c r="K389" s="3"/>
       <c r="L389" s="4" t="str">
-        <f t="shared" ref="L389:L390" si="39">IF(COUNTA(B389:K389)=0,"",AVERAGE(B389:K389))</f>
+        <f t="shared" ref="L389:L390" si="40">IF(COUNTA(B389:K389)=0,"",AVERAGE(B389:K389))</f>
         <v/>
       </c>
     </row>
@@ -50634,7 +50776,7 @@
       <c r="J390" s="3"/>
       <c r="K390" s="3"/>
       <c r="L390" s="4" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
     </row>

--- a/app/mevduat-kredi-faizleri/data/hoca-ile-borsa-faiz-takip-sablonu-guncel.xlsx
+++ b/app/mevduat-kredi-faizleri/data/hoca-ile-borsa-faiz-takip-sablonu-guncel.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projeler\hoca-ile-borsa\app\mevduat-kredi-faizleri\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCBE0F7C-DF6A-4280-8995-8AF5CF4E27D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4E29BE7-D9B7-4175-9E3E-96C973A2BF84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Mevduat" sheetId="1" r:id="rId1"/>
@@ -553,6 +553,9 @@
                 <c:pt idx="69">
                   <c:v>46230</c:v>
                 </c:pt>
+                <c:pt idx="70">
+                  <c:v>46231</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -773,7 +776,7 @@
                   <c:v>43.508695652173913</c:v>
                 </c:pt>
                 <c:pt idx="70">
-                  <c:v>0</c:v>
+                  <c:v>43.508695652173913</c:v>
                 </c:pt>
                 <c:pt idx="71">
                   <c:v>0</c:v>
@@ -2089,6 +2092,9 @@
                 <c:pt idx="69">
                   <c:v>46230</c:v>
                 </c:pt>
+                <c:pt idx="70">
+                  <c:v>46231</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2309,7 +2315,7 @@
                   <c:v>3.5600000000000009</c:v>
                 </c:pt>
                 <c:pt idx="70">
-                  <c:v>0</c:v>
+                  <c:v>3.5600000000000009</c:v>
                 </c:pt>
                 <c:pt idx="71">
                   <c:v>0</c:v>
@@ -3625,6 +3631,9 @@
                 <c:pt idx="69">
                   <c:v>46230</c:v>
                 </c:pt>
+                <c:pt idx="70">
+                  <c:v>46231</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3845,7 +3854,7 @@
                   <c:v>2.9155555555555557</c:v>
                 </c:pt>
                 <c:pt idx="70">
-                  <c:v>0</c:v>
+                  <c:v>2.9155555555555557</c:v>
                 </c:pt>
                 <c:pt idx="71">
                   <c:v>0</c:v>
@@ -5161,6 +5170,9 @@
                 <c:pt idx="69">
                   <c:v>46230</c:v>
                 </c:pt>
+                <c:pt idx="70">
+                  <c:v>46231</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -5381,7 +5393,7 @@
                   <c:v>3.3579999999999997</c:v>
                 </c:pt>
                 <c:pt idx="70">
-                  <c:v>0</c:v>
+                  <c:v>3.3579999999999997</c:v>
                 </c:pt>
                 <c:pt idx="71">
                   <c:v>0</c:v>
@@ -12462,33 +12474,81 @@
       </c>
     </row>
     <row r="75" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A75" s="2"/>
-      <c r="B75" s="3"/>
-      <c r="C75" s="3"/>
-      <c r="D75" s="3"/>
-      <c r="E75" s="3"/>
-      <c r="F75" s="3"/>
-      <c r="G75" s="3"/>
-      <c r="H75" s="3"/>
-      <c r="I75" s="3"/>
-      <c r="J75" s="3"/>
-      <c r="K75" s="3"/>
-      <c r="L75" s="3"/>
-      <c r="M75" s="3"/>
-      <c r="N75" s="3"/>
-      <c r="O75" s="3"/>
-      <c r="P75" s="3"/>
-      <c r="Q75" s="3"/>
-      <c r="R75" s="3"/>
-      <c r="S75" s="3"/>
-      <c r="T75" s="3"/>
-      <c r="U75" s="3"/>
-      <c r="V75" s="3"/>
-      <c r="W75" s="3"/>
-      <c r="X75" s="3"/>
-      <c r="Y75" s="4" t="str">
-        <f t="shared" si="26"/>
-        <v/>
+      <c r="A75" s="2">
+        <v>46231</v>
+      </c>
+      <c r="B75" s="3">
+        <v>41.5</v>
+      </c>
+      <c r="C75" s="3">
+        <v>46</v>
+      </c>
+      <c r="D75" s="3">
+        <v>46</v>
+      </c>
+      <c r="E75" s="3">
+        <v>45</v>
+      </c>
+      <c r="F75" s="3">
+        <v>45</v>
+      </c>
+      <c r="G75" s="3">
+        <v>40</v>
+      </c>
+      <c r="H75" s="3">
+        <v>47</v>
+      </c>
+      <c r="I75" s="3">
+        <v>41</v>
+      </c>
+      <c r="J75" s="3">
+        <v>44</v>
+      </c>
+      <c r="K75" s="3">
+        <v>41</v>
+      </c>
+      <c r="L75" s="3">
+        <v>36</v>
+      </c>
+      <c r="M75" s="3">
+        <v>45</v>
+      </c>
+      <c r="N75" s="3">
+        <v>45</v>
+      </c>
+      <c r="O75" s="3">
+        <v>41.95</v>
+      </c>
+      <c r="P75" s="3">
+        <v>40</v>
+      </c>
+      <c r="Q75" s="3">
+        <v>46</v>
+      </c>
+      <c r="R75" s="3">
+        <v>46</v>
+      </c>
+      <c r="S75" s="3">
+        <v>45</v>
+      </c>
+      <c r="T75" s="3">
+        <v>43.5</v>
+      </c>
+      <c r="U75" s="3">
+        <v>43.5</v>
+      </c>
+      <c r="V75" s="3">
+        <v>40</v>
+      </c>
+      <c r="W75" s="3">
+        <v>47</v>
+      </c>
+      <c r="X75" s="3">
+        <v>45.25</v>
+      </c>
+      <c r="Y75" s="4">
+        <f t="shared" ref="Y75" si="28">IF(COUNTA(B75:X75)=0,"",AVERAGE(B75:X75))</f>
+        <v>43.508695652173913</v>
       </c>
     </row>
     <row r="76" spans="1:25" x14ac:dyDescent="0.25">
@@ -14227,7 +14287,7 @@
       <c r="W133" s="3"/>
       <c r="X133" s="3"/>
       <c r="Y133" s="4" t="str">
-        <f t="shared" ref="Y133:Y196" si="28">IF(COUNTA(B133:X133)=0,"",AVERAGE(B133:X133))</f>
+        <f t="shared" ref="Y133:Y196" si="29">IF(COUNTA(B133:X133)=0,"",AVERAGE(B133:X133))</f>
         <v/>
       </c>
     </row>
@@ -14257,7 +14317,7 @@
       <c r="W134" s="3"/>
       <c r="X134" s="3"/>
       <c r="Y134" s="4" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
     </row>
@@ -14287,7 +14347,7 @@
       <c r="W135" s="3"/>
       <c r="X135" s="3"/>
       <c r="Y135" s="4" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
     </row>
@@ -14317,7 +14377,7 @@
       <c r="W136" s="3"/>
       <c r="X136" s="3"/>
       <c r="Y136" s="4" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
     </row>
@@ -14347,7 +14407,7 @@
       <c r="W137" s="3"/>
       <c r="X137" s="3"/>
       <c r="Y137" s="4" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
     </row>
@@ -14377,7 +14437,7 @@
       <c r="W138" s="3"/>
       <c r="X138" s="3"/>
       <c r="Y138" s="4" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
     </row>
@@ -14407,7 +14467,7 @@
       <c r="W139" s="3"/>
       <c r="X139" s="3"/>
       <c r="Y139" s="4" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
     </row>
@@ -14437,7 +14497,7 @@
       <c r="W140" s="3"/>
       <c r="X140" s="3"/>
       <c r="Y140" s="4" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
     </row>
@@ -14467,7 +14527,7 @@
       <c r="W141" s="3"/>
       <c r="X141" s="3"/>
       <c r="Y141" s="4" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
     </row>
@@ -14497,7 +14557,7 @@
       <c r="W142" s="3"/>
       <c r="X142" s="3"/>
       <c r="Y142" s="4" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
     </row>
@@ -14527,7 +14587,7 @@
       <c r="W143" s="3"/>
       <c r="X143" s="3"/>
       <c r="Y143" s="4" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
     </row>
@@ -14557,7 +14617,7 @@
       <c r="W144" s="3"/>
       <c r="X144" s="3"/>
       <c r="Y144" s="4" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
     </row>
@@ -14587,7 +14647,7 @@
       <c r="W145" s="3"/>
       <c r="X145" s="3"/>
       <c r="Y145" s="4" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
     </row>
@@ -14617,7 +14677,7 @@
       <c r="W146" s="3"/>
       <c r="X146" s="3"/>
       <c r="Y146" s="4" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
     </row>
@@ -14647,7 +14707,7 @@
       <c r="W147" s="3"/>
       <c r="X147" s="3"/>
       <c r="Y147" s="4" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
     </row>
@@ -14677,7 +14737,7 @@
       <c r="W148" s="3"/>
       <c r="X148" s="3"/>
       <c r="Y148" s="4" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
     </row>
@@ -14707,7 +14767,7 @@
       <c r="W149" s="3"/>
       <c r="X149" s="3"/>
       <c r="Y149" s="4" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
     </row>
@@ -14737,7 +14797,7 @@
       <c r="W150" s="3"/>
       <c r="X150" s="3"/>
       <c r="Y150" s="4" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
     </row>
@@ -14767,7 +14827,7 @@
       <c r="W151" s="3"/>
       <c r="X151" s="3"/>
       <c r="Y151" s="4" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
     </row>
@@ -14797,7 +14857,7 @@
       <c r="W152" s="3"/>
       <c r="X152" s="3"/>
       <c r="Y152" s="4" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
     </row>
@@ -14827,7 +14887,7 @@
       <c r="W153" s="3"/>
       <c r="X153" s="3"/>
       <c r="Y153" s="4" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
     </row>
@@ -14857,7 +14917,7 @@
       <c r="W154" s="3"/>
       <c r="X154" s="3"/>
       <c r="Y154" s="4" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
     </row>
@@ -14887,7 +14947,7 @@
       <c r="W155" s="3"/>
       <c r="X155" s="3"/>
       <c r="Y155" s="4" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
     </row>
@@ -14917,7 +14977,7 @@
       <c r="W156" s="3"/>
       <c r="X156" s="3"/>
       <c r="Y156" s="4" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
     </row>
@@ -14947,7 +15007,7 @@
       <c r="W157" s="3"/>
       <c r="X157" s="3"/>
       <c r="Y157" s="4" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
     </row>
@@ -14977,7 +15037,7 @@
       <c r="W158" s="3"/>
       <c r="X158" s="3"/>
       <c r="Y158" s="4" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
     </row>
@@ -15007,7 +15067,7 @@
       <c r="W159" s="3"/>
       <c r="X159" s="3"/>
       <c r="Y159" s="4" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
     </row>
@@ -15037,7 +15097,7 @@
       <c r="W160" s="3"/>
       <c r="X160" s="3"/>
       <c r="Y160" s="4" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
     </row>
@@ -15067,7 +15127,7 @@
       <c r="W161" s="3"/>
       <c r="X161" s="3"/>
       <c r="Y161" s="4" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
     </row>
@@ -15097,7 +15157,7 @@
       <c r="W162" s="3"/>
       <c r="X162" s="3"/>
       <c r="Y162" s="4" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
     </row>
@@ -15127,7 +15187,7 @@
       <c r="W163" s="3"/>
       <c r="X163" s="3"/>
       <c r="Y163" s="4" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
     </row>
@@ -15157,7 +15217,7 @@
       <c r="W164" s="3"/>
       <c r="X164" s="3"/>
       <c r="Y164" s="4" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
     </row>
@@ -15187,7 +15247,7 @@
       <c r="W165" s="3"/>
       <c r="X165" s="3"/>
       <c r="Y165" s="4" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
     </row>
@@ -15217,7 +15277,7 @@
       <c r="W166" s="3"/>
       <c r="X166" s="3"/>
       <c r="Y166" s="4" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
     </row>
@@ -15247,7 +15307,7 @@
       <c r="W167" s="3"/>
       <c r="X167" s="3"/>
       <c r="Y167" s="4" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
     </row>
@@ -15277,7 +15337,7 @@
       <c r="W168" s="3"/>
       <c r="X168" s="3"/>
       <c r="Y168" s="4" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
     </row>
@@ -15307,7 +15367,7 @@
       <c r="W169" s="3"/>
       <c r="X169" s="3"/>
       <c r="Y169" s="4" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
     </row>
@@ -15337,7 +15397,7 @@
       <c r="W170" s="3"/>
       <c r="X170" s="3"/>
       <c r="Y170" s="4" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
     </row>
@@ -15367,7 +15427,7 @@
       <c r="W171" s="3"/>
       <c r="X171" s="3"/>
       <c r="Y171" s="4" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
     </row>
@@ -15397,7 +15457,7 @@
       <c r="W172" s="3"/>
       <c r="X172" s="3"/>
       <c r="Y172" s="4" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
     </row>
@@ -15427,7 +15487,7 @@
       <c r="W173" s="3"/>
       <c r="X173" s="3"/>
       <c r="Y173" s="4" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
     </row>
@@ -15457,7 +15517,7 @@
       <c r="W174" s="3"/>
       <c r="X174" s="3"/>
       <c r="Y174" s="4" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
     </row>
@@ -15487,7 +15547,7 @@
       <c r="W175" s="3"/>
       <c r="X175" s="3"/>
       <c r="Y175" s="4" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
     </row>
@@ -15517,7 +15577,7 @@
       <c r="W176" s="3"/>
       <c r="X176" s="3"/>
       <c r="Y176" s="4" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
     </row>
@@ -15547,7 +15607,7 @@
       <c r="W177" s="3"/>
       <c r="X177" s="3"/>
       <c r="Y177" s="4" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
     </row>
@@ -15577,7 +15637,7 @@
       <c r="W178" s="3"/>
       <c r="X178" s="3"/>
       <c r="Y178" s="4" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
     </row>
@@ -15607,7 +15667,7 @@
       <c r="W179" s="3"/>
       <c r="X179" s="3"/>
       <c r="Y179" s="4" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
     </row>
@@ -15637,7 +15697,7 @@
       <c r="W180" s="3"/>
       <c r="X180" s="3"/>
       <c r="Y180" s="4" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
     </row>
@@ -15667,7 +15727,7 @@
       <c r="W181" s="3"/>
       <c r="X181" s="3"/>
       <c r="Y181" s="4" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
     </row>
@@ -15697,7 +15757,7 @@
       <c r="W182" s="3"/>
       <c r="X182" s="3"/>
       <c r="Y182" s="4" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
     </row>
@@ -15727,7 +15787,7 @@
       <c r="W183" s="3"/>
       <c r="X183" s="3"/>
       <c r="Y183" s="4" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
     </row>
@@ -15757,7 +15817,7 @@
       <c r="W184" s="3"/>
       <c r="X184" s="3"/>
       <c r="Y184" s="4" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
     </row>
@@ -15787,7 +15847,7 @@
       <c r="W185" s="3"/>
       <c r="X185" s="3"/>
       <c r="Y185" s="4" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
     </row>
@@ -15817,7 +15877,7 @@
       <c r="W186" s="3"/>
       <c r="X186" s="3"/>
       <c r="Y186" s="4" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
     </row>
@@ -15847,7 +15907,7 @@
       <c r="W187" s="3"/>
       <c r="X187" s="3"/>
       <c r="Y187" s="4" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
     </row>
@@ -15877,7 +15937,7 @@
       <c r="W188" s="3"/>
       <c r="X188" s="3"/>
       <c r="Y188" s="4" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
     </row>
@@ -15907,7 +15967,7 @@
       <c r="W189" s="3"/>
       <c r="X189" s="3"/>
       <c r="Y189" s="4" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
     </row>
@@ -15937,7 +15997,7 @@
       <c r="W190" s="3"/>
       <c r="X190" s="3"/>
       <c r="Y190" s="4" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
     </row>
@@ -15967,7 +16027,7 @@
       <c r="W191" s="3"/>
       <c r="X191" s="3"/>
       <c r="Y191" s="4" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
     </row>
@@ -15997,7 +16057,7 @@
       <c r="W192" s="3"/>
       <c r="X192" s="3"/>
       <c r="Y192" s="4" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
     </row>
@@ -16027,7 +16087,7 @@
       <c r="W193" s="3"/>
       <c r="X193" s="3"/>
       <c r="Y193" s="4" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
     </row>
@@ -16057,7 +16117,7 @@
       <c r="W194" s="3"/>
       <c r="X194" s="3"/>
       <c r="Y194" s="4" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
     </row>
@@ -16087,7 +16147,7 @@
       <c r="W195" s="3"/>
       <c r="X195" s="3"/>
       <c r="Y195" s="4" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
     </row>
@@ -16117,7 +16177,7 @@
       <c r="W196" s="3"/>
       <c r="X196" s="3"/>
       <c r="Y196" s="4" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
     </row>
@@ -16147,7 +16207,7 @@
       <c r="W197" s="3"/>
       <c r="X197" s="3"/>
       <c r="Y197" s="4" t="str">
-        <f t="shared" ref="Y197:Y260" si="29">IF(COUNTA(B197:X197)=0,"",AVERAGE(B197:X197))</f>
+        <f t="shared" ref="Y197:Y260" si="30">IF(COUNTA(B197:X197)=0,"",AVERAGE(B197:X197))</f>
         <v/>
       </c>
     </row>
@@ -16177,7 +16237,7 @@
       <c r="W198" s="3"/>
       <c r="X198" s="3"/>
       <c r="Y198" s="4" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
     </row>
@@ -16207,7 +16267,7 @@
       <c r="W199" s="3"/>
       <c r="X199" s="3"/>
       <c r="Y199" s="4" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
     </row>
@@ -16237,7 +16297,7 @@
       <c r="W200" s="3"/>
       <c r="X200" s="3"/>
       <c r="Y200" s="4" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
     </row>
@@ -16267,7 +16327,7 @@
       <c r="W201" s="3"/>
       <c r="X201" s="3"/>
       <c r="Y201" s="4" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
     </row>
@@ -16297,7 +16357,7 @@
       <c r="W202" s="3"/>
       <c r="X202" s="3"/>
       <c r="Y202" s="4" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
     </row>
@@ -16327,7 +16387,7 @@
       <c r="W203" s="3"/>
       <c r="X203" s="3"/>
       <c r="Y203" s="4" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
     </row>
@@ -16357,7 +16417,7 @@
       <c r="W204" s="3"/>
       <c r="X204" s="3"/>
       <c r="Y204" s="4" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
     </row>
@@ -16387,7 +16447,7 @@
       <c r="W205" s="3"/>
       <c r="X205" s="3"/>
       <c r="Y205" s="4" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
     </row>
@@ -16417,7 +16477,7 @@
       <c r="W206" s="3"/>
       <c r="X206" s="3"/>
       <c r="Y206" s="4" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
     </row>
@@ -16447,7 +16507,7 @@
       <c r="W207" s="3"/>
       <c r="X207" s="3"/>
       <c r="Y207" s="4" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
     </row>
@@ -16477,7 +16537,7 @@
       <c r="W208" s="3"/>
       <c r="X208" s="3"/>
       <c r="Y208" s="4" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
     </row>
@@ -16507,7 +16567,7 @@
       <c r="W209" s="3"/>
       <c r="X209" s="3"/>
       <c r="Y209" s="4" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
     </row>
@@ -16537,7 +16597,7 @@
       <c r="W210" s="3"/>
       <c r="X210" s="3"/>
       <c r="Y210" s="4" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
     </row>
@@ -16567,7 +16627,7 @@
       <c r="W211" s="3"/>
       <c r="X211" s="3"/>
       <c r="Y211" s="4" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
     </row>
@@ -16597,7 +16657,7 @@
       <c r="W212" s="3"/>
       <c r="X212" s="3"/>
       <c r="Y212" s="4" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
     </row>
@@ -16627,7 +16687,7 @@
       <c r="W213" s="3"/>
       <c r="X213" s="3"/>
       <c r="Y213" s="4" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
     </row>
@@ -16657,7 +16717,7 @@
       <c r="W214" s="3"/>
       <c r="X214" s="3"/>
       <c r="Y214" s="4" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
     </row>
@@ -16687,7 +16747,7 @@
       <c r="W215" s="3"/>
       <c r="X215" s="3"/>
       <c r="Y215" s="4" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
     </row>
@@ -16717,7 +16777,7 @@
       <c r="W216" s="3"/>
       <c r="X216" s="3"/>
       <c r="Y216" s="4" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
     </row>
@@ -16747,7 +16807,7 @@
       <c r="W217" s="3"/>
       <c r="X217" s="3"/>
       <c r="Y217" s="4" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
     </row>
@@ -16777,7 +16837,7 @@
       <c r="W218" s="3"/>
       <c r="X218" s="3"/>
       <c r="Y218" s="4" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
     </row>
@@ -16807,7 +16867,7 @@
       <c r="W219" s="3"/>
       <c r="X219" s="3"/>
       <c r="Y219" s="4" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
     </row>
@@ -16837,7 +16897,7 @@
       <c r="W220" s="3"/>
       <c r="X220" s="3"/>
       <c r="Y220" s="4" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
     </row>
@@ -16867,7 +16927,7 @@
       <c r="W221" s="3"/>
       <c r="X221" s="3"/>
       <c r="Y221" s="4" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
     </row>
@@ -16897,7 +16957,7 @@
       <c r="W222" s="3"/>
       <c r="X222" s="3"/>
       <c r="Y222" s="4" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
     </row>
@@ -16927,7 +16987,7 @@
       <c r="W223" s="3"/>
       <c r="X223" s="3"/>
       <c r="Y223" s="4" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
     </row>
@@ -16957,7 +17017,7 @@
       <c r="W224" s="3"/>
       <c r="X224" s="3"/>
       <c r="Y224" s="4" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
     </row>
@@ -16987,7 +17047,7 @@
       <c r="W225" s="3"/>
       <c r="X225" s="3"/>
       <c r="Y225" s="4" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
     </row>
@@ -17017,7 +17077,7 @@
       <c r="W226" s="3"/>
       <c r="X226" s="3"/>
       <c r="Y226" s="4" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
     </row>
@@ -17047,7 +17107,7 @@
       <c r="W227" s="3"/>
       <c r="X227" s="3"/>
       <c r="Y227" s="4" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
     </row>
@@ -17077,7 +17137,7 @@
       <c r="W228" s="3"/>
       <c r="X228" s="3"/>
       <c r="Y228" s="4" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
     </row>
@@ -17107,7 +17167,7 @@
       <c r="W229" s="3"/>
       <c r="X229" s="3"/>
       <c r="Y229" s="4" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
     </row>
@@ -17137,7 +17197,7 @@
       <c r="W230" s="3"/>
       <c r="X230" s="3"/>
       <c r="Y230" s="4" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
     </row>
@@ -17167,7 +17227,7 @@
       <c r="W231" s="3"/>
       <c r="X231" s="3"/>
       <c r="Y231" s="4" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
     </row>
@@ -17197,7 +17257,7 @@
       <c r="W232" s="3"/>
       <c r="X232" s="3"/>
       <c r="Y232" s="4" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
     </row>
@@ -17227,7 +17287,7 @@
       <c r="W233" s="3"/>
       <c r="X233" s="3"/>
       <c r="Y233" s="4" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
     </row>
@@ -17257,7 +17317,7 @@
       <c r="W234" s="3"/>
       <c r="X234" s="3"/>
       <c r="Y234" s="4" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
     </row>
@@ -17287,7 +17347,7 @@
       <c r="W235" s="3"/>
       <c r="X235" s="3"/>
       <c r="Y235" s="4" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
     </row>
@@ -17317,7 +17377,7 @@
       <c r="W236" s="3"/>
       <c r="X236" s="3"/>
       <c r="Y236" s="4" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
     </row>
@@ -17347,7 +17407,7 @@
       <c r="W237" s="3"/>
       <c r="X237" s="3"/>
       <c r="Y237" s="4" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
     </row>
@@ -17377,7 +17437,7 @@
       <c r="W238" s="3"/>
       <c r="X238" s="3"/>
       <c r="Y238" s="4" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
     </row>
@@ -17407,7 +17467,7 @@
       <c r="W239" s="3"/>
       <c r="X239" s="3"/>
       <c r="Y239" s="4" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
     </row>
@@ -17437,7 +17497,7 @@
       <c r="W240" s="3"/>
       <c r="X240" s="3"/>
       <c r="Y240" s="4" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
     </row>
@@ -17467,7 +17527,7 @@
       <c r="W241" s="3"/>
       <c r="X241" s="3"/>
       <c r="Y241" s="4" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
     </row>
@@ -17497,7 +17557,7 @@
       <c r="W242" s="3"/>
       <c r="X242" s="3"/>
       <c r="Y242" s="4" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
     </row>
@@ -17527,7 +17587,7 @@
       <c r="W243" s="3"/>
       <c r="X243" s="3"/>
       <c r="Y243" s="4" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
     </row>
@@ -17557,7 +17617,7 @@
       <c r="W244" s="3"/>
       <c r="X244" s="3"/>
       <c r="Y244" s="4" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
     </row>
@@ -17587,7 +17647,7 @@
       <c r="W245" s="3"/>
       <c r="X245" s="3"/>
       <c r="Y245" s="4" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
     </row>
@@ -17617,7 +17677,7 @@
       <c r="W246" s="3"/>
       <c r="X246" s="3"/>
       <c r="Y246" s="4" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
     </row>
@@ -17647,7 +17707,7 @@
       <c r="W247" s="3"/>
       <c r="X247" s="3"/>
       <c r="Y247" s="4" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
     </row>
@@ -17677,7 +17737,7 @@
       <c r="W248" s="3"/>
       <c r="X248" s="3"/>
       <c r="Y248" s="4" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
     </row>
@@ -17707,7 +17767,7 @@
       <c r="W249" s="3"/>
       <c r="X249" s="3"/>
       <c r="Y249" s="4" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
     </row>
@@ -17737,7 +17797,7 @@
       <c r="W250" s="3"/>
       <c r="X250" s="3"/>
       <c r="Y250" s="4" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
     </row>
@@ -17767,7 +17827,7 @@
       <c r="W251" s="3"/>
       <c r="X251" s="3"/>
       <c r="Y251" s="4" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
     </row>
@@ -17797,7 +17857,7 @@
       <c r="W252" s="3"/>
       <c r="X252" s="3"/>
       <c r="Y252" s="4" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
     </row>
@@ -17827,7 +17887,7 @@
       <c r="W253" s="3"/>
       <c r="X253" s="3"/>
       <c r="Y253" s="4" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
     </row>
@@ -17857,7 +17917,7 @@
       <c r="W254" s="3"/>
       <c r="X254" s="3"/>
       <c r="Y254" s="4" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
     </row>
@@ -17887,7 +17947,7 @@
       <c r="W255" s="3"/>
       <c r="X255" s="3"/>
       <c r="Y255" s="4" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
     </row>
@@ -17917,7 +17977,7 @@
       <c r="W256" s="3"/>
       <c r="X256" s="3"/>
       <c r="Y256" s="4" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
     </row>
@@ -17947,7 +18007,7 @@
       <c r="W257" s="3"/>
       <c r="X257" s="3"/>
       <c r="Y257" s="4" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
     </row>
@@ -17977,7 +18037,7 @@
       <c r="W258" s="3"/>
       <c r="X258" s="3"/>
       <c r="Y258" s="4" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
     </row>
@@ -18007,7 +18067,7 @@
       <c r="W259" s="3"/>
       <c r="X259" s="3"/>
       <c r="Y259" s="4" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
     </row>
@@ -18037,7 +18097,7 @@
       <c r="W260" s="3"/>
       <c r="X260" s="3"/>
       <c r="Y260" s="4" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
     </row>
@@ -18067,7 +18127,7 @@
       <c r="W261" s="3"/>
       <c r="X261" s="3"/>
       <c r="Y261" s="4" t="str">
-        <f t="shared" ref="Y261:Y324" si="30">IF(COUNTA(B261:X261)=0,"",AVERAGE(B261:X261))</f>
+        <f t="shared" ref="Y261:Y324" si="31">IF(COUNTA(B261:X261)=0,"",AVERAGE(B261:X261))</f>
         <v/>
       </c>
     </row>
@@ -18097,7 +18157,7 @@
       <c r="W262" s="3"/>
       <c r="X262" s="3"/>
       <c r="Y262" s="4" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
     </row>
@@ -18127,7 +18187,7 @@
       <c r="W263" s="3"/>
       <c r="X263" s="3"/>
       <c r="Y263" s="4" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
     </row>
@@ -18157,7 +18217,7 @@
       <c r="W264" s="3"/>
       <c r="X264" s="3"/>
       <c r="Y264" s="4" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
     </row>
@@ -18187,7 +18247,7 @@
       <c r="W265" s="3"/>
       <c r="X265" s="3"/>
       <c r="Y265" s="4" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
     </row>
@@ -18217,7 +18277,7 @@
       <c r="W266" s="3"/>
       <c r="X266" s="3"/>
       <c r="Y266" s="4" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
     </row>
@@ -18247,7 +18307,7 @@
       <c r="W267" s="3"/>
       <c r="X267" s="3"/>
       <c r="Y267" s="4" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
     </row>
@@ -18277,7 +18337,7 @@
       <c r="W268" s="3"/>
       <c r="X268" s="3"/>
       <c r="Y268" s="4" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
     </row>
@@ -18307,7 +18367,7 @@
       <c r="W269" s="3"/>
       <c r="X269" s="3"/>
       <c r="Y269" s="4" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
     </row>
@@ -18337,7 +18397,7 @@
       <c r="W270" s="3"/>
       <c r="X270" s="3"/>
       <c r="Y270" s="4" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
     </row>
@@ -18367,7 +18427,7 @@
       <c r="W271" s="3"/>
       <c r="X271" s="3"/>
       <c r="Y271" s="4" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
     </row>
@@ -18397,7 +18457,7 @@
       <c r="W272" s="3"/>
       <c r="X272" s="3"/>
       <c r="Y272" s="4" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
     </row>
@@ -18427,7 +18487,7 @@
       <c r="W273" s="3"/>
       <c r="X273" s="3"/>
       <c r="Y273" s="4" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
     </row>
@@ -18457,7 +18517,7 @@
       <c r="W274" s="3"/>
       <c r="X274" s="3"/>
       <c r="Y274" s="4" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
     </row>
@@ -18487,7 +18547,7 @@
       <c r="W275" s="3"/>
       <c r="X275" s="3"/>
       <c r="Y275" s="4" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
     </row>
@@ -18517,7 +18577,7 @@
       <c r="W276" s="3"/>
       <c r="X276" s="3"/>
       <c r="Y276" s="4" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
     </row>
@@ -18547,7 +18607,7 @@
       <c r="W277" s="3"/>
       <c r="X277" s="3"/>
       <c r="Y277" s="4" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
     </row>
@@ -18577,7 +18637,7 @@
       <c r="W278" s="3"/>
       <c r="X278" s="3"/>
       <c r="Y278" s="4" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
     </row>
@@ -18607,7 +18667,7 @@
       <c r="W279" s="3"/>
       <c r="X279" s="3"/>
       <c r="Y279" s="4" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
     </row>
@@ -18637,7 +18697,7 @@
       <c r="W280" s="3"/>
       <c r="X280" s="3"/>
       <c r="Y280" s="4" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
     </row>
@@ -18667,7 +18727,7 @@
       <c r="W281" s="3"/>
       <c r="X281" s="3"/>
       <c r="Y281" s="4" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
     </row>
@@ -18697,7 +18757,7 @@
       <c r="W282" s="3"/>
       <c r="X282" s="3"/>
       <c r="Y282" s="4" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
     </row>
@@ -18727,7 +18787,7 @@
       <c r="W283" s="3"/>
       <c r="X283" s="3"/>
       <c r="Y283" s="4" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
     </row>
@@ -18757,7 +18817,7 @@
       <c r="W284" s="3"/>
       <c r="X284" s="3"/>
       <c r="Y284" s="4" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
     </row>
@@ -18787,7 +18847,7 @@
       <c r="W285" s="3"/>
       <c r="X285" s="3"/>
       <c r="Y285" s="4" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
     </row>
@@ -18817,7 +18877,7 @@
       <c r="W286" s="3"/>
       <c r="X286" s="3"/>
       <c r="Y286" s="4" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
     </row>
@@ -18847,7 +18907,7 @@
       <c r="W287" s="3"/>
       <c r="X287" s="3"/>
       <c r="Y287" s="4" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
     </row>
@@ -18877,7 +18937,7 @@
       <c r="W288" s="3"/>
       <c r="X288" s="3"/>
       <c r="Y288" s="4" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
     </row>
@@ -18907,7 +18967,7 @@
       <c r="W289" s="3"/>
       <c r="X289" s="3"/>
       <c r="Y289" s="4" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
     </row>
@@ -18937,7 +18997,7 @@
       <c r="W290" s="3"/>
       <c r="X290" s="3"/>
       <c r="Y290" s="4" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
     </row>
@@ -18967,7 +19027,7 @@
       <c r="W291" s="3"/>
       <c r="X291" s="3"/>
       <c r="Y291" s="4" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
     </row>
@@ -18997,7 +19057,7 @@
       <c r="W292" s="3"/>
       <c r="X292" s="3"/>
       <c r="Y292" s="4" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
     </row>
@@ -19027,7 +19087,7 @@
       <c r="W293" s="3"/>
       <c r="X293" s="3"/>
       <c r="Y293" s="4" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
     </row>
@@ -19057,7 +19117,7 @@
       <c r="W294" s="3"/>
       <c r="X294" s="3"/>
       <c r="Y294" s="4" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
     </row>
@@ -19087,7 +19147,7 @@
       <c r="W295" s="3"/>
       <c r="X295" s="3"/>
       <c r="Y295" s="4" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
     </row>
@@ -19117,7 +19177,7 @@
       <c r="W296" s="3"/>
       <c r="X296" s="3"/>
       <c r="Y296" s="4" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
     </row>
@@ -19147,7 +19207,7 @@
       <c r="W297" s="3"/>
       <c r="X297" s="3"/>
       <c r="Y297" s="4" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
     </row>
@@ -19177,7 +19237,7 @@
       <c r="W298" s="3"/>
       <c r="X298" s="3"/>
       <c r="Y298" s="4" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
     </row>
@@ -19207,7 +19267,7 @@
       <c r="W299" s="3"/>
       <c r="X299" s="3"/>
       <c r="Y299" s="4" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
     </row>
@@ -19237,7 +19297,7 @@
       <c r="W300" s="3"/>
       <c r="X300" s="3"/>
       <c r="Y300" s="4" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
     </row>
@@ -19267,7 +19327,7 @@
       <c r="W301" s="3"/>
       <c r="X301" s="3"/>
       <c r="Y301" s="4" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
     </row>
@@ -19297,7 +19357,7 @@
       <c r="W302" s="3"/>
       <c r="X302" s="3"/>
       <c r="Y302" s="4" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
     </row>
@@ -19327,7 +19387,7 @@
       <c r="W303" s="3"/>
       <c r="X303" s="3"/>
       <c r="Y303" s="4" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
     </row>
@@ -19357,7 +19417,7 @@
       <c r="W304" s="3"/>
       <c r="X304" s="3"/>
       <c r="Y304" s="4" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
     </row>
@@ -19387,7 +19447,7 @@
       <c r="W305" s="3"/>
       <c r="X305" s="3"/>
       <c r="Y305" s="4" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
     </row>
@@ -19417,7 +19477,7 @@
       <c r="W306" s="3"/>
       <c r="X306" s="3"/>
       <c r="Y306" s="4" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
     </row>
@@ -19447,7 +19507,7 @@
       <c r="W307" s="3"/>
       <c r="X307" s="3"/>
       <c r="Y307" s="4" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
     </row>
@@ -19477,7 +19537,7 @@
       <c r="W308" s="3"/>
       <c r="X308" s="3"/>
       <c r="Y308" s="4" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
     </row>
@@ -19507,7 +19567,7 @@
       <c r="W309" s="3"/>
       <c r="X309" s="3"/>
       <c r="Y309" s="4" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
     </row>
@@ -19537,7 +19597,7 @@
       <c r="W310" s="3"/>
       <c r="X310" s="3"/>
       <c r="Y310" s="4" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
     </row>
@@ -19567,7 +19627,7 @@
       <c r="W311" s="3"/>
       <c r="X311" s="3"/>
       <c r="Y311" s="4" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
     </row>
@@ -19597,7 +19657,7 @@
       <c r="W312" s="3"/>
       <c r="X312" s="3"/>
       <c r="Y312" s="4" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
     </row>
@@ -19627,7 +19687,7 @@
       <c r="W313" s="3"/>
       <c r="X313" s="3"/>
       <c r="Y313" s="4" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
     </row>
@@ -19657,7 +19717,7 @@
       <c r="W314" s="3"/>
       <c r="X314" s="3"/>
       <c r="Y314" s="4" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
     </row>
@@ -19687,7 +19747,7 @@
       <c r="W315" s="3"/>
       <c r="X315" s="3"/>
       <c r="Y315" s="4" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
     </row>
@@ -19717,7 +19777,7 @@
       <c r="W316" s="3"/>
       <c r="X316" s="3"/>
       <c r="Y316" s="4" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
     </row>
@@ -19747,7 +19807,7 @@
       <c r="W317" s="3"/>
       <c r="X317" s="3"/>
       <c r="Y317" s="4" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
     </row>
@@ -19777,7 +19837,7 @@
       <c r="W318" s="3"/>
       <c r="X318" s="3"/>
       <c r="Y318" s="4" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
     </row>
@@ -19807,7 +19867,7 @@
       <c r="W319" s="3"/>
       <c r="X319" s="3"/>
       <c r="Y319" s="4" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
     </row>
@@ -19837,7 +19897,7 @@
       <c r="W320" s="3"/>
       <c r="X320" s="3"/>
       <c r="Y320" s="4" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
     </row>
@@ -19867,7 +19927,7 @@
       <c r="W321" s="3"/>
       <c r="X321" s="3"/>
       <c r="Y321" s="4" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
     </row>
@@ -19897,7 +19957,7 @@
       <c r="W322" s="3"/>
       <c r="X322" s="3"/>
       <c r="Y322" s="4" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
     </row>
@@ -19927,7 +19987,7 @@
       <c r="W323" s="3"/>
       <c r="X323" s="3"/>
       <c r="Y323" s="4" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
     </row>
@@ -19957,7 +20017,7 @@
       <c r="W324" s="3"/>
       <c r="X324" s="3"/>
       <c r="Y324" s="4" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
     </row>
@@ -19987,7 +20047,7 @@
       <c r="W325" s="3"/>
       <c r="X325" s="3"/>
       <c r="Y325" s="4" t="str">
-        <f t="shared" ref="Y325:Y388" si="31">IF(COUNTA(B325:X325)=0,"",AVERAGE(B325:X325))</f>
+        <f t="shared" ref="Y325:Y388" si="32">IF(COUNTA(B325:X325)=0,"",AVERAGE(B325:X325))</f>
         <v/>
       </c>
     </row>
@@ -20017,7 +20077,7 @@
       <c r="W326" s="3"/>
       <c r="X326" s="3"/>
       <c r="Y326" s="4" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
     </row>
@@ -20047,7 +20107,7 @@
       <c r="W327" s="3"/>
       <c r="X327" s="3"/>
       <c r="Y327" s="4" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
     </row>
@@ -20077,7 +20137,7 @@
       <c r="W328" s="3"/>
       <c r="X328" s="3"/>
       <c r="Y328" s="4" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
     </row>
@@ -20107,7 +20167,7 @@
       <c r="W329" s="3"/>
       <c r="X329" s="3"/>
       <c r="Y329" s="4" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
     </row>
@@ -20137,7 +20197,7 @@
       <c r="W330" s="3"/>
       <c r="X330" s="3"/>
       <c r="Y330" s="4" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
     </row>
@@ -20167,7 +20227,7 @@
       <c r="W331" s="3"/>
       <c r="X331" s="3"/>
       <c r="Y331" s="4" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
     </row>
@@ -20197,7 +20257,7 @@
       <c r="W332" s="3"/>
       <c r="X332" s="3"/>
       <c r="Y332" s="4" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
     </row>
@@ -20227,7 +20287,7 @@
       <c r="W333" s="3"/>
       <c r="X333" s="3"/>
       <c r="Y333" s="4" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
     </row>
@@ -20257,7 +20317,7 @@
       <c r="W334" s="3"/>
       <c r="X334" s="3"/>
       <c r="Y334" s="4" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
     </row>
@@ -20287,7 +20347,7 @@
       <c r="W335" s="3"/>
       <c r="X335" s="3"/>
       <c r="Y335" s="4" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
     </row>
@@ -20317,7 +20377,7 @@
       <c r="W336" s="3"/>
       <c r="X336" s="3"/>
       <c r="Y336" s="4" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
     </row>
@@ -20347,7 +20407,7 @@
       <c r="W337" s="3"/>
       <c r="X337" s="3"/>
       <c r="Y337" s="4" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
     </row>
@@ -20377,7 +20437,7 @@
       <c r="W338" s="3"/>
       <c r="X338" s="3"/>
       <c r="Y338" s="4" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
     </row>
@@ -20407,7 +20467,7 @@
       <c r="W339" s="3"/>
       <c r="X339" s="3"/>
       <c r="Y339" s="4" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
     </row>
@@ -20437,7 +20497,7 @@
       <c r="W340" s="3"/>
       <c r="X340" s="3"/>
       <c r="Y340" s="4" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
     </row>
@@ -20467,7 +20527,7 @@
       <c r="W341" s="3"/>
       <c r="X341" s="3"/>
       <c r="Y341" s="4" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
     </row>
@@ -20497,7 +20557,7 @@
       <c r="W342" s="3"/>
       <c r="X342" s="3"/>
       <c r="Y342" s="4" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
     </row>
@@ -20527,7 +20587,7 @@
       <c r="W343" s="3"/>
       <c r="X343" s="3"/>
       <c r="Y343" s="4" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
     </row>
@@ -20557,7 +20617,7 @@
       <c r="W344" s="3"/>
       <c r="X344" s="3"/>
       <c r="Y344" s="4" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
     </row>
@@ -20587,7 +20647,7 @@
       <c r="W345" s="3"/>
       <c r="X345" s="3"/>
       <c r="Y345" s="4" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
     </row>
@@ -20617,7 +20677,7 @@
       <c r="W346" s="3"/>
       <c r="X346" s="3"/>
       <c r="Y346" s="4" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
     </row>
@@ -20647,7 +20707,7 @@
       <c r="W347" s="3"/>
       <c r="X347" s="3"/>
       <c r="Y347" s="4" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
     </row>
@@ -20677,7 +20737,7 @@
       <c r="W348" s="3"/>
       <c r="X348" s="3"/>
       <c r="Y348" s="4" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
     </row>
@@ -20707,7 +20767,7 @@
       <c r="W349" s="3"/>
       <c r="X349" s="3"/>
       <c r="Y349" s="4" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
     </row>
@@ -20737,7 +20797,7 @@
       <c r="W350" s="3"/>
       <c r="X350" s="3"/>
       <c r="Y350" s="4" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
     </row>
@@ -20767,7 +20827,7 @@
       <c r="W351" s="3"/>
       <c r="X351" s="3"/>
       <c r="Y351" s="4" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
     </row>
@@ -20797,7 +20857,7 @@
       <c r="W352" s="3"/>
       <c r="X352" s="3"/>
       <c r="Y352" s="4" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
     </row>
@@ -20827,7 +20887,7 @@
       <c r="W353" s="3"/>
       <c r="X353" s="3"/>
       <c r="Y353" s="4" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
     </row>
@@ -20857,7 +20917,7 @@
       <c r="W354" s="3"/>
       <c r="X354" s="3"/>
       <c r="Y354" s="4" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
     </row>
@@ -20887,7 +20947,7 @@
       <c r="W355" s="3"/>
       <c r="X355" s="3"/>
       <c r="Y355" s="4" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
     </row>
@@ -20917,7 +20977,7 @@
       <c r="W356" s="3"/>
       <c r="X356" s="3"/>
       <c r="Y356" s="4" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
     </row>
@@ -20947,7 +21007,7 @@
       <c r="W357" s="3"/>
       <c r="X357" s="3"/>
       <c r="Y357" s="4" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
     </row>
@@ -20977,7 +21037,7 @@
       <c r="W358" s="3"/>
       <c r="X358" s="3"/>
       <c r="Y358" s="4" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
     </row>
@@ -21007,7 +21067,7 @@
       <c r="W359" s="3"/>
       <c r="X359" s="3"/>
       <c r="Y359" s="4" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
     </row>
@@ -21037,7 +21097,7 @@
       <c r="W360" s="3"/>
       <c r="X360" s="3"/>
       <c r="Y360" s="4" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
     </row>
@@ -21067,7 +21127,7 @@
       <c r="W361" s="3"/>
       <c r="X361" s="3"/>
       <c r="Y361" s="4" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
     </row>
@@ -21097,7 +21157,7 @@
       <c r="W362" s="3"/>
       <c r="X362" s="3"/>
       <c r="Y362" s="4" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
     </row>
@@ -21127,7 +21187,7 @@
       <c r="W363" s="3"/>
       <c r="X363" s="3"/>
       <c r="Y363" s="4" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
     </row>
@@ -21157,7 +21217,7 @@
       <c r="W364" s="3"/>
       <c r="X364" s="3"/>
       <c r="Y364" s="4" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
     </row>
@@ -21187,7 +21247,7 @@
       <c r="W365" s="3"/>
       <c r="X365" s="3"/>
       <c r="Y365" s="4" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
     </row>
@@ -21217,7 +21277,7 @@
       <c r="W366" s="3"/>
       <c r="X366" s="3"/>
       <c r="Y366" s="4" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
     </row>
@@ -21247,7 +21307,7 @@
       <c r="W367" s="3"/>
       <c r="X367" s="3"/>
       <c r="Y367" s="4" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
     </row>
@@ -21277,7 +21337,7 @@
       <c r="W368" s="3"/>
       <c r="X368" s="3"/>
       <c r="Y368" s="4" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
     </row>
@@ -21307,7 +21367,7 @@
       <c r="W369" s="3"/>
       <c r="X369" s="3"/>
       <c r="Y369" s="4" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
     </row>
@@ -21337,7 +21397,7 @@
       <c r="W370" s="3"/>
       <c r="X370" s="3"/>
       <c r="Y370" s="4" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
     </row>
@@ -21367,7 +21427,7 @@
       <c r="W371" s="3"/>
       <c r="X371" s="3"/>
       <c r="Y371" s="4" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
     </row>
@@ -21397,7 +21457,7 @@
       <c r="W372" s="3"/>
       <c r="X372" s="3"/>
       <c r="Y372" s="4" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
     </row>
@@ -21427,7 +21487,7 @@
       <c r="W373" s="3"/>
       <c r="X373" s="3"/>
       <c r="Y373" s="4" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
     </row>
@@ -21457,7 +21517,7 @@
       <c r="W374" s="3"/>
       <c r="X374" s="3"/>
       <c r="Y374" s="4" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
     </row>
@@ -21487,7 +21547,7 @@
       <c r="W375" s="3"/>
       <c r="X375" s="3"/>
       <c r="Y375" s="4" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
     </row>
@@ -21517,7 +21577,7 @@
       <c r="W376" s="3"/>
       <c r="X376" s="3"/>
       <c r="Y376" s="4" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
     </row>
@@ -21547,7 +21607,7 @@
       <c r="W377" s="3"/>
       <c r="X377" s="3"/>
       <c r="Y377" s="4" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
     </row>
@@ -21577,7 +21637,7 @@
       <c r="W378" s="3"/>
       <c r="X378" s="3"/>
       <c r="Y378" s="4" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
     </row>
@@ -21607,7 +21667,7 @@
       <c r="W379" s="3"/>
       <c r="X379" s="3"/>
       <c r="Y379" s="4" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
     </row>
@@ -21637,7 +21697,7 @@
       <c r="W380" s="3"/>
       <c r="X380" s="3"/>
       <c r="Y380" s="4" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
     </row>
@@ -21667,7 +21727,7 @@
       <c r="W381" s="3"/>
       <c r="X381" s="3"/>
       <c r="Y381" s="4" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
     </row>
@@ -21697,7 +21757,7 @@
       <c r="W382" s="3"/>
       <c r="X382" s="3"/>
       <c r="Y382" s="4" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
     </row>
@@ -21727,7 +21787,7 @@
       <c r="W383" s="3"/>
       <c r="X383" s="3"/>
       <c r="Y383" s="4" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
     </row>
@@ -21757,7 +21817,7 @@
       <c r="W384" s="3"/>
       <c r="X384" s="3"/>
       <c r="Y384" s="4" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
     </row>
@@ -21787,7 +21847,7 @@
       <c r="W385" s="3"/>
       <c r="X385" s="3"/>
       <c r="Y385" s="4" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
     </row>
@@ -21817,7 +21877,7 @@
       <c r="W386" s="3"/>
       <c r="X386" s="3"/>
       <c r="Y386" s="4" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
     </row>
@@ -21847,7 +21907,7 @@
       <c r="W387" s="3"/>
       <c r="X387" s="3"/>
       <c r="Y387" s="4" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
     </row>
@@ -21877,7 +21937,7 @@
       <c r="W388" s="3"/>
       <c r="X388" s="3"/>
       <c r="Y388" s="4" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
     </row>
@@ -21907,7 +21967,7 @@
       <c r="W389" s="3"/>
       <c r="X389" s="3"/>
       <c r="Y389" s="4" t="str">
-        <f t="shared" ref="Y389:Y390" si="32">IF(COUNTA(B389:X389)=0,"",AVERAGE(B389:X389))</f>
+        <f t="shared" ref="Y389:Y390" si="33">IF(COUNTA(B389:X389)=0,"",AVERAGE(B389:X389))</f>
         <v/>
       </c>
     </row>
@@ -21937,7 +21997,7 @@
       <c r="W390" s="3"/>
       <c r="X390" s="3"/>
       <c r="Y390" s="4" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
     </row>
@@ -26702,29 +26762,69 @@
       </c>
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A75" s="2"/>
-      <c r="B75" s="3"/>
-      <c r="C75" s="3"/>
-      <c r="D75" s="3"/>
-      <c r="E75" s="3"/>
-      <c r="F75" s="3"/>
-      <c r="G75" s="3"/>
-      <c r="H75" s="3"/>
-      <c r="I75" s="3"/>
-      <c r="J75" s="3"/>
-      <c r="K75" s="3"/>
-      <c r="L75" s="3"/>
-      <c r="M75" s="3"/>
-      <c r="N75" s="3"/>
-      <c r="O75" s="3"/>
-      <c r="P75" s="3"/>
-      <c r="Q75" s="3"/>
-      <c r="R75" s="3"/>
-      <c r="S75" s="3"/>
-      <c r="T75" s="3"/>
-      <c r="U75" s="4" t="str">
-        <f t="shared" si="34"/>
-        <v/>
+      <c r="A75" s="2">
+        <v>46231</v>
+      </c>
+      <c r="B75" s="3">
+        <v>3.79</v>
+      </c>
+      <c r="C75" s="3">
+        <v>3.95</v>
+      </c>
+      <c r="D75" s="3">
+        <v>3.69</v>
+      </c>
+      <c r="E75" s="3">
+        <v>2.89</v>
+      </c>
+      <c r="F75" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="G75" s="3">
+        <v>3.99</v>
+      </c>
+      <c r="H75" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="I75" s="3">
+        <v>3.39</v>
+      </c>
+      <c r="J75" s="3">
+        <v>3.49</v>
+      </c>
+      <c r="K75" s="3">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="L75" s="3">
+        <v>3.29</v>
+      </c>
+      <c r="M75" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="N75" s="3">
+        <v>3.84</v>
+      </c>
+      <c r="O75" s="3">
+        <v>3.84</v>
+      </c>
+      <c r="P75" s="3">
+        <v>3.89</v>
+      </c>
+      <c r="Q75" s="3">
+        <v>3.65</v>
+      </c>
+      <c r="R75" s="3">
+        <v>3.89</v>
+      </c>
+      <c r="S75" s="3">
+        <v>4.99</v>
+      </c>
+      <c r="T75" s="3">
+        <v>1.99</v>
+      </c>
+      <c r="U75" s="4">
+        <f t="shared" ref="U75" si="36">IF(COUNTA(B75:T75)=0,"",AVERAGE(B75:T75))</f>
+        <v>3.5600000000000009</v>
       </c>
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
@@ -28231,7 +28331,7 @@
       <c r="S133" s="3"/>
       <c r="T133" s="3"/>
       <c r="U133" s="4" t="str">
-        <f t="shared" ref="U133:U196" si="36">IF(COUNTA(B133:T133)=0,"",AVERAGE(B133:T133))</f>
+        <f t="shared" ref="U133:U196" si="37">IF(COUNTA(B133:T133)=0,"",AVERAGE(B133:T133))</f>
         <v/>
       </c>
     </row>
@@ -28257,7 +28357,7 @@
       <c r="S134" s="3"/>
       <c r="T134" s="3"/>
       <c r="U134" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -28283,7 +28383,7 @@
       <c r="S135" s="3"/>
       <c r="T135" s="3"/>
       <c r="U135" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -28309,7 +28409,7 @@
       <c r="S136" s="3"/>
       <c r="T136" s="3"/>
       <c r="U136" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -28335,7 +28435,7 @@
       <c r="S137" s="3"/>
       <c r="T137" s="3"/>
       <c r="U137" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -28361,7 +28461,7 @@
       <c r="S138" s="3"/>
       <c r="T138" s="3"/>
       <c r="U138" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -28387,7 +28487,7 @@
       <c r="S139" s="3"/>
       <c r="T139" s="3"/>
       <c r="U139" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -28413,7 +28513,7 @@
       <c r="S140" s="3"/>
       <c r="T140" s="3"/>
       <c r="U140" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -28439,7 +28539,7 @@
       <c r="S141" s="3"/>
       <c r="T141" s="3"/>
       <c r="U141" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -28465,7 +28565,7 @@
       <c r="S142" s="3"/>
       <c r="T142" s="3"/>
       <c r="U142" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -28491,7 +28591,7 @@
       <c r="S143" s="3"/>
       <c r="T143" s="3"/>
       <c r="U143" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -28517,7 +28617,7 @@
       <c r="S144" s="3"/>
       <c r="T144" s="3"/>
       <c r="U144" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -28543,7 +28643,7 @@
       <c r="S145" s="3"/>
       <c r="T145" s="3"/>
       <c r="U145" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -28569,7 +28669,7 @@
       <c r="S146" s="3"/>
       <c r="T146" s="3"/>
       <c r="U146" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -28595,7 +28695,7 @@
       <c r="S147" s="3"/>
       <c r="T147" s="3"/>
       <c r="U147" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -28621,7 +28721,7 @@
       <c r="S148" s="3"/>
       <c r="T148" s="3"/>
       <c r="U148" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -28647,7 +28747,7 @@
       <c r="S149" s="3"/>
       <c r="T149" s="3"/>
       <c r="U149" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -28673,7 +28773,7 @@
       <c r="S150" s="3"/>
       <c r="T150" s="3"/>
       <c r="U150" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -28699,7 +28799,7 @@
       <c r="S151" s="3"/>
       <c r="T151" s="3"/>
       <c r="U151" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -28725,7 +28825,7 @@
       <c r="S152" s="3"/>
       <c r="T152" s="3"/>
       <c r="U152" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -28751,7 +28851,7 @@
       <c r="S153" s="3"/>
       <c r="T153" s="3"/>
       <c r="U153" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -28777,7 +28877,7 @@
       <c r="S154" s="3"/>
       <c r="T154" s="3"/>
       <c r="U154" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -28803,7 +28903,7 @@
       <c r="S155" s="3"/>
       <c r="T155" s="3"/>
       <c r="U155" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -28829,7 +28929,7 @@
       <c r="S156" s="3"/>
       <c r="T156" s="3"/>
       <c r="U156" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -28855,7 +28955,7 @@
       <c r="S157" s="3"/>
       <c r="T157" s="3"/>
       <c r="U157" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -28881,7 +28981,7 @@
       <c r="S158" s="3"/>
       <c r="T158" s="3"/>
       <c r="U158" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -28907,7 +29007,7 @@
       <c r="S159" s="3"/>
       <c r="T159" s="3"/>
       <c r="U159" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -28933,7 +29033,7 @@
       <c r="S160" s="3"/>
       <c r="T160" s="3"/>
       <c r="U160" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -28959,7 +29059,7 @@
       <c r="S161" s="3"/>
       <c r="T161" s="3"/>
       <c r="U161" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -28985,7 +29085,7 @@
       <c r="S162" s="3"/>
       <c r="T162" s="3"/>
       <c r="U162" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -29011,7 +29111,7 @@
       <c r="S163" s="3"/>
       <c r="T163" s="3"/>
       <c r="U163" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -29037,7 +29137,7 @@
       <c r="S164" s="3"/>
       <c r="T164" s="3"/>
       <c r="U164" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -29063,7 +29163,7 @@
       <c r="S165" s="3"/>
       <c r="T165" s="3"/>
       <c r="U165" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -29089,7 +29189,7 @@
       <c r="S166" s="3"/>
       <c r="T166" s="3"/>
       <c r="U166" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -29115,7 +29215,7 @@
       <c r="S167" s="3"/>
       <c r="T167" s="3"/>
       <c r="U167" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -29141,7 +29241,7 @@
       <c r="S168" s="3"/>
       <c r="T168" s="3"/>
       <c r="U168" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -29167,7 +29267,7 @@
       <c r="S169" s="3"/>
       <c r="T169" s="3"/>
       <c r="U169" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -29193,7 +29293,7 @@
       <c r="S170" s="3"/>
       <c r="T170" s="3"/>
       <c r="U170" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -29219,7 +29319,7 @@
       <c r="S171" s="3"/>
       <c r="T171" s="3"/>
       <c r="U171" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -29245,7 +29345,7 @@
       <c r="S172" s="3"/>
       <c r="T172" s="3"/>
       <c r="U172" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -29271,7 +29371,7 @@
       <c r="S173" s="3"/>
       <c r="T173" s="3"/>
       <c r="U173" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -29297,7 +29397,7 @@
       <c r="S174" s="3"/>
       <c r="T174" s="3"/>
       <c r="U174" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -29323,7 +29423,7 @@
       <c r="S175" s="3"/>
       <c r="T175" s="3"/>
       <c r="U175" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -29349,7 +29449,7 @@
       <c r="S176" s="3"/>
       <c r="T176" s="3"/>
       <c r="U176" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -29375,7 +29475,7 @@
       <c r="S177" s="3"/>
       <c r="T177" s="3"/>
       <c r="U177" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -29401,7 +29501,7 @@
       <c r="S178" s="3"/>
       <c r="T178" s="3"/>
       <c r="U178" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -29427,7 +29527,7 @@
       <c r="S179" s="3"/>
       <c r="T179" s="3"/>
       <c r="U179" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -29453,7 +29553,7 @@
       <c r="S180" s="3"/>
       <c r="T180" s="3"/>
       <c r="U180" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -29479,7 +29579,7 @@
       <c r="S181" s="3"/>
       <c r="T181" s="3"/>
       <c r="U181" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -29505,7 +29605,7 @@
       <c r="S182" s="3"/>
       <c r="T182" s="3"/>
       <c r="U182" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -29531,7 +29631,7 @@
       <c r="S183" s="3"/>
       <c r="T183" s="3"/>
       <c r="U183" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -29557,7 +29657,7 @@
       <c r="S184" s="3"/>
       <c r="T184" s="3"/>
       <c r="U184" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -29583,7 +29683,7 @@
       <c r="S185" s="3"/>
       <c r="T185" s="3"/>
       <c r="U185" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -29609,7 +29709,7 @@
       <c r="S186" s="3"/>
       <c r="T186" s="3"/>
       <c r="U186" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -29635,7 +29735,7 @@
       <c r="S187" s="3"/>
       <c r="T187" s="3"/>
       <c r="U187" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -29661,7 +29761,7 @@
       <c r="S188" s="3"/>
       <c r="T188" s="3"/>
       <c r="U188" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -29687,7 +29787,7 @@
       <c r="S189" s="3"/>
       <c r="T189" s="3"/>
       <c r="U189" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -29713,7 +29813,7 @@
       <c r="S190" s="3"/>
       <c r="T190" s="3"/>
       <c r="U190" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -29739,7 +29839,7 @@
       <c r="S191" s="3"/>
       <c r="T191" s="3"/>
       <c r="U191" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -29765,7 +29865,7 @@
       <c r="S192" s="3"/>
       <c r="T192" s="3"/>
       <c r="U192" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -29791,7 +29891,7 @@
       <c r="S193" s="3"/>
       <c r="T193" s="3"/>
       <c r="U193" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -29817,7 +29917,7 @@
       <c r="S194" s="3"/>
       <c r="T194" s="3"/>
       <c r="U194" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -29843,7 +29943,7 @@
       <c r="S195" s="3"/>
       <c r="T195" s="3"/>
       <c r="U195" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -29869,7 +29969,7 @@
       <c r="S196" s="3"/>
       <c r="T196" s="3"/>
       <c r="U196" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -29895,7 +29995,7 @@
       <c r="S197" s="3"/>
       <c r="T197" s="3"/>
       <c r="U197" s="4" t="str">
-        <f t="shared" ref="U197:U260" si="37">IF(COUNTA(B197:T197)=0,"",AVERAGE(B197:T197))</f>
+        <f t="shared" ref="U197:U260" si="38">IF(COUNTA(B197:T197)=0,"",AVERAGE(B197:T197))</f>
         <v/>
       </c>
     </row>
@@ -29921,7 +30021,7 @@
       <c r="S198" s="3"/>
       <c r="T198" s="3"/>
       <c r="U198" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -29947,7 +30047,7 @@
       <c r="S199" s="3"/>
       <c r="T199" s="3"/>
       <c r="U199" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -29973,7 +30073,7 @@
       <c r="S200" s="3"/>
       <c r="T200" s="3"/>
       <c r="U200" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -29999,7 +30099,7 @@
       <c r="S201" s="3"/>
       <c r="T201" s="3"/>
       <c r="U201" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -30025,7 +30125,7 @@
       <c r="S202" s="3"/>
       <c r="T202" s="3"/>
       <c r="U202" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -30051,7 +30151,7 @@
       <c r="S203" s="3"/>
       <c r="T203" s="3"/>
       <c r="U203" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -30077,7 +30177,7 @@
       <c r="S204" s="3"/>
       <c r="T204" s="3"/>
       <c r="U204" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -30103,7 +30203,7 @@
       <c r="S205" s="3"/>
       <c r="T205" s="3"/>
       <c r="U205" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -30129,7 +30229,7 @@
       <c r="S206" s="3"/>
       <c r="T206" s="3"/>
       <c r="U206" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -30155,7 +30255,7 @@
       <c r="S207" s="3"/>
       <c r="T207" s="3"/>
       <c r="U207" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -30181,7 +30281,7 @@
       <c r="S208" s="3"/>
       <c r="T208" s="3"/>
       <c r="U208" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -30207,7 +30307,7 @@
       <c r="S209" s="3"/>
       <c r="T209" s="3"/>
       <c r="U209" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -30233,7 +30333,7 @@
       <c r="S210" s="3"/>
       <c r="T210" s="3"/>
       <c r="U210" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -30259,7 +30359,7 @@
       <c r="S211" s="3"/>
       <c r="T211" s="3"/>
       <c r="U211" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -30285,7 +30385,7 @@
       <c r="S212" s="3"/>
       <c r="T212" s="3"/>
       <c r="U212" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -30311,7 +30411,7 @@
       <c r="S213" s="3"/>
       <c r="T213" s="3"/>
       <c r="U213" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -30337,7 +30437,7 @@
       <c r="S214" s="3"/>
       <c r="T214" s="3"/>
       <c r="U214" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -30363,7 +30463,7 @@
       <c r="S215" s="3"/>
       <c r="T215" s="3"/>
       <c r="U215" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -30389,7 +30489,7 @@
       <c r="S216" s="3"/>
       <c r="T216" s="3"/>
       <c r="U216" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -30415,7 +30515,7 @@
       <c r="S217" s="3"/>
       <c r="T217" s="3"/>
       <c r="U217" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -30441,7 +30541,7 @@
       <c r="S218" s="3"/>
       <c r="T218" s="3"/>
       <c r="U218" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -30467,7 +30567,7 @@
       <c r="S219" s="3"/>
       <c r="T219" s="3"/>
       <c r="U219" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -30493,7 +30593,7 @@
       <c r="S220" s="3"/>
       <c r="T220" s="3"/>
       <c r="U220" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -30519,7 +30619,7 @@
       <c r="S221" s="3"/>
       <c r="T221" s="3"/>
       <c r="U221" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -30545,7 +30645,7 @@
       <c r="S222" s="3"/>
       <c r="T222" s="3"/>
       <c r="U222" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -30571,7 +30671,7 @@
       <c r="S223" s="3"/>
       <c r="T223" s="3"/>
       <c r="U223" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -30597,7 +30697,7 @@
       <c r="S224" s="3"/>
       <c r="T224" s="3"/>
       <c r="U224" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -30623,7 +30723,7 @@
       <c r="S225" s="3"/>
       <c r="T225" s="3"/>
       <c r="U225" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -30649,7 +30749,7 @@
       <c r="S226" s="3"/>
       <c r="T226" s="3"/>
       <c r="U226" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -30675,7 +30775,7 @@
       <c r="S227" s="3"/>
       <c r="T227" s="3"/>
       <c r="U227" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -30701,7 +30801,7 @@
       <c r="S228" s="3"/>
       <c r="T228" s="3"/>
       <c r="U228" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -30727,7 +30827,7 @@
       <c r="S229" s="3"/>
       <c r="T229" s="3"/>
       <c r="U229" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -30753,7 +30853,7 @@
       <c r="S230" s="3"/>
       <c r="T230" s="3"/>
       <c r="U230" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -30779,7 +30879,7 @@
       <c r="S231" s="3"/>
       <c r="T231" s="3"/>
       <c r="U231" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -30805,7 +30905,7 @@
       <c r="S232" s="3"/>
       <c r="T232" s="3"/>
       <c r="U232" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -30831,7 +30931,7 @@
       <c r="S233" s="3"/>
       <c r="T233" s="3"/>
       <c r="U233" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -30857,7 +30957,7 @@
       <c r="S234" s="3"/>
       <c r="T234" s="3"/>
       <c r="U234" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -30883,7 +30983,7 @@
       <c r="S235" s="3"/>
       <c r="T235" s="3"/>
       <c r="U235" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -30909,7 +31009,7 @@
       <c r="S236" s="3"/>
       <c r="T236" s="3"/>
       <c r="U236" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -30935,7 +31035,7 @@
       <c r="S237" s="3"/>
       <c r="T237" s="3"/>
       <c r="U237" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -30961,7 +31061,7 @@
       <c r="S238" s="3"/>
       <c r="T238" s="3"/>
       <c r="U238" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -30987,7 +31087,7 @@
       <c r="S239" s="3"/>
       <c r="T239" s="3"/>
       <c r="U239" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -31013,7 +31113,7 @@
       <c r="S240" s="3"/>
       <c r="T240" s="3"/>
       <c r="U240" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -31039,7 +31139,7 @@
       <c r="S241" s="3"/>
       <c r="T241" s="3"/>
       <c r="U241" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -31065,7 +31165,7 @@
       <c r="S242" s="3"/>
       <c r="T242" s="3"/>
       <c r="U242" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -31091,7 +31191,7 @@
       <c r="S243" s="3"/>
       <c r="T243" s="3"/>
       <c r="U243" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -31117,7 +31217,7 @@
       <c r="S244" s="3"/>
       <c r="T244" s="3"/>
       <c r="U244" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -31143,7 +31243,7 @@
       <c r="S245" s="3"/>
       <c r="T245" s="3"/>
       <c r="U245" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -31169,7 +31269,7 @@
       <c r="S246" s="3"/>
       <c r="T246" s="3"/>
       <c r="U246" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -31195,7 +31295,7 @@
       <c r="S247" s="3"/>
       <c r="T247" s="3"/>
       <c r="U247" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -31221,7 +31321,7 @@
       <c r="S248" s="3"/>
       <c r="T248" s="3"/>
       <c r="U248" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -31247,7 +31347,7 @@
       <c r="S249" s="3"/>
       <c r="T249" s="3"/>
       <c r="U249" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -31273,7 +31373,7 @@
       <c r="S250" s="3"/>
       <c r="T250" s="3"/>
       <c r="U250" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -31299,7 +31399,7 @@
       <c r="S251" s="3"/>
       <c r="T251" s="3"/>
       <c r="U251" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -31325,7 +31425,7 @@
       <c r="S252" s="3"/>
       <c r="T252" s="3"/>
       <c r="U252" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -31351,7 +31451,7 @@
       <c r="S253" s="3"/>
       <c r="T253" s="3"/>
       <c r="U253" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -31377,7 +31477,7 @@
       <c r="S254" s="3"/>
       <c r="T254" s="3"/>
       <c r="U254" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -31403,7 +31503,7 @@
       <c r="S255" s="3"/>
       <c r="T255" s="3"/>
       <c r="U255" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -31429,7 +31529,7 @@
       <c r="S256" s="3"/>
       <c r="T256" s="3"/>
       <c r="U256" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -31455,7 +31555,7 @@
       <c r="S257" s="3"/>
       <c r="T257" s="3"/>
       <c r="U257" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -31481,7 +31581,7 @@
       <c r="S258" s="3"/>
       <c r="T258" s="3"/>
       <c r="U258" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -31507,7 +31607,7 @@
       <c r="S259" s="3"/>
       <c r="T259" s="3"/>
       <c r="U259" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -31533,7 +31633,7 @@
       <c r="S260" s="3"/>
       <c r="T260" s="3"/>
       <c r="U260" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -31559,7 +31659,7 @@
       <c r="S261" s="3"/>
       <c r="T261" s="3"/>
       <c r="U261" s="4" t="str">
-        <f t="shared" ref="U261:U324" si="38">IF(COUNTA(B261:T261)=0,"",AVERAGE(B261:T261))</f>
+        <f t="shared" ref="U261:U324" si="39">IF(COUNTA(B261:T261)=0,"",AVERAGE(B261:T261))</f>
         <v/>
       </c>
     </row>
@@ -31585,7 +31685,7 @@
       <c r="S262" s="3"/>
       <c r="T262" s="3"/>
       <c r="U262" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -31611,7 +31711,7 @@
       <c r="S263" s="3"/>
       <c r="T263" s="3"/>
       <c r="U263" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -31637,7 +31737,7 @@
       <c r="S264" s="3"/>
       <c r="T264" s="3"/>
       <c r="U264" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -31663,7 +31763,7 @@
       <c r="S265" s="3"/>
       <c r="T265" s="3"/>
       <c r="U265" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -31689,7 +31789,7 @@
       <c r="S266" s="3"/>
       <c r="T266" s="3"/>
       <c r="U266" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -31715,7 +31815,7 @@
       <c r="S267" s="3"/>
       <c r="T267" s="3"/>
       <c r="U267" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -31741,7 +31841,7 @@
       <c r="S268" s="3"/>
       <c r="T268" s="3"/>
       <c r="U268" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -31767,7 +31867,7 @@
       <c r="S269" s="3"/>
       <c r="T269" s="3"/>
       <c r="U269" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -31793,7 +31893,7 @@
       <c r="S270" s="3"/>
       <c r="T270" s="3"/>
       <c r="U270" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -31819,7 +31919,7 @@
       <c r="S271" s="3"/>
       <c r="T271" s="3"/>
       <c r="U271" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -31845,7 +31945,7 @@
       <c r="S272" s="3"/>
       <c r="T272" s="3"/>
       <c r="U272" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -31871,7 +31971,7 @@
       <c r="S273" s="3"/>
       <c r="T273" s="3"/>
       <c r="U273" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -31897,7 +31997,7 @@
       <c r="S274" s="3"/>
       <c r="T274" s="3"/>
       <c r="U274" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -31923,7 +32023,7 @@
       <c r="S275" s="3"/>
       <c r="T275" s="3"/>
       <c r="U275" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -31949,7 +32049,7 @@
       <c r="S276" s="3"/>
       <c r="T276" s="3"/>
       <c r="U276" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -31975,7 +32075,7 @@
       <c r="S277" s="3"/>
       <c r="T277" s="3"/>
       <c r="U277" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -32001,7 +32101,7 @@
       <c r="S278" s="3"/>
       <c r="T278" s="3"/>
       <c r="U278" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -32027,7 +32127,7 @@
       <c r="S279" s="3"/>
       <c r="T279" s="3"/>
       <c r="U279" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -32053,7 +32153,7 @@
       <c r="S280" s="3"/>
       <c r="T280" s="3"/>
       <c r="U280" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -32079,7 +32179,7 @@
       <c r="S281" s="3"/>
       <c r="T281" s="3"/>
       <c r="U281" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -32105,7 +32205,7 @@
       <c r="S282" s="3"/>
       <c r="T282" s="3"/>
       <c r="U282" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -32131,7 +32231,7 @@
       <c r="S283" s="3"/>
       <c r="T283" s="3"/>
       <c r="U283" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -32157,7 +32257,7 @@
       <c r="S284" s="3"/>
       <c r="T284" s="3"/>
       <c r="U284" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -32183,7 +32283,7 @@
       <c r="S285" s="3"/>
       <c r="T285" s="3"/>
       <c r="U285" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -32209,7 +32309,7 @@
       <c r="S286" s="3"/>
       <c r="T286" s="3"/>
       <c r="U286" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -32235,7 +32335,7 @@
       <c r="S287" s="3"/>
       <c r="T287" s="3"/>
       <c r="U287" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -32261,7 +32361,7 @@
       <c r="S288" s="3"/>
       <c r="T288" s="3"/>
       <c r="U288" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -32287,7 +32387,7 @@
       <c r="S289" s="3"/>
       <c r="T289" s="3"/>
       <c r="U289" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -32313,7 +32413,7 @@
       <c r="S290" s="3"/>
       <c r="T290" s="3"/>
       <c r="U290" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -32339,7 +32439,7 @@
       <c r="S291" s="3"/>
       <c r="T291" s="3"/>
       <c r="U291" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -32365,7 +32465,7 @@
       <c r="S292" s="3"/>
       <c r="T292" s="3"/>
       <c r="U292" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -32391,7 +32491,7 @@
       <c r="S293" s="3"/>
       <c r="T293" s="3"/>
       <c r="U293" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -32417,7 +32517,7 @@
       <c r="S294" s="3"/>
       <c r="T294" s="3"/>
       <c r="U294" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -32443,7 +32543,7 @@
       <c r="S295" s="3"/>
       <c r="T295" s="3"/>
       <c r="U295" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -32469,7 +32569,7 @@
       <c r="S296" s="3"/>
       <c r="T296" s="3"/>
       <c r="U296" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -32495,7 +32595,7 @@
       <c r="S297" s="3"/>
       <c r="T297" s="3"/>
       <c r="U297" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -32521,7 +32621,7 @@
       <c r="S298" s="3"/>
       <c r="T298" s="3"/>
       <c r="U298" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -32547,7 +32647,7 @@
       <c r="S299" s="3"/>
       <c r="T299" s="3"/>
       <c r="U299" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -32573,7 +32673,7 @@
       <c r="S300" s="3"/>
       <c r="T300" s="3"/>
       <c r="U300" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -32599,7 +32699,7 @@
       <c r="S301" s="3"/>
       <c r="T301" s="3"/>
       <c r="U301" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -32625,7 +32725,7 @@
       <c r="S302" s="3"/>
       <c r="T302" s="3"/>
       <c r="U302" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -32651,7 +32751,7 @@
       <c r="S303" s="3"/>
       <c r="T303" s="3"/>
       <c r="U303" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -32677,7 +32777,7 @@
       <c r="S304" s="3"/>
       <c r="T304" s="3"/>
       <c r="U304" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -32703,7 +32803,7 @@
       <c r="S305" s="3"/>
       <c r="T305" s="3"/>
       <c r="U305" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -32729,7 +32829,7 @@
       <c r="S306" s="3"/>
       <c r="T306" s="3"/>
       <c r="U306" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -32755,7 +32855,7 @@
       <c r="S307" s="3"/>
       <c r="T307" s="3"/>
       <c r="U307" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -32781,7 +32881,7 @@
       <c r="S308" s="3"/>
       <c r="T308" s="3"/>
       <c r="U308" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -32807,7 +32907,7 @@
       <c r="S309" s="3"/>
       <c r="T309" s="3"/>
       <c r="U309" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -32833,7 +32933,7 @@
       <c r="S310" s="3"/>
       <c r="T310" s="3"/>
       <c r="U310" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -32859,7 +32959,7 @@
       <c r="S311" s="3"/>
       <c r="T311" s="3"/>
       <c r="U311" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -32885,7 +32985,7 @@
       <c r="S312" s="3"/>
       <c r="T312" s="3"/>
       <c r="U312" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -32911,7 +33011,7 @@
       <c r="S313" s="3"/>
       <c r="T313" s="3"/>
       <c r="U313" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -32937,7 +33037,7 @@
       <c r="S314" s="3"/>
       <c r="T314" s="3"/>
       <c r="U314" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -32963,7 +33063,7 @@
       <c r="S315" s="3"/>
       <c r="T315" s="3"/>
       <c r="U315" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -32989,7 +33089,7 @@
       <c r="S316" s="3"/>
       <c r="T316" s="3"/>
       <c r="U316" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -33015,7 +33115,7 @@
       <c r="S317" s="3"/>
       <c r="T317" s="3"/>
       <c r="U317" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -33041,7 +33141,7 @@
       <c r="S318" s="3"/>
       <c r="T318" s="3"/>
       <c r="U318" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -33067,7 +33167,7 @@
       <c r="S319" s="3"/>
       <c r="T319" s="3"/>
       <c r="U319" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -33093,7 +33193,7 @@
       <c r="S320" s="3"/>
       <c r="T320" s="3"/>
       <c r="U320" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -33119,7 +33219,7 @@
       <c r="S321" s="3"/>
       <c r="T321" s="3"/>
       <c r="U321" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -33145,7 +33245,7 @@
       <c r="S322" s="3"/>
       <c r="T322" s="3"/>
       <c r="U322" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -33171,7 +33271,7 @@
       <c r="S323" s="3"/>
       <c r="T323" s="3"/>
       <c r="U323" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -33197,7 +33297,7 @@
       <c r="S324" s="3"/>
       <c r="T324" s="3"/>
       <c r="U324" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -33223,7 +33323,7 @@
       <c r="S325" s="3"/>
       <c r="T325" s="3"/>
       <c r="U325" s="4" t="str">
-        <f t="shared" ref="U325:U388" si="39">IF(COUNTA(B325:T325)=0,"",AVERAGE(B325:T325))</f>
+        <f t="shared" ref="U325:U388" si="40">IF(COUNTA(B325:T325)=0,"",AVERAGE(B325:T325))</f>
         <v/>
       </c>
     </row>
@@ -33249,7 +33349,7 @@
       <c r="S326" s="3"/>
       <c r="T326" s="3"/>
       <c r="U326" s="4" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
     </row>
@@ -33275,7 +33375,7 @@
       <c r="S327" s="3"/>
       <c r="T327" s="3"/>
       <c r="U327" s="4" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
     </row>
@@ -33301,7 +33401,7 @@
       <c r="S328" s="3"/>
       <c r="T328" s="3"/>
       <c r="U328" s="4" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
     </row>
@@ -33327,7 +33427,7 @@
       <c r="S329" s="3"/>
       <c r="T329" s="3"/>
       <c r="U329" s="4" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
     </row>
@@ -33353,7 +33453,7 @@
       <c r="S330" s="3"/>
       <c r="T330" s="3"/>
       <c r="U330" s="4" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
     </row>
@@ -33379,7 +33479,7 @@
       <c r="S331" s="3"/>
       <c r="T331" s="3"/>
       <c r="U331" s="4" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
     </row>
@@ -33405,7 +33505,7 @@
       <c r="S332" s="3"/>
       <c r="T332" s="3"/>
       <c r="U332" s="4" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
     </row>
@@ -33431,7 +33531,7 @@
       <c r="S333" s="3"/>
       <c r="T333" s="3"/>
       <c r="U333" s="4" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
     </row>
@@ -33457,7 +33557,7 @@
       <c r="S334" s="3"/>
       <c r="T334" s="3"/>
       <c r="U334" s="4" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
     </row>
@@ -33483,7 +33583,7 @@
       <c r="S335" s="3"/>
       <c r="T335" s="3"/>
       <c r="U335" s="4" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
     </row>
@@ -33509,7 +33609,7 @@
       <c r="S336" s="3"/>
       <c r="T336" s="3"/>
       <c r="U336" s="4" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
     </row>
@@ -33535,7 +33635,7 @@
       <c r="S337" s="3"/>
       <c r="T337" s="3"/>
       <c r="U337" s="4" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
     </row>
@@ -33561,7 +33661,7 @@
       <c r="S338" s="3"/>
       <c r="T338" s="3"/>
       <c r="U338" s="4" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
     </row>
@@ -33587,7 +33687,7 @@
       <c r="S339" s="3"/>
       <c r="T339" s="3"/>
       <c r="U339" s="4" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
     </row>
@@ -33613,7 +33713,7 @@
       <c r="S340" s="3"/>
       <c r="T340" s="3"/>
       <c r="U340" s="4" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
     </row>
@@ -33639,7 +33739,7 @@
       <c r="S341" s="3"/>
       <c r="T341" s="3"/>
       <c r="U341" s="4" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
     </row>
@@ -33665,7 +33765,7 @@
       <c r="S342" s="3"/>
       <c r="T342" s="3"/>
       <c r="U342" s="4" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
     </row>
@@ -33691,7 +33791,7 @@
       <c r="S343" s="3"/>
       <c r="T343" s="3"/>
       <c r="U343" s="4" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
     </row>
@@ -33717,7 +33817,7 @@
       <c r="S344" s="3"/>
       <c r="T344" s="3"/>
       <c r="U344" s="4" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
     </row>
@@ -33743,7 +33843,7 @@
       <c r="S345" s="3"/>
       <c r="T345" s="3"/>
       <c r="U345" s="4" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
     </row>
@@ -33769,7 +33869,7 @@
       <c r="S346" s="3"/>
       <c r="T346" s="3"/>
       <c r="U346" s="4" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
     </row>
@@ -33795,7 +33895,7 @@
       <c r="S347" s="3"/>
       <c r="T347" s="3"/>
       <c r="U347" s="4" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
     </row>
@@ -33821,7 +33921,7 @@
       <c r="S348" s="3"/>
       <c r="T348" s="3"/>
       <c r="U348" s="4" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
     </row>
@@ -33847,7 +33947,7 @@
       <c r="S349" s="3"/>
       <c r="T349" s="3"/>
       <c r="U349" s="4" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
     </row>
@@ -33873,7 +33973,7 @@
       <c r="S350" s="3"/>
       <c r="T350" s="3"/>
       <c r="U350" s="4" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
     </row>
@@ -33899,7 +33999,7 @@
       <c r="S351" s="3"/>
       <c r="T351" s="3"/>
       <c r="U351" s="4" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
     </row>
@@ -33925,7 +34025,7 @@
       <c r="S352" s="3"/>
       <c r="T352" s="3"/>
       <c r="U352" s="4" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
     </row>
@@ -33951,7 +34051,7 @@
       <c r="S353" s="3"/>
       <c r="T353" s="3"/>
       <c r="U353" s="4" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
     </row>
@@ -33977,7 +34077,7 @@
       <c r="S354" s="3"/>
       <c r="T354" s="3"/>
       <c r="U354" s="4" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
     </row>
@@ -34003,7 +34103,7 @@
       <c r="S355" s="3"/>
       <c r="T355" s="3"/>
       <c r="U355" s="4" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
     </row>
@@ -34029,7 +34129,7 @@
       <c r="S356" s="3"/>
       <c r="T356" s="3"/>
       <c r="U356" s="4" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
     </row>
@@ -34055,7 +34155,7 @@
       <c r="S357" s="3"/>
       <c r="T357" s="3"/>
       <c r="U357" s="4" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
     </row>
@@ -34081,7 +34181,7 @@
       <c r="S358" s="3"/>
       <c r="T358" s="3"/>
       <c r="U358" s="4" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
     </row>
@@ -34107,7 +34207,7 @@
       <c r="S359" s="3"/>
       <c r="T359" s="3"/>
       <c r="U359" s="4" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
     </row>
@@ -34133,7 +34233,7 @@
       <c r="S360" s="3"/>
       <c r="T360" s="3"/>
       <c r="U360" s="4" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
     </row>
@@ -34159,7 +34259,7 @@
       <c r="S361" s="3"/>
       <c r="T361" s="3"/>
       <c r="U361" s="4" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
     </row>
@@ -34185,7 +34285,7 @@
       <c r="S362" s="3"/>
       <c r="T362" s="3"/>
       <c r="U362" s="4" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
     </row>
@@ -34211,7 +34311,7 @@
       <c r="S363" s="3"/>
       <c r="T363" s="3"/>
       <c r="U363" s="4" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
     </row>
@@ -34237,7 +34337,7 @@
       <c r="S364" s="3"/>
       <c r="T364" s="3"/>
       <c r="U364" s="4" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
     </row>
@@ -34263,7 +34363,7 @@
       <c r="S365" s="3"/>
       <c r="T365" s="3"/>
       <c r="U365" s="4" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
     </row>
@@ -34289,7 +34389,7 @@
       <c r="S366" s="3"/>
       <c r="T366" s="3"/>
       <c r="U366" s="4" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
     </row>
@@ -34315,7 +34415,7 @@
       <c r="S367" s="3"/>
       <c r="T367" s="3"/>
       <c r="U367" s="4" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
     </row>
@@ -34341,7 +34441,7 @@
       <c r="S368" s="3"/>
       <c r="T368" s="3"/>
       <c r="U368" s="4" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
     </row>
@@ -34367,7 +34467,7 @@
       <c r="S369" s="3"/>
       <c r="T369" s="3"/>
       <c r="U369" s="4" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
     </row>
@@ -34393,7 +34493,7 @@
       <c r="S370" s="3"/>
       <c r="T370" s="3"/>
       <c r="U370" s="4" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
     </row>
@@ -34419,7 +34519,7 @@
       <c r="S371" s="3"/>
       <c r="T371" s="3"/>
       <c r="U371" s="4" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
     </row>
@@ -34445,7 +34545,7 @@
       <c r="S372" s="3"/>
       <c r="T372" s="3"/>
       <c r="U372" s="4" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
     </row>
@@ -34471,7 +34571,7 @@
       <c r="S373" s="3"/>
       <c r="T373" s="3"/>
       <c r="U373" s="4" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
     </row>
@@ -34497,7 +34597,7 @@
       <c r="S374" s="3"/>
       <c r="T374" s="3"/>
       <c r="U374" s="4" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
     </row>
@@ -34523,7 +34623,7 @@
       <c r="S375" s="3"/>
       <c r="T375" s="3"/>
       <c r="U375" s="4" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
     </row>
@@ -34549,7 +34649,7 @@
       <c r="S376" s="3"/>
       <c r="T376" s="3"/>
       <c r="U376" s="4" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
     </row>
@@ -34575,7 +34675,7 @@
       <c r="S377" s="3"/>
       <c r="T377" s="3"/>
       <c r="U377" s="4" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
     </row>
@@ -34601,7 +34701,7 @@
       <c r="S378" s="3"/>
       <c r="T378" s="3"/>
       <c r="U378" s="4" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
     </row>
@@ -34627,7 +34727,7 @@
       <c r="S379" s="3"/>
       <c r="T379" s="3"/>
       <c r="U379" s="4" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
     </row>
@@ -34653,7 +34753,7 @@
       <c r="S380" s="3"/>
       <c r="T380" s="3"/>
       <c r="U380" s="4" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
     </row>
@@ -34679,7 +34779,7 @@
       <c r="S381" s="3"/>
       <c r="T381" s="3"/>
       <c r="U381" s="4" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
     </row>
@@ -34705,7 +34805,7 @@
       <c r="S382" s="3"/>
       <c r="T382" s="3"/>
       <c r="U382" s="4" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
     </row>
@@ -34731,7 +34831,7 @@
       <c r="S383" s="3"/>
       <c r="T383" s="3"/>
       <c r="U383" s="4" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
     </row>
@@ -34757,7 +34857,7 @@
       <c r="S384" s="3"/>
       <c r="T384" s="3"/>
       <c r="U384" s="4" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
     </row>
@@ -34783,7 +34883,7 @@
       <c r="S385" s="3"/>
       <c r="T385" s="3"/>
       <c r="U385" s="4" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
     </row>
@@ -34809,7 +34909,7 @@
       <c r="S386" s="3"/>
       <c r="T386" s="3"/>
       <c r="U386" s="4" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
     </row>
@@ -34835,7 +34935,7 @@
       <c r="S387" s="3"/>
       <c r="T387" s="3"/>
       <c r="U387" s="4" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
     </row>
@@ -34861,7 +34961,7 @@
       <c r="S388" s="3"/>
       <c r="T388" s="3"/>
       <c r="U388" s="4" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
     </row>
@@ -34887,7 +34987,7 @@
       <c r="S389" s="3"/>
       <c r="T389" s="3"/>
       <c r="U389" s="4" t="str">
-        <f t="shared" ref="U389:U390" si="40">IF(COUNTA(B389:T389)=0,"",AVERAGE(B389:T389))</f>
+        <f t="shared" ref="U389:U390" si="41">IF(COUNTA(B389:T389)=0,"",AVERAGE(B389:T389))</f>
         <v/>
       </c>
     </row>
@@ -34913,7 +35013,7 @@
       <c r="S390" s="3"/>
       <c r="T390" s="3"/>
       <c r="U390" s="4" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
     </row>
@@ -37528,19 +37628,39 @@
       </c>
     </row>
     <row r="75" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A75" s="2"/>
-      <c r="B75" s="3"/>
-      <c r="C75" s="3"/>
-      <c r="D75" s="3"/>
-      <c r="E75" s="3"/>
-      <c r="F75" s="3"/>
-      <c r="G75" s="3"/>
-      <c r="H75" s="3"/>
-      <c r="I75" s="3"/>
-      <c r="J75" s="3"/>
-      <c r="K75" s="4" t="str">
-        <f t="shared" si="34"/>
-        <v/>
+      <c r="A75" s="2">
+        <v>46231</v>
+      </c>
+      <c r="B75" s="3">
+        <v>3.1</v>
+      </c>
+      <c r="C75" s="3">
+        <v>3.14</v>
+      </c>
+      <c r="D75" s="3">
+        <v>2.8</v>
+      </c>
+      <c r="E75" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="F75" s="3">
+        <v>2.79</v>
+      </c>
+      <c r="G75" s="3">
+        <v>2.95</v>
+      </c>
+      <c r="H75" s="3">
+        <v>2.69</v>
+      </c>
+      <c r="I75" s="3">
+        <v>2.89</v>
+      </c>
+      <c r="J75" s="3">
+        <v>2.89</v>
+      </c>
+      <c r="K75" s="4">
+        <f t="shared" ref="K75" si="36">IF(COUNTA(B75:J75)=0,"",AVERAGE(B75:J75))</f>
+        <v>2.9155555555555557</v>
       </c>
     </row>
     <row r="76" spans="1:11" x14ac:dyDescent="0.25">
@@ -38467,7 +38587,7 @@
       <c r="I133" s="3"/>
       <c r="J133" s="3"/>
       <c r="K133" s="4" t="str">
-        <f t="shared" ref="K133:K196" si="36">IF(COUNTA(B133:J133)=0,"",AVERAGE(B133:J133))</f>
+        <f t="shared" ref="K133:K196" si="37">IF(COUNTA(B133:J133)=0,"",AVERAGE(B133:J133))</f>
         <v/>
       </c>
     </row>
@@ -38483,7 +38603,7 @@
       <c r="I134" s="3"/>
       <c r="J134" s="3"/>
       <c r="K134" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -38499,7 +38619,7 @@
       <c r="I135" s="3"/>
       <c r="J135" s="3"/>
       <c r="K135" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -38515,7 +38635,7 @@
       <c r="I136" s="3"/>
       <c r="J136" s="3"/>
       <c r="K136" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -38531,7 +38651,7 @@
       <c r="I137" s="3"/>
       <c r="J137" s="3"/>
       <c r="K137" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -38547,7 +38667,7 @@
       <c r="I138" s="3"/>
       <c r="J138" s="3"/>
       <c r="K138" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -38563,7 +38683,7 @@
       <c r="I139" s="3"/>
       <c r="J139" s="3"/>
       <c r="K139" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -38579,7 +38699,7 @@
       <c r="I140" s="3"/>
       <c r="J140" s="3"/>
       <c r="K140" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -38595,7 +38715,7 @@
       <c r="I141" s="3"/>
       <c r="J141" s="3"/>
       <c r="K141" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -38611,7 +38731,7 @@
       <c r="I142" s="3"/>
       <c r="J142" s="3"/>
       <c r="K142" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -38627,7 +38747,7 @@
       <c r="I143" s="3"/>
       <c r="J143" s="3"/>
       <c r="K143" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -38643,7 +38763,7 @@
       <c r="I144" s="3"/>
       <c r="J144" s="3"/>
       <c r="K144" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -38659,7 +38779,7 @@
       <c r="I145" s="3"/>
       <c r="J145" s="3"/>
       <c r="K145" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -38675,7 +38795,7 @@
       <c r="I146" s="3"/>
       <c r="J146" s="3"/>
       <c r="K146" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -38691,7 +38811,7 @@
       <c r="I147" s="3"/>
       <c r="J147" s="3"/>
       <c r="K147" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -38707,7 +38827,7 @@
       <c r="I148" s="3"/>
       <c r="J148" s="3"/>
       <c r="K148" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -38723,7 +38843,7 @@
       <c r="I149" s="3"/>
       <c r="J149" s="3"/>
       <c r="K149" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -38739,7 +38859,7 @@
       <c r="I150" s="3"/>
       <c r="J150" s="3"/>
       <c r="K150" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -38755,7 +38875,7 @@
       <c r="I151" s="3"/>
       <c r="J151" s="3"/>
       <c r="K151" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -38771,7 +38891,7 @@
       <c r="I152" s="3"/>
       <c r="J152" s="3"/>
       <c r="K152" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -38787,7 +38907,7 @@
       <c r="I153" s="3"/>
       <c r="J153" s="3"/>
       <c r="K153" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -38803,7 +38923,7 @@
       <c r="I154" s="3"/>
       <c r="J154" s="3"/>
       <c r="K154" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -38819,7 +38939,7 @@
       <c r="I155" s="3"/>
       <c r="J155" s="3"/>
       <c r="K155" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -38835,7 +38955,7 @@
       <c r="I156" s="3"/>
       <c r="J156" s="3"/>
       <c r="K156" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -38851,7 +38971,7 @@
       <c r="I157" s="3"/>
       <c r="J157" s="3"/>
       <c r="K157" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -38867,7 +38987,7 @@
       <c r="I158" s="3"/>
       <c r="J158" s="3"/>
       <c r="K158" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -38883,7 +39003,7 @@
       <c r="I159" s="3"/>
       <c r="J159" s="3"/>
       <c r="K159" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -38899,7 +39019,7 @@
       <c r="I160" s="3"/>
       <c r="J160" s="3"/>
       <c r="K160" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -38915,7 +39035,7 @@
       <c r="I161" s="3"/>
       <c r="J161" s="3"/>
       <c r="K161" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -38931,7 +39051,7 @@
       <c r="I162" s="3"/>
       <c r="J162" s="3"/>
       <c r="K162" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -38947,7 +39067,7 @@
       <c r="I163" s="3"/>
       <c r="J163" s="3"/>
       <c r="K163" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -38963,7 +39083,7 @@
       <c r="I164" s="3"/>
       <c r="J164" s="3"/>
       <c r="K164" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -38979,7 +39099,7 @@
       <c r="I165" s="3"/>
       <c r="J165" s="3"/>
       <c r="K165" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -38995,7 +39115,7 @@
       <c r="I166" s="3"/>
       <c r="J166" s="3"/>
       <c r="K166" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -39011,7 +39131,7 @@
       <c r="I167" s="3"/>
       <c r="J167" s="3"/>
       <c r="K167" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -39027,7 +39147,7 @@
       <c r="I168" s="3"/>
       <c r="J168" s="3"/>
       <c r="K168" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -39043,7 +39163,7 @@
       <c r="I169" s="3"/>
       <c r="J169" s="3"/>
       <c r="K169" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -39059,7 +39179,7 @@
       <c r="I170" s="3"/>
       <c r="J170" s="3"/>
       <c r="K170" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -39075,7 +39195,7 @@
       <c r="I171" s="3"/>
       <c r="J171" s="3"/>
       <c r="K171" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -39091,7 +39211,7 @@
       <c r="I172" s="3"/>
       <c r="J172" s="3"/>
       <c r="K172" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -39107,7 +39227,7 @@
       <c r="I173" s="3"/>
       <c r="J173" s="3"/>
       <c r="K173" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -39123,7 +39243,7 @@
       <c r="I174" s="3"/>
       <c r="J174" s="3"/>
       <c r="K174" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -39139,7 +39259,7 @@
       <c r="I175" s="3"/>
       <c r="J175" s="3"/>
       <c r="K175" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -39155,7 +39275,7 @@
       <c r="I176" s="3"/>
       <c r="J176" s="3"/>
       <c r="K176" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -39171,7 +39291,7 @@
       <c r="I177" s="3"/>
       <c r="J177" s="3"/>
       <c r="K177" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -39187,7 +39307,7 @@
       <c r="I178" s="3"/>
       <c r="J178" s="3"/>
       <c r="K178" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -39203,7 +39323,7 @@
       <c r="I179" s="3"/>
       <c r="J179" s="3"/>
       <c r="K179" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -39219,7 +39339,7 @@
       <c r="I180" s="3"/>
       <c r="J180" s="3"/>
       <c r="K180" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -39235,7 +39355,7 @@
       <c r="I181" s="3"/>
       <c r="J181" s="3"/>
       <c r="K181" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -39251,7 +39371,7 @@
       <c r="I182" s="3"/>
       <c r="J182" s="3"/>
       <c r="K182" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -39267,7 +39387,7 @@
       <c r="I183" s="3"/>
       <c r="J183" s="3"/>
       <c r="K183" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -39283,7 +39403,7 @@
       <c r="I184" s="3"/>
       <c r="J184" s="3"/>
       <c r="K184" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -39299,7 +39419,7 @@
       <c r="I185" s="3"/>
       <c r="J185" s="3"/>
       <c r="K185" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -39315,7 +39435,7 @@
       <c r="I186" s="3"/>
       <c r="J186" s="3"/>
       <c r="K186" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -39331,7 +39451,7 @@
       <c r="I187" s="3"/>
       <c r="J187" s="3"/>
       <c r="K187" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -39347,7 +39467,7 @@
       <c r="I188" s="3"/>
       <c r="J188" s="3"/>
       <c r="K188" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -39363,7 +39483,7 @@
       <c r="I189" s="3"/>
       <c r="J189" s="3"/>
       <c r="K189" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -39379,7 +39499,7 @@
       <c r="I190" s="3"/>
       <c r="J190" s="3"/>
       <c r="K190" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -39395,7 +39515,7 @@
       <c r="I191" s="3"/>
       <c r="J191" s="3"/>
       <c r="K191" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -39411,7 +39531,7 @@
       <c r="I192" s="3"/>
       <c r="J192" s="3"/>
       <c r="K192" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -39427,7 +39547,7 @@
       <c r="I193" s="3"/>
       <c r="J193" s="3"/>
       <c r="K193" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -39443,7 +39563,7 @@
       <c r="I194" s="3"/>
       <c r="J194" s="3"/>
       <c r="K194" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -39459,7 +39579,7 @@
       <c r="I195" s="3"/>
       <c r="J195" s="3"/>
       <c r="K195" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -39475,7 +39595,7 @@
       <c r="I196" s="3"/>
       <c r="J196" s="3"/>
       <c r="K196" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -39491,7 +39611,7 @@
       <c r="I197" s="3"/>
       <c r="J197" s="3"/>
       <c r="K197" s="4" t="str">
-        <f t="shared" ref="K197:K260" si="37">IF(COUNTA(B197:J197)=0,"",AVERAGE(B197:J197))</f>
+        <f t="shared" ref="K197:K260" si="38">IF(COUNTA(B197:J197)=0,"",AVERAGE(B197:J197))</f>
         <v/>
       </c>
     </row>
@@ -39507,7 +39627,7 @@
       <c r="I198" s="3"/>
       <c r="J198" s="3"/>
       <c r="K198" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -39523,7 +39643,7 @@
       <c r="I199" s="3"/>
       <c r="J199" s="3"/>
       <c r="K199" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -39539,7 +39659,7 @@
       <c r="I200" s="3"/>
       <c r="J200" s="3"/>
       <c r="K200" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -39555,7 +39675,7 @@
       <c r="I201" s="3"/>
       <c r="J201" s="3"/>
       <c r="K201" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -39571,7 +39691,7 @@
       <c r="I202" s="3"/>
       <c r="J202" s="3"/>
       <c r="K202" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -39587,7 +39707,7 @@
       <c r="I203" s="3"/>
       <c r="J203" s="3"/>
       <c r="K203" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -39603,7 +39723,7 @@
       <c r="I204" s="3"/>
       <c r="J204" s="3"/>
       <c r="K204" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -39619,7 +39739,7 @@
       <c r="I205" s="3"/>
       <c r="J205" s="3"/>
       <c r="K205" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -39635,7 +39755,7 @@
       <c r="I206" s="3"/>
       <c r="J206" s="3"/>
       <c r="K206" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -39651,7 +39771,7 @@
       <c r="I207" s="3"/>
       <c r="J207" s="3"/>
       <c r="K207" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -39667,7 +39787,7 @@
       <c r="I208" s="3"/>
       <c r="J208" s="3"/>
       <c r="K208" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -39683,7 +39803,7 @@
       <c r="I209" s="3"/>
       <c r="J209" s="3"/>
       <c r="K209" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -39699,7 +39819,7 @@
       <c r="I210" s="3"/>
       <c r="J210" s="3"/>
       <c r="K210" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -39715,7 +39835,7 @@
       <c r="I211" s="3"/>
       <c r="J211" s="3"/>
       <c r="K211" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -39731,7 +39851,7 @@
       <c r="I212" s="3"/>
       <c r="J212" s="3"/>
       <c r="K212" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -39747,7 +39867,7 @@
       <c r="I213" s="3"/>
       <c r="J213" s="3"/>
       <c r="K213" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -39763,7 +39883,7 @@
       <c r="I214" s="3"/>
       <c r="J214" s="3"/>
       <c r="K214" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -39779,7 +39899,7 @@
       <c r="I215" s="3"/>
       <c r="J215" s="3"/>
       <c r="K215" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -39795,7 +39915,7 @@
       <c r="I216" s="3"/>
       <c r="J216" s="3"/>
       <c r="K216" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -39811,7 +39931,7 @@
       <c r="I217" s="3"/>
       <c r="J217" s="3"/>
       <c r="K217" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -39827,7 +39947,7 @@
       <c r="I218" s="3"/>
       <c r="J218" s="3"/>
       <c r="K218" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -39843,7 +39963,7 @@
       <c r="I219" s="3"/>
       <c r="J219" s="3"/>
       <c r="K219" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -39859,7 +39979,7 @@
       <c r="I220" s="3"/>
       <c r="J220" s="3"/>
       <c r="K220" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -39875,7 +39995,7 @@
       <c r="I221" s="3"/>
       <c r="J221" s="3"/>
       <c r="K221" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -39891,7 +40011,7 @@
       <c r="I222" s="3"/>
       <c r="J222" s="3"/>
       <c r="K222" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -39907,7 +40027,7 @@
       <c r="I223" s="3"/>
       <c r="J223" s="3"/>
       <c r="K223" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -39923,7 +40043,7 @@
       <c r="I224" s="3"/>
       <c r="J224" s="3"/>
       <c r="K224" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -39939,7 +40059,7 @@
       <c r="I225" s="3"/>
       <c r="J225" s="3"/>
       <c r="K225" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -39955,7 +40075,7 @@
       <c r="I226" s="3"/>
       <c r="J226" s="3"/>
       <c r="K226" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -39971,7 +40091,7 @@
       <c r="I227" s="3"/>
       <c r="J227" s="3"/>
       <c r="K227" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -39987,7 +40107,7 @@
       <c r="I228" s="3"/>
       <c r="J228" s="3"/>
       <c r="K228" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -40003,7 +40123,7 @@
       <c r="I229" s="3"/>
       <c r="J229" s="3"/>
       <c r="K229" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -40019,7 +40139,7 @@
       <c r="I230" s="3"/>
       <c r="J230" s="3"/>
       <c r="K230" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -40035,7 +40155,7 @@
       <c r="I231" s="3"/>
       <c r="J231" s="3"/>
       <c r="K231" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -40051,7 +40171,7 @@
       <c r="I232" s="3"/>
       <c r="J232" s="3"/>
       <c r="K232" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -40067,7 +40187,7 @@
       <c r="I233" s="3"/>
       <c r="J233" s="3"/>
       <c r="K233" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -40083,7 +40203,7 @@
       <c r="I234" s="3"/>
       <c r="J234" s="3"/>
       <c r="K234" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -40099,7 +40219,7 @@
       <c r="I235" s="3"/>
       <c r="J235" s="3"/>
       <c r="K235" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -40115,7 +40235,7 @@
       <c r="I236" s="3"/>
       <c r="J236" s="3"/>
       <c r="K236" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -40131,7 +40251,7 @@
       <c r="I237" s="3"/>
       <c r="J237" s="3"/>
       <c r="K237" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -40147,7 +40267,7 @@
       <c r="I238" s="3"/>
       <c r="J238" s="3"/>
       <c r="K238" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -40163,7 +40283,7 @@
       <c r="I239" s="3"/>
       <c r="J239" s="3"/>
       <c r="K239" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -40179,7 +40299,7 @@
       <c r="I240" s="3"/>
       <c r="J240" s="3"/>
       <c r="K240" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -40195,7 +40315,7 @@
       <c r="I241" s="3"/>
       <c r="J241" s="3"/>
       <c r="K241" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -40211,7 +40331,7 @@
       <c r="I242" s="3"/>
       <c r="J242" s="3"/>
       <c r="K242" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -40227,7 +40347,7 @@
       <c r="I243" s="3"/>
       <c r="J243" s="3"/>
       <c r="K243" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -40243,7 +40363,7 @@
       <c r="I244" s="3"/>
       <c r="J244" s="3"/>
       <c r="K244" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -40259,7 +40379,7 @@
       <c r="I245" s="3"/>
       <c r="J245" s="3"/>
       <c r="K245" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -40275,7 +40395,7 @@
       <c r="I246" s="3"/>
       <c r="J246" s="3"/>
       <c r="K246" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -40291,7 +40411,7 @@
       <c r="I247" s="3"/>
       <c r="J247" s="3"/>
       <c r="K247" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -40307,7 +40427,7 @@
       <c r="I248" s="3"/>
       <c r="J248" s="3"/>
       <c r="K248" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -40323,7 +40443,7 @@
       <c r="I249" s="3"/>
       <c r="J249" s="3"/>
       <c r="K249" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -40339,7 +40459,7 @@
       <c r="I250" s="3"/>
       <c r="J250" s="3"/>
       <c r="K250" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -40355,7 +40475,7 @@
       <c r="I251" s="3"/>
       <c r="J251" s="3"/>
       <c r="K251" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -40371,7 +40491,7 @@
       <c r="I252" s="3"/>
       <c r="J252" s="3"/>
       <c r="K252" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -40387,7 +40507,7 @@
       <c r="I253" s="3"/>
       <c r="J253" s="3"/>
       <c r="K253" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -40403,7 +40523,7 @@
       <c r="I254" s="3"/>
       <c r="J254" s="3"/>
       <c r="K254" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -40419,7 +40539,7 @@
       <c r="I255" s="3"/>
       <c r="J255" s="3"/>
       <c r="K255" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -40435,7 +40555,7 @@
       <c r="I256" s="3"/>
       <c r="J256" s="3"/>
       <c r="K256" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -40451,7 +40571,7 @@
       <c r="I257" s="3"/>
       <c r="J257" s="3"/>
       <c r="K257" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -40467,7 +40587,7 @@
       <c r="I258" s="3"/>
       <c r="J258" s="3"/>
       <c r="K258" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -40483,7 +40603,7 @@
       <c r="I259" s="3"/>
       <c r="J259" s="3"/>
       <c r="K259" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -40499,7 +40619,7 @@
       <c r="I260" s="3"/>
       <c r="J260" s="3"/>
       <c r="K260" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -40515,7 +40635,7 @@
       <c r="I261" s="3"/>
       <c r="J261" s="3"/>
       <c r="K261" s="4" t="str">
-        <f t="shared" ref="K261:K324" si="38">IF(COUNTA(B261:J261)=0,"",AVERAGE(B261:J261))</f>
+        <f t="shared" ref="K261:K324" si="39">IF(COUNTA(B261:J261)=0,"",AVERAGE(B261:J261))</f>
         <v/>
       </c>
     </row>
@@ -40531,7 +40651,7 @@
       <c r="I262" s="3"/>
       <c r="J262" s="3"/>
       <c r="K262" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -40547,7 +40667,7 @@
       <c r="I263" s="3"/>
       <c r="J263" s="3"/>
       <c r="K263" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -40563,7 +40683,7 @@
       <c r="I264" s="3"/>
       <c r="J264" s="3"/>
       <c r="K264" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -40579,7 +40699,7 @@
       <c r="I265" s="3"/>
       <c r="J265" s="3"/>
       <c r="K265" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -40595,7 +40715,7 @@
       <c r="I266" s="3"/>
       <c r="J266" s="3"/>
       <c r="K266" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -40611,7 +40731,7 @@
       <c r="I267" s="3"/>
       <c r="J267" s="3"/>
       <c r="K267" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -40627,7 +40747,7 @@
       <c r="I268" s="3"/>
       <c r="J268" s="3"/>
       <c r="K268" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -40643,7 +40763,7 @@
       <c r="I269" s="3"/>
       <c r="J269" s="3"/>
       <c r="K269" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -40659,7 +40779,7 @@
       <c r="I270" s="3"/>
       <c r="J270" s="3"/>
       <c r="K270" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -40675,7 +40795,7 @@
       <c r="I271" s="3"/>
       <c r="J271" s="3"/>
       <c r="K271" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -40691,7 +40811,7 @@
       <c r="I272" s="3"/>
       <c r="J272" s="3"/>
       <c r="K272" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -40707,7 +40827,7 @@
       <c r="I273" s="3"/>
       <c r="J273" s="3"/>
       <c r="K273" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -40723,7 +40843,7 @@
       <c r="I274" s="3"/>
       <c r="J274" s="3"/>
       <c r="K274" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -40739,7 +40859,7 @@
       <c r="I275" s="3"/>
       <c r="J275" s="3"/>
       <c r="K275" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -40755,7 +40875,7 @@
       <c r="I276" s="3"/>
       <c r="J276" s="3"/>
       <c r="K276" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -40771,7 +40891,7 @@
       <c r="I277" s="3"/>
       <c r="J277" s="3"/>
       <c r="K277" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -40787,7 +40907,7 @@
       <c r="I278" s="3"/>
       <c r="J278" s="3"/>
       <c r="K278" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -40803,7 +40923,7 @@
       <c r="I279" s="3"/>
       <c r="J279" s="3"/>
       <c r="K279" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -40819,7 +40939,7 @@
       <c r="I280" s="3"/>
       <c r="J280" s="3"/>
       <c r="K280" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -40835,7 +40955,7 @@
       <c r="I281" s="3"/>
       <c r="J281" s="3"/>
       <c r="K281" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -40851,7 +40971,7 @@
       <c r="I282" s="3"/>
       <c r="J282" s="3"/>
       <c r="K282" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -40867,7 +40987,7 @@
       <c r="I283" s="3"/>
       <c r="J283" s="3"/>
       <c r="K283" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -40883,7 +41003,7 @@
       <c r="I284" s="3"/>
       <c r="J284" s="3"/>
       <c r="K284" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -40899,7 +41019,7 @@
       <c r="I285" s="3"/>
       <c r="J285" s="3"/>
       <c r="K285" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -40915,7 +41035,7 @@
       <c r="I286" s="3"/>
       <c r="J286" s="3"/>
       <c r="K286" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -40931,7 +41051,7 @@
       <c r="I287" s="3"/>
       <c r="J287" s="3"/>
       <c r="K287" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -40947,7 +41067,7 @@
       <c r="I288" s="3"/>
       <c r="J288" s="3"/>
       <c r="K288" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -40963,7 +41083,7 @@
       <c r="I289" s="3"/>
       <c r="J289" s="3"/>
       <c r="K289" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -40979,7 +41099,7 @@
       <c r="I290" s="3"/>
       <c r="J290" s="3"/>
       <c r="K290" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -40995,7 +41115,7 @@
       <c r="I291" s="3"/>
       <c r="J291" s="3"/>
       <c r="K291" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -41011,7 +41131,7 @@
       <c r="I292" s="3"/>
       <c r="J292" s="3"/>
       <c r="K292" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -41027,7 +41147,7 @@
       <c r="I293" s="3"/>
       <c r="J293" s="3"/>
       <c r="K293" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -41043,7 +41163,7 @@
       <c r="I294" s="3"/>
       <c r="J294" s="3"/>
       <c r="K294" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -41059,7 +41179,7 @@
       <c r="I295" s="3"/>
       <c r="J295" s="3"/>
       <c r="K295" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -41075,7 +41195,7 @@
       <c r="I296" s="3"/>
       <c r="J296" s="3"/>
       <c r="K296" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -41091,7 +41211,7 @@
       <c r="I297" s="3"/>
       <c r="J297" s="3"/>
       <c r="K297" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -41107,7 +41227,7 @@
       <c r="I298" s="3"/>
       <c r="J298" s="3"/>
       <c r="K298" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -41123,7 +41243,7 @@
       <c r="I299" s="3"/>
       <c r="J299" s="3"/>
       <c r="K299" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -41139,7 +41259,7 @@
       <c r="I300" s="3"/>
       <c r="J300" s="3"/>
       <c r="K300" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -41155,7 +41275,7 @@
       <c r="I301" s="3"/>
       <c r="J301" s="3"/>
       <c r="K301" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -41171,7 +41291,7 @@
       <c r="I302" s="3"/>
       <c r="J302" s="3"/>
       <c r="K302" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -41187,7 +41307,7 @@
       <c r="I303" s="3"/>
       <c r="J303" s="3"/>
       <c r="K303" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -41203,7 +41323,7 @@
       <c r="I304" s="3"/>
       <c r="J304" s="3"/>
       <c r="K304" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -41219,7 +41339,7 @@
       <c r="I305" s="3"/>
       <c r="J305" s="3"/>
       <c r="K305" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -41235,7 +41355,7 @@
       <c r="I306" s="3"/>
       <c r="J306" s="3"/>
       <c r="K306" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -41251,7 +41371,7 @@
       <c r="I307" s="3"/>
       <c r="J307" s="3"/>
       <c r="K307" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -41267,7 +41387,7 @@
       <c r="I308" s="3"/>
       <c r="J308" s="3"/>
       <c r="K308" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -41283,7 +41403,7 @@
       <c r="I309" s="3"/>
       <c r="J309" s="3"/>
       <c r="K309" s="4" t="str">
-        <f t="shared"